--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -3840,7 +3840,7 @@
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46182.62655407407</v>
+        <v>46188.17367040509</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>141</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -2691,7 +2691,7 @@
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="8">
-        <v>46182.62896958333</v>
+        <v>46190.51816748842</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>76</v>
@@ -4974,7 +4974,7 @@
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46184.198145</v>
+        <v>46190.51911810185</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>202</v>
@@ -5249,7 +5249,7 @@
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46182.627335625</v>
+        <v>46190.519194259265</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>218</v>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46182.62733162037</v>
+        <v>46190.51933267361</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>99</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -3875,7 +3875,7 @@
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46190.67767923611</v>
+        <v>46190.72156443287</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>142</v>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="9">
-        <v>46181.77194856481</v>
+        <v>46190.70825689815</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>200</v>
@@ -5007,9 +5007,11 @@
       <c r="B56" s="5">
         <v>46181.60908480324</v>
       </c>
-      <c r="C56" s="6"/>
+      <c r="C56" s="5">
+        <v>46190.708245752314</v>
+      </c>
       <c r="D56" s="5">
-        <v>46190.675336354165</v>
+        <v>46190.708260555555</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>203</v>
@@ -5057,10 +5059,10 @@
         <v>207</v>
       </c>
       <c r="T56" s="6">
-        <v>0</v>
-      </c>
-      <c r="U56" s="11" t="s">
-        <v>57</v>
+        <v>1</v>
+      </c>
+      <c r="U56" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
@@ -5070,9 +5072,11 @@
       <c r="B57" s="9">
         <v>46181.60908915509</v>
       </c>
-      <c r="C57" s="10"/>
+      <c r="C57" s="9">
+        <v>46190.70821236111</v>
+      </c>
       <c r="D57" s="9">
-        <v>46190.677475335644</v>
+        <v>46190.70821390046</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>209</v>
@@ -5123,9 +5127,11 @@
       <c r="B58" s="5">
         <v>46181.60909384259</v>
       </c>
-      <c r="C58" s="6"/>
+      <c r="C58" s="5">
+        <v>46190.70822138889</v>
+      </c>
       <c r="D58" s="5">
-        <v>46190.677476377314</v>
+        <v>46190.7082228125</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>212</v>
@@ -5176,9 +5182,11 @@
       <c r="B59" s="9">
         <v>46181.61221741898</v>
       </c>
-      <c r="C59" s="10"/>
+      <c r="C59" s="9">
+        <v>46190.70822601852</v>
+      </c>
       <c r="D59" s="9">
-        <v>46190.677470173614</v>
+        <v>46190.708227337964</v>
       </c>
       <c r="E59" s="10" t="s">
         <v>215</v>
@@ -5229,9 +5237,11 @@
       <c r="B60" s="5">
         <v>46181.612357199076</v>
       </c>
-      <c r="C60" s="6"/>
+      <c r="C60" s="5">
+        <v>46190.70823167824</v>
+      </c>
       <c r="D60" s="5">
-        <v>46190.677471469906</v>
+        <v>46190.708233321755</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>217</v>
@@ -5345,7 +5355,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46182.632599652774</v>
+        <v>46190.70821725695</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>209</v>
@@ -5398,7 +5408,7 @@
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46182.632596678246</v>
+        <v>46190.70822666667</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>212</v>
@@ -5449,9 +5459,11 @@
       <c r="B64" s="5">
         <v>46181.61393570602</v>
       </c>
-      <c r="C64" s="6"/>
+      <c r="C64" s="5">
+        <v>46190.70842026621</v>
+      </c>
       <c r="D64" s="5">
-        <v>46182.63259350695</v>
+        <v>46190.70842170139</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>215</v>
@@ -5502,9 +5514,11 @@
       <c r="B65" s="9">
         <v>46181.61396929398</v>
       </c>
-      <c r="C65" s="10"/>
+      <c r="C65" s="9">
+        <v>46190.70842520833</v>
+      </c>
       <c r="D65" s="9">
-        <v>46182.63259271991</v>
+        <v>46190.708426550926</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>217</v>
@@ -5720,9 +5734,11 @@
       <c r="B69" s="9">
         <v>46181.614119606485</v>
       </c>
-      <c r="C69" s="10"/>
+      <c r="C69" s="9">
+        <v>46190.72172383102</v>
+      </c>
       <c r="D69" s="9">
-        <v>46182.63268149305</v>
+        <v>46190.721725358795</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>215</v>
@@ -5771,9 +5787,11 @@
       <c r="B70" s="5">
         <v>46181.61419627315</v>
       </c>
-      <c r="C70" s="6"/>
+      <c r="C70" s="5">
+        <v>46190.72172868055</v>
+      </c>
       <c r="D70" s="5">
-        <v>46182.63267761574</v>
+        <v>46190.7217299537</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>217</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1825" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1827" uniqueCount="399">
   <si>
     <t>50001559 - FERROVIAL</t>
   </si>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46182.62624046297</v>
+        <v>46191.54541342593</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>97</v>
@@ -3061,8 +3061,8 @@
       <c r="T23" s="10">
         <v>0</v>
       </c>
-      <c r="U23" s="11" t="s">
-        <v>57</v>
+      <c r="U23" s="12" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46182.626236412034</v>
+        <v>46191.54541392361</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>103</v>
@@ -3124,8 +3124,8 @@
       <c r="T24" s="6">
         <v>0</v>
       </c>
-      <c r="U24" s="11" t="s">
-        <v>57</v>
+      <c r="U24" s="12" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46182.62623289352</v>
+        <v>46191.545413506945</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>106</v>
@@ -3187,8 +3187,8 @@
       <c r="T25" s="10">
         <v>0</v>
       </c>
-      <c r="U25" s="11" t="s">
-        <v>57</v>
+      <c r="U25" s="12" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46182.62622777778</v>
+        <v>46191.54541386574</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>109</v>
@@ -3250,8 +3250,8 @@
       <c r="T26" s="6">
         <v>0</v>
       </c>
-      <c r="U26" s="11" t="s">
-        <v>57</v>
+      <c r="U26" s="12" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="C49" s="10"/>
       <c r="D49" s="9">
-        <v>46190.70825689815</v>
+        <v>46191.542751388886</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>176</v>
@@ -4557,7 +4557,9 @@
       <c r="R49" s="10"/>
       <c r="S49" s="10"/>
       <c r="T49" s="10"/>
-      <c r="U49" s="10"/>
+      <c r="U49" s="12" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
@@ -4851,9 +4853,11 @@
       <c r="B55" s="9">
         <v>46181.609098182875</v>
       </c>
-      <c r="C55" s="10"/>
+      <c r="C55" s="9">
+        <v>46191.54272982639</v>
+      </c>
       <c r="D55" s="9">
-        <v>46190.519194259265</v>
+        <v>46191.54274247686</v>
       </c>
       <c r="E55" s="10" t="s">
         <v>195</v>
@@ -4901,9 +4905,11 @@
         <v>33</v>
       </c>
       <c r="T55" s="10">
-        <v>0</v>
-      </c>
-      <c r="U55" s="10"/>
+        <v>1</v>
+      </c>
+      <c r="U55" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
@@ -4912,9 +4918,11 @@
       <c r="B56" s="5">
         <v>46181.60910252314</v>
       </c>
-      <c r="C56" s="6"/>
+      <c r="C56" s="5">
+        <v>46191.54270648149</v>
+      </c>
       <c r="D56" s="5">
-        <v>46190.88639516204</v>
+        <v>46191.54270819444</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>185</v>
@@ -4965,9 +4973,11 @@
       <c r="B57" s="9">
         <v>46181.609107951386</v>
       </c>
-      <c r="C57" s="10"/>
+      <c r="C57" s="9">
+        <v>46191.542715625</v>
+      </c>
       <c r="D57" s="9">
-        <v>46190.886395497684</v>
+        <v>46191.54271703704</v>
       </c>
       <c r="E57" s="10" t="s">
         <v>188</v>
@@ -5128,9 +5138,11 @@
       <c r="B60" s="5">
         <v>46181.60911329861</v>
       </c>
-      <c r="C60" s="6"/>
+      <c r="C60" s="5">
+        <v>46191.54538693287</v>
+      </c>
       <c r="D60" s="5">
-        <v>46190.51933267361</v>
+        <v>46191.54539826389</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>100</v>
@@ -5178,10 +5190,10 @@
         <v>33</v>
       </c>
       <c r="T60" s="6">
-        <v>0</v>
-      </c>
-      <c r="U60" s="11" t="s">
-        <v>57</v>
+        <v>1</v>
+      </c>
+      <c r="U60" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -5191,9 +5203,11 @@
       <c r="B61" s="9">
         <v>46181.60912350695</v>
       </c>
-      <c r="C61" s="10"/>
+      <c r="C61" s="9">
+        <v>46191.54535901621</v>
+      </c>
       <c r="D61" s="9">
-        <v>46182.63268751158</v>
+        <v>46191.54536050926</v>
       </c>
       <c r="E61" s="10" t="s">
         <v>185</v>
@@ -5242,9 +5256,11 @@
       <c r="B62" s="5">
         <v>46181.60912782408</v>
       </c>
-      <c r="C62" s="6"/>
+      <c r="C62" s="5">
+        <v>46191.54537241899</v>
+      </c>
       <c r="D62" s="5">
-        <v>46182.63268435185</v>
+        <v>46191.54537386574</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>188</v>
@@ -6433,7 +6449,7 @@
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46182.64085189815</v>
+        <v>46191.54540523148</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>185</v>
@@ -6486,7 +6502,7 @@
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46182.640848043986</v>
+        <v>46191.54540574074</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>185</v>
@@ -6761,7 +6777,7 @@
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46182.64097625</v>
+        <v>46191.545403842596</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>185</v>
@@ -6814,7 +6830,7 @@
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46182.64097288194</v>
+        <v>46191.545404212964</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>185</v>
@@ -7667,7 +7683,7 @@
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46182.641305937505</v>
+        <v>46191.54539792824</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>185</v>
@@ -7836,7 +7852,7 @@
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46182.64140736111</v>
+        <v>46191.54540628473</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>185</v>
@@ -8005,7 +8021,7 @@
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46182.64151996528</v>
+        <v>46191.54540483796</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>185</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1827" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1815" uniqueCount="394">
   <si>
     <t>50001559 - FERROVIAL</t>
   </si>
@@ -247,7 +247,10 @@
     <t>Ingenieria Jefe de proyecto:</t>
   </si>
   <si>
-    <t>Analisis de costeo,Ingenieria basica Rodete,Ingenieria Detalle,Ingenieria Basica Motor</t>
+    <t>Ingenieria basica Rodete,Ingenieria Detalle,Ingenieria Basica Motor</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1215506984569012</t>
@@ -259,7 +262,7 @@
     <t>MOTOR DE STOCK WEG - 02 POLOS - IE3 FRAME 280</t>
   </si>
   <si>
-    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta motor  ot 4347</t>
+    <t>Ingenieria Jefe de proyecto:,propuesta motor  ot 4347</t>
   </si>
   <si>
     <t>1215506984569034</t>
@@ -277,7 +280,7 @@
 </t>
   </si>
   <si>
-    <t>Analisis de costeo,propuesta alabes  ot 4347,propuesta nucleo rodete  ot 4347,Ingenieria Jefe de proyecto:</t>
+    <t>propuesta alabes  ot 4347,propuesta nucleo rodete  ot 4347,Ingenieria Jefe de proyecto:</t>
   </si>
   <si>
     <t>1215506781549472</t>
@@ -286,22 +289,7 @@
     <t>Ingenieria Detalle</t>
   </si>
   <si>
-    <t>OT 4350 - CODO 135° Ø1600MM,OT 4351 - DUCTO Ø1600MM L:1800MM,Analisis de costeo,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4349- CODO 90° Ø1600MM,Ingenieria Jefe de proyecto:</t>
-  </si>
-  <si>
-    <t>1215506638851079</t>
-  </si>
-  <si>
-    <t>Analisis de costeo</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle,Ingenieria Basica Motor,Ingenieria basica Rodete</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,Costos</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
+    <t>OT 4350 - CODO 135° Ø1600MM,OT 4351 - DUCTO Ø1600MM L:1800MM,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4349- CODO 90° Ø1600MM,Ingenieria Jefe de proyecto:</t>
   </si>
   <si>
     <t>1215504785833005</t>
@@ -310,7 +298,7 @@
     <t>Propuesta compras:</t>
   </si>
   <si>
-    <t>propuesta alabes  ot 4347,propuesta motor  ot 4347,propuesta nucleo rodete  ot 4347,propuesta Corte Laser</t>
+    <t>propuesta alabes  ot 4347,propuesta motor  ot 4347,propuesta nucleo rodete  ot 4347,propuesta Corte Laser ot 4347</t>
   </si>
   <si>
     <t>1215506984585999</t>
@@ -319,7 +307,7 @@
     <t>propuesta motor  ot 4347</t>
   </si>
   <si>
-    <t>Propuesta compras:,Reserva motor</t>
+    <t>Propuesta compras:,Reserva motor ot 4347</t>
   </si>
   <si>
     <t>1215506984586021</t>
@@ -328,7 +316,7 @@
     <t>propuesta alabes  ot 4347</t>
   </si>
   <si>
-    <t>Propuesta compras:,Reserva alabe</t>
+    <t>Propuesta compras:,Reserva alabe ot 4347</t>
   </si>
   <si>
     <t>1215506638889337</t>
@@ -340,13 +328,13 @@
     <t>benjamin.bustos@zitron.com</t>
   </si>
   <si>
-    <t>Propuesta compras:,Reserva rodete</t>
+    <t>Propuesta compras:,Reserva rodete ot 4347</t>
   </si>
   <si>
     <t>1215506984624474</t>
   </si>
   <si>
-    <t>propuesta Corte Laser</t>
+    <t>propuesta Corte Laser ot 4347</t>
   </si>
   <si>
     <t>hugo isla martinez</t>
@@ -364,7 +352,7 @@
     <t>1215506984624491</t>
   </si>
   <si>
-    <t xml:space="preserve">Propuesta Corte plasma </t>
+    <t>Propuesta Corte plasma  ot 4347</t>
   </si>
   <si>
     <t xml:space="preserve">Generación OC Corte Plasma  ot 4342 -4344 </t>
@@ -373,7 +361,7 @@
     <t>1215506992580924</t>
   </si>
   <si>
-    <t>Propuesta Mecanizado</t>
+    <t>Propuesta Mecanizado ot 4347</t>
   </si>
   <si>
     <t>Generación OC Mecanizado ot 4342 -4344</t>
@@ -382,7 +370,7 @@
     <t>1215506992580936</t>
   </si>
   <si>
-    <t xml:space="preserve">Propuesta Fabricación externa </t>
+    <t xml:space="preserve">Propuesta Fabricación externa ot 4347 </t>
   </si>
   <si>
     <t>Generacion OC Fabricación Externa ot 4342 -4344</t>
@@ -406,19 +394,19 @@
     <t>1215789383150150</t>
   </si>
   <si>
-    <t>Reserva motor</t>
+    <t>Reserva motor ot 4347</t>
   </si>
   <si>
     <t>1215789383150151</t>
   </si>
   <si>
-    <t>Reserva alabe</t>
+    <t>Reserva alabe ot 4347</t>
   </si>
   <si>
     <t>1215789383150152</t>
   </si>
   <si>
-    <t>Reserva rodete</t>
+    <t>Reserva rodete ot 4347</t>
   </si>
   <si>
     <t>1215504785833007</t>
@@ -664,7 +652,7 @@
     <t>1215506819701527</t>
   </si>
   <si>
-    <t>Propuesta Corte plasma ,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Propuesta Mecanizado,Propuesta Fabricación externa ,propuesta Corte Laser,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
+    <t>Propuesta Corte plasma  ot 4347,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Propuesta Mecanizado ot 4347,Propuesta Fabricación externa ot 4347 ,propuesta Corte Laser ot 4347,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
   </si>
   <si>
     <t>1215506781840190</t>
@@ -1223,9 +1211,6 @@
   </si>
   <si>
     <t>Costos</t>
-  </si>
-  <si>
-    <t>Despacho,Analisis de costeo</t>
   </si>
   <si>
     <t>1215506993311036</t>
@@ -1773,7 +1758,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U157"/>
+  <dimension ref="A1:U156"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -2466,7 +2451,7 @@
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46190.677476805555</v>
+        <v>46191.67894028935</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>65</v>
@@ -2502,11 +2487,13 @@
       <c r="R14" s="6"/>
       <c r="S14" s="6"/>
       <c r="T14" s="6"/>
-      <c r="U14" s="6"/>
+      <c r="U14" s="12" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B15" s="9">
         <v>46181.60883864583</v>
@@ -2515,10 +2502,10 @@
         <v>46190.67744403935</v>
       </c>
       <c r="D15" s="9">
-        <v>46190.67746287037</v>
+        <v>46191.67892994213</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>26</v>
@@ -2539,7 +2526,7 @@
         <v>26</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M15" s="10" t="s">
         <v>26</v>
@@ -2551,7 +2538,7 @@
         <v>37</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q15" s="9">
         <v>46162</v>
@@ -2571,7 +2558,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B16" s="5">
         <v>46181.60884395833</v>
@@ -2580,10 +2567,10 @@
         <v>46190.67745200232</v>
       </c>
       <c r="D16" s="5">
-        <v>46190.677479039354</v>
+        <v>46191.67892980324</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
@@ -2604,7 +2591,7 @@
         <v>26</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M16" s="6" t="s">
         <v>26</v>
@@ -2616,7 +2603,7 @@
         <v>37</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q16" s="5">
         <v>46162</v>
@@ -2636,7 +2623,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B17" s="9">
         <v>46181.608850046294</v>
@@ -2645,10 +2632,10 @@
         <v>46190.67745870371</v>
       </c>
       <c r="D17" s="9">
-        <v>46190.677484375</v>
+        <v>46191.67892980324</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>26</v>
@@ -2681,7 +2668,7 @@
         <v>37</v>
       </c>
       <c r="P17" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q17" s="9">
         <v>46162</v>
@@ -2701,33 +2688,27 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B18" s="5">
-        <v>46181.60885618055</v>
+        <v>46181.60864670139</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46190.67748425926</v>
+        <v>46190.67771045139</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I18" s="5">
-        <v>46162</v>
-      </c>
-      <c r="J18" s="5">
-        <v>46171</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
       <c r="K18" s="6" t="s">
         <v>26</v>
       </c>
@@ -2735,95 +2716,103 @@
         <v>26</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q18" s="5">
-        <v>46162</v>
-      </c>
-      <c r="R18" s="5">
-        <v>46171</v>
-      </c>
-      <c r="S18" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T18" s="6">
-        <v>0</v>
-      </c>
-      <c r="U18" s="12" t="s">
-        <v>82</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q18" s="6"/>
+      <c r="R18" s="6"/>
+      <c r="S18" s="6"/>
+      <c r="T18" s="6"/>
+      <c r="U18" s="6"/>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B19" s="9">
+        <v>46181.608864236114</v>
+      </c>
+      <c r="C19" s="9">
+        <v>46190.677672986116</v>
+      </c>
+      <c r="D19" s="9">
+        <v>46190.88639424769</v>
+      </c>
+      <c r="E19" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="B19" s="9">
-        <v>46181.60864670139</v>
-      </c>
-      <c r="C19" s="10"/>
-      <c r="D19" s="9">
-        <v>46190.67771045139</v>
-      </c>
-      <c r="E19" s="10" t="s">
+      <c r="F19" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I19" s="9">
+        <v>46167</v>
+      </c>
+      <c r="J19" s="9">
+        <v>46168</v>
+      </c>
+      <c r="K19" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L19" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M19" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N19" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="O19" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="P19" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="F19" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L19" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M19" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="N19" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O19" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="P19" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q19" s="10"/>
-      <c r="R19" s="10"/>
-      <c r="S19" s="10"/>
-      <c r="T19" s="10"/>
-      <c r="U19" s="10"/>
+      <c r="Q19" s="9">
+        <v>46167</v>
+      </c>
+      <c r="R19" s="9">
+        <v>46168</v>
+      </c>
+      <c r="S19" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T19" s="10">
+        <v>1</v>
+      </c>
+      <c r="U19" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B20" s="5">
+        <v>46181.60886979167</v>
+      </c>
+      <c r="C20" s="5">
+        <v>46190.677678657405</v>
+      </c>
+      <c r="D20" s="5">
+        <v>46190.88638454861</v>
+      </c>
+      <c r="E20" s="6" t="s">
         <v>86</v>
-      </c>
-      <c r="B20" s="5">
-        <v>46181.608864236114</v>
-      </c>
-      <c r="C20" s="5">
-        <v>46190.677672986116</v>
-      </c>
-      <c r="D20" s="5">
-        <v>46190.88639424769</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>87</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2835,10 +2824,10 @@
         <v>31</v>
       </c>
       <c r="I20" s="5">
-        <v>46167</v>
+        <v>46174</v>
       </c>
       <c r="J20" s="5">
-        <v>46168</v>
+        <v>46175</v>
       </c>
       <c r="K20" s="6" t="s">
         <v>26</v>
@@ -2850,19 +2839,19 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Q20" s="5">
-        <v>46167</v>
+        <v>46174</v>
       </c>
       <c r="R20" s="5">
-        <v>46168</v>
+        <v>46175</v>
       </c>
       <c r="S20" s="7" t="s">
         <v>33</v>
@@ -2876,28 +2865,26 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B21" s="9">
+        <v>46181.60887520833</v>
+      </c>
+      <c r="C21" s="10"/>
+      <c r="D21" s="9">
+        <v>46190.886384502315</v>
+      </c>
+      <c r="E21" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="B21" s="9">
-        <v>46181.60886979167</v>
-      </c>
-      <c r="C21" s="9">
-        <v>46190.677678657405</v>
-      </c>
-      <c r="D21" s="9">
-        <v>46190.88638454861</v>
-      </c>
-      <c r="E21" s="10" t="s">
+      <c r="F21" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="F21" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>30</v>
-      </c>
       <c r="H21" s="10" t="s">
-        <v>31</v>
+        <v>90</v>
       </c>
       <c r="I21" s="9">
         <v>46174</v>
@@ -2915,10 +2902,10 @@
         <v>26</v>
       </c>
       <c r="N21" s="10" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P21" s="10" t="s">
         <v>91</v>
@@ -2944,11 +2931,11 @@
         <v>92</v>
       </c>
       <c r="B22" s="5">
-        <v>46181.60887520833</v>
+        <v>46181.60888054398</v>
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="5">
-        <v>46190.886384502315</v>
+        <v>46191.67365563658</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>93</v>
@@ -2960,13 +2947,13 @@
         <v>94</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I22" s="5">
-        <v>46174</v>
+        <v>46248</v>
       </c>
       <c r="J22" s="5">
-        <v>46175</v>
+        <v>46251</v>
       </c>
       <c r="K22" s="6" t="s">
         <v>26</v>
@@ -2978,52 +2965,52 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q22" s="5">
-        <v>46174</v>
+        <v>46248</v>
       </c>
       <c r="R22" s="5">
-        <v>46175</v>
+        <v>46251</v>
       </c>
       <c r="S22" s="7" t="s">
         <v>33</v>
       </c>
       <c r="T22" s="6">
-        <v>1</v>
-      </c>
-      <c r="U22" s="7" t="s">
-        <v>27</v>
+        <v>0</v>
+      </c>
+      <c r="U22" s="12" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B23" s="9">
-        <v>46181.60888054398</v>
+        <v>46181.60888559028</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46191.54541342593</v>
+        <v>46191.67366451389</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="I23" s="9">
         <v>46248</v>
@@ -3041,13 +3028,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="10" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="O23" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="P23" s="10" t="s">
         <v>100</v>
-      </c>
-      <c r="P23" s="10" t="s">
-        <v>101</v>
       </c>
       <c r="Q23" s="9">
         <v>46248</v>
@@ -3062,31 +3049,31 @@
         <v>0</v>
       </c>
       <c r="U23" s="12" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B24" s="5">
-        <v>46181.60888559028</v>
+        <v>46181.60888961806</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46191.54541392361</v>
+        <v>46191.67367153935</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="I24" s="5">
         <v>46248</v>
@@ -3104,13 +3091,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Q24" s="5">
         <v>46248</v>
@@ -3125,31 +3112,31 @@
         <v>0</v>
       </c>
       <c r="U24" s="12" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B25" s="9">
-        <v>46181.60888961806</v>
+        <v>46181.6088934375</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="9">
-        <v>46191.545413506945</v>
+        <v>46191.67370431713</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="I25" s="9">
         <v>46248</v>
@@ -3167,13 +3154,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q25" s="9">
         <v>46248</v>
@@ -3188,103 +3175,97 @@
         <v>0</v>
       </c>
       <c r="U25" s="12" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B26" s="5">
+        <v>46181.608897638886</v>
+      </c>
+      <c r="C26" s="5">
+        <v>46190.67785231481</v>
+      </c>
+      <c r="D26" s="5">
+        <v>46190.67787061342</v>
+      </c>
+      <c r="E26" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="B26" s="5">
-        <v>46181.6088934375</v>
-      </c>
-      <c r="C26" s="6"/>
-      <c r="D26" s="5">
-        <v>46191.54541386574</v>
-      </c>
-      <c r="E26" s="6" t="s">
+      <c r="F26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="I26" s="5">
+        <v>46168</v>
+      </c>
+      <c r="J26" s="5">
+        <v>46169</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N26" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="O26" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="P26" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="F26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="I26" s="5">
-        <v>46248</v>
-      </c>
-      <c r="J26" s="5">
-        <v>46251</v>
-      </c>
-      <c r="K26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N26" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="O26" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="P26" s="6" t="s">
-        <v>110</v>
-      </c>
       <c r="Q26" s="5">
-        <v>46248</v>
+        <v>46168</v>
       </c>
       <c r="R26" s="5">
-        <v>46251</v>
+        <v>46169</v>
       </c>
       <c r="S26" s="7" t="s">
         <v>33</v>
       </c>
       <c r="T26" s="6">
-        <v>0</v>
-      </c>
-      <c r="U26" s="12" t="s">
-        <v>82</v>
+        <v>1</v>
+      </c>
+      <c r="U26" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B27" s="9">
+        <v>46190.88204489583</v>
+      </c>
+      <c r="C27" s="10"/>
+      <c r="D27" s="9">
+        <v>46190.88358329861</v>
+      </c>
+      <c r="E27" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="B27" s="9">
-        <v>46181.608897638886</v>
-      </c>
-      <c r="C27" s="9">
-        <v>46190.67785231481</v>
-      </c>
-      <c r="D27" s="9">
-        <v>46190.67787061342</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>112</v>
-      </c>
       <c r="F27" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I27" s="9">
-        <v>46168</v>
-      </c>
-      <c r="J27" s="9">
-        <v>46169</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
       <c r="K27" s="10" t="s">
         <v>26</v>
       </c>
@@ -3292,56 +3273,52 @@
         <v>26</v>
       </c>
       <c r="M27" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>84</v>
+        <v>26</v>
       </c>
       <c r="O27" s="10" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q27" s="9">
-        <v>46168</v>
-      </c>
-      <c r="R27" s="9">
-        <v>46169</v>
-      </c>
-      <c r="S27" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T27" s="10">
-        <v>1</v>
-      </c>
-      <c r="U27" s="7" t="s">
-        <v>27</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q27" s="10"/>
+      <c r="R27" s="10"/>
+      <c r="S27" s="10"/>
+      <c r="T27" s="10"/>
+      <c r="U27" s="10"/>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B28" s="5">
-        <v>46190.88204489583</v>
+        <v>46190.88321909722</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46190.88358329861</v>
+        <v>46191.67371679399</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
+        <v>90</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="I28" s="5">
+        <v>46169</v>
+      </c>
+      <c r="J28" s="5">
+        <v>46175</v>
+      </c>
       <c r="K28" s="6" t="s">
         <v>26</v>
       </c>
@@ -3349,51 +3326,61 @@
         <v>26</v>
       </c>
       <c r="M28" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N28" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="O28" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="P28" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q28" s="5">
+        <v>46169</v>
+      </c>
+      <c r="R28" s="5">
+        <v>46175</v>
+      </c>
+      <c r="S28" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T28" s="6">
         <v>0</v>
       </c>
-      <c r="N28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="P28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="6"/>
-      <c r="S28" s="6"/>
-      <c r="T28" s="6"/>
-      <c r="U28" s="6"/>
+      <c r="U28" s="12" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B29" s="9">
-        <v>46190.88321909722</v>
+        <v>46190.88327185185</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="9">
-        <v>46190.88627418982</v>
+        <v>46191.6737259838</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I29" s="9">
-        <v>46169</v>
+        <v>46176</v>
       </c>
       <c r="J29" s="9">
-        <v>46175</v>
+        <v>46182</v>
       </c>
       <c r="K29" s="10" t="s">
         <v>26</v>
@@ -3405,19 +3392,19 @@
         <v>26</v>
       </c>
       <c r="N29" s="10" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="Q29" s="9">
-        <v>46169</v>
+        <v>46176</v>
       </c>
       <c r="R29" s="9">
-        <v>46175</v>
+        <v>46182</v>
       </c>
       <c r="S29" s="7" t="s">
         <v>33</v>
@@ -3426,31 +3413,31 @@
         <v>0</v>
       </c>
       <c r="U29" s="12" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B30" s="5">
-        <v>46190.88327185185</v>
+        <v>46190.88332659722</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46190.88627429398</v>
+        <v>46191.67374731481</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I30" s="5">
         <v>46176</v>
@@ -3468,10 +3455,10 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>26</v>
@@ -3488,39 +3475,33 @@
       <c r="T30" s="6">
         <v>0</v>
       </c>
-      <c r="U30" s="12" t="s">
-        <v>82</v>
+      <c r="U30" s="11" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B31" s="9">
-        <v>46190.88332659722</v>
+        <v>46181.608652256946</v>
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46190.88612969907</v>
+        <v>46190.886375057875</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="I31" s="9">
-        <v>46176</v>
-      </c>
-      <c r="J31" s="9">
-        <v>46182</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10"/>
+      <c r="J31" s="10"/>
       <c r="K31" s="10" t="s">
         <v>26</v>
       </c>
@@ -3528,56 +3509,52 @@
         <v>26</v>
       </c>
       <c r="M31" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>115</v>
+        <v>26</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="P31" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="Q31" s="9">
-        <v>46176</v>
-      </c>
-      <c r="R31" s="9">
-        <v>46182</v>
-      </c>
-      <c r="S31" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T31" s="10">
-        <v>0</v>
-      </c>
-      <c r="U31" s="11" t="s">
-        <v>57</v>
-      </c>
+      <c r="Q31" s="10"/>
+      <c r="R31" s="10"/>
+      <c r="S31" s="10"/>
+      <c r="T31" s="10"/>
+      <c r="U31" s="10"/>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B32" s="5">
-        <v>46181.608652256946</v>
+        <v>46181.60900793981</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46190.886375057875</v>
+        <v>46182.62666353009</v>
       </c>
       <c r="E32" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="F32" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="6"/>
+      <c r="H32" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="I32" s="5">
+        <v>46170</v>
+      </c>
+      <c r="J32" s="5">
+        <v>46225</v>
+      </c>
       <c r="K32" s="6" t="s">
         <v>26</v>
       </c>
@@ -3585,51 +3562,61 @@
         <v>26</v>
       </c>
       <c r="M32" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N32" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="O32" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="P32" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q32" s="5">
+        <v>46170</v>
+      </c>
+      <c r="R32" s="5">
+        <v>46225</v>
+      </c>
+      <c r="S32" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T32" s="6">
         <v>0</v>
       </c>
-      <c r="N32" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O32" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="P32" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q32" s="6"/>
-      <c r="R32" s="6"/>
-      <c r="S32" s="6"/>
-      <c r="T32" s="6"/>
-      <c r="U32" s="6"/>
+      <c r="U32" s="11" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B33" s="9">
-        <v>46181.60900793981</v>
+        <v>46181.60901165509</v>
       </c>
       <c r="C33" s="10"/>
       <c r="D33" s="9">
-        <v>46182.62666353009</v>
+        <v>46190.67786118056</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="I33" s="9">
         <v>46170</v>
       </c>
       <c r="J33" s="9">
-        <v>46225</v>
+        <v>46176</v>
       </c>
       <c r="K33" s="10" t="s">
         <v>26</v>
@@ -3641,58 +3628,48 @@
         <v>26</v>
       </c>
       <c r="N33" s="10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q33" s="9">
-        <v>46170</v>
-      </c>
-      <c r="R33" s="9">
-        <v>46225</v>
-      </c>
-      <c r="S33" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T33" s="10">
-        <v>0</v>
-      </c>
-      <c r="U33" s="11" t="s">
-        <v>57</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="Q33" s="10"/>
+      <c r="R33" s="10"/>
+      <c r="S33" s="10"/>
+      <c r="T33" s="10"/>
+      <c r="U33" s="10"/>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B34" s="5">
-        <v>46181.60901165509</v>
+        <v>46181.60901612269</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46190.67786118056</v>
+        <v>46182.626637905094</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="I34" s="5">
-        <v>46170</v>
+        <v>46177</v>
       </c>
       <c r="J34" s="5">
-        <v>46176</v>
+        <v>46225</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>26</v>
@@ -3704,13 +3681,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3720,32 +3697,32 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B35" s="9">
-        <v>46181.60901612269</v>
+        <v>46181.60902011574</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="9">
-        <v>46182.626637905094</v>
+        <v>46182.6267959838</v>
       </c>
       <c r="E35" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="H35" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="F35" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G35" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>128</v>
-      </c>
       <c r="I35" s="9">
-        <v>46177</v>
+        <v>46252</v>
       </c>
       <c r="J35" s="9">
-        <v>46225</v>
+        <v>46262</v>
       </c>
       <c r="K35" s="10" t="s">
         <v>26</v>
@@ -3757,48 +3734,58 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q35" s="10"/>
-      <c r="R35" s="10"/>
-      <c r="S35" s="10"/>
-      <c r="T35" s="10"/>
-      <c r="U35" s="10"/>
+        <v>119</v>
+      </c>
+      <c r="Q35" s="9">
+        <v>46252</v>
+      </c>
+      <c r="R35" s="9">
+        <v>46262</v>
+      </c>
+      <c r="S35" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T35" s="10">
+        <v>0</v>
+      </c>
+      <c r="U35" s="11" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>135</v>
       </c>
       <c r="B36" s="5">
-        <v>46181.60902011574</v>
+        <v>46181.60902488426</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46182.6267959838</v>
+        <v>46182.62676782407</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="I36" s="5">
         <v>46252</v>
       </c>
       <c r="J36" s="5">
-        <v>46262</v>
+        <v>46253</v>
       </c>
       <c r="K36" s="6" t="s">
         <v>26</v>
@@ -3810,20 +3797,16 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>138</v>
+        <v>93</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q36" s="5">
-        <v>46252</v>
-      </c>
-      <c r="R36" s="5">
-        <v>46262</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="Q36" s="6"/>
+      <c r="R36" s="6"/>
       <c r="S36" s="7" t="s">
         <v>33</v>
       </c>
@@ -3836,50 +3819,50 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B37" s="9">
-        <v>46181.60902488426</v>
+        <v>46181.609029803236</v>
       </c>
       <c r="C37" s="10"/>
       <c r="D37" s="9">
-        <v>46182.62676782407</v>
+        <v>46182.6267641088</v>
       </c>
       <c r="E37" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="H37" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="I37" s="9">
+        <v>46254</v>
+      </c>
+      <c r="J37" s="9">
+        <v>46262</v>
+      </c>
+      <c r="K37" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L37" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M37" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N37" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="O37" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="P37" s="10" t="s">
         <v>140</v>
-      </c>
-      <c r="F37" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G37" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="I37" s="9">
-        <v>46252</v>
-      </c>
-      <c r="J37" s="9">
-        <v>46253</v>
-      </c>
-      <c r="K37" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L37" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M37" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N37" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="O37" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="P37" s="10" t="s">
-        <v>141</v>
       </c>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -3895,29 +3878,29 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46181.609029803236</v>
+        <v>46181.60903511574</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46182.6267641088</v>
+        <v>46182.626906840276</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="I38" s="5">
-        <v>46254</v>
+        <v>46252</v>
       </c>
       <c r="J38" s="5">
         <v>46262</v>
@@ -3932,16 +3915,20 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q38" s="6"/>
-      <c r="R38" s="6"/>
+        <v>26</v>
+      </c>
+      <c r="Q38" s="5">
+        <v>46252</v>
+      </c>
+      <c r="R38" s="5">
+        <v>46262</v>
+      </c>
       <c r="S38" s="7" t="s">
         <v>33</v>
       </c>
@@ -3954,32 +3941,32 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B39" s="9">
-        <v>46181.60903511574</v>
+        <v>46181.60903861111</v>
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46182.626906840276</v>
+        <v>46182.626871608794</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>146</v>
+        <v>100</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="I39" s="9">
         <v>46252</v>
       </c>
       <c r="J39" s="9">
-        <v>46262</v>
+        <v>46253</v>
       </c>
       <c r="K39" s="10" t="s">
         <v>26</v>
@@ -3991,58 +3978,48 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>147</v>
+        <v>99</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q39" s="9">
-        <v>46252</v>
-      </c>
-      <c r="R39" s="9">
-        <v>46262</v>
-      </c>
-      <c r="S39" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T39" s="10">
-        <v>0</v>
-      </c>
-      <c r="U39" s="11" t="s">
-        <v>57</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="Q39" s="10"/>
+      <c r="R39" s="10"/>
+      <c r="S39" s="10"/>
+      <c r="T39" s="10"/>
+      <c r="U39" s="10"/>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B40" s="5">
-        <v>46181.60903861111</v>
+        <v>46181.609042951386</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46182.626871608794</v>
+        <v>46182.626868680556</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>104</v>
+        <v>147</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="I40" s="5">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="J40" s="5">
-        <v>46253</v>
+        <v>46262</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>26</v>
@@ -4054,13 +4031,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4070,32 +4047,32 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B41" s="9">
-        <v>46181.609042951386</v>
+        <v>46181.609047164355</v>
       </c>
       <c r="C41" s="10"/>
       <c r="D41" s="9">
-        <v>46182.626868680556</v>
+        <v>46183.70162199074</v>
       </c>
       <c r="E41" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G41" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="F41" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G41" s="10" t="s">
-        <v>136</v>
-      </c>
       <c r="H41" s="10" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="I41" s="9">
-        <v>46254</v>
+        <v>46252</v>
       </c>
       <c r="J41" s="9">
-        <v>46262</v>
+        <v>46290</v>
       </c>
       <c r="K41" s="10" t="s">
         <v>26</v>
@@ -4107,48 +4084,58 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>146</v>
+        <v>119</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>104</v>
+        <v>153</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="Q41" s="10"/>
-      <c r="R41" s="10"/>
-      <c r="S41" s="10"/>
-      <c r="T41" s="10"/>
-      <c r="U41" s="10"/>
+        <v>26</v>
+      </c>
+      <c r="Q41" s="9">
+        <v>46283</v>
+      </c>
+      <c r="R41" s="9">
+        <v>46290</v>
+      </c>
+      <c r="S41" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T41" s="10">
+        <v>0</v>
+      </c>
+      <c r="U41" s="11" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B42" s="5">
-        <v>46181.609047164355</v>
+        <v>46181.60905075232</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46183.70162199074</v>
+        <v>46182.62705136574</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>154</v>
+        <v>106</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="I42" s="5">
         <v>46252</v>
       </c>
       <c r="J42" s="5">
-        <v>46290</v>
+        <v>46260</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>26</v>
@@ -4160,58 +4147,48 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>157</v>
+        <v>105</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q42" s="5">
-        <v>46283</v>
-      </c>
-      <c r="R42" s="5">
-        <v>46290</v>
-      </c>
-      <c r="S42" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T42" s="6">
-        <v>0</v>
-      </c>
-      <c r="U42" s="11" t="s">
-        <v>57</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="Q42" s="6"/>
+      <c r="R42" s="6"/>
+      <c r="S42" s="6"/>
+      <c r="T42" s="6"/>
+      <c r="U42" s="6"/>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B43" s="9">
-        <v>46181.60905075232</v>
+        <v>46181.60905546296</v>
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46182.62705136574</v>
+        <v>46183.70547770833</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>110</v>
+        <v>157</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="I43" s="9">
-        <v>46252</v>
+        <v>46261</v>
       </c>
       <c r="J43" s="9">
-        <v>46260</v>
+        <v>46289</v>
       </c>
       <c r="K43" s="10" t="s">
         <v>26</v>
@@ -4223,13 +4200,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -4239,32 +4216,32 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B44" s="5">
-        <v>46181.60905546296</v>
+        <v>46181.60906018519</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46183.70547770833</v>
+        <v>46182.62707423611</v>
       </c>
       <c r="E44" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G44" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="F44" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>155</v>
-      </c>
       <c r="H44" s="6" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="I44" s="5">
-        <v>46261</v>
+        <v>46290</v>
       </c>
       <c r="J44" s="5">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="K44" s="6" t="s">
         <v>26</v>
@@ -4276,13 +4253,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>110</v>
+        <v>157</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>162</v>
+        <v>26</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4295,11 +4272,11 @@
         <v>163</v>
       </c>
       <c r="B45" s="9">
-        <v>46181.60906018519</v>
+        <v>46181.609063310185</v>
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46182.62707423611</v>
+        <v>46182.62725847222</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>164</v>
@@ -4308,69 +4285,79 @@
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="I45" s="9">
+        <v>46252</v>
+      </c>
+      <c r="J45" s="9">
+        <v>46262</v>
+      </c>
+      <c r="K45" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L45" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M45" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N45" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="O45" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="H45" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="I45" s="9">
-        <v>46290</v>
-      </c>
-      <c r="J45" s="9">
-        <v>46290</v>
-      </c>
-      <c r="K45" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L45" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M45" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N45" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="O45" s="10" t="s">
-        <v>161</v>
-      </c>
       <c r="P45" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="Q45" s="10"/>
-      <c r="R45" s="10"/>
-      <c r="S45" s="10"/>
-      <c r="T45" s="10"/>
-      <c r="U45" s="10"/>
+      <c r="Q45" s="9">
+        <v>46252</v>
+      </c>
+      <c r="R45" s="9">
+        <v>46262</v>
+      </c>
+      <c r="S45" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T45" s="10">
+        <v>0</v>
+      </c>
+      <c r="U45" s="11" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B46" s="5">
-        <v>46181.609063310185</v>
+        <v>46181.60906703703</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46182.62725847222</v>
+        <v>46182.62720454861</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>168</v>
+        <v>103</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="I46" s="5">
         <v>46252</v>
       </c>
       <c r="J46" s="5">
-        <v>46262</v>
+        <v>46253</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>26</v>
@@ -4382,58 +4369,48 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>169</v>
+        <v>102</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q46" s="5">
-        <v>46252</v>
-      </c>
-      <c r="R46" s="5">
-        <v>46262</v>
-      </c>
-      <c r="S46" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T46" s="6">
-        <v>0</v>
-      </c>
-      <c r="U46" s="11" t="s">
-        <v>57</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="Q46" s="6"/>
+      <c r="R46" s="6"/>
+      <c r="S46" s="6"/>
+      <c r="T46" s="6"/>
+      <c r="U46" s="6"/>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B47" s="9">
-        <v>46181.60906703703</v>
+        <v>46181.60907681713</v>
       </c>
       <c r="C47" s="10"/>
       <c r="D47" s="9">
-        <v>46182.62720454861</v>
+        <v>46182.627201296295</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>107</v>
+        <v>169</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="I47" s="9">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="J47" s="9">
-        <v>46253</v>
+        <v>46262</v>
       </c>
       <c r="K47" s="10" t="s">
         <v>26</v>
@@ -4445,13 +4422,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
@@ -4461,80 +4438,84 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B48" s="5">
-        <v>46181.60907681713</v>
+        <v>46181.6090815625</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46182.627201296295</v>
+        <v>46191.542751388886</v>
       </c>
       <c r="E48" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H48" s="6"/>
+      <c r="I48" s="6"/>
+      <c r="J48" s="6"/>
+      <c r="K48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M48" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="N48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O48" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="F48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G48" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="I48" s="5">
-        <v>46254</v>
-      </c>
-      <c r="J48" s="5">
-        <v>46262</v>
-      </c>
-      <c r="K48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N48" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="O48" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="P48" s="6" t="s">
-        <v>174</v>
+        <v>26</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
       <c r="S48" s="6"/>
       <c r="T48" s="6"/>
-      <c r="U48" s="6"/>
+      <c r="U48" s="12" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="B49" s="9">
+        <v>46181.60908480324</v>
+      </c>
+      <c r="C49" s="9">
+        <v>46190.708245752314</v>
+      </c>
+      <c r="D49" s="9">
+        <v>46190.708260555555</v>
+      </c>
+      <c r="E49" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="B49" s="9">
-        <v>46181.6090815625</v>
-      </c>
-      <c r="C49" s="10"/>
-      <c r="D49" s="9">
-        <v>46191.542751388886</v>
-      </c>
-      <c r="E49" s="10" t="s">
+      <c r="F49" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G49" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="F49" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G49" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H49" s="10"/>
-      <c r="I49" s="10"/>
-      <c r="J49" s="10"/>
+      <c r="H49" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="I49" s="9">
+        <v>46174</v>
+      </c>
+      <c r="J49" s="9">
+        <v>46191</v>
+      </c>
       <c r="K49" s="10" t="s">
         <v>26</v>
       </c>
@@ -4542,49 +4523,57 @@
         <v>26</v>
       </c>
       <c r="M49" s="10" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N49" s="10" t="s">
-        <v>26</v>
+        <v>172</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P49" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q49" s="10"/>
-      <c r="R49" s="10"/>
-      <c r="S49" s="10"/>
-      <c r="T49" s="10"/>
-      <c r="U49" s="12" t="s">
-        <v>82</v>
+        <v>172</v>
+      </c>
+      <c r="Q49" s="9">
+        <v>46174</v>
+      </c>
+      <c r="R49" s="9">
+        <v>46191</v>
+      </c>
+      <c r="S49" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="T49" s="10">
+        <v>1</v>
+      </c>
+      <c r="U49" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B50" s="5">
-        <v>46181.60908480324</v>
+        <v>46181.60908915509</v>
       </c>
       <c r="C50" s="5">
-        <v>46190.708245752314</v>
+        <v>46190.70821236111</v>
       </c>
       <c r="D50" s="5">
-        <v>46190.708260555555</v>
+        <v>46190.70821390046</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="I50" s="5">
         <v>46174</v>
@@ -4602,54 +4591,44 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="O50" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="P50" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="P50" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q50" s="5">
-        <v>46174</v>
-      </c>
-      <c r="R50" s="5">
-        <v>46191</v>
-      </c>
-      <c r="S50" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="T50" s="6">
-        <v>1</v>
-      </c>
-      <c r="U50" s="7" t="s">
-        <v>27</v>
-      </c>
+      <c r="Q50" s="6"/>
+      <c r="R50" s="6"/>
+      <c r="S50" s="6"/>
+      <c r="T50" s="6"/>
+      <c r="U50" s="6"/>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="B51" s="9">
+        <v>46181.60909384259</v>
+      </c>
+      <c r="C51" s="9">
+        <v>46190.70822138889</v>
+      </c>
+      <c r="D51" s="9">
+        <v>46190.7082228125</v>
+      </c>
+      <c r="E51" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="B51" s="9">
-        <v>46181.60908915509</v>
-      </c>
-      <c r="C51" s="9">
-        <v>46190.70821236111</v>
-      </c>
-      <c r="D51" s="9">
-        <v>46190.70821390046</v>
-      </c>
-      <c r="E51" s="10" t="s">
-        <v>185</v>
-      </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="I51" s="9">
         <v>46174</v>
@@ -4667,13 +4646,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q51" s="10"/>
       <c r="R51" s="10"/>
@@ -4683,28 +4662,28 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B52" s="5">
+        <v>46181.61221741898</v>
+      </c>
+      <c r="C52" s="5">
+        <v>46190.70822601852</v>
+      </c>
+      <c r="D52" s="5">
+        <v>46190.708227337964</v>
+      </c>
+      <c r="E52" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="B52" s="5">
-        <v>46181.60909384259</v>
-      </c>
-      <c r="C52" s="5">
-        <v>46190.70822138889</v>
-      </c>
-      <c r="D52" s="5">
-        <v>46190.7082228125</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>188</v>
-      </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="I52" s="5">
         <v>46174</v>
@@ -4722,13 +4701,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4738,28 +4717,28 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B53" s="9">
-        <v>46181.61221741898</v>
+        <v>46181.612357199076</v>
       </c>
       <c r="C53" s="9">
-        <v>46190.70822601852</v>
+        <v>46190.70823167824</v>
       </c>
       <c r="D53" s="9">
-        <v>46190.708227337964</v>
+        <v>46190.708233321755</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="I53" s="9">
         <v>46174</v>
@@ -4777,13 +4756,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4793,34 +4772,34 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B54" s="5">
-        <v>46181.612357199076</v>
+        <v>46181.609098182875</v>
       </c>
       <c r="C54" s="5">
-        <v>46190.70823167824</v>
+        <v>46191.54272982639</v>
       </c>
       <c r="D54" s="5">
-        <v>46190.708233321755</v>
+        <v>46191.54274247686</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="I54" s="5">
-        <v>46174</v>
+        <v>46227</v>
       </c>
       <c r="J54" s="5">
-        <v>46191</v>
+        <v>46246</v>
       </c>
       <c r="K54" s="6" t="s">
         <v>26</v>
@@ -4832,44 +4811,54 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>76</v>
+        <v>178</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="Q54" s="6"/>
-      <c r="R54" s="6"/>
-      <c r="S54" s="6"/>
-      <c r="T54" s="6"/>
-      <c r="U54" s="6"/>
+        <v>172</v>
+      </c>
+      <c r="Q54" s="5">
+        <v>46227</v>
+      </c>
+      <c r="R54" s="5">
+        <v>46246</v>
+      </c>
+      <c r="S54" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T54" s="6">
+        <v>1</v>
+      </c>
+      <c r="U54" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B55" s="9">
-        <v>46181.609098182875</v>
+        <v>46181.60910252314</v>
       </c>
       <c r="C55" s="9">
-        <v>46191.54272982639</v>
+        <v>46191.54270648149</v>
       </c>
       <c r="D55" s="9">
-        <v>46191.54274247686</v>
+        <v>46191.54270819444</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="I55" s="9">
         <v>46227</v>
@@ -4887,54 +4876,44 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q55" s="9">
-        <v>46227</v>
-      </c>
-      <c r="R55" s="9">
-        <v>46246</v>
-      </c>
-      <c r="S55" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T55" s="10">
-        <v>1</v>
-      </c>
-      <c r="U55" s="7" t="s">
-        <v>27</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="Q55" s="10"/>
+      <c r="R55" s="10"/>
+      <c r="S55" s="10"/>
+      <c r="T55" s="10"/>
+      <c r="U55" s="10"/>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B56" s="5">
-        <v>46181.60910252314</v>
+        <v>46181.609107951386</v>
       </c>
       <c r="C56" s="5">
-        <v>46191.54270648149</v>
+        <v>46191.542715625</v>
       </c>
       <c r="D56" s="5">
-        <v>46191.54270819444</v>
+        <v>46191.54271703704</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="I56" s="5">
         <v>46227</v>
@@ -4952,13 +4931,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="O56" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="P56" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="O56" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="P56" s="6" t="s">
-        <v>197</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4968,28 +4947,28 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B57" s="9">
-        <v>46181.609107951386</v>
+        <v>46181.61393570602</v>
       </c>
       <c r="C57" s="9">
-        <v>46191.542715625</v>
+        <v>46190.70842026621</v>
       </c>
       <c r="D57" s="9">
-        <v>46191.54271703704</v>
+        <v>46190.70842170139</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="I57" s="9">
         <v>46227</v>
@@ -5007,13 +4986,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -5023,28 +5002,28 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B58" s="5">
-        <v>46181.61393570602</v>
+        <v>46181.61396929398</v>
       </c>
       <c r="C58" s="5">
-        <v>46190.70842026621</v>
+        <v>46190.70842520833</v>
       </c>
       <c r="D58" s="5">
-        <v>46190.70842170139</v>
+        <v>46190.708426550926</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="I58" s="5">
         <v>46227</v>
@@ -5062,13 +5041,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5078,34 +5057,34 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B59" s="9">
-        <v>46181.61396929398</v>
+        <v>46181.60911329861</v>
       </c>
       <c r="C59" s="9">
-        <v>46190.70842520833</v>
+        <v>46191.54538693287</v>
       </c>
       <c r="D59" s="9">
-        <v>46190.708426550926</v>
+        <v>46191.54539826389</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>193</v>
+        <v>96</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="I59" s="9">
-        <v>46227</v>
+        <v>46247</v>
       </c>
       <c r="J59" s="9">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="K59" s="10" t="s">
         <v>26</v>
@@ -5117,48 +5096,56 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>195</v>
+        <v>172</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="Q59" s="10"/>
-      <c r="R59" s="10"/>
-      <c r="S59" s="10"/>
-      <c r="T59" s="10"/>
-      <c r="U59" s="10"/>
+        <v>199</v>
+      </c>
+      <c r="Q59" s="9">
+        <v>46247</v>
+      </c>
+      <c r="R59" s="9">
+        <v>46247</v>
+      </c>
+      <c r="S59" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T59" s="10">
+        <v>1</v>
+      </c>
+      <c r="U59" s="7" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B60" s="5">
-        <v>46181.60911329861</v>
+        <v>46181.60912350695</v>
       </c>
       <c r="C60" s="5">
-        <v>46191.54538693287</v>
+        <v>46191.54535901621</v>
       </c>
       <c r="D60" s="5">
-        <v>46191.54539826389</v>
+        <v>46191.54536050926</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>100</v>
+        <v>181</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="I60" s="5">
-        <v>46247</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="I60" s="6"/>
       <c r="J60" s="5">
         <v>46247</v>
       </c>
@@ -5172,54 +5159,44 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>176</v>
+        <v>96</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q60" s="5">
-        <v>46247</v>
-      </c>
-      <c r="R60" s="5">
-        <v>46247</v>
-      </c>
-      <c r="S60" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T60" s="6">
-        <v>1</v>
-      </c>
-      <c r="U60" s="7" t="s">
-        <v>27</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="Q60" s="6"/>
+      <c r="R60" s="6"/>
+      <c r="S60" s="6"/>
+      <c r="T60" s="6"/>
+      <c r="U60" s="6"/>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B61" s="9">
-        <v>46181.60912350695</v>
+        <v>46181.60912782408</v>
       </c>
       <c r="C61" s="9">
-        <v>46191.54535901621</v>
+        <v>46191.54537241899</v>
       </c>
       <c r="D61" s="9">
-        <v>46191.54536050926</v>
+        <v>46191.54537386574</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="I61" s="10"/>
       <c r="J61" s="9">
@@ -5235,13 +5212,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="10" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="P61" s="10" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="Q61" s="10"/>
       <c r="R61" s="10"/>
@@ -5251,28 +5228,28 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B62" s="5">
-        <v>46181.60912782408</v>
+        <v>46181.614119606485</v>
       </c>
       <c r="C62" s="5">
-        <v>46191.54537241899</v>
+        <v>46190.72172383102</v>
       </c>
       <c r="D62" s="5">
-        <v>46191.54537386574</v>
+        <v>46190.721725358795</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="I62" s="6"/>
       <c r="J62" s="5">
@@ -5288,13 +5265,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>100</v>
+        <v>26</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5304,28 +5281,28 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B63" s="9">
-        <v>46181.614119606485</v>
+        <v>46181.61419627315</v>
       </c>
       <c r="C63" s="9">
-        <v>46190.72172383102</v>
+        <v>46190.72172868055</v>
       </c>
       <c r="D63" s="9">
-        <v>46190.721725358795</v>
+        <v>46190.7217299537</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="I63" s="10"/>
       <c r="J63" s="9">
@@ -5341,10 +5318,10 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="P63" s="10" t="s">
         <v>26</v>
@@ -5357,79 +5334,89 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B64" s="5">
+        <v>46181.60913207176</v>
+      </c>
+      <c r="C64" s="6"/>
+      <c r="D64" s="5">
+        <v>46182.633118067126</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="B64" s="5">
-        <v>46181.61419627315</v>
-      </c>
-      <c r="C64" s="5">
-        <v>46190.72172868055</v>
-      </c>
-      <c r="D64" s="5">
-        <v>46190.7217299537</v>
-      </c>
-      <c r="E64" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="F64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G64" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="H64" s="6" t="s">
+      <c r="I64" s="5">
+        <v>46322</v>
+      </c>
+      <c r="J64" s="5">
+        <v>46322</v>
+      </c>
+      <c r="K64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N64" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="O64" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="I64" s="6"/>
-      <c r="J64" s="5">
-        <v>46247</v>
-      </c>
-      <c r="K64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N64" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="O64" s="6" t="s">
-        <v>193</v>
-      </c>
       <c r="P64" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="Q64" s="6"/>
-      <c r="R64" s="6"/>
-      <c r="S64" s="6"/>
-      <c r="T64" s="6"/>
-      <c r="U64" s="6"/>
+      <c r="Q64" s="5">
+        <v>46322</v>
+      </c>
+      <c r="R64" s="5">
+        <v>46322</v>
+      </c>
+      <c r="S64" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T64" s="6">
+        <v>0</v>
+      </c>
+      <c r="U64" s="11" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
         <v>208</v>
       </c>
       <c r="B65" s="9">
-        <v>46181.60913207176</v>
+        <v>46181.609135833336</v>
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46182.633118067126</v>
+        <v>46182.63311847222</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>209</v>
+        <v>181</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="I65" s="9">
         <v>46322</v>
@@ -5447,52 +5434,42 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="P65" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q65" s="9">
-        <v>46322</v>
-      </c>
-      <c r="R65" s="9">
-        <v>46322</v>
-      </c>
-      <c r="S65" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T65" s="10">
-        <v>0</v>
-      </c>
-      <c r="U65" s="11" t="s">
-        <v>57</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="Q65" s="10"/>
+      <c r="R65" s="10"/>
+      <c r="S65" s="10"/>
+      <c r="T65" s="10"/>
+      <c r="U65" s="10"/>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B66" s="5">
-        <v>46181.609135833336</v>
+        <v>46181.614311909725</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46182.63311847222</v>
+        <v>46182.63311923611</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>185</v>
+        <v>211</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="I66" s="5">
         <v>46322</v>
@@ -5510,13 +5487,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>213</v>
+        <v>181</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5526,33 +5503,27 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B67" s="9">
-        <v>46181.614311909725</v>
+        <v>46181.60918671296</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="9">
-        <v>46182.63311923611</v>
+        <v>46181.77983537037</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F67" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="H67" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="I67" s="9">
-        <v>46322</v>
-      </c>
-      <c r="J67" s="9">
-        <v>46322</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H67" s="10"/>
+      <c r="I67" s="10"/>
+      <c r="J67" s="10"/>
       <c r="K67" s="10" t="s">
         <v>26</v>
       </c>
@@ -5560,16 +5531,16 @@
         <v>26</v>
       </c>
       <c r="M67" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>209</v>
+        <v>26</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>185</v>
+        <v>214</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>185</v>
+        <v>26</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5579,27 +5550,33 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B68" s="5">
-        <v>46181.60918671296</v>
+        <v>46181.609196087964</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46181.77983537037</v>
+        <v>46182.63576145833</v>
       </c>
       <c r="E68" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G68" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="F68" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H68" s="6"/>
-      <c r="I68" s="6"/>
-      <c r="J68" s="6"/>
+      <c r="H68" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="I68" s="5">
+        <v>46252</v>
+      </c>
+      <c r="J68" s="5">
+        <v>46253</v>
+      </c>
       <c r="K68" s="6" t="s">
         <v>26</v>
       </c>
@@ -5607,75 +5584,85 @@
         <v>26</v>
       </c>
       <c r="M68" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N68" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="O68" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="P68" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q68" s="5">
+        <v>46252</v>
+      </c>
+      <c r="R68" s="5">
+        <v>46253</v>
+      </c>
+      <c r="S68" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T68" s="6">
         <v>0</v>
       </c>
-      <c r="N68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O68" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="P68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q68" s="6"/>
-      <c r="R68" s="6"/>
-      <c r="S68" s="6"/>
-      <c r="T68" s="6"/>
-      <c r="U68" s="6"/>
+      <c r="U68" s="11" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B69" s="9">
-        <v>46181.609196087964</v>
+        <v>46181.609201921296</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="9">
-        <v>46182.63576145833</v>
+        <v>46182.63583637732</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>221</v>
+        <v>161</v>
       </c>
       <c r="H69" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="I69" s="9">
+        <v>46254</v>
+      </c>
+      <c r="J69" s="9">
+        <v>46255</v>
+      </c>
+      <c r="K69" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L69" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M69" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N69" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="O69" s="10" t="s">
         <v>222</v>
-      </c>
-      <c r="I69" s="9">
-        <v>46252</v>
-      </c>
-      <c r="J69" s="9">
-        <v>46253</v>
-      </c>
-      <c r="K69" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L69" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M69" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N69" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="O69" s="10" t="s">
-        <v>143</v>
       </c>
       <c r="P69" s="10" t="s">
         <v>223</v>
       </c>
       <c r="Q69" s="9">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="R69" s="9">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="S69" s="7" t="s">
         <v>33</v>
@@ -5692,11 +5679,11 @@
         <v>224</v>
       </c>
       <c r="B70" s="5">
-        <v>46181.609201921296</v>
+        <v>46181.60920746528</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46182.63583637732</v>
+        <v>46182.635758460645</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>225</v>
@@ -5705,16 +5692,16 @@
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>165</v>
+        <v>217</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>166</v>
+        <v>218</v>
       </c>
       <c r="I70" s="5">
-        <v>46254</v>
+        <v>46252</v>
       </c>
       <c r="J70" s="5">
-        <v>46255</v>
+        <v>46253</v>
       </c>
       <c r="K70" s="6" t="s">
         <v>26</v>
@@ -5726,19 +5713,19 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="O70" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="P70" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="P70" s="6" t="s">
-        <v>227</v>
-      </c>
       <c r="Q70" s="5">
-        <v>46254</v>
+        <v>46252</v>
       </c>
       <c r="R70" s="5">
-        <v>46255</v>
+        <v>46253</v>
       </c>
       <c r="S70" s="7" t="s">
         <v>33</v>
@@ -5752,56 +5739,56 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B71" s="9">
-        <v>46181.60920746528</v>
+        <v>46181.609212870375</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46182.635758460645</v>
+        <v>46182.63583289352</v>
       </c>
       <c r="E71" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="F71" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G71" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="H71" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="I71" s="9">
+        <v>46254</v>
+      </c>
+      <c r="J71" s="9">
+        <v>46255</v>
+      </c>
+      <c r="K71" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L71" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M71" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N71" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="O71" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="P71" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="F71" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G71" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>222</v>
-      </c>
-      <c r="I71" s="9">
-        <v>46252</v>
-      </c>
-      <c r="J71" s="9">
-        <v>46253</v>
-      </c>
-      <c r="K71" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L71" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M71" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N71" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="O71" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="P71" s="10" t="s">
-        <v>230</v>
-      </c>
       <c r="Q71" s="9">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="R71" s="9">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="S71" s="7" t="s">
         <v>33</v>
@@ -5815,56 +5802,56 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B72" s="5">
-        <v>46181.609212870375</v>
+        <v>46181.60921715278</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46182.63583289352</v>
+        <v>46182.63575501158</v>
       </c>
       <c r="E72" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="F72" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G72" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="I72" s="5">
+        <v>46252</v>
+      </c>
+      <c r="J72" s="5">
+        <v>46253</v>
+      </c>
+      <c r="K72" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L72" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M72" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N72" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="O72" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="P72" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="F72" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G72" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="I72" s="5">
-        <v>46254</v>
-      </c>
-      <c r="J72" s="5">
-        <v>46255</v>
-      </c>
-      <c r="K72" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L72" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M72" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N72" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="O72" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="P72" s="6" t="s">
-        <v>233</v>
-      </c>
       <c r="Q72" s="5">
-        <v>46254</v>
+        <v>46252</v>
       </c>
       <c r="R72" s="5">
-        <v>46255</v>
+        <v>46253</v>
       </c>
       <c r="S72" s="7" t="s">
         <v>33</v>
@@ -5878,32 +5865,32 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B73" s="9">
-        <v>46181.60921715278</v>
+        <v>46181.60922180556</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="9">
-        <v>46182.63575501158</v>
+        <v>46182.63582844907</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>221</v>
+        <v>161</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>222</v>
+        <v>162</v>
       </c>
       <c r="I73" s="9">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="J73" s="9">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="K73" s="10" t="s">
         <v>26</v>
@@ -5915,19 +5902,19 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>173</v>
+        <v>231</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="Q73" s="9">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="R73" s="9">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="S73" s="7" t="s">
         <v>33</v>
@@ -5941,90 +5928,80 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B74" s="5">
-        <v>46181.60922180556</v>
+        <v>46181.60922590278</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46182.63582844907</v>
+        <v>46181.782424143516</v>
       </c>
       <c r="E74" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H74" s="6"/>
+      <c r="I74" s="6"/>
+      <c r="J74" s="6"/>
+      <c r="K74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M74" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="N74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O74" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="F74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G74" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="I74" s="5">
-        <v>46254</v>
-      </c>
-      <c r="J74" s="5">
-        <v>46255</v>
-      </c>
-      <c r="K74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N74" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="O74" s="6" t="s">
-        <v>235</v>
-      </c>
       <c r="P74" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="Q74" s="5">
-        <v>46254</v>
-      </c>
-      <c r="R74" s="5">
-        <v>46255</v>
-      </c>
-      <c r="S74" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T74" s="6">
-        <v>0</v>
-      </c>
-      <c r="U74" s="11" t="s">
-        <v>57</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q74" s="6"/>
+      <c r="R74" s="6"/>
+      <c r="S74" s="6"/>
+      <c r="T74" s="6"/>
+      <c r="U74" s="6"/>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B75" s="9">
-        <v>46181.60922590278</v>
+        <v>46181.60922940972</v>
       </c>
       <c r="C75" s="10"/>
       <c r="D75" s="9">
-        <v>46181.782424143516</v>
+        <v>46182.63612115741</v>
       </c>
       <c r="E75" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="F75" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G75" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="F75" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G75" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H75" s="10"/>
-      <c r="I75" s="10"/>
-      <c r="J75" s="10"/>
+      <c r="H75" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="I75" s="9">
+        <v>46258</v>
+      </c>
+      <c r="J75" s="9">
+        <v>46266</v>
+      </c>
       <c r="K75" s="10" t="s">
         <v>26</v>
       </c>
@@ -6032,45 +6009,55 @@
         <v>26</v>
       </c>
       <c r="M75" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N75" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="O75" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="P75" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q75" s="9">
+        <v>46258</v>
+      </c>
+      <c r="R75" s="9">
+        <v>46266</v>
+      </c>
+      <c r="S75" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T75" s="10">
         <v>0</v>
       </c>
-      <c r="N75" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O75" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="P75" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q75" s="10"/>
-      <c r="R75" s="10"/>
-      <c r="S75" s="10"/>
-      <c r="T75" s="10"/>
-      <c r="U75" s="10"/>
+      <c r="U75" s="11" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B76" s="5">
-        <v>46181.60922940972</v>
+        <v>46181.60923553241</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46182.63612115741</v>
+        <v>46182.63598688657</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>242</v>
+        <v>181</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="I76" s="5">
         <v>46258</v>
@@ -6088,52 +6075,42 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O76" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="P76" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="P76" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="Q76" s="5">
-        <v>46258</v>
-      </c>
-      <c r="R76" s="5">
-        <v>46266</v>
-      </c>
-      <c r="S76" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T76" s="6">
-        <v>0</v>
-      </c>
-      <c r="U76" s="11" t="s">
-        <v>57</v>
-      </c>
+      <c r="Q76" s="6"/>
+      <c r="R76" s="6"/>
+      <c r="S76" s="6"/>
+      <c r="T76" s="6"/>
+      <c r="U76" s="6"/>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B77" s="9">
-        <v>46181.60923553241</v>
+        <v>46181.609241805556</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46182.63598688657</v>
+        <v>46182.63598342593</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="I77" s="9">
         <v>46258</v>
@@ -6151,13 +6128,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>249</v>
+        <v>181</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -6167,26 +6144,26 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B78" s="5">
-        <v>46181.609241805556</v>
+        <v>46181.6145286574</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46182.63598342593</v>
+        <v>46182.63598072917</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="I78" s="5">
         <v>46258</v>
@@ -6204,13 +6181,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>185</v>
+        <v>26</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6220,26 +6197,26 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B79" s="9">
-        <v>46181.6145286574</v>
+        <v>46181.61460722222</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="9">
-        <v>46182.63598072917</v>
+        <v>46182.63597787037</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="I79" s="9">
         <v>46258</v>
@@ -6257,10 +6234,10 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="P79" s="10" t="s">
         <v>26</v>
@@ -6273,26 +6250,26 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B80" s="5">
-        <v>46181.61460722222</v>
+        <v>46181.61464366898</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46182.63597787037</v>
+        <v>46182.635973807875</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="I80" s="5">
         <v>46258</v>
@@ -6310,10 +6287,10 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>26</v>
@@ -6326,32 +6303,32 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B81" s="9">
-        <v>46181.61464366898</v>
+        <v>46181.609247002314</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46182.635973807875</v>
+        <v>46182.64087873843</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>193</v>
+        <v>253</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="I81" s="9">
-        <v>46258</v>
+        <v>46267</v>
       </c>
       <c r="J81" s="9">
-        <v>46266</v>
+        <v>46288</v>
       </c>
       <c r="K81" s="10" t="s">
         <v>26</v>
@@ -6363,42 +6340,52 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="O81" s="10" t="s">
         <v>254</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q81" s="10"/>
-      <c r="R81" s="10"/>
-      <c r="S81" s="10"/>
-      <c r="T81" s="10"/>
-      <c r="U81" s="10"/>
+        <v>235</v>
+      </c>
+      <c r="Q81" s="9">
+        <v>46267</v>
+      </c>
+      <c r="R81" s="9">
+        <v>46288</v>
+      </c>
+      <c r="S81" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T81" s="10">
+        <v>0</v>
+      </c>
+      <c r="U81" s="11" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B82" s="5">
-        <v>46181.609247002314</v>
+        <v>46181.60925648148</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46182.64087873843</v>
+        <v>46191.54540523148</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>257</v>
+        <v>181</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="I82" s="5">
         <v>46267</v>
@@ -6416,52 +6403,42 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="Q82" s="5">
-        <v>46267</v>
-      </c>
-      <c r="R82" s="5">
-        <v>46288</v>
-      </c>
-      <c r="S82" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T82" s="6">
-        <v>0</v>
-      </c>
-      <c r="U82" s="11" t="s">
-        <v>57</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="Q82" s="6"/>
+      <c r="R82" s="6"/>
+      <c r="S82" s="6"/>
+      <c r="T82" s="6"/>
+      <c r="U82" s="6"/>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B83" s="9">
-        <v>46181.60925648148</v>
+        <v>46181.609262199076</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46191.54540523148</v>
+        <v>46191.54540574074</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="I83" s="9">
         <v>46267</v>
@@ -6479,13 +6456,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="O83" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="P83" s="10" t="s">
         <v>257</v>
-      </c>
-      <c r="O83" s="10" t="s">
-        <v>260</v>
-      </c>
-      <c r="P83" s="10" t="s">
-        <v>261</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6495,26 +6472,26 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B84" s="5">
-        <v>46181.609262199076</v>
+        <v>46181.61473356481</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46191.54540574074</v>
+        <v>46182.64084413194</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="I84" s="5">
         <v>46267</v>
@@ -6532,13 +6509,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="O84" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="P84" s="6" t="s">
         <v>260</v>
-      </c>
-      <c r="P84" s="6" t="s">
-        <v>261</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6548,26 +6525,26 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B85" s="9">
-        <v>46181.61473356481</v>
+        <v>46181.61477212963</v>
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46182.64084413194</v>
+        <v>46182.64084086806</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="I85" s="9">
         <v>46267</v>
@@ -6585,13 +6562,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6601,26 +6578,26 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B86" s="5">
-        <v>46181.61477212963</v>
+        <v>46181.61484836806</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46182.64084086806</v>
+        <v>46182.6408357176</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="I86" s="5">
         <v>46267</v>
@@ -6638,13 +6615,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6654,32 +6631,32 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B87" s="9">
-        <v>46181.61484836806</v>
+        <v>46181.60926783565</v>
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46182.6408357176</v>
+        <v>46182.64099746528</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>193</v>
+        <v>266</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>243</v>
+        <v>161</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>244</v>
+        <v>162</v>
       </c>
       <c r="I87" s="9">
-        <v>46267</v>
+        <v>46289</v>
       </c>
       <c r="J87" s="9">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="K87" s="10" t="s">
         <v>26</v>
@@ -6691,42 +6668,52 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="Q87" s="10"/>
-      <c r="R87" s="10"/>
-      <c r="S87" s="10"/>
-      <c r="T87" s="10"/>
-      <c r="U87" s="10"/>
+        <v>235</v>
+      </c>
+      <c r="Q87" s="9">
+        <v>46289</v>
+      </c>
+      <c r="R87" s="9">
+        <v>46289</v>
+      </c>
+      <c r="S87" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T87" s="10">
+        <v>0</v>
+      </c>
+      <c r="U87" s="11" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B88" s="5">
-        <v>46181.60926783565</v>
+        <v>46181.60927226851</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46182.64099746528</v>
+        <v>46191.545403842596</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>270</v>
+        <v>181</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="I88" s="5">
         <v>46289</v>
@@ -6744,52 +6731,42 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>239</v>
+        <v>266</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="Q88" s="5">
-        <v>46289</v>
-      </c>
-      <c r="R88" s="5">
-        <v>46289</v>
-      </c>
-      <c r="S88" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T88" s="6">
-        <v>0</v>
-      </c>
-      <c r="U88" s="11" t="s">
-        <v>57</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="Q88" s="6"/>
+      <c r="R88" s="6"/>
+      <c r="S88" s="6"/>
+      <c r="T88" s="6"/>
+      <c r="U88" s="6"/>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B89" s="9">
-        <v>46181.60927226851</v>
+        <v>46181.60927799769</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46191.545403842596</v>
+        <v>46191.545404212964</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="I89" s="9">
         <v>46289</v>
@@ -6807,13 +6784,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="O89" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="P89" s="10" t="s">
         <v>270</v>
-      </c>
-      <c r="O89" s="10" t="s">
-        <v>260</v>
-      </c>
-      <c r="P89" s="10" t="s">
-        <v>272</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6823,26 +6800,26 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B90" s="5">
-        <v>46181.60927799769</v>
+        <v>46181.614954062505</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46191.545404212964</v>
+        <v>46182.64096971064</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>185</v>
+        <v>260</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="I90" s="5">
         <v>46289</v>
@@ -6860,13 +6837,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>260</v>
+        <v>184</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>274</v>
+        <v>184</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6876,26 +6853,26 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B91" s="9">
-        <v>46181.614954062505</v>
+        <v>46181.61498993056</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46182.64096971064</v>
+        <v>46182.64096709491</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="I91" s="9">
         <v>46289</v>
@@ -6913,13 +6890,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q91" s="10"/>
       <c r="R91" s="10"/>
@@ -6929,26 +6906,26 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B92" s="5">
-        <v>46181.61498993056</v>
+        <v>46181.61502625</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46182.64096709491</v>
+        <v>46182.64096319444</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="I92" s="5">
         <v>46289</v>
@@ -6966,13 +6943,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>191</v>
+        <v>274</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6982,33 +6959,27 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B93" s="9">
-        <v>46181.61502625</v>
+        <v>46181.60928361111</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46182.64096319444</v>
+        <v>46182.567648321754</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>268</v>
+        <v>213</v>
       </c>
       <c r="F93" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="H93" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="I93" s="9">
-        <v>46289</v>
-      </c>
-      <c r="J93" s="9">
-        <v>46289</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H93" s="10"/>
+      <c r="I93" s="10"/>
+      <c r="J93" s="10"/>
       <c r="K93" s="10" t="s">
         <v>26</v>
       </c>
@@ -7016,16 +6987,16 @@
         <v>26</v>
       </c>
       <c r="M93" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>270</v>
+        <v>26</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>193</v>
+        <v>276</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>278</v>
+        <v>26</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -7035,27 +7006,33 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B94" s="5">
-        <v>46181.60928361111</v>
+        <v>46181.609286990744</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46182.567648321754</v>
+        <v>46190.88639451389</v>
       </c>
       <c r="E94" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="F94" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G94" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="F94" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H94" s="6"/>
-      <c r="I94" s="6"/>
-      <c r="J94" s="6"/>
+      <c r="H94" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="I94" s="5">
+        <v>46182</v>
+      </c>
+      <c r="J94" s="5">
+        <v>46183</v>
+      </c>
       <c r="K94" s="6" t="s">
         <v>26</v>
       </c>
@@ -7063,33 +7040,43 @@
         <v>26</v>
       </c>
       <c r="M94" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N94" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="O94" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="P94" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="Q94" s="5">
+        <v>46182</v>
+      </c>
+      <c r="R94" s="5">
+        <v>46183</v>
+      </c>
+      <c r="S94" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="T94" s="6">
         <v>0</v>
       </c>
-      <c r="N94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O94" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="P94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q94" s="6"/>
-      <c r="R94" s="6"/>
-      <c r="S94" s="6"/>
-      <c r="T94" s="6"/>
-      <c r="U94" s="6"/>
+      <c r="U94" s="12" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
         <v>281</v>
       </c>
       <c r="B95" s="9">
-        <v>46181.609286990744</v>
+        <v>46181.609292974535</v>
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46190.88639451389</v>
+        <v>46190.886394166664</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>282</v>
@@ -7098,16 +7085,16 @@
         <v>26</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="H95" s="10" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="I95" s="9">
-        <v>46182</v>
+        <v>46290</v>
       </c>
       <c r="J95" s="9">
-        <v>46183</v>
+        <v>46293</v>
       </c>
       <c r="K95" s="10" t="s">
         <v>26</v>
@@ -7119,58 +7106,58 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="O95" s="10" t="s">
         <v>26</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="Q95" s="9">
-        <v>46182</v>
+        <v>46290</v>
       </c>
       <c r="R95" s="9">
-        <v>46183</v>
-      </c>
-      <c r="S95" s="11" t="s">
-        <v>284</v>
+        <v>46293</v>
+      </c>
+      <c r="S95" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="T95" s="10">
         <v>0</v>
       </c>
       <c r="U95" s="12" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B96" s="5">
-        <v>46181.609292974535</v>
+        <v>46181.60929881944</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46190.886394166664</v>
+        <v>46190.886404791665</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="I96" s="5">
-        <v>46290</v>
+        <v>46226</v>
       </c>
       <c r="J96" s="5">
-        <v>46293</v>
+        <v>46227</v>
       </c>
       <c r="K96" s="6" t="s">
         <v>26</v>
@@ -7182,19 +7169,19 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="Q96" s="5">
-        <v>46290</v>
+        <v>46226</v>
       </c>
       <c r="R96" s="5">
-        <v>46293</v>
+        <v>46227</v>
       </c>
       <c r="S96" s="7" t="s">
         <v>33</v>
@@ -7203,37 +7190,37 @@
         <v>0</v>
       </c>
       <c r="U96" s="12" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B97" s="9">
-        <v>46181.60929881944</v>
+        <v>46181.60930480324</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46190.886404791665</v>
+        <v>46182.64108152778</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="I97" s="9">
-        <v>46226</v>
+        <v>46293</v>
       </c>
       <c r="J97" s="9">
-        <v>46227</v>
+        <v>46294</v>
       </c>
       <c r="K97" s="10" t="s">
         <v>26</v>
@@ -7245,19 +7232,19 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>26</v>
+        <v>157</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q97" s="9">
-        <v>46226</v>
+        <v>46293</v>
       </c>
       <c r="R97" s="9">
-        <v>46227</v>
+        <v>46294</v>
       </c>
       <c r="S97" s="7" t="s">
         <v>33</v>
@@ -7265,38 +7252,38 @@
       <c r="T97" s="10">
         <v>0</v>
       </c>
-      <c r="U97" s="12" t="s">
-        <v>82</v>
+      <c r="U97" s="11" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B98" s="5">
-        <v>46181.60930480324</v>
+        <v>46181.60935271991</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46182.64108152778</v>
+        <v>46182.641076203705</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>290</v>
+        <v>60</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="I98" s="5">
-        <v>46293</v>
+        <v>46226</v>
       </c>
       <c r="J98" s="5">
-        <v>46294</v>
+        <v>46227</v>
       </c>
       <c r="K98" s="6" t="s">
         <v>26</v>
@@ -7308,19 +7295,19 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>161</v>
+        <v>129</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>291</v>
+        <v>55</v>
       </c>
       <c r="Q98" s="5">
-        <v>46293</v>
+        <v>46226</v>
       </c>
       <c r="R98" s="5">
-        <v>46294</v>
+        <v>46227</v>
       </c>
       <c r="S98" s="7" t="s">
         <v>33</v>
@@ -7334,33 +7321,27 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B99" s="9">
-        <v>46181.60935271991</v>
+        <v>46181.60936674768</v>
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46182.641076203705</v>
+        <v>46182.633312060185</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>60</v>
+        <v>290</v>
       </c>
       <c r="F99" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>222</v>
-      </c>
-      <c r="I99" s="9">
-        <v>46226</v>
-      </c>
-      <c r="J99" s="9">
-        <v>46227</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H99" s="10"/>
+      <c r="I99" s="10"/>
+      <c r="J99" s="10"/>
       <c r="K99" s="10" t="s">
         <v>26</v>
       </c>
@@ -7368,102 +7349,108 @@
         <v>26</v>
       </c>
       <c r="M99" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>217</v>
+        <v>26</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>133</v>
+        <v>291</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q99" s="9">
-        <v>46226</v>
-      </c>
-      <c r="R99" s="9">
-        <v>46227</v>
-      </c>
-      <c r="S99" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T99" s="10">
-        <v>0</v>
-      </c>
-      <c r="U99" s="11" t="s">
-        <v>57</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q99" s="10"/>
+      <c r="R99" s="10"/>
+      <c r="S99" s="10"/>
+      <c r="T99" s="10"/>
+      <c r="U99" s="10"/>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B100" s="5">
-        <v>46181.60936674768</v>
+        <v>46181.609371666666</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46182.633312060185</v>
+        <v>46182.64123547454</v>
       </c>
       <c r="E100" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="F100" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G100" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="I100" s="5">
+        <v>46290</v>
+      </c>
+      <c r="J100" s="5">
+        <v>46310</v>
+      </c>
+      <c r="K100" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L100" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M100" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N100" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="O100" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="F100" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G100" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H100" s="6"/>
-      <c r="I100" s="6"/>
-      <c r="J100" s="6"/>
-      <c r="K100" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L100" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M100" s="6" t="s">
+      <c r="P100" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q100" s="5">
+        <v>46290</v>
+      </c>
+      <c r="R100" s="5">
+        <v>46310</v>
+      </c>
+      <c r="S100" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T100" s="6">
         <v>0</v>
       </c>
-      <c r="N100" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O100" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="P100" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q100" s="6"/>
-      <c r="R100" s="6"/>
-      <c r="S100" s="6"/>
-      <c r="T100" s="6"/>
-      <c r="U100" s="6"/>
+      <c r="U100" s="11" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B101" s="9">
-        <v>46181.609371666666</v>
+        <v>46181.609378587964</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46182.64123547454</v>
+        <v>46182.64119599537</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>297</v>
+        <v>181</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I101" s="9">
         <v>46290</v>
@@ -7481,52 +7468,42 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>294</v>
-      </c>
-      <c r="Q101" s="9">
-        <v>46290</v>
-      </c>
-      <c r="R101" s="9">
-        <v>46310</v>
-      </c>
-      <c r="S101" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T101" s="10">
-        <v>0</v>
-      </c>
-      <c r="U101" s="11" t="s">
-        <v>57</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="Q101" s="10"/>
+      <c r="R101" s="10"/>
+      <c r="S101" s="10"/>
+      <c r="T101" s="10"/>
+      <c r="U101" s="10"/>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B102" s="5">
-        <v>46181.609378587964</v>
+        <v>46181.61514019676</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46182.64119599537</v>
+        <v>46182.64119222222</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I102" s="5">
         <v>46290</v>
@@ -7544,13 +7521,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>300</v>
+        <v>181</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7560,32 +7537,32 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B103" s="9">
-        <v>46181.61514019676</v>
+        <v>46181.609386111115</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46182.64119222222</v>
+        <v>46182.641349328704</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>185</v>
+        <v>300</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I103" s="9">
-        <v>46290</v>
+        <v>46311</v>
       </c>
       <c r="J103" s="9">
-        <v>46310</v>
+        <v>46314</v>
       </c>
       <c r="K103" s="10" t="s">
         <v>26</v>
@@ -7597,42 +7574,52 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>302</v>
-      </c>
-      <c r="Q103" s="10"/>
-      <c r="R103" s="10"/>
-      <c r="S103" s="10"/>
-      <c r="T103" s="10"/>
-      <c r="U103" s="10"/>
+        <v>290</v>
+      </c>
+      <c r="Q103" s="9">
+        <v>46311</v>
+      </c>
+      <c r="R103" s="9">
+        <v>46314</v>
+      </c>
+      <c r="S103" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T103" s="10">
+        <v>0</v>
+      </c>
+      <c r="U103" s="11" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B104" s="5">
-        <v>46181.609386111115</v>
+        <v>46181.60939194444</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46182.641349328704</v>
+        <v>46191.54539792824</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>304</v>
+        <v>181</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I104" s="5">
         <v>46311</v>
@@ -7650,52 +7637,42 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>185</v>
+        <v>302</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="Q104" s="5">
-        <v>46311</v>
-      </c>
-      <c r="R104" s="5">
-        <v>46314</v>
-      </c>
-      <c r="S104" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T104" s="6">
-        <v>0</v>
-      </c>
-      <c r="U104" s="11" t="s">
-        <v>57</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="Q104" s="6"/>
+      <c r="R104" s="6"/>
+      <c r="S104" s="6"/>
+      <c r="T104" s="6"/>
+      <c r="U104" s="6"/>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B105" s="9">
-        <v>46181.60939194444</v>
+        <v>46181.61518315972</v>
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46191.54539792824</v>
+        <v>46182.64130309028</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I105" s="9">
         <v>46311</v>
@@ -7713,13 +7690,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>307</v>
+        <v>26</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7729,32 +7706,32 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B106" s="5">
-        <v>46181.61518315972</v>
+        <v>46181.60939866898</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46182.64130309028</v>
+        <v>46182.64144489584</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>185</v>
+        <v>307</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I106" s="5">
-        <v>46311</v>
+        <v>46315</v>
       </c>
       <c r="J106" s="5">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="K106" s="6" t="s">
         <v>26</v>
@@ -7766,42 +7743,52 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>309</v>
+        <v>181</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q106" s="6"/>
-      <c r="R106" s="6"/>
-      <c r="S106" s="6"/>
-      <c r="T106" s="6"/>
-      <c r="U106" s="6"/>
+        <v>290</v>
+      </c>
+      <c r="Q106" s="5">
+        <v>46315</v>
+      </c>
+      <c r="R106" s="5">
+        <v>46316</v>
+      </c>
+      <c r="S106" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T106" s="6">
+        <v>0</v>
+      </c>
+      <c r="U106" s="11" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B107" s="9">
-        <v>46181.60939866898</v>
+        <v>46181.60940505787</v>
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46182.64144489584</v>
+        <v>46191.54540628473</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>311</v>
+        <v>181</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I107" s="9">
         <v>46315</v>
@@ -7819,52 +7806,42 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>185</v>
+        <v>309</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>294</v>
-      </c>
-      <c r="Q107" s="9">
-        <v>46315</v>
-      </c>
-      <c r="R107" s="9">
-        <v>46316</v>
-      </c>
-      <c r="S107" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T107" s="10">
-        <v>0</v>
-      </c>
-      <c r="U107" s="11" t="s">
-        <v>57</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="Q107" s="10"/>
+      <c r="R107" s="10"/>
+      <c r="S107" s="10"/>
+      <c r="T107" s="10"/>
+      <c r="U107" s="10"/>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B108" s="5">
-        <v>46181.60940505787</v>
+        <v>46181.61523613426</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46191.54540628473</v>
+        <v>46182.64140446759</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I108" s="5">
         <v>46315</v>
@@ -7882,13 +7859,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>314</v>
+        <v>26</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7898,32 +7875,32 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B109" s="9">
-        <v>46181.61523613426</v>
+        <v>46181.60941365741</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46182.64140446759</v>
+        <v>46182.64155526621</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>185</v>
+        <v>314</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I109" s="9">
-        <v>46315</v>
+        <v>46317</v>
       </c>
       <c r="J109" s="9">
-        <v>46316</v>
+        <v>46318</v>
       </c>
       <c r="K109" s="10" t="s">
         <v>26</v>
@@ -7935,42 +7912,52 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>311</v>
+        <v>290</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>316</v>
+        <v>181</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q109" s="10"/>
-      <c r="R109" s="10"/>
-      <c r="S109" s="10"/>
-      <c r="T109" s="10"/>
-      <c r="U109" s="10"/>
+        <v>290</v>
+      </c>
+      <c r="Q109" s="9">
+        <v>46317</v>
+      </c>
+      <c r="R109" s="9">
+        <v>46318</v>
+      </c>
+      <c r="S109" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T109" s="10">
+        <v>0</v>
+      </c>
+      <c r="U109" s="11" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B110" s="5">
-        <v>46181.60941365741</v>
+        <v>46181.60941929398</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46182.64155526621</v>
+        <v>46191.54540483796</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>318</v>
+        <v>181</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I110" s="5">
         <v>46317</v>
@@ -7988,52 +7975,42 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>185</v>
+        <v>316</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="Q110" s="5">
-        <v>46317</v>
-      </c>
-      <c r="R110" s="5">
-        <v>46318</v>
-      </c>
-      <c r="S110" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T110" s="6">
-        <v>0</v>
-      </c>
-      <c r="U110" s="11" t="s">
-        <v>57</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="Q110" s="6"/>
+      <c r="R110" s="6"/>
+      <c r="S110" s="6"/>
+      <c r="T110" s="6"/>
+      <c r="U110" s="6"/>
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B111" s="9">
-        <v>46181.60941929398</v>
+        <v>46181.61528053241</v>
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46191.54540483796</v>
+        <v>46182.64151664352</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I111" s="9">
         <v>46317</v>
@@ -8051,13 +8028,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>321</v>
+        <v>26</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -8067,32 +8044,32 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B112" s="5">
-        <v>46181.61528053241</v>
+        <v>46181.60942706019</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46182.64151664352</v>
+        <v>46182.64166112269</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>185</v>
+        <v>321</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I112" s="5">
-        <v>46317</v>
+        <v>46321</v>
       </c>
       <c r="J112" s="5">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="K112" s="6" t="s">
         <v>26</v>
@@ -8104,42 +8081,52 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>318</v>
+        <v>290</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>323</v>
+        <v>181</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q112" s="6"/>
-      <c r="R112" s="6"/>
-      <c r="S112" s="6"/>
-      <c r="T112" s="6"/>
-      <c r="U112" s="6"/>
+        <v>290</v>
+      </c>
+      <c r="Q112" s="5">
+        <v>46321</v>
+      </c>
+      <c r="R112" s="5">
+        <v>46321</v>
+      </c>
+      <c r="S112" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T112" s="6">
+        <v>0</v>
+      </c>
+      <c r="U112" s="11" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B113" s="9">
-        <v>46181.60942706019</v>
+        <v>46181.60943415509</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46182.64166112269</v>
+        <v>46182.641623125004</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>325</v>
+        <v>181</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I113" s="9">
         <v>46321</v>
@@ -8157,52 +8144,42 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>294</v>
+        <v>321</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>294</v>
-      </c>
-      <c r="Q113" s="9">
-        <v>46321</v>
-      </c>
-      <c r="R113" s="9">
-        <v>46321</v>
-      </c>
-      <c r="S113" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T113" s="10">
-        <v>0</v>
-      </c>
-      <c r="U113" s="11" t="s">
-        <v>57</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="Q113" s="10"/>
+      <c r="R113" s="10"/>
+      <c r="S113" s="10"/>
+      <c r="T113" s="10"/>
+      <c r="U113" s="10"/>
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B114" s="5">
-        <v>46181.60943415509</v>
+        <v>46181.61532783565</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46182.641623125004</v>
+        <v>46182.64161924769</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I114" s="5">
         <v>46321</v>
@@ -8220,13 +8197,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>327</v>
+        <v>211</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8236,32 +8213,32 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B115" s="9">
-        <v>46181.61532783565</v>
+        <v>46181.60944410879</v>
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46182.64161924769</v>
+        <v>46182.82922638889</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>185</v>
+        <v>326</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I115" s="9">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="J115" s="9">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="K115" s="10" t="s">
         <v>26</v>
@@ -8273,42 +8250,52 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>325</v>
+        <v>290</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q115" s="10"/>
-      <c r="R115" s="10"/>
-      <c r="S115" s="10"/>
-      <c r="T115" s="10"/>
-      <c r="U115" s="10"/>
+        <v>327</v>
+      </c>
+      <c r="Q115" s="9">
+        <v>46323</v>
+      </c>
+      <c r="R115" s="9">
+        <v>46323</v>
+      </c>
+      <c r="S115" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T115" s="10">
+        <v>0</v>
+      </c>
+      <c r="U115" s="11" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B116" s="5">
-        <v>46181.60944410879</v>
+        <v>46181.60944996528</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46182.82922638889</v>
+        <v>46182.64173178241</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>330</v>
+        <v>181</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I116" s="5">
         <v>46323</v>
@@ -8326,52 +8313,42 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>294</v>
+        <v>326</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="Q116" s="5">
-        <v>46323</v>
-      </c>
-      <c r="R116" s="5">
-        <v>46323</v>
-      </c>
-      <c r="S116" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T116" s="6">
-        <v>0</v>
-      </c>
-      <c r="U116" s="11" t="s">
-        <v>57</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="Q116" s="6"/>
+      <c r="R116" s="6"/>
+      <c r="S116" s="6"/>
+      <c r="T116" s="6"/>
+      <c r="U116" s="6"/>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B117" s="9">
-        <v>46181.60944996528</v>
+        <v>46181.61537143518</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46182.64173178241</v>
+        <v>46182.64172883102</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H117" s="10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I117" s="9">
         <v>46323</v>
@@ -8389,13 +8366,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="10" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>185</v>
+        <v>211</v>
       </c>
       <c r="P117" s="10" t="s">
-        <v>333</v>
+        <v>26</v>
       </c>
       <c r="Q117" s="10"/>
       <c r="R117" s="10"/>
@@ -8405,33 +8382,27 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B118" s="5">
-        <v>46181.61537143518</v>
+        <v>46181.60945642361</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46182.64172883102</v>
+        <v>46182.634494212965</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>185</v>
+        <v>332</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="H118" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="I118" s="5">
-        <v>46323</v>
-      </c>
-      <c r="J118" s="5">
-        <v>46323</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H118" s="6"/>
+      <c r="I118" s="6"/>
+      <c r="J118" s="6"/>
       <c r="K118" s="6" t="s">
         <v>26</v>
       </c>
@@ -8439,13 +8410,13 @@
         <v>26</v>
       </c>
       <c r="M118" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>330</v>
+        <v>26</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>215</v>
+        <v>333</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>26</v>
@@ -8458,27 +8429,33 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B119" s="9">
-        <v>46181.60945642361</v>
+        <v>46181.60946096065</v>
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46182.634494212965</v>
+        <v>46182.64186350694</v>
       </c>
       <c r="E119" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="F119" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G119" s="10" t="s">
         <v>336</v>
       </c>
-      <c r="F119" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G119" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H119" s="10"/>
-      <c r="I119" s="10"/>
-      <c r="J119" s="10"/>
+      <c r="H119" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="I119" s="9">
+        <v>46324</v>
+      </c>
+      <c r="J119" s="9">
+        <v>46324</v>
+      </c>
       <c r="K119" s="10" t="s">
         <v>26</v>
       </c>
@@ -8486,45 +8463,55 @@
         <v>26</v>
       </c>
       <c r="M119" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="N119" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="O119" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="P119" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="Q119" s="9">
+        <v>46324</v>
+      </c>
+      <c r="R119" s="9">
+        <v>46324</v>
+      </c>
+      <c r="S119" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T119" s="10">
         <v>0</v>
       </c>
-      <c r="N119" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O119" s="10" t="s">
-        <v>337</v>
-      </c>
-      <c r="P119" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q119" s="10"/>
-      <c r="R119" s="10"/>
-      <c r="S119" s="10"/>
-      <c r="T119" s="10"/>
-      <c r="U119" s="10"/>
+      <c r="U119" s="11" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B120" s="5">
-        <v>46181.60946096065</v>
+        <v>46181.60946868056</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46182.64186350694</v>
+        <v>46182.641845254635</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>339</v>
+        <v>181</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="I120" s="5">
         <v>46324</v>
@@ -8542,52 +8529,42 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>342</v>
+        <v>181</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="Q120" s="5">
-        <v>46324</v>
-      </c>
-      <c r="R120" s="5">
-        <v>46324</v>
-      </c>
-      <c r="S120" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T120" s="6">
-        <v>0</v>
-      </c>
-      <c r="U120" s="11" t="s">
-        <v>57</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="Q120" s="6"/>
+      <c r="R120" s="6"/>
+      <c r="S120" s="6"/>
+      <c r="T120" s="6"/>
+      <c r="U120" s="6"/>
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B121" s="9">
-        <v>46181.60946868056</v>
+        <v>46181.609475034726</v>
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46182.641845254635</v>
+        <v>46182.64184081019</v>
       </c>
       <c r="E121" s="10" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="F121" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="H121" s="10" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="I121" s="9">
         <v>46324</v>
@@ -8605,13 +8582,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="10" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="O121" s="10" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="P121" s="10" t="s">
-        <v>344</v>
+        <v>181</v>
       </c>
       <c r="Q121" s="10"/>
       <c r="R121" s="10"/>
@@ -8621,26 +8598,26 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B122" s="5">
-        <v>46181.609475034726</v>
+        <v>46181.60947921296</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46182.64184081019</v>
+        <v>46182.641837766205</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>185</v>
+        <v>59</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="I122" s="5">
         <v>46324</v>
@@ -8658,13 +8635,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>185</v>
+        <v>59</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>185</v>
+        <v>59</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8674,14 +8651,14 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B123" s="9">
-        <v>46181.60947921296</v>
+        <v>46181.61605960648</v>
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46182.641837766205</v>
+        <v>46182.641834548616</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>59</v>
@@ -8690,10 +8667,10 @@
         <v>26</v>
       </c>
       <c r="G123" s="10" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="H123" s="10" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="I123" s="9">
         <v>46324</v>
@@ -8711,7 +8688,7 @@
         <v>26</v>
       </c>
       <c r="N123" s="10" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="O123" s="10" t="s">
         <v>59</v>
@@ -8727,26 +8704,26 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B124" s="5">
-        <v>46181.61605960648</v>
+        <v>46181.61617203704</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46182.641834548616</v>
+        <v>46182.64182482639</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>59</v>
+        <v>184</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="I124" s="5">
         <v>46324</v>
@@ -8764,13 +8741,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>59</v>
+        <v>260</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>59</v>
+        <v>184</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8780,26 +8757,26 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B125" s="9">
-        <v>46181.61617203704</v>
+        <v>46181.61620771991</v>
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46182.64182482639</v>
+        <v>46182.64182413195</v>
       </c>
       <c r="E125" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F125" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="10" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="H125" s="10" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="I125" s="9">
         <v>46324</v>
@@ -8817,13 +8794,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="10" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="O125" s="10" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="P125" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q125" s="10"/>
       <c r="R125" s="10"/>
@@ -8833,26 +8810,26 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B126" s="5">
-        <v>46181.61620771991</v>
+        <v>46181.616245833335</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46182.64182413195</v>
+        <v>46182.641823425925</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>191</v>
+        <v>274</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="I126" s="5">
         <v>46324</v>
@@ -8870,13 +8847,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8886,32 +8863,32 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B127" s="9">
-        <v>46181.616245833335</v>
+        <v>46181.60948424769</v>
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46182.641823425925</v>
+        <v>46182.64199267361</v>
       </c>
       <c r="E127" s="10" t="s">
-        <v>278</v>
+        <v>348</v>
       </c>
       <c r="F127" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>340</v>
+        <v>90</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>341</v>
+        <v>90</v>
       </c>
       <c r="I127" s="9">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="J127" s="9">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="K127" s="10" t="s">
         <v>26</v>
@@ -8923,42 +8900,52 @@
         <v>26</v>
       </c>
       <c r="N127" s="10" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="O127" s="10" t="s">
-        <v>268</v>
+        <v>181</v>
       </c>
       <c r="P127" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="Q127" s="10"/>
-      <c r="R127" s="10"/>
-      <c r="S127" s="10"/>
-      <c r="T127" s="10"/>
-      <c r="U127" s="10"/>
+        <v>332</v>
+      </c>
+      <c r="Q127" s="9">
+        <v>46325</v>
+      </c>
+      <c r="R127" s="9">
+        <v>46325</v>
+      </c>
+      <c r="S127" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T127" s="10">
+        <v>0</v>
+      </c>
+      <c r="U127" s="11" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B128" s="5">
-        <v>46181.60948424769</v>
+        <v>46181.60948969907</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46182.64199267361</v>
+        <v>46182.641973854166</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>352</v>
+        <v>181</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I128" s="5">
         <v>46325</v>
@@ -8976,52 +8963,42 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="Q128" s="5">
-        <v>46325</v>
-      </c>
-      <c r="R128" s="5">
-        <v>46325</v>
-      </c>
-      <c r="S128" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T128" s="6">
-        <v>0</v>
-      </c>
-      <c r="U128" s="11" t="s">
-        <v>57</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="Q128" s="6"/>
+      <c r="R128" s="6"/>
+      <c r="S128" s="6"/>
+      <c r="T128" s="6"/>
+      <c r="U128" s="6"/>
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B129" s="9">
-        <v>46181.60948969907</v>
+        <v>46181.60949538194</v>
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46182.641973854166</v>
+        <v>46182.64197085648</v>
       </c>
       <c r="E129" s="10" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H129" s="10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I129" s="9">
         <v>46325</v>
@@ -9039,13 +9016,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="10" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="O129" s="10" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="P129" s="10" t="s">
-        <v>354</v>
+        <v>181</v>
       </c>
       <c r="Q129" s="10"/>
       <c r="R129" s="10"/>
@@ -9055,26 +9032,26 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B130" s="5">
-        <v>46181.60949538194</v>
+        <v>46181.609560185185</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46182.64197085648</v>
+        <v>46182.641967118056</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>185</v>
+        <v>59</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I130" s="5">
         <v>46325</v>
@@ -9092,13 +9069,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>185</v>
+        <v>59</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>185</v>
+        <v>59</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9108,14 +9085,14 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="8" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B131" s="9">
-        <v>46181.609560185185</v>
+        <v>46181.61659114584</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46182.641967118056</v>
+        <v>46182.64196408565</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>59</v>
@@ -9124,10 +9101,10 @@
         <v>26</v>
       </c>
       <c r="G131" s="10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H131" s="10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I131" s="9">
         <v>46325</v>
@@ -9145,7 +9122,7 @@
         <v>26</v>
       </c>
       <c r="N131" s="10" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="O131" s="10" t="s">
         <v>59</v>
@@ -9161,26 +9138,26 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B132" s="5">
-        <v>46181.61659114584</v>
+        <v>46181.61662431713</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46182.64196408565</v>
+        <v>46182.64196105324</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>59</v>
+        <v>184</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I132" s="5">
         <v>46325</v>
@@ -9198,13 +9175,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>59</v>
+        <v>184</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>59</v>
+        <v>184</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9214,26 +9191,26 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B133" s="9">
-        <v>46181.61662431713</v>
+        <v>46181.61666238426</v>
       </c>
       <c r="C133" s="10"/>
       <c r="D133" s="9">
-        <v>46182.64196105324</v>
+        <v>46182.64195453704</v>
       </c>
       <c r="E133" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H133" s="10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I133" s="9">
         <v>46325</v>
@@ -9251,13 +9228,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="10" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="O133" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="P133" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q133" s="10"/>
       <c r="R133" s="10"/>
@@ -9267,26 +9244,26 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B134" s="5">
-        <v>46181.61666238426</v>
+        <v>46181.61670006944</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46182.64195453704</v>
+        <v>46182.64195372685</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I134" s="5">
         <v>46325</v>
@@ -9304,13 +9281,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>191</v>
+        <v>274</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9320,32 +9297,32 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B135" s="9">
-        <v>46181.61670006944</v>
+        <v>46181.60956560185</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="9">
-        <v>46182.64195372685</v>
+        <v>46182.82952324074</v>
       </c>
       <c r="E135" s="10" t="s">
-        <v>193</v>
+        <v>358</v>
       </c>
       <c r="F135" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="10" t="s">
-        <v>94</v>
+        <v>239</v>
       </c>
       <c r="H135" s="10" t="s">
-        <v>94</v>
+        <v>240</v>
       </c>
       <c r="I135" s="9">
-        <v>46325</v>
+        <v>46328</v>
       </c>
       <c r="J135" s="9">
-        <v>46325</v>
+        <v>46328</v>
       </c>
       <c r="K135" s="10" t="s">
         <v>26</v>
@@ -9357,42 +9334,52 @@
         <v>26</v>
       </c>
       <c r="N135" s="10" t="s">
-        <v>352</v>
+        <v>332</v>
       </c>
       <c r="O135" s="10" t="s">
-        <v>278</v>
+        <v>181</v>
       </c>
       <c r="P135" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="Q135" s="10"/>
-      <c r="R135" s="10"/>
-      <c r="S135" s="10"/>
-      <c r="T135" s="10"/>
-      <c r="U135" s="10"/>
+        <v>332</v>
+      </c>
+      <c r="Q135" s="9">
+        <v>46328</v>
+      </c>
+      <c r="R135" s="9">
+        <v>46328</v>
+      </c>
+      <c r="S135" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T135" s="10">
+        <v>0</v>
+      </c>
+      <c r="U135" s="11" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B136" s="5">
-        <v>46181.60956560185</v>
+        <v>46181.60957188657</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46182.82952324074</v>
+        <v>46182.82945300926</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>362</v>
+        <v>181</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="I136" s="5">
         <v>46328</v>
@@ -9410,52 +9397,42 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>336</v>
+        <v>358</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="Q136" s="5">
-        <v>46328</v>
-      </c>
-      <c r="R136" s="5">
-        <v>46328</v>
-      </c>
-      <c r="S136" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T136" s="6">
-        <v>0</v>
-      </c>
-      <c r="U136" s="11" t="s">
-        <v>57</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="Q136" s="6"/>
+      <c r="R136" s="6"/>
+      <c r="S136" s="6"/>
+      <c r="T136" s="6"/>
+      <c r="U136" s="6"/>
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="8" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B137" s="9">
-        <v>46181.60957188657</v>
+        <v>46181.609583576384</v>
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46182.82945300926</v>
+        <v>46182.829453784725</v>
       </c>
       <c r="E137" s="10" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="10" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H137" s="10" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="I137" s="9">
         <v>46328</v>
@@ -9473,13 +9450,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="10" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="O137" s="10" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="P137" s="10" t="s">
-        <v>364</v>
+        <v>181</v>
       </c>
       <c r="Q137" s="10"/>
       <c r="R137" s="10"/>
@@ -9489,26 +9466,26 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B138" s="5">
-        <v>46181.609583576384</v>
+        <v>46181.60958841435</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46182.829453784725</v>
+        <v>46182.829454583334</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>185</v>
+        <v>59</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="I138" s="5">
         <v>46328</v>
@@ -9526,13 +9503,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>185</v>
+        <v>59</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>185</v>
+        <v>59</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9542,14 +9519,14 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B139" s="9">
-        <v>46181.60958841435</v>
+        <v>46181.616839849536</v>
       </c>
       <c r="C139" s="10"/>
       <c r="D139" s="9">
-        <v>46182.829454583334</v>
+        <v>46182.829455706014</v>
       </c>
       <c r="E139" s="10" t="s">
         <v>59</v>
@@ -9558,10 +9535,10 @@
         <v>26</v>
       </c>
       <c r="G139" s="10" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H139" s="10" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="I139" s="9">
         <v>46328</v>
@@ -9579,7 +9556,7 @@
         <v>26</v>
       </c>
       <c r="N139" s="10" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="O139" s="10" t="s">
         <v>59</v>
@@ -9595,26 +9572,26 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B140" s="5">
-        <v>46181.616839849536</v>
+        <v>46181.61689748843</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46182.829455706014</v>
+        <v>46182.8294564699</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>59</v>
+        <v>184</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="I140" s="5">
         <v>46328</v>
@@ -9632,13 +9609,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>59</v>
+        <v>184</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>59</v>
+        <v>184</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9648,26 +9625,26 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B141" s="9">
-        <v>46181.61689748843</v>
+        <v>46181.616942569446</v>
       </c>
       <c r="C141" s="10"/>
       <c r="D141" s="9">
-        <v>46182.8294564699</v>
+        <v>46182.82945721065</v>
       </c>
       <c r="E141" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F141" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="10" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H141" s="10" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="I141" s="9">
         <v>46328</v>
@@ -9685,13 +9662,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="10" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="O141" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="P141" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q141" s="10"/>
       <c r="R141" s="10"/>
@@ -9701,26 +9678,26 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B142" s="5">
-        <v>46181.616942569446</v>
+        <v>46181.6169815162</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46182.82945721065</v>
+        <v>46182.82945796296</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="I142" s="5">
         <v>46328</v>
@@ -9738,13 +9715,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9754,32 +9731,32 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B143" s="9">
-        <v>46181.6169815162</v>
+        <v>46181.609592673616</v>
       </c>
       <c r="C143" s="10"/>
       <c r="D143" s="9">
-        <v>46182.82945796296</v>
+        <v>46182.642407384265</v>
       </c>
       <c r="E143" s="10" t="s">
-        <v>193</v>
+        <v>368</v>
       </c>
       <c r="F143" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="10" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H143" s="10" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="I143" s="9">
-        <v>46328</v>
+        <v>46329</v>
       </c>
       <c r="J143" s="9">
-        <v>46328</v>
+        <v>46329</v>
       </c>
       <c r="K143" s="10" t="s">
         <v>26</v>
@@ -9791,42 +9768,52 @@
         <v>26</v>
       </c>
       <c r="N143" s="10" t="s">
-        <v>362</v>
+        <v>332</v>
       </c>
       <c r="O143" s="10" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="P143" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="Q143" s="10"/>
-      <c r="R143" s="10"/>
-      <c r="S143" s="10"/>
-      <c r="T143" s="10"/>
-      <c r="U143" s="10"/>
+        <v>369</v>
+      </c>
+      <c r="Q143" s="9">
+        <v>46329</v>
+      </c>
+      <c r="R143" s="9">
+        <v>46329</v>
+      </c>
+      <c r="S143" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T143" s="10">
+        <v>0</v>
+      </c>
+      <c r="U143" s="11" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B144" s="5">
-        <v>46181.609592673616</v>
+        <v>46181.60960517361</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46182.642407384265</v>
+        <v>46182.8294527199</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>372</v>
+        <v>181</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="I144" s="5">
         <v>46329</v>
@@ -9844,52 +9831,42 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>336</v>
+        <v>368</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>373</v>
-      </c>
-      <c r="Q144" s="5">
-        <v>46329</v>
-      </c>
-      <c r="R144" s="5">
-        <v>46329</v>
-      </c>
-      <c r="S144" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T144" s="6">
-        <v>0</v>
-      </c>
-      <c r="U144" s="11" t="s">
-        <v>57</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="Q144" s="6"/>
+      <c r="R144" s="6"/>
+      <c r="S144" s="6"/>
+      <c r="T144" s="6"/>
+      <c r="U144" s="6"/>
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B145" s="9">
-        <v>46181.60960517361</v>
+        <v>46181.609610011576</v>
       </c>
       <c r="C145" s="10"/>
       <c r="D145" s="9">
-        <v>46182.8294527199</v>
+        <v>46182.829451909725</v>
       </c>
       <c r="E145" s="10" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="F145" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="10" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H145" s="10" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="I145" s="9">
         <v>46329</v>
@@ -9907,13 +9884,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="10" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="O145" s="10" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="P145" s="10" t="s">
-        <v>372</v>
+        <v>26</v>
       </c>
       <c r="Q145" s="10"/>
       <c r="R145" s="10"/>
@@ -9923,26 +9900,26 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B146" s="5">
-        <v>46181.609610011576</v>
+        <v>46181.609613796296</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46182.829451909725</v>
+        <v>46182.829452025464</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>185</v>
+        <v>59</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="I146" s="5">
         <v>46329</v>
@@ -9960,10 +9937,10 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>185</v>
+        <v>59</v>
       </c>
       <c r="P146" s="6" t="s">
         <v>26</v>
@@ -9976,14 +9953,14 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B147" s="9">
-        <v>46181.609613796296</v>
+        <v>46181.61712142361</v>
       </c>
       <c r="C147" s="10"/>
       <c r="D147" s="9">
-        <v>46182.829452025464</v>
+        <v>46182.82945197917</v>
       </c>
       <c r="E147" s="10" t="s">
         <v>59</v>
@@ -9992,10 +9969,10 @@
         <v>26</v>
       </c>
       <c r="G147" s="10" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H147" s="10" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="I147" s="9">
         <v>46329</v>
@@ -10013,7 +9990,7 @@
         <v>26</v>
       </c>
       <c r="N147" s="10" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="O147" s="10" t="s">
         <v>59</v>
@@ -10029,26 +10006,26 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B148" s="5">
-        <v>46181.61712142361</v>
+        <v>46181.61716094907</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46182.82945197917</v>
+        <v>46182.82945207176</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>59</v>
+        <v>184</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="I148" s="5">
         <v>46329</v>
@@ -10066,10 +10043,10 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>59</v>
+        <v>184</v>
       </c>
       <c r="P148" s="6" t="s">
         <v>26</v>
@@ -10082,26 +10059,26 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B149" s="9">
-        <v>46181.61716094907</v>
+        <v>46181.61719633102</v>
       </c>
       <c r="C149" s="10"/>
       <c r="D149" s="9">
-        <v>46182.82945207176</v>
+        <v>46182.829452025464</v>
       </c>
       <c r="E149" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="10" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H149" s="10" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="I149" s="9">
         <v>46329</v>
@@ -10119,10 +10096,10 @@
         <v>26</v>
       </c>
       <c r="N149" s="10" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="O149" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="P149" s="10" t="s">
         <v>26</v>
@@ -10135,26 +10112,26 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B150" s="5">
-        <v>46181.61719633102</v>
+        <v>46181.617235451384</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46182.829452025464</v>
+        <v>46182.829452418984</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="I150" s="5">
         <v>46329</v>
@@ -10172,10 +10149,10 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="P150" s="6" t="s">
         <v>26</v>
@@ -10188,33 +10165,27 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B151" s="9">
-        <v>46181.617235451384</v>
+        <v>46181.60961741898</v>
       </c>
       <c r="C151" s="10"/>
       <c r="D151" s="9">
-        <v>46182.829452418984</v>
+        <v>46182.63449439815</v>
       </c>
       <c r="E151" s="10" t="s">
-        <v>193</v>
+        <v>378</v>
       </c>
       <c r="F151" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G151" s="10" t="s">
-        <v>243</v>
-      </c>
-      <c r="H151" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="I151" s="9">
-        <v>46329</v>
-      </c>
-      <c r="J151" s="9">
-        <v>46329</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H151" s="10"/>
+      <c r="I151" s="10"/>
+      <c r="J151" s="10"/>
       <c r="K151" s="10" t="s">
         <v>26</v>
       </c>
@@ -10222,13 +10193,13 @@
         <v>26</v>
       </c>
       <c r="M151" s="10" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N151" s="10" t="s">
-        <v>372</v>
+        <v>26</v>
       </c>
       <c r="O151" s="10" t="s">
-        <v>193</v>
+        <v>379</v>
       </c>
       <c r="P151" s="10" t="s">
         <v>26</v>
@@ -10241,27 +10212,33 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B152" s="5">
-        <v>46181.60961741898</v>
+        <v>46181.60962174769</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46182.63449439815</v>
+        <v>46182.64244836806</v>
       </c>
       <c r="E152" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="F152" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G152" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="F152" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G152" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H152" s="6"/>
-      <c r="I152" s="6"/>
-      <c r="J152" s="6"/>
+      <c r="H152" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="I152" s="5">
+        <v>46330</v>
+      </c>
+      <c r="J152" s="5">
+        <v>46337</v>
+      </c>
       <c r="K152" s="6" t="s">
         <v>26</v>
       </c>
@@ -10269,33 +10246,43 @@
         <v>26</v>
       </c>
       <c r="M152" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N152" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="O152" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="P152" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="Q152" s="5">
+        <v>46330</v>
+      </c>
+      <c r="R152" s="5">
+        <v>46337</v>
+      </c>
+      <c r="S152" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="T152" s="6">
         <v>0</v>
       </c>
-      <c r="N152" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O152" s="6" t="s">
-        <v>383</v>
-      </c>
-      <c r="P152" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q152" s="6"/>
-      <c r="R152" s="6"/>
-      <c r="S152" s="6"/>
-      <c r="T152" s="6"/>
-      <c r="U152" s="6"/>
+      <c r="U152" s="11" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="8" t="s">
         <v>384</v>
       </c>
       <c r="B153" s="9">
-        <v>46181.60962174769</v>
+        <v>46181.60962780092</v>
       </c>
       <c r="C153" s="10"/>
       <c r="D153" s="9">
-        <v>46182.64244836806</v>
+        <v>46191.67892958333</v>
       </c>
       <c r="E153" s="10" t="s">
         <v>385</v>
@@ -10304,10 +10291,10 @@
         <v>26</v>
       </c>
       <c r="G153" s="10" t="s">
-        <v>386</v>
+        <v>30</v>
       </c>
       <c r="H153" s="10" t="s">
-        <v>387</v>
+        <v>31</v>
       </c>
       <c r="I153" s="9">
         <v>46330</v>
@@ -10325,13 +10312,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="O153" s="10" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="P153" s="10" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="Q153" s="9">
         <v>46330</v>
@@ -10351,33 +10338,27 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B154" s="5">
-        <v>46181.60962780092</v>
+        <v>46181.60963489584</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46182.64249208334</v>
+        <v>46182.63449431713</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F154" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H154" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I154" s="5">
-        <v>46330</v>
-      </c>
-      <c r="J154" s="5">
-        <v>46337</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H154" s="6"/>
+      <c r="I154" s="6"/>
+      <c r="J154" s="6"/>
       <c r="K154" s="6" t="s">
         <v>26</v>
       </c>
@@ -10385,23 +10366,19 @@
         <v>26</v>
       </c>
       <c r="M154" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>382</v>
+        <v>26</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>382</v>
-      </c>
-      <c r="Q154" s="5">
-        <v>46330</v>
-      </c>
-      <c r="R154" s="5">
-        <v>46337</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q154" s="6"/>
+      <c r="R154" s="6"/>
       <c r="S154" s="7" t="s">
         <v>33</v>
       </c>
@@ -10414,27 +10391,33 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="8" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B155" s="9">
-        <v>46181.60963489584</v>
+        <v>46181.609640208335</v>
       </c>
       <c r="C155" s="10"/>
       <c r="D155" s="9">
-        <v>46182.63449431713</v>
+        <v>46182.64254377315</v>
       </c>
       <c r="E155" s="10" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="F155" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G155" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H155" s="10"/>
-      <c r="I155" s="10"/>
-      <c r="J155" s="10"/>
+        <v>48</v>
+      </c>
+      <c r="H155" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="I155" s="9">
+        <v>46330</v>
+      </c>
+      <c r="J155" s="9">
+        <v>46338</v>
+      </c>
       <c r="K155" s="10" t="s">
         <v>26</v>
       </c>
@@ -10442,19 +10425,23 @@
         <v>26</v>
       </c>
       <c r="M155" s="10" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N155" s="10" t="s">
-        <v>26</v>
+        <v>387</v>
       </c>
       <c r="O155" s="10" t="s">
-        <v>393</v>
+        <v>368</v>
       </c>
       <c r="P155" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q155" s="10"/>
-      <c r="R155" s="10"/>
+        <v>391</v>
+      </c>
+      <c r="Q155" s="9">
+        <v>46330</v>
+      </c>
+      <c r="R155" s="9">
+        <v>46338</v>
+      </c>
       <c r="S155" s="7" t="s">
         <v>33</v>
       </c>
@@ -10467,17 +10454,17 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B156" s="5">
-        <v>46181.609640208335</v>
+        <v>46181.609646365745</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46182.64254377315</v>
+        <v>46182.64254079861</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
@@ -10489,10 +10476,10 @@
         <v>49</v>
       </c>
       <c r="I156" s="5">
-        <v>46330</v>
+        <v>46339</v>
       </c>
       <c r="J156" s="5">
-        <v>46338</v>
+        <v>46349</v>
       </c>
       <c r="K156" s="6" t="s">
         <v>26</v>
@@ -10504,19 +10491,19 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>372</v>
+        <v>390</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="Q156" s="5">
-        <v>46330</v>
+        <v>46339</v>
       </c>
       <c r="R156" s="5">
-        <v>46338</v>
+        <v>46349</v>
       </c>
       <c r="S156" s="7" t="s">
         <v>33</v>
@@ -10525,69 +10512,6 @@
         <v>0</v>
       </c>
       <c r="U156" s="11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="157" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A157" s="8" t="s">
-        <v>397</v>
-      </c>
-      <c r="B157" s="9">
-        <v>46181.609646365745</v>
-      </c>
-      <c r="C157" s="10"/>
-      <c r="D157" s="9">
-        <v>46182.64254079861</v>
-      </c>
-      <c r="E157" s="10" t="s">
-        <v>398</v>
-      </c>
-      <c r="F157" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G157" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="H157" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="I157" s="9">
-        <v>46339</v>
-      </c>
-      <c r="J157" s="9">
-        <v>46349</v>
-      </c>
-      <c r="K157" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L157" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M157" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N157" s="10" t="s">
-        <v>392</v>
-      </c>
-      <c r="O157" s="10" t="s">
-        <v>395</v>
-      </c>
-      <c r="P157" s="10" t="s">
-        <v>392</v>
-      </c>
-      <c r="Q157" s="9">
-        <v>46339</v>
-      </c>
-      <c r="R157" s="9">
-        <v>46349</v>
-      </c>
-      <c r="S157" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T157" s="10">
-        <v>0</v>
-      </c>
-      <c r="U157" s="11" t="s">
         <v>57</v>
       </c>
     </row>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1815" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1813" uniqueCount="394">
   <si>
     <t>50001559 - FERROVIAL</t>
   </si>
@@ -92,9 +92,6 @@
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>Tarea Terminada</t>
   </si>
   <si>
     <t>1215506708202451</t>
@@ -138,6 +135,9 @@
     <t>Baja</t>
   </si>
   <si>
+    <t>Tarea Terminada</t>
+  </si>
+  <si>
     <t>1215506781516040</t>
   </si>
   <si>
@@ -250,9 +250,6 @@
     <t>Ingenieria basica Rodete,Ingenieria Detalle,Ingenieria Basica Motor</t>
   </si>
   <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
     <t>1215506984569012</t>
   </si>
   <si>
@@ -347,6 +344,9 @@
   </si>
   <si>
     <t>Generación OC materiales corte Laser ot 4342 -4344,Propuesta compras:</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1215506984624491</t>
@@ -1288,17 +1288,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF62d26f"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFBFBFBF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF62d26f"/>
       </patternFill>
     </fill>
     <fill>
@@ -1369,8 +1369,8 @@
     <xf numFmtId="14" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1867,7 +1867,7 @@
         <v>46190.67646162037</v>
       </c>
       <c r="D4" s="5">
-        <v>46190.67647303241</v>
+        <v>46191.77859822917</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1902,74 +1902,70 @@
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
       <c r="S4" s="6"/>
-      <c r="T4" s="6">
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="8">
+        <v>46181.60880893518</v>
+      </c>
+      <c r="C5" s="8">
+        <v>46190.675863854165</v>
+      </c>
+      <c r="D5" s="8">
+        <v>46190.676329525464</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="9"/>
+      <c r="J5" s="8">
+        <v>46161</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="P5" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>46161</v>
+      </c>
+      <c r="R5" s="8">
+        <v>46161</v>
+      </c>
+      <c r="S5" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T5" s="9">
         <v>1</v>
       </c>
-      <c r="U4" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="9">
-        <v>46181.60880893518</v>
-      </c>
-      <c r="C5" s="9">
-        <v>46190.675863854165</v>
-      </c>
-      <c r="D5" s="9">
-        <v>46190.676329525464</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H5" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="10"/>
-      <c r="J5" s="9">
-        <v>46161</v>
-      </c>
-      <c r="K5" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L5" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="M5" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N5" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="O5" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="P5" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q5" s="9">
-        <v>46161</v>
-      </c>
-      <c r="R5" s="9">
-        <v>46161</v>
-      </c>
-      <c r="S5" s="7" t="s">
+      <c r="U5" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="T5" s="10">
-        <v>1</v>
-      </c>
-      <c r="U5" s="7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -1992,10 +1988,10 @@
         <v>26</v>
       </c>
       <c r="G6" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="6" t="s">
         <v>30</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>31</v>
       </c>
       <c r="I6" s="6"/>
       <c r="J6" s="5">
@@ -2005,7 +2001,7 @@
         <v>26</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M6" s="6" t="s">
         <v>26</v>
@@ -2025,77 +2021,77 @@
       <c r="R6" s="5">
         <v>46161</v>
       </c>
-      <c r="S6" s="7" t="s">
-        <v>33</v>
+      <c r="S6" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T6" s="6">
         <v>1</v>
       </c>
-      <c r="U6" s="7" t="s">
-        <v>27</v>
+      <c r="U6" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="8">
         <v>46181.60881648149</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="8">
         <v>46190.67642019676</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="8">
         <v>46190.67643417824</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="10" t="s">
+      <c r="F7" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H7" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I7" s="10"/>
-      <c r="J7" s="9">
+      <c r="I7" s="9"/>
+      <c r="J7" s="8">
         <v>46161</v>
       </c>
-      <c r="K7" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L7" s="10" t="s">
+      <c r="K7" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M7" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N7" s="10" t="s">
+      <c r="M7" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N7" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="O7" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="P7" s="10" t="s">
+      <c r="O7" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="P7" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="Q7" s="9">
+      <c r="Q7" s="8">
         <v>46161</v>
       </c>
-      <c r="R7" s="9">
+      <c r="R7" s="8">
         <v>46161</v>
       </c>
-      <c r="S7" s="7" t="s">
+      <c r="S7" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T7" s="9">
+        <v>1</v>
+      </c>
+      <c r="U7" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="T7" s="10">
-        <v>1</v>
-      </c>
-      <c r="U7" s="7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
@@ -2118,10 +2114,10 @@
         <v>26</v>
       </c>
       <c r="G8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" s="6" t="s">
         <v>30</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>31</v>
       </c>
       <c r="I8" s="6"/>
       <c r="J8" s="5">
@@ -2151,62 +2147,62 @@
       <c r="R8" s="5">
         <v>46161</v>
       </c>
-      <c r="S8" s="7" t="s">
-        <v>33</v>
+      <c r="S8" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T8" s="6">
         <v>1</v>
       </c>
-      <c r="U8" s="7" t="s">
-        <v>27</v>
+      <c r="U8" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="8">
         <v>46181.60863523148</v>
       </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="9">
+      <c r="C9" s="9"/>
+      <c r="D9" s="8">
         <v>46190.6778103588</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="G9" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L9" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M9" s="10" t="s">
+      <c r="G9" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M9" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="N9" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O9" s="10" t="s">
+      <c r="N9" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="O9" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="P9" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q9" s="10"/>
-      <c r="R9" s="10"/>
-      <c r="S9" s="10"/>
-      <c r="T9" s="10"/>
-      <c r="U9" s="10"/>
+      <c r="P9" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q9" s="9"/>
+      <c r="R9" s="9"/>
+      <c r="S9" s="9"/>
+      <c r="T9" s="9"/>
+      <c r="U9" s="9"/>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
@@ -2263,73 +2259,73 @@
       <c r="R10" s="5">
         <v>46167</v>
       </c>
-      <c r="S10" s="7" t="s">
-        <v>33</v>
+      <c r="S10" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T10" s="6">
         <v>1</v>
       </c>
-      <c r="U10" s="7" t="s">
-        <v>27</v>
+      <c r="U10" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11" s="8">
         <v>46181.60882959491</v>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="9">
+      <c r="C11" s="9"/>
+      <c r="D11" s="8">
         <v>46182.62580337963</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F11" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="10" t="s">
+      <c r="F11" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="I11" s="9">
+      <c r="I11" s="8">
         <v>46230</v>
       </c>
-      <c r="J11" s="9">
+      <c r="J11" s="8">
         <v>46238</v>
       </c>
-      <c r="K11" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L11" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M11" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N11" s="10" t="s">
+      <c r="K11" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N11" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="O11" s="10" t="s">
+      <c r="O11" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="P11" s="10" t="s">
+      <c r="P11" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="Q11" s="9">
+      <c r="Q11" s="8">
         <v>46230</v>
       </c>
-      <c r="R11" s="9">
+      <c r="R11" s="8">
         <v>46238</v>
       </c>
-      <c r="S11" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T11" s="10">
+      <c r="S11" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T11" s="9">
         <v>0</v>
       </c>
       <c r="U11" s="11" t="s">
@@ -2390,57 +2386,57 @@
       <c r="U12" s="6"/>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="8">
         <v>46181.61813184028</v>
       </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="9">
+      <c r="C13" s="9"/>
+      <c r="D13" s="8">
         <v>46182.625892881944</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="F13" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G13" s="10" t="s">
+      <c r="F13" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" s="8">
         <v>46230</v>
       </c>
-      <c r="J13" s="9">
+      <c r="J13" s="8">
         <v>46238</v>
       </c>
-      <c r="K13" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L13" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M13" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N13" s="10" t="s">
+      <c r="K13" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N13" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="O13" s="10" t="s">
+      <c r="O13" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="P13" s="10" t="s">
+      <c r="P13" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="Q13" s="10"/>
-      <c r="R13" s="10"/>
-      <c r="S13" s="10"/>
-      <c r="T13" s="10"/>
-      <c r="U13" s="10"/>
+      <c r="Q13" s="9"/>
+      <c r="R13" s="9"/>
+      <c r="S13" s="9"/>
+      <c r="T13" s="9"/>
+      <c r="U13" s="9"/>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
@@ -2451,7 +2447,7 @@
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46191.67894028935</v>
+        <v>46191.77864815972</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>65</v>
@@ -2487,78 +2483,76 @@
       <c r="R14" s="6"/>
       <c r="S14" s="6"/>
       <c r="T14" s="6"/>
-      <c r="U14" s="12" t="s">
+      <c r="U14" s="6"/>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
+      <c r="B15" s="8">
+        <v>46181.60883864583</v>
+      </c>
+      <c r="C15" s="8">
+        <v>46190.67744403935</v>
+      </c>
+      <c r="D15" s="8">
+        <v>46191.67892994213</v>
+      </c>
+      <c r="E15" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="B15" s="9">
-        <v>46181.60883864583</v>
-      </c>
-      <c r="C15" s="9">
-        <v>46190.67744403935</v>
-      </c>
-      <c r="D15" s="9">
-        <v>46191.67892994213</v>
-      </c>
-      <c r="E15" s="10" t="s">
+      <c r="F15" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15" s="8">
+        <v>46162</v>
+      </c>
+      <c r="J15" s="8">
+        <v>46164</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L15" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="F15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I15" s="9">
+      <c r="M15" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N15" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="O15" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="P15" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q15" s="8">
         <v>46162</v>
       </c>
-      <c r="J15" s="9">
+      <c r="R15" s="8">
         <v>46164</v>
       </c>
-      <c r="K15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L15" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="M15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N15" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="O15" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="P15" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q15" s="9">
-        <v>46162</v>
-      </c>
-      <c r="R15" s="9">
-        <v>46164</v>
-      </c>
-      <c r="S15" s="7" t="s">
+      <c r="S15" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T15" s="9">
+        <v>1</v>
+      </c>
+      <c r="U15" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="T15" s="10">
-        <v>1</v>
-      </c>
-      <c r="U15" s="7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B16" s="5">
         <v>46181.60884395833</v>
@@ -2570,16 +2564,16 @@
         <v>46191.67892980324</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G16" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>30</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>31</v>
       </c>
       <c r="I16" s="5">
         <v>46162</v>
@@ -2591,7 +2585,7 @@
         <v>26</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M16" s="6" t="s">
         <v>26</v>
@@ -2603,7 +2597,7 @@
         <v>37</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q16" s="5">
         <v>46162</v>
@@ -2611,84 +2605,84 @@
       <c r="R16" s="5">
         <v>46171</v>
       </c>
-      <c r="S16" s="7" t="s">
-        <v>33</v>
+      <c r="S16" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T16" s="6">
         <v>1</v>
       </c>
-      <c r="U16" s="7" t="s">
-        <v>27</v>
+      <c r="U16" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="8">
+        <v>46181.608850046294</v>
+      </c>
+      <c r="C17" s="8">
+        <v>46190.67745870371</v>
+      </c>
+      <c r="D17" s="8">
+        <v>46191.67892980324</v>
+      </c>
+      <c r="E17" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="B17" s="9">
-        <v>46181.608850046294</v>
-      </c>
-      <c r="C17" s="9">
-        <v>46190.67745870371</v>
-      </c>
-      <c r="D17" s="9">
-        <v>46191.67892980324</v>
-      </c>
-      <c r="E17" s="10" t="s">
+      <c r="F17" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" s="8">
+        <v>46162</v>
+      </c>
+      <c r="J17" s="8">
+        <v>46171</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M17" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N17" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="O17" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="P17" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="F17" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I17" s="9">
+      <c r="Q17" s="8">
         <v>46162</v>
       </c>
-      <c r="J17" s="9">
+      <c r="R17" s="8">
         <v>46171</v>
       </c>
-      <c r="K17" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L17" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M17" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N17" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="O17" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="P17" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q17" s="9">
-        <v>46162</v>
-      </c>
-      <c r="R17" s="9">
-        <v>46171</v>
-      </c>
-      <c r="S17" s="7" t="s">
+      <c r="S17" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T17" s="9">
+        <v>1</v>
+      </c>
+      <c r="U17" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="T17" s="10">
-        <v>1</v>
-      </c>
-      <c r="U17" s="7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B18" s="5">
         <v>46181.60864670139</v>
@@ -2698,7 +2692,7 @@
         <v>46190.67771045139</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>25</v>
@@ -2722,7 +2716,7 @@
         <v>26</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P18" s="6" t="s">
         <v>26</v>
@@ -2734,73 +2728,73 @@
       <c r="U18" s="6"/>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B19" s="8">
+        <v>46181.608864236114</v>
+      </c>
+      <c r="C19" s="8">
+        <v>46190.677672986116</v>
+      </c>
+      <c r="D19" s="8">
+        <v>46190.88639424769</v>
+      </c>
+      <c r="E19" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="B19" s="9">
-        <v>46181.608864236114</v>
-      </c>
-      <c r="C19" s="9">
-        <v>46190.677672986116</v>
-      </c>
-      <c r="D19" s="9">
-        <v>46190.88639424769</v>
-      </c>
-      <c r="E19" s="10" t="s">
+      <c r="F19" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" s="8">
+        <v>46167</v>
+      </c>
+      <c r="J19" s="8">
+        <v>46168</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M19" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N19" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="O19" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="P19" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="F19" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I19" s="9">
+      <c r="Q19" s="8">
         <v>46167</v>
       </c>
-      <c r="J19" s="9">
+      <c r="R19" s="8">
         <v>46168</v>
       </c>
-      <c r="K19" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L19" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M19" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N19" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="O19" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="P19" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q19" s="9">
-        <v>46167</v>
-      </c>
-      <c r="R19" s="9">
-        <v>46168</v>
-      </c>
-      <c r="S19" s="7" t="s">
+      <c r="S19" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T19" s="9">
+        <v>1</v>
+      </c>
+      <c r="U19" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="T19" s="10">
-        <v>1</v>
-      </c>
-      <c r="U19" s="7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B20" s="5">
         <v>46181.60886979167</v>
@@ -2812,16 +2806,16 @@
         <v>46190.88638454861</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H20" s="6" t="s">
         <v>30</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>31</v>
       </c>
       <c r="I20" s="5">
         <v>46174</v>
@@ -2839,13 +2833,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Q20" s="5">
         <v>46174</v>
@@ -2853,82 +2847,82 @@
       <c r="R20" s="5">
         <v>46175</v>
       </c>
-      <c r="S20" s="7" t="s">
-        <v>33</v>
+      <c r="S20" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T20" s="6">
         <v>1</v>
       </c>
-      <c r="U20" s="7" t="s">
-        <v>27</v>
+      <c r="U20" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21" s="8">
+        <v>46181.60887520833</v>
+      </c>
+      <c r="C21" s="9"/>
+      <c r="D21" s="8">
+        <v>46190.886384502315</v>
+      </c>
+      <c r="E21" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="B21" s="9">
-        <v>46181.60887520833</v>
-      </c>
-      <c r="C21" s="10"/>
-      <c r="D21" s="9">
-        <v>46190.886384502315</v>
-      </c>
-      <c r="E21" s="10" t="s">
+      <c r="F21" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="F21" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G21" s="10" t="s">
+      <c r="H21" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="I21" s="8">
+        <v>46174</v>
+      </c>
+      <c r="J21" s="8">
+        <v>46175</v>
+      </c>
+      <c r="K21" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M21" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N21" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="O21" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="P21" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="H21" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="I21" s="9">
+      <c r="Q21" s="8">
         <v>46174</v>
       </c>
-      <c r="J21" s="9">
+      <c r="R21" s="8">
         <v>46175</v>
       </c>
-      <c r="K21" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L21" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M21" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N21" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="O21" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="P21" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q21" s="9">
-        <v>46174</v>
-      </c>
-      <c r="R21" s="9">
-        <v>46175</v>
-      </c>
-      <c r="S21" s="7" t="s">
+      <c r="S21" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T21" s="9">
+        <v>1</v>
+      </c>
+      <c r="U21" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="T21" s="10">
-        <v>1</v>
-      </c>
-      <c r="U21" s="7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B22" s="5">
         <v>46181.60888054398</v>
@@ -2938,16 +2932,16 @@
         <v>46191.67365563658</v>
       </c>
       <c r="E22" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="F22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G22" s="6" t="s">
+      <c r="H22" s="6" t="s">
         <v>94</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>95</v>
       </c>
       <c r="I22" s="5">
         <v>46248</v>
@@ -2965,13 +2959,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O22" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="P22" s="6" t="s">
         <v>96</v>
-      </c>
-      <c r="P22" s="6" t="s">
-        <v>97</v>
       </c>
       <c r="Q22" s="5">
         <v>46248</v>
@@ -2979,77 +2973,77 @@
       <c r="R22" s="5">
         <v>46251</v>
       </c>
-      <c r="S22" s="7" t="s">
-        <v>33</v>
+      <c r="S22" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T22" s="6">
         <v>0</v>
       </c>
       <c r="U22" s="12" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="B23" s="9">
+      <c r="B23" s="8">
         <v>46181.60888559028</v>
       </c>
-      <c r="C23" s="10"/>
-      <c r="D23" s="9">
+      <c r="C23" s="9"/>
+      <c r="D23" s="8">
         <v>46191.67366451389</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="E23" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="F23" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G23" s="10" t="s">
+      <c r="F23" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H23" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="H23" s="10" t="s">
+      <c r="I23" s="8">
+        <v>46248</v>
+      </c>
+      <c r="J23" s="8">
+        <v>46251</v>
+      </c>
+      <c r="K23" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M23" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N23" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="O23" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="I23" s="9">
+      <c r="P23" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q23" s="8">
         <v>46248</v>
       </c>
-      <c r="J23" s="9">
+      <c r="R23" s="8">
         <v>46251</v>
       </c>
-      <c r="K23" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L23" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M23" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N23" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="O23" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="P23" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q23" s="9">
-        <v>46248</v>
-      </c>
-      <c r="R23" s="9">
-        <v>46251</v>
-      </c>
-      <c r="S23" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T23" s="10">
+      <c r="S23" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T23" s="9">
         <v>0</v>
       </c>
       <c r="U23" s="12" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
@@ -3070,10 +3064,10 @@
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>94</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>95</v>
       </c>
       <c r="I24" s="5">
         <v>46248</v>
@@ -3091,10 +3085,10 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>103</v>
@@ -3105,77 +3099,77 @@
       <c r="R24" s="5">
         <v>46251</v>
       </c>
-      <c r="S24" s="7" t="s">
-        <v>33</v>
+      <c r="S24" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
       <c r="U24" s="12" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="B25" s="9">
+      <c r="B25" s="8">
         <v>46181.6088934375</v>
       </c>
-      <c r="C25" s="10"/>
-      <c r="D25" s="9">
+      <c r="C25" s="9"/>
+      <c r="D25" s="8">
         <v>46191.67370431713</v>
       </c>
-      <c r="E25" s="10" t="s">
+      <c r="E25" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="F25" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G25" s="10" t="s">
+      <c r="F25" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H25" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="H25" s="10" t="s">
+      <c r="I25" s="8">
+        <v>46248</v>
+      </c>
+      <c r="J25" s="8">
+        <v>46251</v>
+      </c>
+      <c r="K25" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L25" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M25" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N25" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="O25" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="I25" s="9">
+      <c r="P25" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q25" s="8">
         <v>46248</v>
       </c>
-      <c r="J25" s="9">
+      <c r="R25" s="8">
         <v>46251</v>
       </c>
-      <c r="K25" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L25" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M25" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N25" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="O25" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="P25" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q25" s="9">
-        <v>46248</v>
-      </c>
-      <c r="R25" s="9">
-        <v>46251</v>
-      </c>
-      <c r="S25" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T25" s="10">
+      <c r="S25" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T25" s="9">
         <v>0</v>
       </c>
       <c r="U25" s="12" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
@@ -3198,10 +3192,10 @@
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>30</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>31</v>
       </c>
       <c r="I26" s="5">
         <v>46168</v>
@@ -3219,7 +3213,7 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>47</v>
@@ -3233,62 +3227,62 @@
       <c r="R26" s="5">
         <v>46169</v>
       </c>
-      <c r="S26" s="7" t="s">
-        <v>33</v>
+      <c r="S26" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T26" s="6">
         <v>1</v>
       </c>
-      <c r="U26" s="7" t="s">
-        <v>27</v>
+      <c r="U26" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="B27" s="9">
+      <c r="B27" s="8">
         <v>46190.88204489583</v>
       </c>
-      <c r="C27" s="10"/>
-      <c r="D27" s="9">
+      <c r="C27" s="9"/>
+      <c r="D27" s="8">
         <v>46190.88358329861</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="E27" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="F27" s="10" t="s">
+      <c r="F27" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="G27" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
-      <c r="K27" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L27" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M27" s="10" t="s">
+      <c r="G27" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M27" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="N27" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O27" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="P27" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q27" s="10"/>
-      <c r="R27" s="10"/>
-      <c r="S27" s="10"/>
-      <c r="T27" s="10"/>
-      <c r="U27" s="10"/>
+      <c r="N27" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="O27" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="P27" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q27" s="9"/>
+      <c r="R27" s="9"/>
+      <c r="S27" s="9"/>
+      <c r="T27" s="9"/>
+      <c r="U27" s="9"/>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
@@ -3308,10 +3302,10 @@
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I28" s="5">
         <v>46169</v>
@@ -3332,7 +3326,7 @@
         <v>111</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>26</v>
@@ -3343,77 +3337,77 @@
       <c r="R28" s="5">
         <v>46175</v>
       </c>
-      <c r="S28" s="7" t="s">
-        <v>33</v>
+      <c r="S28" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
       <c r="U28" s="12" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="B29" s="9">
+      <c r="B29" s="8">
         <v>46190.88327185185</v>
       </c>
-      <c r="C29" s="10"/>
-      <c r="D29" s="9">
+      <c r="C29" s="9"/>
+      <c r="D29" s="8">
         <v>46191.6737259838</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="E29" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="F29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="H29" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="I29" s="9">
+      <c r="F29" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="I29" s="8">
         <v>46176</v>
       </c>
-      <c r="J29" s="9">
+      <c r="J29" s="8">
         <v>46182</v>
       </c>
-      <c r="K29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N29" s="10" t="s">
+      <c r="K29" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L29" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M29" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N29" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="O29" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="P29" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q29" s="9">
+      <c r="O29" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="P29" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q29" s="8">
         <v>46176</v>
       </c>
-      <c r="R29" s="9">
+      <c r="R29" s="8">
         <v>46182</v>
       </c>
-      <c r="S29" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T29" s="10">
+      <c r="S29" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T29" s="9">
         <v>0</v>
       </c>
       <c r="U29" s="12" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -3434,10 +3428,10 @@
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I30" s="5">
         <v>46176</v>
@@ -3458,7 +3452,7 @@
         <v>111</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>26</v>
@@ -3469,8 +3463,8 @@
       <c r="R30" s="5">
         <v>46182</v>
       </c>
-      <c r="S30" s="7" t="s">
-        <v>33</v>
+      <c r="S30" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
@@ -3480,51 +3474,51 @@
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="B31" s="9">
+      <c r="B31" s="8">
         <v>46181.608652256946</v>
       </c>
-      <c r="C31" s="10"/>
-      <c r="D31" s="9">
+      <c r="C31" s="9"/>
+      <c r="D31" s="8">
         <v>46190.886375057875</v>
       </c>
-      <c r="E31" s="10" t="s">
+      <c r="E31" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="F31" s="10" t="s">
+      <c r="F31" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="G31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H31" s="10"/>
-      <c r="I31" s="10"/>
-      <c r="J31" s="10"/>
-      <c r="K31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M31" s="10" t="s">
+      <c r="G31" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L31" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M31" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="N31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O31" s="10" t="s">
+      <c r="N31" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="O31" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="P31" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q31" s="10"/>
-      <c r="R31" s="10"/>
-      <c r="S31" s="10"/>
-      <c r="T31" s="10"/>
-      <c r="U31" s="10"/>
+      <c r="P31" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q31" s="9"/>
+      <c r="R31" s="9"/>
+      <c r="S31" s="9"/>
+      <c r="T31" s="9"/>
+      <c r="U31" s="9"/>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
@@ -3579,8 +3573,8 @@
       <c r="R32" s="5">
         <v>46225</v>
       </c>
-      <c r="S32" s="7" t="s">
-        <v>33</v>
+      <c r="S32" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
@@ -3590,57 +3584,57 @@
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="B33" s="9">
+      <c r="B33" s="8">
         <v>46181.60901165509</v>
       </c>
-      <c r="C33" s="10"/>
-      <c r="D33" s="9">
+      <c r="C33" s="9"/>
+      <c r="D33" s="8">
         <v>46190.67786118056</v>
       </c>
-      <c r="E33" s="10" t="s">
+      <c r="E33" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="F33" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="10" t="s">
+      <c r="F33" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="H33" s="10" t="s">
+      <c r="H33" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="I33" s="9">
+      <c r="I33" s="8">
         <v>46170</v>
       </c>
-      <c r="J33" s="9">
+      <c r="J33" s="8">
         <v>46176</v>
       </c>
-      <c r="K33" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L33" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M33" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N33" s="10" t="s">
+      <c r="K33" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L33" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M33" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N33" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="O33" s="10" t="s">
+      <c r="O33" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="P33" s="10" t="s">
+      <c r="P33" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="Q33" s="10"/>
-      <c r="R33" s="10"/>
-      <c r="S33" s="10"/>
-      <c r="T33" s="10"/>
-      <c r="U33" s="10"/>
+      <c r="Q33" s="9"/>
+      <c r="R33" s="9"/>
+      <c r="S33" s="9"/>
+      <c r="T33" s="9"/>
+      <c r="U33" s="9"/>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
@@ -3696,62 +3690,62 @@
       <c r="U34" s="6"/>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="B35" s="9">
+      <c r="B35" s="8">
         <v>46181.60902011574</v>
       </c>
-      <c r="C35" s="10"/>
-      <c r="D35" s="9">
+      <c r="C35" s="9"/>
+      <c r="D35" s="8">
         <v>46182.6267959838</v>
       </c>
-      <c r="E35" s="10" t="s">
+      <c r="E35" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="F35" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G35" s="10" t="s">
+      <c r="F35" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="H35" s="10" t="s">
+      <c r="H35" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="I35" s="9">
+      <c r="I35" s="8">
         <v>46252</v>
       </c>
-      <c r="J35" s="9">
+      <c r="J35" s="8">
         <v>46262</v>
       </c>
-      <c r="K35" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L35" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M35" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N35" s="10" t="s">
+      <c r="K35" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L35" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M35" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N35" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="O35" s="10" t="s">
+      <c r="O35" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="P35" s="10" t="s">
+      <c r="P35" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="Q35" s="9">
+      <c r="Q35" s="8">
         <v>46252</v>
       </c>
-      <c r="R35" s="9">
+      <c r="R35" s="8">
         <v>46262</v>
       </c>
-      <c r="S35" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T35" s="10">
+      <c r="S35" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T35" s="9">
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
@@ -3800,15 +3794,15 @@
         <v>120</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>137</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
-      <c r="S36" s="7" t="s">
-        <v>33</v>
+      <c r="S36" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
@@ -3818,58 +3812,58 @@
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="B37" s="9">
+      <c r="B37" s="8">
         <v>46181.609029803236</v>
       </c>
-      <c r="C37" s="10"/>
-      <c r="D37" s="9">
+      <c r="C37" s="9"/>
+      <c r="D37" s="8">
         <v>46182.6267641088</v>
       </c>
-      <c r="E37" s="10" t="s">
+      <c r="E37" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="F37" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G37" s="10" t="s">
+      <c r="F37" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G37" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="H37" s="10" t="s">
+      <c r="H37" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="I37" s="9">
+      <c r="I37" s="8">
         <v>46254</v>
       </c>
-      <c r="J37" s="9">
+      <c r="J37" s="8">
         <v>46262</v>
       </c>
-      <c r="K37" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L37" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M37" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N37" s="10" t="s">
+      <c r="K37" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L37" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M37" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N37" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="O37" s="10" t="s">
+      <c r="O37" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="P37" s="10" t="s">
+      <c r="P37" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="Q37" s="10"/>
-      <c r="R37" s="10"/>
-      <c r="S37" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T37" s="10">
+      <c r="Q37" s="9"/>
+      <c r="R37" s="9"/>
+      <c r="S37" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T37" s="9">
         <v>0</v>
       </c>
       <c r="U37" s="11" t="s">
@@ -3929,8 +3923,8 @@
       <c r="R38" s="5">
         <v>46262</v>
       </c>
-      <c r="S38" s="7" t="s">
-        <v>33</v>
+      <c r="S38" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T38" s="6">
         <v>0</v>
@@ -3940,57 +3934,57 @@
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="B39" s="9">
+      <c r="B39" s="8">
         <v>46181.60903861111</v>
       </c>
-      <c r="C39" s="10"/>
-      <c r="D39" s="9">
+      <c r="C39" s="9"/>
+      <c r="D39" s="8">
         <v>46182.626871608794</v>
       </c>
-      <c r="E39" s="10" t="s">
+      <c r="E39" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="F39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="10" t="s">
+      <c r="F39" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="H39" s="10" t="s">
+      <c r="H39" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="I39" s="9">
+      <c r="I39" s="8">
         <v>46252</v>
       </c>
-      <c r="J39" s="9">
+      <c r="J39" s="8">
         <v>46253</v>
       </c>
-      <c r="K39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N39" s="10" t="s">
+      <c r="K39" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L39" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M39" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N39" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="O39" s="10" t="s">
+      <c r="O39" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="P39" s="10" t="s">
+      <c r="P39" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="Q39" s="10"/>
-      <c r="R39" s="10"/>
-      <c r="S39" s="10"/>
-      <c r="T39" s="10"/>
-      <c r="U39" s="10"/>
+      <c r="Q39" s="9"/>
+      <c r="R39" s="9"/>
+      <c r="S39" s="9"/>
+      <c r="T39" s="9"/>
+      <c r="U39" s="9"/>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
@@ -4046,62 +4040,62 @@
       <c r="U40" s="6"/>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="B41" s="9">
+      <c r="B41" s="8">
         <v>46181.609047164355</v>
       </c>
-      <c r="C41" s="10"/>
-      <c r="D41" s="9">
+      <c r="C41" s="9"/>
+      <c r="D41" s="8">
         <v>46183.70162199074</v>
       </c>
-      <c r="E41" s="10" t="s">
+      <c r="E41" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="F41" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G41" s="10" t="s">
+      <c r="F41" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G41" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="H41" s="10" t="s">
+      <c r="H41" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="I41" s="9">
+      <c r="I41" s="8">
         <v>46252</v>
       </c>
-      <c r="J41" s="9">
+      <c r="J41" s="8">
         <v>46290</v>
       </c>
-      <c r="K41" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L41" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M41" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N41" s="10" t="s">
+      <c r="K41" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L41" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M41" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N41" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="O41" s="10" t="s">
+      <c r="O41" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="P41" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q41" s="9">
+      <c r="P41" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q41" s="8">
         <v>46283</v>
       </c>
-      <c r="R41" s="9">
+      <c r="R41" s="8">
         <v>46290</v>
       </c>
-      <c r="S41" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T41" s="10">
+      <c r="S41" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T41" s="9">
         <v>0</v>
       </c>
       <c r="U41" s="11" t="s">
@@ -4162,57 +4156,57 @@
       <c r="U42" s="6"/>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="B43" s="9">
+      <c r="B43" s="8">
         <v>46181.60905546296</v>
       </c>
-      <c r="C43" s="10"/>
-      <c r="D43" s="9">
+      <c r="C43" s="9"/>
+      <c r="D43" s="8">
         <v>46183.70547770833</v>
       </c>
-      <c r="E43" s="10" t="s">
+      <c r="E43" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="F43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="10" t="s">
+      <c r="F43" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="H43" s="10" t="s">
+      <c r="H43" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="I43" s="9">
+      <c r="I43" s="8">
         <v>46261</v>
       </c>
-      <c r="J43" s="9">
+      <c r="J43" s="8">
         <v>46289</v>
       </c>
-      <c r="K43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M43" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N43" s="10" t="s">
+      <c r="K43" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L43" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M43" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N43" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="O43" s="10" t="s">
+      <c r="O43" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="P43" s="10" t="s">
+      <c r="P43" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="Q43" s="10"/>
-      <c r="R43" s="10"/>
-      <c r="S43" s="10"/>
-      <c r="T43" s="10"/>
-      <c r="U43" s="10"/>
+      <c r="Q43" s="9"/>
+      <c r="R43" s="9"/>
+      <c r="S43" s="9"/>
+      <c r="T43" s="9"/>
+      <c r="U43" s="9"/>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
@@ -4268,62 +4262,62 @@
       <c r="U44" s="6"/>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="B45" s="9">
+      <c r="B45" s="8">
         <v>46181.609063310185</v>
       </c>
-      <c r="C45" s="10"/>
-      <c r="D45" s="9">
+      <c r="C45" s="9"/>
+      <c r="D45" s="8">
         <v>46182.62725847222</v>
       </c>
-      <c r="E45" s="10" t="s">
+      <c r="E45" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="F45" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G45" s="10" t="s">
+      <c r="F45" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G45" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="H45" s="10" t="s">
+      <c r="H45" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="I45" s="9">
+      <c r="I45" s="8">
         <v>46252</v>
       </c>
-      <c r="J45" s="9">
+      <c r="J45" s="8">
         <v>46262</v>
       </c>
-      <c r="K45" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L45" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M45" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N45" s="10" t="s">
+      <c r="K45" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L45" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M45" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N45" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="O45" s="10" t="s">
+      <c r="O45" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="P45" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q45" s="9">
+      <c r="P45" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q45" s="8">
         <v>46252</v>
       </c>
-      <c r="R45" s="9">
+      <c r="R45" s="8">
         <v>46262</v>
       </c>
-      <c r="S45" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T45" s="10">
+      <c r="S45" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T45" s="9">
         <v>0</v>
       </c>
       <c r="U45" s="11" t="s">
@@ -4384,57 +4378,57 @@
       <c r="U46" s="6"/>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="B47" s="9">
+      <c r="B47" s="8">
         <v>46181.60907681713</v>
       </c>
-      <c r="C47" s="10"/>
-      <c r="D47" s="9">
+      <c r="C47" s="9"/>
+      <c r="D47" s="8">
         <v>46182.627201296295</v>
       </c>
-      <c r="E47" s="10" t="s">
+      <c r="E47" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="F47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="10" t="s">
+      <c r="F47" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="H47" s="10" t="s">
+      <c r="H47" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="I47" s="9">
+      <c r="I47" s="8">
         <v>46254</v>
       </c>
-      <c r="J47" s="9">
+      <c r="J47" s="8">
         <v>46262</v>
       </c>
-      <c r="K47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M47" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N47" s="10" t="s">
+      <c r="K47" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L47" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M47" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N47" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="O47" s="10" t="s">
+      <c r="O47" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="P47" s="10" t="s">
+      <c r="P47" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="Q47" s="10"/>
-      <c r="R47" s="10"/>
-      <c r="S47" s="10"/>
-      <c r="T47" s="10"/>
-      <c r="U47" s="10"/>
+      <c r="Q47" s="9"/>
+      <c r="R47" s="9"/>
+      <c r="S47" s="9"/>
+      <c r="T47" s="9"/>
+      <c r="U47" s="9"/>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
@@ -4482,72 +4476,72 @@
       <c r="S48" s="6"/>
       <c r="T48" s="6"/>
       <c r="U48" s="12" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A49" s="8" t="s">
+      <c r="A49" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="B49" s="9">
+      <c r="B49" s="8">
         <v>46181.60908480324</v>
       </c>
-      <c r="C49" s="9">
+      <c r="C49" s="8">
         <v>46190.708245752314</v>
       </c>
-      <c r="D49" s="9">
+      <c r="D49" s="8">
         <v>46190.708260555555</v>
       </c>
-      <c r="E49" s="10" t="s">
+      <c r="E49" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="F49" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G49" s="10" t="s">
+      <c r="F49" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G49" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H49" s="10" t="s">
+      <c r="H49" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="I49" s="9">
+      <c r="I49" s="8">
         <v>46174</v>
       </c>
-      <c r="J49" s="9">
+      <c r="J49" s="8">
         <v>46191</v>
       </c>
-      <c r="K49" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L49" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M49" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N49" s="10" t="s">
+      <c r="K49" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L49" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M49" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N49" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="O49" s="10" t="s">
+      <c r="O49" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="P49" s="10" t="s">
+      <c r="P49" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="Q49" s="9">
+      <c r="Q49" s="8">
         <v>46174</v>
       </c>
-      <c r="R49" s="9">
+      <c r="R49" s="8">
         <v>46191</v>
       </c>
       <c r="S49" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="T49" s="10">
+      <c r="T49" s="9">
         <v>1</v>
       </c>
-      <c r="U49" s="7" t="s">
-        <v>27</v>
+      <c r="U49" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -4594,7 +4588,7 @@
         <v>175</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>182</v>
@@ -4606,59 +4600,59 @@
       <c r="U50" s="6"/>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A51" s="8" t="s">
+      <c r="A51" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="B51" s="9">
+      <c r="B51" s="8">
         <v>46181.60909384259</v>
       </c>
-      <c r="C51" s="9">
+      <c r="C51" s="8">
         <v>46190.70822138889</v>
       </c>
-      <c r="D51" s="9">
+      <c r="D51" s="8">
         <v>46190.7082228125</v>
       </c>
-      <c r="E51" s="10" t="s">
+      <c r="E51" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="F51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G51" s="10" t="s">
+      <c r="F51" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G51" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H51" s="10" t="s">
+      <c r="H51" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="I51" s="9">
+      <c r="I51" s="8">
         <v>46174</v>
       </c>
-      <c r="J51" s="9">
+      <c r="J51" s="8">
         <v>46191</v>
       </c>
-      <c r="K51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M51" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N51" s="10" t="s">
+      <c r="K51" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L51" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M51" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N51" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="O51" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="P51" s="10" t="s">
+      <c r="O51" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="P51" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="Q51" s="10"/>
-      <c r="R51" s="10"/>
-      <c r="S51" s="10"/>
-      <c r="T51" s="10"/>
-      <c r="U51" s="10"/>
+      <c r="Q51" s="9"/>
+      <c r="R51" s="9"/>
+      <c r="S51" s="9"/>
+      <c r="T51" s="9"/>
+      <c r="U51" s="9"/>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
@@ -4704,7 +4698,7 @@
         <v>175</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>187</v>
@@ -4716,59 +4710,59 @@
       <c r="U52" s="6"/>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A53" s="8" t="s">
+      <c r="A53" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="B53" s="9">
+      <c r="B53" s="8">
         <v>46181.612357199076</v>
       </c>
-      <c r="C53" s="9">
+      <c r="C53" s="8">
         <v>46190.70823167824</v>
       </c>
-      <c r="D53" s="9">
+      <c r="D53" s="8">
         <v>46190.708233321755</v>
       </c>
-      <c r="E53" s="10" t="s">
+      <c r="E53" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="F53" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G53" s="10" t="s">
+      <c r="F53" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H53" s="10" t="s">
+      <c r="H53" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="I53" s="9">
+      <c r="I53" s="8">
         <v>46174</v>
       </c>
-      <c r="J53" s="9">
+      <c r="J53" s="8">
         <v>46191</v>
       </c>
-      <c r="K53" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L53" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M53" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N53" s="10" t="s">
+      <c r="K53" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L53" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M53" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N53" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="O53" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="P53" s="10" t="s">
+      <c r="O53" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="P53" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="Q53" s="10"/>
-      <c r="R53" s="10"/>
-      <c r="S53" s="10"/>
-      <c r="T53" s="10"/>
-      <c r="U53" s="10"/>
+      <c r="Q53" s="9"/>
+      <c r="R53" s="9"/>
+      <c r="S53" s="9"/>
+      <c r="T53" s="9"/>
+      <c r="U53" s="9"/>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
@@ -4825,70 +4819,70 @@
       <c r="R54" s="5">
         <v>46246</v>
       </c>
-      <c r="S54" s="7" t="s">
-        <v>33</v>
+      <c r="S54" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T54" s="6">
         <v>1</v>
       </c>
-      <c r="U54" s="7" t="s">
-        <v>27</v>
+      <c r="U54" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A55" s="8" t="s">
+      <c r="A55" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="B55" s="9">
+      <c r="B55" s="8">
         <v>46181.60910252314</v>
       </c>
-      <c r="C55" s="9">
+      <c r="C55" s="8">
         <v>46191.54270648149</v>
       </c>
-      <c r="D55" s="9">
+      <c r="D55" s="8">
         <v>46191.54270819444</v>
       </c>
-      <c r="E55" s="10" t="s">
+      <c r="E55" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="F55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G55" s="10" t="s">
+      <c r="F55" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G55" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H55" s="10" t="s">
+      <c r="H55" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="I55" s="9">
+      <c r="I55" s="8">
         <v>46227</v>
       </c>
-      <c r="J55" s="9">
+      <c r="J55" s="8">
         <v>46246</v>
       </c>
-      <c r="K55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M55" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N55" s="10" t="s">
+      <c r="K55" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L55" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M55" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N55" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="O55" s="10" t="s">
+      <c r="O55" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="P55" s="10" t="s">
+      <c r="P55" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="Q55" s="10"/>
-      <c r="R55" s="10"/>
-      <c r="S55" s="10"/>
-      <c r="T55" s="10"/>
-      <c r="U55" s="10"/>
+      <c r="Q55" s="9"/>
+      <c r="R55" s="9"/>
+      <c r="S55" s="9"/>
+      <c r="T55" s="9"/>
+      <c r="U55" s="9"/>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
@@ -4946,59 +4940,59 @@
       <c r="U56" s="6"/>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A57" s="8" t="s">
+      <c r="A57" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="B57" s="9">
+      <c r="B57" s="8">
         <v>46181.61393570602</v>
       </c>
-      <c r="C57" s="9">
+      <c r="C57" s="8">
         <v>46190.70842026621</v>
       </c>
-      <c r="D57" s="9">
+      <c r="D57" s="8">
         <v>46190.70842170139</v>
       </c>
-      <c r="E57" s="10" t="s">
+      <c r="E57" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="F57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G57" s="10" t="s">
+      <c r="F57" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G57" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H57" s="10" t="s">
+      <c r="H57" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="I57" s="9">
+      <c r="I57" s="8">
         <v>46227</v>
       </c>
-      <c r="J57" s="9">
+      <c r="J57" s="8">
         <v>46246</v>
       </c>
-      <c r="K57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M57" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N57" s="10" t="s">
+      <c r="K57" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L57" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M57" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N57" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="O57" s="10" t="s">
+      <c r="O57" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="P57" s="10" t="s">
+      <c r="P57" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="Q57" s="10"/>
-      <c r="R57" s="10"/>
-      <c r="S57" s="10"/>
-      <c r="T57" s="10"/>
-      <c r="U57" s="10"/>
+      <c r="Q57" s="9"/>
+      <c r="R57" s="9"/>
+      <c r="S57" s="9"/>
+      <c r="T57" s="9"/>
+      <c r="U57" s="9"/>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
@@ -5056,68 +5050,68 @@
       <c r="U58" s="6"/>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A59" s="8" t="s">
+      <c r="A59" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="B59" s="9">
+      <c r="B59" s="8">
         <v>46181.60911329861</v>
       </c>
-      <c r="C59" s="9">
+      <c r="C59" s="8">
         <v>46191.54538693287</v>
       </c>
-      <c r="D59" s="9">
+      <c r="D59" s="8">
         <v>46191.54539826389</v>
       </c>
-      <c r="E59" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="F59" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G59" s="10" t="s">
+      <c r="E59" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G59" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H59" s="10" t="s">
+      <c r="H59" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="I59" s="9">
+      <c r="I59" s="8">
         <v>46247</v>
       </c>
-      <c r="J59" s="9">
+      <c r="J59" s="8">
         <v>46247</v>
       </c>
-      <c r="K59" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L59" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M59" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N59" s="10" t="s">
+      <c r="K59" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L59" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M59" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N59" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="O59" s="10" t="s">
+      <c r="O59" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="P59" s="10" t="s">
+      <c r="P59" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="Q59" s="9">
+      <c r="Q59" s="8">
         <v>46247</v>
       </c>
-      <c r="R59" s="9">
+      <c r="R59" s="8">
         <v>46247</v>
       </c>
-      <c r="S59" s="7" t="s">
+      <c r="S59" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T59" s="9">
+        <v>1</v>
+      </c>
+      <c r="U59" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="T59" s="10">
-        <v>1</v>
-      </c>
-      <c r="U59" s="7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -5159,13 +5153,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>181</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5174,57 +5168,57 @@
       <c r="U60" s="6"/>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A61" s="8" t="s">
+      <c r="A61" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="B61" s="9">
+      <c r="B61" s="8">
         <v>46181.60912782408</v>
       </c>
-      <c r="C61" s="9">
+      <c r="C61" s="8">
         <v>46191.54537241899</v>
       </c>
-      <c r="D61" s="9">
+      <c r="D61" s="8">
         <v>46191.54537386574</v>
       </c>
-      <c r="E61" s="10" t="s">
+      <c r="E61" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="F61" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G61" s="10" t="s">
+      <c r="F61" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G61" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H61" s="10" t="s">
+      <c r="H61" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="I61" s="10"/>
-      <c r="J61" s="9">
+      <c r="I61" s="9"/>
+      <c r="J61" s="8">
         <v>46247</v>
       </c>
-      <c r="K61" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L61" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M61" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N61" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="O61" s="10" t="s">
+      <c r="K61" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L61" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M61" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N61" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="O61" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="P61" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q61" s="10"/>
-      <c r="R61" s="10"/>
-      <c r="S61" s="10"/>
-      <c r="T61" s="10"/>
-      <c r="U61" s="10"/>
+      <c r="P61" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q61" s="9"/>
+      <c r="R61" s="9"/>
+      <c r="S61" s="9"/>
+      <c r="T61" s="9"/>
+      <c r="U61" s="9"/>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
@@ -5265,7 +5259,7 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>187</v>
@@ -5280,57 +5274,57 @@
       <c r="U62" s="6"/>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A63" s="8" t="s">
+      <c r="A63" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="B63" s="9">
+      <c r="B63" s="8">
         <v>46181.61419627315</v>
       </c>
-      <c r="C63" s="9">
+      <c r="C63" s="8">
         <v>46190.72172868055</v>
       </c>
-      <c r="D63" s="9">
+      <c r="D63" s="8">
         <v>46190.7217299537</v>
       </c>
-      <c r="E63" s="10" t="s">
+      <c r="E63" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="F63" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G63" s="10" t="s">
+      <c r="F63" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G63" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="H63" s="10" t="s">
+      <c r="H63" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="I63" s="10"/>
-      <c r="J63" s="9">
+      <c r="I63" s="9"/>
+      <c r="J63" s="8">
         <v>46247</v>
       </c>
-      <c r="K63" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L63" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M63" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N63" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="O63" s="10" t="s">
+      <c r="K63" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L63" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M63" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N63" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="O63" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="P63" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q63" s="10"/>
-      <c r="R63" s="10"/>
-      <c r="S63" s="10"/>
-      <c r="T63" s="10"/>
-      <c r="U63" s="10"/>
+      <c r="P63" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q63" s="9"/>
+      <c r="R63" s="9"/>
+      <c r="S63" s="9"/>
+      <c r="T63" s="9"/>
+      <c r="U63" s="9"/>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
@@ -5385,8 +5379,8 @@
       <c r="R64" s="5">
         <v>46322</v>
       </c>
-      <c r="S64" s="7" t="s">
-        <v>33</v>
+      <c r="S64" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T64" s="6">
         <v>0</v>
@@ -5396,57 +5390,57 @@
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A65" s="8" t="s">
+      <c r="A65" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="B65" s="9">
+      <c r="B65" s="8">
         <v>46181.609135833336</v>
       </c>
-      <c r="C65" s="10"/>
-      <c r="D65" s="9">
+      <c r="C65" s="9"/>
+      <c r="D65" s="8">
         <v>46182.63311847222</v>
       </c>
-      <c r="E65" s="10" t="s">
+      <c r="E65" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="F65" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G65" s="10" t="s">
+      <c r="F65" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G65" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="H65" s="10" t="s">
+      <c r="H65" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="I65" s="9">
+      <c r="I65" s="8">
         <v>46322</v>
       </c>
-      <c r="J65" s="9">
+      <c r="J65" s="8">
         <v>46322</v>
       </c>
-      <c r="K65" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L65" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M65" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N65" s="10" t="s">
+      <c r="K65" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L65" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M65" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N65" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="O65" s="10" t="s">
+      <c r="O65" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="P65" s="10" t="s">
+      <c r="P65" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="Q65" s="10"/>
-      <c r="R65" s="10"/>
-      <c r="S65" s="10"/>
-      <c r="T65" s="10"/>
-      <c r="U65" s="10"/>
+      <c r="Q65" s="9"/>
+      <c r="R65" s="9"/>
+      <c r="S65" s="9"/>
+      <c r="T65" s="9"/>
+      <c r="U65" s="9"/>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
@@ -5502,51 +5496,51 @@
       <c r="U66" s="6"/>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A67" s="8" t="s">
+      <c r="A67" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="B67" s="9">
+      <c r="B67" s="8">
         <v>46181.60918671296</v>
       </c>
-      <c r="C67" s="10"/>
-      <c r="D67" s="9">
+      <c r="C67" s="9"/>
+      <c r="D67" s="8">
         <v>46181.77983537037</v>
       </c>
-      <c r="E67" s="10" t="s">
+      <c r="E67" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="F67" s="10" t="s">
+      <c r="F67" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="G67" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H67" s="10"/>
-      <c r="I67" s="10"/>
-      <c r="J67" s="10"/>
-      <c r="K67" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L67" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M67" s="10" t="s">
+      <c r="G67" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H67" s="9"/>
+      <c r="I67" s="9"/>
+      <c r="J67" s="9"/>
+      <c r="K67" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L67" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M67" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="N67" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O67" s="10" t="s">
+      <c r="N67" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="O67" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="P67" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q67" s="10"/>
-      <c r="R67" s="10"/>
-      <c r="S67" s="10"/>
-      <c r="T67" s="10"/>
-      <c r="U67" s="10"/>
+      <c r="P67" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q67" s="9"/>
+      <c r="R67" s="9"/>
+      <c r="S67" s="9"/>
+      <c r="T67" s="9"/>
+      <c r="U67" s="9"/>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
@@ -5601,8 +5595,8 @@
       <c r="R68" s="5">
         <v>46253</v>
       </c>
-      <c r="S68" s="7" t="s">
-        <v>33</v>
+      <c r="S68" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T68" s="6">
         <v>0</v>
@@ -5612,62 +5606,62 @@
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A69" s="8" t="s">
+      <c r="A69" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="B69" s="9">
+      <c r="B69" s="8">
         <v>46181.609201921296</v>
       </c>
-      <c r="C69" s="10"/>
-      <c r="D69" s="9">
+      <c r="C69" s="9"/>
+      <c r="D69" s="8">
         <v>46182.63583637732</v>
       </c>
-      <c r="E69" s="10" t="s">
+      <c r="E69" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="F69" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G69" s="10" t="s">
+      <c r="F69" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G69" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="H69" s="10" t="s">
+      <c r="H69" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="I69" s="9">
+      <c r="I69" s="8">
         <v>46254</v>
       </c>
-      <c r="J69" s="9">
+      <c r="J69" s="8">
         <v>46255</v>
       </c>
-      <c r="K69" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L69" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M69" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N69" s="10" t="s">
+      <c r="K69" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L69" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M69" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N69" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="O69" s="10" t="s">
+      <c r="O69" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="P69" s="10" t="s">
+      <c r="P69" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="Q69" s="9">
+      <c r="Q69" s="8">
         <v>46254</v>
       </c>
-      <c r="R69" s="9">
+      <c r="R69" s="8">
         <v>46255</v>
       </c>
-      <c r="S69" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T69" s="10">
+      <c r="S69" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T69" s="9">
         <v>0</v>
       </c>
       <c r="U69" s="11" t="s">
@@ -5727,8 +5721,8 @@
       <c r="R70" s="5">
         <v>46253</v>
       </c>
-      <c r="S70" s="7" t="s">
-        <v>33</v>
+      <c r="S70" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T70" s="6">
         <v>0</v>
@@ -5738,62 +5732,62 @@
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A71" s="8" t="s">
+      <c r="A71" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="B71" s="9">
+      <c r="B71" s="8">
         <v>46181.609212870375</v>
       </c>
-      <c r="C71" s="10"/>
-      <c r="D71" s="9">
+      <c r="C71" s="9"/>
+      <c r="D71" s="8">
         <v>46182.63583289352</v>
       </c>
-      <c r="E71" s="10" t="s">
+      <c r="E71" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="F71" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G71" s="10" t="s">
+      <c r="F71" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G71" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="H71" s="10" t="s">
+      <c r="H71" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="I71" s="9">
+      <c r="I71" s="8">
         <v>46254</v>
       </c>
-      <c r="J71" s="9">
+      <c r="J71" s="8">
         <v>46255</v>
       </c>
-      <c r="K71" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L71" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M71" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N71" s="10" t="s">
+      <c r="K71" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L71" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M71" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N71" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="O71" s="10" t="s">
+      <c r="O71" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="P71" s="10" t="s">
+      <c r="P71" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="Q71" s="9">
+      <c r="Q71" s="8">
         <v>46254</v>
       </c>
-      <c r="R71" s="9">
+      <c r="R71" s="8">
         <v>46255</v>
       </c>
-      <c r="S71" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T71" s="10">
+      <c r="S71" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T71" s="9">
         <v>0</v>
       </c>
       <c r="U71" s="11" t="s">
@@ -5853,8 +5847,8 @@
       <c r="R72" s="5">
         <v>46253</v>
       </c>
-      <c r="S72" s="7" t="s">
-        <v>33</v>
+      <c r="S72" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T72" s="6">
         <v>0</v>
@@ -5864,62 +5858,62 @@
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A73" s="8" t="s">
+      <c r="A73" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="B73" s="9">
+      <c r="B73" s="8">
         <v>46181.60922180556</v>
       </c>
-      <c r="C73" s="10"/>
-      <c r="D73" s="9">
+      <c r="C73" s="9"/>
+      <c r="D73" s="8">
         <v>46182.63582844907</v>
       </c>
-      <c r="E73" s="10" t="s">
+      <c r="E73" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="F73" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G73" s="10" t="s">
+      <c r="F73" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G73" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="H73" s="10" t="s">
+      <c r="H73" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="I73" s="9">
+      <c r="I73" s="8">
         <v>46254</v>
       </c>
-      <c r="J73" s="9">
+      <c r="J73" s="8">
         <v>46255</v>
       </c>
-      <c r="K73" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L73" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M73" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N73" s="10" t="s">
+      <c r="K73" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L73" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M73" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N73" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="O73" s="10" t="s">
+      <c r="O73" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="P73" s="10" t="s">
+      <c r="P73" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="Q73" s="9">
+      <c r="Q73" s="8">
         <v>46254</v>
       </c>
-      <c r="R73" s="9">
+      <c r="R73" s="8">
         <v>46255</v>
       </c>
-      <c r="S73" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T73" s="10">
+      <c r="S73" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T73" s="9">
         <v>0</v>
       </c>
       <c r="U73" s="11" t="s">
@@ -5974,62 +5968,62 @@
       <c r="U74" s="6"/>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A75" s="8" t="s">
+      <c r="A75" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="B75" s="9">
+      <c r="B75" s="8">
         <v>46181.60922940972</v>
       </c>
-      <c r="C75" s="10"/>
-      <c r="D75" s="9">
+      <c r="C75" s="9"/>
+      <c r="D75" s="8">
         <v>46182.63612115741</v>
       </c>
-      <c r="E75" s="10" t="s">
+      <c r="E75" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="F75" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G75" s="10" t="s">
+      <c r="F75" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G75" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="H75" s="10" t="s">
+      <c r="H75" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="I75" s="9">
+      <c r="I75" s="8">
         <v>46258</v>
       </c>
-      <c r="J75" s="9">
+      <c r="J75" s="8">
         <v>46266</v>
       </c>
-      <c r="K75" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L75" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M75" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N75" s="10" t="s">
+      <c r="K75" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L75" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M75" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N75" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="O75" s="10" t="s">
+      <c r="O75" s="9" t="s">
         <v>241</v>
       </c>
-      <c r="P75" s="10" t="s">
+      <c r="P75" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="Q75" s="9">
+      <c r="Q75" s="8">
         <v>46258</v>
       </c>
-      <c r="R75" s="9">
+      <c r="R75" s="8">
         <v>46266</v>
       </c>
-      <c r="S75" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T75" s="10">
+      <c r="S75" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T75" s="9">
         <v>0</v>
       </c>
       <c r="U75" s="11" t="s">
@@ -6090,57 +6084,57 @@
       <c r="U76" s="6"/>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A77" s="8" t="s">
+      <c r="A77" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="B77" s="9">
+      <c r="B77" s="8">
         <v>46181.609241805556</v>
       </c>
-      <c r="C77" s="10"/>
-      <c r="D77" s="9">
+      <c r="C77" s="9"/>
+      <c r="D77" s="8">
         <v>46182.63598342593</v>
       </c>
-      <c r="E77" s="10" t="s">
+      <c r="E77" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="F77" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G77" s="10" t="s">
+      <c r="F77" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G77" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="H77" s="10" t="s">
+      <c r="H77" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="I77" s="9">
+      <c r="I77" s="8">
         <v>46258</v>
       </c>
-      <c r="J77" s="9">
+      <c r="J77" s="8">
         <v>46266</v>
       </c>
-      <c r="K77" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L77" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M77" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N77" s="10" t="s">
+      <c r="K77" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L77" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M77" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N77" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="O77" s="10" t="s">
+      <c r="O77" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="P77" s="10" t="s">
+      <c r="P77" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="Q77" s="10"/>
-      <c r="R77" s="10"/>
-      <c r="S77" s="10"/>
-      <c r="T77" s="10"/>
-      <c r="U77" s="10"/>
+      <c r="Q77" s="9"/>
+      <c r="R77" s="9"/>
+      <c r="S77" s="9"/>
+      <c r="T77" s="9"/>
+      <c r="U77" s="9"/>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
@@ -6196,57 +6190,57 @@
       <c r="U78" s="6"/>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A79" s="8" t="s">
+      <c r="A79" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="B79" s="9">
+      <c r="B79" s="8">
         <v>46181.61460722222</v>
       </c>
-      <c r="C79" s="10"/>
-      <c r="D79" s="9">
+      <c r="C79" s="9"/>
+      <c r="D79" s="8">
         <v>46182.63597787037</v>
       </c>
-      <c r="E79" s="10" t="s">
+      <c r="E79" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="F79" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G79" s="10" t="s">
+      <c r="F79" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G79" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="H79" s="10" t="s">
+      <c r="H79" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="I79" s="9">
+      <c r="I79" s="8">
         <v>46258</v>
       </c>
-      <c r="J79" s="9">
+      <c r="J79" s="8">
         <v>46266</v>
       </c>
-      <c r="K79" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L79" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M79" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N79" s="10" t="s">
+      <c r="K79" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L79" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M79" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N79" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="O79" s="10" t="s">
+      <c r="O79" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="P79" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q79" s="10"/>
-      <c r="R79" s="10"/>
-      <c r="S79" s="10"/>
-      <c r="T79" s="10"/>
-      <c r="U79" s="10"/>
+      <c r="P79" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q79" s="9"/>
+      <c r="R79" s="9"/>
+      <c r="S79" s="9"/>
+      <c r="T79" s="9"/>
+      <c r="U79" s="9"/>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
@@ -6302,62 +6296,62 @@
       <c r="U80" s="6"/>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A81" s="8" t="s">
+      <c r="A81" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="B81" s="9">
+      <c r="B81" s="8">
         <v>46181.609247002314</v>
       </c>
-      <c r="C81" s="10"/>
-      <c r="D81" s="9">
+      <c r="C81" s="9"/>
+      <c r="D81" s="8">
         <v>46182.64087873843</v>
       </c>
-      <c r="E81" s="10" t="s">
+      <c r="E81" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="F81" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G81" s="10" t="s">
+      <c r="F81" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G81" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="H81" s="10" t="s">
+      <c r="H81" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="I81" s="9">
+      <c r="I81" s="8">
         <v>46267</v>
       </c>
-      <c r="J81" s="9">
+      <c r="J81" s="8">
         <v>46288</v>
       </c>
-      <c r="K81" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L81" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M81" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N81" s="10" t="s">
+      <c r="K81" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L81" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M81" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N81" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="O81" s="10" t="s">
+      <c r="O81" s="9" t="s">
         <v>254</v>
       </c>
-      <c r="P81" s="10" t="s">
+      <c r="P81" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="Q81" s="9">
+      <c r="Q81" s="8">
         <v>46267</v>
       </c>
-      <c r="R81" s="9">
+      <c r="R81" s="8">
         <v>46288</v>
       </c>
-      <c r="S81" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T81" s="10">
+      <c r="S81" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T81" s="9">
         <v>0</v>
       </c>
       <c r="U81" s="11" t="s">
@@ -6418,57 +6412,57 @@
       <c r="U82" s="6"/>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A83" s="8" t="s">
+      <c r="A83" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="B83" s="9">
+      <c r="B83" s="8">
         <v>46181.609262199076</v>
       </c>
-      <c r="C83" s="10"/>
-      <c r="D83" s="9">
+      <c r="C83" s="9"/>
+      <c r="D83" s="8">
         <v>46191.54540574074</v>
       </c>
-      <c r="E83" s="10" t="s">
+      <c r="E83" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="F83" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G83" s="10" t="s">
+      <c r="F83" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G83" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="H83" s="10" t="s">
+      <c r="H83" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="I83" s="9">
+      <c r="I83" s="8">
         <v>46267</v>
       </c>
-      <c r="J83" s="9">
+      <c r="J83" s="8">
         <v>46288</v>
       </c>
-      <c r="K83" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L83" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M83" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N83" s="10" t="s">
+      <c r="K83" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L83" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M83" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N83" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="O83" s="10" t="s">
+      <c r="O83" s="9" t="s">
         <v>256</v>
       </c>
-      <c r="P83" s="10" t="s">
+      <c r="P83" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="Q83" s="10"/>
-      <c r="R83" s="10"/>
-      <c r="S83" s="10"/>
-      <c r="T83" s="10"/>
-      <c r="U83" s="10"/>
+      <c r="Q83" s="9"/>
+      <c r="R83" s="9"/>
+      <c r="S83" s="9"/>
+      <c r="T83" s="9"/>
+      <c r="U83" s="9"/>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
@@ -6524,57 +6518,57 @@
       <c r="U84" s="6"/>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A85" s="8" t="s">
+      <c r="A85" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="B85" s="9">
+      <c r="B85" s="8">
         <v>46181.61477212963</v>
       </c>
-      <c r="C85" s="10"/>
-      <c r="D85" s="9">
+      <c r="C85" s="9"/>
+      <c r="D85" s="8">
         <v>46182.64084086806</v>
       </c>
-      <c r="E85" s="10" t="s">
+      <c r="E85" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="F85" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G85" s="10" t="s">
+      <c r="F85" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G85" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="H85" s="10" t="s">
+      <c r="H85" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="I85" s="9">
+      <c r="I85" s="8">
         <v>46267</v>
       </c>
-      <c r="J85" s="9">
+      <c r="J85" s="8">
         <v>46288</v>
       </c>
-      <c r="K85" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L85" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M85" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N85" s="10" t="s">
+      <c r="K85" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L85" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M85" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N85" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="O85" s="10" t="s">
+      <c r="O85" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="P85" s="10" t="s">
+      <c r="P85" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="Q85" s="10"/>
-      <c r="R85" s="10"/>
-      <c r="S85" s="10"/>
-      <c r="T85" s="10"/>
-      <c r="U85" s="10"/>
+      <c r="Q85" s="9"/>
+      <c r="R85" s="9"/>
+      <c r="S85" s="9"/>
+      <c r="T85" s="9"/>
+      <c r="U85" s="9"/>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
@@ -6630,62 +6624,62 @@
       <c r="U86" s="6"/>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A87" s="8" t="s">
+      <c r="A87" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="B87" s="9">
+      <c r="B87" s="8">
         <v>46181.60926783565</v>
       </c>
-      <c r="C87" s="10"/>
-      <c r="D87" s="9">
+      <c r="C87" s="9"/>
+      <c r="D87" s="8">
         <v>46182.64099746528</v>
       </c>
-      <c r="E87" s="10" t="s">
+      <c r="E87" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="F87" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G87" s="10" t="s">
+      <c r="F87" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G87" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="H87" s="10" t="s">
+      <c r="H87" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="I87" s="9">
+      <c r="I87" s="8">
         <v>46289</v>
       </c>
-      <c r="J87" s="9">
+      <c r="J87" s="8">
         <v>46289</v>
       </c>
-      <c r="K87" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L87" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M87" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N87" s="10" t="s">
+      <c r="K87" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L87" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M87" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N87" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="O87" s="10" t="s">
+      <c r="O87" s="9" t="s">
         <v>254</v>
       </c>
-      <c r="P87" s="10" t="s">
+      <c r="P87" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="Q87" s="9">
+      <c r="Q87" s="8">
         <v>46289</v>
       </c>
-      <c r="R87" s="9">
+      <c r="R87" s="8">
         <v>46289</v>
       </c>
-      <c r="S87" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T87" s="10">
+      <c r="S87" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T87" s="9">
         <v>0</v>
       </c>
       <c r="U87" s="11" t="s">
@@ -6746,57 +6740,57 @@
       <c r="U88" s="6"/>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A89" s="8" t="s">
+      <c r="A89" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="B89" s="9">
+      <c r="B89" s="8">
         <v>46181.60927799769</v>
       </c>
-      <c r="C89" s="10"/>
-      <c r="D89" s="9">
+      <c r="C89" s="9"/>
+      <c r="D89" s="8">
         <v>46191.545404212964</v>
       </c>
-      <c r="E89" s="10" t="s">
+      <c r="E89" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="F89" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G89" s="10" t="s">
+      <c r="F89" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G89" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="H89" s="10" t="s">
+      <c r="H89" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="I89" s="9">
+      <c r="I89" s="8">
         <v>46289</v>
       </c>
-      <c r="J89" s="9">
+      <c r="J89" s="8">
         <v>46289</v>
       </c>
-      <c r="K89" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L89" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M89" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N89" s="10" t="s">
+      <c r="K89" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L89" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M89" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N89" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="O89" s="10" t="s">
+      <c r="O89" s="9" t="s">
         <v>256</v>
       </c>
-      <c r="P89" s="10" t="s">
+      <c r="P89" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="Q89" s="10"/>
-      <c r="R89" s="10"/>
-      <c r="S89" s="10"/>
-      <c r="T89" s="10"/>
-      <c r="U89" s="10"/>
+      <c r="Q89" s="9"/>
+      <c r="R89" s="9"/>
+      <c r="S89" s="9"/>
+      <c r="T89" s="9"/>
+      <c r="U89" s="9"/>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
@@ -6852,57 +6846,57 @@
       <c r="U90" s="6"/>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A91" s="8" t="s">
+      <c r="A91" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="B91" s="9">
+      <c r="B91" s="8">
         <v>46181.61498993056</v>
       </c>
-      <c r="C91" s="10"/>
-      <c r="D91" s="9">
+      <c r="C91" s="9"/>
+      <c r="D91" s="8">
         <v>46182.64096709491</v>
       </c>
-      <c r="E91" s="10" t="s">
+      <c r="E91" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="F91" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G91" s="10" t="s">
+      <c r="F91" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G91" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="H91" s="10" t="s">
+      <c r="H91" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="I91" s="9">
+      <c r="I91" s="8">
         <v>46289</v>
       </c>
-      <c r="J91" s="9">
+      <c r="J91" s="8">
         <v>46289</v>
       </c>
-      <c r="K91" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L91" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M91" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N91" s="10" t="s">
+      <c r="K91" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L91" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M91" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N91" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="O91" s="10" t="s">
+      <c r="O91" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="P91" s="10" t="s">
+      <c r="P91" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="Q91" s="10"/>
-      <c r="R91" s="10"/>
-      <c r="S91" s="10"/>
-      <c r="T91" s="10"/>
-      <c r="U91" s="10"/>
+      <c r="Q91" s="9"/>
+      <c r="R91" s="9"/>
+      <c r="S91" s="9"/>
+      <c r="T91" s="9"/>
+      <c r="U91" s="9"/>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
@@ -6958,51 +6952,51 @@
       <c r="U92" s="6"/>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A93" s="8" t="s">
+      <c r="A93" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="B93" s="9">
+      <c r="B93" s="8">
         <v>46181.60928361111</v>
       </c>
-      <c r="C93" s="10"/>
-      <c r="D93" s="9">
+      <c r="C93" s="9"/>
+      <c r="D93" s="8">
         <v>46182.567648321754</v>
       </c>
-      <c r="E93" s="10" t="s">
+      <c r="E93" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="F93" s="10" t="s">
+      <c r="F93" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="G93" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H93" s="10"/>
-      <c r="I93" s="10"/>
-      <c r="J93" s="10"/>
-      <c r="K93" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L93" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M93" s="10" t="s">
+      <c r="G93" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H93" s="9"/>
+      <c r="I93" s="9"/>
+      <c r="J93" s="9"/>
+      <c r="K93" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L93" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M93" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="N93" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O93" s="10" t="s">
+      <c r="N93" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="O93" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="P93" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q93" s="10"/>
-      <c r="R93" s="10"/>
-      <c r="S93" s="10"/>
-      <c r="T93" s="10"/>
-      <c r="U93" s="10"/>
+      <c r="P93" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q93" s="9"/>
+      <c r="R93" s="9"/>
+      <c r="S93" s="9"/>
+      <c r="T93" s="9"/>
+      <c r="U93" s="9"/>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
@@ -7064,70 +7058,70 @@
         <v>0</v>
       </c>
       <c r="U94" s="12" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A95" s="8" t="s">
+      <c r="A95" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="B95" s="9">
+      <c r="B95" s="8">
         <v>46181.609292974535</v>
       </c>
-      <c r="C95" s="10"/>
-      <c r="D95" s="9">
+      <c r="C95" s="9"/>
+      <c r="D95" s="8">
         <v>46190.886394166664</v>
       </c>
-      <c r="E95" s="10" t="s">
+      <c r="E95" s="9" t="s">
         <v>282</v>
       </c>
-      <c r="F95" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G95" s="10" t="s">
+      <c r="F95" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G95" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="H95" s="10" t="s">
+      <c r="H95" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="I95" s="9">
+      <c r="I95" s="8">
         <v>46290</v>
       </c>
-      <c r="J95" s="9">
+      <c r="J95" s="8">
         <v>46293</v>
       </c>
-      <c r="K95" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L95" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M95" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N95" s="10" t="s">
+      <c r="K95" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L95" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M95" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N95" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="O95" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="P95" s="10" t="s">
+      <c r="O95" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="P95" s="9" t="s">
         <v>279</v>
       </c>
-      <c r="Q95" s="9">
+      <c r="Q95" s="8">
         <v>46290</v>
       </c>
-      <c r="R95" s="9">
+      <c r="R95" s="8">
         <v>46293</v>
       </c>
-      <c r="S95" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T95" s="10">
+      <c r="S95" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T95" s="9">
         <v>0</v>
       </c>
       <c r="U95" s="12" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
@@ -7183,73 +7177,73 @@
       <c r="R96" s="5">
         <v>46227</v>
       </c>
-      <c r="S96" s="7" t="s">
-        <v>33</v>
+      <c r="S96" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T96" s="6">
         <v>0</v>
       </c>
       <c r="U96" s="12" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A97" s="8" t="s">
+      <c r="A97" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="B97" s="9">
+      <c r="B97" s="8">
         <v>46181.60930480324</v>
       </c>
-      <c r="C97" s="10"/>
-      <c r="D97" s="9">
+      <c r="C97" s="9"/>
+      <c r="D97" s="8">
         <v>46182.64108152778</v>
       </c>
-      <c r="E97" s="10" t="s">
+      <c r="E97" s="9" t="s">
         <v>286</v>
       </c>
-      <c r="F97" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G97" s="10" t="s">
+      <c r="F97" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G97" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="H97" s="10" t="s">
+      <c r="H97" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="I97" s="9">
+      <c r="I97" s="8">
         <v>46293</v>
       </c>
-      <c r="J97" s="9">
+      <c r="J97" s="8">
         <v>46294</v>
       </c>
-      <c r="K97" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L97" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M97" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N97" s="10" t="s">
+      <c r="K97" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L97" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M97" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N97" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="O97" s="10" t="s">
+      <c r="O97" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="P97" s="10" t="s">
+      <c r="P97" s="9" t="s">
         <v>287</v>
       </c>
-      <c r="Q97" s="9">
+      <c r="Q97" s="8">
         <v>46293</v>
       </c>
-      <c r="R97" s="9">
+      <c r="R97" s="8">
         <v>46294</v>
       </c>
-      <c r="S97" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T97" s="10">
+      <c r="S97" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T97" s="9">
         <v>0</v>
       </c>
       <c r="U97" s="11" t="s">
@@ -7309,8 +7303,8 @@
       <c r="R98" s="5">
         <v>46227</v>
       </c>
-      <c r="S98" s="7" t="s">
-        <v>33</v>
+      <c r="S98" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T98" s="6">
         <v>0</v>
@@ -7320,51 +7314,51 @@
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A99" s="8" t="s">
+      <c r="A99" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="B99" s="9">
+      <c r="B99" s="8">
         <v>46181.60936674768</v>
       </c>
-      <c r="C99" s="10"/>
-      <c r="D99" s="9">
+      <c r="C99" s="9"/>
+      <c r="D99" s="8">
         <v>46182.633312060185</v>
       </c>
-      <c r="E99" s="10" t="s">
+      <c r="E99" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="F99" s="10" t="s">
+      <c r="F99" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="G99" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H99" s="10"/>
-      <c r="I99" s="10"/>
-      <c r="J99" s="10"/>
-      <c r="K99" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L99" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M99" s="10" t="s">
+      <c r="G99" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H99" s="9"/>
+      <c r="I99" s="9"/>
+      <c r="J99" s="9"/>
+      <c r="K99" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L99" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M99" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="N99" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O99" s="10" t="s">
+      <c r="N99" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="O99" s="9" t="s">
         <v>291</v>
       </c>
-      <c r="P99" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q99" s="10"/>
-      <c r="R99" s="10"/>
-      <c r="S99" s="10"/>
-      <c r="T99" s="10"/>
-      <c r="U99" s="10"/>
+      <c r="P99" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q99" s="9"/>
+      <c r="R99" s="9"/>
+      <c r="S99" s="9"/>
+      <c r="T99" s="9"/>
+      <c r="U99" s="9"/>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
@@ -7384,10 +7378,10 @@
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I100" s="5">
         <v>46290</v>
@@ -7419,8 +7413,8 @@
       <c r="R100" s="5">
         <v>46310</v>
       </c>
-      <c r="S100" s="7" t="s">
-        <v>33</v>
+      <c r="S100" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T100" s="6">
         <v>0</v>
@@ -7430,57 +7424,57 @@
       </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A101" s="8" t="s">
+      <c r="A101" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="B101" s="9">
+      <c r="B101" s="8">
         <v>46181.609378587964</v>
       </c>
-      <c r="C101" s="10"/>
-      <c r="D101" s="9">
+      <c r="C101" s="9"/>
+      <c r="D101" s="8">
         <v>46182.64119599537</v>
       </c>
-      <c r="E101" s="10" t="s">
+      <c r="E101" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="F101" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G101" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="I101" s="9">
+      <c r="F101" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G101" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="H101" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="I101" s="8">
         <v>46290</v>
       </c>
-      <c r="J101" s="9">
+      <c r="J101" s="8">
         <v>46310</v>
       </c>
-      <c r="K101" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L101" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M101" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N101" s="10" t="s">
+      <c r="K101" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L101" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M101" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N101" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="O101" s="10" t="s">
+      <c r="O101" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="P101" s="10" t="s">
+      <c r="P101" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="Q101" s="10"/>
-      <c r="R101" s="10"/>
-      <c r="S101" s="10"/>
-      <c r="T101" s="10"/>
-      <c r="U101" s="10"/>
+      <c r="Q101" s="9"/>
+      <c r="R101" s="9"/>
+      <c r="S101" s="9"/>
+      <c r="T101" s="9"/>
+      <c r="U101" s="9"/>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
@@ -7500,10 +7494,10 @@
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I102" s="5">
         <v>46290</v>
@@ -7536,62 +7530,62 @@
       <c r="U102" s="6"/>
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A103" s="8" t="s">
+      <c r="A103" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="B103" s="9">
+      <c r="B103" s="8">
         <v>46181.609386111115</v>
       </c>
-      <c r="C103" s="10"/>
-      <c r="D103" s="9">
+      <c r="C103" s="9"/>
+      <c r="D103" s="8">
         <v>46182.641349328704</v>
       </c>
-      <c r="E103" s="10" t="s">
+      <c r="E103" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="F103" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G103" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="H103" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="I103" s="9">
+      <c r="F103" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G103" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="H103" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="I103" s="8">
         <v>46311</v>
       </c>
-      <c r="J103" s="9">
+      <c r="J103" s="8">
         <v>46314</v>
       </c>
-      <c r="K103" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L103" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M103" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N103" s="10" t="s">
+      <c r="K103" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L103" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M103" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N103" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="O103" s="10" t="s">
+      <c r="O103" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="P103" s="10" t="s">
+      <c r="P103" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="Q103" s="9">
+      <c r="Q103" s="8">
         <v>46311</v>
       </c>
-      <c r="R103" s="9">
+      <c r="R103" s="8">
         <v>46314</v>
       </c>
-      <c r="S103" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T103" s="10">
+      <c r="S103" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T103" s="9">
         <v>0</v>
       </c>
       <c r="U103" s="11" t="s">
@@ -7616,10 +7610,10 @@
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I104" s="5">
         <v>46311</v>
@@ -7652,57 +7646,57 @@
       <c r="U104" s="6"/>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A105" s="8" t="s">
+      <c r="A105" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="B105" s="9">
+      <c r="B105" s="8">
         <v>46181.61518315972</v>
       </c>
-      <c r="C105" s="10"/>
-      <c r="D105" s="9">
+      <c r="C105" s="9"/>
+      <c r="D105" s="8">
         <v>46182.64130309028</v>
       </c>
-      <c r="E105" s="10" t="s">
+      <c r="E105" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="F105" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G105" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="H105" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="I105" s="9">
+      <c r="F105" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G105" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="H105" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="I105" s="8">
         <v>46311</v>
       </c>
-      <c r="J105" s="9">
+      <c r="J105" s="8">
         <v>46314</v>
       </c>
-      <c r="K105" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L105" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M105" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N105" s="10" t="s">
+      <c r="K105" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L105" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M105" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N105" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="O105" s="10" t="s">
+      <c r="O105" s="9" t="s">
         <v>305</v>
       </c>
-      <c r="P105" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q105" s="10"/>
-      <c r="R105" s="10"/>
-      <c r="S105" s="10"/>
-      <c r="T105" s="10"/>
-      <c r="U105" s="10"/>
+      <c r="P105" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q105" s="9"/>
+      <c r="R105" s="9"/>
+      <c r="S105" s="9"/>
+      <c r="T105" s="9"/>
+      <c r="U105" s="9"/>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
@@ -7722,10 +7716,10 @@
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I106" s="5">
         <v>46315</v>
@@ -7757,8 +7751,8 @@
       <c r="R106" s="5">
         <v>46316</v>
       </c>
-      <c r="S106" s="7" t="s">
-        <v>33</v>
+      <c r="S106" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T106" s="6">
         <v>0</v>
@@ -7768,57 +7762,57 @@
       </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A107" s="8" t="s">
+      <c r="A107" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="B107" s="9">
+      <c r="B107" s="8">
         <v>46181.60940505787</v>
       </c>
-      <c r="C107" s="10"/>
-      <c r="D107" s="9">
+      <c r="C107" s="9"/>
+      <c r="D107" s="8">
         <v>46191.54540628473</v>
       </c>
-      <c r="E107" s="10" t="s">
+      <c r="E107" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="F107" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G107" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="H107" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="I107" s="9">
+      <c r="F107" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G107" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="H107" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="I107" s="8">
         <v>46315</v>
       </c>
-      <c r="J107" s="9">
+      <c r="J107" s="8">
         <v>46316</v>
       </c>
-      <c r="K107" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L107" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M107" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N107" s="10" t="s">
+      <c r="K107" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L107" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M107" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N107" s="9" t="s">
         <v>307</v>
       </c>
-      <c r="O107" s="10" t="s">
+      <c r="O107" s="9" t="s">
         <v>309</v>
       </c>
-      <c r="P107" s="10" t="s">
+      <c r="P107" s="9" t="s">
         <v>310</v>
       </c>
-      <c r="Q107" s="10"/>
-      <c r="R107" s="10"/>
-      <c r="S107" s="10"/>
-      <c r="T107" s="10"/>
-      <c r="U107" s="10"/>
+      <c r="Q107" s="9"/>
+      <c r="R107" s="9"/>
+      <c r="S107" s="9"/>
+      <c r="T107" s="9"/>
+      <c r="U107" s="9"/>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
@@ -7838,10 +7832,10 @@
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I108" s="5">
         <v>46315</v>
@@ -7874,62 +7868,62 @@
       <c r="U108" s="6"/>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A109" s="8" t="s">
+      <c r="A109" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="B109" s="9">
+      <c r="B109" s="8">
         <v>46181.60941365741</v>
       </c>
-      <c r="C109" s="10"/>
-      <c r="D109" s="9">
+      <c r="C109" s="9"/>
+      <c r="D109" s="8">
         <v>46182.64155526621</v>
       </c>
-      <c r="E109" s="10" t="s">
+      <c r="E109" s="9" t="s">
         <v>314</v>
       </c>
-      <c r="F109" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G109" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="H109" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="I109" s="9">
+      <c r="F109" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G109" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="H109" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="I109" s="8">
         <v>46317</v>
       </c>
-      <c r="J109" s="9">
+      <c r="J109" s="8">
         <v>46318</v>
       </c>
-      <c r="K109" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L109" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M109" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N109" s="10" t="s">
+      <c r="K109" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L109" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M109" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N109" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="O109" s="10" t="s">
+      <c r="O109" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="P109" s="10" t="s">
+      <c r="P109" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="Q109" s="9">
+      <c r="Q109" s="8">
         <v>46317</v>
       </c>
-      <c r="R109" s="9">
+      <c r="R109" s="8">
         <v>46318</v>
       </c>
-      <c r="S109" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T109" s="10">
+      <c r="S109" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T109" s="9">
         <v>0</v>
       </c>
       <c r="U109" s="11" t="s">
@@ -7954,10 +7948,10 @@
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I110" s="5">
         <v>46317</v>
@@ -7990,57 +7984,57 @@
       <c r="U110" s="6"/>
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A111" s="8" t="s">
+      <c r="A111" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="B111" s="9">
+      <c r="B111" s="8">
         <v>46181.61528053241</v>
       </c>
-      <c r="C111" s="10"/>
-      <c r="D111" s="9">
+      <c r="C111" s="9"/>
+      <c r="D111" s="8">
         <v>46182.64151664352</v>
       </c>
-      <c r="E111" s="10" t="s">
+      <c r="E111" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="F111" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G111" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="H111" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="I111" s="9">
+      <c r="F111" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G111" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="H111" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="I111" s="8">
         <v>46317</v>
       </c>
-      <c r="J111" s="9">
+      <c r="J111" s="8">
         <v>46318</v>
       </c>
-      <c r="K111" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L111" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M111" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N111" s="10" t="s">
+      <c r="K111" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L111" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M111" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N111" s="9" t="s">
         <v>314</v>
       </c>
-      <c r="O111" s="10" t="s">
+      <c r="O111" s="9" t="s">
         <v>319</v>
       </c>
-      <c r="P111" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q111" s="10"/>
-      <c r="R111" s="10"/>
-      <c r="S111" s="10"/>
-      <c r="T111" s="10"/>
-      <c r="U111" s="10"/>
+      <c r="P111" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q111" s="9"/>
+      <c r="R111" s="9"/>
+      <c r="S111" s="9"/>
+      <c r="T111" s="9"/>
+      <c r="U111" s="9"/>
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
@@ -8060,10 +8054,10 @@
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I112" s="5">
         <v>46321</v>
@@ -8095,8 +8089,8 @@
       <c r="R112" s="5">
         <v>46321</v>
       </c>
-      <c r="S112" s="7" t="s">
-        <v>33</v>
+      <c r="S112" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T112" s="6">
         <v>0</v>
@@ -8106,57 +8100,57 @@
       </c>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A113" s="8" t="s">
+      <c r="A113" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="B113" s="9">
+      <c r="B113" s="8">
         <v>46181.60943415509</v>
       </c>
-      <c r="C113" s="10"/>
-      <c r="D113" s="9">
+      <c r="C113" s="9"/>
+      <c r="D113" s="8">
         <v>46182.641623125004</v>
       </c>
-      <c r="E113" s="10" t="s">
+      <c r="E113" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="F113" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G113" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="H113" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="I113" s="9">
+      <c r="F113" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G113" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="H113" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="I113" s="8">
         <v>46321</v>
       </c>
-      <c r="J113" s="9">
+      <c r="J113" s="8">
         <v>46321</v>
       </c>
-      <c r="K113" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L113" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M113" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N113" s="10" t="s">
+      <c r="K113" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L113" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M113" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N113" s="9" t="s">
         <v>321</v>
       </c>
-      <c r="O113" s="10" t="s">
+      <c r="O113" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="P113" s="10" t="s">
+      <c r="P113" s="9" t="s">
         <v>323</v>
       </c>
-      <c r="Q113" s="10"/>
-      <c r="R113" s="10"/>
-      <c r="S113" s="10"/>
-      <c r="T113" s="10"/>
-      <c r="U113" s="10"/>
+      <c r="Q113" s="9"/>
+      <c r="R113" s="9"/>
+      <c r="S113" s="9"/>
+      <c r="T113" s="9"/>
+      <c r="U113" s="9"/>
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
@@ -8176,10 +8170,10 @@
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I114" s="5">
         <v>46321</v>
@@ -8212,62 +8206,62 @@
       <c r="U114" s="6"/>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A115" s="8" t="s">
+      <c r="A115" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="B115" s="9">
+      <c r="B115" s="8">
         <v>46181.60944410879</v>
       </c>
-      <c r="C115" s="10"/>
-      <c r="D115" s="9">
+      <c r="C115" s="9"/>
+      <c r="D115" s="8">
         <v>46182.82922638889</v>
       </c>
-      <c r="E115" s="10" t="s">
+      <c r="E115" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="F115" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G115" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="H115" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="I115" s="9">
+      <c r="F115" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G115" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="H115" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="I115" s="8">
         <v>46323</v>
       </c>
-      <c r="J115" s="9">
+      <c r="J115" s="8">
         <v>46323</v>
       </c>
-      <c r="K115" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L115" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M115" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N115" s="10" t="s">
+      <c r="K115" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L115" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M115" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N115" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="O115" s="10" t="s">
+      <c r="O115" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="P115" s="10" t="s">
+      <c r="P115" s="9" t="s">
         <v>327</v>
       </c>
-      <c r="Q115" s="9">
+      <c r="Q115" s="8">
         <v>46323</v>
       </c>
-      <c r="R115" s="9">
+      <c r="R115" s="8">
         <v>46323</v>
       </c>
-      <c r="S115" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T115" s="10">
+      <c r="S115" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T115" s="9">
         <v>0</v>
       </c>
       <c r="U115" s="11" t="s">
@@ -8292,10 +8286,10 @@
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I116" s="5">
         <v>46323</v>
@@ -8328,57 +8322,57 @@
       <c r="U116" s="6"/>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A117" s="8" t="s">
+      <c r="A117" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="B117" s="9">
+      <c r="B117" s="8">
         <v>46181.61537143518</v>
       </c>
-      <c r="C117" s="10"/>
-      <c r="D117" s="9">
+      <c r="C117" s="9"/>
+      <c r="D117" s="8">
         <v>46182.64172883102</v>
       </c>
-      <c r="E117" s="10" t="s">
+      <c r="E117" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="F117" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G117" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="H117" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="I117" s="9">
+      <c r="F117" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G117" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="H117" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="I117" s="8">
         <v>46323</v>
       </c>
-      <c r="J117" s="9">
+      <c r="J117" s="8">
         <v>46323</v>
       </c>
-      <c r="K117" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L117" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M117" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N117" s="10" t="s">
+      <c r="K117" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L117" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M117" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N117" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="O117" s="10" t="s">
+      <c r="O117" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="P117" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q117" s="10"/>
-      <c r="R117" s="10"/>
-      <c r="S117" s="10"/>
-      <c r="T117" s="10"/>
-      <c r="U117" s="10"/>
+      <c r="P117" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q117" s="9"/>
+      <c r="R117" s="9"/>
+      <c r="S117" s="9"/>
+      <c r="T117" s="9"/>
+      <c r="U117" s="9"/>
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
@@ -8428,62 +8422,62 @@
       <c r="U118" s="6"/>
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A119" s="8" t="s">
+      <c r="A119" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="B119" s="9">
+      <c r="B119" s="8">
         <v>46181.60946096065</v>
       </c>
-      <c r="C119" s="10"/>
-      <c r="D119" s="9">
+      <c r="C119" s="9"/>
+      <c r="D119" s="8">
         <v>46182.64186350694</v>
       </c>
-      <c r="E119" s="10" t="s">
+      <c r="E119" s="9" t="s">
         <v>335</v>
       </c>
-      <c r="F119" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G119" s="10" t="s">
+      <c r="F119" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G119" s="9" t="s">
         <v>336</v>
       </c>
-      <c r="H119" s="10" t="s">
+      <c r="H119" s="9" t="s">
         <v>337</v>
       </c>
-      <c r="I119" s="9">
+      <c r="I119" s="8">
         <v>46324</v>
       </c>
-      <c r="J119" s="9">
+      <c r="J119" s="8">
         <v>46324</v>
       </c>
-      <c r="K119" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L119" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M119" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N119" s="10" t="s">
+      <c r="K119" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L119" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M119" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N119" s="9" t="s">
         <v>332</v>
       </c>
-      <c r="O119" s="10" t="s">
+      <c r="O119" s="9" t="s">
         <v>338</v>
       </c>
-      <c r="P119" s="10" t="s">
+      <c r="P119" s="9" t="s">
         <v>332</v>
       </c>
-      <c r="Q119" s="9">
+      <c r="Q119" s="8">
         <v>46324</v>
       </c>
-      <c r="R119" s="9">
+      <c r="R119" s="8">
         <v>46324</v>
       </c>
-      <c r="S119" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T119" s="10">
+      <c r="S119" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T119" s="9">
         <v>0</v>
       </c>
       <c r="U119" s="11" t="s">
@@ -8544,57 +8538,57 @@
       <c r="U120" s="6"/>
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A121" s="8" t="s">
+      <c r="A121" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="B121" s="9">
+      <c r="B121" s="8">
         <v>46181.609475034726</v>
       </c>
-      <c r="C121" s="10"/>
-      <c r="D121" s="9">
+      <c r="C121" s="9"/>
+      <c r="D121" s="8">
         <v>46182.64184081019</v>
       </c>
-      <c r="E121" s="10" t="s">
+      <c r="E121" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="F121" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G121" s="10" t="s">
+      <c r="F121" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G121" s="9" t="s">
         <v>336</v>
       </c>
-      <c r="H121" s="10" t="s">
+      <c r="H121" s="9" t="s">
         <v>337</v>
       </c>
-      <c r="I121" s="9">
+      <c r="I121" s="8">
         <v>46324</v>
       </c>
-      <c r="J121" s="9">
+      <c r="J121" s="8">
         <v>46324</v>
       </c>
-      <c r="K121" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L121" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M121" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N121" s="10" t="s">
+      <c r="K121" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L121" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M121" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N121" s="9" t="s">
         <v>335</v>
       </c>
-      <c r="O121" s="10" t="s">
+      <c r="O121" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="P121" s="10" t="s">
+      <c r="P121" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="Q121" s="10"/>
-      <c r="R121" s="10"/>
-      <c r="S121" s="10"/>
-      <c r="T121" s="10"/>
-      <c r="U121" s="10"/>
+      <c r="Q121" s="9"/>
+      <c r="R121" s="9"/>
+      <c r="S121" s="9"/>
+      <c r="T121" s="9"/>
+      <c r="U121" s="9"/>
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
@@ -8650,57 +8644,57 @@
       <c r="U122" s="6"/>
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A123" s="8" t="s">
+      <c r="A123" s="7" t="s">
         <v>343</v>
       </c>
-      <c r="B123" s="9">
+      <c r="B123" s="8">
         <v>46181.61605960648</v>
       </c>
-      <c r="C123" s="10"/>
-      <c r="D123" s="9">
+      <c r="C123" s="9"/>
+      <c r="D123" s="8">
         <v>46182.641834548616</v>
       </c>
-      <c r="E123" s="10" t="s">
+      <c r="E123" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="F123" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G123" s="10" t="s">
+      <c r="F123" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G123" s="9" t="s">
         <v>336</v>
       </c>
-      <c r="H123" s="10" t="s">
+      <c r="H123" s="9" t="s">
         <v>337</v>
       </c>
-      <c r="I123" s="9">
+      <c r="I123" s="8">
         <v>46324</v>
       </c>
-      <c r="J123" s="9">
+      <c r="J123" s="8">
         <v>46324</v>
       </c>
-      <c r="K123" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L123" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M123" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N123" s="10" t="s">
+      <c r="K123" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L123" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M123" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N123" s="9" t="s">
         <v>335</v>
       </c>
-      <c r="O123" s="10" t="s">
+      <c r="O123" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="P123" s="10" t="s">
+      <c r="P123" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="Q123" s="10"/>
-      <c r="R123" s="10"/>
-      <c r="S123" s="10"/>
-      <c r="T123" s="10"/>
-      <c r="U123" s="10"/>
+      <c r="Q123" s="9"/>
+      <c r="R123" s="9"/>
+      <c r="S123" s="9"/>
+      <c r="T123" s="9"/>
+      <c r="U123" s="9"/>
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
@@ -8756,57 +8750,57 @@
       <c r="U124" s="6"/>
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A125" s="8" t="s">
+      <c r="A125" s="7" t="s">
         <v>345</v>
       </c>
-      <c r="B125" s="9">
+      <c r="B125" s="8">
         <v>46181.61620771991</v>
       </c>
-      <c r="C125" s="10"/>
-      <c r="D125" s="9">
+      <c r="C125" s="9"/>
+      <c r="D125" s="8">
         <v>46182.64182413195</v>
       </c>
-      <c r="E125" s="10" t="s">
+      <c r="E125" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="F125" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G125" s="10" t="s">
+      <c r="F125" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G125" s="9" t="s">
         <v>336</v>
       </c>
-      <c r="H125" s="10" t="s">
+      <c r="H125" s="9" t="s">
         <v>337</v>
       </c>
-      <c r="I125" s="9">
+      <c r="I125" s="8">
         <v>46324</v>
       </c>
-      <c r="J125" s="9">
+      <c r="J125" s="8">
         <v>46324</v>
       </c>
-      <c r="K125" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L125" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M125" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N125" s="10" t="s">
+      <c r="K125" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L125" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M125" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N125" s="9" t="s">
         <v>335</v>
       </c>
-      <c r="O125" s="10" t="s">
+      <c r="O125" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="P125" s="10" t="s">
+      <c r="P125" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="Q125" s="10"/>
-      <c r="R125" s="10"/>
-      <c r="S125" s="10"/>
-      <c r="T125" s="10"/>
-      <c r="U125" s="10"/>
+      <c r="Q125" s="9"/>
+      <c r="R125" s="9"/>
+      <c r="S125" s="9"/>
+      <c r="T125" s="9"/>
+      <c r="U125" s="9"/>
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
@@ -8862,62 +8856,62 @@
       <c r="U126" s="6"/>
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A127" s="8" t="s">
+      <c r="A127" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="B127" s="9">
+      <c r="B127" s="8">
         <v>46181.60948424769</v>
       </c>
-      <c r="C127" s="10"/>
-      <c r="D127" s="9">
+      <c r="C127" s="9"/>
+      <c r="D127" s="8">
         <v>46182.64199267361</v>
       </c>
-      <c r="E127" s="10" t="s">
+      <c r="E127" s="9" t="s">
         <v>348</v>
       </c>
-      <c r="F127" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G127" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="H127" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="I127" s="9">
+      <c r="F127" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G127" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="H127" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="I127" s="8">
         <v>46325</v>
       </c>
-      <c r="J127" s="9">
+      <c r="J127" s="8">
         <v>46325</v>
       </c>
-      <c r="K127" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L127" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M127" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N127" s="10" t="s">
+      <c r="K127" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L127" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M127" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N127" s="9" t="s">
         <v>332</v>
       </c>
-      <c r="O127" s="10" t="s">
+      <c r="O127" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="P127" s="10" t="s">
+      <c r="P127" s="9" t="s">
         <v>332</v>
       </c>
-      <c r="Q127" s="9">
+      <c r="Q127" s="8">
         <v>46325</v>
       </c>
-      <c r="R127" s="9">
+      <c r="R127" s="8">
         <v>46325</v>
       </c>
-      <c r="S127" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T127" s="10">
+      <c r="S127" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T127" s="9">
         <v>0</v>
       </c>
       <c r="U127" s="11" t="s">
@@ -8942,10 +8936,10 @@
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I128" s="5">
         <v>46325</v>
@@ -8978,57 +8972,57 @@
       <c r="U128" s="6"/>
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A129" s="8" t="s">
+      <c r="A129" s="7" t="s">
         <v>351</v>
       </c>
-      <c r="B129" s="9">
+      <c r="B129" s="8">
         <v>46181.60949538194</v>
       </c>
-      <c r="C129" s="10"/>
-      <c r="D129" s="9">
+      <c r="C129" s="9"/>
+      <c r="D129" s="8">
         <v>46182.64197085648</v>
       </c>
-      <c r="E129" s="10" t="s">
+      <c r="E129" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="F129" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G129" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="H129" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="I129" s="9">
+      <c r="F129" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G129" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="H129" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="I129" s="8">
         <v>46325</v>
       </c>
-      <c r="J129" s="9">
+      <c r="J129" s="8">
         <v>46325</v>
       </c>
-      <c r="K129" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L129" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M129" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N129" s="10" t="s">
+      <c r="K129" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L129" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M129" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N129" s="9" t="s">
         <v>348</v>
       </c>
-      <c r="O129" s="10" t="s">
+      <c r="O129" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="P129" s="10" t="s">
+      <c r="P129" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="Q129" s="10"/>
-      <c r="R129" s="10"/>
-      <c r="S129" s="10"/>
-      <c r="T129" s="10"/>
-      <c r="U129" s="10"/>
+      <c r="Q129" s="9"/>
+      <c r="R129" s="9"/>
+      <c r="S129" s="9"/>
+      <c r="T129" s="9"/>
+      <c r="U129" s="9"/>
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
@@ -9048,10 +9042,10 @@
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I130" s="5">
         <v>46325</v>
@@ -9084,57 +9078,57 @@
       <c r="U130" s="6"/>
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A131" s="8" t="s">
+      <c r="A131" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="B131" s="9">
+      <c r="B131" s="8">
         <v>46181.61659114584</v>
       </c>
-      <c r="C131" s="10"/>
-      <c r="D131" s="9">
+      <c r="C131" s="9"/>
+      <c r="D131" s="8">
         <v>46182.64196408565</v>
       </c>
-      <c r="E131" s="10" t="s">
+      <c r="E131" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="F131" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G131" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="H131" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="I131" s="9">
+      <c r="F131" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G131" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="H131" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="I131" s="8">
         <v>46325</v>
       </c>
-      <c r="J131" s="9">
+      <c r="J131" s="8">
         <v>46325</v>
       </c>
-      <c r="K131" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L131" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M131" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N131" s="10" t="s">
+      <c r="K131" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L131" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M131" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N131" s="9" t="s">
         <v>348</v>
       </c>
-      <c r="O131" s="10" t="s">
+      <c r="O131" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="P131" s="10" t="s">
+      <c r="P131" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="Q131" s="10"/>
-      <c r="R131" s="10"/>
-      <c r="S131" s="10"/>
-      <c r="T131" s="10"/>
-      <c r="U131" s="10"/>
+      <c r="Q131" s="9"/>
+      <c r="R131" s="9"/>
+      <c r="S131" s="9"/>
+      <c r="T131" s="9"/>
+      <c r="U131" s="9"/>
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
@@ -9154,10 +9148,10 @@
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I132" s="5">
         <v>46325</v>
@@ -9190,57 +9184,57 @@
       <c r="U132" s="6"/>
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A133" s="8" t="s">
+      <c r="A133" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="B133" s="9">
+      <c r="B133" s="8">
         <v>46181.61666238426</v>
       </c>
-      <c r="C133" s="10"/>
-      <c r="D133" s="9">
+      <c r="C133" s="9"/>
+      <c r="D133" s="8">
         <v>46182.64195453704</v>
       </c>
-      <c r="E133" s="10" t="s">
+      <c r="E133" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="F133" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G133" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="H133" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="I133" s="9">
+      <c r="F133" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G133" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="H133" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="I133" s="8">
         <v>46325</v>
       </c>
-      <c r="J133" s="9">
+      <c r="J133" s="8">
         <v>46325</v>
       </c>
-      <c r="K133" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L133" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M133" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N133" s="10" t="s">
+      <c r="K133" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L133" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M133" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N133" s="9" t="s">
         <v>348</v>
       </c>
-      <c r="O133" s="10" t="s">
+      <c r="O133" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="P133" s="10" t="s">
+      <c r="P133" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="Q133" s="10"/>
-      <c r="R133" s="10"/>
-      <c r="S133" s="10"/>
-      <c r="T133" s="10"/>
-      <c r="U133" s="10"/>
+      <c r="Q133" s="9"/>
+      <c r="R133" s="9"/>
+      <c r="S133" s="9"/>
+      <c r="T133" s="9"/>
+      <c r="U133" s="9"/>
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
@@ -9260,10 +9254,10 @@
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I134" s="5">
         <v>46325</v>
@@ -9296,62 +9290,62 @@
       <c r="U134" s="6"/>
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A135" s="8" t="s">
+      <c r="A135" s="7" t="s">
         <v>357</v>
       </c>
-      <c r="B135" s="9">
+      <c r="B135" s="8">
         <v>46181.60956560185</v>
       </c>
-      <c r="C135" s="10"/>
-      <c r="D135" s="9">
+      <c r="C135" s="9"/>
+      <c r="D135" s="8">
         <v>46182.82952324074</v>
       </c>
-      <c r="E135" s="10" t="s">
+      <c r="E135" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="F135" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G135" s="10" t="s">
+      <c r="F135" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G135" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="H135" s="10" t="s">
+      <c r="H135" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="I135" s="9">
+      <c r="I135" s="8">
         <v>46328</v>
       </c>
-      <c r="J135" s="9">
+      <c r="J135" s="8">
         <v>46328</v>
       </c>
-      <c r="K135" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L135" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M135" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N135" s="10" t="s">
+      <c r="K135" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L135" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M135" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N135" s="9" t="s">
         <v>332</v>
       </c>
-      <c r="O135" s="10" t="s">
+      <c r="O135" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="P135" s="10" t="s">
+      <c r="P135" s="9" t="s">
         <v>332</v>
       </c>
-      <c r="Q135" s="9">
+      <c r="Q135" s="8">
         <v>46328</v>
       </c>
-      <c r="R135" s="9">
+      <c r="R135" s="8">
         <v>46328</v>
       </c>
-      <c r="S135" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T135" s="10">
+      <c r="S135" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T135" s="9">
         <v>0</v>
       </c>
       <c r="U135" s="11" t="s">
@@ -9412,57 +9406,57 @@
       <c r="U136" s="6"/>
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A137" s="8" t="s">
+      <c r="A137" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="B137" s="9">
+      <c r="B137" s="8">
         <v>46181.609583576384</v>
       </c>
-      <c r="C137" s="10"/>
-      <c r="D137" s="9">
+      <c r="C137" s="9"/>
+      <c r="D137" s="8">
         <v>46182.829453784725</v>
       </c>
-      <c r="E137" s="10" t="s">
+      <c r="E137" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="F137" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G137" s="10" t="s">
+      <c r="F137" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G137" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="H137" s="10" t="s">
+      <c r="H137" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="I137" s="9">
+      <c r="I137" s="8">
         <v>46328</v>
       </c>
-      <c r="J137" s="9">
+      <c r="J137" s="8">
         <v>46328</v>
       </c>
-      <c r="K137" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L137" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M137" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N137" s="10" t="s">
+      <c r="K137" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L137" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M137" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N137" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="O137" s="10" t="s">
+      <c r="O137" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="P137" s="10" t="s">
+      <c r="P137" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="Q137" s="10"/>
-      <c r="R137" s="10"/>
-      <c r="S137" s="10"/>
-      <c r="T137" s="10"/>
-      <c r="U137" s="10"/>
+      <c r="Q137" s="9"/>
+      <c r="R137" s="9"/>
+      <c r="S137" s="9"/>
+      <c r="T137" s="9"/>
+      <c r="U137" s="9"/>
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
@@ -9518,57 +9512,57 @@
       <c r="U138" s="6"/>
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A139" s="8" t="s">
+      <c r="A139" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="B139" s="9">
+      <c r="B139" s="8">
         <v>46181.616839849536</v>
       </c>
-      <c r="C139" s="10"/>
-      <c r="D139" s="9">
+      <c r="C139" s="9"/>
+      <c r="D139" s="8">
         <v>46182.829455706014</v>
       </c>
-      <c r="E139" s="10" t="s">
+      <c r="E139" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="F139" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G139" s="10" t="s">
+      <c r="F139" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G139" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="H139" s="10" t="s">
+      <c r="H139" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="I139" s="9">
+      <c r="I139" s="8">
         <v>46328</v>
       </c>
-      <c r="J139" s="9">
+      <c r="J139" s="8">
         <v>46328</v>
       </c>
-      <c r="K139" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L139" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M139" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N139" s="10" t="s">
+      <c r="K139" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L139" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M139" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N139" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="O139" s="10" t="s">
+      <c r="O139" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="P139" s="10" t="s">
+      <c r="P139" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="Q139" s="10"/>
-      <c r="R139" s="10"/>
-      <c r="S139" s="10"/>
-      <c r="T139" s="10"/>
-      <c r="U139" s="10"/>
+      <c r="Q139" s="9"/>
+      <c r="R139" s="9"/>
+      <c r="S139" s="9"/>
+      <c r="T139" s="9"/>
+      <c r="U139" s="9"/>
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
@@ -9624,57 +9618,57 @@
       <c r="U140" s="6"/>
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A141" s="8" t="s">
+      <c r="A141" s="7" t="s">
         <v>365</v>
       </c>
-      <c r="B141" s="9">
+      <c r="B141" s="8">
         <v>46181.616942569446</v>
       </c>
-      <c r="C141" s="10"/>
-      <c r="D141" s="9">
+      <c r="C141" s="9"/>
+      <c r="D141" s="8">
         <v>46182.82945721065</v>
       </c>
-      <c r="E141" s="10" t="s">
+      <c r="E141" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="F141" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G141" s="10" t="s">
+      <c r="F141" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G141" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="H141" s="10" t="s">
+      <c r="H141" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="I141" s="9">
+      <c r="I141" s="8">
         <v>46328</v>
       </c>
-      <c r="J141" s="9">
+      <c r="J141" s="8">
         <v>46328</v>
       </c>
-      <c r="K141" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L141" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M141" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N141" s="10" t="s">
+      <c r="K141" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L141" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M141" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N141" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="O141" s="10" t="s">
+      <c r="O141" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="P141" s="10" t="s">
+      <c r="P141" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="Q141" s="10"/>
-      <c r="R141" s="10"/>
-      <c r="S141" s="10"/>
-      <c r="T141" s="10"/>
-      <c r="U141" s="10"/>
+      <c r="Q141" s="9"/>
+      <c r="R141" s="9"/>
+      <c r="S141" s="9"/>
+      <c r="T141" s="9"/>
+      <c r="U141" s="9"/>
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
@@ -9730,62 +9724,62 @@
       <c r="U142" s="6"/>
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A143" s="8" t="s">
+      <c r="A143" s="7" t="s">
         <v>367</v>
       </c>
-      <c r="B143" s="9">
+      <c r="B143" s="8">
         <v>46181.609592673616</v>
       </c>
-      <c r="C143" s="10"/>
-      <c r="D143" s="9">
+      <c r="C143" s="9"/>
+      <c r="D143" s="8">
         <v>46182.642407384265</v>
       </c>
-      <c r="E143" s="10" t="s">
+      <c r="E143" s="9" t="s">
         <v>368</v>
       </c>
-      <c r="F143" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G143" s="10" t="s">
+      <c r="F143" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G143" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="H143" s="10" t="s">
+      <c r="H143" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="I143" s="9">
+      <c r="I143" s="8">
         <v>46329</v>
       </c>
-      <c r="J143" s="9">
+      <c r="J143" s="8">
         <v>46329</v>
       </c>
-      <c r="K143" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L143" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M143" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N143" s="10" t="s">
+      <c r="K143" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L143" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M143" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N143" s="9" t="s">
         <v>332</v>
       </c>
-      <c r="O143" s="10" t="s">
+      <c r="O143" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="P143" s="10" t="s">
+      <c r="P143" s="9" t="s">
         <v>369</v>
       </c>
-      <c r="Q143" s="9">
+      <c r="Q143" s="8">
         <v>46329</v>
       </c>
-      <c r="R143" s="9">
+      <c r="R143" s="8">
         <v>46329</v>
       </c>
-      <c r="S143" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T143" s="10">
+      <c r="S143" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T143" s="9">
         <v>0</v>
       </c>
       <c r="U143" s="11" t="s">
@@ -9846,57 +9840,57 @@
       <c r="U144" s="6"/>
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A145" s="8" t="s">
+      <c r="A145" s="7" t="s">
         <v>371</v>
       </c>
-      <c r="B145" s="9">
+      <c r="B145" s="8">
         <v>46181.609610011576</v>
       </c>
-      <c r="C145" s="10"/>
-      <c r="D145" s="9">
+      <c r="C145" s="9"/>
+      <c r="D145" s="8">
         <v>46182.829451909725</v>
       </c>
-      <c r="E145" s="10" t="s">
+      <c r="E145" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="F145" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G145" s="10" t="s">
+      <c r="F145" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G145" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="H145" s="10" t="s">
+      <c r="H145" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="I145" s="9">
+      <c r="I145" s="8">
         <v>46329</v>
       </c>
-      <c r="J145" s="9">
+      <c r="J145" s="8">
         <v>46329</v>
       </c>
-      <c r="K145" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L145" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M145" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N145" s="10" t="s">
+      <c r="K145" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L145" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M145" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N145" s="9" t="s">
         <v>368</v>
       </c>
-      <c r="O145" s="10" t="s">
+      <c r="O145" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="P145" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q145" s="10"/>
-      <c r="R145" s="10"/>
-      <c r="S145" s="10"/>
-      <c r="T145" s="10"/>
-      <c r="U145" s="10"/>
+      <c r="P145" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q145" s="9"/>
+      <c r="R145" s="9"/>
+      <c r="S145" s="9"/>
+      <c r="T145" s="9"/>
+      <c r="U145" s="9"/>
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
@@ -9952,57 +9946,57 @@
       <c r="U146" s="6"/>
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A147" s="8" t="s">
+      <c r="A147" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="B147" s="9">
+      <c r="B147" s="8">
         <v>46181.61712142361</v>
       </c>
-      <c r="C147" s="10"/>
-      <c r="D147" s="9">
+      <c r="C147" s="9"/>
+      <c r="D147" s="8">
         <v>46182.82945197917</v>
       </c>
-      <c r="E147" s="10" t="s">
+      <c r="E147" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="F147" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G147" s="10" t="s">
+      <c r="F147" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G147" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="H147" s="10" t="s">
+      <c r="H147" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="I147" s="9">
+      <c r="I147" s="8">
         <v>46329</v>
       </c>
-      <c r="J147" s="9">
+      <c r="J147" s="8">
         <v>46329</v>
       </c>
-      <c r="K147" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L147" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M147" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N147" s="10" t="s">
+      <c r="K147" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L147" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M147" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N147" s="9" t="s">
         <v>368</v>
       </c>
-      <c r="O147" s="10" t="s">
+      <c r="O147" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="P147" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q147" s="10"/>
-      <c r="R147" s="10"/>
-      <c r="S147" s="10"/>
-      <c r="T147" s="10"/>
-      <c r="U147" s="10"/>
+      <c r="P147" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q147" s="9"/>
+      <c r="R147" s="9"/>
+      <c r="S147" s="9"/>
+      <c r="T147" s="9"/>
+      <c r="U147" s="9"/>
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
@@ -10058,57 +10052,57 @@
       <c r="U148" s="6"/>
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A149" s="8" t="s">
+      <c r="A149" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="B149" s="9">
+      <c r="B149" s="8">
         <v>46181.61719633102</v>
       </c>
-      <c r="C149" s="10"/>
-      <c r="D149" s="9">
+      <c r="C149" s="9"/>
+      <c r="D149" s="8">
         <v>46182.829452025464</v>
       </c>
-      <c r="E149" s="10" t="s">
+      <c r="E149" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="F149" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G149" s="10" t="s">
+      <c r="F149" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G149" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="H149" s="10" t="s">
+      <c r="H149" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="I149" s="9">
+      <c r="I149" s="8">
         <v>46329</v>
       </c>
-      <c r="J149" s="9">
+      <c r="J149" s="8">
         <v>46329</v>
       </c>
-      <c r="K149" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L149" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M149" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N149" s="10" t="s">
+      <c r="K149" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L149" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M149" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N149" s="9" t="s">
         <v>368</v>
       </c>
-      <c r="O149" s="10" t="s">
+      <c r="O149" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="P149" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q149" s="10"/>
-      <c r="R149" s="10"/>
-      <c r="S149" s="10"/>
-      <c r="T149" s="10"/>
-      <c r="U149" s="10"/>
+      <c r="P149" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q149" s="9"/>
+      <c r="R149" s="9"/>
+      <c r="S149" s="9"/>
+      <c r="T149" s="9"/>
+      <c r="U149" s="9"/>
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
@@ -10164,51 +10158,51 @@
       <c r="U150" s="6"/>
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A151" s="8" t="s">
+      <c r="A151" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="B151" s="9">
+      <c r="B151" s="8">
         <v>46181.60961741898</v>
       </c>
-      <c r="C151" s="10"/>
-      <c r="D151" s="9">
+      <c r="C151" s="9"/>
+      <c r="D151" s="8">
         <v>46182.63449439815</v>
       </c>
-      <c r="E151" s="10" t="s">
+      <c r="E151" s="9" t="s">
         <v>378</v>
       </c>
-      <c r="F151" s="10" t="s">
+      <c r="F151" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="G151" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H151" s="10"/>
-      <c r="I151" s="10"/>
-      <c r="J151" s="10"/>
-      <c r="K151" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L151" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M151" s="10" t="s">
+      <c r="G151" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H151" s="9"/>
+      <c r="I151" s="9"/>
+      <c r="J151" s="9"/>
+      <c r="K151" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L151" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M151" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="N151" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="O151" s="10" t="s">
+      <c r="N151" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="O151" s="9" t="s">
         <v>379</v>
       </c>
-      <c r="P151" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q151" s="10"/>
-      <c r="R151" s="10"/>
-      <c r="S151" s="10"/>
-      <c r="T151" s="10"/>
-      <c r="U151" s="10"/>
+      <c r="P151" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q151" s="9"/>
+      <c r="R151" s="9"/>
+      <c r="S151" s="9"/>
+      <c r="T151" s="9"/>
+      <c r="U151" s="9"/>
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
@@ -10263,8 +10257,8 @@
       <c r="R152" s="5">
         <v>46337</v>
       </c>
-      <c r="S152" s="7" t="s">
-        <v>33</v>
+      <c r="S152" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T152" s="6">
         <v>0</v>
@@ -10274,62 +10268,62 @@
       </c>
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A153" s="8" t="s">
+      <c r="A153" s="7" t="s">
         <v>384</v>
       </c>
-      <c r="B153" s="9">
+      <c r="B153" s="8">
         <v>46181.60962780092</v>
       </c>
-      <c r="C153" s="10"/>
-      <c r="D153" s="9">
+      <c r="C153" s="9"/>
+      <c r="D153" s="8">
         <v>46191.67892958333</v>
       </c>
-      <c r="E153" s="10" t="s">
+      <c r="E153" s="9" t="s">
         <v>385</v>
       </c>
-      <c r="F153" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G153" s="10" t="s">
+      <c r="F153" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G153" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="H153" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H153" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="I153" s="9">
+      <c r="I153" s="8">
         <v>46330</v>
       </c>
-      <c r="J153" s="9">
+      <c r="J153" s="8">
         <v>46337</v>
       </c>
-      <c r="K153" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L153" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M153" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N153" s="10" t="s">
+      <c r="K153" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L153" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M153" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N153" s="9" t="s">
         <v>378</v>
       </c>
-      <c r="O153" s="10" t="s">
+      <c r="O153" s="9" t="s">
         <v>368</v>
       </c>
-      <c r="P153" s="10" t="s">
+      <c r="P153" s="9" t="s">
         <v>378</v>
       </c>
-      <c r="Q153" s="9">
+      <c r="Q153" s="8">
         <v>46330</v>
       </c>
-      <c r="R153" s="9">
+      <c r="R153" s="8">
         <v>46337</v>
       </c>
-      <c r="S153" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T153" s="10">
+      <c r="S153" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T153" s="9">
         <v>0</v>
       </c>
       <c r="U153" s="11" t="s">
@@ -10379,8 +10373,8 @@
       </c>
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
-      <c r="S154" s="7" t="s">
-        <v>33</v>
+      <c r="S154" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T154" s="6">
         <v>0</v>
@@ -10390,62 +10384,62 @@
       </c>
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A155" s="8" t="s">
+      <c r="A155" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="B155" s="9">
+      <c r="B155" s="8">
         <v>46181.609640208335</v>
       </c>
-      <c r="C155" s="10"/>
-      <c r="D155" s="9">
+      <c r="C155" s="9"/>
+      <c r="D155" s="8">
         <v>46182.64254377315</v>
       </c>
-      <c r="E155" s="10" t="s">
+      <c r="E155" s="9" t="s">
         <v>390</v>
       </c>
-      <c r="F155" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G155" s="10" t="s">
+      <c r="F155" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G155" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="H155" s="10" t="s">
+      <c r="H155" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="I155" s="9">
+      <c r="I155" s="8">
         <v>46330</v>
       </c>
-      <c r="J155" s="9">
+      <c r="J155" s="8">
         <v>46338</v>
       </c>
-      <c r="K155" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="L155" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M155" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="N155" s="10" t="s">
+      <c r="K155" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L155" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M155" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N155" s="9" t="s">
         <v>387</v>
       </c>
-      <c r="O155" s="10" t="s">
+      <c r="O155" s="9" t="s">
         <v>368</v>
       </c>
-      <c r="P155" s="10" t="s">
+      <c r="P155" s="9" t="s">
         <v>391</v>
       </c>
-      <c r="Q155" s="9">
+      <c r="Q155" s="8">
         <v>46330</v>
       </c>
-      <c r="R155" s="9">
+      <c r="R155" s="8">
         <v>46338</v>
       </c>
-      <c r="S155" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="T155" s="10">
+      <c r="S155" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T155" s="9">
         <v>0</v>
       </c>
       <c r="U155" s="11" t="s">
@@ -10505,8 +10499,8 @@
       <c r="R156" s="5">
         <v>46349</v>
       </c>
-      <c r="S156" s="7" t="s">
-        <v>33</v>
+      <c r="S156" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T156" s="6">
         <v>0</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1813" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1813" uniqueCount="393">
   <si>
     <t>50001559 - FERROVIAL</t>
   </si>
@@ -592,7 +592,7 @@
     <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4349- CODO 90° Ø1600MM</t>
   </si>
   <si>
-    <t>Media</t>
+    <t>Alta</t>
   </si>
   <si>
     <t>1215506639092978</t>
@@ -893,9 +893,6 @@
   </si>
   <si>
     <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Bodega:</t>
-  </si>
-  <si>
-    <t>Alta</t>
   </si>
   <si>
     <t>1215506992958412</t>
@@ -4490,7 +4487,7 @@
         <v>46190.708245752314</v>
       </c>
       <c r="D49" s="8">
-        <v>46190.708260555555</v>
+        <v>46192.17287283565</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>175</v>
@@ -4534,7 +4531,7 @@
       <c r="R49" s="8">
         <v>46191</v>
       </c>
-      <c r="S49" s="12" t="s">
+      <c r="S49" s="11" t="s">
         <v>179</v>
       </c>
       <c r="T49" s="9">
@@ -7052,7 +7049,7 @@
         <v>46183</v>
       </c>
       <c r="S94" s="11" t="s">
-        <v>280</v>
+        <v>179</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
@@ -7063,7 +7060,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B95" s="8">
         <v>46181.609292974535</v>
@@ -7073,7 +7070,7 @@
         <v>46190.886394166664</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -7126,7 +7123,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B96" s="5">
         <v>46181.60929881944</v>
@@ -7136,7 +7133,7 @@
         <v>46190.886404791665</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7189,7 +7186,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B97" s="8">
         <v>46181.60930480324</v>
@@ -7199,7 +7196,7 @@
         <v>46182.64108152778</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
@@ -7232,7 +7229,7 @@
         <v>157</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q97" s="8">
         <v>46293</v>
@@ -7252,7 +7249,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B98" s="5">
         <v>46181.60935271991</v>
@@ -7315,7 +7312,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B99" s="8">
         <v>46181.60936674768</v>
@@ -7325,7 +7322,7 @@
         <v>46182.633312060185</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>25</v>
@@ -7349,7 +7346,7 @@
         <v>26</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P99" s="9" t="s">
         <v>26</v>
@@ -7362,7 +7359,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B100" s="5">
         <v>46181.609371666666</v>
@@ -7372,7 +7369,7 @@
         <v>46182.64123547454</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7399,13 +7396,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Q100" s="5">
         <v>46290</v>
@@ -7425,7 +7422,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B101" s="8">
         <v>46181.609378587964</v>
@@ -7462,13 +7459,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7478,7 +7475,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B102" s="5">
         <v>46181.61514019676</v>
@@ -7515,13 +7512,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>181</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7531,7 +7528,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B103" s="8">
         <v>46181.609386111115</v>
@@ -7541,7 +7538,7 @@
         <v>46182.641349328704</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -7568,13 +7565,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O103" s="9" t="s">
         <v>181</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Q103" s="8">
         <v>46311</v>
@@ -7594,7 +7591,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B104" s="5">
         <v>46181.60939194444</v>
@@ -7631,13 +7628,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O104" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="P104" s="6" t="s">
         <v>302</v>
-      </c>
-      <c r="P104" s="6" t="s">
-        <v>303</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7647,7 +7644,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B105" s="8">
         <v>46181.61518315972</v>
@@ -7684,10 +7681,10 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P105" s="9" t="s">
         <v>26</v>
@@ -7700,7 +7697,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B106" s="5">
         <v>46181.60939866898</v>
@@ -7710,7 +7707,7 @@
         <v>46182.64144489584</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7737,13 +7734,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>181</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Q106" s="5">
         <v>46315</v>
@@ -7763,7 +7760,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B107" s="8">
         <v>46181.60940505787</v>
@@ -7800,13 +7797,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O107" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="P107" s="9" t="s">
         <v>309</v>
-      </c>
-      <c r="P107" s="9" t="s">
-        <v>310</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -7816,7 +7813,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B108" s="5">
         <v>46181.61523613426</v>
@@ -7853,10 +7850,10 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>26</v>
@@ -7869,7 +7866,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B109" s="8">
         <v>46181.60941365741</v>
@@ -7879,7 +7876,7 @@
         <v>46182.64155526621</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -7906,13 +7903,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O109" s="9" t="s">
         <v>181</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Q109" s="8">
         <v>46317</v>
@@ -7932,7 +7929,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B110" s="5">
         <v>46181.60941929398</v>
@@ -7969,13 +7966,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="O110" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="P110" s="6" t="s">
         <v>316</v>
-      </c>
-      <c r="P110" s="6" t="s">
-        <v>317</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -7985,7 +7982,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B111" s="8">
         <v>46181.61528053241</v>
@@ -8022,10 +8019,10 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="P111" s="9" t="s">
         <v>26</v>
@@ -8038,7 +8035,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B112" s="5">
         <v>46181.60942706019</v>
@@ -8048,7 +8045,7 @@
         <v>46182.64166112269</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8075,13 +8072,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>181</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Q112" s="5">
         <v>46321</v>
@@ -8101,7 +8098,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B113" s="8">
         <v>46181.60943415509</v>
@@ -8138,13 +8135,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O113" s="9" t="s">
         <v>181</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8154,7 +8151,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B114" s="5">
         <v>46181.61532783565</v>
@@ -8191,7 +8188,7 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>181</v>
@@ -8207,7 +8204,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B115" s="8">
         <v>46181.60944410879</v>
@@ -8217,7 +8214,7 @@
         <v>46182.82922638889</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
@@ -8244,13 +8241,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O115" s="9" t="s">
         <v>181</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="Q115" s="8">
         <v>46323</v>
@@ -8270,7 +8267,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B116" s="5">
         <v>46181.60944996528</v>
@@ -8307,13 +8304,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="O116" s="6" t="s">
         <v>181</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8323,7 +8320,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B117" s="8">
         <v>46181.61537143518</v>
@@ -8360,7 +8357,7 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="O117" s="9" t="s">
         <v>211</v>
@@ -8376,7 +8373,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B118" s="5">
         <v>46181.60945642361</v>
@@ -8386,7 +8383,7 @@
         <v>46182.634494212965</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>25</v>
@@ -8410,7 +8407,7 @@
         <v>26</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>26</v>
@@ -8423,7 +8420,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B119" s="8">
         <v>46181.60946096065</v>
@@ -8433,16 +8430,16 @@
         <v>46182.64186350694</v>
       </c>
       <c r="E119" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="F119" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G119" s="9" t="s">
         <v>335</v>
       </c>
-      <c r="F119" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G119" s="9" t="s">
+      <c r="H119" s="9" t="s">
         <v>336</v>
-      </c>
-      <c r="H119" s="9" t="s">
-        <v>337</v>
       </c>
       <c r="I119" s="8">
         <v>46324</v>
@@ -8460,13 +8457,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q119" s="8">
         <v>46324</v>
@@ -8486,7 +8483,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B120" s="5">
         <v>46181.60946868056</v>
@@ -8502,10 +8499,10 @@
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="H120" s="6" t="s">
         <v>336</v>
-      </c>
-      <c r="H120" s="6" t="s">
-        <v>337</v>
       </c>
       <c r="I120" s="5">
         <v>46324</v>
@@ -8523,13 +8520,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>181</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8539,7 +8536,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B121" s="8">
         <v>46181.609475034726</v>
@@ -8555,10 +8552,10 @@
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="H121" s="9" t="s">
         <v>336</v>
-      </c>
-      <c r="H121" s="9" t="s">
-        <v>337</v>
       </c>
       <c r="I121" s="8">
         <v>46324</v>
@@ -8576,7 +8573,7 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O121" s="9" t="s">
         <v>181</v>
@@ -8592,7 +8589,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B122" s="5">
         <v>46181.60947921296</v>
@@ -8608,10 +8605,10 @@
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="H122" s="6" t="s">
         <v>336</v>
-      </c>
-      <c r="H122" s="6" t="s">
-        <v>337</v>
       </c>
       <c r="I122" s="5">
         <v>46324</v>
@@ -8629,7 +8626,7 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>59</v>
@@ -8645,7 +8642,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B123" s="8">
         <v>46181.61605960648</v>
@@ -8661,10 +8658,10 @@
         <v>26</v>
       </c>
       <c r="G123" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="H123" s="9" t="s">
         <v>336</v>
-      </c>
-      <c r="H123" s="9" t="s">
-        <v>337</v>
       </c>
       <c r="I123" s="8">
         <v>46324</v>
@@ -8682,7 +8679,7 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O123" s="9" t="s">
         <v>59</v>
@@ -8698,7 +8695,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B124" s="5">
         <v>46181.61617203704</v>
@@ -8714,10 +8711,10 @@
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="H124" s="6" t="s">
         <v>336</v>
-      </c>
-      <c r="H124" s="6" t="s">
-        <v>337</v>
       </c>
       <c r="I124" s="5">
         <v>46324</v>
@@ -8735,7 +8732,7 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>260</v>
@@ -8751,7 +8748,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B125" s="8">
         <v>46181.61620771991</v>
@@ -8767,10 +8764,10 @@
         <v>26</v>
       </c>
       <c r="G125" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="H125" s="9" t="s">
         <v>336</v>
-      </c>
-      <c r="H125" s="9" t="s">
-        <v>337</v>
       </c>
       <c r="I125" s="8">
         <v>46324</v>
@@ -8788,7 +8785,7 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O125" s="9" t="s">
         <v>262</v>
@@ -8804,7 +8801,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B126" s="5">
         <v>46181.616245833335</v>
@@ -8820,10 +8817,10 @@
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="H126" s="6" t="s">
         <v>336</v>
-      </c>
-      <c r="H126" s="6" t="s">
-        <v>337</v>
       </c>
       <c r="I126" s="5">
         <v>46324</v>
@@ -8841,7 +8838,7 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>264</v>
@@ -8857,7 +8854,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B127" s="8">
         <v>46181.60948424769</v>
@@ -8867,7 +8864,7 @@
         <v>46182.64199267361</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
@@ -8894,13 +8891,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O127" s="9" t="s">
         <v>181</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q127" s="8">
         <v>46325</v>
@@ -8920,7 +8917,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B128" s="5">
         <v>46181.60948969907</v>
@@ -8957,13 +8954,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O128" s="6" t="s">
         <v>181</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -8973,7 +8970,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B129" s="8">
         <v>46181.60949538194</v>
@@ -9010,7 +9007,7 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O129" s="9" t="s">
         <v>181</v>
@@ -9026,7 +9023,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B130" s="5">
         <v>46181.609560185185</v>
@@ -9063,7 +9060,7 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O130" s="6" t="s">
         <v>59</v>
@@ -9079,7 +9076,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B131" s="8">
         <v>46181.61659114584</v>
@@ -9116,7 +9113,7 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O131" s="9" t="s">
         <v>59</v>
@@ -9132,7 +9129,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B132" s="5">
         <v>46181.61662431713</v>
@@ -9169,7 +9166,7 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O132" s="6" t="s">
         <v>184</v>
@@ -9185,7 +9182,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B133" s="8">
         <v>46181.61666238426</v>
@@ -9222,7 +9219,7 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O133" s="9" t="s">
         <v>187</v>
@@ -9238,7 +9235,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B134" s="5">
         <v>46181.61670006944</v>
@@ -9275,7 +9272,7 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>274</v>
@@ -9291,7 +9288,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B135" s="8">
         <v>46181.60956560185</v>
@@ -9301,7 +9298,7 @@
         <v>46182.82952324074</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
@@ -9328,13 +9325,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O135" s="9" t="s">
         <v>181</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q135" s="8">
         <v>46328</v>
@@ -9354,7 +9351,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B136" s="5">
         <v>46181.60957188657</v>
@@ -9391,13 +9388,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="O136" s="6" t="s">
         <v>181</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9407,7 +9404,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B137" s="8">
         <v>46181.609583576384</v>
@@ -9444,7 +9441,7 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="O137" s="9" t="s">
         <v>181</v>
@@ -9460,7 +9457,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B138" s="5">
         <v>46181.60958841435</v>
@@ -9497,7 +9494,7 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="O138" s="6" t="s">
         <v>59</v>
@@ -9513,7 +9510,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B139" s="8">
         <v>46181.616839849536</v>
@@ -9550,7 +9547,7 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="O139" s="9" t="s">
         <v>59</v>
@@ -9566,7 +9563,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B140" s="5">
         <v>46181.61689748843</v>
@@ -9603,7 +9600,7 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="O140" s="6" t="s">
         <v>184</v>
@@ -9619,7 +9616,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B141" s="8">
         <v>46181.616942569446</v>
@@ -9656,7 +9653,7 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="O141" s="9" t="s">
         <v>187</v>
@@ -9672,7 +9669,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B142" s="5">
         <v>46181.6169815162</v>
@@ -9709,7 +9706,7 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="O142" s="6" t="s">
         <v>189</v>
@@ -9725,7 +9722,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B143" s="8">
         <v>46181.609592673616</v>
@@ -9735,7 +9732,7 @@
         <v>46182.642407384265</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>26</v>
@@ -9762,13 +9759,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O143" s="9" t="s">
         <v>181</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="Q143" s="8">
         <v>46329</v>
@@ -9788,7 +9785,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B144" s="5">
         <v>46181.60960517361</v>
@@ -9825,13 +9822,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="O144" s="6" t="s">
         <v>181</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -9841,7 +9838,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B145" s="8">
         <v>46181.609610011576</v>
@@ -9878,7 +9875,7 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="O145" s="9" t="s">
         <v>181</v>
@@ -9894,7 +9891,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B146" s="5">
         <v>46181.609613796296</v>
@@ -9931,7 +9928,7 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="O146" s="6" t="s">
         <v>59</v>
@@ -9947,7 +9944,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B147" s="8">
         <v>46181.61712142361</v>
@@ -9984,7 +9981,7 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="O147" s="9" t="s">
         <v>59</v>
@@ -10000,7 +9997,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B148" s="5">
         <v>46181.61716094907</v>
@@ -10037,7 +10034,7 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="O148" s="6" t="s">
         <v>184</v>
@@ -10053,7 +10050,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B149" s="8">
         <v>46181.61719633102</v>
@@ -10090,7 +10087,7 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="O149" s="9" t="s">
         <v>187</v>
@@ -10106,7 +10103,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B150" s="5">
         <v>46181.617235451384</v>
@@ -10143,7 +10140,7 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="O150" s="6" t="s">
         <v>189</v>
@@ -10159,7 +10156,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B151" s="8">
         <v>46181.60961741898</v>
@@ -10169,7 +10166,7 @@
         <v>46182.63449439815</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>25</v>
@@ -10193,7 +10190,7 @@
         <v>26</v>
       </c>
       <c r="O151" s="9" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="P151" s="9" t="s">
         <v>26</v>
@@ -10206,7 +10203,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B152" s="5">
         <v>46181.60962174769</v>
@@ -10216,16 +10213,16 @@
         <v>46182.64244836806</v>
       </c>
       <c r="E152" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="F152" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G152" s="6" t="s">
         <v>381</v>
       </c>
-      <c r="F152" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G152" s="6" t="s">
+      <c r="H152" s="6" t="s">
         <v>382</v>
-      </c>
-      <c r="H152" s="6" t="s">
-        <v>383</v>
       </c>
       <c r="I152" s="5">
         <v>46330</v>
@@ -10243,13 +10240,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="Q152" s="5">
         <v>46330</v>
@@ -10269,7 +10266,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B153" s="8">
         <v>46181.60962780092</v>
@@ -10279,7 +10276,7 @@
         <v>46191.67892958333</v>
       </c>
       <c r="E153" s="9" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F153" s="9" t="s">
         <v>26</v>
@@ -10306,13 +10303,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="9" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="O153" s="9" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P153" s="9" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="Q153" s="8">
         <v>46330</v>
@@ -10332,7 +10329,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B154" s="5">
         <v>46181.60963489584</v>
@@ -10342,7 +10339,7 @@
         <v>46182.63449431713</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>25</v>
@@ -10366,7 +10363,7 @@
         <v>26</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="P154" s="6" t="s">
         <v>26</v>
@@ -10385,7 +10382,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B155" s="8">
         <v>46181.609640208335</v>
@@ -10395,7 +10392,7 @@
         <v>46182.64254377315</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>26</v>
@@ -10422,13 +10419,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="9" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O155" s="9" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="P155" s="9" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="Q155" s="8">
         <v>46330</v>
@@ -10448,7 +10445,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B156" s="5">
         <v>46181.609646365745</v>
@@ -10458,7 +10455,7 @@
         <v>46182.64254079861</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
@@ -10485,13 +10482,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="Q156" s="5">
         <v>46339</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -3526,7 +3526,7 @@
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46182.62666353009</v>
+        <v>46195.6859309838</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>122</v>
@@ -3587,9 +3587,11 @@
       <c r="B33" s="8">
         <v>46181.60901165509</v>
       </c>
-      <c r="C33" s="9"/>
+      <c r="C33" s="8">
+        <v>46195.685925451384</v>
+      </c>
       <c r="D33" s="8">
-        <v>46190.67786118056</v>
+        <v>46195.68592747685</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>109</v>
@@ -3642,7 +3644,7 @@
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46182.626637905094</v>
+        <v>46195.685932430555</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>129</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -346,25 +346,25 @@
     <t>Generación OC materiales corte Laser ot 4342 -4344,Propuesta compras:</t>
   </si>
   <si>
+    <t>1215506984624491</t>
+  </si>
+  <si>
+    <t>Propuesta Corte plasma  ot 4347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC Corte Plasma  ot 4342 -4344 </t>
+  </si>
+  <si>
+    <t>1215506992580924</t>
+  </si>
+  <si>
+    <t>Propuesta Mecanizado ot 4347</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado ot 4342 -4344</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1215506984624491</t>
-  </si>
-  <si>
-    <t>Propuesta Corte plasma  ot 4347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC Corte Plasma  ot 4342 -4344 </t>
-  </si>
-  <si>
-    <t>1215506992580924</t>
-  </si>
-  <si>
-    <t>Propuesta Mecanizado ot 4347</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado ot 4342 -4344</t>
   </si>
   <si>
     <t>1215506992580936</t>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46190.67771045139</v>
+        <v>46196.65857491898</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>79</v>
@@ -2924,9 +2924,11 @@
       <c r="B22" s="5">
         <v>46181.60888054398</v>
       </c>
-      <c r="C22" s="6"/>
+      <c r="C22" s="5">
+        <v>46196.658568541665</v>
+      </c>
       <c r="D22" s="5">
-        <v>46191.67365563658</v>
+        <v>46196.65858296296</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>92</v>
@@ -2974,25 +2976,27 @@
         <v>32</v>
       </c>
       <c r="T22" s="6">
-        <v>0</v>
-      </c>
-      <c r="U22" s="12" t="s">
-        <v>97</v>
+        <v>1</v>
+      </c>
+      <c r="U22" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B23" s="8">
         <v>46181.60888559028</v>
       </c>
-      <c r="C23" s="9"/>
+      <c r="C23" s="8">
+        <v>46196.65883074074</v>
+      </c>
       <c r="D23" s="8">
-        <v>46191.67366451389</v>
+        <v>46196.658845625</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
@@ -3025,7 +3029,7 @@
         <v>95</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q23" s="8">
         <v>46248</v>
@@ -3037,15 +3041,15 @@
         <v>32</v>
       </c>
       <c r="T23" s="9">
-        <v>0</v>
-      </c>
-      <c r="U23" s="12" t="s">
-        <v>97</v>
+        <v>1</v>
+      </c>
+      <c r="U23" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B24" s="5">
         <v>46181.60888961806</v>
@@ -3055,7 +3059,7 @@
         <v>46191.67367153935</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -3088,7 +3092,7 @@
         <v>95</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Q24" s="5">
         <v>46248</v>
@@ -3103,7 +3107,7 @@
         <v>0</v>
       </c>
       <c r="U24" s="12" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -3166,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="U25" s="12" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
@@ -3341,7 +3345,7 @@
         <v>0</v>
       </c>
       <c r="U28" s="12" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -3404,7 +3408,7 @@
         <v>0</v>
       </c>
       <c r="U29" s="12" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -3760,7 +3764,7 @@
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46182.62676782407</v>
+        <v>46196.65857439815</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
@@ -3941,10 +3945,10 @@
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46182.626871608794</v>
+        <v>46196.65883732639</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
@@ -3974,7 +3978,7 @@
         <v>142</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>145</v>
@@ -4027,7 +4031,7 @@
         <v>142</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>148</v>
@@ -4335,7 +4339,7 @@
         <v>46182.62720454861</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
@@ -4365,7 +4369,7 @@
         <v>164</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>167</v>
@@ -4418,7 +4422,7 @@
         <v>164</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P47" s="9" t="s">
         <v>170</v>
@@ -4475,7 +4479,7 @@
       <c r="S48" s="6"/>
       <c r="T48" s="6"/>
       <c r="U48" s="12" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -7057,7 +7061,7 @@
         <v>0</v>
       </c>
       <c r="U94" s="12" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -7120,7 +7124,7 @@
         <v>0</v>
       </c>
       <c r="U95" s="12" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
@@ -7183,7 +7187,7 @@
         <v>0</v>
       </c>
       <c r="U96" s="12" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -778,7 +778,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT2 4232 ZVN 1-9-86/2 </t>
+    <t xml:space="preserve">OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT2 4307 ZVN 1-9-86/2 </t>
   </si>
   <si>
     <t>OT 4349- CODO 90° Ø1600MM,OT 4350 - CODO 135° Ø1600MM,OT 4351 - DUCTO Ø1600MM L:1800MM,Caldereria:</t>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1813" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1815" uniqueCount="393">
   <si>
     <t>50001559 - FERROVIAL</t>
   </si>
@@ -298,6 +298,9 @@
     <t>propuesta alabes  ot 4347,propuesta motor  ot 4347,propuesta nucleo rodete  ot 4347,propuesta Corte Laser ot 4347</t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
     <t>1215506984585999</t>
   </si>
   <si>
@@ -362,9 +365,6 @@
   </si>
   <si>
     <t>Generación OC Mecanizado ot 4342 -4344</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1215506992580936</t>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46196.65857491898</v>
+        <v>46197.42282767361</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>79</v>
@@ -2722,11 +2722,13 @@
       <c r="R18" s="6"/>
       <c r="S18" s="6"/>
       <c r="T18" s="6"/>
-      <c r="U18" s="6"/>
+      <c r="U18" s="12" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B19" s="8">
         <v>46181.608864236114</v>
@@ -2738,7 +2740,7 @@
         <v>46190.88639424769</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
@@ -2771,7 +2773,7 @@
         <v>68</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q19" s="8">
         <v>46167</v>
@@ -2791,7 +2793,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B20" s="5">
         <v>46181.60886979167</v>
@@ -2803,7 +2805,7 @@
         <v>46190.88638454861</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2836,7 +2838,7 @@
         <v>72</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q20" s="5">
         <v>46174</v>
@@ -2856,26 +2858,28 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B21" s="8">
         <v>46181.60887520833</v>
       </c>
-      <c r="C21" s="9"/>
+      <c r="C21" s="8">
+        <v>46197.42280901621</v>
+      </c>
       <c r="D21" s="8">
-        <v>46190.886384502315</v>
+        <v>46197.422811446755</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I21" s="8">
         <v>46174</v>
@@ -2899,7 +2903,7 @@
         <v>72</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q21" s="8">
         <v>46174</v>
@@ -2919,7 +2923,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B22" s="5">
         <v>46181.60888054398</v>
@@ -2931,16 +2935,16 @@
         <v>46196.65858296296</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I22" s="5">
         <v>46248</v>
@@ -2961,10 +2965,10 @@
         <v>79</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q22" s="5">
         <v>46248</v>
@@ -2984,7 +2988,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B23" s="8">
         <v>46181.60888559028</v>
@@ -2996,16 +3000,16 @@
         <v>46196.658845625</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I23" s="8">
         <v>46248</v>
@@ -3026,10 +3030,10 @@
         <v>79</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q23" s="8">
         <v>46248</v>
@@ -3049,7 +3053,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B24" s="5">
         <v>46181.60888961806</v>
@@ -3059,16 +3063,16 @@
         <v>46191.67367153935</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I24" s="5">
         <v>46248</v>
@@ -3089,10 +3093,10 @@
         <v>79</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q24" s="5">
         <v>46248</v>
@@ -3107,7 +3111,7 @@
         <v>0</v>
       </c>
       <c r="U24" s="12" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -3128,10 +3132,10 @@
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I25" s="8">
         <v>46248</v>
@@ -3152,7 +3156,7 @@
         <v>79</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P25" s="9" t="s">
         <v>106</v>
@@ -3170,7 +3174,7 @@
         <v>0</v>
       </c>
       <c r="U25" s="12" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
@@ -3245,9 +3249,11 @@
       <c r="B27" s="8">
         <v>46190.88204489583</v>
       </c>
-      <c r="C27" s="9"/>
+      <c r="C27" s="8">
+        <v>46197.42407642362</v>
+      </c>
       <c r="D27" s="8">
-        <v>46190.88358329861</v>
+        <v>46197.424089050925</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>111</v>
@@ -3282,8 +3288,12 @@
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
       <c r="S27" s="9"/>
-      <c r="T27" s="9"/>
-      <c r="U27" s="9"/>
+      <c r="T27" s="9">
+        <v>1</v>
+      </c>
+      <c r="U27" s="10" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
@@ -3292,9 +3302,11 @@
       <c r="B28" s="5">
         <v>46190.88321909722</v>
       </c>
-      <c r="C28" s="6"/>
+      <c r="C28" s="5">
+        <v>46197.42354282408</v>
+      </c>
       <c r="D28" s="5">
-        <v>46191.67371679399</v>
+        <v>46197.42355928241</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>113</v>
@@ -3303,10 +3315,10 @@
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I28" s="5">
         <v>46169</v>
@@ -3327,7 +3339,7 @@
         <v>111</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>26</v>
@@ -3342,10 +3354,10 @@
         <v>32</v>
       </c>
       <c r="T28" s="6">
-        <v>0</v>
-      </c>
-      <c r="U28" s="12" t="s">
-        <v>103</v>
+        <v>1</v>
+      </c>
+      <c r="U28" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -3355,9 +3367,11 @@
       <c r="B29" s="8">
         <v>46190.88327185185</v>
       </c>
-      <c r="C29" s="9"/>
+      <c r="C29" s="8">
+        <v>46197.42396493055</v>
+      </c>
       <c r="D29" s="8">
-        <v>46191.6737259838</v>
+        <v>46197.423981597225</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>115</v>
@@ -3366,10 +3380,10 @@
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I29" s="8">
         <v>46176</v>
@@ -3390,7 +3404,7 @@
         <v>111</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P29" s="9" t="s">
         <v>26</v>
@@ -3405,10 +3419,10 @@
         <v>32</v>
       </c>
       <c r="T29" s="9">
-        <v>0</v>
-      </c>
-      <c r="U29" s="12" t="s">
-        <v>103</v>
+        <v>1</v>
+      </c>
+      <c r="U29" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -3418,9 +3432,11 @@
       <c r="B30" s="5">
         <v>46190.88332659722</v>
       </c>
-      <c r="C30" s="6"/>
+      <c r="C30" s="5">
+        <v>46197.42406122685</v>
+      </c>
       <c r="D30" s="5">
-        <v>46191.67374731481</v>
+        <v>46197.42407648148</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>117</v>
@@ -3429,10 +3445,10 @@
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I30" s="5">
         <v>46176</v>
@@ -3453,7 +3469,7 @@
         <v>111</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>26</v>
@@ -3468,10 +3484,10 @@
         <v>32</v>
       </c>
       <c r="T30" s="6">
-        <v>0</v>
-      </c>
-      <c r="U30" s="11" t="s">
-        <v>57</v>
+        <v>1</v>
+      </c>
+      <c r="U30" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -3797,7 +3813,7 @@
         <v>120</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>137</v>
@@ -3948,7 +3964,7 @@
         <v>46196.65883732639</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
@@ -3978,7 +3994,7 @@
         <v>142</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>145</v>
@@ -4031,7 +4047,7 @@
         <v>142</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>148</v>
@@ -4339,7 +4355,7 @@
         <v>46182.62720454861</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
@@ -4369,7 +4385,7 @@
         <v>164</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>167</v>
@@ -4422,7 +4438,7 @@
         <v>164</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P47" s="9" t="s">
         <v>170</v>
@@ -4479,7 +4495,7 @@
       <c r="S48" s="6"/>
       <c r="T48" s="6"/>
       <c r="U48" s="12" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -5066,7 +5082,7 @@
         <v>46191.54539826389</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
@@ -5156,13 +5172,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>181</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5209,13 +5225,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>184</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5262,7 +5278,7 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>187</v>
@@ -5315,7 +5331,7 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O63" s="9" t="s">
         <v>189</v>
@@ -7061,7 +7077,7 @@
         <v>0</v>
       </c>
       <c r="U94" s="12" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -7124,7 +7140,7 @@
         <v>0</v>
       </c>
       <c r="U95" s="12" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
@@ -7187,7 +7203,7 @@
         <v>0</v>
       </c>
       <c r="U96" s="12" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
@@ -7381,10 +7397,10 @@
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I100" s="5">
         <v>46290</v>
@@ -7444,10 +7460,10 @@
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I101" s="8">
         <v>46290</v>
@@ -7497,10 +7513,10 @@
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I102" s="5">
         <v>46290</v>
@@ -7550,10 +7566,10 @@
         <v>26</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I103" s="8">
         <v>46311</v>
@@ -7613,10 +7629,10 @@
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I104" s="5">
         <v>46311</v>
@@ -7666,10 +7682,10 @@
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H105" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I105" s="8">
         <v>46311</v>
@@ -7719,10 +7735,10 @@
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I106" s="5">
         <v>46315</v>
@@ -7782,10 +7798,10 @@
         <v>26</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H107" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I107" s="8">
         <v>46315</v>
@@ -7835,10 +7851,10 @@
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I108" s="5">
         <v>46315</v>
@@ -7888,10 +7904,10 @@
         <v>26</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H109" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I109" s="8">
         <v>46317</v>
@@ -7951,10 +7967,10 @@
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I110" s="5">
         <v>46317</v>
@@ -8004,10 +8020,10 @@
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I111" s="8">
         <v>46317</v>
@@ -8057,10 +8073,10 @@
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I112" s="5">
         <v>46321</v>
@@ -8120,10 +8136,10 @@
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I113" s="8">
         <v>46321</v>
@@ -8173,10 +8189,10 @@
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I114" s="5">
         <v>46321</v>
@@ -8226,10 +8242,10 @@
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I115" s="8">
         <v>46323</v>
@@ -8289,10 +8305,10 @@
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I116" s="5">
         <v>46323</v>
@@ -8342,10 +8358,10 @@
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I117" s="8">
         <v>46323</v>
@@ -8876,10 +8892,10 @@
         <v>26</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H127" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I127" s="8">
         <v>46325</v>
@@ -8939,10 +8955,10 @@
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I128" s="5">
         <v>46325</v>
@@ -8992,10 +9008,10 @@
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I129" s="8">
         <v>46325</v>
@@ -9045,10 +9061,10 @@
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I130" s="5">
         <v>46325</v>
@@ -9098,10 +9114,10 @@
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I131" s="8">
         <v>46325</v>
@@ -9151,10 +9167,10 @@
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I132" s="5">
         <v>46325</v>
@@ -9204,10 +9220,10 @@
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I133" s="8">
         <v>46325</v>
@@ -9257,10 +9273,10 @@
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I134" s="5">
         <v>46325</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -3121,9 +3121,11 @@
       <c r="B25" s="8">
         <v>46181.6088934375</v>
       </c>
-      <c r="C25" s="9"/>
+      <c r="C25" s="8">
+        <v>46197.64511049769</v>
+      </c>
       <c r="D25" s="8">
-        <v>46191.67370431713</v>
+        <v>46197.64512664352</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>105</v>
@@ -3171,10 +3173,10 @@
         <v>32</v>
       </c>
       <c r="T25" s="9">
-        <v>0</v>
-      </c>
-      <c r="U25" s="12" t="s">
-        <v>81</v>
+        <v>1</v>
+      </c>
+      <c r="U25" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
@@ -4130,7 +4132,7 @@
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46182.62705136574</v>
+        <v>46197.6451175</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>106</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1815" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1815" uniqueCount="395">
   <si>
     <t>50001559 - FERROVIAL</t>
   </si>
@@ -583,22 +583,28 @@
     <t>Planos preliminar</t>
   </si>
   <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4349- CODO 90° Ø1600MM</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>1215506639092978</t>
+  </si>
+  <si>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
+  </si>
+  <si>
     <t>Hernan Roberto Gutierrez Barrientos</t>
   </si>
   <si>
     <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4349- CODO 90° Ø1600MM</t>
-  </si>
-  <si>
-    <t>Alta</t>
-  </si>
-  <si>
-    <t>1215506639092978</t>
-  </si>
-  <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
   </si>
   <si>
     <t>Planos preliminar,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
@@ -4511,7 +4517,7 @@
         <v>46190.708245752314</v>
       </c>
       <c r="D49" s="8">
-        <v>46192.17287283565</v>
+        <v>46197.7158150926</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>175</v>
@@ -4585,10 +4591,10 @@
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="I50" s="5">
         <v>46174</v>
@@ -4612,7 +4618,7 @@
         <v>76</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4622,7 +4628,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B51" s="8">
         <v>46181.60909384259</v>
@@ -4634,16 +4640,16 @@
         <v>46190.7082228125</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="I51" s="8">
         <v>46174</v>
@@ -4667,7 +4673,7 @@
         <v>76</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4677,7 +4683,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B52" s="5">
         <v>46181.61221741898</v>
@@ -4689,16 +4695,16 @@
         <v>46190.708227337964</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="I52" s="5">
         <v>46174</v>
@@ -4722,7 +4728,7 @@
         <v>76</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4732,7 +4738,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B53" s="8">
         <v>46181.612357199076</v>
@@ -4744,16 +4750,16 @@
         <v>46190.708233321755</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="I53" s="8">
         <v>46174</v>
@@ -4777,7 +4783,7 @@
         <v>76</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -4787,7 +4793,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B54" s="5">
         <v>46181.609098182875</v>
@@ -4796,10 +4802,10 @@
         <v>46191.54272982639</v>
       </c>
       <c r="D54" s="5">
-        <v>46191.54274247686</v>
+        <v>46197.71584820602</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
@@ -4852,7 +4858,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B55" s="8">
         <v>46181.60910252314</v>
@@ -4870,10 +4876,10 @@
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="I55" s="8">
         <v>46227</v>
@@ -4891,13 +4897,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="O55" s="9" t="s">
         <v>181</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4907,7 +4913,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B56" s="5">
         <v>46181.609107951386</v>
@@ -4919,16 +4925,16 @@
         <v>46191.54271703704</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="I56" s="5">
         <v>46227</v>
@@ -4946,13 +4952,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4962,7 +4968,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B57" s="8">
         <v>46181.61393570602</v>
@@ -4974,16 +4980,16 @@
         <v>46190.70842170139</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="I57" s="8">
         <v>46227</v>
@@ -5001,13 +5007,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5017,7 +5023,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B58" s="5">
         <v>46181.61396929398</v>
@@ -5029,16 +5035,16 @@
         <v>46190.708426550926</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="I58" s="5">
         <v>46227</v>
@@ -5056,13 +5062,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="O58" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="O58" s="6" t="s">
-        <v>189</v>
-      </c>
       <c r="P58" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5072,7 +5078,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B59" s="8">
         <v>46181.60911329861</v>
@@ -5090,10 +5096,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="I59" s="8">
         <v>46247</v>
@@ -5117,7 +5123,7 @@
         <v>178</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q59" s="8">
         <v>46247</v>
@@ -5137,7 +5143,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B60" s="5">
         <v>46181.60912350695</v>
@@ -5155,10 +5161,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="I60" s="6"/>
       <c r="J60" s="5">
@@ -5190,7 +5196,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B61" s="8">
         <v>46181.60912782408</v>
@@ -5202,16 +5208,16 @@
         <v>46191.54537386574</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="I61" s="9"/>
       <c r="J61" s="8">
@@ -5230,7 +5236,7 @@
         <v>96</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>96</v>
@@ -5243,7 +5249,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B62" s="5">
         <v>46181.614119606485</v>
@@ -5255,16 +5261,16 @@
         <v>46190.721725358795</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="I62" s="6"/>
       <c r="J62" s="5">
@@ -5283,7 +5289,7 @@
         <v>96</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5296,7 +5302,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B63" s="8">
         <v>46181.61419627315</v>
@@ -5308,16 +5314,16 @@
         <v>46190.7217299537</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="I63" s="9"/>
       <c r="J63" s="8">
@@ -5336,7 +5342,7 @@
         <v>96</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5349,7 +5355,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B64" s="5">
         <v>46181.60913207176</v>
@@ -5359,16 +5365,16 @@
         <v>46182.633118067126</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I64" s="5">
         <v>46322</v>
@@ -5412,7 +5418,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B65" s="8">
         <v>46181.609135833336</v>
@@ -5428,10 +5434,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I65" s="8">
         <v>46322</v>
@@ -5449,13 +5455,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="O65" s="9" t="s">
         <v>181</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5465,7 +5471,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B66" s="5">
         <v>46181.614311909725</v>
@@ -5475,16 +5481,16 @@
         <v>46182.63311923611</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I66" s="5">
         <v>46322</v>
@@ -5502,7 +5508,7 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>181</v>
@@ -5518,7 +5524,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B67" s="8">
         <v>46181.60918671296</v>
@@ -5528,7 +5534,7 @@
         <v>46181.77983537037</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>25</v>
@@ -5552,7 +5558,7 @@
         <v>26</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>26</v>
@@ -5565,7 +5571,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B68" s="5">
         <v>46181.609196087964</v>
@@ -5575,16 +5581,16 @@
         <v>46182.63576145833</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I68" s="5">
         <v>46252</v>
@@ -5602,13 +5608,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>139</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q68" s="5">
         <v>46252</v>
@@ -5628,7 +5634,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B69" s="8">
         <v>46181.609201921296</v>
@@ -5638,7 +5644,7 @@
         <v>46182.63583637732</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
@@ -5665,13 +5671,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q69" s="8">
         <v>46254</v>
@@ -5691,7 +5697,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B70" s="5">
         <v>46181.60920746528</v>
@@ -5701,16 +5707,16 @@
         <v>46182.635758460645</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I70" s="5">
         <v>46252</v>
@@ -5728,13 +5734,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>147</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q70" s="5">
         <v>46252</v>
@@ -5754,7 +5760,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B71" s="8">
         <v>46181.609212870375</v>
@@ -5764,7 +5770,7 @@
         <v>46182.63583289352</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
@@ -5791,13 +5797,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q71" s="8">
         <v>46254</v>
@@ -5817,7 +5823,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B72" s="5">
         <v>46181.60921715278</v>
@@ -5827,16 +5833,16 @@
         <v>46182.63575501158</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I72" s="5">
         <v>46252</v>
@@ -5854,13 +5860,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>169</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q72" s="5">
         <v>46252</v>
@@ -5880,7 +5886,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B73" s="8">
         <v>46181.60922180556</v>
@@ -5890,7 +5896,7 @@
         <v>46182.63582844907</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
@@ -5917,13 +5923,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="O73" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="P73" s="9" t="s">
         <v>231</v>
-      </c>
-      <c r="P73" s="9" t="s">
-        <v>229</v>
       </c>
       <c r="Q73" s="8">
         <v>46254</v>
@@ -5943,7 +5949,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B74" s="5">
         <v>46181.60922590278</v>
@@ -5953,7 +5959,7 @@
         <v>46181.782424143516</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>25</v>
@@ -5977,7 +5983,7 @@
         <v>26</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>26</v>
@@ -5990,7 +5996,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B75" s="8">
         <v>46181.60922940972</v>
@@ -6000,16 +6006,16 @@
         <v>46182.63612115741</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I75" s="8">
         <v>46258</v>
@@ -6027,13 +6033,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q75" s="8">
         <v>46258</v>
@@ -6053,7 +6059,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B76" s="5">
         <v>46181.60923553241</v>
@@ -6069,10 +6075,10 @@
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I76" s="5">
         <v>46258</v>
@@ -6090,13 +6096,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6106,7 +6112,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B77" s="8">
         <v>46181.609241805556</v>
@@ -6122,10 +6128,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I77" s="8">
         <v>46258</v>
@@ -6143,10 +6149,10 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>181</v>
@@ -6159,7 +6165,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B78" s="5">
         <v>46181.6145286574</v>
@@ -6169,16 +6175,16 @@
         <v>46182.63598072917</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I78" s="5">
         <v>46258</v>
@@ -6196,10 +6202,10 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6212,7 +6218,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B79" s="8">
         <v>46181.61460722222</v>
@@ -6222,16 +6228,16 @@
         <v>46182.63597787037</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I79" s="8">
         <v>46258</v>
@@ -6249,10 +6255,10 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P79" s="9" t="s">
         <v>26</v>
@@ -6265,7 +6271,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B80" s="5">
         <v>46181.61464366898</v>
@@ -6275,16 +6281,16 @@
         <v>46182.635973807875</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I80" s="5">
         <v>46258</v>
@@ -6302,10 +6308,10 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>26</v>
@@ -6318,7 +6324,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B81" s="8">
         <v>46181.609247002314</v>
@@ -6328,16 +6334,16 @@
         <v>46182.64087873843</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I81" s="8">
         <v>46267</v>
@@ -6355,13 +6361,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q81" s="8">
         <v>46267</v>
@@ -6381,7 +6387,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B82" s="5">
         <v>46181.60925648148</v>
@@ -6397,10 +6403,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I82" s="5">
         <v>46267</v>
@@ -6418,13 +6424,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6434,7 +6440,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B83" s="8">
         <v>46181.609262199076</v>
@@ -6450,10 +6456,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I83" s="8">
         <v>46267</v>
@@ -6471,13 +6477,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6487,7 +6493,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B84" s="5">
         <v>46181.61473356481</v>
@@ -6497,16 +6503,16 @@
         <v>46182.64084413194</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I84" s="5">
         <v>46267</v>
@@ -6524,13 +6530,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6540,7 +6546,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B85" s="8">
         <v>46181.61477212963</v>
@@ -6550,16 +6556,16 @@
         <v>46182.64084086806</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I85" s="8">
         <v>46267</v>
@@ -6577,13 +6583,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -6593,7 +6599,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B86" s="5">
         <v>46181.61484836806</v>
@@ -6603,16 +6609,16 @@
         <v>46182.6408357176</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I86" s="5">
         <v>46267</v>
@@ -6630,13 +6636,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6646,7 +6652,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B87" s="8">
         <v>46181.60926783565</v>
@@ -6656,7 +6662,7 @@
         <v>46182.64099746528</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
@@ -6683,13 +6689,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q87" s="8">
         <v>46289</v>
@@ -6709,7 +6715,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B88" s="5">
         <v>46181.60927226851</v>
@@ -6746,13 +6752,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6762,7 +6768,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B89" s="8">
         <v>46181.60927799769</v>
@@ -6799,13 +6805,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -6815,7 +6821,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B90" s="5">
         <v>46181.614954062505</v>
@@ -6825,7 +6831,7 @@
         <v>46182.64096971064</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6852,13 +6858,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6868,7 +6874,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B91" s="8">
         <v>46181.61498993056</v>
@@ -6878,7 +6884,7 @@
         <v>46182.64096709491</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -6905,13 +6911,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -6921,7 +6927,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B92" s="5">
         <v>46181.61502625</v>
@@ -6931,7 +6937,7 @@
         <v>46182.64096319444</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6958,13 +6964,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6974,7 +6980,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B93" s="8">
         <v>46181.60928361111</v>
@@ -6984,7 +6990,7 @@
         <v>46182.567648321754</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>25</v>
@@ -7008,7 +7014,7 @@
         <v>26</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="P93" s="9" t="s">
         <v>26</v>
@@ -7021,7 +7027,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B94" s="5">
         <v>46181.609286990744</v>
@@ -7031,16 +7037,16 @@
         <v>46190.88639451389</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I94" s="5">
         <v>46182</v>
@@ -7058,13 +7064,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q94" s="5">
         <v>46182</v>
@@ -7084,7 +7090,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B95" s="8">
         <v>46181.609292974535</v>
@@ -7094,16 +7100,16 @@
         <v>46190.886394166664</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I95" s="8">
         <v>46290</v>
@@ -7121,13 +7127,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="O95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q95" s="8">
         <v>46290</v>
@@ -7147,7 +7153,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B96" s="5">
         <v>46181.60929881944</v>
@@ -7157,16 +7163,16 @@
         <v>46190.886404791665</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I96" s="5">
         <v>46226</v>
@@ -7184,13 +7190,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q96" s="5">
         <v>46226</v>
@@ -7210,7 +7216,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B97" s="8">
         <v>46181.60930480324</v>
@@ -7220,16 +7226,16 @@
         <v>46182.64108152778</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I97" s="8">
         <v>46293</v>
@@ -7247,13 +7253,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="O97" s="9" t="s">
         <v>157</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q97" s="8">
         <v>46293</v>
@@ -7273,7 +7279,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B98" s="5">
         <v>46181.60935271991</v>
@@ -7289,10 +7295,10 @@
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I98" s="5">
         <v>46226</v>
@@ -7310,7 +7316,7 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="O98" s="6" t="s">
         <v>129</v>
@@ -7336,7 +7342,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B99" s="8">
         <v>46181.60936674768</v>
@@ -7346,7 +7352,7 @@
         <v>46182.633312060185</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>25</v>
@@ -7370,7 +7376,7 @@
         <v>26</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="P99" s="9" t="s">
         <v>26</v>
@@ -7383,7 +7389,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B100" s="5">
         <v>46181.609371666666</v>
@@ -7393,7 +7399,7 @@
         <v>46182.64123547454</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7420,13 +7426,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q100" s="5">
         <v>46290</v>
@@ -7446,7 +7452,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B101" s="8">
         <v>46181.609378587964</v>
@@ -7483,13 +7489,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7499,7 +7505,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B102" s="5">
         <v>46181.61514019676</v>
@@ -7536,13 +7542,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>181</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7552,7 +7558,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B103" s="8">
         <v>46181.609386111115</v>
@@ -7562,7 +7568,7 @@
         <v>46182.641349328704</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -7589,13 +7595,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="O103" s="9" t="s">
         <v>181</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q103" s="8">
         <v>46311</v>
@@ -7615,7 +7621,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B104" s="5">
         <v>46181.60939194444</v>
@@ -7652,13 +7658,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7668,7 +7674,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B105" s="8">
         <v>46181.61518315972</v>
@@ -7705,10 +7711,10 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="P105" s="9" t="s">
         <v>26</v>
@@ -7721,7 +7727,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B106" s="5">
         <v>46181.60939866898</v>
@@ -7731,7 +7737,7 @@
         <v>46182.64144489584</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7758,13 +7764,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>181</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q106" s="5">
         <v>46315</v>
@@ -7784,7 +7790,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B107" s="8">
         <v>46181.60940505787</v>
@@ -7821,13 +7827,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -7837,7 +7843,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B108" s="5">
         <v>46181.61523613426</v>
@@ -7874,10 +7880,10 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>26</v>
@@ -7890,7 +7896,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B109" s="8">
         <v>46181.60941365741</v>
@@ -7900,7 +7906,7 @@
         <v>46182.64155526621</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -7927,13 +7933,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="O109" s="9" t="s">
         <v>181</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q109" s="8">
         <v>46317</v>
@@ -7953,7 +7959,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B110" s="5">
         <v>46181.60941929398</v>
@@ -7990,13 +7996,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8006,7 +8012,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B111" s="8">
         <v>46181.61528053241</v>
@@ -8043,10 +8049,10 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="P111" s="9" t="s">
         <v>26</v>
@@ -8059,7 +8065,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B112" s="5">
         <v>46181.60942706019</v>
@@ -8069,7 +8075,7 @@
         <v>46182.64166112269</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8096,13 +8102,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>181</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q112" s="5">
         <v>46321</v>
@@ -8122,7 +8128,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B113" s="8">
         <v>46181.60943415509</v>
@@ -8159,13 +8165,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="O113" s="9" t="s">
         <v>181</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8175,7 +8181,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B114" s="5">
         <v>46181.61532783565</v>
@@ -8212,13 +8218,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>181</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8228,7 +8234,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B115" s="8">
         <v>46181.60944410879</v>
@@ -8238,7 +8244,7 @@
         <v>46182.82922638889</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
@@ -8265,13 +8271,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="O115" s="9" t="s">
         <v>181</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q115" s="8">
         <v>46323</v>
@@ -8291,7 +8297,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B116" s="5">
         <v>46181.60944996528</v>
@@ -8328,13 +8334,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="O116" s="6" t="s">
         <v>181</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8344,7 +8350,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B117" s="8">
         <v>46181.61537143518</v>
@@ -8381,10 +8387,10 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="P117" s="9" t="s">
         <v>26</v>
@@ -8397,7 +8403,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B118" s="5">
         <v>46181.60945642361</v>
@@ -8407,7 +8413,7 @@
         <v>46182.634494212965</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>25</v>
@@ -8431,7 +8437,7 @@
         <v>26</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>26</v>
@@ -8444,7 +8450,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B119" s="8">
         <v>46181.60946096065</v>
@@ -8454,16 +8460,16 @@
         <v>46182.64186350694</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H119" s="9" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="I119" s="8">
         <v>46324</v>
@@ -8481,13 +8487,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q119" s="8">
         <v>46324</v>
@@ -8507,7 +8513,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B120" s="5">
         <v>46181.60946868056</v>
@@ -8523,10 +8529,10 @@
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="I120" s="5">
         <v>46324</v>
@@ -8544,13 +8550,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>181</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8560,7 +8566,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B121" s="8">
         <v>46181.609475034726</v>
@@ -8576,10 +8582,10 @@
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H121" s="9" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="I121" s="8">
         <v>46324</v>
@@ -8597,7 +8603,7 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="O121" s="9" t="s">
         <v>181</v>
@@ -8613,7 +8619,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B122" s="5">
         <v>46181.60947921296</v>
@@ -8629,10 +8635,10 @@
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="I122" s="5">
         <v>46324</v>
@@ -8650,7 +8656,7 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>59</v>
@@ -8666,7 +8672,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B123" s="8">
         <v>46181.61605960648</v>
@@ -8682,10 +8688,10 @@
         <v>26</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H123" s="9" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="I123" s="8">
         <v>46324</v>
@@ -8703,7 +8709,7 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="O123" s="9" t="s">
         <v>59</v>
@@ -8719,7 +8725,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B124" s="5">
         <v>46181.61617203704</v>
@@ -8729,16 +8735,16 @@
         <v>46182.64182482639</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="I124" s="5">
         <v>46324</v>
@@ -8756,13 +8762,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8772,7 +8778,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B125" s="8">
         <v>46181.61620771991</v>
@@ -8782,16 +8788,16 @@
         <v>46182.64182413195</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H125" s="9" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="I125" s="8">
         <v>46324</v>
@@ -8809,13 +8815,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -8825,7 +8831,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B126" s="5">
         <v>46181.616245833335</v>
@@ -8835,16 +8841,16 @@
         <v>46182.641823425925</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="I126" s="5">
         <v>46324</v>
@@ -8862,13 +8868,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8878,7 +8884,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B127" s="8">
         <v>46181.60948424769</v>
@@ -8888,7 +8894,7 @@
         <v>46182.64199267361</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
@@ -8915,13 +8921,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O127" s="9" t="s">
         <v>181</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q127" s="8">
         <v>46325</v>
@@ -8941,7 +8947,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B128" s="5">
         <v>46181.60948969907</v>
@@ -8978,13 +8984,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="O128" s="6" t="s">
         <v>181</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -8994,7 +9000,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B129" s="8">
         <v>46181.60949538194</v>
@@ -9031,7 +9037,7 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="O129" s="9" t="s">
         <v>181</v>
@@ -9047,7 +9053,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B130" s="5">
         <v>46181.609560185185</v>
@@ -9084,7 +9090,7 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="O130" s="6" t="s">
         <v>59</v>
@@ -9100,7 +9106,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B131" s="8">
         <v>46181.61659114584</v>
@@ -9137,7 +9143,7 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="O131" s="9" t="s">
         <v>59</v>
@@ -9153,7 +9159,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B132" s="5">
         <v>46181.61662431713</v>
@@ -9163,7 +9169,7 @@
         <v>46182.64196105324</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9190,13 +9196,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9206,7 +9212,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B133" s="8">
         <v>46181.61666238426</v>
@@ -9216,7 +9222,7 @@
         <v>46182.64195453704</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
@@ -9243,13 +9249,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9259,7 +9265,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B134" s="5">
         <v>46181.61670006944</v>
@@ -9269,7 +9275,7 @@
         <v>46182.64195372685</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9296,13 +9302,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9312,7 +9318,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B135" s="8">
         <v>46181.60956560185</v>
@@ -9322,16 +9328,16 @@
         <v>46182.82952324074</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I135" s="8">
         <v>46328</v>
@@ -9349,13 +9355,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O135" s="9" t="s">
         <v>181</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q135" s="8">
         <v>46328</v>
@@ -9375,7 +9381,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B136" s="5">
         <v>46181.60957188657</v>
@@ -9391,10 +9397,10 @@
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I136" s="5">
         <v>46328</v>
@@ -9412,13 +9418,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="O136" s="6" t="s">
         <v>181</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9428,7 +9434,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B137" s="8">
         <v>46181.609583576384</v>
@@ -9444,10 +9450,10 @@
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I137" s="8">
         <v>46328</v>
@@ -9465,7 +9471,7 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="O137" s="9" t="s">
         <v>181</v>
@@ -9481,7 +9487,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B138" s="5">
         <v>46181.60958841435</v>
@@ -9497,10 +9503,10 @@
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I138" s="5">
         <v>46328</v>
@@ -9518,7 +9524,7 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="O138" s="6" t="s">
         <v>59</v>
@@ -9534,7 +9540,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B139" s="8">
         <v>46181.616839849536</v>
@@ -9550,10 +9556,10 @@
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I139" s="8">
         <v>46328</v>
@@ -9571,7 +9577,7 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="O139" s="9" t="s">
         <v>59</v>
@@ -9587,7 +9593,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B140" s="5">
         <v>46181.61689748843</v>
@@ -9597,16 +9603,16 @@
         <v>46182.8294564699</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I140" s="5">
         <v>46328</v>
@@ -9624,13 +9630,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9640,7 +9646,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B141" s="8">
         <v>46181.616942569446</v>
@@ -9650,16 +9656,16 @@
         <v>46182.82945721065</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I141" s="8">
         <v>46328</v>
@@ -9677,13 +9683,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -9693,7 +9699,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B142" s="5">
         <v>46181.6169815162</v>
@@ -9703,16 +9709,16 @@
         <v>46182.82945796296</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I142" s="5">
         <v>46328</v>
@@ -9730,13 +9736,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9746,7 +9752,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B143" s="8">
         <v>46181.609592673616</v>
@@ -9756,16 +9762,16 @@
         <v>46182.642407384265</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I143" s="8">
         <v>46329</v>
@@ -9783,13 +9789,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O143" s="9" t="s">
         <v>181</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q143" s="8">
         <v>46329</v>
@@ -9809,7 +9815,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B144" s="5">
         <v>46181.60960517361</v>
@@ -9825,10 +9831,10 @@
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I144" s="5">
         <v>46329</v>
@@ -9846,13 +9852,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="O144" s="6" t="s">
         <v>181</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -9862,7 +9868,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B145" s="8">
         <v>46181.609610011576</v>
@@ -9878,10 +9884,10 @@
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H145" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I145" s="8">
         <v>46329</v>
@@ -9899,7 +9905,7 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="O145" s="9" t="s">
         <v>181</v>
@@ -9915,7 +9921,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B146" s="5">
         <v>46181.609613796296</v>
@@ -9931,10 +9937,10 @@
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I146" s="5">
         <v>46329</v>
@@ -9952,7 +9958,7 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="O146" s="6" t="s">
         <v>59</v>
@@ -9968,7 +9974,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B147" s="8">
         <v>46181.61712142361</v>
@@ -9984,10 +9990,10 @@
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I147" s="8">
         <v>46329</v>
@@ -10005,7 +10011,7 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="O147" s="9" t="s">
         <v>59</v>
@@ -10021,7 +10027,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B148" s="5">
         <v>46181.61716094907</v>
@@ -10031,16 +10037,16 @@
         <v>46182.82945207176</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I148" s="5">
         <v>46329</v>
@@ -10058,10 +10064,10 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="P148" s="6" t="s">
         <v>26</v>
@@ -10074,7 +10080,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B149" s="8">
         <v>46181.61719633102</v>
@@ -10084,16 +10090,16 @@
         <v>46182.829452025464</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H149" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I149" s="8">
         <v>46329</v>
@@ -10111,10 +10117,10 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="P149" s="9" t="s">
         <v>26</v>
@@ -10127,7 +10133,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B150" s="5">
         <v>46181.617235451384</v>
@@ -10137,16 +10143,16 @@
         <v>46182.829452418984</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I150" s="5">
         <v>46329</v>
@@ -10164,10 +10170,10 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P150" s="6" t="s">
         <v>26</v>
@@ -10180,7 +10186,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B151" s="8">
         <v>46181.60961741898</v>
@@ -10190,7 +10196,7 @@
         <v>46182.63449439815</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>25</v>
@@ -10214,7 +10220,7 @@
         <v>26</v>
       </c>
       <c r="O151" s="9" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="P151" s="9" t="s">
         <v>26</v>
@@ -10227,7 +10233,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B152" s="5">
         <v>46181.60962174769</v>
@@ -10237,16 +10243,16 @@
         <v>46182.64244836806</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="I152" s="5">
         <v>46330</v>
@@ -10264,13 +10270,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q152" s="5">
         <v>46330</v>
@@ -10290,7 +10296,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B153" s="8">
         <v>46181.60962780092</v>
@@ -10300,7 +10306,7 @@
         <v>46191.67892958333</v>
       </c>
       <c r="E153" s="9" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F153" s="9" t="s">
         <v>26</v>
@@ -10327,13 +10333,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="9" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="O153" s="9" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="P153" s="9" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q153" s="8">
         <v>46330</v>
@@ -10353,7 +10359,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B154" s="5">
         <v>46181.60963489584</v>
@@ -10363,7 +10369,7 @@
         <v>46182.63449431713</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>25</v>
@@ -10387,7 +10393,7 @@
         <v>26</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="P154" s="6" t="s">
         <v>26</v>
@@ -10406,7 +10412,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B155" s="8">
         <v>46181.609640208335</v>
@@ -10416,7 +10422,7 @@
         <v>46182.64254377315</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>26</v>
@@ -10443,13 +10449,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="9" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="O155" s="9" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="P155" s="9" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="Q155" s="8">
         <v>46330</v>
@@ -10469,7 +10475,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B156" s="5">
         <v>46181.609646365745</v>
@@ -10479,7 +10485,7 @@
         <v>46182.64254079861</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
@@ -10506,13 +10512,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="Q156" s="5">
         <v>46339</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -1864,13 +1864,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46181.60862950231</v>
+        <v>46181.44196283565</v>
       </c>
       <c r="C4" s="5">
-        <v>46190.67646162037</v>
+        <v>46190.5097949537</v>
       </c>
       <c r="D4" s="5">
-        <v>46191.77859822917</v>
+        <v>46191.6119315625</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1913,13 +1913,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46181.60880893518</v>
+        <v>46181.44214226852</v>
       </c>
       <c r="C5" s="8">
-        <v>46190.675863854165</v>
+        <v>46190.5091971875</v>
       </c>
       <c r="D5" s="8">
-        <v>46190.676329525464</v>
+        <v>46190.50966285879</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1976,13 +1976,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46181.60881340278</v>
+        <v>46181.44214673611</v>
       </c>
       <c r="C6" s="5">
-        <v>46190.67626129629</v>
+        <v>46190.50959462963</v>
       </c>
       <c r="D6" s="5">
-        <v>46190.676280844906</v>
+        <v>46190.50961417824</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2039,13 +2039,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="8">
-        <v>46181.60881648149</v>
+        <v>46181.442149814815</v>
       </c>
       <c r="C7" s="8">
-        <v>46190.67642019676</v>
+        <v>46190.50975353009</v>
       </c>
       <c r="D7" s="8">
-        <v>46190.67643417824</v>
+        <v>46190.509767511576</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>37</v>
@@ -2102,13 +2102,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46181.60882040509</v>
+        <v>46181.442153738426</v>
       </c>
       <c r="C8" s="5">
-        <v>46190.67644660879</v>
+        <v>46190.509779942135</v>
       </c>
       <c r="D8" s="5">
-        <v>46190.67646199074</v>
+        <v>46190.50979532408</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2165,11 +2165,11 @@
         <v>43</v>
       </c>
       <c r="B9" s="8">
-        <v>46181.60863523148</v>
+        <v>46181.44196856482</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="8">
-        <v>46190.6778103588</v>
+        <v>46190.51114369213</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>44</v>
@@ -2212,13 +2212,13 @@
         <v>46</v>
       </c>
       <c r="B10" s="5">
-        <v>46181.608824131945</v>
+        <v>46181.44215746528</v>
       </c>
       <c r="C10" s="5">
-        <v>46190.67780464121</v>
+        <v>46190.511137974536</v>
       </c>
       <c r="D10" s="5">
-        <v>46190.67781991899</v>
+        <v>46190.511153252315</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -2277,11 +2277,11 @@
         <v>51</v>
       </c>
       <c r="B11" s="8">
-        <v>46181.60882959491</v>
+        <v>46181.442162928244</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="8">
-        <v>46182.62580337963</v>
+        <v>46182.45913671296</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>52</v>
@@ -2340,11 +2340,11 @@
         <v>58</v>
       </c>
       <c r="B12" s="5">
-        <v>46181.608834976854</v>
+        <v>46181.44216831018</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46182.62589634259</v>
+        <v>46182.45922967592</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>59</v>
@@ -2393,11 +2393,11 @@
         <v>62</v>
       </c>
       <c r="B13" s="8">
-        <v>46181.61813184028</v>
+        <v>46181.45146517361</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46182.625892881944</v>
+        <v>46182.45922621527</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>59</v>
@@ -2446,11 +2446,11 @@
         <v>64</v>
       </c>
       <c r="B14" s="5">
-        <v>46181.60864021991</v>
+        <v>46181.44197355324</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46191.77864815972</v>
+        <v>46191.61198149306</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>65</v>
@@ -2493,13 +2493,13 @@
         <v>67</v>
       </c>
       <c r="B15" s="8">
-        <v>46181.60883864583</v>
+        <v>46181.44217197917</v>
       </c>
       <c r="C15" s="8">
-        <v>46190.67744403935</v>
+        <v>46190.510777372685</v>
       </c>
       <c r="D15" s="8">
-        <v>46191.67892994213</v>
+        <v>46191.512263275465</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>68</v>
@@ -2558,13 +2558,13 @@
         <v>71</v>
       </c>
       <c r="B16" s="5">
-        <v>46181.60884395833</v>
+        <v>46181.44217729167</v>
       </c>
       <c r="C16" s="5">
-        <v>46190.67745200232</v>
+        <v>46190.510785335646</v>
       </c>
       <c r="D16" s="5">
-        <v>46191.67892980324</v>
+        <v>46191.512263136574</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>72</v>
@@ -2623,13 +2623,13 @@
         <v>75</v>
       </c>
       <c r="B17" s="8">
-        <v>46181.608850046294</v>
+        <v>46181.44218337963</v>
       </c>
       <c r="C17" s="8">
-        <v>46190.67745870371</v>
+        <v>46190.510792037036</v>
       </c>
       <c r="D17" s="8">
-        <v>46191.67892980324</v>
+        <v>46191.512263136574</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>76</v>
@@ -2688,11 +2688,11 @@
         <v>78</v>
       </c>
       <c r="B18" s="5">
-        <v>46181.60864670139</v>
+        <v>46181.441980034724</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46197.42282767361</v>
+        <v>46197.256161006946</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>79</v>
@@ -2737,13 +2737,13 @@
         <v>82</v>
       </c>
       <c r="B19" s="8">
-        <v>46181.608864236114</v>
+        <v>46181.44219756944</v>
       </c>
       <c r="C19" s="8">
-        <v>46190.677672986116</v>
+        <v>46190.511006319444</v>
       </c>
       <c r="D19" s="8">
-        <v>46190.88639424769</v>
+        <v>46190.71972758102</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>83</v>
@@ -2802,13 +2802,13 @@
         <v>85</v>
       </c>
       <c r="B20" s="5">
-        <v>46181.60886979167</v>
+        <v>46181.442203125</v>
       </c>
       <c r="C20" s="5">
-        <v>46190.677678657405</v>
+        <v>46190.51101199074</v>
       </c>
       <c r="D20" s="5">
-        <v>46190.88638454861</v>
+        <v>46190.71971788195</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>86</v>
@@ -2867,13 +2867,13 @@
         <v>88</v>
       </c>
       <c r="B21" s="8">
-        <v>46181.60887520833</v>
+        <v>46181.442208541666</v>
       </c>
       <c r="C21" s="8">
-        <v>46197.42280901621</v>
+        <v>46197.256142349535</v>
       </c>
       <c r="D21" s="8">
-        <v>46197.422811446755</v>
+        <v>46197.25614478009</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>89</v>
@@ -2932,13 +2932,13 @@
         <v>92</v>
       </c>
       <c r="B22" s="5">
-        <v>46181.60888054398</v>
+        <v>46181.442213877315</v>
       </c>
       <c r="C22" s="5">
-        <v>46196.658568541665</v>
+        <v>46196.491901875</v>
       </c>
       <c r="D22" s="5">
-        <v>46196.65858296296</v>
+        <v>46196.4919162963</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>93</v>
@@ -2997,13 +2997,13 @@
         <v>98</v>
       </c>
       <c r="B23" s="8">
-        <v>46181.60888559028</v>
+        <v>46181.44221892361</v>
       </c>
       <c r="C23" s="8">
-        <v>46196.65883074074</v>
+        <v>46196.49216407408</v>
       </c>
       <c r="D23" s="8">
-        <v>46196.658845625</v>
+        <v>46196.49217895833</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>99</v>
@@ -3062,11 +3062,11 @@
         <v>101</v>
       </c>
       <c r="B24" s="5">
-        <v>46181.60888961806</v>
+        <v>46181.44222295139</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46191.67367153935</v>
+        <v>46191.507004872685</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>102</v>
@@ -3125,13 +3125,13 @@
         <v>104</v>
       </c>
       <c r="B25" s="8">
-        <v>46181.6088934375</v>
+        <v>46181.44222677083</v>
       </c>
       <c r="C25" s="8">
-        <v>46197.64511049769</v>
+        <v>46197.478443831016</v>
       </c>
       <c r="D25" s="8">
-        <v>46197.64512664352</v>
+        <v>46197.47845997685</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>105</v>
@@ -3190,13 +3190,13 @@
         <v>107</v>
       </c>
       <c r="B26" s="5">
-        <v>46181.608897638886</v>
+        <v>46181.44223097222</v>
       </c>
       <c r="C26" s="5">
-        <v>46190.67785231481</v>
+        <v>46190.51118564815</v>
       </c>
       <c r="D26" s="5">
-        <v>46190.67787061342</v>
+        <v>46190.511203946764</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>108</v>
@@ -3255,13 +3255,13 @@
         <v>110</v>
       </c>
       <c r="B27" s="8">
-        <v>46190.88204489583</v>
+        <v>46190.71537822917</v>
       </c>
       <c r="C27" s="8">
-        <v>46197.42407642362</v>
+        <v>46197.257409756945</v>
       </c>
       <c r="D27" s="8">
-        <v>46197.424089050925</v>
+        <v>46197.25742238426</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>111</v>
@@ -3308,13 +3308,13 @@
         <v>112</v>
       </c>
       <c r="B28" s="5">
-        <v>46190.88321909722</v>
+        <v>46190.71655243056</v>
       </c>
       <c r="C28" s="5">
-        <v>46197.42354282408</v>
+        <v>46197.25687615741</v>
       </c>
       <c r="D28" s="5">
-        <v>46197.42355928241</v>
+        <v>46197.25689261574</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>113</v>
@@ -3373,13 +3373,13 @@
         <v>114</v>
       </c>
       <c r="B29" s="8">
-        <v>46190.88327185185</v>
+        <v>46190.71660518518</v>
       </c>
       <c r="C29" s="8">
-        <v>46197.42396493055</v>
+        <v>46197.25729826389</v>
       </c>
       <c r="D29" s="8">
-        <v>46197.423981597225</v>
+        <v>46197.25731493055</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>115</v>
@@ -3438,13 +3438,13 @@
         <v>116</v>
       </c>
       <c r="B30" s="5">
-        <v>46190.88332659722</v>
+        <v>46190.71665993056</v>
       </c>
       <c r="C30" s="5">
-        <v>46197.42406122685</v>
+        <v>46197.25739456018</v>
       </c>
       <c r="D30" s="5">
-        <v>46197.42407648148</v>
+        <v>46197.25740981482</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>117</v>
@@ -3503,11 +3503,11 @@
         <v>118</v>
       </c>
       <c r="B31" s="8">
-        <v>46181.608652256946</v>
+        <v>46181.44198559028</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46190.886375057875</v>
+        <v>46190.7197083912</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>119</v>
@@ -3550,11 +3550,11 @@
         <v>121</v>
       </c>
       <c r="B32" s="5">
-        <v>46181.60900793981</v>
+        <v>46181.44234127315</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46195.6859309838</v>
+        <v>46195.51926431713</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>122</v>
@@ -3613,13 +3613,13 @@
         <v>126</v>
       </c>
       <c r="B33" s="8">
-        <v>46181.60901165509</v>
+        <v>46181.44234498843</v>
       </c>
       <c r="C33" s="8">
-        <v>46195.685925451384</v>
+        <v>46195.51925878473</v>
       </c>
       <c r="D33" s="8">
-        <v>46195.68592747685</v>
+        <v>46195.519260810186</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>109</v>
@@ -3668,11 +3668,11 @@
         <v>128</v>
       </c>
       <c r="B34" s="5">
-        <v>46181.60901612269</v>
+        <v>46181.44234945602</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46195.685932430555</v>
+        <v>46195.51926576388</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>129</v>
@@ -3721,11 +3721,11 @@
         <v>131</v>
       </c>
       <c r="B35" s="8">
-        <v>46181.60902011574</v>
+        <v>46181.44235344908</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46182.6267959838</v>
+        <v>46182.46012931713</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>120</v>
@@ -3784,11 +3784,11 @@
         <v>135</v>
       </c>
       <c r="B36" s="5">
-        <v>46181.60902488426</v>
+        <v>46181.442358217595</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46196.65857439815</v>
+        <v>46196.491907731484</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
@@ -3843,11 +3843,11 @@
         <v>138</v>
       </c>
       <c r="B37" s="8">
-        <v>46181.609029803236</v>
+        <v>46181.44236313658</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="8">
-        <v>46182.6267641088</v>
+        <v>46182.460097442134</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>139</v>
@@ -3902,11 +3902,11 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46181.60903511574</v>
+        <v>46181.442368449076</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46182.626906840276</v>
+        <v>46182.46024017361</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -3965,11 +3965,11 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46181.60903861111</v>
+        <v>46181.442371944446</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46196.65883732639</v>
+        <v>46196.49217065972</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>100</v>
@@ -4018,11 +4018,11 @@
         <v>146</v>
       </c>
       <c r="B40" s="5">
-        <v>46181.609042951386</v>
+        <v>46181.44237628472</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46182.626868680556</v>
+        <v>46182.460202013885</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>147</v>
@@ -4071,11 +4071,11 @@
         <v>149</v>
       </c>
       <c r="B41" s="8">
-        <v>46181.609047164355</v>
+        <v>46181.44238049768</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="8">
-        <v>46183.70162199074</v>
+        <v>46183.534955324074</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>150</v>
@@ -4134,11 +4134,11 @@
         <v>154</v>
       </c>
       <c r="B42" s="5">
-        <v>46181.60905075232</v>
+        <v>46181.44238408565</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46197.6451175</v>
+        <v>46197.47845083333</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>106</v>
@@ -4187,11 +4187,11 @@
         <v>156</v>
       </c>
       <c r="B43" s="8">
-        <v>46181.60905546296</v>
+        <v>46181.44238879629</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="8">
-        <v>46183.70547770833</v>
+        <v>46183.53881104167</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>157</v>
@@ -4240,11 +4240,11 @@
         <v>159</v>
       </c>
       <c r="B44" s="5">
-        <v>46181.60906018519</v>
+        <v>46181.44239351852</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46182.62707423611</v>
+        <v>46182.460407569444</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>160</v>
@@ -4293,11 +4293,11 @@
         <v>163</v>
       </c>
       <c r="B45" s="8">
-        <v>46181.609063310185</v>
+        <v>46181.44239664351</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46182.62725847222</v>
+        <v>46182.46059180556</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>164</v>
@@ -4356,11 +4356,11 @@
         <v>166</v>
       </c>
       <c r="B46" s="5">
-        <v>46181.60906703703</v>
+        <v>46181.442400370375</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46182.62720454861</v>
+        <v>46182.46053788194</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>103</v>
@@ -4409,11 +4409,11 @@
         <v>168</v>
       </c>
       <c r="B47" s="8">
-        <v>46181.60907681713</v>
+        <v>46181.44241015046</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46182.627201296295</v>
+        <v>46182.46053462963</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>169</v>
@@ -4462,11 +4462,11 @@
         <v>171</v>
       </c>
       <c r="B48" s="5">
-        <v>46181.6090815625</v>
+        <v>46181.442414895835</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46191.542751388886</v>
+        <v>46191.37608472222</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>172</v>
@@ -4511,13 +4511,13 @@
         <v>174</v>
       </c>
       <c r="B49" s="8">
-        <v>46181.60908480324</v>
+        <v>46181.442418136576</v>
       </c>
       <c r="C49" s="8">
-        <v>46190.708245752314</v>
+        <v>46190.54157908565</v>
       </c>
       <c r="D49" s="8">
-        <v>46197.7158150926</v>
+        <v>46197.549148425926</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>175</v>
@@ -4576,13 +4576,13 @@
         <v>180</v>
       </c>
       <c r="B50" s="5">
-        <v>46181.60908915509</v>
+        <v>46181.44242248843</v>
       </c>
       <c r="C50" s="5">
-        <v>46190.70821236111</v>
+        <v>46190.54154569445</v>
       </c>
       <c r="D50" s="5">
-        <v>46190.70821390046</v>
+        <v>46190.54154723379</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>181</v>
@@ -4631,13 +4631,13 @@
         <v>185</v>
       </c>
       <c r="B51" s="8">
-        <v>46181.60909384259</v>
+        <v>46181.44242717593</v>
       </c>
       <c r="C51" s="8">
-        <v>46190.70822138889</v>
+        <v>46190.54155472222</v>
       </c>
       <c r="D51" s="8">
-        <v>46190.7082228125</v>
+        <v>46190.541556145836</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>186</v>
@@ -4686,13 +4686,13 @@
         <v>188</v>
       </c>
       <c r="B52" s="5">
-        <v>46181.61221741898</v>
+        <v>46181.445550752316</v>
       </c>
       <c r="C52" s="5">
-        <v>46190.70822601852</v>
+        <v>46190.541559351856</v>
       </c>
       <c r="D52" s="5">
-        <v>46190.708227337964</v>
+        <v>46190.54156067129</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>189</v>
@@ -4741,13 +4741,13 @@
         <v>190</v>
       </c>
       <c r="B53" s="8">
-        <v>46181.612357199076</v>
+        <v>46181.445690532404</v>
       </c>
       <c r="C53" s="8">
-        <v>46190.70823167824</v>
+        <v>46190.541565011576</v>
       </c>
       <c r="D53" s="8">
-        <v>46190.708233321755</v>
+        <v>46190.5415666551</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>191</v>
@@ -4796,13 +4796,13 @@
         <v>192</v>
       </c>
       <c r="B54" s="5">
-        <v>46181.609098182875</v>
+        <v>46181.4424315162</v>
       </c>
       <c r="C54" s="5">
-        <v>46191.54272982639</v>
+        <v>46191.376063159725</v>
       </c>
       <c r="D54" s="5">
-        <v>46197.71584820602</v>
+        <v>46197.54918153935</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>193</v>
@@ -4861,13 +4861,13 @@
         <v>194</v>
       </c>
       <c r="B55" s="8">
-        <v>46181.60910252314</v>
+        <v>46181.44243585649</v>
       </c>
       <c r="C55" s="8">
-        <v>46191.54270648149</v>
+        <v>46191.376039814815</v>
       </c>
       <c r="D55" s="8">
-        <v>46191.54270819444</v>
+        <v>46191.37604152778</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>181</v>
@@ -4916,13 +4916,13 @@
         <v>196</v>
       </c>
       <c r="B56" s="5">
-        <v>46181.609107951386</v>
+        <v>46181.44244128472</v>
       </c>
       <c r="C56" s="5">
-        <v>46191.542715625</v>
+        <v>46191.37604895834</v>
       </c>
       <c r="D56" s="5">
-        <v>46191.54271703704</v>
+        <v>46191.37605037037</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>186</v>
@@ -4971,13 +4971,13 @@
         <v>198</v>
       </c>
       <c r="B57" s="8">
-        <v>46181.61393570602</v>
+        <v>46181.44726903935</v>
       </c>
       <c r="C57" s="8">
-        <v>46190.70842026621</v>
+        <v>46190.54175359954</v>
       </c>
       <c r="D57" s="8">
-        <v>46190.70842170139</v>
+        <v>46190.54175503472</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>189</v>
@@ -5026,13 +5026,13 @@
         <v>199</v>
       </c>
       <c r="B58" s="5">
-        <v>46181.61396929398</v>
+        <v>46181.44730262732</v>
       </c>
       <c r="C58" s="5">
-        <v>46190.70842520833</v>
+        <v>46190.541758541665</v>
       </c>
       <c r="D58" s="5">
-        <v>46190.708426550926</v>
+        <v>46190.54175988426</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>191</v>
@@ -5081,13 +5081,13 @@
         <v>200</v>
       </c>
       <c r="B59" s="8">
-        <v>46181.60911329861</v>
+        <v>46181.44244663195</v>
       </c>
       <c r="C59" s="8">
-        <v>46191.54538693287</v>
+        <v>46191.378720266206</v>
       </c>
       <c r="D59" s="8">
-        <v>46191.54539826389</v>
+        <v>46191.37873159722</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>96</v>
@@ -5146,13 +5146,13 @@
         <v>202</v>
       </c>
       <c r="B60" s="5">
-        <v>46181.60912350695</v>
+        <v>46181.442456840276</v>
       </c>
       <c r="C60" s="5">
-        <v>46191.54535901621</v>
+        <v>46191.378692349535</v>
       </c>
       <c r="D60" s="5">
-        <v>46191.54536050926</v>
+        <v>46191.37869384259</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>181</v>
@@ -5199,13 +5199,13 @@
         <v>203</v>
       </c>
       <c r="B61" s="8">
-        <v>46181.60912782408</v>
+        <v>46181.44246115741</v>
       </c>
       <c r="C61" s="8">
-        <v>46191.54537241899</v>
+        <v>46191.378705752315</v>
       </c>
       <c r="D61" s="8">
-        <v>46191.54537386574</v>
+        <v>46191.378707199074</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>186</v>
@@ -5252,13 +5252,13 @@
         <v>204</v>
       </c>
       <c r="B62" s="5">
-        <v>46181.614119606485</v>
+        <v>46181.447452939814</v>
       </c>
       <c r="C62" s="5">
-        <v>46190.72172383102</v>
+        <v>46190.555057164354</v>
       </c>
       <c r="D62" s="5">
-        <v>46190.721725358795</v>
+        <v>46190.55505869213</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>189</v>
@@ -5305,13 +5305,13 @@
         <v>205</v>
       </c>
       <c r="B63" s="8">
-        <v>46181.61419627315</v>
+        <v>46181.44752960648</v>
       </c>
       <c r="C63" s="8">
-        <v>46190.72172868055</v>
+        <v>46190.55506201389</v>
       </c>
       <c r="D63" s="8">
-        <v>46190.7217299537</v>
+        <v>46190.555063287036</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>191</v>
@@ -5358,11 +5358,11 @@
         <v>206</v>
       </c>
       <c r="B64" s="5">
-        <v>46181.60913207176</v>
+        <v>46181.442465405096</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46182.633118067126</v>
+        <v>46182.46645140046</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>207</v>
@@ -5421,11 +5421,11 @@
         <v>210</v>
       </c>
       <c r="B65" s="8">
-        <v>46181.609135833336</v>
+        <v>46181.442469166665</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46182.63311847222</v>
+        <v>46182.46645180555</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>181</v>
@@ -5474,11 +5474,11 @@
         <v>212</v>
       </c>
       <c r="B66" s="5">
-        <v>46181.614311909725</v>
+        <v>46181.44764524305</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46182.63311923611</v>
+        <v>46182.466452569446</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>213</v>
@@ -5527,11 +5527,11 @@
         <v>214</v>
       </c>
       <c r="B67" s="8">
-        <v>46181.60918671296</v>
+        <v>46181.4425200463</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46181.77983537037</v>
+        <v>46181.613168703705</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>215</v>
@@ -5574,11 +5574,11 @@
         <v>217</v>
       </c>
       <c r="B68" s="5">
-        <v>46181.609196087964</v>
+        <v>46181.4425294213</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46182.63576145833</v>
+        <v>46182.46909479167</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>218</v>
@@ -5637,11 +5637,11 @@
         <v>222</v>
       </c>
       <c r="B69" s="8">
-        <v>46181.609201921296</v>
+        <v>46181.44253525463</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46182.63583637732</v>
+        <v>46182.46916971065</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>223</v>
@@ -5700,11 +5700,11 @@
         <v>226</v>
       </c>
       <c r="B70" s="5">
-        <v>46181.60920746528</v>
+        <v>46181.44254079861</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46182.635758460645</v>
+        <v>46182.46909179398</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>227</v>
@@ -5763,11 +5763,11 @@
         <v>229</v>
       </c>
       <c r="B71" s="8">
-        <v>46181.609212870375</v>
+        <v>46181.4425462037</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46182.63583289352</v>
+        <v>46182.46916622685</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>230</v>
@@ -5826,11 +5826,11 @@
         <v>232</v>
       </c>
       <c r="B72" s="5">
-        <v>46181.60921715278</v>
+        <v>46181.442550486114</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46182.63575501158</v>
+        <v>46182.46908834491</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>233</v>
@@ -5889,11 +5889,11 @@
         <v>235</v>
       </c>
       <c r="B73" s="8">
-        <v>46181.60922180556</v>
+        <v>46181.442555138885</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46182.63582844907</v>
+        <v>46182.46916178241</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>234</v>
@@ -5952,11 +5952,11 @@
         <v>236</v>
       </c>
       <c r="B74" s="5">
-        <v>46181.60922590278</v>
+        <v>46181.44255923611</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46181.782424143516</v>
+        <v>46181.61575747685</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>237</v>
@@ -5999,11 +5999,11 @@
         <v>239</v>
       </c>
       <c r="B75" s="8">
-        <v>46181.60922940972</v>
+        <v>46181.44256274306</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46182.63612115741</v>
+        <v>46182.46945449074</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>240</v>
@@ -6062,11 +6062,11 @@
         <v>245</v>
       </c>
       <c r="B76" s="5">
-        <v>46181.60923553241</v>
+        <v>46181.442568865736</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46182.63598688657</v>
+        <v>46182.46932021991</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>181</v>
@@ -6115,11 +6115,11 @@
         <v>248</v>
       </c>
       <c r="B77" s="8">
-        <v>46181.609241805556</v>
+        <v>46181.44257513889</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46182.63598342593</v>
+        <v>46182.46931675926</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>181</v>
@@ -6168,11 +6168,11 @@
         <v>250</v>
       </c>
       <c r="B78" s="5">
-        <v>46181.6145286574</v>
+        <v>46181.447861990746</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46182.63598072917</v>
+        <v>46182.4693140625</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>186</v>
@@ -6221,11 +6221,11 @@
         <v>251</v>
       </c>
       <c r="B79" s="8">
-        <v>46181.61460722222</v>
+        <v>46181.447940555554</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46182.63597787037</v>
+        <v>46182.469311203706</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>189</v>
@@ -6274,11 +6274,11 @@
         <v>253</v>
       </c>
       <c r="B80" s="5">
-        <v>46181.61464366898</v>
+        <v>46181.44797700232</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46182.635973807875</v>
+        <v>46182.469307141204</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>191</v>
@@ -6327,11 +6327,11 @@
         <v>254</v>
       </c>
       <c r="B81" s="8">
-        <v>46181.609247002314</v>
+        <v>46181.44258033565</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46182.64087873843</v>
+        <v>46182.47421207176</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>255</v>
@@ -6390,11 +6390,11 @@
         <v>257</v>
       </c>
       <c r="B82" s="5">
-        <v>46181.60925648148</v>
+        <v>46181.44258981482</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46191.54540523148</v>
+        <v>46191.37873856482</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>181</v>
@@ -6443,11 +6443,11 @@
         <v>260</v>
       </c>
       <c r="B83" s="8">
-        <v>46181.609262199076</v>
+        <v>46181.44259553241</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46191.54540574074</v>
+        <v>46191.378739074076</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>181</v>
@@ -6496,11 +6496,11 @@
         <v>261</v>
       </c>
       <c r="B84" s="5">
-        <v>46181.61473356481</v>
+        <v>46181.44806689815</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46182.64084413194</v>
+        <v>46182.47417746528</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>186</v>
@@ -6549,11 +6549,11 @@
         <v>263</v>
       </c>
       <c r="B85" s="8">
-        <v>46181.61477212963</v>
+        <v>46181.44810546296</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46182.64084086806</v>
+        <v>46182.47417420139</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>189</v>
@@ -6602,11 +6602,11 @@
         <v>265</v>
       </c>
       <c r="B86" s="5">
-        <v>46181.61484836806</v>
+        <v>46181.44818170139</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46182.6408357176</v>
+        <v>46182.474169050925</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>191</v>
@@ -6655,11 +6655,11 @@
         <v>267</v>
       </c>
       <c r="B87" s="8">
-        <v>46181.60926783565</v>
+        <v>46181.44260116898</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46182.64099746528</v>
+        <v>46182.47433079861</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>268</v>
@@ -6718,11 +6718,11 @@
         <v>269</v>
       </c>
       <c r="B88" s="5">
-        <v>46181.60927226851</v>
+        <v>46181.44260560186</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46191.545403842596</v>
+        <v>46191.378737175924</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>181</v>
@@ -6771,11 +6771,11 @@
         <v>271</v>
       </c>
       <c r="B89" s="8">
-        <v>46181.60927799769</v>
+        <v>46181.44261133102</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46191.545404212964</v>
+        <v>46191.3787375463</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>181</v>
@@ -6824,11 +6824,11 @@
         <v>273</v>
       </c>
       <c r="B90" s="5">
-        <v>46181.614954062505</v>
+        <v>46181.44828739583</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46182.64096971064</v>
+        <v>46182.474303043986</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>262</v>
@@ -6877,11 +6877,11 @@
         <v>274</v>
       </c>
       <c r="B91" s="8">
-        <v>46181.61498993056</v>
+        <v>46181.44832326389</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46182.64096709491</v>
+        <v>46182.474300428235</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>264</v>
@@ -6930,11 +6930,11 @@
         <v>275</v>
       </c>
       <c r="B92" s="5">
-        <v>46181.61502625</v>
+        <v>46181.44835958333</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46182.64096319444</v>
+        <v>46182.47429652778</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>266</v>
@@ -6983,11 +6983,11 @@
         <v>277</v>
       </c>
       <c r="B93" s="8">
-        <v>46181.60928361111</v>
+        <v>46181.44261694445</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46182.567648321754</v>
+        <v>46182.4009816551</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>215</v>
@@ -7030,11 +7030,11 @@
         <v>279</v>
       </c>
       <c r="B94" s="5">
-        <v>46181.609286990744</v>
+        <v>46181.44262032407</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46190.88639451389</v>
+        <v>46190.71972784722</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>280</v>
@@ -7093,11 +7093,11 @@
         <v>282</v>
       </c>
       <c r="B95" s="8">
-        <v>46181.609292974535</v>
+        <v>46181.44262630787</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46190.886394166664</v>
+        <v>46190.7197275</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>283</v>
@@ -7156,11 +7156,11 @@
         <v>284</v>
       </c>
       <c r="B96" s="5">
-        <v>46181.60929881944</v>
+        <v>46181.44263215278</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46190.886404791665</v>
+        <v>46190.719738125</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>285</v>
@@ -7219,11 +7219,11 @@
         <v>286</v>
       </c>
       <c r="B97" s="8">
-        <v>46181.60930480324</v>
+        <v>46181.44263813658</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46182.64108152778</v>
+        <v>46182.474414861106</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>287</v>
@@ -7282,11 +7282,11 @@
         <v>289</v>
       </c>
       <c r="B98" s="5">
-        <v>46181.60935271991</v>
+        <v>46181.44268605324</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46182.641076203705</v>
+        <v>46182.47440953704</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>60</v>
@@ -7345,11 +7345,11 @@
         <v>290</v>
       </c>
       <c r="B99" s="8">
-        <v>46181.60936674768</v>
+        <v>46181.44270008102</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46182.633312060185</v>
+        <v>46182.46664539352</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>291</v>
@@ -7392,11 +7392,11 @@
         <v>293</v>
       </c>
       <c r="B100" s="5">
-        <v>46181.609371666666</v>
+        <v>46181.442705</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46182.64123547454</v>
+        <v>46182.47456880787</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>294</v>
@@ -7455,11 +7455,11 @@
         <v>296</v>
       </c>
       <c r="B101" s="8">
-        <v>46181.609378587964</v>
+        <v>46181.44271192129</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46182.64119599537</v>
+        <v>46182.474529328705</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>181</v>
@@ -7508,11 +7508,11 @@
         <v>298</v>
       </c>
       <c r="B102" s="5">
-        <v>46181.61514019676</v>
+        <v>46181.448473530094</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46182.64119222222</v>
+        <v>46182.47452555556</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>181</v>
@@ -7561,11 +7561,11 @@
         <v>300</v>
       </c>
       <c r="B103" s="8">
-        <v>46181.609386111115</v>
+        <v>46181.44271944444</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46182.641349328704</v>
+        <v>46182.47468266204</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>301</v>
@@ -7624,11 +7624,11 @@
         <v>302</v>
       </c>
       <c r="B104" s="5">
-        <v>46181.60939194444</v>
+        <v>46181.44272527778</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46191.54539792824</v>
+        <v>46191.378731261575</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>181</v>
@@ -7677,11 +7677,11 @@
         <v>305</v>
       </c>
       <c r="B105" s="8">
-        <v>46181.61518315972</v>
+        <v>46181.44851649305</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46182.64130309028</v>
+        <v>46182.47463642361</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>181</v>
@@ -7730,11 +7730,11 @@
         <v>307</v>
       </c>
       <c r="B106" s="5">
-        <v>46181.60939866898</v>
+        <v>46181.44273200231</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46182.64144489584</v>
+        <v>46182.47477822917</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>308</v>
@@ -7793,11 +7793,11 @@
         <v>309</v>
       </c>
       <c r="B107" s="8">
-        <v>46181.60940505787</v>
+        <v>46181.442738391204</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46191.54540628473</v>
+        <v>46191.378739618056</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>181</v>
@@ -7846,11 +7846,11 @@
         <v>312</v>
       </c>
       <c r="B108" s="5">
-        <v>46181.61523613426</v>
+        <v>46181.4485694676</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46182.64140446759</v>
+        <v>46182.47473780093</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>181</v>
@@ -7899,11 +7899,11 @@
         <v>314</v>
       </c>
       <c r="B109" s="8">
-        <v>46181.60941365741</v>
+        <v>46181.44274699074</v>
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="8">
-        <v>46182.64155526621</v>
+        <v>46182.474888599536</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>315</v>
@@ -7962,11 +7962,11 @@
         <v>316</v>
       </c>
       <c r="B110" s="5">
-        <v>46181.60941929398</v>
+        <v>46181.442752627314</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46191.54540483796</v>
+        <v>46191.3787381713</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>181</v>
@@ -8015,11 +8015,11 @@
         <v>319</v>
       </c>
       <c r="B111" s="8">
-        <v>46181.61528053241</v>
+        <v>46181.44861386574</v>
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46182.64151664352</v>
+        <v>46182.47484997685</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>181</v>
@@ -8068,11 +8068,11 @@
         <v>321</v>
       </c>
       <c r="B112" s="5">
-        <v>46181.60942706019</v>
+        <v>46181.44276039352</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46182.64166112269</v>
+        <v>46182.47499445602</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>322</v>
@@ -8131,11 +8131,11 @@
         <v>323</v>
       </c>
       <c r="B113" s="8">
-        <v>46181.60943415509</v>
+        <v>46181.44276748842</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46182.641623125004</v>
+        <v>46182.47495645833</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>181</v>
@@ -8184,11 +8184,11 @@
         <v>325</v>
       </c>
       <c r="B114" s="5">
-        <v>46181.61532783565</v>
+        <v>46181.44866116898</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46182.64161924769</v>
+        <v>46182.47495258102</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>181</v>
@@ -8237,11 +8237,11 @@
         <v>326</v>
       </c>
       <c r="B115" s="8">
-        <v>46181.60944410879</v>
+        <v>46181.442777442135</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46182.82922638889</v>
+        <v>46182.66255972222</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>327</v>
@@ -8300,11 +8300,11 @@
         <v>329</v>
       </c>
       <c r="B116" s="5">
-        <v>46181.60944996528</v>
+        <v>46181.44278329861</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46182.64173178241</v>
+        <v>46182.47506511574</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>181</v>
@@ -8353,11 +8353,11 @@
         <v>331</v>
       </c>
       <c r="B117" s="8">
-        <v>46181.61537143518</v>
+        <v>46181.44870476852</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46182.64172883102</v>
+        <v>46182.47506216435</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>181</v>
@@ -8406,11 +8406,11 @@
         <v>332</v>
       </c>
       <c r="B118" s="5">
-        <v>46181.60945642361</v>
+        <v>46181.44278975694</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46182.634494212965</v>
+        <v>46182.467827546294</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>333</v>
@@ -8453,11 +8453,11 @@
         <v>335</v>
       </c>
       <c r="B119" s="8">
-        <v>46181.60946096065</v>
+        <v>46181.44279429398</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46182.64186350694</v>
+        <v>46182.47519684028</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>336</v>
@@ -8516,11 +8516,11 @@
         <v>340</v>
       </c>
       <c r="B120" s="5">
-        <v>46181.60946868056</v>
+        <v>46181.44280201389</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46182.641845254635</v>
+        <v>46182.47517858796</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>181</v>
@@ -8569,11 +8569,11 @@
         <v>342</v>
       </c>
       <c r="B121" s="8">
-        <v>46181.609475034726</v>
+        <v>46181.442808368054</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46182.64184081019</v>
+        <v>46182.47517414352</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>181</v>
@@ -8622,11 +8622,11 @@
         <v>343</v>
       </c>
       <c r="B122" s="5">
-        <v>46181.60947921296</v>
+        <v>46181.442812546295</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46182.641837766205</v>
+        <v>46182.47517109953</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>59</v>
@@ -8675,11 +8675,11 @@
         <v>344</v>
       </c>
       <c r="B123" s="8">
-        <v>46181.61605960648</v>
+        <v>46181.449392939816</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46182.641834548616</v>
+        <v>46182.475167881945</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>59</v>
@@ -8728,11 +8728,11 @@
         <v>345</v>
       </c>
       <c r="B124" s="5">
-        <v>46181.61617203704</v>
+        <v>46181.44950537037</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46182.64182482639</v>
+        <v>46182.47515815972</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>186</v>
@@ -8781,11 +8781,11 @@
         <v>346</v>
       </c>
       <c r="B125" s="8">
-        <v>46181.61620771991</v>
+        <v>46181.44954105324</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46182.64182413195</v>
+        <v>46182.47515746528</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>189</v>
@@ -8834,11 +8834,11 @@
         <v>347</v>
       </c>
       <c r="B126" s="5">
-        <v>46181.616245833335</v>
+        <v>46181.44957916667</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46182.641823425925</v>
+        <v>46182.47515675926</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>276</v>
@@ -8887,11 +8887,11 @@
         <v>348</v>
       </c>
       <c r="B127" s="8">
-        <v>46181.60948424769</v>
+        <v>46181.44281758102</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46182.64199267361</v>
+        <v>46182.47532600694</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>349</v>
@@ -8950,11 +8950,11 @@
         <v>350</v>
       </c>
       <c r="B128" s="5">
-        <v>46181.60948969907</v>
+        <v>46181.44282303241</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46182.641973854166</v>
+        <v>46182.4753071875</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>181</v>
@@ -9003,11 +9003,11 @@
         <v>352</v>
       </c>
       <c r="B129" s="8">
-        <v>46181.60949538194</v>
+        <v>46181.44282871528</v>
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46182.64197085648</v>
+        <v>46182.475304189815</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>181</v>
@@ -9056,11 +9056,11 @@
         <v>353</v>
       </c>
       <c r="B130" s="5">
-        <v>46181.609560185185</v>
+        <v>46181.44289351851</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46182.641967118056</v>
+        <v>46182.47530045139</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>59</v>
@@ -9109,11 +9109,11 @@
         <v>354</v>
       </c>
       <c r="B131" s="8">
-        <v>46181.61659114584</v>
+        <v>46181.449924479166</v>
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46182.64196408565</v>
+        <v>46182.47529741898</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>59</v>
@@ -9162,11 +9162,11 @@
         <v>355</v>
       </c>
       <c r="B132" s="5">
-        <v>46181.61662431713</v>
+        <v>46181.44995765046</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46182.64196105324</v>
+        <v>46182.475294386575</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>186</v>
@@ -9215,11 +9215,11 @@
         <v>356</v>
       </c>
       <c r="B133" s="8">
-        <v>46181.61666238426</v>
+        <v>46181.449995717594</v>
       </c>
       <c r="C133" s="9"/>
       <c r="D133" s="8">
-        <v>46182.64195453704</v>
+        <v>46182.47528787037</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>189</v>
@@ -9268,11 +9268,11 @@
         <v>357</v>
       </c>
       <c r="B134" s="5">
-        <v>46181.61670006944</v>
+        <v>46181.450033402776</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46182.64195372685</v>
+        <v>46182.47528706018</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>191</v>
@@ -9321,11 +9321,11 @@
         <v>358</v>
       </c>
       <c r="B135" s="8">
-        <v>46181.60956560185</v>
+        <v>46181.44289893519</v>
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="8">
-        <v>46182.82952324074</v>
+        <v>46182.662856574076</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>359</v>
@@ -9384,11 +9384,11 @@
         <v>360</v>
       </c>
       <c r="B136" s="5">
-        <v>46181.60957188657</v>
+        <v>46181.44290521991</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46182.82945300926</v>
+        <v>46182.6627863426</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>181</v>
@@ -9437,11 +9437,11 @@
         <v>362</v>
       </c>
       <c r="B137" s="8">
-        <v>46181.609583576384</v>
+        <v>46181.44291690973</v>
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46182.829453784725</v>
+        <v>46182.66278711805</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>181</v>
@@ -9490,11 +9490,11 @@
         <v>363</v>
       </c>
       <c r="B138" s="5">
-        <v>46181.60958841435</v>
+        <v>46181.442921747686</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46182.829454583334</v>
+        <v>46182.66278791666</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>59</v>
@@ -9543,11 +9543,11 @@
         <v>364</v>
       </c>
       <c r="B139" s="8">
-        <v>46181.616839849536</v>
+        <v>46181.45017318287</v>
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46182.829455706014</v>
+        <v>46182.66278903935</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>59</v>
@@ -9596,11 +9596,11 @@
         <v>365</v>
       </c>
       <c r="B140" s="5">
-        <v>46181.61689748843</v>
+        <v>46181.45023082176</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46182.8294564699</v>
+        <v>46182.662789803246</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>186</v>
@@ -9649,11 +9649,11 @@
         <v>366</v>
       </c>
       <c r="B141" s="8">
-        <v>46181.616942569446</v>
+        <v>46181.45027590278</v>
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46182.82945721065</v>
+        <v>46182.66279054398</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>189</v>
@@ -9702,11 +9702,11 @@
         <v>367</v>
       </c>
       <c r="B142" s="5">
-        <v>46181.6169815162</v>
+        <v>46181.45031484954</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46182.82945796296</v>
+        <v>46182.6627912963</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>191</v>
@@ -9755,11 +9755,11 @@
         <v>368</v>
       </c>
       <c r="B143" s="8">
-        <v>46181.609592673616</v>
+        <v>46181.442926006945</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46182.642407384265</v>
+        <v>46182.47574071759</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>369</v>
@@ -9818,11 +9818,11 @@
         <v>371</v>
       </c>
       <c r="B144" s="5">
-        <v>46181.60960517361</v>
+        <v>46181.442938506945</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46182.8294527199</v>
+        <v>46182.66278605324</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>181</v>
@@ -9871,11 +9871,11 @@
         <v>372</v>
       </c>
       <c r="B145" s="8">
-        <v>46181.609610011576</v>
+        <v>46181.44294334491</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46182.829451909725</v>
+        <v>46182.662785243054</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>181</v>
@@ -9924,11 +9924,11 @@
         <v>373</v>
       </c>
       <c r="B146" s="5">
-        <v>46181.609613796296</v>
+        <v>46181.44294712963</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46182.829452025464</v>
+        <v>46182.6627853588</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>59</v>
@@ -9977,11 +9977,11 @@
         <v>374</v>
       </c>
       <c r="B147" s="8">
-        <v>46181.61712142361</v>
+        <v>46181.450454756945</v>
       </c>
       <c r="C147" s="9"/>
       <c r="D147" s="8">
-        <v>46182.82945197917</v>
+        <v>46182.662785312496</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>59</v>
@@ -10030,11 +10030,11 @@
         <v>375</v>
       </c>
       <c r="B148" s="5">
-        <v>46181.61716094907</v>
+        <v>46181.450494282406</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46182.82945207176</v>
+        <v>46182.66278540509</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>186</v>
@@ -10083,11 +10083,11 @@
         <v>376</v>
       </c>
       <c r="B149" s="8">
-        <v>46181.61719633102</v>
+        <v>46181.45052966435</v>
       </c>
       <c r="C149" s="9"/>
       <c r="D149" s="8">
-        <v>46182.829452025464</v>
+        <v>46182.6627853588</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>189</v>
@@ -10136,11 +10136,11 @@
         <v>377</v>
       </c>
       <c r="B150" s="5">
-        <v>46181.617235451384</v>
+        <v>46181.45056878473</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46182.829452418984</v>
+        <v>46182.66278575231</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>191</v>
@@ -10189,11 +10189,11 @@
         <v>378</v>
       </c>
       <c r="B151" s="8">
-        <v>46181.60961741898</v>
+        <v>46181.44295075232</v>
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="8">
-        <v>46182.63449439815</v>
+        <v>46182.46782773148</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>379</v>
@@ -10236,11 +10236,11 @@
         <v>381</v>
       </c>
       <c r="B152" s="5">
-        <v>46181.60962174769</v>
+        <v>46181.44295508102</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46182.64244836806</v>
+        <v>46182.47578170139</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>382</v>
@@ -10299,11 +10299,11 @@
         <v>385</v>
       </c>
       <c r="B153" s="8">
-        <v>46181.60962780092</v>
+        <v>46181.442961134264</v>
       </c>
       <c r="C153" s="9"/>
       <c r="D153" s="8">
-        <v>46191.67892958333</v>
+        <v>46191.512262916665</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>386</v>
@@ -10362,11 +10362,11 @@
         <v>387</v>
       </c>
       <c r="B154" s="5">
-        <v>46181.60963489584</v>
+        <v>46181.44296822917</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46182.63449431713</v>
+        <v>46182.467827650464</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>388</v>
@@ -10415,11 +10415,11 @@
         <v>390</v>
       </c>
       <c r="B155" s="8">
-        <v>46181.609640208335</v>
+        <v>46181.44297354166</v>
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46182.64254377315</v>
+        <v>46182.47587710648</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>391</v>
@@ -10478,11 +10478,11 @@
         <v>393</v>
       </c>
       <c r="B156" s="5">
-        <v>46181.609646365745</v>
+        <v>46181.44297969907</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46182.64254079861</v>
+        <v>46182.475874131946</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>394</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -1864,13 +1864,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46181.44196283565</v>
+        <v>46181.60862950231</v>
       </c>
       <c r="C4" s="5">
-        <v>46190.5097949537</v>
+        <v>46190.67646162037</v>
       </c>
       <c r="D4" s="5">
-        <v>46191.6119315625</v>
+        <v>46191.77859822917</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1913,13 +1913,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46181.44214226852</v>
+        <v>46181.60880893518</v>
       </c>
       <c r="C5" s="8">
-        <v>46190.5091971875</v>
+        <v>46190.675863854165</v>
       </c>
       <c r="D5" s="8">
-        <v>46190.50966285879</v>
+        <v>46190.676329525464</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1976,13 +1976,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46181.44214673611</v>
+        <v>46181.60881340278</v>
       </c>
       <c r="C6" s="5">
-        <v>46190.50959462963</v>
+        <v>46190.67626129629</v>
       </c>
       <c r="D6" s="5">
-        <v>46190.50961417824</v>
+        <v>46190.676280844906</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2039,13 +2039,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="8">
-        <v>46181.442149814815</v>
+        <v>46181.60881648149</v>
       </c>
       <c r="C7" s="8">
-        <v>46190.50975353009</v>
+        <v>46190.67642019676</v>
       </c>
       <c r="D7" s="8">
-        <v>46190.509767511576</v>
+        <v>46190.67643417824</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>37</v>
@@ -2102,13 +2102,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46181.442153738426</v>
+        <v>46181.60882040509</v>
       </c>
       <c r="C8" s="5">
-        <v>46190.509779942135</v>
+        <v>46190.67644660879</v>
       </c>
       <c r="D8" s="5">
-        <v>46190.50979532408</v>
+        <v>46190.67646199074</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2165,11 +2165,11 @@
         <v>43</v>
       </c>
       <c r="B9" s="8">
-        <v>46181.44196856482</v>
+        <v>46181.60863523148</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="8">
-        <v>46190.51114369213</v>
+        <v>46190.6778103588</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>44</v>
@@ -2212,13 +2212,13 @@
         <v>46</v>
       </c>
       <c r="B10" s="5">
-        <v>46181.44215746528</v>
+        <v>46181.608824131945</v>
       </c>
       <c r="C10" s="5">
-        <v>46190.511137974536</v>
+        <v>46190.67780464121</v>
       </c>
       <c r="D10" s="5">
-        <v>46190.511153252315</v>
+        <v>46190.67781991899</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -2277,11 +2277,11 @@
         <v>51</v>
       </c>
       <c r="B11" s="8">
-        <v>46181.442162928244</v>
+        <v>46181.60882959491</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="8">
-        <v>46182.45913671296</v>
+        <v>46182.62580337963</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>52</v>
@@ -2340,11 +2340,11 @@
         <v>58</v>
       </c>
       <c r="B12" s="5">
-        <v>46181.44216831018</v>
+        <v>46181.608834976854</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46182.45922967592</v>
+        <v>46182.62589634259</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>59</v>
@@ -2393,11 +2393,11 @@
         <v>62</v>
       </c>
       <c r="B13" s="8">
-        <v>46181.45146517361</v>
+        <v>46181.61813184028</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46182.45922621527</v>
+        <v>46182.625892881944</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>59</v>
@@ -2446,11 +2446,11 @@
         <v>64</v>
       </c>
       <c r="B14" s="5">
-        <v>46181.44197355324</v>
+        <v>46181.60864021991</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46191.61198149306</v>
+        <v>46191.77864815972</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>65</v>
@@ -2493,13 +2493,13 @@
         <v>67</v>
       </c>
       <c r="B15" s="8">
-        <v>46181.44217197917</v>
+        <v>46181.60883864583</v>
       </c>
       <c r="C15" s="8">
-        <v>46190.510777372685</v>
+        <v>46190.67744403935</v>
       </c>
       <c r="D15" s="8">
-        <v>46191.512263275465</v>
+        <v>46191.67892994213</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>68</v>
@@ -2558,13 +2558,13 @@
         <v>71</v>
       </c>
       <c r="B16" s="5">
-        <v>46181.44217729167</v>
+        <v>46181.60884395833</v>
       </c>
       <c r="C16" s="5">
-        <v>46190.510785335646</v>
+        <v>46190.67745200232</v>
       </c>
       <c r="D16" s="5">
-        <v>46191.512263136574</v>
+        <v>46191.67892980324</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>72</v>
@@ -2623,13 +2623,13 @@
         <v>75</v>
       </c>
       <c r="B17" s="8">
-        <v>46181.44218337963</v>
+        <v>46181.608850046294</v>
       </c>
       <c r="C17" s="8">
-        <v>46190.510792037036</v>
+        <v>46190.67745870371</v>
       </c>
       <c r="D17" s="8">
-        <v>46191.512263136574</v>
+        <v>46191.67892980324</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>76</v>
@@ -2688,11 +2688,11 @@
         <v>78</v>
       </c>
       <c r="B18" s="5">
-        <v>46181.441980034724</v>
+        <v>46181.60864670139</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46197.256161006946</v>
+        <v>46197.42282767361</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>79</v>
@@ -2737,13 +2737,13 @@
         <v>82</v>
       </c>
       <c r="B19" s="8">
-        <v>46181.44219756944</v>
+        <v>46181.608864236114</v>
       </c>
       <c r="C19" s="8">
-        <v>46190.511006319444</v>
+        <v>46190.677672986116</v>
       </c>
       <c r="D19" s="8">
-        <v>46190.71972758102</v>
+        <v>46190.88639424769</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>83</v>
@@ -2802,13 +2802,13 @@
         <v>85</v>
       </c>
       <c r="B20" s="5">
-        <v>46181.442203125</v>
+        <v>46181.60886979167</v>
       </c>
       <c r="C20" s="5">
-        <v>46190.51101199074</v>
+        <v>46190.677678657405</v>
       </c>
       <c r="D20" s="5">
-        <v>46190.71971788195</v>
+        <v>46190.88638454861</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>86</v>
@@ -2867,13 +2867,13 @@
         <v>88</v>
       </c>
       <c r="B21" s="8">
-        <v>46181.442208541666</v>
+        <v>46181.60887520833</v>
       </c>
       <c r="C21" s="8">
-        <v>46197.256142349535</v>
+        <v>46197.42280901621</v>
       </c>
       <c r="D21" s="8">
-        <v>46197.25614478009</v>
+        <v>46197.422811446755</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>89</v>
@@ -2932,13 +2932,13 @@
         <v>92</v>
       </c>
       <c r="B22" s="5">
-        <v>46181.442213877315</v>
+        <v>46181.60888054398</v>
       </c>
       <c r="C22" s="5">
-        <v>46196.491901875</v>
+        <v>46196.658568541665</v>
       </c>
       <c r="D22" s="5">
-        <v>46196.4919162963</v>
+        <v>46196.65858296296</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>93</v>
@@ -2997,13 +2997,13 @@
         <v>98</v>
       </c>
       <c r="B23" s="8">
-        <v>46181.44221892361</v>
+        <v>46181.60888559028</v>
       </c>
       <c r="C23" s="8">
-        <v>46196.49216407408</v>
+        <v>46196.65883074074</v>
       </c>
       <c r="D23" s="8">
-        <v>46196.49217895833</v>
+        <v>46196.658845625</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>99</v>
@@ -3062,11 +3062,11 @@
         <v>101</v>
       </c>
       <c r="B24" s="5">
-        <v>46181.44222295139</v>
+        <v>46181.60888961806</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46191.507004872685</v>
+        <v>46191.67367153935</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>102</v>
@@ -3125,13 +3125,13 @@
         <v>104</v>
       </c>
       <c r="B25" s="8">
-        <v>46181.44222677083</v>
+        <v>46181.6088934375</v>
       </c>
       <c r="C25" s="8">
-        <v>46197.478443831016</v>
+        <v>46197.64511049769</v>
       </c>
       <c r="D25" s="8">
-        <v>46197.47845997685</v>
+        <v>46197.64512664352</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>105</v>
@@ -3190,13 +3190,13 @@
         <v>107</v>
       </c>
       <c r="B26" s="5">
-        <v>46181.44223097222</v>
+        <v>46181.608897638886</v>
       </c>
       <c r="C26" s="5">
-        <v>46190.51118564815</v>
+        <v>46190.67785231481</v>
       </c>
       <c r="D26" s="5">
-        <v>46190.511203946764</v>
+        <v>46190.67787061342</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>108</v>
@@ -3255,13 +3255,13 @@
         <v>110</v>
       </c>
       <c r="B27" s="8">
-        <v>46190.71537822917</v>
+        <v>46190.88204489583</v>
       </c>
       <c r="C27" s="8">
-        <v>46197.257409756945</v>
+        <v>46197.42407642362</v>
       </c>
       <c r="D27" s="8">
-        <v>46197.25742238426</v>
+        <v>46197.424089050925</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>111</v>
@@ -3308,13 +3308,13 @@
         <v>112</v>
       </c>
       <c r="B28" s="5">
-        <v>46190.71655243056</v>
+        <v>46190.88321909722</v>
       </c>
       <c r="C28" s="5">
-        <v>46197.25687615741</v>
+        <v>46197.42354282408</v>
       </c>
       <c r="D28" s="5">
-        <v>46197.25689261574</v>
+        <v>46197.42355928241</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>113</v>
@@ -3373,13 +3373,13 @@
         <v>114</v>
       </c>
       <c r="B29" s="8">
-        <v>46190.71660518518</v>
+        <v>46190.88327185185</v>
       </c>
       <c r="C29" s="8">
-        <v>46197.25729826389</v>
+        <v>46197.42396493055</v>
       </c>
       <c r="D29" s="8">
-        <v>46197.25731493055</v>
+        <v>46197.423981597225</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>115</v>
@@ -3438,13 +3438,13 @@
         <v>116</v>
       </c>
       <c r="B30" s="5">
-        <v>46190.71665993056</v>
+        <v>46190.88332659722</v>
       </c>
       <c r="C30" s="5">
-        <v>46197.25739456018</v>
+        <v>46197.42406122685</v>
       </c>
       <c r="D30" s="5">
-        <v>46197.25740981482</v>
+        <v>46197.42407648148</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>117</v>
@@ -3503,11 +3503,11 @@
         <v>118</v>
       </c>
       <c r="B31" s="8">
-        <v>46181.44198559028</v>
+        <v>46181.608652256946</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46190.7197083912</v>
+        <v>46190.886375057875</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>119</v>
@@ -3550,11 +3550,11 @@
         <v>121</v>
       </c>
       <c r="B32" s="5">
-        <v>46181.44234127315</v>
+        <v>46181.60900793981</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46195.51926431713</v>
+        <v>46195.6859309838</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>122</v>
@@ -3613,13 +3613,13 @@
         <v>126</v>
       </c>
       <c r="B33" s="8">
-        <v>46181.44234498843</v>
+        <v>46181.60901165509</v>
       </c>
       <c r="C33" s="8">
-        <v>46195.51925878473</v>
+        <v>46195.685925451384</v>
       </c>
       <c r="D33" s="8">
-        <v>46195.519260810186</v>
+        <v>46195.68592747685</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>109</v>
@@ -3668,11 +3668,11 @@
         <v>128</v>
       </c>
       <c r="B34" s="5">
-        <v>46181.44234945602</v>
+        <v>46181.60901612269</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46195.51926576388</v>
+        <v>46195.685932430555</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>129</v>
@@ -3721,11 +3721,11 @@
         <v>131</v>
       </c>
       <c r="B35" s="8">
-        <v>46181.44235344908</v>
+        <v>46181.60902011574</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46182.46012931713</v>
+        <v>46182.6267959838</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>120</v>
@@ -3784,11 +3784,11 @@
         <v>135</v>
       </c>
       <c r="B36" s="5">
-        <v>46181.442358217595</v>
+        <v>46181.60902488426</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46196.491907731484</v>
+        <v>46196.65857439815</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
@@ -3843,11 +3843,11 @@
         <v>138</v>
       </c>
       <c r="B37" s="8">
-        <v>46181.44236313658</v>
+        <v>46181.609029803236</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="8">
-        <v>46182.460097442134</v>
+        <v>46182.6267641088</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>139</v>
@@ -3902,11 +3902,11 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46181.442368449076</v>
+        <v>46181.60903511574</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46182.46024017361</v>
+        <v>46182.626906840276</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -3965,11 +3965,11 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46181.442371944446</v>
+        <v>46181.60903861111</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46196.49217065972</v>
+        <v>46196.65883732639</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>100</v>
@@ -4018,11 +4018,11 @@
         <v>146</v>
       </c>
       <c r="B40" s="5">
-        <v>46181.44237628472</v>
+        <v>46181.609042951386</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46182.460202013885</v>
+        <v>46182.626868680556</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>147</v>
@@ -4071,11 +4071,11 @@
         <v>149</v>
       </c>
       <c r="B41" s="8">
-        <v>46181.44238049768</v>
+        <v>46181.609047164355</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="8">
-        <v>46183.534955324074</v>
+        <v>46183.70162199074</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>150</v>
@@ -4134,11 +4134,11 @@
         <v>154</v>
       </c>
       <c r="B42" s="5">
-        <v>46181.44238408565</v>
+        <v>46181.60905075232</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46197.47845083333</v>
+        <v>46197.6451175</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>106</v>
@@ -4187,11 +4187,11 @@
         <v>156</v>
       </c>
       <c r="B43" s="8">
-        <v>46181.44238879629</v>
+        <v>46181.60905546296</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="8">
-        <v>46183.53881104167</v>
+        <v>46183.70547770833</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>157</v>
@@ -4240,11 +4240,11 @@
         <v>159</v>
       </c>
       <c r="B44" s="5">
-        <v>46181.44239351852</v>
+        <v>46181.60906018519</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46182.460407569444</v>
+        <v>46182.62707423611</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>160</v>
@@ -4293,11 +4293,11 @@
         <v>163</v>
       </c>
       <c r="B45" s="8">
-        <v>46181.44239664351</v>
+        <v>46181.609063310185</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46182.46059180556</v>
+        <v>46182.62725847222</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>164</v>
@@ -4356,11 +4356,11 @@
         <v>166</v>
       </c>
       <c r="B46" s="5">
-        <v>46181.442400370375</v>
+        <v>46181.60906703703</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46182.46053788194</v>
+        <v>46182.62720454861</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>103</v>
@@ -4409,11 +4409,11 @@
         <v>168</v>
       </c>
       <c r="B47" s="8">
-        <v>46181.44241015046</v>
+        <v>46181.60907681713</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46182.46053462963</v>
+        <v>46182.627201296295</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>169</v>
@@ -4462,11 +4462,11 @@
         <v>171</v>
       </c>
       <c r="B48" s="5">
-        <v>46181.442414895835</v>
+        <v>46181.6090815625</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46191.37608472222</v>
+        <v>46191.542751388886</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>172</v>
@@ -4511,13 +4511,13 @@
         <v>174</v>
       </c>
       <c r="B49" s="8">
-        <v>46181.442418136576</v>
+        <v>46181.60908480324</v>
       </c>
       <c r="C49" s="8">
-        <v>46190.54157908565</v>
+        <v>46190.708245752314</v>
       </c>
       <c r="D49" s="8">
-        <v>46197.549148425926</v>
+        <v>46197.7158150926</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>175</v>
@@ -4576,13 +4576,13 @@
         <v>180</v>
       </c>
       <c r="B50" s="5">
-        <v>46181.44242248843</v>
+        <v>46181.60908915509</v>
       </c>
       <c r="C50" s="5">
-        <v>46190.54154569445</v>
+        <v>46190.70821236111</v>
       </c>
       <c r="D50" s="5">
-        <v>46190.54154723379</v>
+        <v>46190.70821390046</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>181</v>
@@ -4631,13 +4631,13 @@
         <v>185</v>
       </c>
       <c r="B51" s="8">
-        <v>46181.44242717593</v>
+        <v>46181.60909384259</v>
       </c>
       <c r="C51" s="8">
-        <v>46190.54155472222</v>
+        <v>46190.70822138889</v>
       </c>
       <c r="D51" s="8">
-        <v>46190.541556145836</v>
+        <v>46190.7082228125</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>186</v>
@@ -4686,13 +4686,13 @@
         <v>188</v>
       </c>
       <c r="B52" s="5">
-        <v>46181.445550752316</v>
+        <v>46181.61221741898</v>
       </c>
       <c r="C52" s="5">
-        <v>46190.541559351856</v>
+        <v>46190.70822601852</v>
       </c>
       <c r="D52" s="5">
-        <v>46190.54156067129</v>
+        <v>46190.708227337964</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>189</v>
@@ -4741,13 +4741,13 @@
         <v>190</v>
       </c>
       <c r="B53" s="8">
-        <v>46181.445690532404</v>
+        <v>46181.612357199076</v>
       </c>
       <c r="C53" s="8">
-        <v>46190.541565011576</v>
+        <v>46190.70823167824</v>
       </c>
       <c r="D53" s="8">
-        <v>46190.5415666551</v>
+        <v>46190.708233321755</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>191</v>
@@ -4796,13 +4796,13 @@
         <v>192</v>
       </c>
       <c r="B54" s="5">
-        <v>46181.4424315162</v>
+        <v>46181.609098182875</v>
       </c>
       <c r="C54" s="5">
-        <v>46191.376063159725</v>
+        <v>46191.54272982639</v>
       </c>
       <c r="D54" s="5">
-        <v>46197.54918153935</v>
+        <v>46197.71584820602</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>193</v>
@@ -4861,13 +4861,13 @@
         <v>194</v>
       </c>
       <c r="B55" s="8">
-        <v>46181.44243585649</v>
+        <v>46181.60910252314</v>
       </c>
       <c r="C55" s="8">
-        <v>46191.376039814815</v>
+        <v>46191.54270648149</v>
       </c>
       <c r="D55" s="8">
-        <v>46191.37604152778</v>
+        <v>46191.54270819444</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>181</v>
@@ -4916,13 +4916,13 @@
         <v>196</v>
       </c>
       <c r="B56" s="5">
-        <v>46181.44244128472</v>
+        <v>46181.609107951386</v>
       </c>
       <c r="C56" s="5">
-        <v>46191.37604895834</v>
+        <v>46191.542715625</v>
       </c>
       <c r="D56" s="5">
-        <v>46191.37605037037</v>
+        <v>46191.54271703704</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>186</v>
@@ -4971,13 +4971,13 @@
         <v>198</v>
       </c>
       <c r="B57" s="8">
-        <v>46181.44726903935</v>
+        <v>46181.61393570602</v>
       </c>
       <c r="C57" s="8">
-        <v>46190.54175359954</v>
+        <v>46190.70842026621</v>
       </c>
       <c r="D57" s="8">
-        <v>46190.54175503472</v>
+        <v>46190.70842170139</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>189</v>
@@ -5026,13 +5026,13 @@
         <v>199</v>
       </c>
       <c r="B58" s="5">
-        <v>46181.44730262732</v>
+        <v>46181.61396929398</v>
       </c>
       <c r="C58" s="5">
-        <v>46190.541758541665</v>
+        <v>46190.70842520833</v>
       </c>
       <c r="D58" s="5">
-        <v>46190.54175988426</v>
+        <v>46190.708426550926</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>191</v>
@@ -5081,13 +5081,13 @@
         <v>200</v>
       </c>
       <c r="B59" s="8">
-        <v>46181.44244663195</v>
+        <v>46181.60911329861</v>
       </c>
       <c r="C59" s="8">
-        <v>46191.378720266206</v>
+        <v>46191.54538693287</v>
       </c>
       <c r="D59" s="8">
-        <v>46191.37873159722</v>
+        <v>46191.54539826389</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>96</v>
@@ -5146,13 +5146,13 @@
         <v>202</v>
       </c>
       <c r="B60" s="5">
-        <v>46181.442456840276</v>
+        <v>46181.60912350695</v>
       </c>
       <c r="C60" s="5">
-        <v>46191.378692349535</v>
+        <v>46191.54535901621</v>
       </c>
       <c r="D60" s="5">
-        <v>46191.37869384259</v>
+        <v>46191.54536050926</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>181</v>
@@ -5199,13 +5199,13 @@
         <v>203</v>
       </c>
       <c r="B61" s="8">
-        <v>46181.44246115741</v>
+        <v>46181.60912782408</v>
       </c>
       <c r="C61" s="8">
-        <v>46191.378705752315</v>
+        <v>46191.54537241899</v>
       </c>
       <c r="D61" s="8">
-        <v>46191.378707199074</v>
+        <v>46191.54537386574</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>186</v>
@@ -5252,13 +5252,13 @@
         <v>204</v>
       </c>
       <c r="B62" s="5">
-        <v>46181.447452939814</v>
+        <v>46181.614119606485</v>
       </c>
       <c r="C62" s="5">
-        <v>46190.555057164354</v>
+        <v>46190.72172383102</v>
       </c>
       <c r="D62" s="5">
-        <v>46190.55505869213</v>
+        <v>46190.721725358795</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>189</v>
@@ -5305,13 +5305,13 @@
         <v>205</v>
       </c>
       <c r="B63" s="8">
-        <v>46181.44752960648</v>
+        <v>46181.61419627315</v>
       </c>
       <c r="C63" s="8">
-        <v>46190.55506201389</v>
+        <v>46190.72172868055</v>
       </c>
       <c r="D63" s="8">
-        <v>46190.555063287036</v>
+        <v>46190.7217299537</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>191</v>
@@ -5358,11 +5358,11 @@
         <v>206</v>
       </c>
       <c r="B64" s="5">
-        <v>46181.442465405096</v>
+        <v>46181.60913207176</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46182.46645140046</v>
+        <v>46182.633118067126</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>207</v>
@@ -5421,11 +5421,11 @@
         <v>210</v>
       </c>
       <c r="B65" s="8">
-        <v>46181.442469166665</v>
+        <v>46181.609135833336</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46182.46645180555</v>
+        <v>46182.63311847222</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>181</v>
@@ -5474,11 +5474,11 @@
         <v>212</v>
       </c>
       <c r="B66" s="5">
-        <v>46181.44764524305</v>
+        <v>46181.614311909725</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46182.466452569446</v>
+        <v>46182.63311923611</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>213</v>
@@ -5527,11 +5527,11 @@
         <v>214</v>
       </c>
       <c r="B67" s="8">
-        <v>46181.4425200463</v>
+        <v>46181.60918671296</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46181.613168703705</v>
+        <v>46181.77983537037</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>215</v>
@@ -5574,11 +5574,11 @@
         <v>217</v>
       </c>
       <c r="B68" s="5">
-        <v>46181.4425294213</v>
+        <v>46181.609196087964</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46182.46909479167</v>
+        <v>46182.63576145833</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>218</v>
@@ -5637,11 +5637,11 @@
         <v>222</v>
       </c>
       <c r="B69" s="8">
-        <v>46181.44253525463</v>
+        <v>46181.609201921296</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46182.46916971065</v>
+        <v>46182.63583637732</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>223</v>
@@ -5700,11 +5700,11 @@
         <v>226</v>
       </c>
       <c r="B70" s="5">
-        <v>46181.44254079861</v>
+        <v>46181.60920746528</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46182.46909179398</v>
+        <v>46182.635758460645</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>227</v>
@@ -5763,11 +5763,11 @@
         <v>229</v>
       </c>
       <c r="B71" s="8">
-        <v>46181.4425462037</v>
+        <v>46181.609212870375</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46182.46916622685</v>
+        <v>46182.63583289352</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>230</v>
@@ -5826,11 +5826,11 @@
         <v>232</v>
       </c>
       <c r="B72" s="5">
-        <v>46181.442550486114</v>
+        <v>46181.60921715278</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46182.46908834491</v>
+        <v>46182.63575501158</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>233</v>
@@ -5889,11 +5889,11 @@
         <v>235</v>
       </c>
       <c r="B73" s="8">
-        <v>46181.442555138885</v>
+        <v>46181.60922180556</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46182.46916178241</v>
+        <v>46182.63582844907</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>234</v>
@@ -5952,11 +5952,11 @@
         <v>236</v>
       </c>
       <c r="B74" s="5">
-        <v>46181.44255923611</v>
+        <v>46181.60922590278</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46181.61575747685</v>
+        <v>46181.782424143516</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>237</v>
@@ -5999,11 +5999,11 @@
         <v>239</v>
       </c>
       <c r="B75" s="8">
-        <v>46181.44256274306</v>
+        <v>46181.60922940972</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46182.46945449074</v>
+        <v>46182.63612115741</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>240</v>
@@ -6062,11 +6062,11 @@
         <v>245</v>
       </c>
       <c r="B76" s="5">
-        <v>46181.442568865736</v>
+        <v>46181.60923553241</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46182.46932021991</v>
+        <v>46182.63598688657</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>181</v>
@@ -6115,11 +6115,11 @@
         <v>248</v>
       </c>
       <c r="B77" s="8">
-        <v>46181.44257513889</v>
+        <v>46181.609241805556</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46182.46931675926</v>
+        <v>46182.63598342593</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>181</v>
@@ -6168,11 +6168,11 @@
         <v>250</v>
       </c>
       <c r="B78" s="5">
-        <v>46181.447861990746</v>
+        <v>46181.6145286574</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46182.4693140625</v>
+        <v>46182.63598072917</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>186</v>
@@ -6221,11 +6221,11 @@
         <v>251</v>
       </c>
       <c r="B79" s="8">
-        <v>46181.447940555554</v>
+        <v>46181.61460722222</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46182.469311203706</v>
+        <v>46182.63597787037</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>189</v>
@@ -6274,11 +6274,11 @@
         <v>253</v>
       </c>
       <c r="B80" s="5">
-        <v>46181.44797700232</v>
+        <v>46181.61464366898</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46182.469307141204</v>
+        <v>46182.635973807875</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>191</v>
@@ -6327,11 +6327,11 @@
         <v>254</v>
       </c>
       <c r="B81" s="8">
-        <v>46181.44258033565</v>
+        <v>46181.609247002314</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46182.47421207176</v>
+        <v>46182.64087873843</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>255</v>
@@ -6390,11 +6390,11 @@
         <v>257</v>
       </c>
       <c r="B82" s="5">
-        <v>46181.44258981482</v>
+        <v>46181.60925648148</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46191.37873856482</v>
+        <v>46191.54540523148</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>181</v>
@@ -6443,11 +6443,11 @@
         <v>260</v>
       </c>
       <c r="B83" s="8">
-        <v>46181.44259553241</v>
+        <v>46181.609262199076</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46191.378739074076</v>
+        <v>46191.54540574074</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>181</v>
@@ -6496,11 +6496,11 @@
         <v>261</v>
       </c>
       <c r="B84" s="5">
-        <v>46181.44806689815</v>
+        <v>46181.61473356481</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46182.47417746528</v>
+        <v>46182.64084413194</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>186</v>
@@ -6549,11 +6549,11 @@
         <v>263</v>
       </c>
       <c r="B85" s="8">
-        <v>46181.44810546296</v>
+        <v>46181.61477212963</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46182.47417420139</v>
+        <v>46182.64084086806</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>189</v>
@@ -6602,11 +6602,11 @@
         <v>265</v>
       </c>
       <c r="B86" s="5">
-        <v>46181.44818170139</v>
+        <v>46181.61484836806</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46182.474169050925</v>
+        <v>46182.6408357176</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>191</v>
@@ -6655,11 +6655,11 @@
         <v>267</v>
       </c>
       <c r="B87" s="8">
-        <v>46181.44260116898</v>
+        <v>46181.60926783565</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46182.47433079861</v>
+        <v>46182.64099746528</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>268</v>
@@ -6718,11 +6718,11 @@
         <v>269</v>
       </c>
       <c r="B88" s="5">
-        <v>46181.44260560186</v>
+        <v>46181.60927226851</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46191.378737175924</v>
+        <v>46191.545403842596</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>181</v>
@@ -6771,11 +6771,11 @@
         <v>271</v>
       </c>
       <c r="B89" s="8">
-        <v>46181.44261133102</v>
+        <v>46181.60927799769</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46191.3787375463</v>
+        <v>46191.545404212964</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>181</v>
@@ -6824,11 +6824,11 @@
         <v>273</v>
       </c>
       <c r="B90" s="5">
-        <v>46181.44828739583</v>
+        <v>46181.614954062505</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46182.474303043986</v>
+        <v>46182.64096971064</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>262</v>
@@ -6877,11 +6877,11 @@
         <v>274</v>
       </c>
       <c r="B91" s="8">
-        <v>46181.44832326389</v>
+        <v>46181.61498993056</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46182.474300428235</v>
+        <v>46182.64096709491</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>264</v>
@@ -6930,11 +6930,11 @@
         <v>275</v>
       </c>
       <c r="B92" s="5">
-        <v>46181.44835958333</v>
+        <v>46181.61502625</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46182.47429652778</v>
+        <v>46182.64096319444</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>266</v>
@@ -6983,11 +6983,11 @@
         <v>277</v>
       </c>
       <c r="B93" s="8">
-        <v>46181.44261694445</v>
+        <v>46181.60928361111</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46182.4009816551</v>
+        <v>46182.567648321754</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>215</v>
@@ -7030,11 +7030,11 @@
         <v>279</v>
       </c>
       <c r="B94" s="5">
-        <v>46181.44262032407</v>
+        <v>46181.609286990744</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46190.71972784722</v>
+        <v>46190.88639451389</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>280</v>
@@ -7093,11 +7093,11 @@
         <v>282</v>
       </c>
       <c r="B95" s="8">
-        <v>46181.44262630787</v>
+        <v>46181.609292974535</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46190.7197275</v>
+        <v>46190.886394166664</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>283</v>
@@ -7156,11 +7156,11 @@
         <v>284</v>
       </c>
       <c r="B96" s="5">
-        <v>46181.44263215278</v>
+        <v>46181.60929881944</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46190.719738125</v>
+        <v>46190.886404791665</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>285</v>
@@ -7219,11 +7219,11 @@
         <v>286</v>
       </c>
       <c r="B97" s="8">
-        <v>46181.44263813658</v>
+        <v>46181.60930480324</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46182.474414861106</v>
+        <v>46182.64108152778</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>287</v>
@@ -7282,11 +7282,11 @@
         <v>289</v>
       </c>
       <c r="B98" s="5">
-        <v>46181.44268605324</v>
+        <v>46181.60935271991</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46182.47440953704</v>
+        <v>46182.641076203705</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>60</v>
@@ -7345,11 +7345,11 @@
         <v>290</v>
       </c>
       <c r="B99" s="8">
-        <v>46181.44270008102</v>
+        <v>46181.60936674768</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46182.46664539352</v>
+        <v>46182.633312060185</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>291</v>
@@ -7392,11 +7392,11 @@
         <v>293</v>
       </c>
       <c r="B100" s="5">
-        <v>46181.442705</v>
+        <v>46181.609371666666</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46182.47456880787</v>
+        <v>46182.64123547454</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>294</v>
@@ -7455,11 +7455,11 @@
         <v>296</v>
       </c>
       <c r="B101" s="8">
-        <v>46181.44271192129</v>
+        <v>46181.609378587964</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46182.474529328705</v>
+        <v>46182.64119599537</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>181</v>
@@ -7508,11 +7508,11 @@
         <v>298</v>
       </c>
       <c r="B102" s="5">
-        <v>46181.448473530094</v>
+        <v>46181.61514019676</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46182.47452555556</v>
+        <v>46182.64119222222</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>181</v>
@@ -7561,11 +7561,11 @@
         <v>300</v>
       </c>
       <c r="B103" s="8">
-        <v>46181.44271944444</v>
+        <v>46181.609386111115</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46182.47468266204</v>
+        <v>46182.641349328704</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>301</v>
@@ -7624,11 +7624,11 @@
         <v>302</v>
       </c>
       <c r="B104" s="5">
-        <v>46181.44272527778</v>
+        <v>46181.60939194444</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46191.378731261575</v>
+        <v>46191.54539792824</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>181</v>
@@ -7677,11 +7677,11 @@
         <v>305</v>
       </c>
       <c r="B105" s="8">
-        <v>46181.44851649305</v>
+        <v>46181.61518315972</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46182.47463642361</v>
+        <v>46182.64130309028</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>181</v>
@@ -7730,11 +7730,11 @@
         <v>307</v>
       </c>
       <c r="B106" s="5">
-        <v>46181.44273200231</v>
+        <v>46181.60939866898</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46182.47477822917</v>
+        <v>46182.64144489584</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>308</v>
@@ -7793,11 +7793,11 @@
         <v>309</v>
       </c>
       <c r="B107" s="8">
-        <v>46181.442738391204</v>
+        <v>46181.60940505787</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46191.378739618056</v>
+        <v>46191.54540628473</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>181</v>
@@ -7846,11 +7846,11 @@
         <v>312</v>
       </c>
       <c r="B108" s="5">
-        <v>46181.4485694676</v>
+        <v>46181.61523613426</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46182.47473780093</v>
+        <v>46182.64140446759</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>181</v>
@@ -7899,11 +7899,11 @@
         <v>314</v>
       </c>
       <c r="B109" s="8">
-        <v>46181.44274699074</v>
+        <v>46181.60941365741</v>
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="8">
-        <v>46182.474888599536</v>
+        <v>46182.64155526621</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>315</v>
@@ -7962,11 +7962,11 @@
         <v>316</v>
       </c>
       <c r="B110" s="5">
-        <v>46181.442752627314</v>
+        <v>46181.60941929398</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46191.3787381713</v>
+        <v>46191.54540483796</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>181</v>
@@ -8015,11 +8015,11 @@
         <v>319</v>
       </c>
       <c r="B111" s="8">
-        <v>46181.44861386574</v>
+        <v>46181.61528053241</v>
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46182.47484997685</v>
+        <v>46182.64151664352</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>181</v>
@@ -8068,11 +8068,11 @@
         <v>321</v>
       </c>
       <c r="B112" s="5">
-        <v>46181.44276039352</v>
+        <v>46181.60942706019</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46182.47499445602</v>
+        <v>46182.64166112269</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>322</v>
@@ -8131,11 +8131,11 @@
         <v>323</v>
       </c>
       <c r="B113" s="8">
-        <v>46181.44276748842</v>
+        <v>46181.60943415509</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46182.47495645833</v>
+        <v>46182.641623125004</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>181</v>
@@ -8184,11 +8184,11 @@
         <v>325</v>
       </c>
       <c r="B114" s="5">
-        <v>46181.44866116898</v>
+        <v>46181.61532783565</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46182.47495258102</v>
+        <v>46182.64161924769</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>181</v>
@@ -8237,11 +8237,11 @@
         <v>326</v>
       </c>
       <c r="B115" s="8">
-        <v>46181.442777442135</v>
+        <v>46181.60944410879</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46182.66255972222</v>
+        <v>46182.82922638889</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>327</v>
@@ -8300,11 +8300,11 @@
         <v>329</v>
       </c>
       <c r="B116" s="5">
-        <v>46181.44278329861</v>
+        <v>46181.60944996528</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46182.47506511574</v>
+        <v>46182.64173178241</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>181</v>
@@ -8353,11 +8353,11 @@
         <v>331</v>
       </c>
       <c r="B117" s="8">
-        <v>46181.44870476852</v>
+        <v>46181.61537143518</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46182.47506216435</v>
+        <v>46182.64172883102</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>181</v>
@@ -8406,11 +8406,11 @@
         <v>332</v>
       </c>
       <c r="B118" s="5">
-        <v>46181.44278975694</v>
+        <v>46181.60945642361</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46182.467827546294</v>
+        <v>46182.634494212965</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>333</v>
@@ -8453,11 +8453,11 @@
         <v>335</v>
       </c>
       <c r="B119" s="8">
-        <v>46181.44279429398</v>
+        <v>46181.60946096065</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46182.47519684028</v>
+        <v>46182.64186350694</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>336</v>
@@ -8516,11 +8516,11 @@
         <v>340</v>
       </c>
       <c r="B120" s="5">
-        <v>46181.44280201389</v>
+        <v>46181.60946868056</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46182.47517858796</v>
+        <v>46182.641845254635</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>181</v>
@@ -8569,11 +8569,11 @@
         <v>342</v>
       </c>
       <c r="B121" s="8">
-        <v>46181.442808368054</v>
+        <v>46181.609475034726</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46182.47517414352</v>
+        <v>46182.64184081019</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>181</v>
@@ -8622,11 +8622,11 @@
         <v>343</v>
       </c>
       <c r="B122" s="5">
-        <v>46181.442812546295</v>
+        <v>46181.60947921296</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46182.47517109953</v>
+        <v>46182.641837766205</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>59</v>
@@ -8675,11 +8675,11 @@
         <v>344</v>
       </c>
       <c r="B123" s="8">
-        <v>46181.449392939816</v>
+        <v>46181.61605960648</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46182.475167881945</v>
+        <v>46182.641834548616</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>59</v>
@@ -8728,11 +8728,11 @@
         <v>345</v>
       </c>
       <c r="B124" s="5">
-        <v>46181.44950537037</v>
+        <v>46181.61617203704</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46182.47515815972</v>
+        <v>46182.64182482639</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>186</v>
@@ -8781,11 +8781,11 @@
         <v>346</v>
       </c>
       <c r="B125" s="8">
-        <v>46181.44954105324</v>
+        <v>46181.61620771991</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46182.47515746528</v>
+        <v>46182.64182413195</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>189</v>
@@ -8834,11 +8834,11 @@
         <v>347</v>
       </c>
       <c r="B126" s="5">
-        <v>46181.44957916667</v>
+        <v>46181.616245833335</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46182.47515675926</v>
+        <v>46182.641823425925</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>276</v>
@@ -8887,11 +8887,11 @@
         <v>348</v>
       </c>
       <c r="B127" s="8">
-        <v>46181.44281758102</v>
+        <v>46181.60948424769</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46182.47532600694</v>
+        <v>46182.64199267361</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>349</v>
@@ -8950,11 +8950,11 @@
         <v>350</v>
       </c>
       <c r="B128" s="5">
-        <v>46181.44282303241</v>
+        <v>46181.60948969907</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46182.4753071875</v>
+        <v>46182.641973854166</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>181</v>
@@ -9003,11 +9003,11 @@
         <v>352</v>
       </c>
       <c r="B129" s="8">
-        <v>46181.44282871528</v>
+        <v>46181.60949538194</v>
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46182.475304189815</v>
+        <v>46182.64197085648</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>181</v>
@@ -9056,11 +9056,11 @@
         <v>353</v>
       </c>
       <c r="B130" s="5">
-        <v>46181.44289351851</v>
+        <v>46181.609560185185</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46182.47530045139</v>
+        <v>46182.641967118056</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>59</v>
@@ -9109,11 +9109,11 @@
         <v>354</v>
       </c>
       <c r="B131" s="8">
-        <v>46181.449924479166</v>
+        <v>46181.61659114584</v>
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46182.47529741898</v>
+        <v>46182.64196408565</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>59</v>
@@ -9162,11 +9162,11 @@
         <v>355</v>
       </c>
       <c r="B132" s="5">
-        <v>46181.44995765046</v>
+        <v>46181.61662431713</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46182.475294386575</v>
+        <v>46182.64196105324</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>186</v>
@@ -9215,11 +9215,11 @@
         <v>356</v>
       </c>
       <c r="B133" s="8">
-        <v>46181.449995717594</v>
+        <v>46181.61666238426</v>
       </c>
       <c r="C133" s="9"/>
       <c r="D133" s="8">
-        <v>46182.47528787037</v>
+        <v>46182.64195453704</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>189</v>
@@ -9268,11 +9268,11 @@
         <v>357</v>
       </c>
       <c r="B134" s="5">
-        <v>46181.450033402776</v>
+        <v>46181.61670006944</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46182.47528706018</v>
+        <v>46182.64195372685</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>191</v>
@@ -9321,11 +9321,11 @@
         <v>358</v>
       </c>
       <c r="B135" s="8">
-        <v>46181.44289893519</v>
+        <v>46181.60956560185</v>
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="8">
-        <v>46182.662856574076</v>
+        <v>46182.82952324074</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>359</v>
@@ -9384,11 +9384,11 @@
         <v>360</v>
       </c>
       <c r="B136" s="5">
-        <v>46181.44290521991</v>
+        <v>46181.60957188657</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46182.6627863426</v>
+        <v>46182.82945300926</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>181</v>
@@ -9437,11 +9437,11 @@
         <v>362</v>
       </c>
       <c r="B137" s="8">
-        <v>46181.44291690973</v>
+        <v>46181.609583576384</v>
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46182.66278711805</v>
+        <v>46182.829453784725</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>181</v>
@@ -9490,11 +9490,11 @@
         <v>363</v>
       </c>
       <c r="B138" s="5">
-        <v>46181.442921747686</v>
+        <v>46181.60958841435</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46182.66278791666</v>
+        <v>46182.829454583334</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>59</v>
@@ -9543,11 +9543,11 @@
         <v>364</v>
       </c>
       <c r="B139" s="8">
-        <v>46181.45017318287</v>
+        <v>46181.616839849536</v>
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46182.66278903935</v>
+        <v>46182.829455706014</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>59</v>
@@ -9596,11 +9596,11 @@
         <v>365</v>
       </c>
       <c r="B140" s="5">
-        <v>46181.45023082176</v>
+        <v>46181.61689748843</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46182.662789803246</v>
+        <v>46182.8294564699</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>186</v>
@@ -9649,11 +9649,11 @@
         <v>366</v>
       </c>
       <c r="B141" s="8">
-        <v>46181.45027590278</v>
+        <v>46181.616942569446</v>
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46182.66279054398</v>
+        <v>46182.82945721065</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>189</v>
@@ -9702,11 +9702,11 @@
         <v>367</v>
       </c>
       <c r="B142" s="5">
-        <v>46181.45031484954</v>
+        <v>46181.6169815162</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46182.6627912963</v>
+        <v>46182.82945796296</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>191</v>
@@ -9755,11 +9755,11 @@
         <v>368</v>
       </c>
       <c r="B143" s="8">
-        <v>46181.442926006945</v>
+        <v>46181.609592673616</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46182.47574071759</v>
+        <v>46182.642407384265</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>369</v>
@@ -9818,11 +9818,11 @@
         <v>371</v>
       </c>
       <c r="B144" s="5">
-        <v>46181.442938506945</v>
+        <v>46181.60960517361</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46182.66278605324</v>
+        <v>46182.8294527199</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>181</v>
@@ -9871,11 +9871,11 @@
         <v>372</v>
       </c>
       <c r="B145" s="8">
-        <v>46181.44294334491</v>
+        <v>46181.609610011576</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46182.662785243054</v>
+        <v>46182.829451909725</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>181</v>
@@ -9924,11 +9924,11 @@
         <v>373</v>
       </c>
       <c r="B146" s="5">
-        <v>46181.44294712963</v>
+        <v>46181.609613796296</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46182.6627853588</v>
+        <v>46182.829452025464</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>59</v>
@@ -9977,11 +9977,11 @@
         <v>374</v>
       </c>
       <c r="B147" s="8">
-        <v>46181.450454756945</v>
+        <v>46181.61712142361</v>
       </c>
       <c r="C147" s="9"/>
       <c r="D147" s="8">
-        <v>46182.662785312496</v>
+        <v>46182.82945197917</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>59</v>
@@ -10030,11 +10030,11 @@
         <v>375</v>
       </c>
       <c r="B148" s="5">
-        <v>46181.450494282406</v>
+        <v>46181.61716094907</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46182.66278540509</v>
+        <v>46182.82945207176</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>186</v>
@@ -10083,11 +10083,11 @@
         <v>376</v>
       </c>
       <c r="B149" s="8">
-        <v>46181.45052966435</v>
+        <v>46181.61719633102</v>
       </c>
       <c r="C149" s="9"/>
       <c r="D149" s="8">
-        <v>46182.6627853588</v>
+        <v>46182.829452025464</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>189</v>
@@ -10136,11 +10136,11 @@
         <v>377</v>
       </c>
       <c r="B150" s="5">
-        <v>46181.45056878473</v>
+        <v>46181.617235451384</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46182.66278575231</v>
+        <v>46182.829452418984</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>191</v>
@@ -10189,11 +10189,11 @@
         <v>378</v>
       </c>
       <c r="B151" s="8">
-        <v>46181.44295075232</v>
+        <v>46181.60961741898</v>
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="8">
-        <v>46182.46782773148</v>
+        <v>46182.63449439815</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>379</v>
@@ -10236,11 +10236,11 @@
         <v>381</v>
       </c>
       <c r="B152" s="5">
-        <v>46181.44295508102</v>
+        <v>46181.60962174769</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46182.47578170139</v>
+        <v>46182.64244836806</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>382</v>
@@ -10299,11 +10299,11 @@
         <v>385</v>
       </c>
       <c r="B153" s="8">
-        <v>46181.442961134264</v>
+        <v>46181.60962780092</v>
       </c>
       <c r="C153" s="9"/>
       <c r="D153" s="8">
-        <v>46191.512262916665</v>
+        <v>46191.67892958333</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>386</v>
@@ -10362,11 +10362,11 @@
         <v>387</v>
       </c>
       <c r="B154" s="5">
-        <v>46181.44296822917</v>
+        <v>46181.60963489584</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46182.467827650464</v>
+        <v>46182.63449431713</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>388</v>
@@ -10415,11 +10415,11 @@
         <v>390</v>
       </c>
       <c r="B155" s="8">
-        <v>46181.44297354166</v>
+        <v>46181.609640208335</v>
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46182.47587710648</v>
+        <v>46182.64254377315</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>391</v>
@@ -10478,11 +10478,11 @@
         <v>393</v>
       </c>
       <c r="B156" s="5">
-        <v>46181.44297969907</v>
+        <v>46181.609646365745</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46182.475874131946</v>
+        <v>46182.64254079861</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>394</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -3725,7 +3725,7 @@
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46182.6267959838</v>
+        <v>46199.57115935185</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>120</v>
@@ -3786,9 +3786,11 @@
       <c r="B36" s="5">
         <v>46181.60902488426</v>
       </c>
-      <c r="C36" s="6"/>
+      <c r="C36" s="5">
+        <v>46199.57115320602</v>
+      </c>
       <c r="D36" s="5">
-        <v>46196.65857439815</v>
+        <v>46199.57115532407</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
@@ -3847,7 +3849,7 @@
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="8">
-        <v>46182.6267641088</v>
+        <v>46199.57161773148</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>139</v>
@@ -3904,9 +3906,11 @@
       <c r="B38" s="5">
         <v>46181.60903511574</v>
       </c>
-      <c r="C38" s="6"/>
+      <c r="C38" s="5">
+        <v>46199.57234078704</v>
+      </c>
       <c r="D38" s="5">
-        <v>46182.626906840276</v>
+        <v>46199.572352546296</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -3954,10 +3958,10 @@
         <v>32</v>
       </c>
       <c r="T38" s="6">
-        <v>0</v>
-      </c>
-      <c r="U38" s="11" t="s">
-        <v>57</v>
+        <v>1</v>
+      </c>
+      <c r="U38" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
@@ -3967,9 +3971,11 @@
       <c r="B39" s="8">
         <v>46181.60903861111</v>
       </c>
-      <c r="C39" s="9"/>
+      <c r="C39" s="8">
+        <v>46199.57221719908</v>
+      </c>
       <c r="D39" s="8">
-        <v>46196.65883732639</v>
+        <v>46199.57256810185</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>100</v>
@@ -4020,9 +4026,11 @@
       <c r="B40" s="5">
         <v>46181.609042951386</v>
       </c>
-      <c r="C40" s="6"/>
+      <c r="C40" s="5">
+        <v>46199.57232475694</v>
+      </c>
       <c r="D40" s="5">
-        <v>46182.626868680556</v>
+        <v>46199.57232634259</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>147</v>
@@ -5704,7 +5712,7 @@
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46182.635758460645</v>
+        <v>46199.572346076384</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>227</v>
@@ -5754,8 +5762,8 @@
       <c r="T70" s="6">
         <v>0</v>
       </c>
-      <c r="U70" s="11" t="s">
-        <v>57</v>
+      <c r="U70" s="12" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -373,7 +373,7 @@
     <t xml:space="preserve">Propuesta Fabricación externa ot 4347 </t>
   </si>
   <si>
-    <t>Generacion OC Fabricación Externa ot 4342 -4344</t>
+    <t>Generacion OC Fabricación Externa ot 4347</t>
   </si>
   <si>
     <t>1215506992580948</t>
@@ -514,28 +514,28 @@
     <t>rosemary.singh@zitron.com</t>
   </si>
   <si>
-    <t>Fabricación estructura proveedor externo ot 4342 -4344,Generacion OC Fabricación Externa ot 4342 -4344</t>
+    <t>Fabricación estructura proveedor externo ot 4347,Generacion OC Fabricación Externa ot 4347</t>
   </si>
   <si>
     <t>1215506819661464</t>
   </si>
   <si>
-    <t>Fabricación estructura proveedor externo ot 4342 -4344,Fabricación Externa  ot 4347</t>
+    <t>Fabricación estructura proveedor externo ot 4347,Fabricación Externa  ot 4347</t>
   </si>
   <si>
     <t>1215506639064735</t>
   </si>
   <si>
-    <t>Fabricación estructura proveedor externo ot 4342 -4344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Externa  ot 4347,Control de calidad fabricación externa  ot 4342 -4344,Recepcion fabricación externa </t>
+    <t>Fabricación estructura proveedor externo ot 4347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Externa  ot 4347,Control de calidad fabricación externa  ot 4347,Recepcion fabricación externa </t>
   </si>
   <si>
     <t>1215506639064752</t>
   </si>
   <si>
-    <t>Control de calidad fabricación externa  ot 4342 -4344</t>
+    <t>Control de calidad fabricación externa  ot 4347</t>
   </si>
   <si>
     <t>Nicolás López</t>
@@ -4081,9 +4081,11 @@
       <c r="B41" s="8">
         <v>46181.609047164355</v>
       </c>
-      <c r="C41" s="9"/>
+      <c r="C41" s="8">
+        <v>46204.67472811343</v>
+      </c>
       <c r="D41" s="8">
-        <v>46183.70162199074</v>
+        <v>46204.6747446875</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>150</v>
@@ -4131,10 +4133,10 @@
         <v>32</v>
       </c>
       <c r="T41" s="9">
-        <v>0</v>
-      </c>
-      <c r="U41" s="11" t="s">
-        <v>57</v>
+        <v>1</v>
+      </c>
+      <c r="U41" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
@@ -4144,9 +4146,11 @@
       <c r="B42" s="5">
         <v>46181.60905075232</v>
       </c>
-      <c r="C42" s="6"/>
+      <c r="C42" s="5">
+        <v>46204.67332877315</v>
+      </c>
       <c r="D42" s="5">
-        <v>46197.6451175</v>
+        <v>46204.67396857639</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>106</v>
@@ -4197,9 +4201,11 @@
       <c r="B43" s="8">
         <v>46181.60905546296</v>
       </c>
-      <c r="C43" s="9"/>
+      <c r="C43" s="8">
+        <v>46204.67337491898</v>
+      </c>
       <c r="D43" s="8">
-        <v>46183.70547770833</v>
+        <v>46204.67391837963</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>157</v>
@@ -4252,7 +4258,7 @@
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46182.62707423611</v>
+        <v>46204.67384744213</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>160</v>
@@ -7231,7 +7237,7 @@
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46182.64108152778</v>
+        <v>46204.67339321759</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>287</v>
@@ -7281,8 +7287,8 @@
       <c r="T97" s="9">
         <v>0</v>
       </c>
-      <c r="U97" s="11" t="s">
-        <v>57</v>
+      <c r="U97" s="12" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -6017,7 +6017,7 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46182.63612115741</v>
+        <v>46204.88302877315</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>240</v>
@@ -6080,7 +6080,7 @@
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46182.63598688657</v>
+        <v>46204.88313940972</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>181</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -298,448 +298,448 @@
     <t>propuesta alabes  ot 4347,propuesta motor  ot 4347,propuesta nucleo rodete  ot 4347,propuesta Corte Laser ot 4347</t>
   </si>
   <si>
+    <t>1215506984585999</t>
+  </si>
+  <si>
+    <t>propuesta motor  ot 4347</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Reserva motor ot 4347</t>
+  </si>
+  <si>
+    <t>1215506984586021</t>
+  </si>
+  <si>
+    <t>propuesta alabes  ot 4347</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Reserva alabe ot 4347</t>
+  </si>
+  <si>
+    <t>1215506638889337</t>
+  </si>
+  <si>
+    <t>propuesta nucleo rodete  ot 4347</t>
+  </si>
+  <si>
+    <t>benjamin.bustos@zitron.com</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Reserva rodete ot 4347</t>
+  </si>
+  <si>
+    <t>1215506984624474</t>
+  </si>
+  <si>
+    <t>propuesta Corte Laser ot 4347</t>
+  </si>
+  <si>
+    <t>hugo isla martinez</t>
+  </si>
+  <si>
+    <t>hugo.isla@zitron.com</t>
+  </si>
+  <si>
+    <t>check planos</t>
+  </si>
+  <si>
+    <t>Generación OC materiales corte Laser ot 4342 -4344,Propuesta compras:</t>
+  </si>
+  <si>
+    <t>1215506984624491</t>
+  </si>
+  <si>
+    <t>Propuesta Corte plasma  ot 4347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC Corte Plasma  ot 4342 -4344 </t>
+  </si>
+  <si>
+    <t>1215506992580924</t>
+  </si>
+  <si>
+    <t>Propuesta Mecanizado ot 4347</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado ot 4342 -4344</t>
+  </si>
+  <si>
+    <t>1215506992580936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propuesta Fabricación externa ot 4347 </t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación Externa ot 4347</t>
+  </si>
+  <si>
+    <t>1215506992580948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propuesta Tableros </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC   ot 4343 </t>
+  </si>
+  <si>
+    <t>1215789383150135</t>
+  </si>
+  <si>
+    <t>Reserva material</t>
+  </si>
+  <si>
+    <t>1215789383150150</t>
+  </si>
+  <si>
+    <t>Reserva motor ot 4347</t>
+  </si>
+  <si>
+    <t>1215789383150151</t>
+  </si>
+  <si>
+    <t>Reserva alabe ot 4347</t>
+  </si>
+  <si>
+    <t>1215789383150152</t>
+  </si>
+  <si>
+    <t>Reserva rodete ot 4347</t>
+  </si>
+  <si>
+    <t>1215504785833007</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t>Materiales corte Laser ot 4347</t>
+  </si>
+  <si>
+    <t>1215506819635552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tableros ot 4348  </t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC   ot 4343 ,fabricación tableros   ot 4343 </t>
+  </si>
+  <si>
+    <t>1215506819635564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tableros ot 4348  ,fabricación tableros   ot 4343 </t>
+  </si>
+  <si>
+    <t>1215506781705104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fabricación tableros   ot 4343 </t>
+  </si>
+  <si>
+    <t>Tableros ot 4348  ,Recepcion Tableros</t>
+  </si>
+  <si>
+    <t>1215506781705121</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC materiales corte Laser ot 4342 -4344,Fabricacion Corte Laser ot 4342 -4344 </t>
+  </si>
+  <si>
+    <t>1215506781722628</t>
+  </si>
+  <si>
+    <t>Generación OC materiales corte Laser ot 4342 -4344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materiales corte Laser ot 4347,Fabricacion Corte Laser ot 4342 -4344 </t>
+  </si>
+  <si>
+    <t>1215506819659775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricacion Corte Laser ot 4342 -4344 </t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Materiales corte Laser ot 4347</t>
+  </si>
+  <si>
+    <t>1215506819659795</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  ot 4347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC Corte Plasma  ot 4342 -4344 ,Fabricación Corte Plasma  ot 4342 -4344 </t>
+  </si>
+  <si>
+    <t>1215506781740443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materiales Corte Plasma  ot 4347,Fabricación Corte Plasma  ot 4342 -4344 </t>
+  </si>
+  <si>
+    <t>1215506781740460</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Corte Plasma  ot 4342 -4344 </t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  ot 4347,Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>1215506819661452</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  ot 4347</t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo ot 4347,Generacion OC Fabricación Externa ot 4347</t>
+  </si>
+  <si>
+    <t>1215506819661464</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo ot 4347,Fabricación Externa  ot 4347</t>
+  </si>
+  <si>
+    <t>1215506639064735</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo ot 4347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Externa  ot 4347,Control de calidad fabricación externa  ot 4347,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>1215506639064752</t>
+  </si>
+  <si>
+    <t>Control de calidad fabricación externa  ot 4347</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1215506639064764</t>
+  </si>
+  <si>
+    <t>Mecanizado  ot 4347</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado ot 4342 -4344,Fabricación Mecanizado ot 4342 -4344</t>
+  </si>
+  <si>
+    <t>1215506639065883</t>
+  </si>
+  <si>
+    <t>Mecanizado  ot 4347,Fabricación Mecanizado ot 4342 -4344</t>
+  </si>
+  <si>
+    <t>1215506639065900</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado ot 4342 -4344</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado,Mecanizado  ot 4347</t>
+  </si>
+  <si>
+    <t>1215506984807216</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1215506984807228</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4349- CODO 90° Ø1600MM</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>1215506639092978</t>
+  </si>
+  <si>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>Planos preliminar,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
+  </si>
+  <si>
+    <t>1215506639092995</t>
+  </si>
+  <si>
+    <t>OT 4349- CODO 90° Ø1600MM</t>
+  </si>
+  <si>
+    <t>OT 4349- CODO 90° Ø1600MM,Planos preliminar</t>
+  </si>
+  <si>
+    <t>1215504785833010</t>
+  </si>
+  <si>
+    <t>OT 4350 - CODO 135° Ø1600MM</t>
+  </si>
+  <si>
+    <t>1215504785833011</t>
+  </si>
+  <si>
+    <t>OT 4351 - DUCTO Ø1600MM L:1800MM</t>
+  </si>
+  <si>
+    <t>1215506992781082</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>1215506992781099</t>
+  </si>
+  <si>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1215506819701309</t>
+  </si>
+  <si>
+    <t>OT 4349- CODO 90° Ø1600MM,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1215504785833012</t>
+  </si>
+  <si>
+    <t>1215504785833013</t>
+  </si>
+  <si>
+    <t>1215506819701527</t>
+  </si>
+  <si>
+    <t>Propuesta Corte plasma  ot 4347,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Propuesta Mecanizado ot 4347,Propuesta Fabricación externa ot 4347 ,propuesta Corte Laser ot 4347,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
+  </si>
+  <si>
+    <t>1215506781840190</t>
+  </si>
+  <si>
+    <t>1215506781840207</t>
+  </si>
+  <si>
+    <t>1215504785833014</t>
+  </si>
+  <si>
+    <t>1215504785833017</t>
+  </si>
+  <si>
+    <t>1215506781849603</t>
+  </si>
+  <si>
+    <t>check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>1215506781849615</t>
+  </si>
+  <si>
+    <t>check pruebas FAT,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
+  </si>
+  <si>
+    <t>1215504785833018</t>
+  </si>
+  <si>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPO</t>
+  </si>
+  <si>
+    <t>1215506639141999</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion materiales corte laser,control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1215506639142011</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1215506984940147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma,Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>OT 4349- CODO 90° Ø1600MM,OT 4350 - CODO 135° Ø1600MM,OT 4351 - DUCTO Ø1600MM L:1800MM,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Bodega:,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
+  </si>
+  <si>
+    <t>1215506984940169</t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>control de calidad corte laser ,Control de calidad Corte plasma</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1215506984585999</t>
-  </si>
-  <si>
-    <t>propuesta motor  ot 4347</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Reserva motor ot 4347</t>
-  </si>
-  <si>
-    <t>1215506984586021</t>
-  </si>
-  <si>
-    <t>propuesta alabes  ot 4347</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Reserva alabe ot 4347</t>
-  </si>
-  <si>
-    <t>1215506638889337</t>
-  </si>
-  <si>
-    <t>propuesta nucleo rodete  ot 4347</t>
-  </si>
-  <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Reserva rodete ot 4347</t>
-  </si>
-  <si>
-    <t>1215506984624474</t>
-  </si>
-  <si>
-    <t>propuesta Corte Laser ot 4347</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
-  </si>
-  <si>
-    <t>check planos</t>
-  </si>
-  <si>
-    <t>Generación OC materiales corte Laser ot 4342 -4344,Propuesta compras:</t>
-  </si>
-  <si>
-    <t>1215506984624491</t>
-  </si>
-  <si>
-    <t>Propuesta Corte plasma  ot 4347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC Corte Plasma  ot 4342 -4344 </t>
-  </si>
-  <si>
-    <t>1215506992580924</t>
-  </si>
-  <si>
-    <t>Propuesta Mecanizado ot 4347</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado ot 4342 -4344</t>
-  </si>
-  <si>
-    <t>1215506992580936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propuesta Fabricación externa ot 4347 </t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación Externa ot 4347</t>
-  </si>
-  <si>
-    <t>1215506992580948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propuesta Tableros </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC   ot 4343 </t>
-  </si>
-  <si>
-    <t>1215789383150135</t>
-  </si>
-  <si>
-    <t>Reserva material</t>
-  </si>
-  <si>
-    <t>1215789383150150</t>
-  </si>
-  <si>
-    <t>Reserva motor ot 4347</t>
-  </si>
-  <si>
-    <t>1215789383150151</t>
-  </si>
-  <si>
-    <t>Reserva alabe ot 4347</t>
-  </si>
-  <si>
-    <t>1215789383150152</t>
-  </si>
-  <si>
-    <t>Reserva rodete ot 4347</t>
-  </si>
-  <si>
-    <t>1215504785833007</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t>Materiales corte Laser ot 4347</t>
-  </si>
-  <si>
-    <t>1215506819635552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tableros ot 4348  </t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC   ot 4343 ,fabricación tableros   ot 4343 </t>
-  </si>
-  <si>
-    <t>1215506819635564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tableros ot 4348  ,fabricación tableros   ot 4343 </t>
-  </si>
-  <si>
-    <t>1215506781705104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fabricación tableros   ot 4343 </t>
-  </si>
-  <si>
-    <t>Tableros ot 4348  ,Recepcion Tableros</t>
-  </si>
-  <si>
-    <t>1215506781705121</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC materiales corte Laser ot 4342 -4344,Fabricacion Corte Laser ot 4342 -4344 </t>
-  </si>
-  <si>
-    <t>1215506781722628</t>
-  </si>
-  <si>
-    <t>Generación OC materiales corte Laser ot 4342 -4344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Materiales corte Laser ot 4347,Fabricacion Corte Laser ot 4342 -4344 </t>
-  </si>
-  <si>
-    <t>1215506819659775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricacion Corte Laser ot 4342 -4344 </t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Materiales corte Laser ot 4347</t>
-  </si>
-  <si>
-    <t>1215506819659795</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  ot 4347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC Corte Plasma  ot 4342 -4344 ,Fabricación Corte Plasma  ot 4342 -4344 </t>
-  </si>
-  <si>
-    <t>1215506781740443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Materiales Corte Plasma  ot 4347,Fabricación Corte Plasma  ot 4342 -4344 </t>
-  </si>
-  <si>
-    <t>1215506781740460</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Corte Plasma  ot 4342 -4344 </t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  ot 4347,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>1215506819661452</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  ot 4347</t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo ot 4347,Generacion OC Fabricación Externa ot 4347</t>
-  </si>
-  <si>
-    <t>1215506819661464</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo ot 4347,Fabricación Externa  ot 4347</t>
-  </si>
-  <si>
-    <t>1215506639064735</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo ot 4347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Externa  ot 4347,Control de calidad fabricación externa  ot 4347,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>1215506639064752</t>
-  </si>
-  <si>
-    <t>Control de calidad fabricación externa  ot 4347</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1215506639064764</t>
-  </si>
-  <si>
-    <t>Mecanizado  ot 4347</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado ot 4342 -4344,Fabricación Mecanizado ot 4342 -4344</t>
-  </si>
-  <si>
-    <t>1215506639065883</t>
-  </si>
-  <si>
-    <t>Mecanizado  ot 4347,Fabricación Mecanizado ot 4342 -4344</t>
-  </si>
-  <si>
-    <t>1215506639065900</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado ot 4342 -4344</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado,Mecanizado  ot 4347</t>
-  </si>
-  <si>
-    <t>1215506984807216</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1215506984807228</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4349- CODO 90° Ø1600MM</t>
-  </si>
-  <si>
-    <t>Alta</t>
-  </si>
-  <si>
-    <t>1215506639092978</t>
-  </si>
-  <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Planos preliminar,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
-  </si>
-  <si>
-    <t>1215506639092995</t>
-  </si>
-  <si>
-    <t>OT 4349- CODO 90° Ø1600MM</t>
-  </si>
-  <si>
-    <t>OT 4349- CODO 90° Ø1600MM,Planos preliminar</t>
-  </si>
-  <si>
-    <t>1215504785833010</t>
-  </si>
-  <si>
-    <t>OT 4350 - CODO 135° Ø1600MM</t>
-  </si>
-  <si>
-    <t>1215504785833011</t>
-  </si>
-  <si>
-    <t>OT 4351 - DUCTO Ø1600MM L:1800MM</t>
-  </si>
-  <si>
-    <t>1215506992781082</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>1215506992781099</t>
-  </si>
-  <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1215506819701309</t>
-  </si>
-  <si>
-    <t>OT 4349- CODO 90° Ø1600MM,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1215504785833012</t>
-  </si>
-  <si>
-    <t>1215504785833013</t>
-  </si>
-  <si>
-    <t>1215506819701527</t>
-  </si>
-  <si>
-    <t>Propuesta Corte plasma  ot 4347,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Propuesta Mecanizado ot 4347,Propuesta Fabricación externa ot 4347 ,propuesta Corte Laser ot 4347,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
-  </si>
-  <si>
-    <t>1215506781840190</t>
-  </si>
-  <si>
-    <t>1215506781840207</t>
-  </si>
-  <si>
-    <t>1215504785833014</t>
-  </si>
-  <si>
-    <t>1215504785833017</t>
-  </si>
-  <si>
-    <t>1215506781849603</t>
-  </si>
-  <si>
-    <t>check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>1215506781849615</t>
-  </si>
-  <si>
-    <t>check pruebas FAT,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
-  </si>
-  <si>
-    <t>1215504785833018</t>
-  </si>
-  <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPO</t>
-  </si>
-  <si>
-    <t>1215506639141999</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion materiales corte laser,control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1215506639142011</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1215506984940147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma,Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>OT 4349- CODO 90° Ø1600MM,OT 4350 - CODO 135° Ø1600MM,OT 4351 - DUCTO Ø1600MM L:1800MM,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Bodega:,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
-  </si>
-  <si>
-    <t>1215506984940169</t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>control de calidad corte laser ,Control de calidad Corte plasma</t>
   </si>
   <si>
     <t>1215506819763590</t>
@@ -2448,9 +2448,11 @@
       <c r="B14" s="5">
         <v>46181.60864021991</v>
       </c>
-      <c r="C14" s="6"/>
+      <c r="C14" s="5">
+        <v>46204.9032446412</v>
+      </c>
       <c r="D14" s="5">
-        <v>46191.77864815972</v>
+        <v>46204.903260949075</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>65</v>
@@ -2485,8 +2487,12 @@
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
       <c r="S14" s="6"/>
-      <c r="T14" s="6"/>
-      <c r="U14" s="6"/>
+      <c r="T14" s="6">
+        <v>1</v>
+      </c>
+      <c r="U14" s="10" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
@@ -2690,9 +2696,11 @@
       <c r="B18" s="5">
         <v>46181.60864670139</v>
       </c>
-      <c r="C18" s="6"/>
+      <c r="C18" s="5">
+        <v>46204.888791840276</v>
+      </c>
       <c r="D18" s="5">
-        <v>46197.42282767361</v>
+        <v>46204.88880490741</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>79</v>
@@ -2727,14 +2735,16 @@
       <c r="Q18" s="6"/>
       <c r="R18" s="6"/>
       <c r="S18" s="6"/>
-      <c r="T18" s="6"/>
-      <c r="U18" s="12" t="s">
-        <v>81</v>
+      <c r="T18" s="6">
+        <v>1</v>
+      </c>
+      <c r="U18" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B19" s="8">
         <v>46181.608864236114</v>
@@ -2746,7 +2756,7 @@
         <v>46190.88639424769</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
@@ -2779,7 +2789,7 @@
         <v>68</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q19" s="8">
         <v>46167</v>
@@ -2799,7 +2809,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B20" s="5">
         <v>46181.60886979167</v>
@@ -2811,7 +2821,7 @@
         <v>46190.88638454861</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2844,7 +2854,7 @@
         <v>72</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Q20" s="5">
         <v>46174</v>
@@ -2864,7 +2874,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B21" s="8">
         <v>46181.60887520833</v>
@@ -2876,16 +2886,16 @@
         <v>46197.422811446755</v>
       </c>
       <c r="E21" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="F21" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>90</v>
-      </c>
       <c r="H21" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I21" s="8">
         <v>46174</v>
@@ -2909,7 +2919,7 @@
         <v>72</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q21" s="8">
         <v>46174</v>
@@ -2929,7 +2939,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B22" s="5">
         <v>46181.60888054398</v>
@@ -2941,16 +2951,16 @@
         <v>46196.65858296296</v>
       </c>
       <c r="E22" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="F22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G22" s="6" t="s">
+      <c r="H22" s="6" t="s">
         <v>94</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>95</v>
       </c>
       <c r="I22" s="5">
         <v>46248</v>
@@ -2971,10 +2981,10 @@
         <v>79</v>
       </c>
       <c r="O22" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="P22" s="6" t="s">
         <v>96</v>
-      </c>
-      <c r="P22" s="6" t="s">
-        <v>97</v>
       </c>
       <c r="Q22" s="5">
         <v>46248</v>
@@ -2994,7 +3004,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B23" s="8">
         <v>46181.60888559028</v>
@@ -3006,16 +3016,16 @@
         <v>46196.658845625</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H23" s="9" t="s">
         <v>94</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>95</v>
       </c>
       <c r="I23" s="8">
         <v>46248</v>
@@ -3036,10 +3046,10 @@
         <v>79</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q23" s="8">
         <v>46248</v>
@@ -3059,26 +3069,28 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B24" s="5">
         <v>46181.60888961806</v>
       </c>
-      <c r="C24" s="6"/>
+      <c r="C24" s="5">
+        <v>46204.888766944445</v>
+      </c>
       <c r="D24" s="5">
-        <v>46191.67367153935</v>
+        <v>46204.888792060185</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>94</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>95</v>
       </c>
       <c r="I24" s="5">
         <v>46248</v>
@@ -3099,10 +3111,10 @@
         <v>79</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Q24" s="5">
         <v>46248</v>
@@ -3114,15 +3126,15 @@
         <v>32</v>
       </c>
       <c r="T24" s="6">
-        <v>0</v>
-      </c>
-      <c r="U24" s="12" t="s">
-        <v>81</v>
+        <v>1</v>
+      </c>
+      <c r="U24" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B25" s="8">
         <v>46181.6088934375</v>
@@ -3134,16 +3146,16 @@
         <v>46197.64512664352</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H25" s="9" t="s">
         <v>94</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>95</v>
       </c>
       <c r="I25" s="8">
         <v>46248</v>
@@ -3164,10 +3176,10 @@
         <v>79</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q25" s="8">
         <v>46248</v>
@@ -3187,7 +3199,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B26" s="5">
         <v>46181.608897638886</v>
@@ -3199,7 +3211,7 @@
         <v>46190.67787061342</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
@@ -3232,7 +3244,7 @@
         <v>47</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q26" s="5">
         <v>46168</v>
@@ -3252,7 +3264,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B27" s="8">
         <v>46190.88204489583</v>
@@ -3264,7 +3276,7 @@
         <v>46197.424089050925</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>25</v>
@@ -3305,7 +3317,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B28" s="5">
         <v>46190.88321909722</v>
@@ -3317,16 +3329,16 @@
         <v>46197.42355928241</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I28" s="5">
         <v>46169</v>
@@ -3344,10 +3356,10 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>26</v>
@@ -3370,7 +3382,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B29" s="8">
         <v>46190.88327185185</v>
@@ -3382,16 +3394,16 @@
         <v>46197.423981597225</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I29" s="8">
         <v>46176</v>
@@ -3409,10 +3421,10 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P29" s="9" t="s">
         <v>26</v>
@@ -3435,7 +3447,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B30" s="5">
         <v>46190.88332659722</v>
@@ -3447,16 +3459,16 @@
         <v>46197.42407648148</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I30" s="5">
         <v>46176</v>
@@ -3474,10 +3486,10 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>26</v>
@@ -3500,7 +3512,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B31" s="8">
         <v>46181.608652256946</v>
@@ -3510,7 +3522,7 @@
         <v>46190.886375057875</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>25</v>
@@ -3534,7 +3546,7 @@
         <v>26</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P31" s="9" t="s">
         <v>26</v>
@@ -3547,7 +3559,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B32" s="5">
         <v>46181.60900793981</v>
@@ -3557,16 +3569,16 @@
         <v>46195.6859309838</v>
       </c>
       <c r="E32" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="F32" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G32" s="6" t="s">
+      <c r="H32" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="I32" s="5">
         <v>46170</v>
@@ -3584,10 +3596,10 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3610,7 +3622,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B33" s="8">
         <v>46181.60901165509</v>
@@ -3622,16 +3634,16 @@
         <v>46195.68592747685</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="H33" s="9" t="s">
         <v>123</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>124</v>
       </c>
       <c r="I33" s="8">
         <v>46170</v>
@@ -3649,13 +3661,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3665,7 +3677,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B34" s="5">
         <v>46181.60901612269</v>
@@ -3675,16 +3687,16 @@
         <v>46195.685932430555</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="I34" s="5">
         <v>46177</v>
@@ -3702,13 +3714,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3718,7 +3730,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B35" s="8">
         <v>46181.60902011574</v>
@@ -3728,16 +3740,16 @@
         <v>46199.57115935185</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="H35" s="9" t="s">
         <v>132</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>133</v>
       </c>
       <c r="I35" s="8">
         <v>46252</v>
@@ -3755,13 +3767,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q35" s="8">
         <v>46252</v>
@@ -3781,7 +3793,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B36" s="5">
         <v>46181.60902488426</v>
@@ -3793,16 +3805,16 @@
         <v>46199.57115532407</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>133</v>
       </c>
       <c r="I36" s="5">
         <v>46252</v>
@@ -3820,13 +3832,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3842,7 +3854,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B37" s="8">
         <v>46181.609029803236</v>
@@ -3852,16 +3864,16 @@
         <v>46199.57161773148</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="H37" s="9" t="s">
         <v>132</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>133</v>
       </c>
       <c r="I37" s="8">
         <v>46254</v>
@@ -3879,13 +3891,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3901,7 +3913,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B38" s="5">
         <v>46181.60903511574</v>
@@ -3913,16 +3925,16 @@
         <v>46199.572352546296</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>133</v>
       </c>
       <c r="I38" s="5">
         <v>46252</v>
@@ -3940,10 +3952,10 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3966,7 +3978,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B39" s="8">
         <v>46181.60903861111</v>
@@ -3978,16 +3990,16 @@
         <v>46199.57256810185</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="H39" s="9" t="s">
         <v>132</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>133</v>
       </c>
       <c r="I39" s="8">
         <v>46252</v>
@@ -4005,13 +4017,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -4021,7 +4033,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B40" s="5">
         <v>46181.609042951386</v>
@@ -4033,16 +4045,16 @@
         <v>46199.57232634259</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>133</v>
       </c>
       <c r="I40" s="5">
         <v>46254</v>
@@ -4060,13 +4072,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4076,7 +4088,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B41" s="8">
         <v>46181.609047164355</v>
@@ -4088,16 +4100,16 @@
         <v>46204.6747446875</v>
       </c>
       <c r="E41" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G41" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="F41" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G41" s="9" t="s">
+      <c r="H41" s="9" t="s">
         <v>151</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>152</v>
       </c>
       <c r="I41" s="8">
         <v>46252</v>
@@ -4115,10 +4127,10 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P41" s="9" t="s">
         <v>26</v>
@@ -4141,7 +4153,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B42" s="5">
         <v>46181.60905075232</v>
@@ -4153,16 +4165,16 @@
         <v>46204.67396857639</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>151</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>152</v>
       </c>
       <c r="I42" s="5">
         <v>46252</v>
@@ -4180,13 +4192,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4196,7 +4208,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B43" s="8">
         <v>46181.60905546296</v>
@@ -4208,16 +4220,16 @@
         <v>46204.67391837963</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="H43" s="9" t="s">
         <v>151</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>152</v>
       </c>
       <c r="I43" s="8">
         <v>46261</v>
@@ -4235,13 +4247,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -4251,7 +4263,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B44" s="5">
         <v>46181.60906018519</v>
@@ -4261,16 +4273,16 @@
         <v>46204.67384744213</v>
       </c>
       <c r="E44" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G44" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="F44" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G44" s="6" t="s">
+      <c r="H44" s="6" t="s">
         <v>161</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>162</v>
       </c>
       <c r="I44" s="5">
         <v>46290</v>
@@ -4288,10 +4300,10 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>26</v>
@@ -4304,7 +4316,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B45" s="8">
         <v>46181.609063310185</v>
@@ -4314,16 +4326,16 @@
         <v>46182.62725847222</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="H45" s="9" t="s">
         <v>132</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>133</v>
       </c>
       <c r="I45" s="8">
         <v>46252</v>
@@ -4341,10 +4353,10 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>26</v>
@@ -4367,26 +4379,26 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B46" s="5">
         <v>46181.60906703703</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46182.62720454861</v>
+        <v>46204.88877467593</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>133</v>
       </c>
       <c r="I46" s="5">
         <v>46252</v>
@@ -4404,13 +4416,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4420,7 +4432,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B47" s="8">
         <v>46181.60907681713</v>
@@ -4430,16 +4442,16 @@
         <v>46182.627201296295</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="H47" s="9" t="s">
         <v>132</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>133</v>
       </c>
       <c r="I47" s="8">
         <v>46254</v>
@@ -4457,13 +4469,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
@@ -4473,17 +4485,17 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B48" s="5">
         <v>46181.6090815625</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46191.542751388886</v>
+        <v>46204.9033168287</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>25</v>
@@ -4507,7 +4519,7 @@
         <v>26</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>26</v>
@@ -4516,13 +4528,11 @@
       <c r="R48" s="6"/>
       <c r="S48" s="6"/>
       <c r="T48" s="6"/>
-      <c r="U48" s="12" t="s">
-        <v>81</v>
-      </c>
+      <c r="U48" s="6"/>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B49" s="8">
         <v>46181.60908480324</v>
@@ -4534,16 +4544,16 @@
         <v>46197.7158150926</v>
       </c>
       <c r="E49" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G49" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="F49" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G49" s="9" t="s">
+      <c r="H49" s="9" t="s">
         <v>176</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>177</v>
       </c>
       <c r="I49" s="8">
         <v>46174</v>
@@ -4561,13 +4571,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q49" s="8">
         <v>46174</v>
@@ -4576,7 +4586,7 @@
         <v>46191</v>
       </c>
       <c r="S49" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="T49" s="9">
         <v>1</v>
@@ -4587,7 +4597,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B50" s="5">
         <v>46181.60908915509</v>
@@ -4599,16 +4609,16 @@
         <v>46190.70821390046</v>
       </c>
       <c r="E50" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="H50" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I50" s="5">
         <v>46174</v>
@@ -4626,13 +4636,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>76</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4642,7 +4652,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B51" s="8">
         <v>46181.60909384259</v>
@@ -4654,16 +4664,16 @@
         <v>46190.7082228125</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="H51" s="9" t="s">
         <v>182</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>183</v>
       </c>
       <c r="I51" s="8">
         <v>46174</v>
@@ -4681,13 +4691,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>76</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4697,7 +4707,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B52" s="5">
         <v>46181.61221741898</v>
@@ -4709,16 +4719,16 @@
         <v>46190.708227337964</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I52" s="5">
         <v>46174</v>
@@ -4736,13 +4746,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>76</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4752,7 +4762,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B53" s="8">
         <v>46181.612357199076</v>
@@ -4764,16 +4774,16 @@
         <v>46190.708233321755</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="H53" s="9" t="s">
         <v>182</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>183</v>
       </c>
       <c r="I53" s="8">
         <v>46174</v>
@@ -4791,13 +4801,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>76</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -4807,7 +4817,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B54" s="5">
         <v>46181.609098182875</v>
@@ -4819,16 +4829,16 @@
         <v>46197.71584820602</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>177</v>
       </c>
       <c r="I54" s="5">
         <v>46227</v>
@@ -4846,13 +4856,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q54" s="5">
         <v>46227</v>
@@ -4872,7 +4882,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B55" s="8">
         <v>46181.60910252314</v>
@@ -4884,16 +4894,16 @@
         <v>46191.54270819444</v>
       </c>
       <c r="E55" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G55" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="F55" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G55" s="9" t="s">
+      <c r="H55" s="9" t="s">
         <v>182</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>183</v>
       </c>
       <c r="I55" s="8">
         <v>46227</v>
@@ -4911,13 +4921,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4927,7 +4937,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B56" s="5">
         <v>46181.609107951386</v>
@@ -4939,16 +4949,16 @@
         <v>46191.54271703704</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I56" s="5">
         <v>46227</v>
@@ -4966,13 +4976,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4982,7 +4992,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B57" s="8">
         <v>46181.61393570602</v>
@@ -4994,16 +5004,16 @@
         <v>46190.70842170139</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="H57" s="9" t="s">
         <v>182</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>183</v>
       </c>
       <c r="I57" s="8">
         <v>46227</v>
@@ -5021,13 +5031,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5037,7 +5047,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B58" s="5">
         <v>46181.61396929398</v>
@@ -5049,16 +5059,16 @@
         <v>46190.708426550926</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I58" s="5">
         <v>46227</v>
@@ -5076,13 +5086,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5092,7 +5102,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B59" s="8">
         <v>46181.60911329861</v>
@@ -5104,16 +5114,16 @@
         <v>46191.54539826389</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="H59" s="9" t="s">
         <v>182</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>183</v>
       </c>
       <c r="I59" s="8">
         <v>46247</v>
@@ -5131,13 +5141,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q59" s="8">
         <v>46247</v>
@@ -5157,7 +5167,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B60" s="5">
         <v>46181.60912350695</v>
@@ -5169,16 +5179,16 @@
         <v>46191.54536050926</v>
       </c>
       <c r="E60" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="F60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G60" s="6" t="s">
+      <c r="H60" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I60" s="6"/>
       <c r="J60" s="5">
@@ -5194,13 +5204,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5210,7 +5220,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B61" s="8">
         <v>46181.60912782408</v>
@@ -5222,16 +5232,16 @@
         <v>46191.54537386574</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="H61" s="9" t="s">
         <v>182</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>183</v>
       </c>
       <c r="I61" s="9"/>
       <c r="J61" s="8">
@@ -5247,13 +5257,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5263,7 +5273,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B62" s="5">
         <v>46181.614119606485</v>
@@ -5275,16 +5285,16 @@
         <v>46190.721725358795</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I62" s="6"/>
       <c r="J62" s="5">
@@ -5300,10 +5310,10 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5316,7 +5326,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B63" s="8">
         <v>46181.61419627315</v>
@@ -5328,16 +5338,16 @@
         <v>46190.7217299537</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="H63" s="9" t="s">
         <v>182</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>183</v>
       </c>
       <c r="I63" s="9"/>
       <c r="J63" s="8">
@@ -5353,10 +5363,10 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5369,7 +5379,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B64" s="5">
         <v>46181.60913207176</v>
@@ -5379,16 +5389,16 @@
         <v>46182.633118067126</v>
       </c>
       <c r="E64" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G64" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="F64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G64" s="6" t="s">
+      <c r="H64" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I64" s="5">
         <v>46322</v>
@@ -5406,10 +5416,10 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>26</v>
@@ -5432,7 +5442,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B65" s="8">
         <v>46181.609135833336</v>
@@ -5442,16 +5452,16 @@
         <v>46182.63311847222</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="H65" s="9" t="s">
         <v>208</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>209</v>
       </c>
       <c r="I65" s="8">
         <v>46322</v>
@@ -5469,13 +5479,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5485,7 +5495,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B66" s="5">
         <v>46181.614311909725</v>
@@ -5495,16 +5505,16 @@
         <v>46182.63311923611</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I66" s="5">
         <v>46322</v>
@@ -5522,13 +5532,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5538,7 +5548,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B67" s="8">
         <v>46181.60918671296</v>
@@ -5548,7 +5558,7 @@
         <v>46181.77983537037</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>25</v>
@@ -5572,7 +5582,7 @@
         <v>26</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>26</v>
@@ -5585,7 +5595,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B68" s="5">
         <v>46181.609196087964</v>
@@ -5595,16 +5605,16 @@
         <v>46182.63576145833</v>
       </c>
       <c r="E68" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G68" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="F68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G68" s="6" t="s">
+      <c r="H68" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I68" s="5">
         <v>46252</v>
@@ -5622,13 +5632,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q68" s="5">
         <v>46252</v>
@@ -5648,7 +5658,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B69" s="8">
         <v>46181.609201921296</v>
@@ -5658,16 +5668,16 @@
         <v>46182.63583637732</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="H69" s="9" t="s">
         <v>161</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>162</v>
       </c>
       <c r="I69" s="8">
         <v>46254</v>
@@ -5685,13 +5695,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O69" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="P69" s="9" t="s">
         <v>224</v>
-      </c>
-      <c r="P69" s="9" t="s">
-        <v>225</v>
       </c>
       <c r="Q69" s="8">
         <v>46254</v>
@@ -5711,7 +5721,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B70" s="5">
         <v>46181.60920746528</v>
@@ -5721,16 +5731,16 @@
         <v>46199.572346076384</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I70" s="5">
         <v>46252</v>
@@ -5748,13 +5758,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q70" s="5">
         <v>46252</v>
@@ -5769,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="U70" s="12" t="s">
-        <v>81</v>
+        <v>228</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -5790,10 +5800,10 @@
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="H71" s="9" t="s">
         <v>161</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>162</v>
       </c>
       <c r="I71" s="8">
         <v>46254</v>
@@ -5811,10 +5821,10 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>231</v>
@@ -5853,10 +5863,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I72" s="5">
         <v>46252</v>
@@ -5874,10 +5884,10 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>234</v>
@@ -5916,10 +5926,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="H73" s="9" t="s">
         <v>161</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>162</v>
       </c>
       <c r="I73" s="8">
         <v>46254</v>
@@ -5937,7 +5947,7 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O73" s="9" t="s">
         <v>233</v>
@@ -6083,7 +6093,7 @@
         <v>46204.88313940972</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6136,7 +6146,7 @@
         <v>46182.63598342593</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
@@ -6169,7 +6179,7 @@
         <v>249</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
@@ -6189,7 +6199,7 @@
         <v>46182.63598072917</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6242,7 +6252,7 @@
         <v>46182.63597787037</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
@@ -6295,7 +6305,7 @@
         <v>46182.635973807875</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6411,7 +6421,7 @@
         <v>46191.54540523148</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6464,7 +6474,7 @@
         <v>46191.54540574074</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
@@ -6517,7 +6527,7 @@
         <v>46182.64084413194</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6570,7 +6580,7 @@
         <v>46182.64084086806</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
@@ -6623,7 +6633,7 @@
         <v>46182.6408357176</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6682,10 +6692,10 @@
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="H87" s="9" t="s">
         <v>161</v>
-      </c>
-      <c r="H87" s="9" t="s">
-        <v>162</v>
       </c>
       <c r="I87" s="8">
         <v>46289</v>
@@ -6739,16 +6749,16 @@
         <v>46191.545403842596</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>161</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>162</v>
       </c>
       <c r="I88" s="5">
         <v>46289</v>
@@ -6792,16 +6802,16 @@
         <v>46191.545404212964</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="H89" s="9" t="s">
         <v>161</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>162</v>
       </c>
       <c r="I89" s="8">
         <v>46289</v>
@@ -6851,10 +6861,10 @@
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="H90" s="6" t="s">
         <v>161</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>162</v>
       </c>
       <c r="I90" s="5">
         <v>46289</v>
@@ -6875,10 +6885,10 @@
         <v>268</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6904,10 +6914,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="H91" s="9" t="s">
         <v>161</v>
-      </c>
-      <c r="H91" s="9" t="s">
-        <v>162</v>
       </c>
       <c r="I91" s="8">
         <v>46289</v>
@@ -6928,10 +6938,10 @@
         <v>268</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -6957,10 +6967,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>161</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>162</v>
       </c>
       <c r="I92" s="5">
         <v>46289</v>
@@ -6981,7 +6991,7 @@
         <v>268</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>276</v>
@@ -7004,7 +7014,7 @@
         <v>46182.567648321754</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>25</v>
@@ -7057,10 +7067,10 @@
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I94" s="5">
         <v>46182</v>
@@ -7078,7 +7088,7 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>26</v>
@@ -7093,13 +7103,13 @@
         <v>46183</v>
       </c>
       <c r="S94" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
       <c r="U94" s="12" t="s">
-        <v>81</v>
+        <v>228</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -7120,10 +7130,10 @@
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="H95" s="9" t="s">
         <v>219</v>
-      </c>
-      <c r="H95" s="9" t="s">
-        <v>220</v>
       </c>
       <c r="I95" s="8">
         <v>46290</v>
@@ -7141,7 +7151,7 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O95" s="9" t="s">
         <v>26</v>
@@ -7162,7 +7172,7 @@
         <v>0</v>
       </c>
       <c r="U95" s="12" t="s">
-        <v>81</v>
+        <v>228</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
@@ -7183,10 +7193,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H96" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I96" s="5">
         <v>46226</v>
@@ -7204,7 +7214,7 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>26</v>
@@ -7225,7 +7235,7 @@
         <v>0</v>
       </c>
       <c r="U96" s="12" t="s">
-        <v>81</v>
+        <v>228</v>
       </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
@@ -7246,10 +7256,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="H97" s="9" t="s">
         <v>219</v>
-      </c>
-      <c r="H97" s="9" t="s">
-        <v>220</v>
       </c>
       <c r="I97" s="8">
         <v>46293</v>
@@ -7267,10 +7277,10 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P97" s="9" t="s">
         <v>288</v>
@@ -7288,7 +7298,7 @@
         <v>0</v>
       </c>
       <c r="U97" s="12" t="s">
-        <v>81</v>
+        <v>228</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
@@ -7309,10 +7319,10 @@
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H98" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I98" s="5">
         <v>46226</v>
@@ -7330,10 +7340,10 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>55</v>
@@ -7363,7 +7373,7 @@
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46182.633312060185</v>
+        <v>46204.895167395836</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>291</v>
@@ -7419,10 +7429,10 @@
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I100" s="5">
         <v>46290</v>
@@ -7476,16 +7486,16 @@
         <v>46182.64119599537</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I101" s="8">
         <v>46290</v>
@@ -7529,16 +7539,16 @@
         <v>46182.64119222222</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I102" s="5">
         <v>46290</v>
@@ -7559,7 +7569,7 @@
         <v>294</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>299</v>
@@ -7577,9 +7587,11 @@
       <c r="B103" s="8">
         <v>46181.609386111115</v>
       </c>
-      <c r="C103" s="9"/>
+      <c r="C103" s="8">
+        <v>46204.895157314815</v>
+      </c>
       <c r="D103" s="8">
-        <v>46182.641349328704</v>
+        <v>46204.895310810185</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>301</v>
@@ -7588,10 +7600,10 @@
         <v>26</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I103" s="8">
         <v>46311</v>
@@ -7612,7 +7624,7 @@
         <v>291</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P103" s="9" t="s">
         <v>291</v>
@@ -7627,10 +7639,10 @@
         <v>32</v>
       </c>
       <c r="T103" s="9">
-        <v>0</v>
-      </c>
-      <c r="U103" s="11" t="s">
-        <v>57</v>
+        <v>1</v>
+      </c>
+      <c r="U103" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
@@ -7640,21 +7652,23 @@
       <c r="B104" s="5">
         <v>46181.60939194444</v>
       </c>
-      <c r="C104" s="6"/>
+      <c r="C104" s="5">
+        <v>46204.89505366898</v>
+      </c>
       <c r="D104" s="5">
-        <v>46191.54539792824</v>
+        <v>46204.89505523148</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I104" s="5">
         <v>46311</v>
@@ -7693,21 +7707,23 @@
       <c r="B105" s="8">
         <v>46181.61518315972</v>
       </c>
-      <c r="C105" s="9"/>
+      <c r="C105" s="8">
+        <v>46204.89514296297</v>
+      </c>
       <c r="D105" s="8">
-        <v>46182.64130309028</v>
+        <v>46204.89514483797</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H105" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I105" s="8">
         <v>46311</v>
@@ -7757,10 +7773,10 @@
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I106" s="5">
         <v>46315</v>
@@ -7781,7 +7797,7 @@
         <v>291</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>291</v>
@@ -7811,19 +7827,19 @@
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46191.54540628473</v>
+        <v>46204.89506170139</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H107" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I107" s="8">
         <v>46315</v>
@@ -7867,16 +7883,16 @@
         <v>46182.64140446759</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I108" s="5">
         <v>46315</v>
@@ -7926,10 +7942,10 @@
         <v>26</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H109" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I109" s="8">
         <v>46317</v>
@@ -7950,7 +7966,7 @@
         <v>291</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P109" s="9" t="s">
         <v>291</v>
@@ -7983,16 +7999,16 @@
         <v>46191.54540483796</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I110" s="5">
         <v>46317</v>
@@ -8036,16 +8052,16 @@
         <v>46182.64151664352</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I111" s="8">
         <v>46317</v>
@@ -8095,10 +8111,10 @@
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I112" s="5">
         <v>46321</v>
@@ -8119,7 +8135,7 @@
         <v>291</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>291</v>
@@ -8152,16 +8168,16 @@
         <v>46182.641623125004</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I113" s="8">
         <v>46321</v>
@@ -8182,7 +8198,7 @@
         <v>322</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P113" s="9" t="s">
         <v>324</v>
@@ -8205,16 +8221,16 @@
         <v>46182.64161924769</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I114" s="5">
         <v>46321</v>
@@ -8235,10 +8251,10 @@
         <v>322</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8264,10 +8280,10 @@
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I115" s="8">
         <v>46323</v>
@@ -8288,7 +8304,7 @@
         <v>291</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P115" s="9" t="s">
         <v>328</v>
@@ -8321,16 +8337,16 @@
         <v>46182.64173178241</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I116" s="5">
         <v>46323</v>
@@ -8351,7 +8367,7 @@
         <v>327</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>330</v>
@@ -8374,16 +8390,16 @@
         <v>46182.64172883102</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I117" s="8">
         <v>46323</v>
@@ -8404,7 +8420,7 @@
         <v>327</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P117" s="9" t="s">
         <v>26</v>
@@ -8537,7 +8553,7 @@
         <v>46182.641845254635</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8567,7 +8583,7 @@
         <v>336</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>341</v>
@@ -8590,7 +8606,7 @@
         <v>46182.64184081019</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -8620,10 +8636,10 @@
         <v>336</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8749,7 +8765,7 @@
         <v>46182.64182482639</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8782,7 +8798,7 @@
         <v>262</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8802,7 +8818,7 @@
         <v>46182.64182413195</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -8835,7 +8851,7 @@
         <v>264</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -8888,7 +8904,7 @@
         <v>266</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8914,10 +8930,10 @@
         <v>26</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H127" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I127" s="8">
         <v>46325</v>
@@ -8938,7 +8954,7 @@
         <v>333</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P127" s="9" t="s">
         <v>333</v>
@@ -8971,16 +8987,16 @@
         <v>46182.641973854166</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I128" s="5">
         <v>46325</v>
@@ -9001,7 +9017,7 @@
         <v>349</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>351</v>
@@ -9024,16 +9040,16 @@
         <v>46182.64197085648</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I129" s="8">
         <v>46325</v>
@@ -9054,10 +9070,10 @@
         <v>349</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q129" s="9"/>
       <c r="R129" s="9"/>
@@ -9083,10 +9099,10 @@
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I130" s="5">
         <v>46325</v>
@@ -9136,10 +9152,10 @@
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I131" s="8">
         <v>46325</v>
@@ -9183,16 +9199,16 @@
         <v>46182.64196105324</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I132" s="5">
         <v>46325</v>
@@ -9213,10 +9229,10 @@
         <v>349</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9236,16 +9252,16 @@
         <v>46182.64195453704</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I133" s="8">
         <v>46325</v>
@@ -9266,10 +9282,10 @@
         <v>349</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9289,16 +9305,16 @@
         <v>46182.64195372685</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I134" s="5">
         <v>46325</v>
@@ -9322,7 +9338,7 @@
         <v>276</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9372,7 +9388,7 @@
         <v>333</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P135" s="9" t="s">
         <v>333</v>
@@ -9405,7 +9421,7 @@
         <v>46182.82945300926</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9435,7 +9451,7 @@
         <v>359</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P136" s="6" t="s">
         <v>361</v>
@@ -9458,7 +9474,7 @@
         <v>46182.829453784725</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
@@ -9488,10 +9504,10 @@
         <v>359</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q137" s="9"/>
       <c r="R137" s="9"/>
@@ -9617,7 +9633,7 @@
         <v>46182.8294564699</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9647,10 +9663,10 @@
         <v>359</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9670,7 +9686,7 @@
         <v>46182.82945721065</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
@@ -9700,10 +9716,10 @@
         <v>359</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -9723,7 +9739,7 @@
         <v>46182.82945796296</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -9753,10 +9769,10 @@
         <v>359</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9806,7 +9822,7 @@
         <v>333</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P143" s="9" t="s">
         <v>370</v>
@@ -9839,7 +9855,7 @@
         <v>46182.8294527199</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -9869,7 +9885,7 @@
         <v>369</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P144" s="6" t="s">
         <v>369</v>
@@ -9892,7 +9908,7 @@
         <v>46182.829451909725</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
@@ -9922,7 +9938,7 @@
         <v>369</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P145" s="9" t="s">
         <v>26</v>
@@ -10051,7 +10067,7 @@
         <v>46182.82945207176</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
@@ -10081,7 +10097,7 @@
         <v>369</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="P148" s="6" t="s">
         <v>26</v>
@@ -10104,7 +10120,7 @@
         <v>46182.829452025464</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
@@ -10134,7 +10150,7 @@
         <v>369</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P149" s="9" t="s">
         <v>26</v>
@@ -10157,7 +10173,7 @@
         <v>46182.829452418984</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
@@ -10187,7 +10203,7 @@
         <v>369</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P150" s="6" t="s">
         <v>26</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1815" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1816" uniqueCount="395">
   <si>
     <t>50001559 - FERROVIAL</t>
   </si>
@@ -415,6 +415,9 @@
     <t>Materiales corte Laser ot 4347</t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
     <t>1215506819635552</t>
   </si>
   <si>
@@ -737,9 +740,6 @@
   </si>
   <si>
     <t>control de calidad corte laser ,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1215506819763590</t>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46190.886375057875</v>
+        <v>46205.61719612269</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>118</v>
@@ -3555,11 +3555,13 @@
       <c r="R31" s="9"/>
       <c r="S31" s="9"/>
       <c r="T31" s="9"/>
-      <c r="U31" s="9"/>
+      <c r="U31" s="12" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B32" s="5">
         <v>46181.60900793981</v>
@@ -3569,16 +3571,16 @@
         <v>46195.6859309838</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I32" s="5">
         <v>46170</v>
@@ -3599,7 +3601,7 @@
         <v>118</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3622,7 +3624,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B33" s="8">
         <v>46181.60901165509</v>
@@ -3640,10 +3642,10 @@
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I33" s="8">
         <v>46170</v>
@@ -3661,13 +3663,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>107</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3677,7 +3679,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B34" s="5">
         <v>46181.60901612269</v>
@@ -3687,16 +3689,16 @@
         <v>46195.685932430555</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I34" s="5">
         <v>46177</v>
@@ -3714,13 +3716,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>108</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3730,14 +3732,16 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B35" s="8">
         <v>46181.60902011574</v>
       </c>
-      <c r="C35" s="9"/>
+      <c r="C35" s="8">
+        <v>46205.61719040509</v>
+      </c>
       <c r="D35" s="8">
-        <v>46199.57115935185</v>
+        <v>46205.61719211805</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>119</v>
@@ -3746,10 +3750,10 @@
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I35" s="8">
         <v>46252</v>
@@ -3770,7 +3774,7 @@
         <v>118</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P35" s="9" t="s">
         <v>118</v>
@@ -3785,15 +3789,15 @@
         <v>32</v>
       </c>
       <c r="T35" s="9">
-        <v>0</v>
-      </c>
-      <c r="U35" s="11" t="s">
-        <v>57</v>
+        <v>1</v>
+      </c>
+      <c r="U35" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B36" s="5">
         <v>46181.60902488426</v>
@@ -3805,16 +3809,16 @@
         <v>46199.57115532407</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I36" s="5">
         <v>46252</v>
@@ -3838,7 +3842,7 @@
         <v>92</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3854,26 +3858,28 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B37" s="8">
         <v>46181.609029803236</v>
       </c>
-      <c r="C37" s="9"/>
+      <c r="C37" s="8">
+        <v>46205.612570185185</v>
+      </c>
       <c r="D37" s="8">
-        <v>46199.57161773148</v>
+        <v>46205.61257221065</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I37" s="8">
         <v>46254</v>
@@ -3894,10 +3900,10 @@
         <v>119</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3913,7 +3919,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B38" s="5">
         <v>46181.60903511574</v>
@@ -3925,16 +3931,16 @@
         <v>46199.572352546296</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I38" s="5">
         <v>46252</v>
@@ -3955,7 +3961,7 @@
         <v>118</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3978,7 +3984,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B39" s="8">
         <v>46181.60903861111</v>
@@ -3996,10 +4002,10 @@
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I39" s="8">
         <v>46252</v>
@@ -4017,13 +4023,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O39" s="9" t="s">
         <v>98</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -4033,7 +4039,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B40" s="5">
         <v>46181.609042951386</v>
@@ -4045,16 +4051,16 @@
         <v>46199.57232634259</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I40" s="5">
         <v>46254</v>
@@ -4072,13 +4078,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>99</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4088,7 +4094,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B41" s="8">
         <v>46181.609047164355</v>
@@ -4100,16 +4106,16 @@
         <v>46204.6747446875</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I41" s="8">
         <v>46252</v>
@@ -4130,7 +4136,7 @@
         <v>118</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P41" s="9" t="s">
         <v>26</v>
@@ -4153,7 +4159,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B42" s="5">
         <v>46181.60905075232</v>
@@ -4171,10 +4177,10 @@
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I42" s="5">
         <v>46252</v>
@@ -4192,13 +4198,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>104</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4208,7 +4214,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B43" s="8">
         <v>46181.60905546296</v>
@@ -4220,16 +4226,16 @@
         <v>46204.67391837963</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I43" s="8">
         <v>46261</v>
@@ -4247,13 +4253,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O43" s="9" t="s">
         <v>105</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -4263,7 +4269,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B44" s="5">
         <v>46181.60906018519</v>
@@ -4273,16 +4279,16 @@
         <v>46204.67384744213</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I44" s="5">
         <v>46290</v>
@@ -4300,10 +4306,10 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>26</v>
@@ -4316,26 +4322,28 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B45" s="8">
         <v>46181.609063310185</v>
       </c>
-      <c r="C45" s="9"/>
+      <c r="C45" s="8">
+        <v>46205.61289446759</v>
+      </c>
       <c r="D45" s="8">
-        <v>46182.62725847222</v>
+        <v>46205.61290721065</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I45" s="8">
         <v>46252</v>
@@ -4356,7 +4364,7 @@
         <v>118</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>26</v>
@@ -4371,22 +4379,24 @@
         <v>32</v>
       </c>
       <c r="T45" s="9">
-        <v>0</v>
-      </c>
-      <c r="U45" s="11" t="s">
-        <v>57</v>
+        <v>1</v>
+      </c>
+      <c r="U45" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B46" s="5">
         <v>46181.60906703703</v>
       </c>
-      <c r="C46" s="6"/>
+      <c r="C46" s="5">
+        <v>46205.6128353588</v>
+      </c>
       <c r="D46" s="5">
-        <v>46204.88877467593</v>
+        <v>46205.61283694445</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>102</v>
@@ -4395,10 +4405,10 @@
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I46" s="5">
         <v>46252</v>
@@ -4416,13 +4426,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>101</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4432,26 +4442,28 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B47" s="8">
         <v>46181.60907681713</v>
       </c>
-      <c r="C47" s="9"/>
+      <c r="C47" s="8">
+        <v>46205.612877789354</v>
+      </c>
       <c r="D47" s="8">
-        <v>46182.627201296295</v>
+        <v>46205.612879328706</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I47" s="8">
         <v>46254</v>
@@ -4469,13 +4481,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>102</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
@@ -4485,7 +4497,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B48" s="5">
         <v>46181.6090815625</v>
@@ -4495,7 +4507,7 @@
         <v>46204.9033168287</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>25</v>
@@ -4519,7 +4531,7 @@
         <v>26</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>26</v>
@@ -4532,7 +4544,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B49" s="8">
         <v>46181.60908480324</v>
@@ -4544,16 +4556,16 @@
         <v>46197.7158150926</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I49" s="8">
         <v>46174</v>
@@ -4571,13 +4583,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q49" s="8">
         <v>46174</v>
@@ -4586,7 +4598,7 @@
         <v>46191</v>
       </c>
       <c r="S49" s="11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="T49" s="9">
         <v>1</v>
@@ -4597,7 +4609,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B50" s="5">
         <v>46181.60908915509</v>
@@ -4609,16 +4621,16 @@
         <v>46190.70821390046</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I50" s="5">
         <v>46174</v>
@@ -4636,13 +4648,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>76</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4652,7 +4664,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B51" s="8">
         <v>46181.60909384259</v>
@@ -4664,16 +4676,16 @@
         <v>46190.7082228125</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I51" s="8">
         <v>46174</v>
@@ -4691,13 +4703,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>76</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4707,7 +4719,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B52" s="5">
         <v>46181.61221741898</v>
@@ -4719,16 +4731,16 @@
         <v>46190.708227337964</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I52" s="5">
         <v>46174</v>
@@ -4746,13 +4758,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>76</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4762,7 +4774,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B53" s="8">
         <v>46181.612357199076</v>
@@ -4774,16 +4786,16 @@
         <v>46190.708233321755</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I53" s="8">
         <v>46174</v>
@@ -4801,13 +4813,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>76</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -4817,7 +4829,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B54" s="5">
         <v>46181.609098182875</v>
@@ -4829,16 +4841,16 @@
         <v>46197.71584820602</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I54" s="5">
         <v>46227</v>
@@ -4856,13 +4868,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q54" s="5">
         <v>46227</v>
@@ -4882,7 +4894,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B55" s="8">
         <v>46181.60910252314</v>
@@ -4894,16 +4906,16 @@
         <v>46191.54270819444</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I55" s="8">
         <v>46227</v>
@@ -4921,13 +4933,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4937,7 +4949,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B56" s="5">
         <v>46181.609107951386</v>
@@ -4949,16 +4961,16 @@
         <v>46191.54271703704</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I56" s="5">
         <v>46227</v>
@@ -4976,13 +4988,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4992,7 +5004,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B57" s="8">
         <v>46181.61393570602</v>
@@ -5004,16 +5016,16 @@
         <v>46190.70842170139</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I57" s="8">
         <v>46227</v>
@@ -5031,13 +5043,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5047,7 +5059,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B58" s="5">
         <v>46181.61396929398</v>
@@ -5059,16 +5071,16 @@
         <v>46190.708426550926</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I58" s="5">
         <v>46227</v>
@@ -5086,13 +5098,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5102,7 +5114,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B59" s="8">
         <v>46181.60911329861</v>
@@ -5120,10 +5132,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I59" s="8">
         <v>46247</v>
@@ -5141,13 +5153,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q59" s="8">
         <v>46247</v>
@@ -5167,7 +5179,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B60" s="5">
         <v>46181.60912350695</v>
@@ -5179,16 +5191,16 @@
         <v>46191.54536050926</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I60" s="6"/>
       <c r="J60" s="5">
@@ -5207,7 +5219,7 @@
         <v>95</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>95</v>
@@ -5220,7 +5232,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B61" s="8">
         <v>46181.60912782408</v>
@@ -5232,16 +5244,16 @@
         <v>46191.54537386574</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I61" s="9"/>
       <c r="J61" s="8">
@@ -5260,7 +5272,7 @@
         <v>95</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>95</v>
@@ -5273,7 +5285,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B62" s="5">
         <v>46181.614119606485</v>
@@ -5285,16 +5297,16 @@
         <v>46190.721725358795</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I62" s="6"/>
       <c r="J62" s="5">
@@ -5313,7 +5325,7 @@
         <v>95</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5326,7 +5338,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B63" s="8">
         <v>46181.61419627315</v>
@@ -5338,16 +5350,16 @@
         <v>46190.7217299537</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I63" s="9"/>
       <c r="J63" s="8">
@@ -5366,7 +5378,7 @@
         <v>95</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5379,7 +5391,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B64" s="5">
         <v>46181.60913207176</v>
@@ -5389,16 +5401,16 @@
         <v>46182.633118067126</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I64" s="5">
         <v>46322</v>
@@ -5416,10 +5428,10 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>26</v>
@@ -5442,7 +5454,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B65" s="8">
         <v>46181.609135833336</v>
@@ -5452,16 +5464,16 @@
         <v>46182.63311847222</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I65" s="8">
         <v>46322</v>
@@ -5479,13 +5491,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5495,7 +5507,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B66" s="5">
         <v>46181.614311909725</v>
@@ -5505,16 +5517,16 @@
         <v>46182.63311923611</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I66" s="5">
         <v>46322</v>
@@ -5532,13 +5544,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5548,7 +5560,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B67" s="8">
         <v>46181.60918671296</v>
@@ -5558,7 +5570,7 @@
         <v>46181.77983537037</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>25</v>
@@ -5582,7 +5594,7 @@
         <v>26</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>26</v>
@@ -5595,26 +5607,26 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B68" s="5">
         <v>46181.609196087964</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46182.63576145833</v>
+        <v>46205.61258912037</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I68" s="5">
         <v>46252</v>
@@ -5632,13 +5644,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q68" s="5">
         <v>46252</v>
@@ -5652,13 +5664,13 @@
       <c r="T68" s="6">
         <v>0</v>
       </c>
-      <c r="U68" s="11" t="s">
-        <v>57</v>
+      <c r="U68" s="12" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B69" s="8">
         <v>46181.609201921296</v>
@@ -5668,16 +5680,16 @@
         <v>46182.63583637732</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I69" s="8">
         <v>46254</v>
@@ -5695,13 +5707,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q69" s="8">
         <v>46254</v>
@@ -5721,7 +5733,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B70" s="5">
         <v>46181.60920746528</v>
@@ -5731,16 +5743,16 @@
         <v>46199.572346076384</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I70" s="5">
         <v>46252</v>
@@ -5758,13 +5770,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q70" s="5">
         <v>46252</v>
@@ -5779,7 +5791,7 @@
         <v>0</v>
       </c>
       <c r="U70" s="12" t="s">
-        <v>228</v>
+        <v>120</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -5800,10 +5812,10 @@
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I71" s="8">
         <v>46254</v>
@@ -5821,10 +5833,10 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>231</v>
@@ -5854,7 +5866,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46182.63575501158</v>
+        <v>46205.612896701394</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>233</v>
@@ -5863,10 +5875,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I72" s="5">
         <v>46252</v>
@@ -5884,10 +5896,10 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>234</v>
@@ -5904,8 +5916,8 @@
       <c r="T72" s="6">
         <v>0</v>
       </c>
-      <c r="U72" s="11" t="s">
-        <v>57</v>
+      <c r="U72" s="12" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -5926,10 +5938,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I73" s="8">
         <v>46254</v>
@@ -5947,7 +5959,7 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O73" s="9" t="s">
         <v>233</v>
@@ -6093,7 +6105,7 @@
         <v>46204.88313940972</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6146,7 +6158,7 @@
         <v>46182.63598342593</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
@@ -6179,7 +6191,7 @@
         <v>249</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
@@ -6199,7 +6211,7 @@
         <v>46182.63598072917</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6252,7 +6264,7 @@
         <v>46182.63597787037</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
@@ -6305,7 +6317,7 @@
         <v>46182.635973807875</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6421,7 +6433,7 @@
         <v>46191.54540523148</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6474,7 +6486,7 @@
         <v>46191.54540574074</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
@@ -6527,7 +6539,7 @@
         <v>46182.64084413194</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6580,7 +6592,7 @@
         <v>46182.64084086806</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
@@ -6633,7 +6645,7 @@
         <v>46182.6408357176</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6692,10 +6704,10 @@
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I87" s="8">
         <v>46289</v>
@@ -6749,16 +6761,16 @@
         <v>46191.545403842596</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I88" s="5">
         <v>46289</v>
@@ -6802,16 +6814,16 @@
         <v>46191.545404212964</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I89" s="8">
         <v>46289</v>
@@ -6861,10 +6873,10 @@
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I90" s="5">
         <v>46289</v>
@@ -6885,10 +6897,10 @@
         <v>268</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6914,10 +6926,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I91" s="8">
         <v>46289</v>
@@ -6938,10 +6950,10 @@
         <v>268</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -6967,10 +6979,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I92" s="5">
         <v>46289</v>
@@ -6991,7 +7003,7 @@
         <v>268</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>276</v>
@@ -7014,7 +7026,7 @@
         <v>46182.567648321754</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>25</v>
@@ -7067,10 +7079,10 @@
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I94" s="5">
         <v>46182</v>
@@ -7088,7 +7100,7 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>26</v>
@@ -7103,13 +7115,13 @@
         <v>46183</v>
       </c>
       <c r="S94" s="11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="T94" s="6">
         <v>0</v>
       </c>
       <c r="U94" s="12" t="s">
-        <v>228</v>
+        <v>120</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -7130,10 +7142,10 @@
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I95" s="8">
         <v>46290</v>
@@ -7151,7 +7163,7 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O95" s="9" t="s">
         <v>26</v>
@@ -7172,7 +7184,7 @@
         <v>0</v>
       </c>
       <c r="U95" s="12" t="s">
-        <v>228</v>
+        <v>120</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
@@ -7193,10 +7205,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I96" s="5">
         <v>46226</v>
@@ -7214,7 +7226,7 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>26</v>
@@ -7235,7 +7247,7 @@
         <v>0</v>
       </c>
       <c r="U96" s="12" t="s">
-        <v>228</v>
+        <v>120</v>
       </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
@@ -7256,10 +7268,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I97" s="8">
         <v>46293</v>
@@ -7277,10 +7289,10 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P97" s="9" t="s">
         <v>288</v>
@@ -7298,7 +7310,7 @@
         <v>0</v>
       </c>
       <c r="U97" s="12" t="s">
-        <v>228</v>
+        <v>120</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
@@ -7319,10 +7331,10 @@
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I98" s="5">
         <v>46226</v>
@@ -7340,10 +7352,10 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>55</v>
@@ -7486,7 +7498,7 @@
         <v>46182.64119599537</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7539,7 +7551,7 @@
         <v>46182.64119222222</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7569,7 +7581,7 @@
         <v>294</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>299</v>
@@ -7624,7 +7636,7 @@
         <v>291</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P103" s="9" t="s">
         <v>291</v>
@@ -7659,7 +7671,7 @@
         <v>46204.89505523148</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7714,7 +7726,7 @@
         <v>46204.89514483797</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -7797,7 +7809,7 @@
         <v>291</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>291</v>
@@ -7830,7 +7842,7 @@
         <v>46204.89506170139</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -7883,7 +7895,7 @@
         <v>46182.64140446759</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7966,7 +7978,7 @@
         <v>291</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P109" s="9" t="s">
         <v>291</v>
@@ -7999,7 +8011,7 @@
         <v>46191.54540483796</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8052,7 +8064,7 @@
         <v>46182.64151664352</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8135,7 +8147,7 @@
         <v>291</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>291</v>
@@ -8168,7 +8180,7 @@
         <v>46182.641623125004</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8198,7 +8210,7 @@
         <v>322</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P113" s="9" t="s">
         <v>324</v>
@@ -8221,7 +8233,7 @@
         <v>46182.64161924769</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8251,10 +8263,10 @@
         <v>322</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8304,7 +8316,7 @@
         <v>291</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P115" s="9" t="s">
         <v>328</v>
@@ -8337,7 +8349,7 @@
         <v>46182.64173178241</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8367,7 +8379,7 @@
         <v>327</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>330</v>
@@ -8390,7 +8402,7 @@
         <v>46182.64172883102</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
@@ -8420,7 +8432,7 @@
         <v>327</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P117" s="9" t="s">
         <v>26</v>
@@ -8553,7 +8565,7 @@
         <v>46182.641845254635</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8583,7 +8595,7 @@
         <v>336</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>341</v>
@@ -8606,7 +8618,7 @@
         <v>46182.64184081019</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -8636,10 +8648,10 @@
         <v>336</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8765,7 +8777,7 @@
         <v>46182.64182482639</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8798,7 +8810,7 @@
         <v>262</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8818,7 +8830,7 @@
         <v>46182.64182413195</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -8851,7 +8863,7 @@
         <v>264</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -8904,7 +8916,7 @@
         <v>266</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8954,7 +8966,7 @@
         <v>333</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P127" s="9" t="s">
         <v>333</v>
@@ -8987,7 +8999,7 @@
         <v>46182.641973854166</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9017,7 +9029,7 @@
         <v>349</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>351</v>
@@ -9040,7 +9052,7 @@
         <v>46182.64197085648</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
@@ -9070,10 +9082,10 @@
         <v>349</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q129" s="9"/>
       <c r="R129" s="9"/>
@@ -9199,7 +9211,7 @@
         <v>46182.64196105324</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9229,10 +9241,10 @@
         <v>349</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9252,7 +9264,7 @@
         <v>46182.64195453704</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
@@ -9282,10 +9294,10 @@
         <v>349</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9305,7 +9317,7 @@
         <v>46182.64195372685</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9338,7 +9350,7 @@
         <v>276</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9388,7 +9400,7 @@
         <v>333</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P135" s="9" t="s">
         <v>333</v>
@@ -9421,7 +9433,7 @@
         <v>46182.82945300926</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9451,7 +9463,7 @@
         <v>359</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P136" s="6" t="s">
         <v>361</v>
@@ -9474,7 +9486,7 @@
         <v>46182.829453784725</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
@@ -9504,10 +9516,10 @@
         <v>359</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q137" s="9"/>
       <c r="R137" s="9"/>
@@ -9633,7 +9645,7 @@
         <v>46182.8294564699</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9663,10 +9675,10 @@
         <v>359</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9686,7 +9698,7 @@
         <v>46182.82945721065</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
@@ -9716,10 +9728,10 @@
         <v>359</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -9739,7 +9751,7 @@
         <v>46182.82945796296</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -9769,10 +9781,10 @@
         <v>359</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9822,7 +9834,7 @@
         <v>333</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P143" s="9" t="s">
         <v>370</v>
@@ -9855,7 +9867,7 @@
         <v>46182.8294527199</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -9885,7 +9897,7 @@
         <v>369</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P144" s="6" t="s">
         <v>369</v>
@@ -9908,7 +9920,7 @@
         <v>46182.829451909725</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
@@ -9938,7 +9950,7 @@
         <v>369</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P145" s="9" t="s">
         <v>26</v>
@@ -10067,7 +10079,7 @@
         <v>46182.82945207176</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
@@ -10097,7 +10109,7 @@
         <v>369</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P148" s="6" t="s">
         <v>26</v>
@@ -10120,7 +10132,7 @@
         <v>46182.829452025464</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
@@ -10150,7 +10162,7 @@
         <v>369</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P149" s="9" t="s">
         <v>26</v>
@@ -10173,7 +10185,7 @@
         <v>46182.829452418984</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
@@ -10203,7 +10215,7 @@
         <v>369</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P150" s="6" t="s">
         <v>26</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -6039,7 +6039,7 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46204.88302877315</v>
+        <v>46205.887926446754</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>240</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -2948,7 +2948,7 @@
         <v>46196.658568541665</v>
       </c>
       <c r="D22" s="5">
-        <v>46196.65858296296</v>
+        <v>46206.551626817134</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>92</v>
@@ -3013,7 +3013,7 @@
         <v>46196.65883074074</v>
       </c>
       <c r="D23" s="8">
-        <v>46196.658845625</v>
+        <v>46206.5519203588</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>98</v>
@@ -3078,7 +3078,7 @@
         <v>46204.888766944445</v>
       </c>
       <c r="D24" s="5">
-        <v>46204.888792060185</v>
+        <v>46206.5521100926</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>101</v>
@@ -3143,7 +3143,7 @@
         <v>46197.64511049769</v>
       </c>
       <c r="D25" s="8">
-        <v>46197.64512664352</v>
+        <v>46206.552334583335</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>104</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -1864,13 +1864,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46181.60862950231</v>
+        <v>46181.44196283565</v>
       </c>
       <c r="C4" s="5">
-        <v>46190.67646162037</v>
+        <v>46190.5097949537</v>
       </c>
       <c r="D4" s="5">
-        <v>46191.77859822917</v>
+        <v>46191.6119315625</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1913,13 +1913,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46181.60880893518</v>
+        <v>46181.44214226852</v>
       </c>
       <c r="C5" s="8">
-        <v>46190.675863854165</v>
+        <v>46190.5091971875</v>
       </c>
       <c r="D5" s="8">
-        <v>46190.676329525464</v>
+        <v>46190.50966285879</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1976,13 +1976,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46181.60881340278</v>
+        <v>46181.44214673611</v>
       </c>
       <c r="C6" s="5">
-        <v>46190.67626129629</v>
+        <v>46190.50959462963</v>
       </c>
       <c r="D6" s="5">
-        <v>46190.676280844906</v>
+        <v>46190.50961417824</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2039,13 +2039,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="8">
-        <v>46181.60881648149</v>
+        <v>46181.442149814815</v>
       </c>
       <c r="C7" s="8">
-        <v>46190.67642019676</v>
+        <v>46190.50975353009</v>
       </c>
       <c r="D7" s="8">
-        <v>46190.67643417824</v>
+        <v>46190.509767511576</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>37</v>
@@ -2102,13 +2102,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46181.60882040509</v>
+        <v>46181.442153738426</v>
       </c>
       <c r="C8" s="5">
-        <v>46190.67644660879</v>
+        <v>46190.509779942135</v>
       </c>
       <c r="D8" s="5">
-        <v>46190.67646199074</v>
+        <v>46190.50979532408</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2165,11 +2165,11 @@
         <v>43</v>
       </c>
       <c r="B9" s="8">
-        <v>46181.60863523148</v>
+        <v>46181.44196856482</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="8">
-        <v>46190.6778103588</v>
+        <v>46190.51114369213</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>44</v>
@@ -2212,13 +2212,13 @@
         <v>46</v>
       </c>
       <c r="B10" s="5">
-        <v>46181.608824131945</v>
+        <v>46181.44215746528</v>
       </c>
       <c r="C10" s="5">
-        <v>46190.67780464121</v>
+        <v>46190.511137974536</v>
       </c>
       <c r="D10" s="5">
-        <v>46190.67781991899</v>
+        <v>46190.511153252315</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -2277,11 +2277,11 @@
         <v>51</v>
       </c>
       <c r="B11" s="8">
-        <v>46181.60882959491</v>
+        <v>46181.442162928244</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="8">
-        <v>46182.62580337963</v>
+        <v>46182.45913671296</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>52</v>
@@ -2340,11 +2340,11 @@
         <v>58</v>
       </c>
       <c r="B12" s="5">
-        <v>46181.608834976854</v>
+        <v>46181.44216831018</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46182.62589634259</v>
+        <v>46182.45922967592</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>59</v>
@@ -2393,11 +2393,11 @@
         <v>62</v>
       </c>
       <c r="B13" s="8">
-        <v>46181.61813184028</v>
+        <v>46181.45146517361</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46182.625892881944</v>
+        <v>46182.45922621527</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>59</v>
@@ -2446,13 +2446,13 @@
         <v>64</v>
       </c>
       <c r="B14" s="5">
-        <v>46181.60864021991</v>
+        <v>46181.44197355324</v>
       </c>
       <c r="C14" s="5">
-        <v>46204.9032446412</v>
+        <v>46204.73657797454</v>
       </c>
       <c r="D14" s="5">
-        <v>46204.903260949075</v>
+        <v>46204.73659428241</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>65</v>
@@ -2499,13 +2499,13 @@
         <v>67</v>
       </c>
       <c r="B15" s="8">
-        <v>46181.60883864583</v>
+        <v>46181.44217197917</v>
       </c>
       <c r="C15" s="8">
-        <v>46190.67744403935</v>
+        <v>46190.510777372685</v>
       </c>
       <c r="D15" s="8">
-        <v>46191.67892994213</v>
+        <v>46191.512263275465</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>68</v>
@@ -2564,13 +2564,13 @@
         <v>71</v>
       </c>
       <c r="B16" s="5">
-        <v>46181.60884395833</v>
+        <v>46181.44217729167</v>
       </c>
       <c r="C16" s="5">
-        <v>46190.67745200232</v>
+        <v>46190.510785335646</v>
       </c>
       <c r="D16" s="5">
-        <v>46191.67892980324</v>
+        <v>46191.512263136574</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>72</v>
@@ -2629,13 +2629,13 @@
         <v>75</v>
       </c>
       <c r="B17" s="8">
-        <v>46181.608850046294</v>
+        <v>46181.44218337963</v>
       </c>
       <c r="C17" s="8">
-        <v>46190.67745870371</v>
+        <v>46190.510792037036</v>
       </c>
       <c r="D17" s="8">
-        <v>46191.67892980324</v>
+        <v>46191.512263136574</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>76</v>
@@ -2694,13 +2694,13 @@
         <v>78</v>
       </c>
       <c r="B18" s="5">
-        <v>46181.60864670139</v>
+        <v>46181.441980034724</v>
       </c>
       <c r="C18" s="5">
-        <v>46204.888791840276</v>
+        <v>46204.72212517361</v>
       </c>
       <c r="D18" s="5">
-        <v>46204.88880490741</v>
+        <v>46204.722138240744</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>79</v>
@@ -2747,13 +2747,13 @@
         <v>81</v>
       </c>
       <c r="B19" s="8">
-        <v>46181.608864236114</v>
+        <v>46181.44219756944</v>
       </c>
       <c r="C19" s="8">
-        <v>46190.677672986116</v>
+        <v>46190.511006319444</v>
       </c>
       <c r="D19" s="8">
-        <v>46190.88639424769</v>
+        <v>46190.71972758102</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>82</v>
@@ -2812,13 +2812,13 @@
         <v>84</v>
       </c>
       <c r="B20" s="5">
-        <v>46181.60886979167</v>
+        <v>46181.442203125</v>
       </c>
       <c r="C20" s="5">
-        <v>46190.677678657405</v>
+        <v>46190.51101199074</v>
       </c>
       <c r="D20" s="5">
-        <v>46190.88638454861</v>
+        <v>46190.71971788195</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>85</v>
@@ -2877,13 +2877,13 @@
         <v>87</v>
       </c>
       <c r="B21" s="8">
-        <v>46181.60887520833</v>
+        <v>46181.442208541666</v>
       </c>
       <c r="C21" s="8">
-        <v>46197.42280901621</v>
+        <v>46197.256142349535</v>
       </c>
       <c r="D21" s="8">
-        <v>46197.422811446755</v>
+        <v>46197.25614478009</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>88</v>
@@ -2942,13 +2942,13 @@
         <v>91</v>
       </c>
       <c r="B22" s="5">
-        <v>46181.60888054398</v>
+        <v>46181.442213877315</v>
       </c>
       <c r="C22" s="5">
-        <v>46196.658568541665</v>
+        <v>46196.491901875</v>
       </c>
       <c r="D22" s="5">
-        <v>46206.551626817134</v>
+        <v>46206.38496015046</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>92</v>
@@ -3007,13 +3007,13 @@
         <v>97</v>
       </c>
       <c r="B23" s="8">
-        <v>46181.60888559028</v>
+        <v>46181.44221892361</v>
       </c>
       <c r="C23" s="8">
-        <v>46196.65883074074</v>
+        <v>46196.49216407408</v>
       </c>
       <c r="D23" s="8">
-        <v>46206.5519203588</v>
+        <v>46206.38525369213</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>98</v>
@@ -3072,13 +3072,13 @@
         <v>100</v>
       </c>
       <c r="B24" s="5">
-        <v>46181.60888961806</v>
+        <v>46181.44222295139</v>
       </c>
       <c r="C24" s="5">
-        <v>46204.888766944445</v>
+        <v>46204.72210027778</v>
       </c>
       <c r="D24" s="5">
-        <v>46206.5521100926</v>
+        <v>46206.38544342593</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>101</v>
@@ -3137,13 +3137,13 @@
         <v>103</v>
       </c>
       <c r="B25" s="8">
-        <v>46181.6088934375</v>
+        <v>46181.44222677083</v>
       </c>
       <c r="C25" s="8">
-        <v>46197.64511049769</v>
+        <v>46197.478443831016</v>
       </c>
       <c r="D25" s="8">
-        <v>46206.552334583335</v>
+        <v>46206.385667916664</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>104</v>
@@ -3202,13 +3202,13 @@
         <v>106</v>
       </c>
       <c r="B26" s="5">
-        <v>46181.608897638886</v>
+        <v>46181.44223097222</v>
       </c>
       <c r="C26" s="5">
-        <v>46190.67785231481</v>
+        <v>46190.51118564815</v>
       </c>
       <c r="D26" s="5">
-        <v>46190.67787061342</v>
+        <v>46190.511203946764</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>107</v>
@@ -3267,13 +3267,13 @@
         <v>109</v>
       </c>
       <c r="B27" s="8">
-        <v>46190.88204489583</v>
+        <v>46190.71537822917</v>
       </c>
       <c r="C27" s="8">
-        <v>46197.42407642362</v>
+        <v>46197.257409756945</v>
       </c>
       <c r="D27" s="8">
-        <v>46197.424089050925</v>
+        <v>46197.25742238426</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>110</v>
@@ -3320,13 +3320,13 @@
         <v>111</v>
       </c>
       <c r="B28" s="5">
-        <v>46190.88321909722</v>
+        <v>46190.71655243056</v>
       </c>
       <c r="C28" s="5">
-        <v>46197.42354282408</v>
+        <v>46197.25687615741</v>
       </c>
       <c r="D28" s="5">
-        <v>46197.42355928241</v>
+        <v>46197.25689261574</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>112</v>
@@ -3385,13 +3385,13 @@
         <v>113</v>
       </c>
       <c r="B29" s="8">
-        <v>46190.88327185185</v>
+        <v>46190.71660518518</v>
       </c>
       <c r="C29" s="8">
-        <v>46197.42396493055</v>
+        <v>46197.25729826389</v>
       </c>
       <c r="D29" s="8">
-        <v>46197.423981597225</v>
+        <v>46197.25731493055</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>114</v>
@@ -3450,13 +3450,13 @@
         <v>115</v>
       </c>
       <c r="B30" s="5">
-        <v>46190.88332659722</v>
+        <v>46190.71665993056</v>
       </c>
       <c r="C30" s="5">
-        <v>46197.42406122685</v>
+        <v>46197.25739456018</v>
       </c>
       <c r="D30" s="5">
-        <v>46197.42407648148</v>
+        <v>46197.25740981482</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>116</v>
@@ -3515,11 +3515,11 @@
         <v>117</v>
       </c>
       <c r="B31" s="8">
-        <v>46181.608652256946</v>
+        <v>46181.44198559028</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46205.61719612269</v>
+        <v>46205.45052945602</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>118</v>
@@ -3564,11 +3564,11 @@
         <v>121</v>
       </c>
       <c r="B32" s="5">
-        <v>46181.60900793981</v>
+        <v>46181.44234127315</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46195.6859309838</v>
+        <v>46195.51926431713</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>122</v>
@@ -3627,13 +3627,13 @@
         <v>126</v>
       </c>
       <c r="B33" s="8">
-        <v>46181.60901165509</v>
+        <v>46181.44234498843</v>
       </c>
       <c r="C33" s="8">
-        <v>46195.685925451384</v>
+        <v>46195.51925878473</v>
       </c>
       <c r="D33" s="8">
-        <v>46195.68592747685</v>
+        <v>46195.519260810186</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>108</v>
@@ -3682,11 +3682,11 @@
         <v>128</v>
       </c>
       <c r="B34" s="5">
-        <v>46181.60901612269</v>
+        <v>46181.44234945602</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46195.685932430555</v>
+        <v>46195.51926576388</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>129</v>
@@ -3735,13 +3735,13 @@
         <v>131</v>
       </c>
       <c r="B35" s="8">
-        <v>46181.60902011574</v>
+        <v>46181.44235344908</v>
       </c>
       <c r="C35" s="8">
-        <v>46205.61719040509</v>
+        <v>46205.45052373843</v>
       </c>
       <c r="D35" s="8">
-        <v>46205.61719211805</v>
+        <v>46205.45052545139</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>119</v>
@@ -3800,13 +3800,13 @@
         <v>135</v>
       </c>
       <c r="B36" s="5">
-        <v>46181.60902488426</v>
+        <v>46181.442358217595</v>
       </c>
       <c r="C36" s="5">
-        <v>46199.57115320602</v>
+        <v>46199.40448653935</v>
       </c>
       <c r="D36" s="5">
-        <v>46199.57115532407</v>
+        <v>46199.40448865741</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
@@ -3861,13 +3861,13 @@
         <v>138</v>
       </c>
       <c r="B37" s="8">
-        <v>46181.609029803236</v>
+        <v>46181.44236313658</v>
       </c>
       <c r="C37" s="8">
-        <v>46205.612570185185</v>
+        <v>46205.445903518514</v>
       </c>
       <c r="D37" s="8">
-        <v>46205.61257221065</v>
+        <v>46205.44590554398</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>139</v>
@@ -3922,13 +3922,13 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46181.60903511574</v>
+        <v>46181.442368449076</v>
       </c>
       <c r="C38" s="5">
-        <v>46199.57234078704</v>
+        <v>46199.40567412037</v>
       </c>
       <c r="D38" s="5">
-        <v>46199.572352546296</v>
+        <v>46199.405685879625</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -3987,13 +3987,13 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46181.60903861111</v>
+        <v>46181.442371944446</v>
       </c>
       <c r="C39" s="8">
-        <v>46199.57221719908</v>
+        <v>46199.40555053241</v>
       </c>
       <c r="D39" s="8">
-        <v>46199.57256810185</v>
+        <v>46199.40590143518</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>99</v>
@@ -4042,13 +4042,13 @@
         <v>146</v>
       </c>
       <c r="B40" s="5">
-        <v>46181.609042951386</v>
+        <v>46181.44237628472</v>
       </c>
       <c r="C40" s="5">
-        <v>46199.57232475694</v>
+        <v>46199.405658090276</v>
       </c>
       <c r="D40" s="5">
-        <v>46199.57232634259</v>
+        <v>46199.405659675926</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>147</v>
@@ -4097,13 +4097,13 @@
         <v>149</v>
       </c>
       <c r="B41" s="8">
-        <v>46181.609047164355</v>
+        <v>46181.44238049768</v>
       </c>
       <c r="C41" s="8">
-        <v>46204.67472811343</v>
+        <v>46204.50806144676</v>
       </c>
       <c r="D41" s="8">
-        <v>46204.6747446875</v>
+        <v>46204.50807802084</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>150</v>
@@ -4162,13 +4162,13 @@
         <v>154</v>
       </c>
       <c r="B42" s="5">
-        <v>46181.60905075232</v>
+        <v>46181.44238408565</v>
       </c>
       <c r="C42" s="5">
-        <v>46204.67332877315</v>
+        <v>46204.506662106476</v>
       </c>
       <c r="D42" s="5">
-        <v>46204.67396857639</v>
+        <v>46204.50730190972</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>105</v>
@@ -4217,13 +4217,13 @@
         <v>156</v>
       </c>
       <c r="B43" s="8">
-        <v>46181.60905546296</v>
+        <v>46181.44238879629</v>
       </c>
       <c r="C43" s="8">
-        <v>46204.67337491898</v>
+        <v>46204.50670825232</v>
       </c>
       <c r="D43" s="8">
-        <v>46204.67391837963</v>
+        <v>46204.50725171296</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>157</v>
@@ -4272,11 +4272,11 @@
         <v>159</v>
       </c>
       <c r="B44" s="5">
-        <v>46181.60906018519</v>
+        <v>46181.44239351852</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46204.67384744213</v>
+        <v>46204.50718077546</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>160</v>
@@ -4325,13 +4325,13 @@
         <v>163</v>
       </c>
       <c r="B45" s="8">
-        <v>46181.609063310185</v>
+        <v>46181.44239664351</v>
       </c>
       <c r="C45" s="8">
-        <v>46205.61289446759</v>
+        <v>46205.44622780093</v>
       </c>
       <c r="D45" s="8">
-        <v>46205.61290721065</v>
+        <v>46205.446240543984</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>164</v>
@@ -4390,13 +4390,13 @@
         <v>166</v>
       </c>
       <c r="B46" s="5">
-        <v>46181.60906703703</v>
+        <v>46181.442400370375</v>
       </c>
       <c r="C46" s="5">
-        <v>46205.6128353588</v>
+        <v>46205.44616869213</v>
       </c>
       <c r="D46" s="5">
-        <v>46205.61283694445</v>
+        <v>46205.44617027778</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>102</v>
@@ -4445,13 +4445,13 @@
         <v>168</v>
       </c>
       <c r="B47" s="8">
-        <v>46181.60907681713</v>
+        <v>46181.44241015046</v>
       </c>
       <c r="C47" s="8">
-        <v>46205.612877789354</v>
+        <v>46205.44621112269</v>
       </c>
       <c r="D47" s="8">
-        <v>46205.612879328706</v>
+        <v>46205.446212662035</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>169</v>
@@ -4500,11 +4500,11 @@
         <v>171</v>
       </c>
       <c r="B48" s="5">
-        <v>46181.6090815625</v>
+        <v>46181.442414895835</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46204.9033168287</v>
+        <v>46204.73665016204</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>172</v>
@@ -4547,13 +4547,13 @@
         <v>174</v>
       </c>
       <c r="B49" s="8">
-        <v>46181.60908480324</v>
+        <v>46181.442418136576</v>
       </c>
       <c r="C49" s="8">
-        <v>46190.708245752314</v>
+        <v>46190.54157908565</v>
       </c>
       <c r="D49" s="8">
-        <v>46197.7158150926</v>
+        <v>46197.549148425926</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>175</v>
@@ -4612,13 +4612,13 @@
         <v>180</v>
       </c>
       <c r="B50" s="5">
-        <v>46181.60908915509</v>
+        <v>46181.44242248843</v>
       </c>
       <c r="C50" s="5">
-        <v>46190.70821236111</v>
+        <v>46190.54154569445</v>
       </c>
       <c r="D50" s="5">
-        <v>46190.70821390046</v>
+        <v>46190.54154723379</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>181</v>
@@ -4667,13 +4667,13 @@
         <v>185</v>
       </c>
       <c r="B51" s="8">
-        <v>46181.60909384259</v>
+        <v>46181.44242717593</v>
       </c>
       <c r="C51" s="8">
-        <v>46190.70822138889</v>
+        <v>46190.54155472222</v>
       </c>
       <c r="D51" s="8">
-        <v>46190.7082228125</v>
+        <v>46190.541556145836</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>186</v>
@@ -4722,13 +4722,13 @@
         <v>188</v>
       </c>
       <c r="B52" s="5">
-        <v>46181.61221741898</v>
+        <v>46181.445550752316</v>
       </c>
       <c r="C52" s="5">
-        <v>46190.70822601852</v>
+        <v>46190.541559351856</v>
       </c>
       <c r="D52" s="5">
-        <v>46190.708227337964</v>
+        <v>46190.54156067129</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>189</v>
@@ -4777,13 +4777,13 @@
         <v>190</v>
       </c>
       <c r="B53" s="8">
-        <v>46181.612357199076</v>
+        <v>46181.445690532404</v>
       </c>
       <c r="C53" s="8">
-        <v>46190.70823167824</v>
+        <v>46190.541565011576</v>
       </c>
       <c r="D53" s="8">
-        <v>46190.708233321755</v>
+        <v>46190.5415666551</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>191</v>
@@ -4832,13 +4832,13 @@
         <v>192</v>
       </c>
       <c r="B54" s="5">
-        <v>46181.609098182875</v>
+        <v>46181.4424315162</v>
       </c>
       <c r="C54" s="5">
-        <v>46191.54272982639</v>
+        <v>46191.376063159725</v>
       </c>
       <c r="D54" s="5">
-        <v>46197.71584820602</v>
+        <v>46197.54918153935</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>193</v>
@@ -4897,13 +4897,13 @@
         <v>194</v>
       </c>
       <c r="B55" s="8">
-        <v>46181.60910252314</v>
+        <v>46181.44243585649</v>
       </c>
       <c r="C55" s="8">
-        <v>46191.54270648149</v>
+        <v>46191.376039814815</v>
       </c>
       <c r="D55" s="8">
-        <v>46191.54270819444</v>
+        <v>46191.37604152778</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>181</v>
@@ -4952,13 +4952,13 @@
         <v>196</v>
       </c>
       <c r="B56" s="5">
-        <v>46181.609107951386</v>
+        <v>46181.44244128472</v>
       </c>
       <c r="C56" s="5">
-        <v>46191.542715625</v>
+        <v>46191.37604895834</v>
       </c>
       <c r="D56" s="5">
-        <v>46191.54271703704</v>
+        <v>46191.37605037037</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>186</v>
@@ -5007,13 +5007,13 @@
         <v>198</v>
       </c>
       <c r="B57" s="8">
-        <v>46181.61393570602</v>
+        <v>46181.44726903935</v>
       </c>
       <c r="C57" s="8">
-        <v>46190.70842026621</v>
+        <v>46190.54175359954</v>
       </c>
       <c r="D57" s="8">
-        <v>46190.70842170139</v>
+        <v>46190.54175503472</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>189</v>
@@ -5062,13 +5062,13 @@
         <v>199</v>
       </c>
       <c r="B58" s="5">
-        <v>46181.61396929398</v>
+        <v>46181.44730262732</v>
       </c>
       <c r="C58" s="5">
-        <v>46190.70842520833</v>
+        <v>46190.541758541665</v>
       </c>
       <c r="D58" s="5">
-        <v>46190.708426550926</v>
+        <v>46190.54175988426</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>191</v>
@@ -5117,13 +5117,13 @@
         <v>200</v>
       </c>
       <c r="B59" s="8">
-        <v>46181.60911329861</v>
+        <v>46181.44244663195</v>
       </c>
       <c r="C59" s="8">
-        <v>46191.54538693287</v>
+        <v>46191.378720266206</v>
       </c>
       <c r="D59" s="8">
-        <v>46191.54539826389</v>
+        <v>46191.37873159722</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>95</v>
@@ -5182,13 +5182,13 @@
         <v>202</v>
       </c>
       <c r="B60" s="5">
-        <v>46181.60912350695</v>
+        <v>46181.442456840276</v>
       </c>
       <c r="C60" s="5">
-        <v>46191.54535901621</v>
+        <v>46191.378692349535</v>
       </c>
       <c r="D60" s="5">
-        <v>46191.54536050926</v>
+        <v>46191.37869384259</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>181</v>
@@ -5235,13 +5235,13 @@
         <v>203</v>
       </c>
       <c r="B61" s="8">
-        <v>46181.60912782408</v>
+        <v>46181.44246115741</v>
       </c>
       <c r="C61" s="8">
-        <v>46191.54537241899</v>
+        <v>46191.378705752315</v>
       </c>
       <c r="D61" s="8">
-        <v>46191.54537386574</v>
+        <v>46191.378707199074</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>186</v>
@@ -5288,13 +5288,13 @@
         <v>204</v>
       </c>
       <c r="B62" s="5">
-        <v>46181.614119606485</v>
+        <v>46181.447452939814</v>
       </c>
       <c r="C62" s="5">
-        <v>46190.72172383102</v>
+        <v>46190.555057164354</v>
       </c>
       <c r="D62" s="5">
-        <v>46190.721725358795</v>
+        <v>46190.55505869213</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>189</v>
@@ -5341,13 +5341,13 @@
         <v>205</v>
       </c>
       <c r="B63" s="8">
-        <v>46181.61419627315</v>
+        <v>46181.44752960648</v>
       </c>
       <c r="C63" s="8">
-        <v>46190.72172868055</v>
+        <v>46190.55506201389</v>
       </c>
       <c r="D63" s="8">
-        <v>46190.7217299537</v>
+        <v>46190.555063287036</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>191</v>
@@ -5394,11 +5394,11 @@
         <v>206</v>
       </c>
       <c r="B64" s="5">
-        <v>46181.60913207176</v>
+        <v>46181.442465405096</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46182.633118067126</v>
+        <v>46182.46645140046</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>207</v>
@@ -5457,11 +5457,11 @@
         <v>210</v>
       </c>
       <c r="B65" s="8">
-        <v>46181.609135833336</v>
+        <v>46181.442469166665</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46182.63311847222</v>
+        <v>46182.46645180555</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>181</v>
@@ -5510,11 +5510,11 @@
         <v>212</v>
       </c>
       <c r="B66" s="5">
-        <v>46181.614311909725</v>
+        <v>46181.44764524305</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46182.63311923611</v>
+        <v>46182.466452569446</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>213</v>
@@ -5563,11 +5563,11 @@
         <v>214</v>
       </c>
       <c r="B67" s="8">
-        <v>46181.60918671296</v>
+        <v>46181.4425200463</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46181.77983537037</v>
+        <v>46181.613168703705</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>215</v>
@@ -5610,11 +5610,11 @@
         <v>217</v>
       </c>
       <c r="B68" s="5">
-        <v>46181.609196087964</v>
+        <v>46181.4425294213</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46205.61258912037</v>
+        <v>46205.4459224537</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>218</v>
@@ -5673,11 +5673,11 @@
         <v>222</v>
       </c>
       <c r="B69" s="8">
-        <v>46181.609201921296</v>
+        <v>46181.44253525463</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46182.63583637732</v>
+        <v>46182.46916971065</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>223</v>
@@ -5736,11 +5736,11 @@
         <v>226</v>
       </c>
       <c r="B70" s="5">
-        <v>46181.60920746528</v>
+        <v>46181.44254079861</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46199.572346076384</v>
+        <v>46199.40567940973</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>227</v>
@@ -5799,11 +5799,11 @@
         <v>229</v>
       </c>
       <c r="B71" s="8">
-        <v>46181.609212870375</v>
+        <v>46181.4425462037</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46182.63583289352</v>
+        <v>46182.46916622685</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>230</v>
@@ -5862,11 +5862,11 @@
         <v>232</v>
       </c>
       <c r="B72" s="5">
-        <v>46181.60921715278</v>
+        <v>46181.442550486114</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46205.612896701394</v>
+        <v>46205.44623003472</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>233</v>
@@ -5925,11 +5925,11 @@
         <v>235</v>
       </c>
       <c r="B73" s="8">
-        <v>46181.60922180556</v>
+        <v>46181.442555138885</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46182.63582844907</v>
+        <v>46182.46916178241</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>234</v>
@@ -5988,11 +5988,11 @@
         <v>236</v>
       </c>
       <c r="B74" s="5">
-        <v>46181.60922590278</v>
+        <v>46181.44255923611</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46181.782424143516</v>
+        <v>46181.61575747685</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>237</v>
@@ -6035,11 +6035,11 @@
         <v>239</v>
       </c>
       <c r="B75" s="8">
-        <v>46181.60922940972</v>
+        <v>46181.44256274306</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46205.887926446754</v>
+        <v>46205.7212597801</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>240</v>
@@ -6098,11 +6098,11 @@
         <v>245</v>
       </c>
       <c r="B76" s="5">
-        <v>46181.60923553241</v>
+        <v>46181.442568865736</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46204.88313940972</v>
+        <v>46204.71647274306</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>181</v>
@@ -6151,11 +6151,11 @@
         <v>248</v>
       </c>
       <c r="B77" s="8">
-        <v>46181.609241805556</v>
+        <v>46181.44257513889</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46182.63598342593</v>
+        <v>46182.46931675926</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>181</v>
@@ -6204,11 +6204,11 @@
         <v>250</v>
       </c>
       <c r="B78" s="5">
-        <v>46181.6145286574</v>
+        <v>46181.447861990746</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46182.63598072917</v>
+        <v>46182.4693140625</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>186</v>
@@ -6257,11 +6257,11 @@
         <v>251</v>
       </c>
       <c r="B79" s="8">
-        <v>46181.61460722222</v>
+        <v>46181.447940555554</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46182.63597787037</v>
+        <v>46182.469311203706</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>189</v>
@@ -6310,11 +6310,11 @@
         <v>253</v>
       </c>
       <c r="B80" s="5">
-        <v>46181.61464366898</v>
+        <v>46181.44797700232</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46182.635973807875</v>
+        <v>46182.469307141204</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>191</v>
@@ -6363,11 +6363,11 @@
         <v>254</v>
       </c>
       <c r="B81" s="8">
-        <v>46181.609247002314</v>
+        <v>46181.44258033565</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46182.64087873843</v>
+        <v>46182.47421207176</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>255</v>
@@ -6426,11 +6426,11 @@
         <v>257</v>
       </c>
       <c r="B82" s="5">
-        <v>46181.60925648148</v>
+        <v>46181.44258981482</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46191.54540523148</v>
+        <v>46191.37873856482</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>181</v>
@@ -6479,11 +6479,11 @@
         <v>260</v>
       </c>
       <c r="B83" s="8">
-        <v>46181.609262199076</v>
+        <v>46181.44259553241</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46191.54540574074</v>
+        <v>46191.378739074076</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>181</v>
@@ -6532,11 +6532,11 @@
         <v>261</v>
       </c>
       <c r="B84" s="5">
-        <v>46181.61473356481</v>
+        <v>46181.44806689815</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46182.64084413194</v>
+        <v>46182.47417746528</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>186</v>
@@ -6585,11 +6585,11 @@
         <v>263</v>
       </c>
       <c r="B85" s="8">
-        <v>46181.61477212963</v>
+        <v>46181.44810546296</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46182.64084086806</v>
+        <v>46182.47417420139</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>189</v>
@@ -6638,11 +6638,11 @@
         <v>265</v>
       </c>
       <c r="B86" s="5">
-        <v>46181.61484836806</v>
+        <v>46181.44818170139</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46182.6408357176</v>
+        <v>46182.474169050925</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>191</v>
@@ -6691,11 +6691,11 @@
         <v>267</v>
       </c>
       <c r="B87" s="8">
-        <v>46181.60926783565</v>
+        <v>46181.44260116898</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46182.64099746528</v>
+        <v>46182.47433079861</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>268</v>
@@ -6754,11 +6754,11 @@
         <v>269</v>
       </c>
       <c r="B88" s="5">
-        <v>46181.60927226851</v>
+        <v>46181.44260560186</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46191.545403842596</v>
+        <v>46191.378737175924</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>181</v>
@@ -6807,11 +6807,11 @@
         <v>271</v>
       </c>
       <c r="B89" s="8">
-        <v>46181.60927799769</v>
+        <v>46181.44261133102</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46191.545404212964</v>
+        <v>46191.3787375463</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>181</v>
@@ -6860,11 +6860,11 @@
         <v>273</v>
       </c>
       <c r="B90" s="5">
-        <v>46181.614954062505</v>
+        <v>46181.44828739583</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46182.64096971064</v>
+        <v>46182.474303043986</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>262</v>
@@ -6913,11 +6913,11 @@
         <v>274</v>
       </c>
       <c r="B91" s="8">
-        <v>46181.61498993056</v>
+        <v>46181.44832326389</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46182.64096709491</v>
+        <v>46182.474300428235</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>264</v>
@@ -6966,11 +6966,11 @@
         <v>275</v>
       </c>
       <c r="B92" s="5">
-        <v>46181.61502625</v>
+        <v>46181.44835958333</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46182.64096319444</v>
+        <v>46182.47429652778</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>266</v>
@@ -7019,11 +7019,11 @@
         <v>277</v>
       </c>
       <c r="B93" s="8">
-        <v>46181.60928361111</v>
+        <v>46181.44261694445</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46182.567648321754</v>
+        <v>46182.4009816551</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>215</v>
@@ -7066,11 +7066,11 @@
         <v>279</v>
       </c>
       <c r="B94" s="5">
-        <v>46181.609286990744</v>
+        <v>46181.44262032407</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46190.88639451389</v>
+        <v>46190.71972784722</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>280</v>
@@ -7129,11 +7129,11 @@
         <v>282</v>
       </c>
       <c r="B95" s="8">
-        <v>46181.609292974535</v>
+        <v>46181.44262630787</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46190.886394166664</v>
+        <v>46190.7197275</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>283</v>
@@ -7192,11 +7192,11 @@
         <v>284</v>
       </c>
       <c r="B96" s="5">
-        <v>46181.60929881944</v>
+        <v>46181.44263215278</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46190.886404791665</v>
+        <v>46190.719738125</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>285</v>
@@ -7255,11 +7255,11 @@
         <v>286</v>
       </c>
       <c r="B97" s="8">
-        <v>46181.60930480324</v>
+        <v>46181.44263813658</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46204.67339321759</v>
+        <v>46204.50672655093</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>287</v>
@@ -7318,11 +7318,11 @@
         <v>289</v>
       </c>
       <c r="B98" s="5">
-        <v>46181.60935271991</v>
+        <v>46181.44268605324</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46182.641076203705</v>
+        <v>46182.47440953704</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>60</v>
@@ -7381,11 +7381,11 @@
         <v>290</v>
       </c>
       <c r="B99" s="8">
-        <v>46181.60936674768</v>
+        <v>46181.44270008102</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46204.895167395836</v>
+        <v>46204.728500729165</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>291</v>
@@ -7428,11 +7428,11 @@
         <v>293</v>
       </c>
       <c r="B100" s="5">
-        <v>46181.609371666666</v>
+        <v>46181.442705</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46182.64123547454</v>
+        <v>46182.47456880787</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>294</v>
@@ -7491,11 +7491,11 @@
         <v>296</v>
       </c>
       <c r="B101" s="8">
-        <v>46181.609378587964</v>
+        <v>46181.44271192129</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46182.64119599537</v>
+        <v>46182.474529328705</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>181</v>
@@ -7544,11 +7544,11 @@
         <v>298</v>
       </c>
       <c r="B102" s="5">
-        <v>46181.61514019676</v>
+        <v>46181.448473530094</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46182.64119222222</v>
+        <v>46182.47452555556</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>181</v>
@@ -7597,13 +7597,13 @@
         <v>300</v>
       </c>
       <c r="B103" s="8">
-        <v>46181.609386111115</v>
+        <v>46181.44271944444</v>
       </c>
       <c r="C103" s="8">
-        <v>46204.895157314815</v>
+        <v>46204.72849064815</v>
       </c>
       <c r="D103" s="8">
-        <v>46204.895310810185</v>
+        <v>46204.72864414351</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>301</v>
@@ -7662,13 +7662,13 @@
         <v>302</v>
       </c>
       <c r="B104" s="5">
-        <v>46181.60939194444</v>
+        <v>46181.44272527778</v>
       </c>
       <c r="C104" s="5">
-        <v>46204.89505366898</v>
+        <v>46204.72838700232</v>
       </c>
       <c r="D104" s="5">
-        <v>46204.89505523148</v>
+        <v>46204.728388564814</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>181</v>
@@ -7717,13 +7717,13 @@
         <v>305</v>
       </c>
       <c r="B105" s="8">
-        <v>46181.61518315972</v>
+        <v>46181.44851649305</v>
       </c>
       <c r="C105" s="8">
-        <v>46204.89514296297</v>
+        <v>46204.728476296295</v>
       </c>
       <c r="D105" s="8">
-        <v>46204.89514483797</v>
+        <v>46204.728478171295</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>181</v>
@@ -7772,11 +7772,11 @@
         <v>307</v>
       </c>
       <c r="B106" s="5">
-        <v>46181.60939866898</v>
+        <v>46181.44273200231</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46182.64144489584</v>
+        <v>46182.47477822917</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>308</v>
@@ -7835,11 +7835,11 @@
         <v>309</v>
       </c>
       <c r="B107" s="8">
-        <v>46181.60940505787</v>
+        <v>46181.442738391204</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46204.89506170139</v>
+        <v>46204.72839503472</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>181</v>
@@ -7888,11 +7888,11 @@
         <v>312</v>
       </c>
       <c r="B108" s="5">
-        <v>46181.61523613426</v>
+        <v>46181.4485694676</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46182.64140446759</v>
+        <v>46182.47473780093</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>181</v>
@@ -7941,11 +7941,11 @@
         <v>314</v>
       </c>
       <c r="B109" s="8">
-        <v>46181.60941365741</v>
+        <v>46181.44274699074</v>
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="8">
-        <v>46182.64155526621</v>
+        <v>46182.474888599536</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>315</v>
@@ -8004,11 +8004,11 @@
         <v>316</v>
       </c>
       <c r="B110" s="5">
-        <v>46181.60941929398</v>
+        <v>46181.442752627314</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46191.54540483796</v>
+        <v>46191.3787381713</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>181</v>
@@ -8057,11 +8057,11 @@
         <v>319</v>
       </c>
       <c r="B111" s="8">
-        <v>46181.61528053241</v>
+        <v>46181.44861386574</v>
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46182.64151664352</v>
+        <v>46182.47484997685</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>181</v>
@@ -8110,11 +8110,11 @@
         <v>321</v>
       </c>
       <c r="B112" s="5">
-        <v>46181.60942706019</v>
+        <v>46181.44276039352</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46182.64166112269</v>
+        <v>46182.47499445602</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>322</v>
@@ -8173,11 +8173,11 @@
         <v>323</v>
       </c>
       <c r="B113" s="8">
-        <v>46181.60943415509</v>
+        <v>46181.44276748842</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46182.641623125004</v>
+        <v>46182.47495645833</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>181</v>
@@ -8226,11 +8226,11 @@
         <v>325</v>
       </c>
       <c r="B114" s="5">
-        <v>46181.61532783565</v>
+        <v>46181.44866116898</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46182.64161924769</v>
+        <v>46182.47495258102</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>181</v>
@@ -8279,11 +8279,11 @@
         <v>326</v>
       </c>
       <c r="B115" s="8">
-        <v>46181.60944410879</v>
+        <v>46181.442777442135</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46182.82922638889</v>
+        <v>46182.66255972222</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>327</v>
@@ -8342,11 +8342,11 @@
         <v>329</v>
       </c>
       <c r="B116" s="5">
-        <v>46181.60944996528</v>
+        <v>46181.44278329861</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46182.64173178241</v>
+        <v>46182.47506511574</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>181</v>
@@ -8395,11 +8395,11 @@
         <v>331</v>
       </c>
       <c r="B117" s="8">
-        <v>46181.61537143518</v>
+        <v>46181.44870476852</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46182.64172883102</v>
+        <v>46182.47506216435</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>181</v>
@@ -8448,11 +8448,11 @@
         <v>332</v>
       </c>
       <c r="B118" s="5">
-        <v>46181.60945642361</v>
+        <v>46181.44278975694</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46182.634494212965</v>
+        <v>46182.467827546294</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>333</v>
@@ -8495,11 +8495,11 @@
         <v>335</v>
       </c>
       <c r="B119" s="8">
-        <v>46181.60946096065</v>
+        <v>46181.44279429398</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46182.64186350694</v>
+        <v>46182.47519684028</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>336</v>
@@ -8558,11 +8558,11 @@
         <v>340</v>
       </c>
       <c r="B120" s="5">
-        <v>46181.60946868056</v>
+        <v>46181.44280201389</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46182.641845254635</v>
+        <v>46182.47517858796</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>181</v>
@@ -8611,11 +8611,11 @@
         <v>342</v>
       </c>
       <c r="B121" s="8">
-        <v>46181.609475034726</v>
+        <v>46181.442808368054</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46182.64184081019</v>
+        <v>46182.47517414352</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>181</v>
@@ -8664,11 +8664,11 @@
         <v>343</v>
       </c>
       <c r="B122" s="5">
-        <v>46181.60947921296</v>
+        <v>46181.442812546295</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46182.641837766205</v>
+        <v>46182.47517109953</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>59</v>
@@ -8717,11 +8717,11 @@
         <v>344</v>
       </c>
       <c r="B123" s="8">
-        <v>46181.61605960648</v>
+        <v>46181.449392939816</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46182.641834548616</v>
+        <v>46182.475167881945</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>59</v>
@@ -8770,11 +8770,11 @@
         <v>345</v>
       </c>
       <c r="B124" s="5">
-        <v>46181.61617203704</v>
+        <v>46181.44950537037</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46182.64182482639</v>
+        <v>46182.47515815972</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>186</v>
@@ -8823,11 +8823,11 @@
         <v>346</v>
       </c>
       <c r="B125" s="8">
-        <v>46181.61620771991</v>
+        <v>46181.44954105324</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46182.64182413195</v>
+        <v>46182.47515746528</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>189</v>
@@ -8876,11 +8876,11 @@
         <v>347</v>
       </c>
       <c r="B126" s="5">
-        <v>46181.616245833335</v>
+        <v>46181.44957916667</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46182.641823425925</v>
+        <v>46182.47515675926</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>276</v>
@@ -8929,11 +8929,11 @@
         <v>348</v>
       </c>
       <c r="B127" s="8">
-        <v>46181.60948424769</v>
+        <v>46181.44281758102</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46182.64199267361</v>
+        <v>46182.47532600694</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>349</v>
@@ -8992,11 +8992,11 @@
         <v>350</v>
       </c>
       <c r="B128" s="5">
-        <v>46181.60948969907</v>
+        <v>46181.44282303241</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46182.641973854166</v>
+        <v>46182.4753071875</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>181</v>
@@ -9045,11 +9045,11 @@
         <v>352</v>
       </c>
       <c r="B129" s="8">
-        <v>46181.60949538194</v>
+        <v>46181.44282871528</v>
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46182.64197085648</v>
+        <v>46182.475304189815</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>181</v>
@@ -9098,11 +9098,11 @@
         <v>353</v>
       </c>
       <c r="B130" s="5">
-        <v>46181.609560185185</v>
+        <v>46181.44289351851</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46182.641967118056</v>
+        <v>46182.47530045139</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>59</v>
@@ -9151,11 +9151,11 @@
         <v>354</v>
       </c>
       <c r="B131" s="8">
-        <v>46181.61659114584</v>
+        <v>46181.449924479166</v>
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46182.64196408565</v>
+        <v>46182.47529741898</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>59</v>
@@ -9204,11 +9204,11 @@
         <v>355</v>
       </c>
       <c r="B132" s="5">
-        <v>46181.61662431713</v>
+        <v>46181.44995765046</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46182.64196105324</v>
+        <v>46182.475294386575</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>186</v>
@@ -9257,11 +9257,11 @@
         <v>356</v>
       </c>
       <c r="B133" s="8">
-        <v>46181.61666238426</v>
+        <v>46181.449995717594</v>
       </c>
       <c r="C133" s="9"/>
       <c r="D133" s="8">
-        <v>46182.64195453704</v>
+        <v>46182.47528787037</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>189</v>
@@ -9310,11 +9310,11 @@
         <v>357</v>
       </c>
       <c r="B134" s="5">
-        <v>46181.61670006944</v>
+        <v>46181.450033402776</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46182.64195372685</v>
+        <v>46182.47528706018</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>191</v>
@@ -9363,11 +9363,11 @@
         <v>358</v>
       </c>
       <c r="B135" s="8">
-        <v>46181.60956560185</v>
+        <v>46181.44289893519</v>
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="8">
-        <v>46182.82952324074</v>
+        <v>46182.662856574076</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>359</v>
@@ -9426,11 +9426,11 @@
         <v>360</v>
       </c>
       <c r="B136" s="5">
-        <v>46181.60957188657</v>
+        <v>46181.44290521991</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46182.82945300926</v>
+        <v>46182.6627863426</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>181</v>
@@ -9479,11 +9479,11 @@
         <v>362</v>
       </c>
       <c r="B137" s="8">
-        <v>46181.609583576384</v>
+        <v>46181.44291690973</v>
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46182.829453784725</v>
+        <v>46182.66278711805</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>181</v>
@@ -9532,11 +9532,11 @@
         <v>363</v>
       </c>
       <c r="B138" s="5">
-        <v>46181.60958841435</v>
+        <v>46181.442921747686</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46182.829454583334</v>
+        <v>46182.66278791666</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>59</v>
@@ -9585,11 +9585,11 @@
         <v>364</v>
       </c>
       <c r="B139" s="8">
-        <v>46181.616839849536</v>
+        <v>46181.45017318287</v>
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46182.829455706014</v>
+        <v>46182.66278903935</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>59</v>
@@ -9638,11 +9638,11 @@
         <v>365</v>
       </c>
       <c r="B140" s="5">
-        <v>46181.61689748843</v>
+        <v>46181.45023082176</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46182.8294564699</v>
+        <v>46182.662789803246</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>186</v>
@@ -9691,11 +9691,11 @@
         <v>366</v>
       </c>
       <c r="B141" s="8">
-        <v>46181.616942569446</v>
+        <v>46181.45027590278</v>
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46182.82945721065</v>
+        <v>46182.66279054398</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>189</v>
@@ -9744,11 +9744,11 @@
         <v>367</v>
       </c>
       <c r="B142" s="5">
-        <v>46181.6169815162</v>
+        <v>46181.45031484954</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46182.82945796296</v>
+        <v>46182.6627912963</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>191</v>
@@ -9797,11 +9797,11 @@
         <v>368</v>
       </c>
       <c r="B143" s="8">
-        <v>46181.609592673616</v>
+        <v>46181.442926006945</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46182.642407384265</v>
+        <v>46182.47574071759</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>369</v>
@@ -9860,11 +9860,11 @@
         <v>371</v>
       </c>
       <c r="B144" s="5">
-        <v>46181.60960517361</v>
+        <v>46181.442938506945</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46182.8294527199</v>
+        <v>46182.66278605324</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>181</v>
@@ -9913,11 +9913,11 @@
         <v>372</v>
       </c>
       <c r="B145" s="8">
-        <v>46181.609610011576</v>
+        <v>46181.44294334491</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46182.829451909725</v>
+        <v>46182.662785243054</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>181</v>
@@ -9966,11 +9966,11 @@
         <v>373</v>
       </c>
       <c r="B146" s="5">
-        <v>46181.609613796296</v>
+        <v>46181.44294712963</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46182.829452025464</v>
+        <v>46182.6627853588</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>59</v>
@@ -10019,11 +10019,11 @@
         <v>374</v>
       </c>
       <c r="B147" s="8">
-        <v>46181.61712142361</v>
+        <v>46181.450454756945</v>
       </c>
       <c r="C147" s="9"/>
       <c r="D147" s="8">
-        <v>46182.82945197917</v>
+        <v>46182.662785312496</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>59</v>
@@ -10072,11 +10072,11 @@
         <v>375</v>
       </c>
       <c r="B148" s="5">
-        <v>46181.61716094907</v>
+        <v>46181.450494282406</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46182.82945207176</v>
+        <v>46182.66278540509</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>186</v>
@@ -10125,11 +10125,11 @@
         <v>376</v>
       </c>
       <c r="B149" s="8">
-        <v>46181.61719633102</v>
+        <v>46181.45052966435</v>
       </c>
       <c r="C149" s="9"/>
       <c r="D149" s="8">
-        <v>46182.829452025464</v>
+        <v>46182.6627853588</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>189</v>
@@ -10178,11 +10178,11 @@
         <v>377</v>
       </c>
       <c r="B150" s="5">
-        <v>46181.617235451384</v>
+        <v>46181.45056878473</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46182.829452418984</v>
+        <v>46182.66278575231</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>191</v>
@@ -10231,11 +10231,11 @@
         <v>378</v>
       </c>
       <c r="B151" s="8">
-        <v>46181.60961741898</v>
+        <v>46181.44295075232</v>
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="8">
-        <v>46182.63449439815</v>
+        <v>46182.46782773148</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>379</v>
@@ -10278,11 +10278,11 @@
         <v>381</v>
       </c>
       <c r="B152" s="5">
-        <v>46181.60962174769</v>
+        <v>46181.44295508102</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46182.64244836806</v>
+        <v>46182.47578170139</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>382</v>
@@ -10341,11 +10341,11 @@
         <v>385</v>
       </c>
       <c r="B153" s="8">
-        <v>46181.60962780092</v>
+        <v>46181.442961134264</v>
       </c>
       <c r="C153" s="9"/>
       <c r="D153" s="8">
-        <v>46191.67892958333</v>
+        <v>46191.512262916665</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>386</v>
@@ -10404,11 +10404,11 @@
         <v>387</v>
       </c>
       <c r="B154" s="5">
-        <v>46181.60963489584</v>
+        <v>46181.44296822917</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46182.63449431713</v>
+        <v>46182.467827650464</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>388</v>
@@ -10457,11 +10457,11 @@
         <v>390</v>
       </c>
       <c r="B155" s="8">
-        <v>46181.609640208335</v>
+        <v>46181.44297354166</v>
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46182.64254377315</v>
+        <v>46182.47587710648</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>391</v>
@@ -10520,11 +10520,11 @@
         <v>393</v>
       </c>
       <c r="B156" s="5">
-        <v>46181.609646365745</v>
+        <v>46181.44297969907</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46182.64254079861</v>
+        <v>46182.475874131946</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>394</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -1864,13 +1864,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46181.44196283565</v>
+        <v>46181.60862950231</v>
       </c>
       <c r="C4" s="5">
-        <v>46190.5097949537</v>
+        <v>46190.67646162037</v>
       </c>
       <c r="D4" s="5">
-        <v>46191.6119315625</v>
+        <v>46191.77859822917</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1913,13 +1913,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46181.44214226852</v>
+        <v>46181.60880893518</v>
       </c>
       <c r="C5" s="8">
-        <v>46190.5091971875</v>
+        <v>46190.675863854165</v>
       </c>
       <c r="D5" s="8">
-        <v>46190.50966285879</v>
+        <v>46190.676329525464</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1976,13 +1976,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46181.44214673611</v>
+        <v>46181.60881340278</v>
       </c>
       <c r="C6" s="5">
-        <v>46190.50959462963</v>
+        <v>46190.67626129629</v>
       </c>
       <c r="D6" s="5">
-        <v>46190.50961417824</v>
+        <v>46190.676280844906</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2039,13 +2039,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="8">
-        <v>46181.442149814815</v>
+        <v>46181.60881648149</v>
       </c>
       <c r="C7" s="8">
-        <v>46190.50975353009</v>
+        <v>46190.67642019676</v>
       </c>
       <c r="D7" s="8">
-        <v>46190.509767511576</v>
+        <v>46190.67643417824</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>37</v>
@@ -2102,13 +2102,13 @@
         <v>40</v>
       </c>
       <c r="B8" s="5">
-        <v>46181.442153738426</v>
+        <v>46181.60882040509</v>
       </c>
       <c r="C8" s="5">
-        <v>46190.509779942135</v>
+        <v>46190.67644660879</v>
       </c>
       <c r="D8" s="5">
-        <v>46190.50979532408</v>
+        <v>46190.67646199074</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>41</v>
@@ -2165,11 +2165,11 @@
         <v>43</v>
       </c>
       <c r="B9" s="8">
-        <v>46181.44196856482</v>
+        <v>46181.60863523148</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="8">
-        <v>46190.51114369213</v>
+        <v>46190.6778103588</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>44</v>
@@ -2212,13 +2212,13 @@
         <v>46</v>
       </c>
       <c r="B10" s="5">
-        <v>46181.44215746528</v>
+        <v>46181.608824131945</v>
       </c>
       <c r="C10" s="5">
-        <v>46190.511137974536</v>
+        <v>46190.67780464121</v>
       </c>
       <c r="D10" s="5">
-        <v>46190.511153252315</v>
+        <v>46190.67781991899</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -2277,11 +2277,11 @@
         <v>51</v>
       </c>
       <c r="B11" s="8">
-        <v>46181.442162928244</v>
+        <v>46181.60882959491</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="8">
-        <v>46182.45913671296</v>
+        <v>46209.81759652778</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>52</v>
@@ -2340,11 +2340,11 @@
         <v>58</v>
       </c>
       <c r="B12" s="5">
-        <v>46181.44216831018</v>
+        <v>46181.608834976854</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46182.45922967592</v>
+        <v>46182.62589634259</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>59</v>
@@ -2393,11 +2393,11 @@
         <v>62</v>
       </c>
       <c r="B13" s="8">
-        <v>46181.45146517361</v>
+        <v>46181.61813184028</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46182.45922621527</v>
+        <v>46182.625892881944</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>59</v>
@@ -2446,13 +2446,13 @@
         <v>64</v>
       </c>
       <c r="B14" s="5">
-        <v>46181.44197355324</v>
+        <v>46181.60864021991</v>
       </c>
       <c r="C14" s="5">
-        <v>46204.73657797454</v>
+        <v>46204.9032446412</v>
       </c>
       <c r="D14" s="5">
-        <v>46204.73659428241</v>
+        <v>46204.903260949075</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>65</v>
@@ -2499,13 +2499,13 @@
         <v>67</v>
       </c>
       <c r="B15" s="8">
-        <v>46181.44217197917</v>
+        <v>46181.60883864583</v>
       </c>
       <c r="C15" s="8">
-        <v>46190.510777372685</v>
+        <v>46190.67744403935</v>
       </c>
       <c r="D15" s="8">
-        <v>46191.512263275465</v>
+        <v>46191.67892994213</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>68</v>
@@ -2564,13 +2564,13 @@
         <v>71</v>
       </c>
       <c r="B16" s="5">
-        <v>46181.44217729167</v>
+        <v>46181.60884395833</v>
       </c>
       <c r="C16" s="5">
-        <v>46190.510785335646</v>
+        <v>46190.67745200232</v>
       </c>
       <c r="D16" s="5">
-        <v>46191.512263136574</v>
+        <v>46191.67892980324</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>72</v>
@@ -2629,13 +2629,13 @@
         <v>75</v>
       </c>
       <c r="B17" s="8">
-        <v>46181.44218337963</v>
+        <v>46181.608850046294</v>
       </c>
       <c r="C17" s="8">
-        <v>46190.510792037036</v>
+        <v>46190.67745870371</v>
       </c>
       <c r="D17" s="8">
-        <v>46191.512263136574</v>
+        <v>46191.67892980324</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>76</v>
@@ -2694,13 +2694,13 @@
         <v>78</v>
       </c>
       <c r="B18" s="5">
-        <v>46181.441980034724</v>
+        <v>46181.60864670139</v>
       </c>
       <c r="C18" s="5">
-        <v>46204.72212517361</v>
+        <v>46204.888791840276</v>
       </c>
       <c r="D18" s="5">
-        <v>46204.722138240744</v>
+        <v>46204.88880490741</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>79</v>
@@ -2747,13 +2747,13 @@
         <v>81</v>
       </c>
       <c r="B19" s="8">
-        <v>46181.44219756944</v>
+        <v>46181.608864236114</v>
       </c>
       <c r="C19" s="8">
-        <v>46190.511006319444</v>
+        <v>46190.677672986116</v>
       </c>
       <c r="D19" s="8">
-        <v>46190.71972758102</v>
+        <v>46190.88639424769</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>82</v>
@@ -2812,13 +2812,13 @@
         <v>84</v>
       </c>
       <c r="B20" s="5">
-        <v>46181.442203125</v>
+        <v>46181.60886979167</v>
       </c>
       <c r="C20" s="5">
-        <v>46190.51101199074</v>
+        <v>46190.677678657405</v>
       </c>
       <c r="D20" s="5">
-        <v>46190.71971788195</v>
+        <v>46190.88638454861</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>85</v>
@@ -2877,13 +2877,13 @@
         <v>87</v>
       </c>
       <c r="B21" s="8">
-        <v>46181.442208541666</v>
+        <v>46181.60887520833</v>
       </c>
       <c r="C21" s="8">
-        <v>46197.256142349535</v>
+        <v>46197.42280901621</v>
       </c>
       <c r="D21" s="8">
-        <v>46197.25614478009</v>
+        <v>46197.422811446755</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>88</v>
@@ -2942,13 +2942,13 @@
         <v>91</v>
       </c>
       <c r="B22" s="5">
-        <v>46181.442213877315</v>
+        <v>46181.60888054398</v>
       </c>
       <c r="C22" s="5">
-        <v>46196.491901875</v>
+        <v>46196.658568541665</v>
       </c>
       <c r="D22" s="5">
-        <v>46206.38496015046</v>
+        <v>46206.551626817134</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>92</v>
@@ -3007,13 +3007,13 @@
         <v>97</v>
       </c>
       <c r="B23" s="8">
-        <v>46181.44221892361</v>
+        <v>46181.60888559028</v>
       </c>
       <c r="C23" s="8">
-        <v>46196.49216407408</v>
+        <v>46196.65883074074</v>
       </c>
       <c r="D23" s="8">
-        <v>46206.38525369213</v>
+        <v>46206.5519203588</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>98</v>
@@ -3072,13 +3072,13 @@
         <v>100</v>
       </c>
       <c r="B24" s="5">
-        <v>46181.44222295139</v>
+        <v>46181.60888961806</v>
       </c>
       <c r="C24" s="5">
-        <v>46204.72210027778</v>
+        <v>46204.888766944445</v>
       </c>
       <c r="D24" s="5">
-        <v>46206.38544342593</v>
+        <v>46206.5521100926</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>101</v>
@@ -3137,13 +3137,13 @@
         <v>103</v>
       </c>
       <c r="B25" s="8">
-        <v>46181.44222677083</v>
+        <v>46181.6088934375</v>
       </c>
       <c r="C25" s="8">
-        <v>46197.478443831016</v>
+        <v>46197.64511049769</v>
       </c>
       <c r="D25" s="8">
-        <v>46206.385667916664</v>
+        <v>46206.552334583335</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>104</v>
@@ -3202,13 +3202,13 @@
         <v>106</v>
       </c>
       <c r="B26" s="5">
-        <v>46181.44223097222</v>
+        <v>46181.608897638886</v>
       </c>
       <c r="C26" s="5">
-        <v>46190.51118564815</v>
+        <v>46190.67785231481</v>
       </c>
       <c r="D26" s="5">
-        <v>46190.511203946764</v>
+        <v>46190.67787061342</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>107</v>
@@ -3267,13 +3267,13 @@
         <v>109</v>
       </c>
       <c r="B27" s="8">
-        <v>46190.71537822917</v>
+        <v>46190.88204489583</v>
       </c>
       <c r="C27" s="8">
-        <v>46197.257409756945</v>
+        <v>46197.42407642362</v>
       </c>
       <c r="D27" s="8">
-        <v>46197.25742238426</v>
+        <v>46197.424089050925</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>110</v>
@@ -3320,13 +3320,13 @@
         <v>111</v>
       </c>
       <c r="B28" s="5">
-        <v>46190.71655243056</v>
+        <v>46190.88321909722</v>
       </c>
       <c r="C28" s="5">
-        <v>46197.25687615741</v>
+        <v>46197.42354282408</v>
       </c>
       <c r="D28" s="5">
-        <v>46197.25689261574</v>
+        <v>46197.42355928241</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>112</v>
@@ -3385,13 +3385,13 @@
         <v>113</v>
       </c>
       <c r="B29" s="8">
-        <v>46190.71660518518</v>
+        <v>46190.88327185185</v>
       </c>
       <c r="C29" s="8">
-        <v>46197.25729826389</v>
+        <v>46197.42396493055</v>
       </c>
       <c r="D29" s="8">
-        <v>46197.25731493055</v>
+        <v>46197.423981597225</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>114</v>
@@ -3450,13 +3450,13 @@
         <v>115</v>
       </c>
       <c r="B30" s="5">
-        <v>46190.71665993056</v>
+        <v>46190.88332659722</v>
       </c>
       <c r="C30" s="5">
-        <v>46197.25739456018</v>
+        <v>46197.42406122685</v>
       </c>
       <c r="D30" s="5">
-        <v>46197.25740981482</v>
+        <v>46197.42407648148</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>116</v>
@@ -3515,11 +3515,11 @@
         <v>117</v>
       </c>
       <c r="B31" s="8">
-        <v>46181.44198559028</v>
+        <v>46181.608652256946</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46205.45052945602</v>
+        <v>46205.61719612269</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>118</v>
@@ -3564,11 +3564,11 @@
         <v>121</v>
       </c>
       <c r="B32" s="5">
-        <v>46181.44234127315</v>
+        <v>46181.60900793981</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46195.51926431713</v>
+        <v>46195.6859309838</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>122</v>
@@ -3627,13 +3627,13 @@
         <v>126</v>
       </c>
       <c r="B33" s="8">
-        <v>46181.44234498843</v>
+        <v>46181.60901165509</v>
       </c>
       <c r="C33" s="8">
-        <v>46195.51925878473</v>
+        <v>46195.685925451384</v>
       </c>
       <c r="D33" s="8">
-        <v>46195.519260810186</v>
+        <v>46195.68592747685</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>108</v>
@@ -3682,11 +3682,11 @@
         <v>128</v>
       </c>
       <c r="B34" s="5">
-        <v>46181.44234945602</v>
+        <v>46181.60901612269</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46195.51926576388</v>
+        <v>46195.685932430555</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>129</v>
@@ -3735,13 +3735,13 @@
         <v>131</v>
       </c>
       <c r="B35" s="8">
-        <v>46181.44235344908</v>
+        <v>46181.60902011574</v>
       </c>
       <c r="C35" s="8">
-        <v>46205.45052373843</v>
+        <v>46205.61719040509</v>
       </c>
       <c r="D35" s="8">
-        <v>46205.45052545139</v>
+        <v>46205.61719211805</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>119</v>
@@ -3800,13 +3800,13 @@
         <v>135</v>
       </c>
       <c r="B36" s="5">
-        <v>46181.442358217595</v>
+        <v>46181.60902488426</v>
       </c>
       <c r="C36" s="5">
-        <v>46199.40448653935</v>
+        <v>46199.57115320602</v>
       </c>
       <c r="D36" s="5">
-        <v>46199.40448865741</v>
+        <v>46199.57115532407</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
@@ -3861,13 +3861,13 @@
         <v>138</v>
       </c>
       <c r="B37" s="8">
-        <v>46181.44236313658</v>
+        <v>46181.609029803236</v>
       </c>
       <c r="C37" s="8">
-        <v>46205.445903518514</v>
+        <v>46205.612570185185</v>
       </c>
       <c r="D37" s="8">
-        <v>46205.44590554398</v>
+        <v>46205.61257221065</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>139</v>
@@ -3922,13 +3922,13 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46181.442368449076</v>
+        <v>46181.60903511574</v>
       </c>
       <c r="C38" s="5">
-        <v>46199.40567412037</v>
+        <v>46199.57234078704</v>
       </c>
       <c r="D38" s="5">
-        <v>46199.405685879625</v>
+        <v>46199.572352546296</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -3987,13 +3987,13 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46181.442371944446</v>
+        <v>46181.60903861111</v>
       </c>
       <c r="C39" s="8">
-        <v>46199.40555053241</v>
+        <v>46199.57221719908</v>
       </c>
       <c r="D39" s="8">
-        <v>46199.40590143518</v>
+        <v>46199.57256810185</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>99</v>
@@ -4042,13 +4042,13 @@
         <v>146</v>
       </c>
       <c r="B40" s="5">
-        <v>46181.44237628472</v>
+        <v>46181.609042951386</v>
       </c>
       <c r="C40" s="5">
-        <v>46199.405658090276</v>
+        <v>46199.57232475694</v>
       </c>
       <c r="D40" s="5">
-        <v>46199.405659675926</v>
+        <v>46199.57232634259</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>147</v>
@@ -4097,13 +4097,13 @@
         <v>149</v>
       </c>
       <c r="B41" s="8">
-        <v>46181.44238049768</v>
+        <v>46181.609047164355</v>
       </c>
       <c r="C41" s="8">
-        <v>46204.50806144676</v>
+        <v>46204.67472811343</v>
       </c>
       <c r="D41" s="8">
-        <v>46204.50807802084</v>
+        <v>46209.82369644676</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>150</v>
@@ -4162,13 +4162,13 @@
         <v>154</v>
       </c>
       <c r="B42" s="5">
-        <v>46181.44238408565</v>
+        <v>46181.60905075232</v>
       </c>
       <c r="C42" s="5">
-        <v>46204.506662106476</v>
+        <v>46204.67332877315</v>
       </c>
       <c r="D42" s="5">
-        <v>46204.50730190972</v>
+        <v>46204.67396857639</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>105</v>
@@ -4217,13 +4217,13 @@
         <v>156</v>
       </c>
       <c r="B43" s="8">
-        <v>46181.44238879629</v>
+        <v>46181.60905546296</v>
       </c>
       <c r="C43" s="8">
-        <v>46204.50670825232</v>
+        <v>46204.67337491898</v>
       </c>
       <c r="D43" s="8">
-        <v>46204.50725171296</v>
+        <v>46204.67391837963</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>157</v>
@@ -4272,11 +4272,11 @@
         <v>159</v>
       </c>
       <c r="B44" s="5">
-        <v>46181.44239351852</v>
+        <v>46181.60906018519</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46204.50718077546</v>
+        <v>46204.67384744213</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>160</v>
@@ -4325,13 +4325,13 @@
         <v>163</v>
       </c>
       <c r="B45" s="8">
-        <v>46181.44239664351</v>
+        <v>46181.609063310185</v>
       </c>
       <c r="C45" s="8">
-        <v>46205.44622780093</v>
+        <v>46205.61289446759</v>
       </c>
       <c r="D45" s="8">
-        <v>46205.446240543984</v>
+        <v>46205.61290721065</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>164</v>
@@ -4390,13 +4390,13 @@
         <v>166</v>
       </c>
       <c r="B46" s="5">
-        <v>46181.442400370375</v>
+        <v>46181.60906703703</v>
       </c>
       <c r="C46" s="5">
-        <v>46205.44616869213</v>
+        <v>46205.6128353588</v>
       </c>
       <c r="D46" s="5">
-        <v>46205.44617027778</v>
+        <v>46205.61283694445</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>102</v>
@@ -4445,13 +4445,13 @@
         <v>168</v>
       </c>
       <c r="B47" s="8">
-        <v>46181.44241015046</v>
+        <v>46181.60907681713</v>
       </c>
       <c r="C47" s="8">
-        <v>46205.44621112269</v>
+        <v>46205.612877789354</v>
       </c>
       <c r="D47" s="8">
-        <v>46205.446212662035</v>
+        <v>46205.612879328706</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>169</v>
@@ -4500,11 +4500,11 @@
         <v>171</v>
       </c>
       <c r="B48" s="5">
-        <v>46181.442414895835</v>
+        <v>46181.6090815625</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46204.73665016204</v>
+        <v>46204.9033168287</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>172</v>
@@ -4547,13 +4547,13 @@
         <v>174</v>
       </c>
       <c r="B49" s="8">
-        <v>46181.442418136576</v>
+        <v>46181.60908480324</v>
       </c>
       <c r="C49" s="8">
-        <v>46190.54157908565</v>
+        <v>46190.708245752314</v>
       </c>
       <c r="D49" s="8">
-        <v>46197.549148425926</v>
+        <v>46197.7158150926</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>175</v>
@@ -4612,13 +4612,13 @@
         <v>180</v>
       </c>
       <c r="B50" s="5">
-        <v>46181.44242248843</v>
+        <v>46181.60908915509</v>
       </c>
       <c r="C50" s="5">
-        <v>46190.54154569445</v>
+        <v>46190.70821236111</v>
       </c>
       <c r="D50" s="5">
-        <v>46190.54154723379</v>
+        <v>46190.70821390046</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>181</v>
@@ -4667,13 +4667,13 @@
         <v>185</v>
       </c>
       <c r="B51" s="8">
-        <v>46181.44242717593</v>
+        <v>46181.60909384259</v>
       </c>
       <c r="C51" s="8">
-        <v>46190.54155472222</v>
+        <v>46190.70822138889</v>
       </c>
       <c r="D51" s="8">
-        <v>46190.541556145836</v>
+        <v>46190.7082228125</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>186</v>
@@ -4722,13 +4722,13 @@
         <v>188</v>
       </c>
       <c r="B52" s="5">
-        <v>46181.445550752316</v>
+        <v>46181.61221741898</v>
       </c>
       <c r="C52" s="5">
-        <v>46190.541559351856</v>
+        <v>46190.70822601852</v>
       </c>
       <c r="D52" s="5">
-        <v>46190.54156067129</v>
+        <v>46190.708227337964</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>189</v>
@@ -4777,13 +4777,13 @@
         <v>190</v>
       </c>
       <c r="B53" s="8">
-        <v>46181.445690532404</v>
+        <v>46181.612357199076</v>
       </c>
       <c r="C53" s="8">
-        <v>46190.541565011576</v>
+        <v>46190.70823167824</v>
       </c>
       <c r="D53" s="8">
-        <v>46190.5415666551</v>
+        <v>46190.708233321755</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>191</v>
@@ -4832,13 +4832,13 @@
         <v>192</v>
       </c>
       <c r="B54" s="5">
-        <v>46181.4424315162</v>
+        <v>46181.609098182875</v>
       </c>
       <c r="C54" s="5">
-        <v>46191.376063159725</v>
+        <v>46191.54272982639</v>
       </c>
       <c r="D54" s="5">
-        <v>46197.54918153935</v>
+        <v>46197.71584820602</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>193</v>
@@ -4897,13 +4897,13 @@
         <v>194</v>
       </c>
       <c r="B55" s="8">
-        <v>46181.44243585649</v>
+        <v>46181.60910252314</v>
       </c>
       <c r="C55" s="8">
-        <v>46191.376039814815</v>
+        <v>46191.54270648149</v>
       </c>
       <c r="D55" s="8">
-        <v>46191.37604152778</v>
+        <v>46191.54270819444</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>181</v>
@@ -4952,13 +4952,13 @@
         <v>196</v>
       </c>
       <c r="B56" s="5">
-        <v>46181.44244128472</v>
+        <v>46181.609107951386</v>
       </c>
       <c r="C56" s="5">
-        <v>46191.37604895834</v>
+        <v>46191.542715625</v>
       </c>
       <c r="D56" s="5">
-        <v>46191.37605037037</v>
+        <v>46191.54271703704</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>186</v>
@@ -5007,13 +5007,13 @@
         <v>198</v>
       </c>
       <c r="B57" s="8">
-        <v>46181.44726903935</v>
+        <v>46181.61393570602</v>
       </c>
       <c r="C57" s="8">
-        <v>46190.54175359954</v>
+        <v>46190.70842026621</v>
       </c>
       <c r="D57" s="8">
-        <v>46190.54175503472</v>
+        <v>46190.70842170139</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>189</v>
@@ -5062,13 +5062,13 @@
         <v>199</v>
       </c>
       <c r="B58" s="5">
-        <v>46181.44730262732</v>
+        <v>46181.61396929398</v>
       </c>
       <c r="C58" s="5">
-        <v>46190.541758541665</v>
+        <v>46190.70842520833</v>
       </c>
       <c r="D58" s="5">
-        <v>46190.54175988426</v>
+        <v>46190.708426550926</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>191</v>
@@ -5117,13 +5117,13 @@
         <v>200</v>
       </c>
       <c r="B59" s="8">
-        <v>46181.44244663195</v>
+        <v>46181.60911329861</v>
       </c>
       <c r="C59" s="8">
-        <v>46191.378720266206</v>
+        <v>46191.54538693287</v>
       </c>
       <c r="D59" s="8">
-        <v>46191.37873159722</v>
+        <v>46191.54539826389</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>95</v>
@@ -5182,13 +5182,13 @@
         <v>202</v>
       </c>
       <c r="B60" s="5">
-        <v>46181.442456840276</v>
+        <v>46181.60912350695</v>
       </c>
       <c r="C60" s="5">
-        <v>46191.378692349535</v>
+        <v>46191.54535901621</v>
       </c>
       <c r="D60" s="5">
-        <v>46191.37869384259</v>
+        <v>46191.54536050926</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>181</v>
@@ -5235,13 +5235,13 @@
         <v>203</v>
       </c>
       <c r="B61" s="8">
-        <v>46181.44246115741</v>
+        <v>46181.60912782408</v>
       </c>
       <c r="C61" s="8">
-        <v>46191.378705752315</v>
+        <v>46191.54537241899</v>
       </c>
       <c r="D61" s="8">
-        <v>46191.378707199074</v>
+        <v>46191.54537386574</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>186</v>
@@ -5288,13 +5288,13 @@
         <v>204</v>
       </c>
       <c r="B62" s="5">
-        <v>46181.447452939814</v>
+        <v>46181.614119606485</v>
       </c>
       <c r="C62" s="5">
-        <v>46190.555057164354</v>
+        <v>46190.72172383102</v>
       </c>
       <c r="D62" s="5">
-        <v>46190.55505869213</v>
+        <v>46190.721725358795</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>189</v>
@@ -5341,13 +5341,13 @@
         <v>205</v>
       </c>
       <c r="B63" s="8">
-        <v>46181.44752960648</v>
+        <v>46181.61419627315</v>
       </c>
       <c r="C63" s="8">
-        <v>46190.55506201389</v>
+        <v>46190.72172868055</v>
       </c>
       <c r="D63" s="8">
-        <v>46190.555063287036</v>
+        <v>46190.7217299537</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>191</v>
@@ -5394,11 +5394,11 @@
         <v>206</v>
       </c>
       <c r="B64" s="5">
-        <v>46181.442465405096</v>
+        <v>46181.60913207176</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46182.46645140046</v>
+        <v>46182.633118067126</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>207</v>
@@ -5457,11 +5457,11 @@
         <v>210</v>
       </c>
       <c r="B65" s="8">
-        <v>46181.442469166665</v>
+        <v>46181.609135833336</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46182.46645180555</v>
+        <v>46182.63311847222</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>181</v>
@@ -5510,11 +5510,11 @@
         <v>212</v>
       </c>
       <c r="B66" s="5">
-        <v>46181.44764524305</v>
+        <v>46181.614311909725</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46182.466452569446</v>
+        <v>46182.63311923611</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>213</v>
@@ -5563,11 +5563,11 @@
         <v>214</v>
       </c>
       <c r="B67" s="8">
-        <v>46181.4425200463</v>
+        <v>46181.60918671296</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46181.613168703705</v>
+        <v>46181.77983537037</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>215</v>
@@ -5610,11 +5610,11 @@
         <v>217</v>
       </c>
       <c r="B68" s="5">
-        <v>46181.4425294213</v>
+        <v>46181.609196087964</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46205.4459224537</v>
+        <v>46205.61258912037</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>218</v>
@@ -5673,11 +5673,11 @@
         <v>222</v>
       </c>
       <c r="B69" s="8">
-        <v>46181.44253525463</v>
+        <v>46181.609201921296</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46182.46916971065</v>
+        <v>46182.63583637732</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>223</v>
@@ -5736,11 +5736,11 @@
         <v>226</v>
       </c>
       <c r="B70" s="5">
-        <v>46181.44254079861</v>
+        <v>46181.60920746528</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46199.40567940973</v>
+        <v>46199.572346076384</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>227</v>
@@ -5799,11 +5799,11 @@
         <v>229</v>
       </c>
       <c r="B71" s="8">
-        <v>46181.4425462037</v>
+        <v>46181.609212870375</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46182.46916622685</v>
+        <v>46182.63583289352</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>230</v>
@@ -5862,11 +5862,11 @@
         <v>232</v>
       </c>
       <c r="B72" s="5">
-        <v>46181.442550486114</v>
+        <v>46181.60921715278</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46205.44623003472</v>
+        <v>46205.612896701394</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>233</v>
@@ -5925,11 +5925,11 @@
         <v>235</v>
       </c>
       <c r="B73" s="8">
-        <v>46181.442555138885</v>
+        <v>46181.60922180556</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46182.46916178241</v>
+        <v>46182.63582844907</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>234</v>
@@ -5988,11 +5988,11 @@
         <v>236</v>
       </c>
       <c r="B74" s="5">
-        <v>46181.44255923611</v>
+        <v>46181.60922590278</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46181.61575747685</v>
+        <v>46181.782424143516</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>237</v>
@@ -6035,11 +6035,11 @@
         <v>239</v>
       </c>
       <c r="B75" s="8">
-        <v>46181.44256274306</v>
+        <v>46181.60922940972</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46205.7212597801</v>
+        <v>46205.887926446754</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>240</v>
@@ -6098,11 +6098,11 @@
         <v>245</v>
       </c>
       <c r="B76" s="5">
-        <v>46181.442568865736</v>
+        <v>46181.60923553241</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46204.71647274306</v>
+        <v>46204.88313940972</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>181</v>
@@ -6151,11 +6151,11 @@
         <v>248</v>
       </c>
       <c r="B77" s="8">
-        <v>46181.44257513889</v>
+        <v>46181.609241805556</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46182.46931675926</v>
+        <v>46182.63598342593</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>181</v>
@@ -6204,11 +6204,11 @@
         <v>250</v>
       </c>
       <c r="B78" s="5">
-        <v>46181.447861990746</v>
+        <v>46181.6145286574</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46182.4693140625</v>
+        <v>46182.63598072917</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>186</v>
@@ -6257,11 +6257,11 @@
         <v>251</v>
       </c>
       <c r="B79" s="8">
-        <v>46181.447940555554</v>
+        <v>46181.61460722222</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46182.469311203706</v>
+        <v>46182.63597787037</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>189</v>
@@ -6310,11 +6310,11 @@
         <v>253</v>
       </c>
       <c r="B80" s="5">
-        <v>46181.44797700232</v>
+        <v>46181.61464366898</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46182.469307141204</v>
+        <v>46182.635973807875</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>191</v>
@@ -6363,11 +6363,11 @@
         <v>254</v>
       </c>
       <c r="B81" s="8">
-        <v>46181.44258033565</v>
+        <v>46181.609247002314</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46182.47421207176</v>
+        <v>46182.64087873843</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>255</v>
@@ -6426,11 +6426,11 @@
         <v>257</v>
       </c>
       <c r="B82" s="5">
-        <v>46181.44258981482</v>
+        <v>46181.60925648148</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46191.37873856482</v>
+        <v>46191.54540523148</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>181</v>
@@ -6479,11 +6479,11 @@
         <v>260</v>
       </c>
       <c r="B83" s="8">
-        <v>46181.44259553241</v>
+        <v>46181.609262199076</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46191.378739074076</v>
+        <v>46191.54540574074</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>181</v>
@@ -6532,11 +6532,11 @@
         <v>261</v>
       </c>
       <c r="B84" s="5">
-        <v>46181.44806689815</v>
+        <v>46181.61473356481</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46182.47417746528</v>
+        <v>46182.64084413194</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>186</v>
@@ -6585,11 +6585,11 @@
         <v>263</v>
       </c>
       <c r="B85" s="8">
-        <v>46181.44810546296</v>
+        <v>46181.61477212963</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46182.47417420139</v>
+        <v>46182.64084086806</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>189</v>
@@ -6638,11 +6638,11 @@
         <v>265</v>
       </c>
       <c r="B86" s="5">
-        <v>46181.44818170139</v>
+        <v>46181.61484836806</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46182.474169050925</v>
+        <v>46182.6408357176</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>191</v>
@@ -6691,11 +6691,11 @@
         <v>267</v>
       </c>
       <c r="B87" s="8">
-        <v>46181.44260116898</v>
+        <v>46181.60926783565</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46182.47433079861</v>
+        <v>46182.64099746528</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>268</v>
@@ -6754,11 +6754,11 @@
         <v>269</v>
       </c>
       <c r="B88" s="5">
-        <v>46181.44260560186</v>
+        <v>46181.60927226851</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46191.378737175924</v>
+        <v>46191.545403842596</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>181</v>
@@ -6807,11 +6807,11 @@
         <v>271</v>
       </c>
       <c r="B89" s="8">
-        <v>46181.44261133102</v>
+        <v>46181.60927799769</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46191.3787375463</v>
+        <v>46191.545404212964</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>181</v>
@@ -6860,11 +6860,11 @@
         <v>273</v>
       </c>
       <c r="B90" s="5">
-        <v>46181.44828739583</v>
+        <v>46181.614954062505</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46182.474303043986</v>
+        <v>46182.64096971064</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>262</v>
@@ -6913,11 +6913,11 @@
         <v>274</v>
       </c>
       <c r="B91" s="8">
-        <v>46181.44832326389</v>
+        <v>46181.61498993056</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46182.474300428235</v>
+        <v>46182.64096709491</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>264</v>
@@ -6966,11 +6966,11 @@
         <v>275</v>
       </c>
       <c r="B92" s="5">
-        <v>46181.44835958333</v>
+        <v>46181.61502625</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46182.47429652778</v>
+        <v>46182.64096319444</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>266</v>
@@ -7019,11 +7019,11 @@
         <v>277</v>
       </c>
       <c r="B93" s="8">
-        <v>46181.44261694445</v>
+        <v>46181.60928361111</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46182.4009816551</v>
+        <v>46182.567648321754</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>215</v>
@@ -7066,11 +7066,11 @@
         <v>279</v>
       </c>
       <c r="B94" s="5">
-        <v>46181.44262032407</v>
+        <v>46181.609286990744</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46190.71972784722</v>
+        <v>46190.88639451389</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>280</v>
@@ -7129,11 +7129,11 @@
         <v>282</v>
       </c>
       <c r="B95" s="8">
-        <v>46181.44262630787</v>
+        <v>46181.609292974535</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46190.7197275</v>
+        <v>46190.886394166664</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>283</v>
@@ -7192,11 +7192,11 @@
         <v>284</v>
       </c>
       <c r="B96" s="5">
-        <v>46181.44263215278</v>
+        <v>46181.60929881944</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46190.719738125</v>
+        <v>46190.886404791665</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>285</v>
@@ -7255,11 +7255,11 @@
         <v>286</v>
       </c>
       <c r="B97" s="8">
-        <v>46181.44263813658</v>
+        <v>46181.60930480324</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46204.50672655093</v>
+        <v>46204.67339321759</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>287</v>
@@ -7318,11 +7318,11 @@
         <v>289</v>
       </c>
       <c r="B98" s="5">
-        <v>46181.44268605324</v>
+        <v>46181.60935271991</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46182.47440953704</v>
+        <v>46182.641076203705</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>60</v>
@@ -7381,11 +7381,11 @@
         <v>290</v>
       </c>
       <c r="B99" s="8">
-        <v>46181.44270008102</v>
+        <v>46181.60936674768</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46204.728500729165</v>
+        <v>46204.895167395836</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>291</v>
@@ -7428,11 +7428,11 @@
         <v>293</v>
       </c>
       <c r="B100" s="5">
-        <v>46181.442705</v>
+        <v>46181.609371666666</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46182.47456880787</v>
+        <v>46182.64123547454</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>294</v>
@@ -7491,11 +7491,11 @@
         <v>296</v>
       </c>
       <c r="B101" s="8">
-        <v>46181.44271192129</v>
+        <v>46181.609378587964</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46182.474529328705</v>
+        <v>46182.64119599537</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>181</v>
@@ -7544,11 +7544,11 @@
         <v>298</v>
       </c>
       <c r="B102" s="5">
-        <v>46181.448473530094</v>
+        <v>46181.61514019676</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46182.47452555556</v>
+        <v>46182.64119222222</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>181</v>
@@ -7597,13 +7597,13 @@
         <v>300</v>
       </c>
       <c r="B103" s="8">
-        <v>46181.44271944444</v>
+        <v>46181.609386111115</v>
       </c>
       <c r="C103" s="8">
-        <v>46204.72849064815</v>
+        <v>46204.895157314815</v>
       </c>
       <c r="D103" s="8">
-        <v>46204.72864414351</v>
+        <v>46204.895310810185</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>301</v>
@@ -7662,13 +7662,13 @@
         <v>302</v>
       </c>
       <c r="B104" s="5">
-        <v>46181.44272527778</v>
+        <v>46181.60939194444</v>
       </c>
       <c r="C104" s="5">
-        <v>46204.72838700232</v>
+        <v>46204.89505366898</v>
       </c>
       <c r="D104" s="5">
-        <v>46204.728388564814</v>
+        <v>46204.89505523148</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>181</v>
@@ -7717,13 +7717,13 @@
         <v>305</v>
       </c>
       <c r="B105" s="8">
-        <v>46181.44851649305</v>
+        <v>46181.61518315972</v>
       </c>
       <c r="C105" s="8">
-        <v>46204.728476296295</v>
+        <v>46204.89514296297</v>
       </c>
       <c r="D105" s="8">
-        <v>46204.728478171295</v>
+        <v>46204.89514483797</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>181</v>
@@ -7772,11 +7772,11 @@
         <v>307</v>
       </c>
       <c r="B106" s="5">
-        <v>46181.44273200231</v>
+        <v>46181.60939866898</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46182.47477822917</v>
+        <v>46182.64144489584</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>308</v>
@@ -7835,11 +7835,11 @@
         <v>309</v>
       </c>
       <c r="B107" s="8">
-        <v>46181.442738391204</v>
+        <v>46181.60940505787</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46204.72839503472</v>
+        <v>46204.89506170139</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>181</v>
@@ -7888,11 +7888,11 @@
         <v>312</v>
       </c>
       <c r="B108" s="5">
-        <v>46181.4485694676</v>
+        <v>46181.61523613426</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46182.47473780093</v>
+        <v>46182.64140446759</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>181</v>
@@ -7941,11 +7941,11 @@
         <v>314</v>
       </c>
       <c r="B109" s="8">
-        <v>46181.44274699074</v>
+        <v>46181.60941365741</v>
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="8">
-        <v>46182.474888599536</v>
+        <v>46182.64155526621</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>315</v>
@@ -8004,11 +8004,11 @@
         <v>316</v>
       </c>
       <c r="B110" s="5">
-        <v>46181.442752627314</v>
+        <v>46181.60941929398</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46191.3787381713</v>
+        <v>46191.54540483796</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>181</v>
@@ -8057,11 +8057,11 @@
         <v>319</v>
       </c>
       <c r="B111" s="8">
-        <v>46181.44861386574</v>
+        <v>46181.61528053241</v>
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46182.47484997685</v>
+        <v>46182.64151664352</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>181</v>
@@ -8110,11 +8110,11 @@
         <v>321</v>
       </c>
       <c r="B112" s="5">
-        <v>46181.44276039352</v>
+        <v>46181.60942706019</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46182.47499445602</v>
+        <v>46182.64166112269</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>322</v>
@@ -8173,11 +8173,11 @@
         <v>323</v>
       </c>
       <c r="B113" s="8">
-        <v>46181.44276748842</v>
+        <v>46181.60943415509</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46182.47495645833</v>
+        <v>46182.641623125004</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>181</v>
@@ -8226,11 +8226,11 @@
         <v>325</v>
       </c>
       <c r="B114" s="5">
-        <v>46181.44866116898</v>
+        <v>46181.61532783565</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46182.47495258102</v>
+        <v>46182.64161924769</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>181</v>
@@ -8279,11 +8279,11 @@
         <v>326</v>
       </c>
       <c r="B115" s="8">
-        <v>46181.442777442135</v>
+        <v>46181.60944410879</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46182.66255972222</v>
+        <v>46182.82922638889</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>327</v>
@@ -8342,11 +8342,11 @@
         <v>329</v>
       </c>
       <c r="B116" s="5">
-        <v>46181.44278329861</v>
+        <v>46181.60944996528</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46182.47506511574</v>
+        <v>46182.64173178241</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>181</v>
@@ -8395,11 +8395,11 @@
         <v>331</v>
       </c>
       <c r="B117" s="8">
-        <v>46181.44870476852</v>
+        <v>46181.61537143518</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46182.47506216435</v>
+        <v>46182.64172883102</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>181</v>
@@ -8448,11 +8448,11 @@
         <v>332</v>
       </c>
       <c r="B118" s="5">
-        <v>46181.44278975694</v>
+        <v>46181.60945642361</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46182.467827546294</v>
+        <v>46182.634494212965</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>333</v>
@@ -8495,11 +8495,11 @@
         <v>335</v>
       </c>
       <c r="B119" s="8">
-        <v>46181.44279429398</v>
+        <v>46181.60946096065</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46182.47519684028</v>
+        <v>46182.64186350694</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>336</v>
@@ -8558,11 +8558,11 @@
         <v>340</v>
       </c>
       <c r="B120" s="5">
-        <v>46181.44280201389</v>
+        <v>46181.60946868056</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46182.47517858796</v>
+        <v>46182.641845254635</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>181</v>
@@ -8611,11 +8611,11 @@
         <v>342</v>
       </c>
       <c r="B121" s="8">
-        <v>46181.442808368054</v>
+        <v>46181.609475034726</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46182.47517414352</v>
+        <v>46182.64184081019</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>181</v>
@@ -8664,11 +8664,11 @@
         <v>343</v>
       </c>
       <c r="B122" s="5">
-        <v>46181.442812546295</v>
+        <v>46181.60947921296</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46182.47517109953</v>
+        <v>46182.641837766205</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>59</v>
@@ -8717,11 +8717,11 @@
         <v>344</v>
       </c>
       <c r="B123" s="8">
-        <v>46181.449392939816</v>
+        <v>46181.61605960648</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46182.475167881945</v>
+        <v>46182.641834548616</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>59</v>
@@ -8770,11 +8770,11 @@
         <v>345</v>
       </c>
       <c r="B124" s="5">
-        <v>46181.44950537037</v>
+        <v>46181.61617203704</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46182.47515815972</v>
+        <v>46182.64182482639</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>186</v>
@@ -8823,11 +8823,11 @@
         <v>346</v>
       </c>
       <c r="B125" s="8">
-        <v>46181.44954105324</v>
+        <v>46181.61620771991</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46182.47515746528</v>
+        <v>46182.64182413195</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>189</v>
@@ -8876,11 +8876,11 @@
         <v>347</v>
       </c>
       <c r="B126" s="5">
-        <v>46181.44957916667</v>
+        <v>46181.616245833335</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46182.47515675926</v>
+        <v>46182.641823425925</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>276</v>
@@ -8929,11 +8929,11 @@
         <v>348</v>
       </c>
       <c r="B127" s="8">
-        <v>46181.44281758102</v>
+        <v>46181.60948424769</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46182.47532600694</v>
+        <v>46182.64199267361</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>349</v>
@@ -8992,11 +8992,11 @@
         <v>350</v>
       </c>
       <c r="B128" s="5">
-        <v>46181.44282303241</v>
+        <v>46181.60948969907</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46182.4753071875</v>
+        <v>46182.641973854166</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>181</v>
@@ -9045,11 +9045,11 @@
         <v>352</v>
       </c>
       <c r="B129" s="8">
-        <v>46181.44282871528</v>
+        <v>46181.60949538194</v>
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46182.475304189815</v>
+        <v>46182.64197085648</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>181</v>
@@ -9098,11 +9098,11 @@
         <v>353</v>
       </c>
       <c r="B130" s="5">
-        <v>46181.44289351851</v>
+        <v>46181.609560185185</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46182.47530045139</v>
+        <v>46182.641967118056</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>59</v>
@@ -9151,11 +9151,11 @@
         <v>354</v>
       </c>
       <c r="B131" s="8">
-        <v>46181.449924479166</v>
+        <v>46181.61659114584</v>
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46182.47529741898</v>
+        <v>46182.64196408565</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>59</v>
@@ -9204,11 +9204,11 @@
         <v>355</v>
       </c>
       <c r="B132" s="5">
-        <v>46181.44995765046</v>
+        <v>46181.61662431713</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46182.475294386575</v>
+        <v>46182.64196105324</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>186</v>
@@ -9257,11 +9257,11 @@
         <v>356</v>
       </c>
       <c r="B133" s="8">
-        <v>46181.449995717594</v>
+        <v>46181.61666238426</v>
       </c>
       <c r="C133" s="9"/>
       <c r="D133" s="8">
-        <v>46182.47528787037</v>
+        <v>46182.64195453704</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>189</v>
@@ -9310,11 +9310,11 @@
         <v>357</v>
       </c>
       <c r="B134" s="5">
-        <v>46181.450033402776</v>
+        <v>46181.61670006944</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46182.47528706018</v>
+        <v>46182.64195372685</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>191</v>
@@ -9363,11 +9363,11 @@
         <v>358</v>
       </c>
       <c r="B135" s="8">
-        <v>46181.44289893519</v>
+        <v>46181.60956560185</v>
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="8">
-        <v>46182.662856574076</v>
+        <v>46182.82952324074</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>359</v>
@@ -9426,11 +9426,11 @@
         <v>360</v>
       </c>
       <c r="B136" s="5">
-        <v>46181.44290521991</v>
+        <v>46181.60957188657</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46182.6627863426</v>
+        <v>46182.82945300926</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>181</v>
@@ -9479,11 +9479,11 @@
         <v>362</v>
       </c>
       <c r="B137" s="8">
-        <v>46181.44291690973</v>
+        <v>46181.609583576384</v>
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46182.66278711805</v>
+        <v>46182.829453784725</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>181</v>
@@ -9532,11 +9532,11 @@
         <v>363</v>
       </c>
       <c r="B138" s="5">
-        <v>46181.442921747686</v>
+        <v>46181.60958841435</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46182.66278791666</v>
+        <v>46182.829454583334</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>59</v>
@@ -9585,11 +9585,11 @@
         <v>364</v>
       </c>
       <c r="B139" s="8">
-        <v>46181.45017318287</v>
+        <v>46181.616839849536</v>
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46182.66278903935</v>
+        <v>46182.829455706014</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>59</v>
@@ -9638,11 +9638,11 @@
         <v>365</v>
       </c>
       <c r="B140" s="5">
-        <v>46181.45023082176</v>
+        <v>46181.61689748843</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46182.662789803246</v>
+        <v>46182.8294564699</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>186</v>
@@ -9691,11 +9691,11 @@
         <v>366</v>
       </c>
       <c r="B141" s="8">
-        <v>46181.45027590278</v>
+        <v>46181.616942569446</v>
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46182.66279054398</v>
+        <v>46182.82945721065</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>189</v>
@@ -9744,11 +9744,11 @@
         <v>367</v>
       </c>
       <c r="B142" s="5">
-        <v>46181.45031484954</v>
+        <v>46181.6169815162</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46182.6627912963</v>
+        <v>46182.82945796296</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>191</v>
@@ -9797,11 +9797,11 @@
         <v>368</v>
       </c>
       <c r="B143" s="8">
-        <v>46181.442926006945</v>
+        <v>46181.609592673616</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46182.47574071759</v>
+        <v>46182.642407384265</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>369</v>
@@ -9860,11 +9860,11 @@
         <v>371</v>
       </c>
       <c r="B144" s="5">
-        <v>46181.442938506945</v>
+        <v>46181.60960517361</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46182.66278605324</v>
+        <v>46182.8294527199</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>181</v>
@@ -9913,11 +9913,11 @@
         <v>372</v>
       </c>
       <c r="B145" s="8">
-        <v>46181.44294334491</v>
+        <v>46181.609610011576</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46182.662785243054</v>
+        <v>46182.829451909725</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>181</v>
@@ -9966,11 +9966,11 @@
         <v>373</v>
       </c>
       <c r="B146" s="5">
-        <v>46181.44294712963</v>
+        <v>46181.609613796296</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46182.6627853588</v>
+        <v>46182.829452025464</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>59</v>
@@ -10019,11 +10019,11 @@
         <v>374</v>
       </c>
       <c r="B147" s="8">
-        <v>46181.450454756945</v>
+        <v>46181.61712142361</v>
       </c>
       <c r="C147" s="9"/>
       <c r="D147" s="8">
-        <v>46182.662785312496</v>
+        <v>46182.82945197917</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>59</v>
@@ -10072,11 +10072,11 @@
         <v>375</v>
       </c>
       <c r="B148" s="5">
-        <v>46181.450494282406</v>
+        <v>46181.61716094907</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46182.66278540509</v>
+        <v>46182.82945207176</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>186</v>
@@ -10125,11 +10125,11 @@
         <v>376</v>
       </c>
       <c r="B149" s="8">
-        <v>46181.45052966435</v>
+        <v>46181.61719633102</v>
       </c>
       <c r="C149" s="9"/>
       <c r="D149" s="8">
-        <v>46182.6627853588</v>
+        <v>46182.829452025464</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>189</v>
@@ -10178,11 +10178,11 @@
         <v>377</v>
       </c>
       <c r="B150" s="5">
-        <v>46181.45056878473</v>
+        <v>46181.617235451384</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46182.66278575231</v>
+        <v>46182.829452418984</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>191</v>
@@ -10231,11 +10231,11 @@
         <v>378</v>
       </c>
       <c r="B151" s="8">
-        <v>46181.44295075232</v>
+        <v>46181.60961741898</v>
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="8">
-        <v>46182.46782773148</v>
+        <v>46182.63449439815</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>379</v>
@@ -10278,11 +10278,11 @@
         <v>381</v>
       </c>
       <c r="B152" s="5">
-        <v>46181.44295508102</v>
+        <v>46181.60962174769</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46182.47578170139</v>
+        <v>46182.64244836806</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>382</v>
@@ -10341,11 +10341,11 @@
         <v>385</v>
       </c>
       <c r="B153" s="8">
-        <v>46181.442961134264</v>
+        <v>46181.60962780092</v>
       </c>
       <c r="C153" s="9"/>
       <c r="D153" s="8">
-        <v>46191.512262916665</v>
+        <v>46191.67892958333</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>386</v>
@@ -10404,11 +10404,11 @@
         <v>387</v>
       </c>
       <c r="B154" s="5">
-        <v>46181.44296822917</v>
+        <v>46181.60963489584</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46182.467827650464</v>
+        <v>46182.63449431713</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>388</v>
@@ -10457,11 +10457,11 @@
         <v>390</v>
       </c>
       <c r="B155" s="8">
-        <v>46181.44297354166</v>
+        <v>46181.609640208335</v>
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46182.47587710648</v>
+        <v>46182.64254377315</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>391</v>
@@ -10520,11 +10520,11 @@
         <v>393</v>
       </c>
       <c r="B156" s="5">
-        <v>46181.44297969907</v>
+        <v>46181.609646365745</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46182.475874131946</v>
+        <v>46182.64254079861</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>394</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1816" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1817" uniqueCount="395">
   <si>
     <t>50001559 - FERROVIAL</t>
   </si>
@@ -4502,9 +4502,11 @@
       <c r="B48" s="5">
         <v>46181.6090815625</v>
       </c>
-      <c r="C48" s="6"/>
+      <c r="C48" s="5">
+        <v>46210.52562674768</v>
+      </c>
       <c r="D48" s="5">
-        <v>46204.9033168287</v>
+        <v>46210.525643402776</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>172</v>
@@ -4539,8 +4541,12 @@
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
       <c r="S48" s="6"/>
-      <c r="T48" s="6"/>
-      <c r="U48" s="6"/>
+      <c r="T48" s="6">
+        <v>1</v>
+      </c>
+      <c r="U48" s="10" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -2281,7 +2281,7 @@
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="8">
-        <v>46209.81759652778</v>
+        <v>46210.824536712964</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>52</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -229,7 +229,7 @@
     <t>OT 4348 - VDF 75KW / IP54</t>
   </si>
   <si>
-    <t>Recepcion Tableros</t>
+    <t xml:space="preserve">Recepcion Tableros OT 4348  </t>
   </si>
   <si>
     <t>Revision Tableros,OT 4348 - VDF 75KW / IP54</t>
@@ -445,7 +445,7 @@
     <t xml:space="preserve">fabricación tableros   ot 4343 </t>
   </si>
   <si>
-    <t>Tableros ot 4348  ,Recepcion Tableros</t>
+    <t xml:space="preserve">Tableros ot 4348  ,Recepcion Tableros OT 4348  </t>
   </si>
   <si>
     <t>1215506781705121</t>
@@ -475,7 +475,7 @@
     <t xml:space="preserve">Fabricacion Corte Laser ot 4342 -4344 </t>
   </si>
   <si>
-    <t>Recepcion materiales corte laser,Materiales corte Laser ot 4347</t>
+    <t>Recepcion materiales corte laser OT 4347,Materiales corte Laser ot 4347</t>
   </si>
   <si>
     <t>1215506819659795</t>
@@ -499,7 +499,7 @@
     <t xml:space="preserve">Fabricación Corte Plasma  ot 4342 -4344 </t>
   </si>
   <si>
-    <t>Materiales Corte Plasma  ot 4347,Recepcion Materiales corte plasma</t>
+    <t>Materiales Corte Plasma  ot 4347,Recepcion Materiales corte plasma OT 4347</t>
   </si>
   <si>
     <t>1215506819661452</t>
@@ -529,7 +529,7 @@
     <t>Fabricación estructura proveedor externo ot 4347</t>
   </si>
   <si>
-    <t xml:space="preserve">Fabricación Externa  ot 4347,Control de calidad fabricación externa  ot 4347,Recepcion fabricación externa </t>
+    <t>Fabricación Externa  ot 4347,Control de calidad fabricación externa  ot 4347,Recepcion fabricación externa  OT 4347</t>
   </si>
   <si>
     <t>1215506639064752</t>
@@ -565,7 +565,7 @@
     <t>Fabricación Mecanizado ot 4342 -4344</t>
   </si>
   <si>
-    <t>Recepcion mecanizado,Mecanizado  ot 4347</t>
+    <t>Recepcion mecanizado OT 4347,Mecanizado  ot 4347</t>
   </si>
   <si>
     <t>1215506984807216</t>
@@ -676,7 +676,7 @@
     <t>1215506781849603</t>
   </si>
   <si>
-    <t>check pruebas FAT</t>
+    <t>check pruebas FAT OT 4347</t>
   </si>
   <si>
     <t>Francisca González Cornejo</t>
@@ -688,7 +688,7 @@
     <t>1215506781849615</t>
   </si>
   <si>
-    <t>check pruebas FAT,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
+    <t>check pruebas FAT OT 4347,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
   </si>
   <si>
     <t>1215504785833018</t>
@@ -703,13 +703,13 @@
     <t>Bodega:</t>
   </si>
   <si>
-    <t xml:space="preserve">Recepcion materiales corte laser,control de calidad corte laser </t>
+    <t>Recepcion materiales corte laser OT 4347,control de calidad corte laser  OT 4347</t>
   </si>
   <si>
     <t>1215506639142011</t>
   </si>
   <si>
-    <t>Recepcion materiales corte laser</t>
+    <t>Recepcion materiales corte laser OT 4347</t>
   </si>
   <si>
     <t>Victor Muñoz</t>
@@ -718,16 +718,16 @@
     <t>victor.munoz@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">Bodega:,control de calidad corte laser </t>
+    <t>Bodega:,control de calidad corte laser  OT 4347</t>
   </si>
   <si>
     <t>1215506984940147</t>
   </si>
   <si>
-    <t xml:space="preserve">control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma,Recepcion materiales corte laser</t>
+    <t>control de calidad corte laser  OT 4347</t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma OT 4347,Recepcion materiales corte laser OT 4347</t>
   </si>
   <si>
     <t>OT 4349- CODO 90° Ø1600MM,OT 4350 - CODO 135° Ø1600MM,OT 4351 - DUCTO Ø1600MM L:1800MM,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Bodega:,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
@@ -736,16 +736,16 @@
     <t>1215506984940169</t>
   </si>
   <si>
-    <t>Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>control de calidad corte laser ,Control de calidad Corte plasma</t>
+    <t>Recepcion Materiales corte plasma OT 4347</t>
+  </si>
+  <si>
+    <t>control de calidad corte laser  OT 4347,Control de calidad Corte plasma OT 4347</t>
   </si>
   <si>
     <t>1215506819763590</t>
   </si>
   <si>
-    <t>Control de calidad Corte plasma</t>
+    <t>Control de calidad Corte plasma OT 4347</t>
   </si>
   <si>
     <t>OT 4349- CODO 90° Ø1600MM,OT 4350 - CODO 135° Ø1600MM,OT 4351 - DUCTO Ø1600MM L:1800MM,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
@@ -754,10 +754,10 @@
     <t>1215506819763607</t>
   </si>
   <si>
-    <t>Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado</t>
+    <t>Recepcion mecanizado OT 4347</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado OT 4347</t>
   </si>
   <si>
     <t>1215506781913601</t>
@@ -769,13 +769,13 @@
     <t>Caldereria:</t>
   </si>
   <si>
-    <t>Armado,Control de calidad Armado,Preparación Materiales</t>
+    <t>OT 4347 Armado,OT 4347 Control de calidad Armado,OT 4347 Preparación Materiales</t>
   </si>
   <si>
     <t>1215506992907651</t>
   </si>
   <si>
-    <t>Preparación Materiales</t>
+    <t>OT 4347 Preparación Materiales</t>
   </si>
   <si>
     <t>Nicolás Mol</t>
@@ -793,16 +793,16 @@
     <t>1215506819773770</t>
   </si>
   <si>
-    <t>control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
+    <t>control de calidad corte laser  OT 4347,Control de calidad Mecanizado OT 4347,Control de calidad Corte plasma OT 4347</t>
+  </si>
+  <si>
+    <t>OT 4347 Preparación Materiales,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
   </si>
   <si>
     <t>1215506819773797</t>
   </si>
   <si>
-    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,control de calidad corte laser </t>
+    <t>Control de calidad Corte plasma OT 4347,Control de calidad Mecanizado OT 4347,control de calidad corte laser  OT 4347</t>
   </si>
   <si>
     <t>1215504785833019</t>
@@ -811,7 +811,7 @@
     <t>1215504802511713</t>
   </si>
   <si>
-    <t>Control de calidad Mecanizado,control de calidad corte laser ,Control de calidad Corte plasma</t>
+    <t>Control de calidad Mecanizado OT 4347,control de calidad corte laser  OT 4347,Control de calidad Corte plasma OT 4347</t>
   </si>
   <si>
     <t>1215504802511714</t>
@@ -820,7 +820,7 @@
     <t>1215506984972272</t>
   </si>
   <si>
-    <t>Armado</t>
+    <t>OT 4347 Armado</t>
   </si>
   <si>
     <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
@@ -832,7 +832,7 @@
     <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,check planos</t>
   </si>
   <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Armado</t>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347 Armado</t>
   </si>
   <si>
     <t>1215506984982910</t>
@@ -859,19 +859,19 @@
     <t>1215506984991511</t>
   </si>
   <si>
-    <t>Control de calidad Armado</t>
+    <t>OT 4347 Control de calidad Armado</t>
   </si>
   <si>
     <t>1215506819777596</t>
   </si>
   <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Control de calidad Armado</t>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347 Control de calidad Armado</t>
   </si>
   <si>
     <t>1215506819777618</t>
   </si>
   <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Control de calidad Armado</t>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347 Control de calidad Armado</t>
   </si>
   <si>
     <t>1215504802511718</t>
@@ -889,13 +889,13 @@
     <t>1215506929522878</t>
   </si>
   <si>
-    <t>Recepcion Rodete,Recepcion Alabe,Recepcion motor</t>
+    <t>Recepcion Rodete OT 4347,Recepcion Alabe OT 4347,Recepcion motor OT 4347</t>
   </si>
   <si>
     <t>1215506929522890</t>
   </si>
   <si>
-    <t>Recepcion Rodete</t>
+    <t>Recepcion Rodete OT 4347</t>
   </si>
   <si>
     <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Bodega:</t>
@@ -904,19 +904,19 @@
     <t>1215506992958412</t>
   </si>
   <si>
-    <t>Recepcion Alabe</t>
+    <t>Recepcion Alabe OT 4347</t>
   </si>
   <si>
     <t>1215506992960641</t>
   </si>
   <si>
-    <t>Recepcion motor</t>
+    <t>Recepcion motor OT 4347</t>
   </si>
   <si>
     <t>1215506992960663</t>
   </si>
   <si>
-    <t xml:space="preserve">Recepcion fabricación externa </t>
+    <t>Recepcion fabricación externa  OT 4347</t>
   </si>
   <si>
     <t>Revestimiento,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
@@ -931,7 +931,7 @@
     <t>Montaje:</t>
   </si>
   <si>
-    <t>Revestimiento,Montaje Alabe,Montaje Rodete,Pruebas FAT,Montaje motor,RE-PINTADO</t>
+    <t>Revestimiento, OT 4347 Montaje Alabe,OT 4347 Montaje Rodete,OT 4347 Pruebas FAT,OT 4347 Montaje motor,OT 4347 RE-PINTADO</t>
   </si>
   <si>
     <t>1215506782065494</t>
@@ -940,13 +940,13 @@
     <t>Revestimiento</t>
   </si>
   <si>
-    <t>Recepcion fabricación externa ,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
+    <t>Recepcion fabricación externa  OT 4347,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
   </si>
   <si>
     <t>1215506782065516</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Recepcion fabricación externa </t>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Recepcion fabricación externa  OT 4347</t>
   </si>
   <si>
     <t>1215504802511721</t>
@@ -958,76 +958,76 @@
     <t>1215506782097502</t>
   </si>
   <si>
-    <t>Montaje Alabe</t>
+    <t xml:space="preserve"> OT 4347 Montaje Alabe</t>
   </si>
   <si>
     <t>1215506782097519</t>
   </si>
   <si>
-    <t>Recepcion Alabe,check planos</t>
-  </si>
-  <si>
-    <t>Montaje Alabe,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
+    <t>Recepcion Alabe OT 4347,check planos</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OT 4347 Montaje Alabe,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
   </si>
   <si>
     <t>1215504802511722</t>
   </si>
   <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Recepcion Alabe</t>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Recepcion Alabe OT 4347</t>
   </si>
   <si>
     <t>1215506782097797</t>
   </si>
   <si>
-    <t>Montaje Rodete</t>
+    <t>OT 4347 Montaje Rodete</t>
   </si>
   <si>
     <t>1215506985116839</t>
   </si>
   <si>
-    <t>check planos,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Montaje Rodete</t>
+    <t>check planos,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Recepcion Rodete OT 4347</t>
+  </si>
+  <si>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347 Montaje Rodete</t>
   </si>
   <si>
     <t>1215504802511723</t>
   </si>
   <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Recepcion Rodete</t>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Recepcion Rodete OT 4347</t>
   </si>
   <si>
     <t>1215506929643016</t>
   </si>
   <si>
-    <t>Montaje motor</t>
+    <t>OT 4347 Montaje motor</t>
   </si>
   <si>
     <t>1215506929643033</t>
   </si>
   <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Recepcion motor,check planos</t>
-  </si>
-  <si>
-    <t>Montaje motor,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Recepcion motor OT 4347,check planos</t>
+  </si>
+  <si>
+    <t>OT 4347 Montaje motor,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
   </si>
   <si>
     <t>1215504802511724</t>
   </si>
   <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Recepcion motor</t>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Recepcion motor OT 4347</t>
   </si>
   <si>
     <t>1215506782124046</t>
   </si>
   <si>
-    <t>Pruebas FAT</t>
+    <t>OT 4347 Pruebas FAT</t>
   </si>
   <si>
     <t>1215506782124063</t>
   </si>
   <si>
-    <t>Pruebas FAT,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
+    <t>OT 4347 Pruebas FAT,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
   </si>
   <si>
     <t>1215504802511725</t>
@@ -1036,7 +1036,7 @@
     <t>1215506929654031</t>
   </si>
   <si>
-    <t>RE-PINTADO</t>
+    <t>OT 4347 RE-PINTADO</t>
   </si>
   <si>
     <t>Coordinacion Entrega con Cliente,Montaje:</t>
@@ -1045,7 +1045,7 @@
     <t>1215506985153721</t>
   </si>
   <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,RE-PINTADO</t>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347 RE-PINTADO</t>
   </si>
   <si>
     <t>1215504802511726</t>
@@ -1072,7 +1072,7 @@
     <t>kpinto@zitron.com</t>
   </si>
   <si>
-    <t>Revision Tableros,RE-PINTADO,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
+    <t>Revision Tableros,OT 4347 RE-PINTADO,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
   </si>
   <si>
     <t>1215506782158209</t>
@@ -5404,7 +5404,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46182.633118067126</v>
+        <v>46212.622826203704</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>207</v>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46205.61258912037</v>
+        <v>46212.62267408565</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>218</v>
@@ -5683,7 +5683,7 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46182.63583637732</v>
+        <v>46212.62269510417</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>223</v>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46199.572346076384</v>
+        <v>46212.622715879625</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>227</v>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46182.63583289352</v>
+        <v>46212.62273200232</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>230</v>
@@ -5872,7 +5872,7 @@
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46205.612896701394</v>
+        <v>46212.622753194446</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>233</v>
@@ -5935,7 +5935,7 @@
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46182.63582844907</v>
+        <v>46212.622788657405</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>234</v>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46205.887926446754</v>
+        <v>46212.62260479167</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>240</v>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46182.64087873843</v>
+        <v>46212.62258834491</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>255</v>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46182.64099746528</v>
+        <v>46212.62263724537</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>268</v>
@@ -7076,7 +7076,7 @@
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46190.88639451389</v>
+        <v>46212.62294230324</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>280</v>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46190.886394166664</v>
+        <v>46212.6229683912</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>283</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46190.886404791665</v>
+        <v>46212.62298586806</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>285</v>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46204.67339321759</v>
+        <v>46212.623013958335</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>287</v>
@@ -7328,7 +7328,7 @@
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46182.641076203705</v>
+        <v>46212.6232265162</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>60</v>
@@ -7609,7 +7609,7 @@
         <v>46204.895157314815</v>
       </c>
       <c r="D103" s="8">
-        <v>46204.895310810185</v>
+        <v>46212.62246368056</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>301</v>
@@ -7782,7 +7782,7 @@
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46182.64144489584</v>
+        <v>46212.62248637731</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>308</v>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="8">
-        <v>46182.64155526621</v>
+        <v>46212.62250564815</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>315</v>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46182.64166112269</v>
+        <v>46212.62252259259</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>322</v>
@@ -8289,7 +8289,7 @@
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46182.82922638889</v>
+        <v>46212.622555497685</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>327</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -4103,7 +4103,7 @@
         <v>46204.67472811343</v>
       </c>
       <c r="D41" s="8">
-        <v>46209.82369644676</v>
+        <v>46212.82441381944</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>150</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -7391,7 +7391,7 @@
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46204.895167395836</v>
+        <v>46213.50490068287</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>291</v>
@@ -7780,9 +7780,11 @@
       <c r="B106" s="5">
         <v>46181.60939866898</v>
       </c>
-      <c r="C106" s="6"/>
+      <c r="C106" s="5">
+        <v>46213.50489005787</v>
+      </c>
       <c r="D106" s="5">
-        <v>46212.62248637731</v>
+        <v>46213.50490375</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>308</v>
@@ -7830,10 +7832,10 @@
         <v>32</v>
       </c>
       <c r="T106" s="6">
-        <v>0</v>
-      </c>
-      <c r="U106" s="11" t="s">
-        <v>57</v>
+        <v>1</v>
+      </c>
+      <c r="U106" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
@@ -7843,9 +7845,11 @@
       <c r="B107" s="8">
         <v>46181.60940505787</v>
       </c>
-      <c r="C107" s="9"/>
+      <c r="C107" s="8">
+        <v>46213.50480490741</v>
+      </c>
       <c r="D107" s="8">
-        <v>46204.89506170139</v>
+        <v>46213.50480686342</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>181</v>
@@ -7896,9 +7900,11 @@
       <c r="B108" s="5">
         <v>46181.61523613426</v>
       </c>
-      <c r="C108" s="6"/>
+      <c r="C108" s="5">
+        <v>46213.50487766204</v>
+      </c>
       <c r="D108" s="5">
-        <v>46182.64140446759</v>
+        <v>46213.50487908565</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>181</v>
@@ -8014,7 +8020,7 @@
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46191.54540483796</v>
+        <v>46213.50480997685</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>181</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1817" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1818" uniqueCount="395">
   <si>
     <t>50001559 - FERROVIAL</t>
   </si>
@@ -5573,7 +5573,7 @@
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46181.77983537037</v>
+        <v>46213.569374502316</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>215</v>
@@ -5618,9 +5618,11 @@
       <c r="B68" s="5">
         <v>46181.609196087964</v>
       </c>
-      <c r="C68" s="6"/>
+      <c r="C68" s="5">
+        <v>46213.5693694213</v>
+      </c>
       <c r="D68" s="5">
-        <v>46212.62267408565</v>
+        <v>46213.56938424769</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>218</v>
@@ -5668,10 +5670,10 @@
         <v>32</v>
       </c>
       <c r="T68" s="6">
-        <v>0</v>
-      </c>
-      <c r="U68" s="12" t="s">
-        <v>120</v>
+        <v>1</v>
+      </c>
+      <c r="U68" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
@@ -5683,7 +5685,7 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46212.62269510417</v>
+        <v>46213.56940306713</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>223</v>
@@ -5733,8 +5735,8 @@
       <c r="T69" s="9">
         <v>0</v>
       </c>
-      <c r="U69" s="11" t="s">
-        <v>57</v>
+      <c r="U69" s="12" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5744,9 +5746,11 @@
       <c r="B70" s="5">
         <v>46181.60920746528</v>
       </c>
-      <c r="C70" s="6"/>
+      <c r="C70" s="5">
+        <v>46213.56938394676</v>
+      </c>
       <c r="D70" s="5">
-        <v>46212.622715879625</v>
+        <v>46213.569400231485</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>227</v>
@@ -5794,10 +5798,10 @@
         <v>32</v>
       </c>
       <c r="T70" s="6">
-        <v>0</v>
-      </c>
-      <c r="U70" s="12" t="s">
-        <v>120</v>
+        <v>1</v>
+      </c>
+      <c r="U70" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -5809,7 +5813,7 @@
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46212.62273200232</v>
+        <v>46213.569403009256</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>230</v>
@@ -5859,8 +5863,8 @@
       <c r="T71" s="9">
         <v>0</v>
       </c>
-      <c r="U71" s="11" t="s">
-        <v>57</v>
+      <c r="U71" s="12" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
@@ -5870,9 +5874,11 @@
       <c r="B72" s="5">
         <v>46181.60921715278</v>
       </c>
-      <c r="C72" s="6"/>
+      <c r="C72" s="5">
+        <v>46213.56940421296</v>
+      </c>
       <c r="D72" s="5">
-        <v>46212.622753194446</v>
+        <v>46213.569419479165</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>233</v>
@@ -5920,10 +5926,10 @@
         <v>32</v>
       </c>
       <c r="T72" s="6">
-        <v>0</v>
-      </c>
-      <c r="U72" s="12" t="s">
-        <v>120</v>
+        <v>1</v>
+      </c>
+      <c r="U72" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -5935,7 +5941,7 @@
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46212.622788657405</v>
+        <v>46213.56941956018</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>234</v>
@@ -5985,8 +5991,8 @@
       <c r="T73" s="9">
         <v>0</v>
       </c>
-      <c r="U73" s="11" t="s">
-        <v>57</v>
+      <c r="U73" s="12" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
@@ -6045,7 +6051,7 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46212.62260479167</v>
+        <v>46213.578914004625</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>240</v>
@@ -7029,7 +7035,7 @@
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46182.567648321754</v>
+        <v>46213.56805377315</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>215</v>
@@ -7065,7 +7071,9 @@
       <c r="R93" s="9"/>
       <c r="S93" s="9"/>
       <c r="T93" s="9"/>
-      <c r="U93" s="9"/>
+      <c r="U93" s="12" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
@@ -7074,9 +7082,11 @@
       <c r="B94" s="5">
         <v>46181.609286990744</v>
       </c>
-      <c r="C94" s="6"/>
+      <c r="C94" s="5">
+        <v>46213.56771503472</v>
+      </c>
       <c r="D94" s="5">
-        <v>46212.62294230324</v>
+        <v>46213.56773226852</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>280</v>
@@ -7124,10 +7134,10 @@
         <v>179</v>
       </c>
       <c r="T94" s="6">
-        <v>0</v>
-      </c>
-      <c r="U94" s="12" t="s">
-        <v>120</v>
+        <v>1</v>
+      </c>
+      <c r="U94" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -7137,9 +7147,11 @@
       <c r="B95" s="8">
         <v>46181.609292974535</v>
       </c>
-      <c r="C95" s="9"/>
+      <c r="C95" s="8">
+        <v>46213.56772936342</v>
+      </c>
       <c r="D95" s="8">
-        <v>46212.6229683912</v>
+        <v>46213.56774653935</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>283</v>
@@ -7187,10 +7199,10 @@
         <v>32</v>
       </c>
       <c r="T95" s="9">
-        <v>0</v>
-      </c>
-      <c r="U95" s="12" t="s">
-        <v>120</v>
+        <v>1</v>
+      </c>
+      <c r="U95" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
@@ -7200,9 +7212,11 @@
       <c r="B96" s="5">
         <v>46181.60929881944</v>
       </c>
-      <c r="C96" s="6"/>
+      <c r="C96" s="5">
+        <v>46213.56803628472</v>
+      </c>
       <c r="D96" s="5">
-        <v>46212.62298586806</v>
+        <v>46213.56805165509</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>285</v>
@@ -7250,10 +7264,10 @@
         <v>32</v>
       </c>
       <c r="T96" s="6">
-        <v>0</v>
-      </c>
-      <c r="U96" s="12" t="s">
-        <v>120</v>
+        <v>1</v>
+      </c>
+      <c r="U96" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
@@ -7674,7 +7688,7 @@
         <v>46204.89505366898</v>
       </c>
       <c r="D104" s="5">
-        <v>46204.89505523148</v>
+        <v>46213.56773570602</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>181</v>
@@ -7729,7 +7743,7 @@
         <v>46204.89514296297</v>
       </c>
       <c r="D105" s="8">
-        <v>46204.89514483797</v>
+        <v>46213.567735150464</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>181</v>
@@ -7849,7 +7863,7 @@
         <v>46213.50480490741</v>
       </c>
       <c r="D107" s="8">
-        <v>46213.50480686342</v>
+        <v>46213.56772277778</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>181</v>
@@ -7904,7 +7918,7 @@
         <v>46213.50487766204</v>
       </c>
       <c r="D108" s="5">
-        <v>46213.50487908565</v>
+        <v>46213.56772202546</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>181</v>
@@ -8020,7 +8034,7 @@
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46213.50480997685</v>
+        <v>46213.56804261574</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>181</v>
@@ -8073,7 +8087,7 @@
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46182.64151664352</v>
+        <v>46213.568041192135</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>181</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -104,6 +104,18 @@
   </si>
   <si>
     <t>francisca@zitron.com</t>
+  </si>
+  <si>
+    <t>Baja</t>
+  </si>
+  <si>
+    <t>Tarea Terminada</t>
+  </si>
+  <si>
+    <t>1215506781516040</t>
+  </si>
+  <si>
+    <t>Alcance del proyecto</t>
   </si>
   <si>
     <t xml:space="preserve">    Planos para:
@@ -130,18 +142,6 @@
         Autosoportado
     Fechas de entrega: 23/06/2026.
 </t>
-  </si>
-  <si>
-    <t>Baja</t>
-  </si>
-  <si>
-    <t>Tarea Terminada</t>
-  </si>
-  <si>
-    <t>1215506781516040</t>
-  </si>
-  <si>
-    <t>Alcance del proyecto</t>
   </si>
   <si>
     <t>1215506781516052</t>
@@ -1919,7 +1919,7 @@
         <v>46190.675863854165</v>
       </c>
       <c r="D5" s="8">
-        <v>46190.676329525464</v>
+        <v>46213.69247820602</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1941,7 +1941,7 @@
         <v>26</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="M5" s="9" t="s">
         <v>26</v>
@@ -1962,18 +1962,18 @@
         <v>46161</v>
       </c>
       <c r="S5" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T5" s="9">
         <v>1</v>
       </c>
       <c r="U5" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B6" s="5">
         <v>46181.60881340278</v>
@@ -1985,7 +1985,7 @@
         <v>46190.676280844906</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>26</v>
@@ -2004,7 +2004,7 @@
         <v>26</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M6" s="6" t="s">
         <v>26</v>
@@ -2025,13 +2025,13 @@
         <v>46161</v>
       </c>
       <c r="S6" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T6" s="6">
         <v>1</v>
       </c>
       <c r="U6" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
@@ -2088,13 +2088,13 @@
         <v>46161</v>
       </c>
       <c r="S7" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T7" s="9">
         <v>1</v>
       </c>
       <c r="U7" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
@@ -2151,13 +2151,13 @@
         <v>46161</v>
       </c>
       <c r="S8" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T8" s="6">
         <v>1</v>
       </c>
       <c r="U8" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
@@ -2263,13 +2263,13 @@
         <v>46167</v>
       </c>
       <c r="S10" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T10" s="6">
         <v>1</v>
       </c>
       <c r="U10" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
@@ -2326,7 +2326,7 @@
         <v>46238</v>
       </c>
       <c r="S11" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T11" s="9">
         <v>0</v>
@@ -2491,7 +2491,7 @@
         <v>1</v>
       </c>
       <c r="U14" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
@@ -2550,13 +2550,13 @@
         <v>46164</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T15" s="9">
         <v>1</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
@@ -2615,13 +2615,13 @@
         <v>46171</v>
       </c>
       <c r="S16" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T16" s="6">
         <v>1</v>
       </c>
       <c r="U16" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
@@ -2680,13 +2680,13 @@
         <v>46171</v>
       </c>
       <c r="S17" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T17" s="9">
         <v>1</v>
       </c>
       <c r="U17" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
@@ -2739,7 +2739,7 @@
         <v>1</v>
       </c>
       <c r="U18" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
@@ -2798,13 +2798,13 @@
         <v>46168</v>
       </c>
       <c r="S19" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T19" s="9">
         <v>1</v>
       </c>
       <c r="U19" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
@@ -2863,13 +2863,13 @@
         <v>46175</v>
       </c>
       <c r="S20" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T20" s="6">
         <v>1</v>
       </c>
       <c r="U20" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
@@ -2928,13 +2928,13 @@
         <v>46175</v>
       </c>
       <c r="S21" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T21" s="9">
         <v>1</v>
       </c>
       <c r="U21" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
@@ -2993,13 +2993,13 @@
         <v>46251</v>
       </c>
       <c r="S22" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T22" s="6">
         <v>1</v>
       </c>
       <c r="U22" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
@@ -3058,13 +3058,13 @@
         <v>46251</v>
       </c>
       <c r="S23" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T23" s="9">
         <v>1</v>
       </c>
       <c r="U23" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
@@ -3123,13 +3123,13 @@
         <v>46251</v>
       </c>
       <c r="S24" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T24" s="6">
         <v>1</v>
       </c>
       <c r="U24" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -3188,13 +3188,13 @@
         <v>46251</v>
       </c>
       <c r="S25" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T25" s="9">
         <v>1</v>
       </c>
       <c r="U25" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
@@ -3253,13 +3253,13 @@
         <v>46169</v>
       </c>
       <c r="S26" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T26" s="6">
         <v>1</v>
       </c>
       <c r="U26" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
@@ -3312,7 +3312,7 @@
         <v>1</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -3371,13 +3371,13 @@
         <v>46175</v>
       </c>
       <c r="S28" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T28" s="6">
         <v>1</v>
       </c>
       <c r="U28" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -3436,13 +3436,13 @@
         <v>46182</v>
       </c>
       <c r="S29" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T29" s="9">
         <v>1</v>
       </c>
       <c r="U29" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -3501,13 +3501,13 @@
         <v>46182</v>
       </c>
       <c r="S30" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T30" s="6">
         <v>1</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -3613,7 +3613,7 @@
         <v>46225</v>
       </c>
       <c r="S32" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
@@ -3786,13 +3786,13 @@
         <v>46262</v>
       </c>
       <c r="S35" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T35" s="9">
         <v>1</v>
       </c>
       <c r="U35" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
@@ -3847,7 +3847,7 @@
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
       <c r="S36" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
@@ -3908,7 +3908,7 @@
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
       <c r="S37" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T37" s="9">
         <v>0</v>
@@ -3973,13 +3973,13 @@
         <v>46262</v>
       </c>
       <c r="S38" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T38" s="6">
         <v>1</v>
       </c>
       <c r="U38" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
@@ -4148,13 +4148,13 @@
         <v>46290</v>
       </c>
       <c r="S41" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T41" s="9">
         <v>1</v>
       </c>
       <c r="U41" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
@@ -4376,13 +4376,13 @@
         <v>46262</v>
       </c>
       <c r="S45" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T45" s="9">
         <v>1</v>
       </c>
       <c r="U45" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
@@ -4545,7 +4545,7 @@
         <v>1</v>
       </c>
       <c r="U48" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -4610,7 +4610,7 @@
         <v>1</v>
       </c>
       <c r="U49" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -4889,13 +4889,13 @@
         <v>46246</v>
       </c>
       <c r="S54" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T54" s="6">
         <v>1</v>
       </c>
       <c r="U54" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
@@ -5174,13 +5174,13 @@
         <v>46247</v>
       </c>
       <c r="S59" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T59" s="9">
         <v>1</v>
       </c>
       <c r="U59" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -5449,7 +5449,7 @@
         <v>46322</v>
       </c>
       <c r="S64" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T64" s="6">
         <v>0</v>
@@ -5667,13 +5667,13 @@
         <v>46253</v>
       </c>
       <c r="S68" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T68" s="6">
         <v>1</v>
       </c>
       <c r="U68" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
@@ -5730,7 +5730,7 @@
         <v>46255</v>
       </c>
       <c r="S69" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T69" s="9">
         <v>0</v>
@@ -5795,13 +5795,13 @@
         <v>46253</v>
       </c>
       <c r="S70" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T70" s="6">
         <v>1</v>
       </c>
       <c r="U70" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -5858,7 +5858,7 @@
         <v>46255</v>
       </c>
       <c r="S71" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T71" s="9">
         <v>0</v>
@@ -5923,13 +5923,13 @@
         <v>46253</v>
       </c>
       <c r="S72" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T72" s="6">
         <v>1</v>
       </c>
       <c r="U72" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -5986,7 +5986,7 @@
         <v>46255</v>
       </c>
       <c r="S73" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T73" s="9">
         <v>0</v>
@@ -6096,7 +6096,7 @@
         <v>46266</v>
       </c>
       <c r="S75" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T75" s="9">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>46288</v>
       </c>
       <c r="S81" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T81" s="9">
         <v>0</v>
@@ -6752,7 +6752,7 @@
         <v>46289</v>
       </c>
       <c r="S87" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T87" s="9">
         <v>0</v>
@@ -7137,7 +7137,7 @@
         <v>1</v>
       </c>
       <c r="U94" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -7196,13 +7196,13 @@
         <v>46293</v>
       </c>
       <c r="S95" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T95" s="9">
         <v>1</v>
       </c>
       <c r="U95" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
@@ -7261,13 +7261,13 @@
         <v>46227</v>
       </c>
       <c r="S96" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T96" s="6">
         <v>1</v>
       </c>
       <c r="U96" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
@@ -7324,7 +7324,7 @@
         <v>46294</v>
       </c>
       <c r="S97" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T97" s="9">
         <v>0</v>
@@ -7387,7 +7387,7 @@
         <v>46227</v>
       </c>
       <c r="S98" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T98" s="6">
         <v>0</v>
@@ -7497,7 +7497,7 @@
         <v>46310</v>
       </c>
       <c r="S100" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T100" s="6">
         <v>0</v>
@@ -7668,13 +7668,13 @@
         <v>46314</v>
       </c>
       <c r="S103" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T103" s="9">
         <v>1</v>
       </c>
       <c r="U103" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
@@ -7843,13 +7843,13 @@
         <v>46316</v>
       </c>
       <c r="S106" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T106" s="6">
         <v>1</v>
       </c>
       <c r="U106" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
@@ -8016,7 +8016,7 @@
         <v>46318</v>
       </c>
       <c r="S109" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T109" s="9">
         <v>0</v>
@@ -8185,7 +8185,7 @@
         <v>46321</v>
       </c>
       <c r="S112" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T112" s="6">
         <v>0</v>
@@ -8354,7 +8354,7 @@
         <v>46323</v>
       </c>
       <c r="S115" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T115" s="9">
         <v>0</v>
@@ -8570,7 +8570,7 @@
         <v>46324</v>
       </c>
       <c r="S119" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T119" s="9">
         <v>0</v>
@@ -9004,7 +9004,7 @@
         <v>46325</v>
       </c>
       <c r="S127" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T127" s="9">
         <v>0</v>
@@ -9438,7 +9438,7 @@
         <v>46328</v>
       </c>
       <c r="S135" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T135" s="9">
         <v>0</v>
@@ -9872,7 +9872,7 @@
         <v>46329</v>
       </c>
       <c r="S143" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T143" s="9">
         <v>0</v>
@@ -10353,7 +10353,7 @@
         <v>46337</v>
       </c>
       <c r="S152" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T152" s="6">
         <v>0</v>
@@ -10416,7 +10416,7 @@
         <v>46337</v>
       </c>
       <c r="S153" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T153" s="9">
         <v>0</v>
@@ -10469,7 +10469,7 @@
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
       <c r="S154" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T154" s="6">
         <v>0</v>
@@ -10532,7 +10532,7 @@
         <v>46338</v>
       </c>
       <c r="S155" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T155" s="9">
         <v>0</v>
@@ -10595,7 +10595,7 @@
         <v>46349</v>
       </c>
       <c r="S156" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T156" s="6">
         <v>0</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1818" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1818" uniqueCount="396">
   <si>
     <t>50001559 - FERROVIAL</t>
   </si>
@@ -104,6 +104,33 @@
   </si>
   <si>
     <t>francisca@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Para el pedido 1559, se tiene 2 ventiladores ZVN 1-14-75/4 + 2 Tableros VDF 75kW para Ferrovial:
+    Planos para:
+        Ventilador ZVN 1-14-75/4 con motor WEG
+        Alcance: Pieza Tipo C 1600-1400mm + 2FAR140/200 + Pieza Tipo B1400-1600mm
+        Adicionales:
+            Codo metálico de 90º de giro, 1600 mm de diámetro, con unión brida-brida en cada extremo (10 unidades)
+            Codo metálico de 135º de giro, 1600 mm de diámetro, con unión brida-brida en cada extremo (2 unidades)
+            Ducto metálico de 1600 mm de diámetro, 1.8 m de largo con unión brida-brida en cada extremo (36 unidades)
+        hgutierrez@zitron.com, favor tu apoyo con los planos de fabricación.
+    Rodete:
+        Alabe s/ plano 2604.01
+        Código:  300010
+        Z12 N900
+    Tratamiento superficial:
+        Estándar Zitrón con 2 capas y color de terminación Blanco RAL 9001.
+    Datos eléctricos para el motor:
+        Motor Stock WEG 75 KW 4 Polos
+        380 VAC, 50 Hz, IP55.
+        Frame 280S/M
+    Tableros eléctricos:
+        VDF 75 KW, 380 VAC, 50 Hz, IP54.
+        Danfoss FC102
+        Autosoportado
+    Fechas de entrega: 23/06/2026.
+ </t>
   </si>
   <si>
     <t>Baja</t>
@@ -1919,7 +1946,7 @@
         <v>46190.675863854165</v>
       </c>
       <c r="D5" s="8">
-        <v>46213.69247820602</v>
+        <v>46213.76202469907</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1941,7 +1968,7 @@
         <v>26</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="M5" s="9" t="s">
         <v>26</v>
@@ -1962,18 +1989,18 @@
         <v>46161</v>
       </c>
       <c r="S5" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T5" s="9">
         <v>1</v>
       </c>
       <c r="U5" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" s="5">
         <v>46181.60881340278</v>
@@ -1985,7 +2012,7 @@
         <v>46190.676280844906</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>26</v>
@@ -2004,7 +2031,7 @@
         <v>26</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M6" s="6" t="s">
         <v>26</v>
@@ -2025,18 +2052,18 @@
         <v>46161</v>
       </c>
       <c r="S6" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T6" s="6">
         <v>1</v>
       </c>
       <c r="U6" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" s="8">
         <v>46181.60881648149</v>
@@ -2048,7 +2075,7 @@
         <v>46190.67643417824</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>26</v>
@@ -2067,7 +2094,7 @@
         <v>26</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M7" s="9" t="s">
         <v>26</v>
@@ -2079,7 +2106,7 @@
         <v>26</v>
       </c>
       <c r="P7" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q7" s="8">
         <v>46161</v>
@@ -2088,18 +2115,18 @@
         <v>46161</v>
       </c>
       <c r="S7" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T7" s="9">
         <v>1</v>
       </c>
       <c r="U7" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B8" s="5">
         <v>46181.60882040509</v>
@@ -2111,7 +2138,7 @@
         <v>46190.67646199074</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>26</v>
@@ -2130,7 +2157,7 @@
         <v>26</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M8" s="6" t="s">
         <v>26</v>
@@ -2151,18 +2178,18 @@
         <v>46161</v>
       </c>
       <c r="S8" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T8" s="6">
         <v>1</v>
       </c>
       <c r="U8" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B9" s="8">
         <v>46181.60863523148</v>
@@ -2172,7 +2199,7 @@
         <v>46190.6778103588</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>25</v>
@@ -2196,7 +2223,7 @@
         <v>26</v>
       </c>
       <c r="O9" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P9" s="9" t="s">
         <v>26</v>
@@ -2209,7 +2236,7 @@
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B10" s="5">
         <v>46181.608824131945</v>
@@ -2221,16 +2248,16 @@
         <v>46190.67781991899</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I10" s="5">
         <v>46162</v>
@@ -2248,13 +2275,13 @@
         <v>26</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q10" s="5">
         <v>46162</v>
@@ -2263,18 +2290,18 @@
         <v>46167</v>
       </c>
       <c r="S10" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T10" s="6">
         <v>1</v>
       </c>
       <c r="U10" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B11" s="8">
         <v>46181.60882959491</v>
@@ -2284,16 +2311,16 @@
         <v>46210.824536712964</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I11" s="8">
         <v>46230</v>
@@ -2311,13 +2338,13 @@
         <v>26</v>
       </c>
       <c r="N11" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O11" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P11" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q11" s="8">
         <v>46230</v>
@@ -2326,18 +2353,18 @@
         <v>46238</v>
       </c>
       <c r="S11" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T11" s="9">
         <v>0</v>
       </c>
       <c r="U11" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B12" s="5">
         <v>46181.608834976854</v>
@@ -2347,16 +2374,16 @@
         <v>46182.62589634259</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I12" s="5">
         <v>46230</v>
@@ -2374,13 +2401,13 @@
         <v>26</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q12" s="6"/>
       <c r="R12" s="6"/>
@@ -2390,7 +2417,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B13" s="8">
         <v>46181.61813184028</v>
@@ -2400,16 +2427,16 @@
         <v>46182.625892881944</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I13" s="8">
         <v>46230</v>
@@ -2427,13 +2454,13 @@
         <v>26</v>
       </c>
       <c r="N13" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P13" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q13" s="9"/>
       <c r="R13" s="9"/>
@@ -2443,7 +2470,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B14" s="5">
         <v>46181.60864021991</v>
@@ -2455,7 +2482,7 @@
         <v>46204.903260949075</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>25</v>
@@ -2479,7 +2506,7 @@
         <v>26</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P14" s="6" t="s">
         <v>26</v>
@@ -2491,12 +2518,12 @@
         <v>1</v>
       </c>
       <c r="U14" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B15" s="8">
         <v>46181.60883864583</v>
@@ -2508,7 +2535,7 @@
         <v>46191.67892994213</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>26</v>
@@ -2529,19 +2556,19 @@
         <v>26</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M15" s="9" t="s">
         <v>26</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O15" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q15" s="8">
         <v>46162</v>
@@ -2550,18 +2577,18 @@
         <v>46164</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T15" s="9">
         <v>1</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B16" s="5">
         <v>46181.60884395833</v>
@@ -2573,7 +2600,7 @@
         <v>46191.67892980324</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
@@ -2594,19 +2621,19 @@
         <v>26</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q16" s="5">
         <v>46162</v>
@@ -2615,18 +2642,18 @@
         <v>46171</v>
       </c>
       <c r="S16" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T16" s="6">
         <v>1</v>
       </c>
       <c r="U16" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B17" s="8">
         <v>46181.608850046294</v>
@@ -2638,7 +2665,7 @@
         <v>46191.67892980324</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>26</v>
@@ -2665,13 +2692,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q17" s="8">
         <v>46162</v>
@@ -2680,18 +2707,18 @@
         <v>46171</v>
       </c>
       <c r="S17" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T17" s="9">
         <v>1</v>
       </c>
       <c r="U17" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B18" s="5">
         <v>46181.60864670139</v>
@@ -2703,7 +2730,7 @@
         <v>46204.88880490741</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>25</v>
@@ -2727,7 +2754,7 @@
         <v>26</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P18" s="6" t="s">
         <v>26</v>
@@ -2739,12 +2766,12 @@
         <v>1</v>
       </c>
       <c r="U18" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B19" s="8">
         <v>46181.608864236114</v>
@@ -2756,7 +2783,7 @@
         <v>46190.88639424769</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
@@ -2783,13 +2810,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q19" s="8">
         <v>46167</v>
@@ -2798,18 +2825,18 @@
         <v>46168</v>
       </c>
       <c r="S19" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T19" s="9">
         <v>1</v>
       </c>
       <c r="U19" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B20" s="5">
         <v>46181.60886979167</v>
@@ -2821,7 +2848,7 @@
         <v>46190.88638454861</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2848,13 +2875,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q20" s="5">
         <v>46174</v>
@@ -2863,18 +2890,18 @@
         <v>46175</v>
       </c>
       <c r="S20" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T20" s="6">
         <v>1</v>
       </c>
       <c r="U20" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B21" s="8">
         <v>46181.60887520833</v>
@@ -2886,16 +2913,16 @@
         <v>46197.422811446755</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I21" s="8">
         <v>46174</v>
@@ -2913,13 +2940,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q21" s="8">
         <v>46174</v>
@@ -2928,18 +2955,18 @@
         <v>46175</v>
       </c>
       <c r="S21" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T21" s="9">
         <v>1</v>
       </c>
       <c r="U21" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B22" s="5">
         <v>46181.60888054398</v>
@@ -2951,16 +2978,16 @@
         <v>46206.551626817134</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I22" s="5">
         <v>46248</v>
@@ -2978,13 +3005,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q22" s="5">
         <v>46248</v>
@@ -2993,18 +3020,18 @@
         <v>46251</v>
       </c>
       <c r="S22" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T22" s="6">
         <v>1</v>
       </c>
       <c r="U22" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B23" s="8">
         <v>46181.60888559028</v>
@@ -3016,16 +3043,16 @@
         <v>46206.5519203588</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I23" s="8">
         <v>46248</v>
@@ -3043,13 +3070,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q23" s="8">
         <v>46248</v>
@@ -3058,18 +3085,18 @@
         <v>46251</v>
       </c>
       <c r="S23" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T23" s="9">
         <v>1</v>
       </c>
       <c r="U23" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B24" s="5">
         <v>46181.60888961806</v>
@@ -3081,16 +3108,16 @@
         <v>46206.5521100926</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I24" s="5">
         <v>46248</v>
@@ -3108,13 +3135,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q24" s="5">
         <v>46248</v>
@@ -3123,18 +3150,18 @@
         <v>46251</v>
       </c>
       <c r="S24" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T24" s="6">
         <v>1</v>
       </c>
       <c r="U24" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B25" s="8">
         <v>46181.6088934375</v>
@@ -3146,16 +3173,16 @@
         <v>46206.552334583335</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I25" s="8">
         <v>46248</v>
@@ -3173,13 +3200,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q25" s="8">
         <v>46248</v>
@@ -3188,18 +3215,18 @@
         <v>46251</v>
       </c>
       <c r="S25" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T25" s="9">
         <v>1</v>
       </c>
       <c r="U25" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B26" s="5">
         <v>46181.608897638886</v>
@@ -3211,7 +3238,7 @@
         <v>46190.67787061342</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
@@ -3238,13 +3265,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q26" s="5">
         <v>46168</v>
@@ -3253,18 +3280,18 @@
         <v>46169</v>
       </c>
       <c r="S26" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T26" s="6">
         <v>1</v>
       </c>
       <c r="U26" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B27" s="8">
         <v>46190.88204489583</v>
@@ -3276,7 +3303,7 @@
         <v>46197.424089050925</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>25</v>
@@ -3312,12 +3339,12 @@
         <v>1</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B28" s="5">
         <v>46190.88321909722</v>
@@ -3329,16 +3356,16 @@
         <v>46197.42355928241</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I28" s="5">
         <v>46169</v>
@@ -3356,10 +3383,10 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>26</v>
@@ -3371,18 +3398,18 @@
         <v>46175</v>
       </c>
       <c r="S28" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T28" s="6">
         <v>1</v>
       </c>
       <c r="U28" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B29" s="8">
         <v>46190.88327185185</v>
@@ -3394,16 +3421,16 @@
         <v>46197.423981597225</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I29" s="8">
         <v>46176</v>
@@ -3421,10 +3448,10 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P29" s="9" t="s">
         <v>26</v>
@@ -3436,18 +3463,18 @@
         <v>46182</v>
       </c>
       <c r="S29" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T29" s="9">
         <v>1</v>
       </c>
       <c r="U29" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B30" s="5">
         <v>46190.88332659722</v>
@@ -3459,16 +3486,16 @@
         <v>46197.42407648148</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I30" s="5">
         <v>46176</v>
@@ -3486,10 +3513,10 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>26</v>
@@ -3501,18 +3528,18 @@
         <v>46182</v>
       </c>
       <c r="S30" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T30" s="6">
         <v>1</v>
       </c>
       <c r="U30" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B31" s="8">
         <v>46181.608652256946</v>
@@ -3522,7 +3549,7 @@
         <v>46205.61719612269</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>25</v>
@@ -3546,7 +3573,7 @@
         <v>26</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P31" s="9" t="s">
         <v>26</v>
@@ -3556,12 +3583,12 @@
       <c r="S31" s="9"/>
       <c r="T31" s="9"/>
       <c r="U31" s="12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B32" s="5">
         <v>46181.60900793981</v>
@@ -3571,16 +3598,16 @@
         <v>46195.6859309838</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I32" s="5">
         <v>46170</v>
@@ -3598,10 +3625,10 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3613,18 +3640,18 @@
         <v>46225</v>
       </c>
       <c r="S32" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B33" s="8">
         <v>46181.60901165509</v>
@@ -3636,16 +3663,16 @@
         <v>46195.68592747685</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I33" s="8">
         <v>46170</v>
@@ -3663,13 +3690,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3679,7 +3706,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B34" s="5">
         <v>46181.60901612269</v>
@@ -3689,16 +3716,16 @@
         <v>46195.685932430555</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I34" s="5">
         <v>46177</v>
@@ -3716,13 +3743,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3732,7 +3759,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B35" s="8">
         <v>46181.60902011574</v>
@@ -3744,16 +3771,16 @@
         <v>46205.61719211805</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I35" s="8">
         <v>46252</v>
@@ -3771,13 +3798,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q35" s="8">
         <v>46252</v>
@@ -3786,18 +3813,18 @@
         <v>46262</v>
       </c>
       <c r="S35" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T35" s="9">
         <v>1</v>
       </c>
       <c r="U35" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B36" s="5">
         <v>46181.60902488426</v>
@@ -3809,16 +3836,16 @@
         <v>46199.57115532407</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I36" s="5">
         <v>46252</v>
@@ -3836,29 +3863,29 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
       <c r="S36" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
       </c>
       <c r="U36" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B37" s="8">
         <v>46181.609029803236</v>
@@ -3870,16 +3897,16 @@
         <v>46205.61257221065</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I37" s="8">
         <v>46254</v>
@@ -3897,29 +3924,29 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
       <c r="S37" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T37" s="9">
         <v>0</v>
       </c>
       <c r="U37" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B38" s="5">
         <v>46181.60903511574</v>
@@ -3931,16 +3958,16 @@
         <v>46199.572352546296</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I38" s="5">
         <v>46252</v>
@@ -3958,10 +3985,10 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3973,18 +4000,18 @@
         <v>46262</v>
       </c>
       <c r="S38" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T38" s="6">
         <v>1</v>
       </c>
       <c r="U38" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B39" s="8">
         <v>46181.60903861111</v>
@@ -3996,16 +4023,16 @@
         <v>46199.57256810185</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I39" s="8">
         <v>46252</v>
@@ -4023,13 +4050,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -4039,7 +4066,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B40" s="5">
         <v>46181.609042951386</v>
@@ -4051,16 +4078,16 @@
         <v>46199.57232634259</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I40" s="5">
         <v>46254</v>
@@ -4078,13 +4105,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4094,7 +4121,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B41" s="8">
         <v>46181.609047164355</v>
@@ -4106,16 +4133,16 @@
         <v>46212.82441381944</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I41" s="8">
         <v>46252</v>
@@ -4133,10 +4160,10 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P41" s="9" t="s">
         <v>26</v>
@@ -4148,18 +4175,18 @@
         <v>46290</v>
       </c>
       <c r="S41" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T41" s="9">
         <v>1</v>
       </c>
       <c r="U41" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B42" s="5">
         <v>46181.60905075232</v>
@@ -4171,16 +4198,16 @@
         <v>46204.67396857639</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I42" s="5">
         <v>46252</v>
@@ -4198,13 +4225,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4214,7 +4241,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B43" s="8">
         <v>46181.60905546296</v>
@@ -4226,16 +4253,16 @@
         <v>46204.67391837963</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I43" s="8">
         <v>46261</v>
@@ -4253,13 +4280,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -4269,7 +4296,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B44" s="5">
         <v>46181.60906018519</v>
@@ -4279,16 +4306,16 @@
         <v>46204.67384744213</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I44" s="5">
         <v>46290</v>
@@ -4306,10 +4333,10 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>26</v>
@@ -4322,7 +4349,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B45" s="8">
         <v>46181.609063310185</v>
@@ -4334,16 +4361,16 @@
         <v>46205.61290721065</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I45" s="8">
         <v>46252</v>
@@ -4361,10 +4388,10 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>26</v>
@@ -4376,18 +4403,18 @@
         <v>46262</v>
       </c>
       <c r="S45" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T45" s="9">
         <v>1</v>
       </c>
       <c r="U45" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B46" s="5">
         <v>46181.60906703703</v>
@@ -4399,16 +4426,16 @@
         <v>46205.61283694445</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I46" s="5">
         <v>46252</v>
@@ -4426,13 +4453,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4442,7 +4469,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B47" s="8">
         <v>46181.60907681713</v>
@@ -4454,16 +4481,16 @@
         <v>46205.612879328706</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I47" s="8">
         <v>46254</v>
@@ -4481,13 +4508,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
@@ -4497,7 +4524,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B48" s="5">
         <v>46181.6090815625</v>
@@ -4509,7 +4536,7 @@
         <v>46210.525643402776</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>25</v>
@@ -4533,7 +4560,7 @@
         <v>26</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>26</v>
@@ -4545,12 +4572,12 @@
         <v>1</v>
       </c>
       <c r="U48" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B49" s="8">
         <v>46181.60908480324</v>
@@ -4562,16 +4589,16 @@
         <v>46197.7158150926</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I49" s="8">
         <v>46174</v>
@@ -4589,13 +4616,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q49" s="8">
         <v>46174</v>
@@ -4604,18 +4631,18 @@
         <v>46191</v>
       </c>
       <c r="S49" s="11" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="T49" s="9">
         <v>1</v>
       </c>
       <c r="U49" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B50" s="5">
         <v>46181.60908915509</v>
@@ -4627,16 +4654,16 @@
         <v>46190.70821390046</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I50" s="5">
         <v>46174</v>
@@ -4654,13 +4681,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4670,7 +4697,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B51" s="8">
         <v>46181.60909384259</v>
@@ -4682,16 +4709,16 @@
         <v>46190.7082228125</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I51" s="8">
         <v>46174</v>
@@ -4709,13 +4736,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4725,7 +4752,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B52" s="5">
         <v>46181.61221741898</v>
@@ -4737,16 +4764,16 @@
         <v>46190.708227337964</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I52" s="5">
         <v>46174</v>
@@ -4764,13 +4791,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4780,7 +4807,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B53" s="8">
         <v>46181.612357199076</v>
@@ -4792,16 +4819,16 @@
         <v>46190.708233321755</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I53" s="8">
         <v>46174</v>
@@ -4819,13 +4846,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -4835,7 +4862,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B54" s="5">
         <v>46181.609098182875</v>
@@ -4847,16 +4874,16 @@
         <v>46197.71584820602</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I54" s="5">
         <v>46227</v>
@@ -4874,13 +4901,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q54" s="5">
         <v>46227</v>
@@ -4889,18 +4916,18 @@
         <v>46246</v>
       </c>
       <c r="S54" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T54" s="6">
         <v>1</v>
       </c>
       <c r="U54" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B55" s="8">
         <v>46181.60910252314</v>
@@ -4912,16 +4939,16 @@
         <v>46191.54270819444</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I55" s="8">
         <v>46227</v>
@@ -4939,13 +4966,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4955,7 +4982,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B56" s="5">
         <v>46181.609107951386</v>
@@ -4967,16 +4994,16 @@
         <v>46191.54271703704</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I56" s="5">
         <v>46227</v>
@@ -4994,13 +5021,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5010,7 +5037,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B57" s="8">
         <v>46181.61393570602</v>
@@ -5022,16 +5049,16 @@
         <v>46190.70842170139</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I57" s="8">
         <v>46227</v>
@@ -5049,13 +5076,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5065,7 +5092,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B58" s="5">
         <v>46181.61396929398</v>
@@ -5077,16 +5104,16 @@
         <v>46190.708426550926</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I58" s="5">
         <v>46227</v>
@@ -5104,13 +5131,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5120,7 +5147,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B59" s="8">
         <v>46181.60911329861</v>
@@ -5132,16 +5159,16 @@
         <v>46191.54539826389</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I59" s="8">
         <v>46247</v>
@@ -5159,13 +5186,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q59" s="8">
         <v>46247</v>
@@ -5174,18 +5201,18 @@
         <v>46247</v>
       </c>
       <c r="S59" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T59" s="9">
         <v>1</v>
       </c>
       <c r="U59" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B60" s="5">
         <v>46181.60912350695</v>
@@ -5197,16 +5224,16 @@
         <v>46191.54536050926</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I60" s="6"/>
       <c r="J60" s="5">
@@ -5222,13 +5249,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5238,7 +5265,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B61" s="8">
         <v>46181.60912782408</v>
@@ -5250,16 +5277,16 @@
         <v>46191.54537386574</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I61" s="9"/>
       <c r="J61" s="8">
@@ -5275,13 +5302,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5291,7 +5318,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B62" s="5">
         <v>46181.614119606485</v>
@@ -5303,16 +5330,16 @@
         <v>46190.721725358795</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I62" s="6"/>
       <c r="J62" s="5">
@@ -5328,10 +5355,10 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5344,7 +5371,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B63" s="8">
         <v>46181.61419627315</v>
@@ -5356,16 +5383,16 @@
         <v>46190.7217299537</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I63" s="9"/>
       <c r="J63" s="8">
@@ -5381,10 +5408,10 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5397,7 +5424,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B64" s="5">
         <v>46181.60913207176</v>
@@ -5407,16 +5434,16 @@
         <v>46212.622826203704</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I64" s="5">
         <v>46322</v>
@@ -5434,10 +5461,10 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>26</v>
@@ -5449,18 +5476,18 @@
         <v>46322</v>
       </c>
       <c r="S64" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T64" s="6">
         <v>0</v>
       </c>
       <c r="U64" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B65" s="8">
         <v>46181.609135833336</v>
@@ -5470,16 +5497,16 @@
         <v>46182.63311847222</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I65" s="8">
         <v>46322</v>
@@ -5497,13 +5524,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5513,7 +5540,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B66" s="5">
         <v>46181.614311909725</v>
@@ -5523,16 +5550,16 @@
         <v>46182.63311923611</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I66" s="5">
         <v>46322</v>
@@ -5550,13 +5577,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5566,7 +5593,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B67" s="8">
         <v>46181.60918671296</v>
@@ -5576,7 +5603,7 @@
         <v>46213.569374502316</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>25</v>
@@ -5600,7 +5627,7 @@
         <v>26</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>26</v>
@@ -5613,7 +5640,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B68" s="5">
         <v>46181.609196087964</v>
@@ -5625,16 +5652,16 @@
         <v>46213.56938424769</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I68" s="5">
         <v>46252</v>
@@ -5652,13 +5679,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q68" s="5">
         <v>46252</v>
@@ -5667,18 +5694,18 @@
         <v>46253</v>
       </c>
       <c r="S68" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T68" s="6">
         <v>1</v>
       </c>
       <c r="U68" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B69" s="8">
         <v>46181.609201921296</v>
@@ -5688,16 +5715,16 @@
         <v>46213.56940306713</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I69" s="8">
         <v>46254</v>
@@ -5715,13 +5742,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q69" s="8">
         <v>46254</v>
@@ -5730,18 +5757,18 @@
         <v>46255</v>
       </c>
       <c r="S69" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T69" s="9">
         <v>0</v>
       </c>
       <c r="U69" s="12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B70" s="5">
         <v>46181.60920746528</v>
@@ -5753,16 +5780,16 @@
         <v>46213.569400231485</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I70" s="5">
         <v>46252</v>
@@ -5780,13 +5807,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q70" s="5">
         <v>46252</v>
@@ -5795,18 +5822,18 @@
         <v>46253</v>
       </c>
       <c r="S70" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T70" s="6">
         <v>1</v>
       </c>
       <c r="U70" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B71" s="8">
         <v>46181.609212870375</v>
@@ -5816,16 +5843,16 @@
         <v>46213.569403009256</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I71" s="8">
         <v>46254</v>
@@ -5843,13 +5870,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q71" s="8">
         <v>46254</v>
@@ -5858,18 +5885,18 @@
         <v>46255</v>
       </c>
       <c r="S71" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T71" s="9">
         <v>0</v>
       </c>
       <c r="U71" s="12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B72" s="5">
         <v>46181.60921715278</v>
@@ -5881,16 +5908,16 @@
         <v>46213.569419479165</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I72" s="5">
         <v>46252</v>
@@ -5908,13 +5935,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q72" s="5">
         <v>46252</v>
@@ -5923,18 +5950,18 @@
         <v>46253</v>
       </c>
       <c r="S72" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T72" s="6">
         <v>1</v>
       </c>
       <c r="U72" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B73" s="8">
         <v>46181.60922180556</v>
@@ -5944,16 +5971,16 @@
         <v>46213.56941956018</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I73" s="8">
         <v>46254</v>
@@ -5971,13 +5998,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q73" s="8">
         <v>46254</v>
@@ -5986,18 +6013,18 @@
         <v>46255</v>
       </c>
       <c r="S73" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T73" s="9">
         <v>0</v>
       </c>
       <c r="U73" s="12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B74" s="5">
         <v>46181.60922590278</v>
@@ -6007,7 +6034,7 @@
         <v>46181.782424143516</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>25</v>
@@ -6031,7 +6058,7 @@
         <v>26</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>26</v>
@@ -6044,7 +6071,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B75" s="8">
         <v>46181.60922940972</v>
@@ -6054,16 +6081,16 @@
         <v>46213.578914004625</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I75" s="8">
         <v>46258</v>
@@ -6081,13 +6108,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q75" s="8">
         <v>46258</v>
@@ -6096,18 +6123,18 @@
         <v>46266</v>
       </c>
       <c r="S75" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T75" s="9">
         <v>0</v>
       </c>
       <c r="U75" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B76" s="5">
         <v>46181.60923553241</v>
@@ -6117,16 +6144,16 @@
         <v>46204.88313940972</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I76" s="5">
         <v>46258</v>
@@ -6144,13 +6171,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6160,7 +6187,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B77" s="8">
         <v>46181.609241805556</v>
@@ -6170,16 +6197,16 @@
         <v>46182.63598342593</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I77" s="8">
         <v>46258</v>
@@ -6197,13 +6224,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
@@ -6213,7 +6240,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B78" s="5">
         <v>46181.6145286574</v>
@@ -6223,16 +6250,16 @@
         <v>46182.63598072917</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I78" s="5">
         <v>46258</v>
@@ -6250,10 +6277,10 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6266,7 +6293,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B79" s="8">
         <v>46181.61460722222</v>
@@ -6276,16 +6303,16 @@
         <v>46182.63597787037</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I79" s="8">
         <v>46258</v>
@@ -6303,10 +6330,10 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P79" s="9" t="s">
         <v>26</v>
@@ -6319,7 +6346,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B80" s="5">
         <v>46181.61464366898</v>
@@ -6329,16 +6356,16 @@
         <v>46182.635973807875</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I80" s="5">
         <v>46258</v>
@@ -6356,10 +6383,10 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>26</v>
@@ -6372,7 +6399,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B81" s="8">
         <v>46181.609247002314</v>
@@ -6382,16 +6409,16 @@
         <v>46212.62258834491</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I81" s="8">
         <v>46267</v>
@@ -6409,13 +6436,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q81" s="8">
         <v>46267</v>
@@ -6424,18 +6451,18 @@
         <v>46288</v>
       </c>
       <c r="S81" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T81" s="9">
         <v>0</v>
       </c>
       <c r="U81" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B82" s="5">
         <v>46181.60925648148</v>
@@ -6445,16 +6472,16 @@
         <v>46191.54540523148</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I82" s="5">
         <v>46267</v>
@@ -6472,13 +6499,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6488,7 +6515,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B83" s="8">
         <v>46181.609262199076</v>
@@ -6498,16 +6525,16 @@
         <v>46191.54540574074</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I83" s="8">
         <v>46267</v>
@@ -6525,13 +6552,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6541,7 +6568,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B84" s="5">
         <v>46181.61473356481</v>
@@ -6551,16 +6578,16 @@
         <v>46182.64084413194</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I84" s="5">
         <v>46267</v>
@@ -6578,13 +6605,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6594,7 +6621,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B85" s="8">
         <v>46181.61477212963</v>
@@ -6604,16 +6631,16 @@
         <v>46182.64084086806</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I85" s="8">
         <v>46267</v>
@@ -6631,13 +6658,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -6647,7 +6674,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B86" s="5">
         <v>46181.61484836806</v>
@@ -6657,16 +6684,16 @@
         <v>46182.6408357176</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I86" s="5">
         <v>46267</v>
@@ -6684,13 +6711,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6700,7 +6727,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B87" s="8">
         <v>46181.60926783565</v>
@@ -6710,16 +6737,16 @@
         <v>46212.62263724537</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I87" s="8">
         <v>46289</v>
@@ -6737,13 +6764,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q87" s="8">
         <v>46289</v>
@@ -6752,18 +6779,18 @@
         <v>46289</v>
       </c>
       <c r="S87" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T87" s="9">
         <v>0</v>
       </c>
       <c r="U87" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B88" s="5">
         <v>46181.60927226851</v>
@@ -6773,16 +6800,16 @@
         <v>46191.545403842596</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I88" s="5">
         <v>46289</v>
@@ -6800,13 +6827,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6816,7 +6843,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B89" s="8">
         <v>46181.60927799769</v>
@@ -6826,16 +6853,16 @@
         <v>46191.545404212964</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I89" s="8">
         <v>46289</v>
@@ -6853,13 +6880,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -6869,7 +6896,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B90" s="5">
         <v>46181.614954062505</v>
@@ -6879,16 +6906,16 @@
         <v>46182.64096971064</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I90" s="5">
         <v>46289</v>
@@ -6906,13 +6933,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6922,7 +6949,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B91" s="8">
         <v>46181.61498993056</v>
@@ -6932,16 +6959,16 @@
         <v>46182.64096709491</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I91" s="8">
         <v>46289</v>
@@ -6959,13 +6986,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -6975,7 +7002,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B92" s="5">
         <v>46181.61502625</v>
@@ -6985,16 +7012,16 @@
         <v>46182.64096319444</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I92" s="5">
         <v>46289</v>
@@ -7012,13 +7039,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7028,7 +7055,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B93" s="8">
         <v>46181.60928361111</v>
@@ -7038,7 +7065,7 @@
         <v>46213.56805377315</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>25</v>
@@ -7062,7 +7089,7 @@
         <v>26</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P93" s="9" t="s">
         <v>26</v>
@@ -7072,12 +7099,12 @@
       <c r="S93" s="9"/>
       <c r="T93" s="9"/>
       <c r="U93" s="12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B94" s="5">
         <v>46181.609286990744</v>
@@ -7089,16 +7116,16 @@
         <v>46213.56773226852</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I94" s="5">
         <v>46182</v>
@@ -7116,13 +7143,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q94" s="5">
         <v>46182</v>
@@ -7131,18 +7158,18 @@
         <v>46183</v>
       </c>
       <c r="S94" s="11" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="T94" s="6">
         <v>1</v>
       </c>
       <c r="U94" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B95" s="8">
         <v>46181.609292974535</v>
@@ -7154,16 +7181,16 @@
         <v>46213.56774653935</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I95" s="8">
         <v>46290</v>
@@ -7181,13 +7208,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q95" s="8">
         <v>46290</v>
@@ -7196,18 +7223,18 @@
         <v>46293</v>
       </c>
       <c r="S95" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T95" s="9">
         <v>1</v>
       </c>
       <c r="U95" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B96" s="5">
         <v>46181.60929881944</v>
@@ -7219,16 +7246,16 @@
         <v>46213.56805165509</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I96" s="5">
         <v>46226</v>
@@ -7246,13 +7273,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q96" s="5">
         <v>46226</v>
@@ -7261,18 +7288,18 @@
         <v>46227</v>
       </c>
       <c r="S96" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T96" s="6">
         <v>1</v>
       </c>
       <c r="U96" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B97" s="8">
         <v>46181.60930480324</v>
@@ -7282,16 +7309,16 @@
         <v>46212.623013958335</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I97" s="8">
         <v>46293</v>
@@ -7309,13 +7336,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q97" s="8">
         <v>46293</v>
@@ -7324,18 +7351,18 @@
         <v>46294</v>
       </c>
       <c r="S97" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T97" s="9">
         <v>0</v>
       </c>
       <c r="U97" s="12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B98" s="5">
         <v>46181.60935271991</v>
@@ -7345,16 +7372,16 @@
         <v>46212.6232265162</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I98" s="5">
         <v>46226</v>
@@ -7372,13 +7399,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q98" s="5">
         <v>46226</v>
@@ -7387,18 +7414,18 @@
         <v>46227</v>
       </c>
       <c r="S98" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T98" s="6">
         <v>0</v>
       </c>
       <c r="U98" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B99" s="8">
         <v>46181.60936674768</v>
@@ -7408,7 +7435,7 @@
         <v>46213.50490068287</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>25</v>
@@ -7432,7 +7459,7 @@
         <v>26</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P99" s="9" t="s">
         <v>26</v>
@@ -7445,7 +7472,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B100" s="5">
         <v>46181.609371666666</v>
@@ -7455,16 +7482,16 @@
         <v>46182.64123547454</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I100" s="5">
         <v>46290</v>
@@ -7482,13 +7509,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q100" s="5">
         <v>46290</v>
@@ -7497,18 +7524,18 @@
         <v>46310</v>
       </c>
       <c r="S100" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T100" s="6">
         <v>0</v>
       </c>
       <c r="U100" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B101" s="8">
         <v>46181.609378587964</v>
@@ -7518,16 +7545,16 @@
         <v>46182.64119599537</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I101" s="8">
         <v>46290</v>
@@ -7545,13 +7572,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7561,7 +7588,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B102" s="5">
         <v>46181.61514019676</v>
@@ -7571,16 +7598,16 @@
         <v>46182.64119222222</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I102" s="5">
         <v>46290</v>
@@ -7598,13 +7625,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7614,7 +7641,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B103" s="8">
         <v>46181.609386111115</v>
@@ -7626,16 +7653,16 @@
         <v>46212.62246368056</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I103" s="8">
         <v>46311</v>
@@ -7653,13 +7680,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q103" s="8">
         <v>46311</v>
@@ -7668,18 +7695,18 @@
         <v>46314</v>
       </c>
       <c r="S103" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T103" s="9">
         <v>1</v>
       </c>
       <c r="U103" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B104" s="5">
         <v>46181.60939194444</v>
@@ -7691,16 +7718,16 @@
         <v>46213.56773570602</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I104" s="5">
         <v>46311</v>
@@ -7718,13 +7745,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7734,7 +7761,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B105" s="8">
         <v>46181.61518315972</v>
@@ -7746,16 +7773,16 @@
         <v>46213.567735150464</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H105" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I105" s="8">
         <v>46311</v>
@@ -7773,10 +7800,10 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P105" s="9" t="s">
         <v>26</v>
@@ -7789,7 +7816,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B106" s="5">
         <v>46181.60939866898</v>
@@ -7801,16 +7828,16 @@
         <v>46213.50490375</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I106" s="5">
         <v>46315</v>
@@ -7828,13 +7855,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q106" s="5">
         <v>46315</v>
@@ -7843,18 +7870,18 @@
         <v>46316</v>
       </c>
       <c r="S106" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T106" s="6">
         <v>1</v>
       </c>
       <c r="U106" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B107" s="8">
         <v>46181.60940505787</v>
@@ -7866,16 +7893,16 @@
         <v>46213.56772277778</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H107" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I107" s="8">
         <v>46315</v>
@@ -7893,13 +7920,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -7909,7 +7936,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B108" s="5">
         <v>46181.61523613426</v>
@@ -7921,16 +7948,16 @@
         <v>46213.56772202546</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I108" s="5">
         <v>46315</v>
@@ -7948,10 +7975,10 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>26</v>
@@ -7964,7 +7991,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B109" s="8">
         <v>46181.60941365741</v>
@@ -7974,16 +8001,16 @@
         <v>46212.62250564815</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H109" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I109" s="8">
         <v>46317</v>
@@ -8001,13 +8028,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q109" s="8">
         <v>46317</v>
@@ -8016,18 +8043,18 @@
         <v>46318</v>
       </c>
       <c r="S109" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T109" s="9">
         <v>0</v>
       </c>
       <c r="U109" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B110" s="5">
         <v>46181.60941929398</v>
@@ -8037,16 +8064,16 @@
         <v>46213.56804261574</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I110" s="5">
         <v>46317</v>
@@ -8064,13 +8091,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8080,7 +8107,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B111" s="8">
         <v>46181.61528053241</v>
@@ -8090,16 +8117,16 @@
         <v>46213.568041192135</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I111" s="8">
         <v>46317</v>
@@ -8117,10 +8144,10 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P111" s="9" t="s">
         <v>26</v>
@@ -8133,7 +8160,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B112" s="5">
         <v>46181.60942706019</v>
@@ -8143,16 +8170,16 @@
         <v>46212.62252259259</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I112" s="5">
         <v>46321</v>
@@ -8170,13 +8197,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q112" s="5">
         <v>46321</v>
@@ -8185,18 +8212,18 @@
         <v>46321</v>
       </c>
       <c r="S112" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T112" s="6">
         <v>0</v>
       </c>
       <c r="U112" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B113" s="8">
         <v>46181.60943415509</v>
@@ -8206,16 +8233,16 @@
         <v>46182.641623125004</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I113" s="8">
         <v>46321</v>
@@ -8233,13 +8260,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8249,7 +8276,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B114" s="5">
         <v>46181.61532783565</v>
@@ -8259,16 +8286,16 @@
         <v>46182.64161924769</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I114" s="5">
         <v>46321</v>
@@ -8286,13 +8313,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8302,7 +8329,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B115" s="8">
         <v>46181.60944410879</v>
@@ -8312,16 +8339,16 @@
         <v>46212.622555497685</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I115" s="8">
         <v>46323</v>
@@ -8339,13 +8366,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q115" s="8">
         <v>46323</v>
@@ -8354,18 +8381,18 @@
         <v>46323</v>
       </c>
       <c r="S115" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T115" s="9">
         <v>0</v>
       </c>
       <c r="U115" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B116" s="5">
         <v>46181.60944996528</v>
@@ -8375,16 +8402,16 @@
         <v>46182.64173178241</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I116" s="5">
         <v>46323</v>
@@ -8402,13 +8429,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8418,7 +8445,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B117" s="8">
         <v>46181.61537143518</v>
@@ -8428,16 +8455,16 @@
         <v>46182.64172883102</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I117" s="8">
         <v>46323</v>
@@ -8455,10 +8482,10 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P117" s="9" t="s">
         <v>26</v>
@@ -8471,7 +8498,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B118" s="5">
         <v>46181.60945642361</v>
@@ -8481,7 +8508,7 @@
         <v>46182.634494212965</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>25</v>
@@ -8505,7 +8532,7 @@
         <v>26</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>26</v>
@@ -8518,7 +8545,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B119" s="8">
         <v>46181.60946096065</v>
@@ -8528,16 +8555,16 @@
         <v>46182.64186350694</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H119" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I119" s="8">
         <v>46324</v>
@@ -8555,13 +8582,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q119" s="8">
         <v>46324</v>
@@ -8570,18 +8597,18 @@
         <v>46324</v>
       </c>
       <c r="S119" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T119" s="9">
         <v>0</v>
       </c>
       <c r="U119" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B120" s="5">
         <v>46181.60946868056</v>
@@ -8591,16 +8618,16 @@
         <v>46182.641845254635</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I120" s="5">
         <v>46324</v>
@@ -8618,13 +8645,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8634,7 +8661,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B121" s="8">
         <v>46181.609475034726</v>
@@ -8644,16 +8671,16 @@
         <v>46182.64184081019</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H121" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I121" s="8">
         <v>46324</v>
@@ -8671,13 +8698,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8687,7 +8714,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B122" s="5">
         <v>46181.60947921296</v>
@@ -8697,16 +8724,16 @@
         <v>46182.641837766205</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I122" s="5">
         <v>46324</v>
@@ -8724,13 +8751,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8740,7 +8767,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B123" s="8">
         <v>46181.61605960648</v>
@@ -8750,16 +8777,16 @@
         <v>46182.641834548616</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H123" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I123" s="8">
         <v>46324</v>
@@ -8777,13 +8804,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q123" s="9"/>
       <c r="R123" s="9"/>
@@ -8793,7 +8820,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B124" s="5">
         <v>46181.61617203704</v>
@@ -8803,16 +8830,16 @@
         <v>46182.64182482639</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I124" s="5">
         <v>46324</v>
@@ -8830,13 +8857,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8846,7 +8873,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B125" s="8">
         <v>46181.61620771991</v>
@@ -8856,16 +8883,16 @@
         <v>46182.64182413195</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H125" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I125" s="8">
         <v>46324</v>
@@ -8883,13 +8910,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -8899,7 +8926,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B126" s="5">
         <v>46181.616245833335</v>
@@ -8909,16 +8936,16 @@
         <v>46182.641823425925</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I126" s="5">
         <v>46324</v>
@@ -8936,13 +8963,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -8952,7 +8979,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B127" s="8">
         <v>46181.60948424769</v>
@@ -8962,16 +8989,16 @@
         <v>46182.64199267361</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H127" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I127" s="8">
         <v>46325</v>
@@ -8989,13 +9016,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q127" s="8">
         <v>46325</v>
@@ -9004,18 +9031,18 @@
         <v>46325</v>
       </c>
       <c r="S127" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T127" s="9">
         <v>0</v>
       </c>
       <c r="U127" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B128" s="5">
         <v>46181.60948969907</v>
@@ -9025,16 +9052,16 @@
         <v>46182.641973854166</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I128" s="5">
         <v>46325</v>
@@ -9052,13 +9079,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9068,7 +9095,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B129" s="8">
         <v>46181.60949538194</v>
@@ -9078,16 +9105,16 @@
         <v>46182.64197085648</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I129" s="8">
         <v>46325</v>
@@ -9105,13 +9132,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q129" s="9"/>
       <c r="R129" s="9"/>
@@ -9121,7 +9148,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B130" s="5">
         <v>46181.609560185185</v>
@@ -9131,16 +9158,16 @@
         <v>46182.641967118056</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I130" s="5">
         <v>46325</v>
@@ -9158,13 +9185,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9174,7 +9201,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B131" s="8">
         <v>46181.61659114584</v>
@@ -9184,16 +9211,16 @@
         <v>46182.64196408565</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I131" s="8">
         <v>46325</v>
@@ -9211,13 +9238,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
@@ -9227,7 +9254,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B132" s="5">
         <v>46181.61662431713</v>
@@ -9237,16 +9264,16 @@
         <v>46182.64196105324</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I132" s="5">
         <v>46325</v>
@@ -9264,13 +9291,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9280,7 +9307,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B133" s="8">
         <v>46181.61666238426</v>
@@ -9290,16 +9317,16 @@
         <v>46182.64195453704</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I133" s="8">
         <v>46325</v>
@@ -9317,13 +9344,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9333,7 +9360,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B134" s="5">
         <v>46181.61670006944</v>
@@ -9343,16 +9370,16 @@
         <v>46182.64195372685</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I134" s="5">
         <v>46325</v>
@@ -9370,13 +9397,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9386,7 +9413,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B135" s="8">
         <v>46181.60956560185</v>
@@ -9396,16 +9423,16 @@
         <v>46182.82952324074</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I135" s="8">
         <v>46328</v>
@@ -9423,13 +9450,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q135" s="8">
         <v>46328</v>
@@ -9438,18 +9465,18 @@
         <v>46328</v>
       </c>
       <c r="S135" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T135" s="9">
         <v>0</v>
       </c>
       <c r="U135" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B136" s="5">
         <v>46181.60957188657</v>
@@ -9459,16 +9486,16 @@
         <v>46182.82945300926</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I136" s="5">
         <v>46328</v>
@@ -9486,13 +9513,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9502,7 +9529,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B137" s="8">
         <v>46181.609583576384</v>
@@ -9512,16 +9539,16 @@
         <v>46182.829453784725</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I137" s="8">
         <v>46328</v>
@@ -9539,13 +9566,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q137" s="9"/>
       <c r="R137" s="9"/>
@@ -9555,7 +9582,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B138" s="5">
         <v>46181.60958841435</v>
@@ -9565,16 +9592,16 @@
         <v>46182.829454583334</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I138" s="5">
         <v>46328</v>
@@ -9592,13 +9619,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9608,7 +9635,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B139" s="8">
         <v>46181.616839849536</v>
@@ -9618,16 +9645,16 @@
         <v>46182.829455706014</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I139" s="8">
         <v>46328</v>
@@ -9645,13 +9672,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
@@ -9661,7 +9688,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B140" s="5">
         <v>46181.61689748843</v>
@@ -9671,16 +9698,16 @@
         <v>46182.8294564699</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I140" s="5">
         <v>46328</v>
@@ -9698,13 +9725,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9714,7 +9741,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B141" s="8">
         <v>46181.616942569446</v>
@@ -9724,16 +9751,16 @@
         <v>46182.82945721065</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I141" s="8">
         <v>46328</v>
@@ -9751,13 +9778,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -9767,7 +9794,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B142" s="5">
         <v>46181.6169815162</v>
@@ -9777,16 +9804,16 @@
         <v>46182.82945796296</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I142" s="5">
         <v>46328</v>
@@ -9804,13 +9831,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9820,7 +9847,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B143" s="8">
         <v>46181.609592673616</v>
@@ -9830,16 +9857,16 @@
         <v>46182.642407384265</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I143" s="8">
         <v>46329</v>
@@ -9857,13 +9884,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q143" s="8">
         <v>46329</v>
@@ -9872,18 +9899,18 @@
         <v>46329</v>
       </c>
       <c r="S143" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T143" s="9">
         <v>0</v>
       </c>
       <c r="U143" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B144" s="5">
         <v>46181.60960517361</v>
@@ -9893,16 +9920,16 @@
         <v>46182.8294527199</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I144" s="5">
         <v>46329</v>
@@ -9920,13 +9947,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -9936,7 +9963,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B145" s="8">
         <v>46181.609610011576</v>
@@ -9946,16 +9973,16 @@
         <v>46182.829451909725</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H145" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I145" s="8">
         <v>46329</v>
@@ -9973,10 +10000,10 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P145" s="9" t="s">
         <v>26</v>
@@ -9989,7 +10016,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B146" s="5">
         <v>46181.609613796296</v>
@@ -9999,16 +10026,16 @@
         <v>46182.829452025464</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I146" s="5">
         <v>46329</v>
@@ -10026,10 +10053,10 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P146" s="6" t="s">
         <v>26</v>
@@ -10042,7 +10069,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B147" s="8">
         <v>46181.61712142361</v>
@@ -10052,16 +10079,16 @@
         <v>46182.82945197917</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I147" s="8">
         <v>46329</v>
@@ -10079,10 +10106,10 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P147" s="9" t="s">
         <v>26</v>
@@ -10095,7 +10122,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B148" s="5">
         <v>46181.61716094907</v>
@@ -10105,16 +10132,16 @@
         <v>46182.82945207176</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I148" s="5">
         <v>46329</v>
@@ -10132,10 +10159,10 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P148" s="6" t="s">
         <v>26</v>
@@ -10148,7 +10175,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B149" s="8">
         <v>46181.61719633102</v>
@@ -10158,16 +10185,16 @@
         <v>46182.829452025464</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H149" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I149" s="8">
         <v>46329</v>
@@ -10185,10 +10212,10 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P149" s="9" t="s">
         <v>26</v>
@@ -10201,7 +10228,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B150" s="5">
         <v>46181.617235451384</v>
@@ -10211,16 +10238,16 @@
         <v>46182.829452418984</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I150" s="5">
         <v>46329</v>
@@ -10238,10 +10265,10 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P150" s="6" t="s">
         <v>26</v>
@@ -10254,7 +10281,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B151" s="8">
         <v>46181.60961741898</v>
@@ -10264,7 +10291,7 @@
         <v>46182.63449439815</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>25</v>
@@ -10288,7 +10315,7 @@
         <v>26</v>
       </c>
       <c r="O151" s="9" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="P151" s="9" t="s">
         <v>26</v>
@@ -10301,7 +10328,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B152" s="5">
         <v>46181.60962174769</v>
@@ -10311,16 +10338,16 @@
         <v>46182.64244836806</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="I152" s="5">
         <v>46330</v>
@@ -10338,13 +10365,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q152" s="5">
         <v>46330</v>
@@ -10353,18 +10380,18 @@
         <v>46337</v>
       </c>
       <c r="S152" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T152" s="6">
         <v>0</v>
       </c>
       <c r="U152" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B153" s="8">
         <v>46181.60962780092</v>
@@ -10374,7 +10401,7 @@
         <v>46191.67892958333</v>
       </c>
       <c r="E153" s="9" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F153" s="9" t="s">
         <v>26</v>
@@ -10401,13 +10428,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="9" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O153" s="9" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="P153" s="9" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q153" s="8">
         <v>46330</v>
@@ -10416,18 +10443,18 @@
         <v>46337</v>
       </c>
       <c r="S153" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T153" s="9">
         <v>0</v>
       </c>
       <c r="U153" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B154" s="5">
         <v>46181.60963489584</v>
@@ -10437,7 +10464,7 @@
         <v>46182.63449431713</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>25</v>
@@ -10461,7 +10488,7 @@
         <v>26</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="P154" s="6" t="s">
         <v>26</v>
@@ -10469,18 +10496,18 @@
       <c r="Q154" s="6"/>
       <c r="R154" s="6"/>
       <c r="S154" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T154" s="6">
         <v>0</v>
       </c>
       <c r="U154" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B155" s="8">
         <v>46181.609640208335</v>
@@ -10490,16 +10517,16 @@
         <v>46182.64254377315</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G155" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H155" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I155" s="8">
         <v>46330</v>
@@ -10517,13 +10544,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="9" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O155" s="9" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="P155" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q155" s="8">
         <v>46330</v>
@@ -10532,18 +10559,18 @@
         <v>46338</v>
       </c>
       <c r="S155" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T155" s="9">
         <v>0</v>
       </c>
       <c r="U155" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B156" s="5">
         <v>46181.609646365745</v>
@@ -10553,16 +10580,16 @@
         <v>46182.64254079861</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I156" s="5">
         <v>46339</v>
@@ -10580,13 +10607,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q156" s="5">
         <v>46339</v>
@@ -10595,13 +10622,13 @@
         <v>46349</v>
       </c>
       <c r="S156" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T156" s="6">
         <v>0</v>
       </c>
       <c r="U156" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46213.578914004625</v>
+        <v>46216.54998206018</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>241</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1818" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1819" uniqueCount="396">
   <si>
     <t>50001559 - FERROVIAL</t>
   </si>
@@ -5598,9 +5598,11 @@
       <c r="B67" s="8">
         <v>46181.60918671296</v>
       </c>
-      <c r="C67" s="9"/>
+      <c r="C67" s="8">
+        <v>46216.64128039352</v>
+      </c>
       <c r="D67" s="8">
-        <v>46213.569374502316</v>
+        <v>46216.64129429398</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>216</v>
@@ -5635,8 +5637,12 @@
       <c r="Q67" s="9"/>
       <c r="R67" s="9"/>
       <c r="S67" s="9"/>
-      <c r="T67" s="9"/>
-      <c r="U67" s="9"/>
+      <c r="T67" s="9">
+        <v>1</v>
+      </c>
+      <c r="U67" s="10" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
@@ -5710,9 +5716,11 @@
       <c r="B69" s="8">
         <v>46181.609201921296</v>
       </c>
-      <c r="C69" s="9"/>
+      <c r="C69" s="8">
+        <v>46216.6412221875</v>
+      </c>
       <c r="D69" s="8">
-        <v>46213.56940306713</v>
+        <v>46216.641245011575</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>224</v>
@@ -5760,10 +5768,10 @@
         <v>32</v>
       </c>
       <c r="T69" s="9">
-        <v>0</v>
-      </c>
-      <c r="U69" s="12" t="s">
-        <v>121</v>
+        <v>1</v>
+      </c>
+      <c r="U69" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -5838,9 +5846,11 @@
       <c r="B71" s="8">
         <v>46181.609212870375</v>
       </c>
-      <c r="C71" s="9"/>
+      <c r="C71" s="8">
+        <v>46216.641230636575</v>
+      </c>
       <c r="D71" s="8">
-        <v>46213.569403009256</v>
+        <v>46216.641249629625</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>231</v>
@@ -5888,10 +5898,10 @@
         <v>32</v>
       </c>
       <c r="T71" s="9">
-        <v>0</v>
-      </c>
-      <c r="U71" s="12" t="s">
-        <v>121</v>
+        <v>1</v>
+      </c>
+      <c r="U71" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
@@ -5966,9 +5976,11 @@
       <c r="B73" s="8">
         <v>46181.60922180556</v>
       </c>
-      <c r="C73" s="9"/>
+      <c r="C73" s="8">
+        <v>46216.64126351852</v>
+      </c>
       <c r="D73" s="8">
-        <v>46213.56941956018</v>
+        <v>46216.641280717595</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>235</v>
@@ -6016,10 +6028,10 @@
         <v>32</v>
       </c>
       <c r="T73" s="9">
-        <v>0</v>
-      </c>
-      <c r="U73" s="12" t="s">
-        <v>121</v>
+        <v>1</v>
+      </c>
+      <c r="U73" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
@@ -6141,7 +6153,7 @@
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46204.88313940972</v>
+        <v>46216.641273009256</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>182</v>
@@ -6194,7 +6206,7 @@
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46182.63598342593</v>
+        <v>46216.64127412037</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>182</v>
@@ -6247,7 +6259,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46182.63598072917</v>
+        <v>46216.64126927083</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>187</v>
@@ -6300,7 +6312,7 @@
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46182.63597787037</v>
+        <v>46216.64127059028</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>190</v>
@@ -6353,7 +6365,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46182.635973807875</v>
+        <v>46216.641271817134</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>192</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1819" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1720" uniqueCount="381">
   <si>
     <t>50001559 - FERROVIAL</t>
   </si>
@@ -757,7 +757,7 @@
     <t>Recepcion Materiales corte plasma OT 4347,Recepcion materiales corte laser OT 4347</t>
   </si>
   <si>
-    <t>OT 4349- CODO 90° Ø1600MM,OT 4350 - CODO 135° Ø1600MM,OT 4351 - DUCTO Ø1600MM L:1800MM,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Bodega:,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Bodega:,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
   </si>
   <si>
     <t>1215506984940169</t>
@@ -775,7 +775,7 @@
     <t>Control de calidad Corte plasma OT 4347</t>
   </si>
   <si>
-    <t>OT 4349- CODO 90° Ø1600MM,OT 4350 - CODO 135° Ø1600MM,OT 4351 - DUCTO Ø1600MM L:1800MM,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
   </si>
   <si>
     <t>1215506819763607</t>
@@ -814,9 +814,6 @@
     <t xml:space="preserve">OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT2 4307 ZVN 1-9-86/2 </t>
   </si>
   <si>
-    <t>OT 4349- CODO 90° Ø1600MM,OT 4350 - CODO 135° Ø1600MM,OT 4351 - DUCTO Ø1600MM L:1800MM,Caldereria:</t>
-  </si>
-  <si>
     <t>1215506819773770</t>
   </si>
   <si>
@@ -832,27 +829,12 @@
     <t>Control de calidad Corte plasma OT 4347,Control de calidad Mecanizado OT 4347,control de calidad corte laser  OT 4347</t>
   </si>
   <si>
-    <t>1215504785833019</t>
-  </si>
-  <si>
-    <t>1215504802511713</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado OT 4347,control de calidad corte laser  OT 4347,Control de calidad Corte plasma OT 4347</t>
-  </si>
-  <si>
-    <t>1215504802511714</t>
-  </si>
-  <si>
     <t>1215506984972272</t>
   </si>
   <si>
     <t>OT 4347 Armado</t>
   </si>
   <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
-  </si>
-  <si>
     <t>1215506984982888</t>
   </si>
   <si>
@@ -865,24 +847,6 @@
     <t>1215506984982910</t>
   </si>
   <si>
-    <t>1215504802511715</t>
-  </si>
-  <si>
-    <t>OT1 4349- CODO 90° Ø1600MM</t>
-  </si>
-  <si>
-    <t>1215504802511716</t>
-  </si>
-  <si>
-    <t>OT2 4350 - CODO 135° Ø1600MM</t>
-  </si>
-  <si>
-    <t>1215504802511717</t>
-  </si>
-  <si>
-    <t>OT3 4351 - DUCTO Ø1600MM L:1800MM</t>
-  </si>
-  <si>
     <t>1215506984991511</t>
   </si>
   <si>
@@ -901,229 +865,220 @@
     <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347 Control de calidad Armado</t>
   </si>
   <si>
-    <t>1215504802511718</t>
-  </si>
-  <si>
-    <t>1215504802511719</t>
-  </si>
-  <si>
-    <t>1215504802511720</t>
+    <t>1215506929522878</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete OT 4347,Recepcion Alabe OT 4347,Recepcion motor OT 4347</t>
+  </si>
+  <si>
+    <t>1215506929522890</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete OT 4347</t>
+  </si>
+  <si>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Bodega:</t>
+  </si>
+  <si>
+    <t>1215506992958412</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe OT 4347</t>
+  </si>
+  <si>
+    <t>1215506992960641</t>
+  </si>
+  <si>
+    <t>Recepcion motor OT 4347</t>
+  </si>
+  <si>
+    <t>1215506992960663</t>
+  </si>
+  <si>
+    <t>Recepcion fabricación externa  OT 4347</t>
+  </si>
+  <si>
+    <t>Revestimiento,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
+  </si>
+  <si>
+    <t>1215506639143085</t>
+  </si>
+  <si>
+    <t>1215506993049488</t>
+  </si>
+  <si>
+    <t>Montaje:</t>
+  </si>
+  <si>
+    <t>Revestimiento, OT 4347 Montaje Alabe,OT 4347 Montaje Rodete,OT 4347 Pruebas FAT,OT 4347 Montaje motor,OT 4347 RE-PINTADO</t>
+  </si>
+  <si>
+    <t>1215506782065494</t>
+  </si>
+  <si>
+    <t>Revestimiento</t>
+  </si>
+  <si>
+    <t>Recepcion fabricación externa  OT 4347,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
+  </si>
+  <si>
+    <t>1215506782065516</t>
+  </si>
+  <si>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Recepcion fabricación externa  OT 4347</t>
+  </si>
+  <si>
+    <t>1215504802511721</t>
+  </si>
+  <si>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
+  </si>
+  <si>
+    <t>1215506782097502</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OT 4347 Montaje Alabe</t>
+  </si>
+  <si>
+    <t>1215506782097519</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe OT 4347,check planos</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> OT 4347 Montaje Alabe,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
+  </si>
+  <si>
+    <t>1215504802511722</t>
+  </si>
+  <si>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Recepcion Alabe OT 4347</t>
+  </si>
+  <si>
+    <t>1215506782097797</t>
+  </si>
+  <si>
+    <t>OT 4347 Montaje Rodete</t>
+  </si>
+  <si>
+    <t>1215506985116839</t>
+  </si>
+  <si>
+    <t>check planos,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Recepcion Rodete OT 4347</t>
+  </si>
+  <si>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347 Montaje Rodete</t>
+  </si>
+  <si>
+    <t>1215504802511723</t>
+  </si>
+  <si>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Recepcion Rodete OT 4347</t>
+  </si>
+  <si>
+    <t>1215506929643016</t>
+  </si>
+  <si>
+    <t>OT 4347 Montaje motor</t>
+  </si>
+  <si>
+    <t>1215506929643033</t>
+  </si>
+  <si>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Recepcion motor OT 4347,check planos</t>
+  </si>
+  <si>
+    <t>OT 4347 Montaje motor,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
+  </si>
+  <si>
+    <t>1215504802511724</t>
+  </si>
+  <si>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Recepcion motor OT 4347</t>
+  </si>
+  <si>
+    <t>1215506782124046</t>
+  </si>
+  <si>
+    <t>OT 4347 Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1215506782124063</t>
+  </si>
+  <si>
+    <t>OT 4347 Pruebas FAT,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
+  </si>
+  <si>
+    <t>1215504802511725</t>
+  </si>
+  <si>
+    <t>1215506929654031</t>
+  </si>
+  <si>
+    <t>OT 4347 RE-PINTADO</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente,Montaje:</t>
+  </si>
+  <si>
+    <t>1215506985153721</t>
+  </si>
+  <si>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347 RE-PINTADO</t>
+  </si>
+  <si>
+    <t>1215504802511726</t>
+  </si>
+  <si>
+    <t>1215506985153738</t>
+  </si>
+  <si>
+    <t>Logistica:</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente,Embalaje,PACKING LIST,Despacho</t>
+  </si>
+  <si>
+    <t>1215506782158182</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
+    <t>Karin Pinto</t>
+  </si>
+  <si>
+    <t>kpinto@zitron.com</t>
+  </si>
+  <si>
+    <t>Revision Tableros,OT 4347 RE-PINTADO,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
+  </si>
+  <si>
+    <t>1215506782158209</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
+  </si>
+  <si>
+    <t>1215506782162385</t>
+  </si>
+  <si>
+    <t>1215506782162397</t>
+  </si>
+  <si>
+    <t>1215504802511727</t>
+  </si>
+  <si>
+    <t>1215504802511728</t>
+  </si>
+  <si>
+    <t>1215504802511729</t>
+  </si>
+  <si>
+    <t>1215504802511730</t>
   </si>
   <si>
     <t>Ot 4351 - DUCTO Ø1600MM L:1800MM</t>
-  </si>
-  <si>
-    <t>1215506929522878</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete OT 4347,Recepcion Alabe OT 4347,Recepcion motor OT 4347</t>
-  </si>
-  <si>
-    <t>1215506929522890</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete OT 4347</t>
-  </si>
-  <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Bodega:</t>
-  </si>
-  <si>
-    <t>1215506992958412</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe OT 4347</t>
-  </si>
-  <si>
-    <t>1215506992960641</t>
-  </si>
-  <si>
-    <t>Recepcion motor OT 4347</t>
-  </si>
-  <si>
-    <t>1215506992960663</t>
-  </si>
-  <si>
-    <t>Recepcion fabricación externa  OT 4347</t>
-  </si>
-  <si>
-    <t>Revestimiento,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
-  </si>
-  <si>
-    <t>1215506639143085</t>
-  </si>
-  <si>
-    <t>1215506993049488</t>
-  </si>
-  <si>
-    <t>Montaje:</t>
-  </si>
-  <si>
-    <t>Revestimiento, OT 4347 Montaje Alabe,OT 4347 Montaje Rodete,OT 4347 Pruebas FAT,OT 4347 Montaje motor,OT 4347 RE-PINTADO</t>
-  </si>
-  <si>
-    <t>1215506782065494</t>
-  </si>
-  <si>
-    <t>Revestimiento</t>
-  </si>
-  <si>
-    <t>Recepcion fabricación externa  OT 4347,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
-  </si>
-  <si>
-    <t>1215506782065516</t>
-  </si>
-  <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Recepcion fabricación externa  OT 4347</t>
-  </si>
-  <si>
-    <t>1215504802511721</t>
-  </si>
-  <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
-  </si>
-  <si>
-    <t>1215506782097502</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OT 4347 Montaje Alabe</t>
-  </si>
-  <si>
-    <t>1215506782097519</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe OT 4347,check planos</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OT 4347 Montaje Alabe,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
-  </si>
-  <si>
-    <t>1215504802511722</t>
-  </si>
-  <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Recepcion Alabe OT 4347</t>
-  </si>
-  <si>
-    <t>1215506782097797</t>
-  </si>
-  <si>
-    <t>OT 4347 Montaje Rodete</t>
-  </si>
-  <si>
-    <t>1215506985116839</t>
-  </si>
-  <si>
-    <t>check planos,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Recepcion Rodete OT 4347</t>
-  </si>
-  <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347 Montaje Rodete</t>
-  </si>
-  <si>
-    <t>1215504802511723</t>
-  </si>
-  <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Recepcion Rodete OT 4347</t>
-  </si>
-  <si>
-    <t>1215506929643016</t>
-  </si>
-  <si>
-    <t>OT 4347 Montaje motor</t>
-  </si>
-  <si>
-    <t>1215506929643033</t>
-  </si>
-  <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Recepcion motor OT 4347,check planos</t>
-  </si>
-  <si>
-    <t>OT 4347 Montaje motor,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
-  </si>
-  <si>
-    <t>1215504802511724</t>
-  </si>
-  <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Recepcion motor OT 4347</t>
-  </si>
-  <si>
-    <t>1215506782124046</t>
-  </si>
-  <si>
-    <t>OT 4347 Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1215506782124063</t>
-  </si>
-  <si>
-    <t>OT 4347 Pruebas FAT,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
-  </si>
-  <si>
-    <t>1215504802511725</t>
-  </si>
-  <si>
-    <t>1215506929654031</t>
-  </si>
-  <si>
-    <t>OT 4347 RE-PINTADO</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente,Montaje:</t>
-  </si>
-  <si>
-    <t>1215506985153721</t>
-  </si>
-  <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347 RE-PINTADO</t>
-  </si>
-  <si>
-    <t>1215504802511726</t>
-  </si>
-  <si>
-    <t>1215506985153738</t>
-  </si>
-  <si>
-    <t>Logistica:</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente,Embalaje,PACKING LIST,Despacho</t>
-  </si>
-  <si>
-    <t>1215506782158182</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente</t>
-  </si>
-  <si>
-    <t>Karin Pinto</t>
-  </si>
-  <si>
-    <t>kpinto@zitron.com</t>
-  </si>
-  <si>
-    <t>Revision Tableros,OT 4347 RE-PINTADO,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
-  </si>
-  <si>
-    <t>1215506782158209</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
-  </si>
-  <si>
-    <t>1215506782162385</t>
-  </si>
-  <si>
-    <t>1215506782162397</t>
-  </si>
-  <si>
-    <t>1215504802511727</t>
-  </si>
-  <si>
-    <t>1215504802511728</t>
-  </si>
-  <si>
-    <t>1215504802511729</t>
-  </si>
-  <si>
-    <t>1215504802511730</t>
   </si>
   <si>
     <t>1215506819930034</t>
@@ -1788,7 +1743,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U156"/>
+  <dimension ref="A1:U147"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -5720,7 +5675,7 @@
         <v>46216.6412221875</v>
       </c>
       <c r="D69" s="8">
-        <v>46216.641245011575</v>
+        <v>46216.71548459491</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>224</v>
@@ -5850,7 +5805,7 @@
         <v>46216.641230636575</v>
       </c>
       <c r="D71" s="8">
-        <v>46216.641249629625</v>
+        <v>46216.715484733795</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>231</v>
@@ -5980,7 +5935,7 @@
         <v>46216.64126351852</v>
       </c>
       <c r="D73" s="8">
-        <v>46216.641280717595</v>
+        <v>46216.71548493055</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>235</v>
@@ -6090,7 +6045,7 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46216.54998206018</v>
+        <v>46216.71555703704</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>241</v>
@@ -6126,7 +6081,7 @@
         <v>244</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="Q75" s="8">
         <v>46258</v>
@@ -6146,7 +6101,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B76" s="5">
         <v>46181.60923553241</v>
@@ -6186,10 +6141,10 @@
         <v>241</v>
       </c>
       <c r="O76" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="P76" s="6" t="s">
         <v>247</v>
-      </c>
-      <c r="P76" s="6" t="s">
-        <v>248</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6199,7 +6154,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B77" s="8">
         <v>46181.609241805556</v>
@@ -6239,7 +6194,7 @@
         <v>241</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>182</v>
@@ -6252,17 +6207,17 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B78" s="5">
-        <v>46181.6145286574</v>
+        <v>46181.609247002314</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46216.64126927083</v>
+        <v>46212.62258834491</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>187</v>
+        <v>251</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -6274,10 +6229,10 @@
         <v>243</v>
       </c>
       <c r="I78" s="5">
-        <v>46258</v>
+        <v>46267</v>
       </c>
       <c r="J78" s="5">
-        <v>46266</v>
+        <v>46288</v>
       </c>
       <c r="K78" s="6" t="s">
         <v>26</v>
@@ -6289,33 +6244,43 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q78" s="6"/>
-      <c r="R78" s="6"/>
-      <c r="S78" s="6"/>
-      <c r="T78" s="6"/>
-      <c r="U78" s="6"/>
+        <v>238</v>
+      </c>
+      <c r="Q78" s="5">
+        <v>46267</v>
+      </c>
+      <c r="R78" s="5">
+        <v>46288</v>
+      </c>
+      <c r="S78" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T78" s="6">
+        <v>0</v>
+      </c>
+      <c r="U78" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
         <v>252</v>
       </c>
       <c r="B79" s="8">
-        <v>46181.61460722222</v>
+        <v>46181.60925648148</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46216.64127059028</v>
+        <v>46191.54540523148</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
@@ -6327,10 +6292,10 @@
         <v>243</v>
       </c>
       <c r="I79" s="8">
-        <v>46258</v>
+        <v>46267</v>
       </c>
       <c r="J79" s="8">
-        <v>46266</v>
+        <v>46288</v>
       </c>
       <c r="K79" s="9" t="s">
         <v>26</v>
@@ -6342,13 +6307,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="O79" s="9" t="s">
         <v>253</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>26</v>
+        <v>254</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6358,17 +6323,17 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B80" s="5">
-        <v>46181.61464366898</v>
+        <v>46181.609262199076</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46216.641271817134</v>
+        <v>46191.54540574074</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -6380,10 +6345,10 @@
         <v>243</v>
       </c>
       <c r="I80" s="5">
-        <v>46258</v>
+        <v>46267</v>
       </c>
       <c r="J80" s="5">
-        <v>46266</v>
+        <v>46288</v>
       </c>
       <c r="K80" s="6" t="s">
         <v>26</v>
@@ -6395,13 +6360,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>253</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>26</v>
+        <v>254</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6411,32 +6376,32 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B81" s="8">
-        <v>46181.609247002314</v>
+        <v>46181.60926783565</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46212.62258834491</v>
+        <v>46212.62263724537</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>242</v>
+        <v>162</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>243</v>
+        <v>163</v>
       </c>
       <c r="I81" s="8">
-        <v>46267</v>
+        <v>46289</v>
       </c>
       <c r="J81" s="8">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="K81" s="9" t="s">
         <v>26</v>
@@ -6451,16 +6416,16 @@
         <v>238</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>257</v>
+        <v>232</v>
       </c>
       <c r="P81" s="9" t="s">
         <v>238</v>
       </c>
       <c r="Q81" s="8">
-        <v>46267</v>
+        <v>46289</v>
       </c>
       <c r="R81" s="8">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="S81" s="10" t="s">
         <v>32</v>
@@ -6477,11 +6442,11 @@
         <v>258</v>
       </c>
       <c r="B82" s="5">
-        <v>46181.60925648148</v>
+        <v>46181.60927226851</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46191.54540523148</v>
+        <v>46191.545403842596</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>182</v>
@@ -6490,16 +6455,16 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>242</v>
+        <v>162</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>243</v>
+        <v>163</v>
       </c>
       <c r="I82" s="5">
-        <v>46267</v>
+        <v>46289</v>
       </c>
       <c r="J82" s="5">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="K82" s="6" t="s">
         <v>26</v>
@@ -6511,13 +6476,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O82" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="P82" s="6" t="s">
         <v>259</v>
-      </c>
-      <c r="P82" s="6" t="s">
-        <v>260</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6527,14 +6492,14 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B83" s="8">
-        <v>46181.609262199076</v>
+        <v>46181.60927799769</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46191.54540574074</v>
+        <v>46191.545404212964</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>182</v>
@@ -6543,16 +6508,16 @@
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>242</v>
+        <v>162</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>243</v>
+        <v>163</v>
       </c>
       <c r="I83" s="8">
-        <v>46267</v>
+        <v>46289</v>
       </c>
       <c r="J83" s="8">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="K83" s="9" t="s">
         <v>26</v>
@@ -6564,13 +6529,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6583,30 +6548,24 @@
         <v>262</v>
       </c>
       <c r="B84" s="5">
-        <v>46181.61473356481</v>
+        <v>46181.60928361111</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46182.64084413194</v>
+        <v>46213.56805377315</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="I84" s="5">
-        <v>46267</v>
-      </c>
-      <c r="J84" s="5">
-        <v>46288</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H84" s="6"/>
+      <c r="I84" s="6"/>
+      <c r="J84" s="6"/>
       <c r="K84" s="6" t="s">
         <v>26</v>
       </c>
@@ -6614,51 +6573,55 @@
         <v>26</v>
       </c>
       <c r="M84" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>256</v>
+        <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>263</v>
+        <v>26</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
       <c r="S84" s="6"/>
       <c r="T84" s="6"/>
-      <c r="U84" s="6"/>
+      <c r="U84" s="12" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
         <v>264</v>
       </c>
       <c r="B85" s="8">
-        <v>46181.61477212963</v>
-      </c>
-      <c r="C85" s="9"/>
+        <v>46181.609286990744</v>
+      </c>
+      <c r="C85" s="8">
+        <v>46213.56771503472</v>
+      </c>
       <c r="D85" s="8">
-        <v>46182.64084086806</v>
+        <v>46213.56773226852</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>190</v>
+        <v>265</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>242</v>
+        <v>220</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="I85" s="8">
-        <v>46267</v>
+        <v>46182</v>
       </c>
       <c r="J85" s="8">
-        <v>46288</v>
+        <v>46183</v>
       </c>
       <c r="K85" s="9" t="s">
         <v>26</v>
@@ -6670,101 +6633,125 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>256</v>
+        <v>216</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>241</v>
+        <v>26</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="Q85" s="9"/>
-      <c r="R85" s="9"/>
-      <c r="S85" s="9"/>
-      <c r="T85" s="9"/>
-      <c r="U85" s="9"/>
+        <v>266</v>
+      </c>
+      <c r="Q85" s="8">
+        <v>46182</v>
+      </c>
+      <c r="R85" s="8">
+        <v>46183</v>
+      </c>
+      <c r="S85" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="T85" s="9">
+        <v>1</v>
+      </c>
+      <c r="U85" s="10" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="B86" s="5">
+        <v>46181.609292974535</v>
+      </c>
+      <c r="C86" s="5">
+        <v>46213.56772936342</v>
+      </c>
+      <c r="D86" s="5">
+        <v>46213.56774653935</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="F86" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G86" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="I86" s="5">
+        <v>46290</v>
+      </c>
+      <c r="J86" s="5">
+        <v>46293</v>
+      </c>
+      <c r="K86" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L86" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M86" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N86" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="O86" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="P86" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="B86" s="5">
-        <v>46181.61484836806</v>
-      </c>
-      <c r="C86" s="6"/>
-      <c r="D86" s="5">
-        <v>46182.6408357176</v>
-      </c>
-      <c r="E86" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="F86" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G86" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="I86" s="5">
-        <v>46267</v>
-      </c>
-      <c r="J86" s="5">
-        <v>46288</v>
-      </c>
-      <c r="K86" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L86" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M86" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N86" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="O86" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="P86" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="Q86" s="6"/>
-      <c r="R86" s="6"/>
-      <c r="S86" s="6"/>
-      <c r="T86" s="6"/>
-      <c r="U86" s="6"/>
+      <c r="Q86" s="5">
+        <v>46290</v>
+      </c>
+      <c r="R86" s="5">
+        <v>46293</v>
+      </c>
+      <c r="S86" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T86" s="6">
+        <v>1</v>
+      </c>
+      <c r="U86" s="10" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B87" s="8">
-        <v>46181.60926783565</v>
-      </c>
-      <c r="C87" s="9"/>
+        <v>46181.60929881944</v>
+      </c>
+      <c r="C87" s="8">
+        <v>46213.56803628472</v>
+      </c>
       <c r="D87" s="8">
-        <v>46212.62263724537</v>
+        <v>46213.56805165509</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>162</v>
+        <v>220</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>163</v>
+        <v>221</v>
       </c>
       <c r="I87" s="8">
-        <v>46289</v>
+        <v>46226</v>
       </c>
       <c r="J87" s="8">
-        <v>46289</v>
+        <v>46227</v>
       </c>
       <c r="K87" s="9" t="s">
         <v>26</v>
@@ -6776,58 +6763,58 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>238</v>
+        <v>216</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>257</v>
+        <v>26</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>238</v>
+        <v>266</v>
       </c>
       <c r="Q87" s="8">
-        <v>46289</v>
+        <v>46226</v>
       </c>
       <c r="R87" s="8">
-        <v>46289</v>
+        <v>46227</v>
       </c>
       <c r="S87" s="10" t="s">
         <v>32</v>
       </c>
       <c r="T87" s="9">
-        <v>0</v>
-      </c>
-      <c r="U87" s="11" t="s">
-        <v>58</v>
+        <v>1</v>
+      </c>
+      <c r="U87" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B88" s="5">
-        <v>46181.60927226851</v>
+        <v>46181.60930480324</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46191.545403842596</v>
+        <v>46212.623013958335</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>182</v>
+        <v>272</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>162</v>
+        <v>220</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>163</v>
+        <v>221</v>
       </c>
       <c r="I88" s="5">
-        <v>46289</v>
+        <v>46293</v>
       </c>
       <c r="J88" s="5">
-        <v>46289</v>
+        <v>46294</v>
       </c>
       <c r="K88" s="6" t="s">
         <v>26</v>
@@ -6839,48 +6826,58 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>269</v>
+        <v>216</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>259</v>
+        <v>158</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q88" s="6"/>
-      <c r="R88" s="6"/>
-      <c r="S88" s="6"/>
-      <c r="T88" s="6"/>
-      <c r="U88" s="6"/>
+        <v>273</v>
+      </c>
+      <c r="Q88" s="5">
+        <v>46293</v>
+      </c>
+      <c r="R88" s="5">
+        <v>46294</v>
+      </c>
+      <c r="S88" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T88" s="6">
+        <v>0</v>
+      </c>
+      <c r="U88" s="12" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B89" s="8">
-        <v>46181.60927799769</v>
+        <v>46181.60935271991</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46191.545404212964</v>
+        <v>46212.6232265162</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>182</v>
+        <v>61</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>162</v>
+        <v>220</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>163</v>
+        <v>221</v>
       </c>
       <c r="I89" s="8">
-        <v>46289</v>
+        <v>46226</v>
       </c>
       <c r="J89" s="8">
-        <v>46289</v>
+        <v>46227</v>
       </c>
       <c r="K89" s="9" t="s">
         <v>26</v>
@@ -6892,49 +6889,53 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>269</v>
+        <v>216</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>259</v>
+        <v>130</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="Q89" s="9"/>
-      <c r="R89" s="9"/>
-      <c r="S89" s="9"/>
-      <c r="T89" s="9"/>
-      <c r="U89" s="9"/>
+        <v>56</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>46226</v>
+      </c>
+      <c r="R89" s="8">
+        <v>46227</v>
+      </c>
+      <c r="S89" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T89" s="9">
+        <v>0</v>
+      </c>
+      <c r="U89" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B90" s="5">
-        <v>46181.614954062505</v>
+        <v>46181.60936674768</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46182.64096971064</v>
+        <v>46213.50490068287</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="I90" s="5">
-        <v>46289</v>
-      </c>
-      <c r="J90" s="5">
-        <v>46289</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H90" s="6"/>
+      <c r="I90" s="6"/>
+      <c r="J90" s="6"/>
       <c r="K90" s="6" t="s">
         <v>26</v>
       </c>
@@ -6942,16 +6943,16 @@
         <v>26</v>
       </c>
       <c r="M90" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>269</v>
+        <v>26</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>187</v>
+        <v>26</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6961,32 +6962,32 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B91" s="8">
-        <v>46181.61498993056</v>
+        <v>46181.609371666666</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46182.64096709491</v>
+        <v>46182.64123547454</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>162</v>
+        <v>90</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>163</v>
+        <v>90</v>
       </c>
       <c r="I91" s="8">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="J91" s="8">
-        <v>46289</v>
+        <v>46310</v>
       </c>
       <c r="K91" s="9" t="s">
         <v>26</v>
@@ -6998,48 +6999,58 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>190</v>
+        <v>280</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="Q91" s="9"/>
-      <c r="R91" s="9"/>
-      <c r="S91" s="9"/>
-      <c r="T91" s="9"/>
-      <c r="U91" s="9"/>
+        <v>276</v>
+      </c>
+      <c r="Q91" s="8">
+        <v>46290</v>
+      </c>
+      <c r="R91" s="8">
+        <v>46310</v>
+      </c>
+      <c r="S91" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T91" s="9">
+        <v>0</v>
+      </c>
+      <c r="U91" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B92" s="5">
-        <v>46181.61502625</v>
+        <v>46181.609378587964</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46182.64096319444</v>
+        <v>46182.64119599537</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>267</v>
+        <v>182</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>162</v>
+        <v>90</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>163</v>
+        <v>90</v>
       </c>
       <c r="I92" s="5">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="J92" s="5">
-        <v>46289</v>
+        <v>46310</v>
       </c>
       <c r="K92" s="6" t="s">
         <v>26</v>
@@ -7051,13 +7062,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>192</v>
+        <v>282</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7067,27 +7078,33 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B93" s="8">
-        <v>46181.60928361111</v>
+        <v>46181.61514019676</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46213.56805377315</v>
+        <v>46182.64119222222</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>216</v>
+        <v>182</v>
       </c>
       <c r="F93" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H93" s="9"/>
-      <c r="I93" s="9"/>
-      <c r="J93" s="9"/>
+        <v>90</v>
+      </c>
+      <c r="H93" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="I93" s="8">
+        <v>46290</v>
+      </c>
+      <c r="J93" s="8">
+        <v>46310</v>
+      </c>
       <c r="K93" s="9" t="s">
         <v>26</v>
       </c>
@@ -7095,55 +7112,53 @@
         <v>26</v>
       </c>
       <c r="M93" s="9" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>26</v>
+        <v>279</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>279</v>
+        <v>182</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>26</v>
+        <v>284</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
       <c r="S93" s="9"/>
       <c r="T93" s="9"/>
-      <c r="U93" s="12" t="s">
-        <v>121</v>
-      </c>
+      <c r="U93" s="9"/>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B94" s="5">
-        <v>46181.609286990744</v>
+        <v>46181.609386111115</v>
       </c>
       <c r="C94" s="5">
-        <v>46213.56771503472</v>
+        <v>46204.895157314815</v>
       </c>
       <c r="D94" s="5">
-        <v>46213.56773226852</v>
+        <v>46212.62246368056</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>220</v>
+        <v>90</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>221</v>
+        <v>90</v>
       </c>
       <c r="I94" s="5">
-        <v>46182</v>
+        <v>46311</v>
       </c>
       <c r="J94" s="5">
-        <v>46183</v>
+        <v>46314</v>
       </c>
       <c r="K94" s="6" t="s">
         <v>26</v>
@@ -7155,22 +7170,22 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>216</v>
+        <v>276</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>26</v>
+        <v>182</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="Q94" s="5">
-        <v>46182</v>
+        <v>46311</v>
       </c>
       <c r="R94" s="5">
-        <v>46183</v>
-      </c>
-      <c r="S94" s="11" t="s">
-        <v>180</v>
+        <v>46314</v>
+      </c>
+      <c r="S94" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T94" s="6">
         <v>1</v>
@@ -7181,34 +7196,34 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B95" s="8">
-        <v>46181.609292974535</v>
+        <v>46181.60939194444</v>
       </c>
       <c r="C95" s="8">
-        <v>46213.56772936342</v>
+        <v>46204.89505366898</v>
       </c>
       <c r="D95" s="8">
-        <v>46213.56774653935</v>
+        <v>46213.56773570602</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>284</v>
+        <v>182</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>220</v>
+        <v>90</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>221</v>
+        <v>90</v>
       </c>
       <c r="I95" s="8">
-        <v>46290</v>
+        <v>46311</v>
       </c>
       <c r="J95" s="8">
-        <v>46293</v>
+        <v>46314</v>
       </c>
       <c r="K95" s="9" t="s">
         <v>26</v>
@@ -7220,123 +7235,105 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>216</v>
+        <v>286</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>26</v>
+        <v>288</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="Q95" s="8">
-        <v>46290</v>
-      </c>
-      <c r="R95" s="8">
-        <v>46293</v>
-      </c>
-      <c r="S95" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="T95" s="9">
-        <v>1</v>
-      </c>
-      <c r="U95" s="10" t="s">
-        <v>33</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="Q95" s="9"/>
+      <c r="R95" s="9"/>
+      <c r="S95" s="9"/>
+      <c r="T95" s="9"/>
+      <c r="U95" s="9"/>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B96" s="5">
-        <v>46181.60929881944</v>
+        <v>46181.61518315972</v>
       </c>
       <c r="C96" s="5">
-        <v>46213.56803628472</v>
+        <v>46204.89514296297</v>
       </c>
       <c r="D96" s="5">
-        <v>46213.56805165509</v>
+        <v>46213.567735150464</v>
       </c>
       <c r="E96" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="F96" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G96" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="I96" s="5">
+        <v>46311</v>
+      </c>
+      <c r="J96" s="5">
+        <v>46314</v>
+      </c>
+      <c r="K96" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L96" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M96" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N96" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="F96" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G96" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="I96" s="5">
-        <v>46226</v>
-      </c>
-      <c r="J96" s="5">
-        <v>46227</v>
-      </c>
-      <c r="K96" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L96" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M96" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N96" s="6" t="s">
-        <v>216</v>
-      </c>
       <c r="O96" s="6" t="s">
-        <v>26</v>
+        <v>291</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="Q96" s="5">
-        <v>46226</v>
-      </c>
-      <c r="R96" s="5">
-        <v>46227</v>
-      </c>
-      <c r="S96" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="T96" s="6">
-        <v>1</v>
-      </c>
-      <c r="U96" s="10" t="s">
-        <v>33</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q96" s="6"/>
+      <c r="R96" s="6"/>
+      <c r="S96" s="6"/>
+      <c r="T96" s="6"/>
+      <c r="U96" s="6"/>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B97" s="8">
-        <v>46181.60930480324</v>
-      </c>
-      <c r="C97" s="9"/>
+        <v>46181.60939866898</v>
+      </c>
+      <c r="C97" s="8">
+        <v>46213.50489005787</v>
+      </c>
       <c r="D97" s="8">
-        <v>46212.623013958335</v>
+        <v>46213.50490375</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>220</v>
+        <v>90</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>221</v>
+        <v>90</v>
       </c>
       <c r="I97" s="8">
-        <v>46293</v>
+        <v>46315</v>
       </c>
       <c r="J97" s="8">
-        <v>46294</v>
+        <v>46316</v>
       </c>
       <c r="K97" s="9" t="s">
         <v>26</v>
@@ -7348,58 +7345,60 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>216</v>
+        <v>276</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="Q97" s="8">
-        <v>46293</v>
+        <v>46315</v>
       </c>
       <c r="R97" s="8">
-        <v>46294</v>
+        <v>46316</v>
       </c>
       <c r="S97" s="10" t="s">
         <v>32</v>
       </c>
       <c r="T97" s="9">
-        <v>0</v>
-      </c>
-      <c r="U97" s="12" t="s">
-        <v>121</v>
+        <v>1</v>
+      </c>
+      <c r="U97" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B98" s="5">
-        <v>46181.60935271991</v>
-      </c>
-      <c r="C98" s="6"/>
+        <v>46181.60940505787</v>
+      </c>
+      <c r="C98" s="5">
+        <v>46213.50480490741</v>
+      </c>
       <c r="D98" s="5">
-        <v>46212.6232265162</v>
+        <v>46213.56772277778</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>61</v>
+        <v>182</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>220</v>
+        <v>90</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>221</v>
+        <v>90</v>
       </c>
       <c r="I98" s="5">
-        <v>46226</v>
+        <v>46315</v>
       </c>
       <c r="J98" s="5">
-        <v>46227</v>
+        <v>46316</v>
       </c>
       <c r="K98" s="6" t="s">
         <v>26</v>
@@ -7411,53 +7410,51 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>216</v>
+        <v>293</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>130</v>
+        <v>295</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q98" s="5">
-        <v>46226</v>
-      </c>
-      <c r="R98" s="5">
-        <v>46227</v>
-      </c>
-      <c r="S98" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="T98" s="6">
-        <v>0</v>
-      </c>
-      <c r="U98" s="11" t="s">
-        <v>58</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="Q98" s="6"/>
+      <c r="R98" s="6"/>
+      <c r="S98" s="6"/>
+      <c r="T98" s="6"/>
+      <c r="U98" s="6"/>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="B99" s="8">
-        <v>46181.60936674768</v>
-      </c>
-      <c r="C99" s="9"/>
+        <v>46181.61523613426</v>
+      </c>
+      <c r="C99" s="8">
+        <v>46213.50487766204</v>
+      </c>
       <c r="D99" s="8">
-        <v>46213.50490068287</v>
+        <v>46213.56772202546</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>292</v>
+        <v>182</v>
       </c>
       <c r="F99" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H99" s="9"/>
-      <c r="I99" s="9"/>
-      <c r="J99" s="9"/>
+        <v>90</v>
+      </c>
+      <c r="H99" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="I99" s="8">
+        <v>46315</v>
+      </c>
+      <c r="J99" s="8">
+        <v>46316</v>
+      </c>
       <c r="K99" s="9" t="s">
         <v>26</v>
       </c>
@@ -7465,13 +7462,13 @@
         <v>26</v>
       </c>
       <c r="M99" s="9" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>26</v>
+        <v>293</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="P99" s="9" t="s">
         <v>26</v>
@@ -7484,17 +7481,17 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B100" s="5">
-        <v>46181.609371666666</v>
+        <v>46181.60941365741</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46182.64123547454</v>
+        <v>46212.62250564815</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7506,10 +7503,10 @@
         <v>90</v>
       </c>
       <c r="I100" s="5">
-        <v>46290</v>
+        <v>46317</v>
       </c>
       <c r="J100" s="5">
-        <v>46310</v>
+        <v>46318</v>
       </c>
       <c r="K100" s="6" t="s">
         <v>26</v>
@@ -7521,19 +7518,19 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>296</v>
+        <v>182</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="Q100" s="5">
-        <v>46290</v>
+        <v>46317</v>
       </c>
       <c r="R100" s="5">
-        <v>46310</v>
+        <v>46318</v>
       </c>
       <c r="S100" s="10" t="s">
         <v>32</v>
@@ -7547,14 +7544,14 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B101" s="8">
-        <v>46181.609378587964</v>
+        <v>46181.60941929398</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46182.64119599537</v>
+        <v>46213.56804261574</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>182</v>
@@ -7569,10 +7566,10 @@
         <v>90</v>
       </c>
       <c r="I101" s="8">
-        <v>46290</v>
+        <v>46317</v>
       </c>
       <c r="J101" s="8">
-        <v>46310</v>
+        <v>46318</v>
       </c>
       <c r="K101" s="9" t="s">
         <v>26</v>
@@ -7584,13 +7581,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7600,14 +7597,14 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B102" s="5">
-        <v>46181.61514019676</v>
+        <v>46181.61528053241</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46182.64119222222</v>
+        <v>46213.568041192135</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>182</v>
@@ -7622,10 +7619,10 @@
         <v>90</v>
       </c>
       <c r="I102" s="5">
-        <v>46290</v>
+        <v>46317</v>
       </c>
       <c r="J102" s="5">
-        <v>46310</v>
+        <v>46318</v>
       </c>
       <c r="K102" s="6" t="s">
         <v>26</v>
@@ -7637,13 +7634,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>182</v>
+        <v>305</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>300</v>
+        <v>26</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7653,19 +7650,17 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B103" s="8">
-        <v>46181.609386111115</v>
-      </c>
-      <c r="C103" s="8">
-        <v>46204.895157314815</v>
-      </c>
+        <v>46181.60942706019</v>
+      </c>
+      <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46212.62246368056</v>
+        <v>46212.62252259259</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -7677,10 +7672,10 @@
         <v>90</v>
       </c>
       <c r="I103" s="8">
-        <v>46311</v>
+        <v>46321</v>
       </c>
       <c r="J103" s="8">
-        <v>46314</v>
+        <v>46321</v>
       </c>
       <c r="K103" s="9" t="s">
         <v>26</v>
@@ -7692,42 +7687,40 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="O103" s="9" t="s">
         <v>182</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="Q103" s="8">
-        <v>46311</v>
+        <v>46321</v>
       </c>
       <c r="R103" s="8">
-        <v>46314</v>
+        <v>46321</v>
       </c>
       <c r="S103" s="10" t="s">
         <v>32</v>
       </c>
       <c r="T103" s="9">
-        <v>1</v>
-      </c>
-      <c r="U103" s="10" t="s">
-        <v>33</v>
+        <v>0</v>
+      </c>
+      <c r="U103" s="11" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="B104" s="5">
-        <v>46181.60939194444</v>
-      </c>
-      <c r="C104" s="5">
-        <v>46204.89505366898</v>
-      </c>
+        <v>46181.60943415509</v>
+      </c>
+      <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46213.56773570602</v>
+        <v>46182.641623125004</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>182</v>
@@ -7742,10 +7735,10 @@
         <v>90</v>
       </c>
       <c r="I104" s="5">
-        <v>46311</v>
+        <v>46321</v>
       </c>
       <c r="J104" s="5">
-        <v>46314</v>
+        <v>46321</v>
       </c>
       <c r="K104" s="6" t="s">
         <v>26</v>
@@ -7757,13 +7750,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>304</v>
+        <v>182</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7773,16 +7766,14 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B105" s="8">
-        <v>46181.61518315972</v>
-      </c>
-      <c r="C105" s="8">
-        <v>46204.89514296297</v>
-      </c>
+        <v>46181.61532783565</v>
+      </c>
+      <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46213.567735150464</v>
+        <v>46182.64161924769</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>182</v>
@@ -7797,10 +7788,10 @@
         <v>90</v>
       </c>
       <c r="I105" s="8">
-        <v>46311</v>
+        <v>46321</v>
       </c>
       <c r="J105" s="8">
-        <v>46314</v>
+        <v>46321</v>
       </c>
       <c r="K105" s="9" t="s">
         <v>26</v>
@@ -7812,13 +7803,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>307</v>
+        <v>182</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>26</v>
+        <v>214</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -7828,19 +7819,17 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B106" s="5">
-        <v>46181.60939866898</v>
-      </c>
-      <c r="C106" s="5">
-        <v>46213.50489005787</v>
-      </c>
+        <v>46181.60944410879</v>
+      </c>
+      <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46213.50490375</v>
+        <v>46212.622555497685</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7852,10 +7841,10 @@
         <v>90</v>
       </c>
       <c r="I106" s="5">
-        <v>46315</v>
+        <v>46323</v>
       </c>
       <c r="J106" s="5">
-        <v>46316</v>
+        <v>46323</v>
       </c>
       <c r="K106" s="6" t="s">
         <v>26</v>
@@ -7867,42 +7856,40 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>182</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="Q106" s="5">
-        <v>46315</v>
+        <v>46323</v>
       </c>
       <c r="R106" s="5">
-        <v>46316</v>
+        <v>46323</v>
       </c>
       <c r="S106" s="10" t="s">
         <v>32</v>
       </c>
       <c r="T106" s="6">
-        <v>1</v>
-      </c>
-      <c r="U106" s="10" t="s">
-        <v>33</v>
+        <v>0</v>
+      </c>
+      <c r="U106" s="11" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B107" s="8">
-        <v>46181.60940505787</v>
-      </c>
-      <c r="C107" s="8">
-        <v>46213.50480490741</v>
-      </c>
+        <v>46181.60944996528</v>
+      </c>
+      <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46213.56772277778</v>
+        <v>46182.64173178241</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>182</v>
@@ -7917,10 +7904,10 @@
         <v>90</v>
       </c>
       <c r="I107" s="8">
-        <v>46315</v>
+        <v>46323</v>
       </c>
       <c r="J107" s="8">
-        <v>46316</v>
+        <v>46323</v>
       </c>
       <c r="K107" s="9" t="s">
         <v>26</v>
@@ -7932,13 +7919,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>311</v>
+        <v>182</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -7948,16 +7935,14 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B108" s="5">
-        <v>46181.61523613426</v>
-      </c>
-      <c r="C108" s="5">
-        <v>46213.50487766204</v>
-      </c>
+        <v>46181.61537143518</v>
+      </c>
+      <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46213.56772202546</v>
+        <v>46182.64172883102</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>182</v>
@@ -7972,10 +7957,10 @@
         <v>90</v>
       </c>
       <c r="I108" s="5">
-        <v>46315</v>
+        <v>46323</v>
       </c>
       <c r="J108" s="5">
-        <v>46316</v>
+        <v>46323</v>
       </c>
       <c r="K108" s="6" t="s">
         <v>26</v>
@@ -7987,10 +7972,10 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>314</v>
+        <v>214</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>26</v>
@@ -8003,33 +7988,27 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B109" s="8">
-        <v>46181.60941365741</v>
+        <v>46181.60945642361</v>
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="8">
-        <v>46212.62250564815</v>
+        <v>46182.634494212965</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F109" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="H109" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="I109" s="8">
-        <v>46317</v>
-      </c>
-      <c r="J109" s="8">
-        <v>46318</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H109" s="9"/>
+      <c r="I109" s="9"/>
+      <c r="J109" s="9"/>
       <c r="K109" s="9" t="s">
         <v>26</v>
       </c>
@@ -8037,61 +8016,51 @@
         <v>26</v>
       </c>
       <c r="M109" s="9" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>292</v>
+        <v>26</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>182</v>
+        <v>319</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="Q109" s="8">
-        <v>46317</v>
-      </c>
-      <c r="R109" s="8">
-        <v>46318</v>
-      </c>
-      <c r="S109" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="T109" s="9">
-        <v>0</v>
-      </c>
-      <c r="U109" s="11" t="s">
-        <v>58</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q109" s="9"/>
+      <c r="R109" s="9"/>
+      <c r="S109" s="9"/>
+      <c r="T109" s="9"/>
+      <c r="U109" s="9"/>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B110" s="5">
-        <v>46181.60941929398</v>
+        <v>46181.60946096065</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46213.56804261574</v>
+        <v>46182.64186350694</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>182</v>
+        <v>321</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>90</v>
+        <v>322</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>90</v>
+        <v>323</v>
       </c>
       <c r="I110" s="5">
-        <v>46317</v>
+        <v>46324</v>
       </c>
       <c r="J110" s="5">
-        <v>46318</v>
+        <v>46324</v>
       </c>
       <c r="K110" s="6" t="s">
         <v>26</v>
@@ -8103,30 +8072,40 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="O110" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="P110" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="P110" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="Q110" s="6"/>
-      <c r="R110" s="6"/>
-      <c r="S110" s="6"/>
-      <c r="T110" s="6"/>
-      <c r="U110" s="6"/>
+      <c r="Q110" s="5">
+        <v>46324</v>
+      </c>
+      <c r="R110" s="5">
+        <v>46324</v>
+      </c>
+      <c r="S110" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T110" s="6">
+        <v>0</v>
+      </c>
+      <c r="U110" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B111" s="8">
-        <v>46181.61528053241</v>
+        <v>46181.60946868056</v>
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46213.568041192135</v>
+        <v>46182.641845254635</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>182</v>
@@ -8135,16 +8114,16 @@
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>90</v>
+        <v>322</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>90</v>
+        <v>323</v>
       </c>
       <c r="I111" s="8">
-        <v>46317</v>
+        <v>46324</v>
       </c>
       <c r="J111" s="8">
-        <v>46318</v>
+        <v>46324</v>
       </c>
       <c r="K111" s="9" t="s">
         <v>26</v>
@@ -8156,13 +8135,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>321</v>
+        <v>182</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>26</v>
+        <v>326</v>
       </c>
       <c r="Q111" s="9"/>
       <c r="R111" s="9"/>
@@ -8172,32 +8151,32 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B112" s="5">
-        <v>46181.60942706019</v>
+        <v>46181.609475034726</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46212.62252259259</v>
+        <v>46182.64184081019</v>
       </c>
       <c r="E112" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="F112" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G112" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="H112" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="F112" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G112" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>90</v>
-      </c>
       <c r="I112" s="5">
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="J112" s="5">
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="K112" s="6" t="s">
         <v>26</v>
@@ -8209,58 +8188,48 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>292</v>
+        <v>321</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>182</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="Q112" s="5">
-        <v>46321</v>
-      </c>
-      <c r="R112" s="5">
-        <v>46321</v>
-      </c>
-      <c r="S112" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="T112" s="6">
-        <v>0</v>
-      </c>
-      <c r="U112" s="11" t="s">
-        <v>58</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="Q112" s="6"/>
+      <c r="R112" s="6"/>
+      <c r="S112" s="6"/>
+      <c r="T112" s="6"/>
+      <c r="U112" s="6"/>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B113" s="8">
-        <v>46181.60943415509</v>
+        <v>46181.60947921296</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46182.641623125004</v>
+        <v>46182.641837766205</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>182</v>
+        <v>60</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>90</v>
+        <v>322</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>90</v>
+        <v>323</v>
       </c>
       <c r="I113" s="8">
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="J113" s="8">
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="K113" s="9" t="s">
         <v>26</v>
@@ -8272,13 +8241,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>182</v>
+        <v>60</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>325</v>
+        <v>60</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8288,32 +8257,32 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B114" s="5">
-        <v>46181.61532783565</v>
+        <v>46181.61605960648</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46182.64161924769</v>
+        <v>46182.641834548616</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>182</v>
+        <v>60</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>90</v>
+        <v>322</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>90</v>
+        <v>323</v>
       </c>
       <c r="I114" s="5">
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="J114" s="5">
-        <v>46321</v>
+        <v>46324</v>
       </c>
       <c r="K114" s="6" t="s">
         <v>26</v>
@@ -8325,13 +8294,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>182</v>
+        <v>60</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>214</v>
+        <v>60</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8341,32 +8310,32 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B115" s="8">
-        <v>46181.60944410879</v>
+        <v>46181.61617203704</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46212.622555497685</v>
+        <v>46216.71559670139</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>328</v>
+        <v>187</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>90</v>
+        <v>322</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>90</v>
+        <v>323</v>
       </c>
       <c r="I115" s="8">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="J115" s="8">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="K115" s="9" t="s">
         <v>26</v>
@@ -8378,58 +8347,48 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>292</v>
+        <v>321</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>182</v>
+        <v>26</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="Q115" s="8">
-        <v>46323</v>
-      </c>
-      <c r="R115" s="8">
-        <v>46323</v>
-      </c>
-      <c r="S115" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="T115" s="9">
-        <v>0</v>
-      </c>
-      <c r="U115" s="11" t="s">
-        <v>58</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="Q115" s="9"/>
+      <c r="R115" s="9"/>
+      <c r="S115" s="9"/>
+      <c r="T115" s="9"/>
+      <c r="U115" s="9"/>
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B116" s="5">
-        <v>46181.60944996528</v>
+        <v>46181.61620771991</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46182.64173178241</v>
+        <v>46216.715609837964</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>90</v>
+        <v>322</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>90</v>
+        <v>323</v>
       </c>
       <c r="I116" s="5">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="J116" s="5">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="K116" s="6" t="s">
         <v>26</v>
@@ -8441,13 +8400,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>182</v>
+        <v>26</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>331</v>
+        <v>190</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8460,29 +8419,29 @@
         <v>332</v>
       </c>
       <c r="B117" s="8">
-        <v>46181.61537143518</v>
+        <v>46181.616245833335</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46182.64172883102</v>
+        <v>46216.715626087964</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>182</v>
+        <v>333</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>90</v>
+        <v>322</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>90</v>
+        <v>323</v>
       </c>
       <c r="I117" s="8">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="J117" s="8">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="K117" s="9" t="s">
         <v>26</v>
@@ -8494,13 +8453,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>214</v>
+        <v>26</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>26</v>
+        <v>192</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8510,27 +8469,33 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B118" s="5">
-        <v>46181.60945642361</v>
+        <v>46181.60948424769</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46182.634494212965</v>
+        <v>46182.64199267361</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H118" s="6"/>
-      <c r="I118" s="6"/>
-      <c r="J118" s="6"/>
+        <v>90</v>
+      </c>
+      <c r="H118" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="I118" s="5">
+        <v>46325</v>
+      </c>
+      <c r="J118" s="5">
+        <v>46325</v>
+      </c>
       <c r="K118" s="6" t="s">
         <v>26</v>
       </c>
@@ -8538,96 +8503,96 @@
         <v>26</v>
       </c>
       <c r="M118" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N118" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="O118" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="P118" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q118" s="5">
+        <v>46325</v>
+      </c>
+      <c r="R118" s="5">
+        <v>46325</v>
+      </c>
+      <c r="S118" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T118" s="6">
         <v>0</v>
       </c>
-      <c r="N118" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O118" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="P118" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q118" s="6"/>
-      <c r="R118" s="6"/>
-      <c r="S118" s="6"/>
-      <c r="T118" s="6"/>
-      <c r="U118" s="6"/>
+      <c r="U118" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
         <v>336</v>
       </c>
       <c r="B119" s="8">
-        <v>46181.60946096065</v>
+        <v>46181.60948969907</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46182.64186350694</v>
+        <v>46182.641973854166</v>
       </c>
       <c r="E119" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F119" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G119" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="H119" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="I119" s="8">
+        <v>46325</v>
+      </c>
+      <c r="J119" s="8">
+        <v>46325</v>
+      </c>
+      <c r="K119" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L119" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M119" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N119" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="O119" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="P119" s="9" t="s">
         <v>337</v>
       </c>
-      <c r="F119" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G119" s="9" t="s">
-        <v>338</v>
-      </c>
-      <c r="H119" s="9" t="s">
-        <v>339</v>
-      </c>
-      <c r="I119" s="8">
-        <v>46324</v>
-      </c>
-      <c r="J119" s="8">
-        <v>46324</v>
-      </c>
-      <c r="K119" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L119" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M119" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N119" s="9" t="s">
-        <v>334</v>
-      </c>
-      <c r="O119" s="9" t="s">
-        <v>340</v>
-      </c>
-      <c r="P119" s="9" t="s">
-        <v>334</v>
-      </c>
-      <c r="Q119" s="8">
-        <v>46324</v>
-      </c>
-      <c r="R119" s="8">
-        <v>46324</v>
-      </c>
-      <c r="S119" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="T119" s="9">
-        <v>0</v>
-      </c>
-      <c r="U119" s="11" t="s">
-        <v>58</v>
-      </c>
+      <c r="Q119" s="9"/>
+      <c r="R119" s="9"/>
+      <c r="S119" s="9"/>
+      <c r="T119" s="9"/>
+      <c r="U119" s="9"/>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B120" s="5">
-        <v>46181.60946868056</v>
+        <v>46181.60949538194</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46182.641845254635</v>
+        <v>46182.64197085648</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>182</v>
@@ -8636,16 +8601,16 @@
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>338</v>
+        <v>90</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>339</v>
+        <v>90</v>
       </c>
       <c r="I120" s="5">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="J120" s="5">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="K120" s="6" t="s">
         <v>26</v>
@@ -8657,13 +8622,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>182</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>342</v>
+        <v>182</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8673,32 +8638,32 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B121" s="8">
-        <v>46181.609475034726</v>
+        <v>46181.609560185185</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46182.64184081019</v>
+        <v>46182.641967118056</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>182</v>
+        <v>60</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>338</v>
+        <v>90</v>
       </c>
       <c r="H121" s="9" t="s">
-        <v>339</v>
+        <v>90</v>
       </c>
       <c r="I121" s="8">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="J121" s="8">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="K121" s="9" t="s">
         <v>26</v>
@@ -8710,13 +8675,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>182</v>
+        <v>60</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>182</v>
+        <v>60</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8726,14 +8691,14 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="B122" s="5">
-        <v>46181.60947921296</v>
+        <v>46181.61659114584</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46182.641837766205</v>
+        <v>46182.64196408565</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>60</v>
@@ -8742,16 +8707,16 @@
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>338</v>
+        <v>90</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>339</v>
+        <v>90</v>
       </c>
       <c r="I122" s="5">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="J122" s="5">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="K122" s="6" t="s">
         <v>26</v>
@@ -8763,7 +8728,7 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>60</v>
@@ -8779,32 +8744,32 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B123" s="8">
-        <v>46181.61605960648</v>
+        <v>46181.61662431713</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46182.641834548616</v>
+        <v>46182.64196105324</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>60</v>
+        <v>187</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>338</v>
+        <v>90</v>
       </c>
       <c r="H123" s="9" t="s">
-        <v>339</v>
+        <v>90</v>
       </c>
       <c r="I123" s="8">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="J123" s="8">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="K123" s="9" t="s">
         <v>26</v>
@@ -8816,13 +8781,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>60</v>
+        <v>187</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>60</v>
+        <v>187</v>
       </c>
       <c r="Q123" s="9"/>
       <c r="R123" s="9"/>
@@ -8832,32 +8797,32 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="B124" s="5">
-        <v>46181.61617203704</v>
+        <v>46181.61666238426</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46182.64182482639</v>
+        <v>46182.64195453704</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>338</v>
+        <v>90</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>339</v>
+        <v>90</v>
       </c>
       <c r="I124" s="5">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="J124" s="5">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="K124" s="6" t="s">
         <v>26</v>
@@ -8869,13 +8834,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>263</v>
+        <v>190</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8885,32 +8850,32 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B125" s="8">
-        <v>46181.61620771991</v>
+        <v>46181.61670006944</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46182.64182413195</v>
+        <v>46182.64195372685</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>338</v>
+        <v>90</v>
       </c>
       <c r="H125" s="9" t="s">
-        <v>339</v>
+        <v>90</v>
       </c>
       <c r="I125" s="8">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="J125" s="8">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="K125" s="9" t="s">
         <v>26</v>
@@ -8922,13 +8887,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>265</v>
+        <v>333</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -8938,32 +8903,32 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="B126" s="5">
-        <v>46181.616245833335</v>
+        <v>46181.60956560185</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46182.641823425925</v>
+        <v>46182.82952324074</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>277</v>
+        <v>345</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>338</v>
+        <v>242</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>339</v>
+        <v>243</v>
       </c>
       <c r="I126" s="5">
-        <v>46324</v>
+        <v>46328</v>
       </c>
       <c r="J126" s="5">
-        <v>46324</v>
+        <v>46328</v>
       </c>
       <c r="K126" s="6" t="s">
         <v>26</v>
@@ -8975,48 +8940,58 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>267</v>
+        <v>182</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="Q126" s="6"/>
-      <c r="R126" s="6"/>
-      <c r="S126" s="6"/>
-      <c r="T126" s="6"/>
-      <c r="U126" s="6"/>
+        <v>318</v>
+      </c>
+      <c r="Q126" s="5">
+        <v>46328</v>
+      </c>
+      <c r="R126" s="5">
+        <v>46328</v>
+      </c>
+      <c r="S126" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T126" s="6">
+        <v>0</v>
+      </c>
+      <c r="U126" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B127" s="8">
-        <v>46181.60948424769</v>
+        <v>46181.60957188657</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46182.64199267361</v>
+        <v>46182.82945300926</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>350</v>
+        <v>182</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>90</v>
+        <v>242</v>
       </c>
       <c r="H127" s="9" t="s">
-        <v>90</v>
+        <v>243</v>
       </c>
       <c r="I127" s="8">
-        <v>46325</v>
+        <v>46328</v>
       </c>
       <c r="J127" s="8">
-        <v>46325</v>
+        <v>46328</v>
       </c>
       <c r="K127" s="9" t="s">
         <v>26</v>
@@ -9028,40 +9003,30 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="O127" s="9" t="s">
         <v>182</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>334</v>
-      </c>
-      <c r="Q127" s="8">
-        <v>46325</v>
-      </c>
-      <c r="R127" s="8">
-        <v>46325</v>
-      </c>
-      <c r="S127" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="T127" s="9">
-        <v>0</v>
-      </c>
-      <c r="U127" s="11" t="s">
-        <v>58</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="Q127" s="9"/>
+      <c r="R127" s="9"/>
+      <c r="S127" s="9"/>
+      <c r="T127" s="9"/>
+      <c r="U127" s="9"/>
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B128" s="5">
-        <v>46181.60948969907</v>
+        <v>46181.609583576384</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46182.641973854166</v>
+        <v>46182.829453784725</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>182</v>
@@ -9070,16 +9035,16 @@
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>90</v>
+        <v>242</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>90</v>
+        <v>243</v>
       </c>
       <c r="I128" s="5">
-        <v>46325</v>
+        <v>46328</v>
       </c>
       <c r="J128" s="5">
-        <v>46325</v>
+        <v>46328</v>
       </c>
       <c r="K128" s="6" t="s">
         <v>26</v>
@@ -9091,13 +9056,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="O128" s="6" t="s">
         <v>182</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>352</v>
+        <v>182</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9107,32 +9072,32 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="B129" s="8">
-        <v>46181.60949538194</v>
+        <v>46181.60958841435</v>
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46182.64197085648</v>
+        <v>46182.829454583334</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>182</v>
+        <v>60</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>90</v>
+        <v>242</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>90</v>
+        <v>243</v>
       </c>
       <c r="I129" s="8">
-        <v>46325</v>
+        <v>46328</v>
       </c>
       <c r="J129" s="8">
-        <v>46325</v>
+        <v>46328</v>
       </c>
       <c r="K129" s="9" t="s">
         <v>26</v>
@@ -9144,13 +9109,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>182</v>
+        <v>60</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>182</v>
+        <v>60</v>
       </c>
       <c r="Q129" s="9"/>
       <c r="R129" s="9"/>
@@ -9160,14 +9125,14 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="B130" s="5">
-        <v>46181.609560185185</v>
+        <v>46181.616839849536</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46182.641967118056</v>
+        <v>46182.829455706014</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>60</v>
@@ -9176,16 +9141,16 @@
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>90</v>
+        <v>242</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>90</v>
+        <v>243</v>
       </c>
       <c r="I130" s="5">
-        <v>46325</v>
+        <v>46328</v>
       </c>
       <c r="J130" s="5">
-        <v>46325</v>
+        <v>46328</v>
       </c>
       <c r="K130" s="6" t="s">
         <v>26</v>
@@ -9197,7 +9162,7 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="O130" s="6" t="s">
         <v>60</v>
@@ -9213,32 +9178,32 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B131" s="8">
-        <v>46181.61659114584</v>
+        <v>46181.61689748843</v>
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46182.64196408565</v>
+        <v>46182.8294564699</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>60</v>
+        <v>187</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>90</v>
+        <v>242</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>90</v>
+        <v>243</v>
       </c>
       <c r="I131" s="8">
-        <v>46325</v>
+        <v>46328</v>
       </c>
       <c r="J131" s="8">
-        <v>46325</v>
+        <v>46328</v>
       </c>
       <c r="K131" s="9" t="s">
         <v>26</v>
@@ -9250,13 +9215,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>60</v>
+        <v>187</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>60</v>
+        <v>187</v>
       </c>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
@@ -9266,32 +9231,32 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B132" s="5">
-        <v>46181.61662431713</v>
+        <v>46181.616942569446</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46182.64196105324</v>
+        <v>46182.82945721065</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>90</v>
+        <v>242</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>90</v>
+        <v>243</v>
       </c>
       <c r="I132" s="5">
-        <v>46325</v>
+        <v>46328</v>
       </c>
       <c r="J132" s="5">
-        <v>46325</v>
+        <v>46328</v>
       </c>
       <c r="K132" s="6" t="s">
         <v>26</v>
@@ -9303,13 +9268,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9319,32 +9284,32 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="B133" s="8">
-        <v>46181.61666238426</v>
+        <v>46181.6169815162</v>
       </c>
       <c r="C133" s="9"/>
       <c r="D133" s="8">
-        <v>46182.64195453704</v>
+        <v>46182.82945796296</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>90</v>
+        <v>242</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>90</v>
+        <v>243</v>
       </c>
       <c r="I133" s="8">
-        <v>46325</v>
+        <v>46328</v>
       </c>
       <c r="J133" s="8">
-        <v>46325</v>
+        <v>46328</v>
       </c>
       <c r="K133" s="9" t="s">
         <v>26</v>
@@ -9356,13 +9321,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9372,32 +9337,32 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="B134" s="5">
-        <v>46181.61670006944</v>
+        <v>46181.609592673616</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46182.64195372685</v>
+        <v>46182.642407384265</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>192</v>
+        <v>355</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>90</v>
+        <v>242</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>90</v>
+        <v>243</v>
       </c>
       <c r="I134" s="5">
-        <v>46325</v>
+        <v>46329</v>
       </c>
       <c r="J134" s="5">
-        <v>46325</v>
+        <v>46329</v>
       </c>
       <c r="K134" s="6" t="s">
         <v>26</v>
@@ -9409,33 +9374,43 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>350</v>
+        <v>318</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>277</v>
+        <v>182</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="Q134" s="6"/>
-      <c r="R134" s="6"/>
-      <c r="S134" s="6"/>
-      <c r="T134" s="6"/>
-      <c r="U134" s="6"/>
+        <v>356</v>
+      </c>
+      <c r="Q134" s="5">
+        <v>46329</v>
+      </c>
+      <c r="R134" s="5">
+        <v>46329</v>
+      </c>
+      <c r="S134" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T134" s="6">
+        <v>0</v>
+      </c>
+      <c r="U134" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B135" s="8">
-        <v>46181.60956560185</v>
+        <v>46181.60960517361</v>
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="8">
-        <v>46182.82952324074</v>
+        <v>46182.8294527199</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>360</v>
+        <v>182</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
@@ -9447,10 +9422,10 @@
         <v>243</v>
       </c>
       <c r="I135" s="8">
-        <v>46328</v>
+        <v>46329</v>
       </c>
       <c r="J135" s="8">
-        <v>46328</v>
+        <v>46329</v>
       </c>
       <c r="K135" s="9" t="s">
         <v>26</v>
@@ -9462,40 +9437,30 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="O135" s="9" t="s">
         <v>182</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>334</v>
-      </c>
-      <c r="Q135" s="8">
-        <v>46328</v>
-      </c>
-      <c r="R135" s="8">
-        <v>46328</v>
-      </c>
-      <c r="S135" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="T135" s="9">
-        <v>0</v>
-      </c>
-      <c r="U135" s="11" t="s">
-        <v>58</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="Q135" s="9"/>
+      <c r="R135" s="9"/>
+      <c r="S135" s="9"/>
+      <c r="T135" s="9"/>
+      <c r="U135" s="9"/>
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B136" s="5">
-        <v>46181.60957188657</v>
+        <v>46181.609610011576</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46182.82945300926</v>
+        <v>46182.829451909725</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>182</v>
@@ -9510,10 +9475,10 @@
         <v>243</v>
       </c>
       <c r="I136" s="5">
-        <v>46328</v>
+        <v>46329</v>
       </c>
       <c r="J136" s="5">
-        <v>46328</v>
+        <v>46329</v>
       </c>
       <c r="K136" s="6" t="s">
         <v>26</v>
@@ -9525,13 +9490,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="O136" s="6" t="s">
         <v>182</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>362</v>
+        <v>26</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9541,17 +9506,17 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="B137" s="8">
-        <v>46181.609583576384</v>
+        <v>46181.609613796296</v>
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46182.829453784725</v>
+        <v>46182.829452025464</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>182</v>
+        <v>60</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
@@ -9563,10 +9528,10 @@
         <v>243</v>
       </c>
       <c r="I137" s="8">
-        <v>46328</v>
+        <v>46329</v>
       </c>
       <c r="J137" s="8">
-        <v>46328</v>
+        <v>46329</v>
       </c>
       <c r="K137" s="9" t="s">
         <v>26</v>
@@ -9578,13 +9543,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>182</v>
+        <v>60</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>182</v>
+        <v>26</v>
       </c>
       <c r="Q137" s="9"/>
       <c r="R137" s="9"/>
@@ -9594,14 +9559,14 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="B138" s="5">
-        <v>46181.60958841435</v>
+        <v>46181.61712142361</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46182.829454583334</v>
+        <v>46182.82945197917</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>60</v>
@@ -9616,10 +9581,10 @@
         <v>243</v>
       </c>
       <c r="I138" s="5">
-        <v>46328</v>
+        <v>46329</v>
       </c>
       <c r="J138" s="5">
-        <v>46328</v>
+        <v>46329</v>
       </c>
       <c r="K138" s="6" t="s">
         <v>26</v>
@@ -9631,13 +9596,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="O138" s="6" t="s">
         <v>60</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9647,17 +9612,17 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="B139" s="8">
-        <v>46181.616839849536</v>
+        <v>46181.61716094907</v>
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46182.829455706014</v>
+        <v>46182.82945207176</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>60</v>
+        <v>187</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
@@ -9669,10 +9634,10 @@
         <v>243</v>
       </c>
       <c r="I139" s="8">
-        <v>46328</v>
+        <v>46329</v>
       </c>
       <c r="J139" s="8">
-        <v>46328</v>
+        <v>46329</v>
       </c>
       <c r="K139" s="9" t="s">
         <v>26</v>
@@ -9684,13 +9649,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>60</v>
+        <v>187</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
@@ -9700,17 +9665,17 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="B140" s="5">
-        <v>46181.61689748843</v>
+        <v>46181.61719633102</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46182.8294564699</v>
+        <v>46182.829452025464</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -9722,10 +9687,10 @@
         <v>243</v>
       </c>
       <c r="I140" s="5">
-        <v>46328</v>
+        <v>46329</v>
       </c>
       <c r="J140" s="5">
-        <v>46328</v>
+        <v>46329</v>
       </c>
       <c r="K140" s="6" t="s">
         <v>26</v>
@@ -9737,13 +9702,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>187</v>
+        <v>26</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -9753,17 +9718,17 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B141" s="8">
-        <v>46181.616942569446</v>
+        <v>46181.617235451384</v>
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46182.82945721065</v>
+        <v>46182.829452418984</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
@@ -9775,10 +9740,10 @@
         <v>243</v>
       </c>
       <c r="I141" s="8">
-        <v>46328</v>
+        <v>46329</v>
       </c>
       <c r="J141" s="8">
-        <v>46328</v>
+        <v>46329</v>
       </c>
       <c r="K141" s="9" t="s">
         <v>26</v>
@@ -9790,13 +9755,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>190</v>
+        <v>26</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -9806,33 +9771,27 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="B142" s="5">
-        <v>46181.6169815162</v>
+        <v>46181.60961741898</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46182.82945796296</v>
+        <v>46182.63449439815</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>192</v>
+        <v>365</v>
       </c>
       <c r="F142" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="H142" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="I142" s="5">
-        <v>46328</v>
-      </c>
-      <c r="J142" s="5">
-        <v>46328</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H142" s="6"/>
+      <c r="I142" s="6"/>
+      <c r="J142" s="6"/>
       <c r="K142" s="6" t="s">
         <v>26</v>
       </c>
@@ -9840,16 +9799,16 @@
         <v>26</v>
       </c>
       <c r="M142" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>360</v>
+        <v>26</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>192</v>
+        <v>366</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>192</v>
+        <v>26</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -9859,32 +9818,32 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B143" s="8">
-        <v>46181.609592673616</v>
+        <v>46181.60962174769</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46182.642407384265</v>
+        <v>46182.64244836806</v>
       </c>
       <c r="E143" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="F143" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G143" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="H143" s="9" t="s">
         <v>370</v>
       </c>
-      <c r="F143" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G143" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="H143" s="9" t="s">
-        <v>243</v>
-      </c>
       <c r="I143" s="8">
-        <v>46329</v>
+        <v>46330</v>
       </c>
       <c r="J143" s="8">
-        <v>46329</v>
+        <v>46337</v>
       </c>
       <c r="K143" s="9" t="s">
         <v>26</v>
@@ -9896,19 +9855,19 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>334</v>
+        <v>365</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>182</v>
+        <v>355</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="Q143" s="8">
-        <v>46329</v>
+        <v>46330</v>
       </c>
       <c r="R143" s="8">
-        <v>46329</v>
+        <v>46337</v>
       </c>
       <c r="S143" s="10" t="s">
         <v>32</v>
@@ -9922,32 +9881,32 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B144" s="5">
-        <v>46181.60960517361</v>
+        <v>46181.60962780092</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46182.8294527199</v>
+        <v>46191.67892958333</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>182</v>
+        <v>372</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>242</v>
+        <v>29</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>243</v>
+        <v>30</v>
       </c>
       <c r="I144" s="5">
-        <v>46329</v>
+        <v>46330</v>
       </c>
       <c r="J144" s="5">
-        <v>46329</v>
+        <v>46337</v>
       </c>
       <c r="K144" s="6" t="s">
         <v>26</v>
@@ -9959,49 +9918,53 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>182</v>
+        <v>355</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="Q144" s="6"/>
-      <c r="R144" s="6"/>
-      <c r="S144" s="6"/>
-      <c r="T144" s="6"/>
-      <c r="U144" s="6"/>
+        <v>365</v>
+      </c>
+      <c r="Q144" s="5">
+        <v>46330</v>
+      </c>
+      <c r="R144" s="5">
+        <v>46337</v>
+      </c>
+      <c r="S144" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T144" s="6">
+        <v>0</v>
+      </c>
+      <c r="U144" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
         <v>373</v>
       </c>
       <c r="B145" s="8">
-        <v>46181.609610011576</v>
+        <v>46181.60963489584</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46182.829451909725</v>
+        <v>46182.63449431713</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>182</v>
+        <v>374</v>
       </c>
       <c r="F145" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="H145" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="I145" s="8">
-        <v>46329</v>
-      </c>
-      <c r="J145" s="8">
-        <v>46329</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H145" s="9"/>
+      <c r="I145" s="9"/>
+      <c r="J145" s="9"/>
       <c r="K145" s="9" t="s">
         <v>26</v>
       </c>
@@ -10009,51 +9972,57 @@
         <v>26</v>
       </c>
       <c r="M145" s="9" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>370</v>
+        <v>26</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>182</v>
+        <v>375</v>
       </c>
       <c r="P145" s="9" t="s">
         <v>26</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
-      <c r="S145" s="9"/>
-      <c r="T145" s="9"/>
-      <c r="U145" s="9"/>
+      <c r="S145" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T145" s="9">
+        <v>0</v>
+      </c>
+      <c r="U145" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B146" s="5">
-        <v>46181.609613796296</v>
+        <v>46181.609640208335</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46182.829452025464</v>
+        <v>46182.64254377315</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>60</v>
+        <v>377</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>242</v>
+        <v>49</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>243</v>
+        <v>50</v>
       </c>
       <c r="I146" s="5">
-        <v>46329</v>
+        <v>46330</v>
       </c>
       <c r="J146" s="5">
-        <v>46329</v>
+        <v>46338</v>
       </c>
       <c r="K146" s="6" t="s">
         <v>26</v>
@@ -10065,48 +10034,58 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>60</v>
+        <v>355</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q146" s="6"/>
-      <c r="R146" s="6"/>
-      <c r="S146" s="6"/>
-      <c r="T146" s="6"/>
-      <c r="U146" s="6"/>
+        <v>378</v>
+      </c>
+      <c r="Q146" s="5">
+        <v>46330</v>
+      </c>
+      <c r="R146" s="5">
+        <v>46338</v>
+      </c>
+      <c r="S146" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T146" s="6">
+        <v>0</v>
+      </c>
+      <c r="U146" s="11" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B147" s="8">
-        <v>46181.61712142361</v>
+        <v>46181.609646365745</v>
       </c>
       <c r="C147" s="9"/>
       <c r="D147" s="8">
-        <v>46182.82945197917</v>
+        <v>46182.64254079861</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>60</v>
+        <v>380</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>242</v>
+        <v>49</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>243</v>
+        <v>50</v>
       </c>
       <c r="I147" s="8">
-        <v>46329</v>
+        <v>46339</v>
       </c>
       <c r="J147" s="8">
-        <v>46329</v>
+        <v>46349</v>
       </c>
       <c r="K147" s="9" t="s">
         <v>26</v>
@@ -10118,528 +10097,27 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>60</v>
+        <v>377</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q147" s="9"/>
-      <c r="R147" s="9"/>
-      <c r="S147" s="9"/>
-      <c r="T147" s="9"/>
-      <c r="U147" s="9"/>
-    </row>
-    <row r="148" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A148" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="B148" s="5">
-        <v>46181.61716094907</v>
-      </c>
-      <c r="C148" s="6"/>
-      <c r="D148" s="5">
-        <v>46182.82945207176</v>
-      </c>
-      <c r="E148" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="F148" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G148" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="H148" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="I148" s="5">
-        <v>46329</v>
-      </c>
-      <c r="J148" s="5">
-        <v>46329</v>
-      </c>
-      <c r="K148" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L148" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M148" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N148" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="O148" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="P148" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q148" s="6"/>
-      <c r="R148" s="6"/>
-      <c r="S148" s="6"/>
-      <c r="T148" s="6"/>
-      <c r="U148" s="6"/>
-    </row>
-    <row r="149" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A149" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="B149" s="8">
-        <v>46181.61719633102</v>
-      </c>
-      <c r="C149" s="9"/>
-      <c r="D149" s="8">
-        <v>46182.829452025464</v>
-      </c>
-      <c r="E149" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="F149" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G149" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="H149" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="I149" s="8">
-        <v>46329</v>
-      </c>
-      <c r="J149" s="8">
-        <v>46329</v>
-      </c>
-      <c r="K149" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L149" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M149" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N149" s="9" t="s">
-        <v>370</v>
-      </c>
-      <c r="O149" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="P149" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q149" s="9"/>
-      <c r="R149" s="9"/>
-      <c r="S149" s="9"/>
-      <c r="T149" s="9"/>
-      <c r="U149" s="9"/>
-    </row>
-    <row r="150" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A150" s="4" t="s">
-        <v>378</v>
-      </c>
-      <c r="B150" s="5">
-        <v>46181.617235451384</v>
-      </c>
-      <c r="C150" s="6"/>
-      <c r="D150" s="5">
-        <v>46182.829452418984</v>
-      </c>
-      <c r="E150" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="F150" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G150" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="H150" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="I150" s="5">
-        <v>46329</v>
-      </c>
-      <c r="J150" s="5">
-        <v>46329</v>
-      </c>
-      <c r="K150" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L150" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M150" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N150" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="O150" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="P150" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q150" s="6"/>
-      <c r="R150" s="6"/>
-      <c r="S150" s="6"/>
-      <c r="T150" s="6"/>
-      <c r="U150" s="6"/>
-    </row>
-    <row r="151" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A151" s="7" t="s">
-        <v>379</v>
-      </c>
-      <c r="B151" s="8">
-        <v>46181.60961741898</v>
-      </c>
-      <c r="C151" s="9"/>
-      <c r="D151" s="8">
-        <v>46182.63449439815</v>
-      </c>
-      <c r="E151" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="F151" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G151" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H151" s="9"/>
-      <c r="I151" s="9"/>
-      <c r="J151" s="9"/>
-      <c r="K151" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L151" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M151" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="Q147" s="8">
+        <v>46339</v>
+      </c>
+      <c r="R147" s="8">
+        <v>46349</v>
+      </c>
+      <c r="S147" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T147" s="9">
         <v>0</v>
       </c>
-      <c r="N151" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O151" s="9" t="s">
-        <v>381</v>
-      </c>
-      <c r="P151" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q151" s="9"/>
-      <c r="R151" s="9"/>
-      <c r="S151" s="9"/>
-      <c r="T151" s="9"/>
-      <c r="U151" s="9"/>
-    </row>
-    <row r="152" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A152" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="B152" s="5">
-        <v>46181.60962174769</v>
-      </c>
-      <c r="C152" s="6"/>
-      <c r="D152" s="5">
-        <v>46182.64244836806</v>
-      </c>
-      <c r="E152" s="6" t="s">
-        <v>383</v>
-      </c>
-      <c r="F152" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G152" s="6" t="s">
-        <v>384</v>
-      </c>
-      <c r="H152" s="6" t="s">
-        <v>385</v>
-      </c>
-      <c r="I152" s="5">
-        <v>46330</v>
-      </c>
-      <c r="J152" s="5">
-        <v>46337</v>
-      </c>
-      <c r="K152" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L152" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M152" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N152" s="6" t="s">
-        <v>380</v>
-      </c>
-      <c r="O152" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="P152" s="6" t="s">
-        <v>380</v>
-      </c>
-      <c r="Q152" s="5">
-        <v>46330</v>
-      </c>
-      <c r="R152" s="5">
-        <v>46337</v>
-      </c>
-      <c r="S152" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="T152" s="6">
-        <v>0</v>
-      </c>
-      <c r="U152" s="11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="153" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A153" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="B153" s="8">
-        <v>46181.60962780092</v>
-      </c>
-      <c r="C153" s="9"/>
-      <c r="D153" s="8">
-        <v>46191.67892958333</v>
-      </c>
-      <c r="E153" s="9" t="s">
-        <v>387</v>
-      </c>
-      <c r="F153" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G153" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="H153" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="I153" s="8">
-        <v>46330</v>
-      </c>
-      <c r="J153" s="8">
-        <v>46337</v>
-      </c>
-      <c r="K153" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L153" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M153" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N153" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="O153" s="9" t="s">
-        <v>370</v>
-      </c>
-      <c r="P153" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="Q153" s="8">
-        <v>46330</v>
-      </c>
-      <c r="R153" s="8">
-        <v>46337</v>
-      </c>
-      <c r="S153" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="T153" s="9">
-        <v>0</v>
-      </c>
-      <c r="U153" s="11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="154" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A154" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="B154" s="5">
-        <v>46181.60963489584</v>
-      </c>
-      <c r="C154" s="6"/>
-      <c r="D154" s="5">
-        <v>46182.63449431713</v>
-      </c>
-      <c r="E154" s="6" t="s">
-        <v>389</v>
-      </c>
-      <c r="F154" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G154" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H154" s="6"/>
-      <c r="I154" s="6"/>
-      <c r="J154" s="6"/>
-      <c r="K154" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L154" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M154" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="N154" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O154" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="P154" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q154" s="6"/>
-      <c r="R154" s="6"/>
-      <c r="S154" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="T154" s="6">
-        <v>0</v>
-      </c>
-      <c r="U154" s="11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="155" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A155" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="B155" s="8">
-        <v>46181.609640208335</v>
-      </c>
-      <c r="C155" s="9"/>
-      <c r="D155" s="8">
-        <v>46182.64254377315</v>
-      </c>
-      <c r="E155" s="9" t="s">
-        <v>392</v>
-      </c>
-      <c r="F155" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G155" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="H155" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="I155" s="8">
-        <v>46330</v>
-      </c>
-      <c r="J155" s="8">
-        <v>46338</v>
-      </c>
-      <c r="K155" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L155" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M155" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N155" s="9" t="s">
-        <v>389</v>
-      </c>
-      <c r="O155" s="9" t="s">
-        <v>370</v>
-      </c>
-      <c r="P155" s="9" t="s">
-        <v>393</v>
-      </c>
-      <c r="Q155" s="8">
-        <v>46330</v>
-      </c>
-      <c r="R155" s="8">
-        <v>46338</v>
-      </c>
-      <c r="S155" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="T155" s="9">
-        <v>0</v>
-      </c>
-      <c r="U155" s="11" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="156" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A156" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="B156" s="5">
-        <v>46181.609646365745</v>
-      </c>
-      <c r="C156" s="6"/>
-      <c r="D156" s="5">
-        <v>46182.64254079861</v>
-      </c>
-      <c r="E156" s="6" t="s">
-        <v>395</v>
-      </c>
-      <c r="F156" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G156" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H156" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="I156" s="5">
-        <v>46339</v>
-      </c>
-      <c r="J156" s="5">
-        <v>46349</v>
-      </c>
-      <c r="K156" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L156" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M156" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N156" s="6" t="s">
-        <v>389</v>
-      </c>
-      <c r="O156" s="6" t="s">
-        <v>392</v>
-      </c>
-      <c r="P156" s="6" t="s">
-        <v>389</v>
-      </c>
-      <c r="Q156" s="5">
-        <v>46339</v>
-      </c>
-      <c r="R156" s="5">
-        <v>46349</v>
-      </c>
-      <c r="S156" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="T156" s="6">
-        <v>0</v>
-      </c>
-      <c r="U156" s="11" t="s">
+      <c r="U147" s="11" t="s">
         <v>58</v>
       </c>
     </row>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -3548,9 +3548,11 @@
       <c r="B32" s="5">
         <v>46181.60900793981</v>
       </c>
-      <c r="C32" s="6"/>
+      <c r="C32" s="5">
+        <v>46217.69797177083</v>
+      </c>
       <c r="D32" s="5">
-        <v>46195.6859309838</v>
+        <v>46217.69798377315</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>123</v>
@@ -3598,10 +3600,10 @@
         <v>32</v>
       </c>
       <c r="T32" s="6">
-        <v>0</v>
-      </c>
-      <c r="U32" s="11" t="s">
-        <v>58</v>
+        <v>1</v>
+      </c>
+      <c r="U32" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
@@ -3666,9 +3668,11 @@
       <c r="B34" s="5">
         <v>46181.60901612269</v>
       </c>
-      <c r="C34" s="6"/>
+      <c r="C34" s="5">
+        <v>46217.69795534722</v>
+      </c>
       <c r="D34" s="5">
-        <v>46195.685932430555</v>
+        <v>46217.69795753472</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>130</v>
@@ -6859,7 +6863,7 @@
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46212.6232265162</v>
+        <v>46217.697973773145</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>61</v>
@@ -6909,8 +6913,8 @@
       <c r="T89" s="9">
         <v>0</v>
       </c>
-      <c r="U89" s="11" t="s">
-        <v>58</v>
+      <c r="U89" s="12" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1720" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1720" uniqueCount="382">
   <si>
     <t>50001559 - FERROVIAL</t>
   </si>
@@ -458,6 +458,9 @@
   </si>
   <si>
     <t xml:space="preserve">Generación OC   ot 4343 ,fabricación tableros   ot 4343 </t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1215506819635564</t>
@@ -3552,7 +3555,7 @@
         <v>46217.69797177083</v>
       </c>
       <c r="D32" s="5">
-        <v>46217.69798377315</v>
+        <v>46218.18782881944</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>123</v>
@@ -3596,8 +3599,8 @@
       <c r="R32" s="5">
         <v>46225</v>
       </c>
-      <c r="S32" s="10" t="s">
-        <v>32</v>
+      <c r="S32" s="12" t="s">
+        <v>127</v>
       </c>
       <c r="T32" s="6">
         <v>1</v>
@@ -3608,7 +3611,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B33" s="8">
         <v>46181.60901165509</v>
@@ -3653,7 +3656,7 @@
         <v>108</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3663,7 +3666,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B34" s="5">
         <v>46181.60901612269</v>
@@ -3675,7 +3678,7 @@
         <v>46217.69795753472</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
@@ -3708,7 +3711,7 @@
         <v>109</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3718,7 +3721,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B35" s="8">
         <v>46181.60902011574</v>
@@ -3736,10 +3739,10 @@
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I35" s="8">
         <v>46252</v>
@@ -3760,7 +3763,7 @@
         <v>119</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P35" s="9" t="s">
         <v>119</v>
@@ -3783,7 +3786,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B36" s="5">
         <v>46181.60902488426</v>
@@ -3795,16 +3798,16 @@
         <v>46199.57115532407</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I36" s="5">
         <v>46252</v>
@@ -3828,7 +3831,7 @@
         <v>93</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3844,7 +3847,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B37" s="8">
         <v>46181.609029803236</v>
@@ -3856,16 +3859,16 @@
         <v>46205.61257221065</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I37" s="8">
         <v>46254</v>
@@ -3886,10 +3889,10 @@
         <v>120</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3905,7 +3908,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B38" s="5">
         <v>46181.60903511574</v>
@@ -3917,16 +3920,16 @@
         <v>46199.572352546296</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I38" s="5">
         <v>46252</v>
@@ -3947,7 +3950,7 @@
         <v>119</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3970,7 +3973,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B39" s="8">
         <v>46181.60903861111</v>
@@ -3988,10 +3991,10 @@
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I39" s="8">
         <v>46252</v>
@@ -4009,13 +4012,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O39" s="9" t="s">
         <v>99</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -4025,7 +4028,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B40" s="5">
         <v>46181.609042951386</v>
@@ -4037,16 +4040,16 @@
         <v>46199.57232634259</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I40" s="5">
         <v>46254</v>
@@ -4064,13 +4067,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>100</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4080,7 +4083,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B41" s="8">
         <v>46181.609047164355</v>
@@ -4092,16 +4095,16 @@
         <v>46212.82441381944</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I41" s="8">
         <v>46252</v>
@@ -4122,7 +4125,7 @@
         <v>119</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P41" s="9" t="s">
         <v>26</v>
@@ -4145,7 +4148,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B42" s="5">
         <v>46181.60905075232</v>
@@ -4163,10 +4166,10 @@
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I42" s="5">
         <v>46252</v>
@@ -4184,13 +4187,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>105</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4200,7 +4203,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B43" s="8">
         <v>46181.60905546296</v>
@@ -4212,16 +4215,16 @@
         <v>46204.67391837963</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I43" s="8">
         <v>46261</v>
@@ -4239,13 +4242,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O43" s="9" t="s">
         <v>106</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -4255,7 +4258,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B44" s="5">
         <v>46181.60906018519</v>
@@ -4265,16 +4268,16 @@
         <v>46204.67384744213</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I44" s="5">
         <v>46290</v>
@@ -4292,10 +4295,10 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>26</v>
@@ -4308,7 +4311,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B45" s="8">
         <v>46181.609063310185</v>
@@ -4320,16 +4323,16 @@
         <v>46205.61290721065</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I45" s="8">
         <v>46252</v>
@@ -4350,7 +4353,7 @@
         <v>119</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>26</v>
@@ -4373,7 +4376,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B46" s="5">
         <v>46181.60906703703</v>
@@ -4391,10 +4394,10 @@
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I46" s="5">
         <v>46252</v>
@@ -4412,13 +4415,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>102</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4428,7 +4431,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B47" s="8">
         <v>46181.60907681713</v>
@@ -4440,16 +4443,16 @@
         <v>46205.612879328706</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I47" s="8">
         <v>46254</v>
@@ -4467,13 +4470,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>103</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
@@ -4483,7 +4486,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B48" s="5">
         <v>46181.6090815625</v>
@@ -4495,7 +4498,7 @@
         <v>46210.525643402776</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>25</v>
@@ -4519,7 +4522,7 @@
         <v>26</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>26</v>
@@ -4536,7 +4539,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B49" s="8">
         <v>46181.60908480324</v>
@@ -4548,16 +4551,16 @@
         <v>46197.7158150926</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I49" s="8">
         <v>46174</v>
@@ -4575,13 +4578,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q49" s="8">
         <v>46174</v>
@@ -4590,7 +4593,7 @@
         <v>46191</v>
       </c>
       <c r="S49" s="11" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="T49" s="9">
         <v>1</v>
@@ -4601,7 +4604,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B50" s="5">
         <v>46181.60908915509</v>
@@ -4613,16 +4616,16 @@
         <v>46190.70821390046</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I50" s="5">
         <v>46174</v>
@@ -4640,13 +4643,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>77</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4656,7 +4659,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B51" s="8">
         <v>46181.60909384259</v>
@@ -4668,16 +4671,16 @@
         <v>46190.7082228125</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I51" s="8">
         <v>46174</v>
@@ -4695,13 +4698,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>77</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4711,7 +4714,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B52" s="5">
         <v>46181.61221741898</v>
@@ -4723,16 +4726,16 @@
         <v>46190.708227337964</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I52" s="5">
         <v>46174</v>
@@ -4750,13 +4753,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>77</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4766,7 +4769,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B53" s="8">
         <v>46181.612357199076</v>
@@ -4778,16 +4781,16 @@
         <v>46190.708233321755</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I53" s="8">
         <v>46174</v>
@@ -4805,13 +4808,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>77</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -4821,7 +4824,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B54" s="5">
         <v>46181.609098182875</v>
@@ -4833,16 +4836,16 @@
         <v>46197.71584820602</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I54" s="5">
         <v>46227</v>
@@ -4860,13 +4863,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q54" s="5">
         <v>46227</v>
@@ -4886,7 +4889,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B55" s="8">
         <v>46181.60910252314</v>
@@ -4898,16 +4901,16 @@
         <v>46191.54270819444</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I55" s="8">
         <v>46227</v>
@@ -4925,13 +4928,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4941,7 +4944,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B56" s="5">
         <v>46181.609107951386</v>
@@ -4953,16 +4956,16 @@
         <v>46191.54271703704</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I56" s="5">
         <v>46227</v>
@@ -4980,13 +4983,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4996,7 +4999,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B57" s="8">
         <v>46181.61393570602</v>
@@ -5008,16 +5011,16 @@
         <v>46190.70842170139</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I57" s="8">
         <v>46227</v>
@@ -5035,13 +5038,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5051,7 +5054,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B58" s="5">
         <v>46181.61396929398</v>
@@ -5063,16 +5066,16 @@
         <v>46190.708426550926</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I58" s="5">
         <v>46227</v>
@@ -5090,13 +5093,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5106,7 +5109,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B59" s="8">
         <v>46181.60911329861</v>
@@ -5124,10 +5127,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I59" s="8">
         <v>46247</v>
@@ -5145,13 +5148,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q59" s="8">
         <v>46247</v>
@@ -5171,7 +5174,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B60" s="5">
         <v>46181.60912350695</v>
@@ -5183,16 +5186,16 @@
         <v>46191.54536050926</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I60" s="6"/>
       <c r="J60" s="5">
@@ -5211,7 +5214,7 @@
         <v>96</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>96</v>
@@ -5224,7 +5227,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B61" s="8">
         <v>46181.60912782408</v>
@@ -5236,16 +5239,16 @@
         <v>46191.54537386574</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I61" s="9"/>
       <c r="J61" s="8">
@@ -5264,7 +5267,7 @@
         <v>96</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>96</v>
@@ -5277,7 +5280,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B62" s="5">
         <v>46181.614119606485</v>
@@ -5289,16 +5292,16 @@
         <v>46190.721725358795</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I62" s="6"/>
       <c r="J62" s="5">
@@ -5317,7 +5320,7 @@
         <v>96</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5330,7 +5333,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B63" s="8">
         <v>46181.61419627315</v>
@@ -5342,16 +5345,16 @@
         <v>46190.7217299537</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I63" s="9"/>
       <c r="J63" s="8">
@@ -5370,7 +5373,7 @@
         <v>96</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5383,7 +5386,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B64" s="5">
         <v>46181.60913207176</v>
@@ -5393,16 +5396,16 @@
         <v>46212.622826203704</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I64" s="5">
         <v>46322</v>
@@ -5420,10 +5423,10 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>26</v>
@@ -5446,7 +5449,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B65" s="8">
         <v>46181.609135833336</v>
@@ -5456,16 +5459,16 @@
         <v>46182.63311847222</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I65" s="8">
         <v>46322</v>
@@ -5483,13 +5486,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5499,7 +5502,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B66" s="5">
         <v>46181.614311909725</v>
@@ -5509,16 +5512,16 @@
         <v>46182.63311923611</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I66" s="5">
         <v>46322</v>
@@ -5536,13 +5539,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5552,7 +5555,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B67" s="8">
         <v>46181.60918671296</v>
@@ -5564,7 +5567,7 @@
         <v>46216.64129429398</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>25</v>
@@ -5588,7 +5591,7 @@
         <v>26</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>26</v>
@@ -5605,7 +5608,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B68" s="5">
         <v>46181.609196087964</v>
@@ -5617,16 +5620,16 @@
         <v>46213.56938424769</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I68" s="5">
         <v>46252</v>
@@ -5644,13 +5647,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q68" s="5">
         <v>46252</v>
@@ -5670,7 +5673,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B69" s="8">
         <v>46181.609201921296</v>
@@ -5682,16 +5685,16 @@
         <v>46216.71548459491</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I69" s="8">
         <v>46254</v>
@@ -5709,13 +5712,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q69" s="8">
         <v>46254</v>
@@ -5735,7 +5738,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B70" s="5">
         <v>46181.60920746528</v>
@@ -5747,16 +5750,16 @@
         <v>46213.569400231485</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I70" s="5">
         <v>46252</v>
@@ -5774,13 +5777,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q70" s="5">
         <v>46252</v>
@@ -5800,7 +5803,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B71" s="8">
         <v>46181.609212870375</v>
@@ -5812,16 +5815,16 @@
         <v>46216.715484733795</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I71" s="8">
         <v>46254</v>
@@ -5839,13 +5842,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q71" s="8">
         <v>46254</v>
@@ -5865,7 +5868,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B72" s="5">
         <v>46181.60921715278</v>
@@ -5877,16 +5880,16 @@
         <v>46213.569419479165</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I72" s="5">
         <v>46252</v>
@@ -5904,13 +5907,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q72" s="5">
         <v>46252</v>
@@ -5930,7 +5933,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B73" s="8">
         <v>46181.60922180556</v>
@@ -5942,16 +5945,16 @@
         <v>46216.71548493055</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I73" s="8">
         <v>46254</v>
@@ -5969,13 +5972,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q73" s="8">
         <v>46254</v>
@@ -5995,7 +5998,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B74" s="5">
         <v>46181.60922590278</v>
@@ -6005,7 +6008,7 @@
         <v>46181.782424143516</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>25</v>
@@ -6029,7 +6032,7 @@
         <v>26</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>26</v>
@@ -6042,7 +6045,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B75" s="8">
         <v>46181.60922940972</v>
@@ -6052,16 +6055,16 @@
         <v>46216.71555703704</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I75" s="8">
         <v>46258</v>
@@ -6079,13 +6082,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q75" s="8">
         <v>46258</v>
@@ -6105,7 +6108,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B76" s="5">
         <v>46181.60923553241</v>
@@ -6115,16 +6118,16 @@
         <v>46216.641273009256</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I76" s="5">
         <v>46258</v>
@@ -6142,13 +6145,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6158,7 +6161,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B77" s="8">
         <v>46181.609241805556</v>
@@ -6168,16 +6171,16 @@
         <v>46216.64127412037</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I77" s="8">
         <v>46258</v>
@@ -6195,13 +6198,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
@@ -6211,7 +6214,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B78" s="5">
         <v>46181.609247002314</v>
@@ -6221,16 +6224,16 @@
         <v>46212.62258834491</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I78" s="5">
         <v>46267</v>
@@ -6248,13 +6251,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q78" s="5">
         <v>46267</v>
@@ -6274,7 +6277,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B79" s="8">
         <v>46181.60925648148</v>
@@ -6284,16 +6287,16 @@
         <v>46191.54540523148</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I79" s="8">
         <v>46267</v>
@@ -6311,13 +6314,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6327,7 +6330,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B80" s="5">
         <v>46181.609262199076</v>
@@ -6337,16 +6340,16 @@
         <v>46191.54540574074</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I80" s="5">
         <v>46267</v>
@@ -6364,13 +6367,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6380,7 +6383,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B81" s="8">
         <v>46181.60926783565</v>
@@ -6390,16 +6393,16 @@
         <v>46212.62263724537</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I81" s="8">
         <v>46289</v>
@@ -6417,13 +6420,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q81" s="8">
         <v>46289</v>
@@ -6443,7 +6446,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B82" s="5">
         <v>46181.60927226851</v>
@@ -6453,16 +6456,16 @@
         <v>46191.545403842596</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I82" s="5">
         <v>46289</v>
@@ -6480,13 +6483,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6496,7 +6499,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B83" s="8">
         <v>46181.60927799769</v>
@@ -6506,16 +6509,16 @@
         <v>46191.545404212964</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I83" s="8">
         <v>46289</v>
@@ -6533,13 +6536,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6549,7 +6552,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B84" s="5">
         <v>46181.60928361111</v>
@@ -6559,7 +6562,7 @@
         <v>46213.56805377315</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>25</v>
@@ -6583,7 +6586,7 @@
         <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6598,7 +6601,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B85" s="8">
         <v>46181.609286990744</v>
@@ -6610,16 +6613,16 @@
         <v>46213.56773226852</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I85" s="8">
         <v>46182</v>
@@ -6637,13 +6640,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q85" s="8">
         <v>46182</v>
@@ -6652,7 +6655,7 @@
         <v>46183</v>
       </c>
       <c r="S85" s="11" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="T85" s="9">
         <v>1</v>
@@ -6663,7 +6666,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B86" s="5">
         <v>46181.609292974535</v>
@@ -6675,16 +6678,16 @@
         <v>46213.56774653935</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I86" s="5">
         <v>46290</v>
@@ -6702,13 +6705,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q86" s="5">
         <v>46290</v>
@@ -6728,7 +6731,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B87" s="8">
         <v>46181.60929881944</v>
@@ -6740,16 +6743,16 @@
         <v>46213.56805165509</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I87" s="8">
         <v>46226</v>
@@ -6767,13 +6770,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q87" s="8">
         <v>46226</v>
@@ -6793,7 +6796,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B88" s="5">
         <v>46181.60930480324</v>
@@ -6803,16 +6806,16 @@
         <v>46212.623013958335</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I88" s="5">
         <v>46293</v>
@@ -6830,13 +6833,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q88" s="5">
         <v>46293</v>
@@ -6856,7 +6859,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B89" s="8">
         <v>46181.60935271991</v>
@@ -6872,10 +6875,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I89" s="8">
         <v>46226</v>
@@ -6893,10 +6896,10 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P89" s="9" t="s">
         <v>56</v>
@@ -6919,7 +6922,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B90" s="5">
         <v>46181.60936674768</v>
@@ -6929,7 +6932,7 @@
         <v>46213.50490068287</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -6953,7 +6956,7 @@
         <v>26</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -6966,7 +6969,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B91" s="8">
         <v>46181.609371666666</v>
@@ -6976,7 +6979,7 @@
         <v>46182.64123547454</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -7003,13 +7006,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q91" s="8">
         <v>46290</v>
@@ -7029,7 +7032,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B92" s="5">
         <v>46181.609378587964</v>
@@ -7039,7 +7042,7 @@
         <v>46182.64119599537</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7066,13 +7069,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7082,7 +7085,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B93" s="8">
         <v>46181.61514019676</v>
@@ -7092,7 +7095,7 @@
         <v>46182.64119222222</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -7119,13 +7122,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7135,7 +7138,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B94" s="5">
         <v>46181.609386111115</v>
@@ -7147,7 +7150,7 @@
         <v>46212.62246368056</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7174,13 +7177,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q94" s="5">
         <v>46311</v>
@@ -7200,7 +7203,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B95" s="8">
         <v>46181.60939194444</v>
@@ -7212,7 +7215,7 @@
         <v>46213.56773570602</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -7239,13 +7242,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7255,7 +7258,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B96" s="5">
         <v>46181.61518315972</v>
@@ -7267,7 +7270,7 @@
         <v>46213.567735150464</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7294,10 +7297,10 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>26</v>
@@ -7310,7 +7313,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B97" s="8">
         <v>46181.60939866898</v>
@@ -7322,7 +7325,7 @@
         <v>46213.50490375</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
@@ -7349,13 +7352,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q97" s="8">
         <v>46315</v>
@@ -7375,7 +7378,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B98" s="5">
         <v>46181.60940505787</v>
@@ -7387,7 +7390,7 @@
         <v>46213.56772277778</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7414,13 +7417,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7430,7 +7433,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B99" s="8">
         <v>46181.61523613426</v>
@@ -7442,7 +7445,7 @@
         <v>46213.56772202546</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7469,10 +7472,10 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P99" s="9" t="s">
         <v>26</v>
@@ -7485,7 +7488,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B100" s="5">
         <v>46181.60941365741</v>
@@ -7495,7 +7498,7 @@
         <v>46212.62250564815</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7522,13 +7525,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q100" s="5">
         <v>46317</v>
@@ -7548,7 +7551,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B101" s="8">
         <v>46181.60941929398</v>
@@ -7558,7 +7561,7 @@
         <v>46213.56804261574</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7585,13 +7588,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7601,7 +7604,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B102" s="5">
         <v>46181.61528053241</v>
@@ -7611,7 +7614,7 @@
         <v>46213.568041192135</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7638,10 +7641,10 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>26</v>
@@ -7654,7 +7657,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B103" s="8">
         <v>46181.60942706019</v>
@@ -7664,7 +7667,7 @@
         <v>46212.62252259259</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -7691,13 +7694,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q103" s="8">
         <v>46321</v>
@@ -7717,7 +7720,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B104" s="5">
         <v>46181.60943415509</v>
@@ -7727,7 +7730,7 @@
         <v>46182.641623125004</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7754,13 +7757,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7770,7 +7773,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B105" s="8">
         <v>46181.61532783565</v>
@@ -7780,7 +7783,7 @@
         <v>46182.64161924769</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -7807,13 +7810,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -7823,7 +7826,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B106" s="5">
         <v>46181.60944410879</v>
@@ -7833,7 +7836,7 @@
         <v>46212.622555497685</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7860,13 +7863,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q106" s="5">
         <v>46323</v>
@@ -7886,7 +7889,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B107" s="8">
         <v>46181.60944996528</v>
@@ -7896,7 +7899,7 @@
         <v>46182.64173178241</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -7923,13 +7926,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -7939,7 +7942,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B108" s="5">
         <v>46181.61537143518</v>
@@ -7949,7 +7952,7 @@
         <v>46182.64172883102</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7976,10 +7979,10 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>26</v>
@@ -7992,7 +7995,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B109" s="8">
         <v>46181.60945642361</v>
@@ -8002,7 +8005,7 @@
         <v>46182.634494212965</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>25</v>
@@ -8026,7 +8029,7 @@
         <v>26</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P109" s="9" t="s">
         <v>26</v>
@@ -8039,7 +8042,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B110" s="5">
         <v>46181.60946096065</v>
@@ -8049,16 +8052,16 @@
         <v>46182.64186350694</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I110" s="5">
         <v>46324</v>
@@ -8076,13 +8079,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q110" s="5">
         <v>46324</v>
@@ -8102,7 +8105,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B111" s="8">
         <v>46181.60946868056</v>
@@ -8112,16 +8115,16 @@
         <v>46182.641845254635</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I111" s="8">
         <v>46324</v>
@@ -8139,13 +8142,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q111" s="9"/>
       <c r="R111" s="9"/>
@@ -8155,7 +8158,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B112" s="5">
         <v>46181.609475034726</v>
@@ -8165,16 +8168,16 @@
         <v>46182.64184081019</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I112" s="5">
         <v>46324</v>
@@ -8192,13 +8195,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8208,7 +8211,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B113" s="8">
         <v>46181.60947921296</v>
@@ -8224,10 +8227,10 @@
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I113" s="8">
         <v>46324</v>
@@ -8245,7 +8248,7 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O113" s="9" t="s">
         <v>60</v>
@@ -8261,7 +8264,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B114" s="5">
         <v>46181.61605960648</v>
@@ -8277,10 +8280,10 @@
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I114" s="5">
         <v>46324</v>
@@ -8298,7 +8301,7 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>60</v>
@@ -8314,7 +8317,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B115" s="8">
         <v>46181.61617203704</v>
@@ -8324,16 +8327,16 @@
         <v>46216.71559670139</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I115" s="8">
         <v>46324</v>
@@ -8351,13 +8354,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O115" s="9" t="s">
         <v>26</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q115" s="9"/>
       <c r="R115" s="9"/>
@@ -8367,7 +8370,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B116" s="5">
         <v>46181.61620771991</v>
@@ -8377,16 +8380,16 @@
         <v>46216.715609837964</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I116" s="5">
         <v>46324</v>
@@ -8404,13 +8407,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8420,7 +8423,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B117" s="8">
         <v>46181.616245833335</v>
@@ -8430,16 +8433,16 @@
         <v>46216.715626087964</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="I117" s="8">
         <v>46324</v>
@@ -8457,13 +8460,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8473,7 +8476,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B118" s="5">
         <v>46181.60948424769</v>
@@ -8483,7 +8486,7 @@
         <v>46182.64199267361</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8510,13 +8513,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q118" s="5">
         <v>46325</v>
@@ -8536,7 +8539,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B119" s="8">
         <v>46181.60948969907</v>
@@ -8546,7 +8549,7 @@
         <v>46182.641973854166</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
@@ -8573,13 +8576,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8589,7 +8592,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B120" s="5">
         <v>46181.60949538194</v>
@@ -8599,7 +8602,7 @@
         <v>46182.64197085648</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8626,13 +8629,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8642,7 +8645,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B121" s="8">
         <v>46181.609560185185</v>
@@ -8679,7 +8682,7 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O121" s="9" t="s">
         <v>60</v>
@@ -8695,7 +8698,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B122" s="5">
         <v>46181.61659114584</v>
@@ -8732,7 +8735,7 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>60</v>
@@ -8748,7 +8751,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B123" s="8">
         <v>46181.61662431713</v>
@@ -8758,7 +8761,7 @@
         <v>46182.64196105324</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
@@ -8785,13 +8788,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q123" s="9"/>
       <c r="R123" s="9"/>
@@ -8801,7 +8804,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B124" s="5">
         <v>46181.61666238426</v>
@@ -8811,7 +8814,7 @@
         <v>46182.64195453704</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8838,13 +8841,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8854,7 +8857,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B125" s="8">
         <v>46181.61670006944</v>
@@ -8864,7 +8867,7 @@
         <v>46182.64195372685</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -8891,13 +8894,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -8907,7 +8910,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B126" s="5">
         <v>46181.60956560185</v>
@@ -8917,16 +8920,16 @@
         <v>46182.82952324074</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I126" s="5">
         <v>46328</v>
@@ -8944,13 +8947,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q126" s="5">
         <v>46328</v>
@@ -8970,7 +8973,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B127" s="8">
         <v>46181.60957188657</v>
@@ -8980,16 +8983,16 @@
         <v>46182.82945300926</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H127" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I127" s="8">
         <v>46328</v>
@@ -9007,13 +9010,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -9023,7 +9026,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B128" s="5">
         <v>46181.609583576384</v>
@@ -9033,16 +9036,16 @@
         <v>46182.829453784725</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I128" s="5">
         <v>46328</v>
@@ -9060,13 +9063,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9076,7 +9079,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B129" s="8">
         <v>46181.60958841435</v>
@@ -9092,10 +9095,10 @@
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I129" s="8">
         <v>46328</v>
@@ -9113,7 +9116,7 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O129" s="9" t="s">
         <v>60</v>
@@ -9129,7 +9132,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B130" s="5">
         <v>46181.616839849536</v>
@@ -9145,10 +9148,10 @@
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I130" s="5">
         <v>46328</v>
@@ -9166,7 +9169,7 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O130" s="6" t="s">
         <v>60</v>
@@ -9182,7 +9185,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B131" s="8">
         <v>46181.61689748843</v>
@@ -9192,16 +9195,16 @@
         <v>46182.8294564699</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I131" s="8">
         <v>46328</v>
@@ -9219,13 +9222,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
@@ -9235,7 +9238,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B132" s="5">
         <v>46181.616942569446</v>
@@ -9245,16 +9248,16 @@
         <v>46182.82945721065</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I132" s="5">
         <v>46328</v>
@@ -9272,13 +9275,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9288,7 +9291,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B133" s="8">
         <v>46181.6169815162</v>
@@ -9298,16 +9301,16 @@
         <v>46182.82945796296</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I133" s="8">
         <v>46328</v>
@@ -9325,13 +9328,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9341,7 +9344,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B134" s="5">
         <v>46181.609592673616</v>
@@ -9351,16 +9354,16 @@
         <v>46182.642407384265</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I134" s="5">
         <v>46329</v>
@@ -9378,13 +9381,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q134" s="5">
         <v>46329</v>
@@ -9404,7 +9407,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B135" s="8">
         <v>46181.60960517361</v>
@@ -9414,16 +9417,16 @@
         <v>46182.8294527199</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I135" s="8">
         <v>46329</v>
@@ -9441,13 +9444,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q135" s="9"/>
       <c r="R135" s="9"/>
@@ -9457,7 +9460,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B136" s="5">
         <v>46181.609610011576</v>
@@ -9467,16 +9470,16 @@
         <v>46182.829451909725</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I136" s="5">
         <v>46329</v>
@@ -9494,10 +9497,10 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P136" s="6" t="s">
         <v>26</v>
@@ -9510,7 +9513,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B137" s="8">
         <v>46181.609613796296</v>
@@ -9526,10 +9529,10 @@
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I137" s="8">
         <v>46329</v>
@@ -9547,7 +9550,7 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O137" s="9" t="s">
         <v>60</v>
@@ -9563,7 +9566,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B138" s="5">
         <v>46181.61712142361</v>
@@ -9579,10 +9582,10 @@
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I138" s="5">
         <v>46329</v>
@@ -9600,7 +9603,7 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O138" s="6" t="s">
         <v>60</v>
@@ -9616,7 +9619,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B139" s="8">
         <v>46181.61716094907</v>
@@ -9626,16 +9629,16 @@
         <v>46182.82945207176</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I139" s="8">
         <v>46329</v>
@@ -9653,10 +9656,10 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P139" s="9" t="s">
         <v>26</v>
@@ -9669,7 +9672,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B140" s="5">
         <v>46181.61719633102</v>
@@ -9679,16 +9682,16 @@
         <v>46182.829452025464</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I140" s="5">
         <v>46329</v>
@@ -9706,10 +9709,10 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P140" s="6" t="s">
         <v>26</v>
@@ -9722,7 +9725,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B141" s="8">
         <v>46181.617235451384</v>
@@ -9732,16 +9735,16 @@
         <v>46182.829452418984</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I141" s="8">
         <v>46329</v>
@@ -9759,10 +9762,10 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P141" s="9" t="s">
         <v>26</v>
@@ -9775,7 +9778,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B142" s="5">
         <v>46181.60961741898</v>
@@ -9785,7 +9788,7 @@
         <v>46182.63449439815</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>25</v>
@@ -9809,7 +9812,7 @@
         <v>26</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P142" s="6" t="s">
         <v>26</v>
@@ -9822,7 +9825,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B143" s="8">
         <v>46181.60962174769</v>
@@ -9832,16 +9835,16 @@
         <v>46182.64244836806</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="I143" s="8">
         <v>46330</v>
@@ -9859,13 +9862,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q143" s="8">
         <v>46330</v>
@@ -9885,7 +9888,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B144" s="5">
         <v>46181.60962780092</v>
@@ -9895,7 +9898,7 @@
         <v>46191.67892958333</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -9922,13 +9925,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q144" s="5">
         <v>46330</v>
@@ -9948,7 +9951,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B145" s="8">
         <v>46181.60963489584</v>
@@ -9958,7 +9961,7 @@
         <v>46182.63449431713</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>25</v>
@@ -9982,7 +9985,7 @@
         <v>26</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P145" s="9" t="s">
         <v>26</v>
@@ -10001,7 +10004,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B146" s="5">
         <v>46181.609640208335</v>
@@ -10011,7 +10014,7 @@
         <v>46182.64254377315</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10038,13 +10041,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q146" s="5">
         <v>46330</v>
@@ -10064,7 +10067,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B147" s="8">
         <v>46181.609646365745</v>
@@ -10074,7 +10077,7 @@
         <v>46182.64254079861</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
@@ -10101,13 +10104,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q147" s="8">
         <v>46339</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1720" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1686" uniqueCount="379">
   <si>
     <t>50001559 - FERROVIAL</t>
   </si>
@@ -349,9 +349,6 @@
     <t>propuesta nucleo rodete  ot 4347</t>
   </si>
   <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
     <t>Propuesta compras:,Reserva rodete ot 4347</t>
   </si>
   <si>
@@ -359,12 +356,6 @@
   </si>
   <si>
     <t>propuesta Corte Laser ot 4347</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
   </si>
   <si>
     <t>check planos</t>
@@ -2877,11 +2868,9 @@
         <v>26</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>90</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H21" s="9"/>
       <c r="I21" s="8">
         <v>46174</v>
       </c>
@@ -2904,7 +2893,7 @@
         <v>73</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q21" s="8">
         <v>46174</v>
@@ -2924,7 +2913,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B22" s="5">
         <v>46181.60888054398</v>
@@ -2936,17 +2925,15 @@
         <v>46206.551626817134</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>95</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H22" s="6"/>
       <c r="I22" s="5">
         <v>46248</v>
       </c>
@@ -2966,10 +2953,10 @@
         <v>80</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="Q22" s="5">
         <v>46248</v>
@@ -2989,7 +2976,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B23" s="8">
         <v>46181.60888559028</v>
@@ -3001,17 +2988,15 @@
         <v>46206.5519203588</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>95</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H23" s="9"/>
       <c r="I23" s="8">
         <v>46248</v>
       </c>
@@ -3031,10 +3016,10 @@
         <v>80</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q23" s="8">
         <v>46248</v>
@@ -3054,7 +3039,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B24" s="5">
         <v>46181.60888961806</v>
@@ -3066,17 +3051,15 @@
         <v>46206.5521100926</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>95</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H24" s="6"/>
       <c r="I24" s="5">
         <v>46248</v>
       </c>
@@ -3096,10 +3079,10 @@
         <v>80</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="Q24" s="5">
         <v>46248</v>
@@ -3119,7 +3102,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B25" s="8">
         <v>46181.6088934375</v>
@@ -3131,17 +3114,15 @@
         <v>46206.552334583335</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>95</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H25" s="9"/>
       <c r="I25" s="8">
         <v>46248</v>
       </c>
@@ -3161,10 +3142,10 @@
         <v>80</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="Q25" s="8">
         <v>46248</v>
@@ -3184,7 +3165,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B26" s="5">
         <v>46181.608897638886</v>
@@ -3196,7 +3177,7 @@
         <v>46190.67787061342</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
@@ -3229,7 +3210,7 @@
         <v>48</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="Q26" s="5">
         <v>46168</v>
@@ -3249,7 +3230,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B27" s="8">
         <v>46190.88204489583</v>
@@ -3261,7 +3242,7 @@
         <v>46197.424089050925</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>25</v>
@@ -3302,7 +3283,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B28" s="5">
         <v>46190.88321909722</v>
@@ -3314,17 +3295,15 @@
         <v>46197.42355928241</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>90</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H28" s="6"/>
       <c r="I28" s="5">
         <v>46169</v>
       </c>
@@ -3341,7 +3320,7 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>83</v>
@@ -3367,7 +3346,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B29" s="8">
         <v>46190.88327185185</v>
@@ -3379,17 +3358,15 @@
         <v>46197.423981597225</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>90</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H29" s="9"/>
       <c r="I29" s="8">
         <v>46176</v>
       </c>
@@ -3406,7 +3383,7 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="O29" s="9" t="s">
         <v>86</v>
@@ -3432,7 +3409,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B30" s="5">
         <v>46190.88332659722</v>
@@ -3444,17 +3421,15 @@
         <v>46197.42407648148</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>90</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H30" s="6"/>
       <c r="I30" s="5">
         <v>46176</v>
       </c>
@@ -3471,7 +3446,7 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>89</v>
@@ -3497,7 +3472,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B31" s="8">
         <v>46181.608652256946</v>
@@ -3507,7 +3482,7 @@
         <v>46205.61719612269</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>25</v>
@@ -3531,7 +3506,7 @@
         <v>26</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="P31" s="9" t="s">
         <v>26</v>
@@ -3541,12 +3516,12 @@
       <c r="S31" s="9"/>
       <c r="T31" s="9"/>
       <c r="U31" s="12" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B32" s="5">
         <v>46181.60900793981</v>
@@ -3558,16 +3533,16 @@
         <v>46218.18782881944</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I32" s="5">
         <v>46170</v>
@@ -3585,10 +3560,10 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3600,7 +3575,7 @@
         <v>46225</v>
       </c>
       <c r="S32" s="12" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="T32" s="6">
         <v>1</v>
@@ -3611,7 +3586,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B33" s="8">
         <v>46181.60901165509</v>
@@ -3623,16 +3598,16 @@
         <v>46195.68592747685</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I33" s="8">
         <v>46170</v>
@@ -3650,13 +3625,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3666,7 +3641,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B34" s="5">
         <v>46181.60901612269</v>
@@ -3678,16 +3653,16 @@
         <v>46217.69795753472</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I34" s="5">
         <v>46177</v>
@@ -3705,13 +3680,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3721,7 +3696,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B35" s="8">
         <v>46181.60902011574</v>
@@ -3733,16 +3708,16 @@
         <v>46205.61719211805</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="I35" s="8">
         <v>46252</v>
@@ -3760,13 +3735,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="Q35" s="8">
         <v>46252</v>
@@ -3786,7 +3761,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B36" s="5">
         <v>46181.60902488426</v>
@@ -3798,16 +3773,16 @@
         <v>46199.57115532407</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="I36" s="5">
         <v>46252</v>
@@ -3825,13 +3800,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3847,7 +3822,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B37" s="8">
         <v>46181.609029803236</v>
@@ -3859,16 +3834,16 @@
         <v>46205.61257221065</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="I37" s="8">
         <v>46254</v>
@@ -3886,13 +3861,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3908,7 +3883,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B38" s="5">
         <v>46181.60903511574</v>
@@ -3920,16 +3895,16 @@
         <v>46199.572352546296</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="I38" s="5">
         <v>46252</v>
@@ -3947,10 +3922,10 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3973,7 +3948,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B39" s="8">
         <v>46181.60903861111</v>
@@ -3985,16 +3960,16 @@
         <v>46199.57256810185</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="I39" s="8">
         <v>46252</v>
@@ -4012,13 +3987,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="O39" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="P39" s="9" t="s">
         <v>144</v>
-      </c>
-      <c r="O39" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="P39" s="9" t="s">
-        <v>147</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -4028,7 +4003,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B40" s="5">
         <v>46181.609042951386</v>
@@ -4040,16 +4015,16 @@
         <v>46199.57232634259</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="I40" s="5">
         <v>46254</v>
@@ -4067,13 +4042,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4083,7 +4058,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B41" s="8">
         <v>46181.609047164355</v>
@@ -4095,16 +4070,16 @@
         <v>46212.82441381944</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I41" s="8">
         <v>46252</v>
@@ -4122,10 +4097,10 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="P41" s="9" t="s">
         <v>26</v>
@@ -4148,7 +4123,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B42" s="5">
         <v>46181.60905075232</v>
@@ -4160,16 +4135,16 @@
         <v>46204.67396857639</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I42" s="5">
         <v>46252</v>
@@ -4187,13 +4162,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4203,7 +4178,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B43" s="8">
         <v>46181.60905546296</v>
@@ -4215,16 +4190,16 @@
         <v>46204.67391837963</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I43" s="8">
         <v>46261</v>
@@ -4242,13 +4217,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -4258,7 +4233,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B44" s="5">
         <v>46181.60906018519</v>
@@ -4268,16 +4243,16 @@
         <v>46204.67384744213</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I44" s="5">
         <v>46290</v>
@@ -4295,10 +4270,10 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>26</v>
@@ -4311,7 +4286,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B45" s="8">
         <v>46181.609063310185</v>
@@ -4323,16 +4298,16 @@
         <v>46205.61290721065</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="I45" s="8">
         <v>46252</v>
@@ -4350,10 +4325,10 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>26</v>
@@ -4376,7 +4351,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B46" s="5">
         <v>46181.60906703703</v>
@@ -4388,16 +4363,16 @@
         <v>46205.61283694445</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="I46" s="5">
         <v>46252</v>
@@ -4415,13 +4390,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="O46" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="P46" s="6" t="s">
         <v>166</v>
-      </c>
-      <c r="O46" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="P46" s="6" t="s">
-        <v>169</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4431,7 +4406,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B47" s="8">
         <v>46181.60907681713</v>
@@ -4443,16 +4418,16 @@
         <v>46205.612879328706</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="I47" s="8">
         <v>46254</v>
@@ -4470,13 +4445,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
@@ -4486,7 +4461,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B48" s="5">
         <v>46181.6090815625</v>
@@ -4498,7 +4473,7 @@
         <v>46210.525643402776</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>25</v>
@@ -4522,7 +4497,7 @@
         <v>26</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>26</v>
@@ -4539,7 +4514,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B49" s="8">
         <v>46181.60908480324</v>
@@ -4551,16 +4526,16 @@
         <v>46197.7158150926</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I49" s="8">
         <v>46174</v>
@@ -4578,13 +4553,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="Q49" s="8">
         <v>46174</v>
@@ -4593,7 +4568,7 @@
         <v>46191</v>
       </c>
       <c r="S49" s="11" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="T49" s="9">
         <v>1</v>
@@ -4604,7 +4579,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B50" s="5">
         <v>46181.60908915509</v>
@@ -4616,16 +4591,16 @@
         <v>46190.70821390046</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I50" s="5">
         <v>46174</v>
@@ -4643,13 +4618,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>77</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4659,7 +4634,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B51" s="8">
         <v>46181.60909384259</v>
@@ -4671,16 +4646,16 @@
         <v>46190.7082228125</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I51" s="8">
         <v>46174</v>
@@ -4698,13 +4673,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>77</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4714,7 +4689,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B52" s="5">
         <v>46181.61221741898</v>
@@ -4726,16 +4701,16 @@
         <v>46190.708227337964</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I52" s="5">
         <v>46174</v>
@@ -4753,13 +4728,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>77</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4769,7 +4744,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B53" s="8">
         <v>46181.612357199076</v>
@@ -4781,16 +4756,16 @@
         <v>46190.708233321755</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I53" s="8">
         <v>46174</v>
@@ -4808,13 +4783,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>77</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -4824,7 +4799,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B54" s="5">
         <v>46181.609098182875</v>
@@ -4836,16 +4811,16 @@
         <v>46197.71584820602</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I54" s="5">
         <v>46227</v>
@@ -4863,13 +4838,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="Q54" s="5">
         <v>46227</v>
@@ -4889,7 +4864,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B55" s="8">
         <v>46181.60910252314</v>
@@ -4901,16 +4876,16 @@
         <v>46191.54270819444</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I55" s="8">
         <v>46227</v>
@@ -4928,13 +4903,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4944,7 +4919,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B56" s="5">
         <v>46181.609107951386</v>
@@ -4956,16 +4931,16 @@
         <v>46191.54271703704</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I56" s="5">
         <v>46227</v>
@@ -4983,13 +4958,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4999,7 +4974,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B57" s="8">
         <v>46181.61393570602</v>
@@ -5011,16 +4986,16 @@
         <v>46190.70842170139</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I57" s="8">
         <v>46227</v>
@@ -5038,13 +5013,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5054,7 +5029,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B58" s="5">
         <v>46181.61396929398</v>
@@ -5066,16 +5041,16 @@
         <v>46190.708426550926</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I58" s="5">
         <v>46227</v>
@@ -5093,13 +5068,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5109,7 +5084,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B59" s="8">
         <v>46181.60911329861</v>
@@ -5121,16 +5096,16 @@
         <v>46191.54539826389</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I59" s="8">
         <v>46247</v>
@@ -5148,13 +5123,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="Q59" s="8">
         <v>46247</v>
@@ -5174,7 +5149,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B60" s="5">
         <v>46181.60912350695</v>
@@ -5186,16 +5161,16 @@
         <v>46191.54536050926</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I60" s="6"/>
       <c r="J60" s="5">
@@ -5211,13 +5186,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5227,7 +5202,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B61" s="8">
         <v>46181.60912782408</v>
@@ -5239,16 +5214,16 @@
         <v>46191.54537386574</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I61" s="9"/>
       <c r="J61" s="8">
@@ -5264,13 +5239,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5280,7 +5255,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B62" s="5">
         <v>46181.614119606485</v>
@@ -5292,16 +5267,16 @@
         <v>46190.721725358795</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I62" s="6"/>
       <c r="J62" s="5">
@@ -5317,10 +5292,10 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5333,7 +5308,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B63" s="8">
         <v>46181.61419627315</v>
@@ -5345,16 +5320,16 @@
         <v>46190.7217299537</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="I63" s="9"/>
       <c r="J63" s="8">
@@ -5370,10 +5345,10 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5386,7 +5361,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B64" s="5">
         <v>46181.60913207176</v>
@@ -5396,16 +5371,16 @@
         <v>46212.622826203704</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="I64" s="5">
         <v>46322</v>
@@ -5423,10 +5398,10 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>26</v>
@@ -5449,7 +5424,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B65" s="8">
         <v>46181.609135833336</v>
@@ -5459,16 +5434,16 @@
         <v>46182.63311847222</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="I65" s="8">
         <v>46322</v>
@@ -5486,13 +5461,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5502,7 +5477,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B66" s="5">
         <v>46181.614311909725</v>
@@ -5512,16 +5487,16 @@
         <v>46182.63311923611</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="I66" s="5">
         <v>46322</v>
@@ -5539,13 +5514,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5555,7 +5530,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B67" s="8">
         <v>46181.60918671296</v>
@@ -5567,7 +5542,7 @@
         <v>46216.64129429398</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>25</v>
@@ -5591,7 +5566,7 @@
         <v>26</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>26</v>
@@ -5608,7 +5583,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B68" s="5">
         <v>46181.609196087964</v>
@@ -5620,16 +5595,16 @@
         <v>46213.56938424769</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I68" s="5">
         <v>46252</v>
@@ -5647,13 +5622,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Q68" s="5">
         <v>46252</v>
@@ -5673,7 +5648,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B69" s="8">
         <v>46181.609201921296</v>
@@ -5685,16 +5660,16 @@
         <v>46216.71548459491</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I69" s="8">
         <v>46254</v>
@@ -5712,13 +5687,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="Q69" s="8">
         <v>46254</v>
@@ -5738,7 +5713,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B70" s="5">
         <v>46181.60920746528</v>
@@ -5750,16 +5725,16 @@
         <v>46213.569400231485</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I70" s="5">
         <v>46252</v>
@@ -5777,13 +5752,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="Q70" s="5">
         <v>46252</v>
@@ -5803,7 +5778,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B71" s="8">
         <v>46181.609212870375</v>
@@ -5815,16 +5790,16 @@
         <v>46216.715484733795</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I71" s="8">
         <v>46254</v>
@@ -5842,13 +5817,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="Q71" s="8">
         <v>46254</v>
@@ -5868,7 +5843,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B72" s="5">
         <v>46181.60921715278</v>
@@ -5880,16 +5855,16 @@
         <v>46213.569419479165</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I72" s="5">
         <v>46252</v>
@@ -5907,13 +5882,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="Q72" s="5">
         <v>46252</v>
@@ -5933,7 +5908,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B73" s="8">
         <v>46181.60922180556</v>
@@ -5945,16 +5920,16 @@
         <v>46216.71548493055</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I73" s="8">
         <v>46254</v>
@@ -5972,13 +5947,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="Q73" s="8">
         <v>46254</v>
@@ -5998,7 +5973,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B74" s="5">
         <v>46181.60922590278</v>
@@ -6008,7 +5983,7 @@
         <v>46181.782424143516</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>25</v>
@@ -6032,7 +6007,7 @@
         <v>26</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>26</v>
@@ -6045,7 +6020,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B75" s="8">
         <v>46181.60922940972</v>
@@ -6055,16 +6030,16 @@
         <v>46216.71555703704</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I75" s="8">
         <v>46258</v>
@@ -6082,13 +6057,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="Q75" s="8">
         <v>46258</v>
@@ -6108,7 +6083,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B76" s="5">
         <v>46181.60923553241</v>
@@ -6118,16 +6093,16 @@
         <v>46216.641273009256</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I76" s="5">
         <v>46258</v>
@@ -6145,13 +6120,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6161,7 +6136,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B77" s="8">
         <v>46181.609241805556</v>
@@ -6171,16 +6146,16 @@
         <v>46216.64127412037</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I77" s="8">
         <v>46258</v>
@@ -6198,13 +6173,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
@@ -6214,7 +6189,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B78" s="5">
         <v>46181.609247002314</v>
@@ -6224,16 +6199,16 @@
         <v>46212.62258834491</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I78" s="5">
         <v>46267</v>
@@ -6251,13 +6226,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="Q78" s="5">
         <v>46267</v>
@@ -6277,7 +6252,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B79" s="8">
         <v>46181.60925648148</v>
@@ -6287,16 +6262,16 @@
         <v>46191.54540523148</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I79" s="8">
         <v>46267</v>
@@ -6314,13 +6289,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="O79" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="P79" s="9" t="s">
         <v>252</v>
-      </c>
-      <c r="O79" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="P79" s="9" t="s">
-        <v>255</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6330,7 +6305,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B80" s="5">
         <v>46181.609262199076</v>
@@ -6340,16 +6315,16 @@
         <v>46191.54540574074</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I80" s="5">
         <v>46267</v>
@@ -6367,13 +6342,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="O80" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="P80" s="6" t="s">
         <v>252</v>
-      </c>
-      <c r="O80" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="P80" s="6" t="s">
-        <v>255</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6383,7 +6358,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B81" s="8">
         <v>46181.60926783565</v>
@@ -6393,16 +6368,16 @@
         <v>46212.62263724537</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I81" s="8">
         <v>46289</v>
@@ -6420,13 +6395,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="Q81" s="8">
         <v>46289</v>
@@ -6446,7 +6421,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B82" s="5">
         <v>46181.60927226851</v>
@@ -6456,16 +6431,16 @@
         <v>46191.545403842596</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I82" s="5">
         <v>46289</v>
@@ -6483,13 +6458,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6499,7 +6474,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B83" s="8">
         <v>46181.60927799769</v>
@@ -6509,16 +6484,16 @@
         <v>46191.545404212964</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I83" s="8">
         <v>46289</v>
@@ -6536,13 +6511,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6552,7 +6527,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B84" s="5">
         <v>46181.60928361111</v>
@@ -6562,7 +6537,7 @@
         <v>46213.56805377315</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>25</v>
@@ -6586,7 +6561,7 @@
         <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6596,12 +6571,12 @@
       <c r="S84" s="6"/>
       <c r="T84" s="6"/>
       <c r="U84" s="12" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B85" s="8">
         <v>46181.609286990744</v>
@@ -6613,16 +6588,16 @@
         <v>46213.56773226852</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I85" s="8">
         <v>46182</v>
@@ -6640,13 +6615,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="O85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="Q85" s="8">
         <v>46182</v>
@@ -6655,7 +6630,7 @@
         <v>46183</v>
       </c>
       <c r="S85" s="11" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="T85" s="9">
         <v>1</v>
@@ -6666,7 +6641,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B86" s="5">
         <v>46181.609292974535</v>
@@ -6678,16 +6653,16 @@
         <v>46213.56774653935</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I86" s="5">
         <v>46290</v>
@@ -6705,13 +6680,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="Q86" s="5">
         <v>46290</v>
@@ -6731,7 +6706,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B87" s="8">
         <v>46181.60929881944</v>
@@ -6743,16 +6718,16 @@
         <v>46213.56805165509</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I87" s="8">
         <v>46226</v>
@@ -6770,13 +6745,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="O87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="Q87" s="8">
         <v>46226</v>
@@ -6796,7 +6771,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B88" s="5">
         <v>46181.60930480324</v>
@@ -6806,16 +6781,16 @@
         <v>46212.623013958335</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I88" s="5">
         <v>46293</v>
@@ -6833,13 +6808,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="Q88" s="5">
         <v>46293</v>
@@ -6854,12 +6829,12 @@
         <v>0</v>
       </c>
       <c r="U88" s="12" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B89" s="8">
         <v>46181.60935271991</v>
@@ -6875,10 +6850,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="I89" s="8">
         <v>46226</v>
@@ -6896,10 +6871,10 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="P89" s="9" t="s">
         <v>56</v>
@@ -6917,12 +6892,12 @@
         <v>0</v>
       </c>
       <c r="U89" s="12" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B90" s="5">
         <v>46181.60936674768</v>
@@ -6932,7 +6907,7 @@
         <v>46213.50490068287</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -6956,7 +6931,7 @@
         <v>26</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -6969,7 +6944,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B91" s="8">
         <v>46181.609371666666</v>
@@ -6979,17 +6954,15 @@
         <v>46182.64123547454</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="H91" s="9" t="s">
-        <v>90</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H91" s="9"/>
       <c r="I91" s="8">
         <v>46290</v>
       </c>
@@ -7006,13 +6979,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="Q91" s="8">
         <v>46290</v>
@@ -7032,7 +7005,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B92" s="5">
         <v>46181.609378587964</v>
@@ -7042,17 +7015,15 @@
         <v>46182.64119599537</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>90</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H92" s="6"/>
       <c r="I92" s="5">
         <v>46290</v>
       </c>
@@ -7069,13 +7040,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="O92" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="O92" s="6" t="s">
-        <v>283</v>
-      </c>
       <c r="P92" s="6" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7085,7 +7056,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B93" s="8">
         <v>46181.61514019676</v>
@@ -7095,17 +7066,15 @@
         <v>46182.64119222222</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="H93" s="9" t="s">
-        <v>90</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H93" s="9"/>
       <c r="I93" s="8">
         <v>46290</v>
       </c>
@@ -7122,13 +7091,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7138,7 +7107,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B94" s="5">
         <v>46181.609386111115</v>
@@ -7150,17 +7119,15 @@
         <v>46212.62246368056</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>90</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H94" s="6"/>
       <c r="I94" s="5">
         <v>46311</v>
       </c>
@@ -7177,13 +7144,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="Q94" s="5">
         <v>46311</v>
@@ -7203,7 +7170,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B95" s="8">
         <v>46181.60939194444</v>
@@ -7215,17 +7182,15 @@
         <v>46213.56773570602</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="H95" s="9" t="s">
-        <v>90</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H95" s="9"/>
       <c r="I95" s="8">
         <v>46311</v>
       </c>
@@ -7242,13 +7207,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="O95" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="P95" s="9" t="s">
         <v>287</v>
-      </c>
-      <c r="O95" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="P95" s="9" t="s">
-        <v>290</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7258,7 +7223,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B96" s="5">
         <v>46181.61518315972</v>
@@ -7270,17 +7235,15 @@
         <v>46213.567735150464</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>90</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H96" s="6"/>
       <c r="I96" s="5">
         <v>46311</v>
       </c>
@@ -7297,10 +7260,10 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>26</v>
@@ -7313,7 +7276,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B97" s="8">
         <v>46181.60939866898</v>
@@ -7325,17 +7288,15 @@
         <v>46213.50490375</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="H97" s="9" t="s">
-        <v>90</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H97" s="9"/>
       <c r="I97" s="8">
         <v>46315</v>
       </c>
@@ -7352,13 +7313,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="Q97" s="8">
         <v>46315</v>
@@ -7378,7 +7339,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B98" s="5">
         <v>46181.60940505787</v>
@@ -7390,17 +7351,15 @@
         <v>46213.56772277778</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>90</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H98" s="6"/>
       <c r="I98" s="5">
         <v>46315</v>
       </c>
@@ -7417,13 +7376,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="O98" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="P98" s="6" t="s">
         <v>294</v>
-      </c>
-      <c r="O98" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="P98" s="6" t="s">
-        <v>297</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7433,7 +7392,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B99" s="8">
         <v>46181.61523613426</v>
@@ -7445,17 +7404,15 @@
         <v>46213.56772202546</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="H99" s="9" t="s">
-        <v>90</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H99" s="9"/>
       <c r="I99" s="8">
         <v>46315</v>
       </c>
@@ -7472,10 +7429,10 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="P99" s="9" t="s">
         <v>26</v>
@@ -7488,7 +7445,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B100" s="5">
         <v>46181.60941365741</v>
@@ -7498,17 +7455,15 @@
         <v>46212.62250564815</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>90</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H100" s="6"/>
       <c r="I100" s="5">
         <v>46317</v>
       </c>
@@ -7525,13 +7480,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="Q100" s="5">
         <v>46317</v>
@@ -7551,7 +7506,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B101" s="8">
         <v>46181.60941929398</v>
@@ -7561,17 +7516,15 @@
         <v>46213.56804261574</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="H101" s="9" t="s">
-        <v>90</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H101" s="9"/>
       <c r="I101" s="8">
         <v>46317</v>
       </c>
@@ -7588,13 +7541,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="O101" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="P101" s="9" t="s">
         <v>301</v>
-      </c>
-      <c r="O101" s="9" t="s">
-        <v>303</v>
-      </c>
-      <c r="P101" s="9" t="s">
-        <v>304</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7604,7 +7557,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B102" s="5">
         <v>46181.61528053241</v>
@@ -7614,17 +7567,15 @@
         <v>46213.568041192135</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>90</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H102" s="6"/>
       <c r="I102" s="5">
         <v>46317</v>
       </c>
@@ -7641,10 +7592,10 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>26</v>
@@ -7657,7 +7608,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B103" s="8">
         <v>46181.60942706019</v>
@@ -7667,17 +7618,15 @@
         <v>46212.62252259259</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="H103" s="9" t="s">
-        <v>90</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H103" s="9"/>
       <c r="I103" s="8">
         <v>46321</v>
       </c>
@@ -7694,13 +7643,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="Q103" s="8">
         <v>46321</v>
@@ -7720,7 +7669,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B104" s="5">
         <v>46181.60943415509</v>
@@ -7730,17 +7679,15 @@
         <v>46182.641623125004</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>90</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H104" s="6"/>
       <c r="I104" s="5">
         <v>46321</v>
       </c>
@@ -7757,13 +7704,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7773,7 +7720,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B105" s="8">
         <v>46181.61532783565</v>
@@ -7783,17 +7730,15 @@
         <v>46182.64161924769</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="H105" s="9" t="s">
-        <v>90</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H105" s="9"/>
       <c r="I105" s="8">
         <v>46321</v>
       </c>
@@ -7810,13 +7755,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -7826,7 +7771,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B106" s="5">
         <v>46181.60944410879</v>
@@ -7836,17 +7781,15 @@
         <v>46212.622555497685</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>90</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H106" s="6"/>
       <c r="I106" s="5">
         <v>46323</v>
       </c>
@@ -7863,13 +7806,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="Q106" s="5">
         <v>46323</v>
@@ -7889,7 +7832,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B107" s="8">
         <v>46181.60944996528</v>
@@ -7899,17 +7842,15 @@
         <v>46182.64173178241</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="H107" s="9" t="s">
-        <v>90</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H107" s="9"/>
       <c r="I107" s="8">
         <v>46323</v>
       </c>
@@ -7926,13 +7867,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="O107" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="P107" s="9" t="s">
         <v>313</v>
-      </c>
-      <c r="O107" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="P107" s="9" t="s">
-        <v>316</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -7942,7 +7883,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B108" s="5">
         <v>46181.61537143518</v>
@@ -7952,17 +7893,15 @@
         <v>46182.64172883102</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>90</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H108" s="6"/>
       <c r="I108" s="5">
         <v>46323</v>
       </c>
@@ -7979,10 +7918,10 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>26</v>
@@ -7995,7 +7934,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B109" s="8">
         <v>46181.60945642361</v>
@@ -8005,7 +7944,7 @@
         <v>46182.634494212965</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>25</v>
@@ -8029,7 +7968,7 @@
         <v>26</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="P109" s="9" t="s">
         <v>26</v>
@@ -8042,7 +7981,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B110" s="5">
         <v>46181.60946096065</v>
@@ -8052,16 +7991,16 @@
         <v>46182.64186350694</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="I110" s="5">
         <v>46324</v>
@@ -8079,13 +8018,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="Q110" s="5">
         <v>46324</v>
@@ -8105,7 +8044,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B111" s="8">
         <v>46181.60946868056</v>
@@ -8115,16 +8054,16 @@
         <v>46182.641845254635</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="I111" s="8">
         <v>46324</v>
@@ -8142,13 +8081,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="Q111" s="9"/>
       <c r="R111" s="9"/>
@@ -8158,7 +8097,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B112" s="5">
         <v>46181.609475034726</v>
@@ -8168,16 +8107,16 @@
         <v>46182.64184081019</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="I112" s="5">
         <v>46324</v>
@@ -8195,13 +8134,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8211,7 +8150,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B113" s="8">
         <v>46181.60947921296</v>
@@ -8227,10 +8166,10 @@
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="I113" s="8">
         <v>46324</v>
@@ -8248,7 +8187,7 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="O113" s="9" t="s">
         <v>60</v>
@@ -8264,7 +8203,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B114" s="5">
         <v>46181.61605960648</v>
@@ -8280,10 +8219,10 @@
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="I114" s="5">
         <v>46324</v>
@@ -8301,7 +8240,7 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>60</v>
@@ -8317,26 +8256,26 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B115" s="8">
         <v>46181.61617203704</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46216.71559670139</v>
+        <v>46218.812014641204</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="I115" s="8">
         <v>46324</v>
@@ -8354,13 +8293,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="O115" s="9" t="s">
         <v>26</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="Q115" s="9"/>
       <c r="R115" s="9"/>
@@ -8370,7 +8309,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B116" s="5">
         <v>46181.61620771991</v>
@@ -8380,16 +8319,16 @@
         <v>46216.715609837964</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="I116" s="5">
         <v>46324</v>
@@ -8407,13 +8346,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="O116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8423,26 +8362,26 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B117" s="8">
         <v>46181.616245833335</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46216.715626087964</v>
+        <v>46218.812044606486</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="I117" s="8">
         <v>46324</v>
@@ -8460,13 +8399,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="O117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8476,7 +8415,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B118" s="5">
         <v>46181.60948424769</v>
@@ -8486,17 +8425,15 @@
         <v>46182.64199267361</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="H118" s="6" t="s">
-        <v>90</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H118" s="6"/>
       <c r="I118" s="5">
         <v>46325</v>
       </c>
@@ -8513,13 +8450,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="Q118" s="5">
         <v>46325</v>
@@ -8539,7 +8476,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B119" s="8">
         <v>46181.60948969907</v>
@@ -8549,17 +8486,15 @@
         <v>46182.641973854166</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="H119" s="9" t="s">
-        <v>90</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H119" s="9"/>
       <c r="I119" s="8">
         <v>46325</v>
       </c>
@@ -8576,13 +8511,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8592,7 +8527,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B120" s="5">
         <v>46181.60949538194</v>
@@ -8602,17 +8537,15 @@
         <v>46182.64197085648</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="H120" s="6" t="s">
-        <v>90</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H120" s="6"/>
       <c r="I120" s="5">
         <v>46325</v>
       </c>
@@ -8629,13 +8562,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8645,7 +8578,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B121" s="8">
         <v>46181.609560185185</v>
@@ -8661,11 +8594,9 @@
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="H121" s="9" t="s">
-        <v>90</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H121" s="9"/>
       <c r="I121" s="8">
         <v>46325</v>
       </c>
@@ -8682,7 +8613,7 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="O121" s="9" t="s">
         <v>60</v>
@@ -8698,7 +8629,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B122" s="5">
         <v>46181.61659114584</v>
@@ -8714,11 +8645,9 @@
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="H122" s="6" t="s">
-        <v>90</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H122" s="6"/>
       <c r="I122" s="5">
         <v>46325</v>
       </c>
@@ -8735,7 +8664,7 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>60</v>
@@ -8751,7 +8680,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B123" s="8">
         <v>46181.61662431713</v>
@@ -8761,17 +8690,15 @@
         <v>46182.64196105324</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="H123" s="9" t="s">
-        <v>90</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H123" s="9"/>
       <c r="I123" s="8">
         <v>46325</v>
       </c>
@@ -8788,13 +8715,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="Q123" s="9"/>
       <c r="R123" s="9"/>
@@ -8804,7 +8731,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B124" s="5">
         <v>46181.61666238426</v>
@@ -8814,17 +8741,15 @@
         <v>46182.64195453704</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="H124" s="6" t="s">
-        <v>90</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H124" s="6"/>
       <c r="I124" s="5">
         <v>46325</v>
       </c>
@@ -8841,13 +8766,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8857,7 +8782,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B125" s="8">
         <v>46181.61670006944</v>
@@ -8867,17 +8792,15 @@
         <v>46182.64195372685</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="H125" s="9" t="s">
-        <v>90</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H125" s="9"/>
       <c r="I125" s="8">
         <v>46325</v>
       </c>
@@ -8894,13 +8817,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -8910,7 +8833,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B126" s="5">
         <v>46181.60956560185</v>
@@ -8920,16 +8843,16 @@
         <v>46182.82952324074</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I126" s="5">
         <v>46328</v>
@@ -8947,13 +8870,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="Q126" s="5">
         <v>46328</v>
@@ -8973,7 +8896,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B127" s="8">
         <v>46181.60957188657</v>
@@ -8983,16 +8906,16 @@
         <v>46182.82945300926</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H127" s="9" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I127" s="8">
         <v>46328</v>
@@ -9010,13 +8933,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -9026,7 +8949,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B128" s="5">
         <v>46181.609583576384</v>
@@ -9036,16 +8959,16 @@
         <v>46182.829453784725</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I128" s="5">
         <v>46328</v>
@@ -9063,13 +8986,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9079,7 +9002,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B129" s="8">
         <v>46181.60958841435</v>
@@ -9095,10 +9018,10 @@
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I129" s="8">
         <v>46328</v>
@@ -9116,7 +9039,7 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="O129" s="9" t="s">
         <v>60</v>
@@ -9132,7 +9055,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B130" s="5">
         <v>46181.616839849536</v>
@@ -9148,10 +9071,10 @@
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I130" s="5">
         <v>46328</v>
@@ -9169,7 +9092,7 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="O130" s="6" t="s">
         <v>60</v>
@@ -9185,7 +9108,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B131" s="8">
         <v>46181.61689748843</v>
@@ -9195,16 +9118,16 @@
         <v>46182.8294564699</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I131" s="8">
         <v>46328</v>
@@ -9222,13 +9145,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
@@ -9238,7 +9161,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B132" s="5">
         <v>46181.616942569446</v>
@@ -9248,16 +9171,16 @@
         <v>46182.82945721065</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I132" s="5">
         <v>46328</v>
@@ -9275,13 +9198,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9291,7 +9214,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B133" s="8">
         <v>46181.6169815162</v>
@@ -9301,16 +9224,16 @@
         <v>46182.82945796296</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I133" s="8">
         <v>46328</v>
@@ -9328,13 +9251,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9344,7 +9267,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B134" s="5">
         <v>46181.609592673616</v>
@@ -9354,16 +9277,16 @@
         <v>46182.642407384265</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I134" s="5">
         <v>46329</v>
@@ -9381,13 +9304,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="Q134" s="5">
         <v>46329</v>
@@ -9407,7 +9330,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B135" s="8">
         <v>46181.60960517361</v>
@@ -9417,16 +9340,16 @@
         <v>46182.8294527199</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I135" s="8">
         <v>46329</v>
@@ -9444,13 +9367,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="Q135" s="9"/>
       <c r="R135" s="9"/>
@@ -9460,7 +9383,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B136" s="5">
         <v>46181.609610011576</v>
@@ -9470,16 +9393,16 @@
         <v>46182.829451909725</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I136" s="5">
         <v>46329</v>
@@ -9497,10 +9420,10 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="P136" s="6" t="s">
         <v>26</v>
@@ -9513,7 +9436,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B137" s="8">
         <v>46181.609613796296</v>
@@ -9529,10 +9452,10 @@
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I137" s="8">
         <v>46329</v>
@@ -9550,7 +9473,7 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="O137" s="9" t="s">
         <v>60</v>
@@ -9566,7 +9489,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B138" s="5">
         <v>46181.61712142361</v>
@@ -9582,10 +9505,10 @@
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I138" s="5">
         <v>46329</v>
@@ -9603,7 +9526,7 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="O138" s="6" t="s">
         <v>60</v>
@@ -9619,7 +9542,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B139" s="8">
         <v>46181.61716094907</v>
@@ -9629,16 +9552,16 @@
         <v>46182.82945207176</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I139" s="8">
         <v>46329</v>
@@ -9656,10 +9579,10 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="P139" s="9" t="s">
         <v>26</v>
@@ -9672,7 +9595,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B140" s="5">
         <v>46181.61719633102</v>
@@ -9682,16 +9605,16 @@
         <v>46182.829452025464</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I140" s="5">
         <v>46329</v>
@@ -9709,10 +9632,10 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P140" s="6" t="s">
         <v>26</v>
@@ -9725,7 +9648,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B141" s="8">
         <v>46181.617235451384</v>
@@ -9735,16 +9658,16 @@
         <v>46182.829452418984</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I141" s="8">
         <v>46329</v>
@@ -9762,10 +9685,10 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="P141" s="9" t="s">
         <v>26</v>
@@ -9778,7 +9701,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B142" s="5">
         <v>46181.60961741898</v>
@@ -9788,7 +9711,7 @@
         <v>46182.63449439815</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>25</v>
@@ -9812,7 +9735,7 @@
         <v>26</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="P142" s="6" t="s">
         <v>26</v>
@@ -9825,7 +9748,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B143" s="8">
         <v>46181.60962174769</v>
@@ -9835,16 +9758,16 @@
         <v>46182.64244836806</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="I143" s="8">
         <v>46330</v>
@@ -9862,13 +9785,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="Q143" s="8">
         <v>46330</v>
@@ -9888,7 +9811,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B144" s="5">
         <v>46181.60962780092</v>
@@ -9898,7 +9821,7 @@
         <v>46191.67892958333</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -9925,13 +9848,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="Q144" s="5">
         <v>46330</v>
@@ -9951,7 +9874,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B145" s="8">
         <v>46181.60963489584</v>
@@ -9961,7 +9884,7 @@
         <v>46182.63449431713</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>25</v>
@@ -9985,7 +9908,7 @@
         <v>26</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="P145" s="9" t="s">
         <v>26</v>
@@ -10004,7 +9927,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B146" s="5">
         <v>46181.609640208335</v>
@@ -10014,7 +9937,7 @@
         <v>46182.64254377315</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10041,13 +9964,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="Q146" s="5">
         <v>46330</v>
@@ -10067,7 +9990,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B147" s="8">
         <v>46181.609646365745</v>
@@ -10077,7 +10000,7 @@
         <v>46182.64254079861</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
@@ -10104,13 +10027,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="O147" s="9" t="s">
         <v>375</v>
       </c>
-      <c r="O147" s="9" t="s">
-        <v>378</v>
-      </c>
       <c r="P147" s="9" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="Q147" s="8">
         <v>46339</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -6715,7 +6715,7 @@
         <v>46213.56803628472</v>
       </c>
       <c r="D87" s="8">
-        <v>46213.56805165509</v>
+        <v>46220.18663762731</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>268</v>
@@ -6759,8 +6759,8 @@
       <c r="R87" s="8">
         <v>46227</v>
       </c>
-      <c r="S87" s="10" t="s">
-        <v>32</v>
+      <c r="S87" s="12" t="s">
+        <v>124</v>
       </c>
       <c r="T87" s="9">
         <v>1</v>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46217.697973773145</v>
+        <v>46220.186637569444</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>61</v>
@@ -6885,8 +6885,8 @@
       <c r="R89" s="8">
         <v>46227</v>
       </c>
-      <c r="S89" s="10" t="s">
-        <v>32</v>
+      <c r="S89" s="12" t="s">
+        <v>124</v>
       </c>
       <c r="T89" s="9">
         <v>0</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1686" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1720" uniqueCount="380">
   <si>
     <t>50001559 - FERROVIAL</t>
   </si>
@@ -347,6 +347,9 @@
   </si>
   <si>
     <t>propuesta nucleo rodete  ot 4347</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
   </si>
   <si>
     <t>Propuesta compras:,Reserva rodete ot 4347</t>
@@ -2859,7 +2862,7 @@
         <v>46197.42280901621</v>
       </c>
       <c r="D21" s="8">
-        <v>46197.422811446755</v>
+        <v>46223.56543164352</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>89</v>
@@ -2868,9 +2871,11 @@
         <v>26</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H21" s="9"/>
+        <v>90</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>90</v>
+      </c>
       <c r="I21" s="8">
         <v>46174</v>
       </c>
@@ -2893,7 +2898,7 @@
         <v>73</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q21" s="8">
         <v>46174</v>
@@ -2913,7 +2918,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B22" s="5">
         <v>46181.60888054398</v>
@@ -2922,18 +2927,20 @@
         <v>46196.658568541665</v>
       </c>
       <c r="D22" s="5">
-        <v>46206.551626817134</v>
+        <v>46223.56542827546</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H22" s="6"/>
+        <v>90</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>90</v>
+      </c>
       <c r="I22" s="5">
         <v>46248</v>
       </c>
@@ -2953,10 +2960,10 @@
         <v>80</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q22" s="5">
         <v>46248</v>
@@ -2976,7 +2983,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B23" s="8">
         <v>46181.60888559028</v>
@@ -2985,18 +2992,20 @@
         <v>46196.65883074074</v>
       </c>
       <c r="D23" s="8">
-        <v>46206.5519203588</v>
+        <v>46223.56542460648</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H23" s="9"/>
+        <v>90</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>90</v>
+      </c>
       <c r="I23" s="8">
         <v>46248</v>
       </c>
@@ -3016,10 +3025,10 @@
         <v>80</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q23" s="8">
         <v>46248</v>
@@ -3039,7 +3048,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B24" s="5">
         <v>46181.60888961806</v>
@@ -3048,18 +3057,20 @@
         <v>46204.888766944445</v>
       </c>
       <c r="D24" s="5">
-        <v>46206.5521100926</v>
+        <v>46223.56542116898</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H24" s="6"/>
+        <v>90</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>90</v>
+      </c>
       <c r="I24" s="5">
         <v>46248</v>
       </c>
@@ -3079,10 +3090,10 @@
         <v>80</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q24" s="5">
         <v>46248</v>
@@ -3102,7 +3113,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B25" s="8">
         <v>46181.6088934375</v>
@@ -3111,18 +3122,20 @@
         <v>46197.64511049769</v>
       </c>
       <c r="D25" s="8">
-        <v>46206.552334583335</v>
+        <v>46223.56541603009</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H25" s="9"/>
+        <v>90</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>90</v>
+      </c>
       <c r="I25" s="8">
         <v>46248</v>
       </c>
@@ -3142,10 +3155,10 @@
         <v>80</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q25" s="8">
         <v>46248</v>
@@ -3165,7 +3178,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B26" s="5">
         <v>46181.608897638886</v>
@@ -3177,7 +3190,7 @@
         <v>46190.67787061342</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
@@ -3210,7 +3223,7 @@
         <v>48</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q26" s="5">
         <v>46168</v>
@@ -3230,7 +3243,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B27" s="8">
         <v>46190.88204489583</v>
@@ -3242,7 +3255,7 @@
         <v>46197.424089050925</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>25</v>
@@ -3283,7 +3296,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B28" s="5">
         <v>46190.88321909722</v>
@@ -3292,18 +3305,20 @@
         <v>46197.42354282408</v>
       </c>
       <c r="D28" s="5">
-        <v>46197.42355928241</v>
+        <v>46223.56549825231</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H28" s="6"/>
+        <v>90</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>90</v>
+      </c>
       <c r="I28" s="5">
         <v>46169</v>
       </c>
@@ -3320,7 +3335,7 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>83</v>
@@ -3346,7 +3361,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B29" s="8">
         <v>46190.88327185185</v>
@@ -3355,18 +3370,20 @@
         <v>46197.42396493055</v>
       </c>
       <c r="D29" s="8">
-        <v>46197.423981597225</v>
+        <v>46223.565494525465</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H29" s="9"/>
+        <v>90</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>90</v>
+      </c>
       <c r="I29" s="8">
         <v>46176</v>
       </c>
@@ -3383,7 +3400,7 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O29" s="9" t="s">
         <v>86</v>
@@ -3409,7 +3426,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B30" s="5">
         <v>46190.88332659722</v>
@@ -3418,18 +3435,20 @@
         <v>46197.42406122685</v>
       </c>
       <c r="D30" s="5">
-        <v>46197.42407648148</v>
+        <v>46223.56549020833</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H30" s="6"/>
+        <v>90</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>90</v>
+      </c>
       <c r="I30" s="5">
         <v>46176</v>
       </c>
@@ -3446,7 +3465,7 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>89</v>
@@ -3472,7 +3491,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B31" s="8">
         <v>46181.608652256946</v>
@@ -3482,7 +3501,7 @@
         <v>46205.61719612269</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>25</v>
@@ -3506,7 +3525,7 @@
         <v>26</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P31" s="9" t="s">
         <v>26</v>
@@ -3516,12 +3535,12 @@
       <c r="S31" s="9"/>
       <c r="T31" s="9"/>
       <c r="U31" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B32" s="5">
         <v>46181.60900793981</v>
@@ -3533,16 +3552,16 @@
         <v>46218.18782881944</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I32" s="5">
         <v>46170</v>
@@ -3560,10 +3579,10 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3575,7 +3594,7 @@
         <v>46225</v>
       </c>
       <c r="S32" s="12" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="T32" s="6">
         <v>1</v>
@@ -3586,7 +3605,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B33" s="8">
         <v>46181.60901165509</v>
@@ -3598,16 +3617,16 @@
         <v>46195.68592747685</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I33" s="8">
         <v>46170</v>
@@ -3625,13 +3644,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3641,7 +3660,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B34" s="5">
         <v>46181.60901612269</v>
@@ -3653,16 +3672,16 @@
         <v>46217.69795753472</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I34" s="5">
         <v>46177</v>
@@ -3680,13 +3699,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3696,7 +3715,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B35" s="8">
         <v>46181.60902011574</v>
@@ -3708,16 +3727,16 @@
         <v>46205.61719211805</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I35" s="8">
         <v>46252</v>
@@ -3735,13 +3754,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q35" s="8">
         <v>46252</v>
@@ -3761,7 +3780,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B36" s="5">
         <v>46181.60902488426</v>
@@ -3773,16 +3792,16 @@
         <v>46199.57115532407</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I36" s="5">
         <v>46252</v>
@@ -3800,13 +3819,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3822,7 +3841,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B37" s="8">
         <v>46181.609029803236</v>
@@ -3834,16 +3853,16 @@
         <v>46205.61257221065</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I37" s="8">
         <v>46254</v>
@@ -3861,13 +3880,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3883,7 +3902,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B38" s="5">
         <v>46181.60903511574</v>
@@ -3895,16 +3914,16 @@
         <v>46199.572352546296</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I38" s="5">
         <v>46252</v>
@@ -3922,10 +3941,10 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3948,7 +3967,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B39" s="8">
         <v>46181.60903861111</v>
@@ -3960,16 +3979,16 @@
         <v>46199.57256810185</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I39" s="8">
         <v>46252</v>
@@ -3987,13 +4006,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -4003,7 +4022,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B40" s="5">
         <v>46181.609042951386</v>
@@ -4015,16 +4034,16 @@
         <v>46199.57232634259</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I40" s="5">
         <v>46254</v>
@@ -4042,13 +4061,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4058,7 +4077,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B41" s="8">
         <v>46181.609047164355</v>
@@ -4070,16 +4089,16 @@
         <v>46212.82441381944</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I41" s="8">
         <v>46252</v>
@@ -4097,10 +4116,10 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P41" s="9" t="s">
         <v>26</v>
@@ -4123,7 +4142,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B42" s="5">
         <v>46181.60905075232</v>
@@ -4135,16 +4154,16 @@
         <v>46204.67396857639</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I42" s="5">
         <v>46252</v>
@@ -4162,13 +4181,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4178,7 +4197,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B43" s="8">
         <v>46181.60905546296</v>
@@ -4190,16 +4209,16 @@
         <v>46204.67391837963</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I43" s="8">
         <v>46261</v>
@@ -4217,13 +4236,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -4233,7 +4252,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B44" s="5">
         <v>46181.60906018519</v>
@@ -4243,16 +4262,16 @@
         <v>46204.67384744213</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I44" s="5">
         <v>46290</v>
@@ -4270,10 +4289,10 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>26</v>
@@ -4286,7 +4305,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B45" s="8">
         <v>46181.609063310185</v>
@@ -4298,16 +4317,16 @@
         <v>46205.61290721065</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I45" s="8">
         <v>46252</v>
@@ -4325,10 +4344,10 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>26</v>
@@ -4351,7 +4370,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B46" s="5">
         <v>46181.60906703703</v>
@@ -4363,16 +4382,16 @@
         <v>46205.61283694445</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I46" s="5">
         <v>46252</v>
@@ -4390,13 +4409,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4406,7 +4425,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B47" s="8">
         <v>46181.60907681713</v>
@@ -4418,16 +4437,16 @@
         <v>46205.612879328706</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I47" s="8">
         <v>46254</v>
@@ -4445,13 +4464,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
@@ -4461,7 +4480,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B48" s="5">
         <v>46181.6090815625</v>
@@ -4473,7 +4492,7 @@
         <v>46210.525643402776</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>25</v>
@@ -4497,7 +4516,7 @@
         <v>26</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>26</v>
@@ -4514,7 +4533,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B49" s="8">
         <v>46181.60908480324</v>
@@ -4526,16 +4545,16 @@
         <v>46197.7158150926</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I49" s="8">
         <v>46174</v>
@@ -4553,13 +4572,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q49" s="8">
         <v>46174</v>
@@ -4568,7 +4587,7 @@
         <v>46191</v>
       </c>
       <c r="S49" s="11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="T49" s="9">
         <v>1</v>
@@ -4579,7 +4598,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B50" s="5">
         <v>46181.60908915509</v>
@@ -4591,16 +4610,16 @@
         <v>46190.70821390046</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I50" s="5">
         <v>46174</v>
@@ -4618,13 +4637,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>77</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4634,7 +4653,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B51" s="8">
         <v>46181.60909384259</v>
@@ -4646,16 +4665,16 @@
         <v>46190.7082228125</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I51" s="8">
         <v>46174</v>
@@ -4673,13 +4692,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>77</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4689,7 +4708,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B52" s="5">
         <v>46181.61221741898</v>
@@ -4701,16 +4720,16 @@
         <v>46190.708227337964</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I52" s="5">
         <v>46174</v>
@@ -4728,13 +4747,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>77</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4744,7 +4763,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B53" s="8">
         <v>46181.612357199076</v>
@@ -4756,16 +4775,16 @@
         <v>46190.708233321755</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I53" s="8">
         <v>46174</v>
@@ -4783,13 +4802,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>77</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -4799,7 +4818,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B54" s="5">
         <v>46181.609098182875</v>
@@ -4811,16 +4830,16 @@
         <v>46197.71584820602</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I54" s="5">
         <v>46227</v>
@@ -4838,13 +4857,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q54" s="5">
         <v>46227</v>
@@ -4864,7 +4883,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B55" s="8">
         <v>46181.60910252314</v>
@@ -4876,16 +4895,16 @@
         <v>46191.54270819444</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I55" s="8">
         <v>46227</v>
@@ -4903,13 +4922,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4919,7 +4938,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B56" s="5">
         <v>46181.609107951386</v>
@@ -4931,16 +4950,16 @@
         <v>46191.54271703704</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I56" s="5">
         <v>46227</v>
@@ -4958,13 +4977,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4974,7 +4993,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B57" s="8">
         <v>46181.61393570602</v>
@@ -4986,16 +5005,16 @@
         <v>46190.70842170139</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I57" s="8">
         <v>46227</v>
@@ -5013,13 +5032,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5029,7 +5048,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B58" s="5">
         <v>46181.61396929398</v>
@@ -5041,16 +5060,16 @@
         <v>46190.708426550926</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I58" s="5">
         <v>46227</v>
@@ -5068,13 +5087,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5084,7 +5103,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B59" s="8">
         <v>46181.60911329861</v>
@@ -5096,16 +5115,16 @@
         <v>46191.54539826389</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I59" s="8">
         <v>46247</v>
@@ -5123,13 +5142,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q59" s="8">
         <v>46247</v>
@@ -5149,7 +5168,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B60" s="5">
         <v>46181.60912350695</v>
@@ -5161,16 +5180,16 @@
         <v>46191.54536050926</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I60" s="6"/>
       <c r="J60" s="5">
@@ -5186,13 +5205,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5202,7 +5221,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B61" s="8">
         <v>46181.60912782408</v>
@@ -5214,16 +5233,16 @@
         <v>46191.54537386574</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I61" s="9"/>
       <c r="J61" s="8">
@@ -5239,13 +5258,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5255,7 +5274,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B62" s="5">
         <v>46181.614119606485</v>
@@ -5267,16 +5286,16 @@
         <v>46190.721725358795</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I62" s="6"/>
       <c r="J62" s="5">
@@ -5292,10 +5311,10 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5308,7 +5327,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B63" s="8">
         <v>46181.61419627315</v>
@@ -5320,16 +5339,16 @@
         <v>46190.7217299537</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I63" s="9"/>
       <c r="J63" s="8">
@@ -5345,10 +5364,10 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5361,7 +5380,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B64" s="5">
         <v>46181.60913207176</v>
@@ -5371,16 +5390,16 @@
         <v>46212.622826203704</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I64" s="5">
         <v>46322</v>
@@ -5398,10 +5417,10 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>26</v>
@@ -5424,7 +5443,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B65" s="8">
         <v>46181.609135833336</v>
@@ -5434,16 +5453,16 @@
         <v>46182.63311847222</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I65" s="8">
         <v>46322</v>
@@ -5461,13 +5480,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5477,7 +5496,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B66" s="5">
         <v>46181.614311909725</v>
@@ -5487,16 +5506,16 @@
         <v>46182.63311923611</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I66" s="5">
         <v>46322</v>
@@ -5514,13 +5533,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5530,7 +5549,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B67" s="8">
         <v>46181.60918671296</v>
@@ -5542,7 +5561,7 @@
         <v>46216.64129429398</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>25</v>
@@ -5566,7 +5585,7 @@
         <v>26</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>26</v>
@@ -5583,7 +5602,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B68" s="5">
         <v>46181.609196087964</v>
@@ -5595,16 +5614,16 @@
         <v>46213.56938424769</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I68" s="5">
         <v>46252</v>
@@ -5622,13 +5641,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q68" s="5">
         <v>46252</v>
@@ -5648,7 +5667,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B69" s="8">
         <v>46181.609201921296</v>
@@ -5660,16 +5679,16 @@
         <v>46216.71548459491</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I69" s="8">
         <v>46254</v>
@@ -5687,13 +5706,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q69" s="8">
         <v>46254</v>
@@ -5713,7 +5732,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B70" s="5">
         <v>46181.60920746528</v>
@@ -5725,16 +5744,16 @@
         <v>46213.569400231485</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I70" s="5">
         <v>46252</v>
@@ -5752,13 +5771,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q70" s="5">
         <v>46252</v>
@@ -5778,7 +5797,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B71" s="8">
         <v>46181.609212870375</v>
@@ -5790,16 +5809,16 @@
         <v>46216.715484733795</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I71" s="8">
         <v>46254</v>
@@ -5817,13 +5836,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q71" s="8">
         <v>46254</v>
@@ -5843,7 +5862,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B72" s="5">
         <v>46181.60921715278</v>
@@ -5855,16 +5874,16 @@
         <v>46213.569419479165</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I72" s="5">
         <v>46252</v>
@@ -5882,13 +5901,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q72" s="5">
         <v>46252</v>
@@ -5908,7 +5927,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B73" s="8">
         <v>46181.60922180556</v>
@@ -5920,16 +5939,16 @@
         <v>46216.71548493055</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I73" s="8">
         <v>46254</v>
@@ -5947,13 +5966,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q73" s="8">
         <v>46254</v>
@@ -5973,7 +5992,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B74" s="5">
         <v>46181.60922590278</v>
@@ -5983,7 +6002,7 @@
         <v>46181.782424143516</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>25</v>
@@ -6007,7 +6026,7 @@
         <v>26</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>26</v>
@@ -6020,7 +6039,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B75" s="8">
         <v>46181.60922940972</v>
@@ -6030,16 +6049,16 @@
         <v>46216.71555703704</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I75" s="8">
         <v>46258</v>
@@ -6057,13 +6076,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q75" s="8">
         <v>46258</v>
@@ -6083,7 +6102,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B76" s="5">
         <v>46181.60923553241</v>
@@ -6093,16 +6112,16 @@
         <v>46216.641273009256</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I76" s="5">
         <v>46258</v>
@@ -6120,13 +6139,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6136,7 +6155,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B77" s="8">
         <v>46181.609241805556</v>
@@ -6146,16 +6165,16 @@
         <v>46216.64127412037</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I77" s="8">
         <v>46258</v>
@@ -6173,13 +6192,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
@@ -6189,7 +6208,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B78" s="5">
         <v>46181.609247002314</v>
@@ -6199,16 +6218,16 @@
         <v>46212.62258834491</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I78" s="5">
         <v>46267</v>
@@ -6226,13 +6245,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q78" s="5">
         <v>46267</v>
@@ -6252,7 +6271,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B79" s="8">
         <v>46181.60925648148</v>
@@ -6262,16 +6281,16 @@
         <v>46191.54540523148</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I79" s="8">
         <v>46267</v>
@@ -6289,13 +6308,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6305,7 +6324,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B80" s="5">
         <v>46181.609262199076</v>
@@ -6315,16 +6334,16 @@
         <v>46191.54540574074</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I80" s="5">
         <v>46267</v>
@@ -6342,13 +6361,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6358,7 +6377,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B81" s="8">
         <v>46181.60926783565</v>
@@ -6368,16 +6387,16 @@
         <v>46212.62263724537</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I81" s="8">
         <v>46289</v>
@@ -6395,13 +6414,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q81" s="8">
         <v>46289</v>
@@ -6421,7 +6440,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B82" s="5">
         <v>46181.60927226851</v>
@@ -6431,16 +6450,16 @@
         <v>46191.545403842596</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I82" s="5">
         <v>46289</v>
@@ -6458,13 +6477,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6474,7 +6493,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B83" s="8">
         <v>46181.60927799769</v>
@@ -6484,16 +6503,16 @@
         <v>46191.545404212964</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I83" s="8">
         <v>46289</v>
@@ -6511,13 +6530,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6527,7 +6546,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B84" s="5">
         <v>46181.60928361111</v>
@@ -6537,7 +6556,7 @@
         <v>46213.56805377315</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>25</v>
@@ -6561,7 +6580,7 @@
         <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6571,12 +6590,12 @@
       <c r="S84" s="6"/>
       <c r="T84" s="6"/>
       <c r="U84" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B85" s="8">
         <v>46181.609286990744</v>
@@ -6588,16 +6607,16 @@
         <v>46213.56773226852</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I85" s="8">
         <v>46182</v>
@@ -6615,13 +6634,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q85" s="8">
         <v>46182</v>
@@ -6630,7 +6649,7 @@
         <v>46183</v>
       </c>
       <c r="S85" s="11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="T85" s="9">
         <v>1</v>
@@ -6641,7 +6660,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B86" s="5">
         <v>46181.609292974535</v>
@@ -6653,16 +6672,16 @@
         <v>46213.56774653935</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I86" s="5">
         <v>46290</v>
@@ -6680,13 +6699,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q86" s="5">
         <v>46290</v>
@@ -6706,7 +6725,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B87" s="8">
         <v>46181.60929881944</v>
@@ -6718,16 +6737,16 @@
         <v>46220.18663762731</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I87" s="8">
         <v>46226</v>
@@ -6745,13 +6764,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q87" s="8">
         <v>46226</v>
@@ -6760,7 +6779,7 @@
         <v>46227</v>
       </c>
       <c r="S87" s="12" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="T87" s="9">
         <v>1</v>
@@ -6771,7 +6790,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B88" s="5">
         <v>46181.60930480324</v>
@@ -6781,16 +6800,16 @@
         <v>46212.623013958335</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I88" s="5">
         <v>46293</v>
@@ -6808,13 +6827,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q88" s="5">
         <v>46293</v>
@@ -6829,12 +6848,12 @@
         <v>0</v>
       </c>
       <c r="U88" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B89" s="8">
         <v>46181.60935271991</v>
@@ -6850,10 +6869,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I89" s="8">
         <v>46226</v>
@@ -6871,10 +6890,10 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P89" s="9" t="s">
         <v>56</v>
@@ -6886,18 +6905,18 @@
         <v>46227</v>
       </c>
       <c r="S89" s="12" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="T89" s="9">
         <v>0</v>
       </c>
       <c r="U89" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B90" s="5">
         <v>46181.60936674768</v>
@@ -6907,7 +6926,7 @@
         <v>46213.50490068287</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -6931,7 +6950,7 @@
         <v>26</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -6944,25 +6963,27 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B91" s="8">
         <v>46181.609371666666</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46182.64123547454</v>
+        <v>46223.56716226852</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H91" s="9"/>
+        <v>90</v>
+      </c>
+      <c r="H91" s="9" t="s">
+        <v>90</v>
+      </c>
       <c r="I91" s="8">
         <v>46290</v>
       </c>
@@ -6979,13 +7000,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q91" s="8">
         <v>46290</v>
@@ -7005,25 +7026,27 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B92" s="5">
         <v>46181.609378587964</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46182.64119599537</v>
+        <v>46223.565613506944</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H92" s="6"/>
+        <v>90</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>90</v>
+      </c>
       <c r="I92" s="5">
         <v>46290</v>
       </c>
@@ -7040,13 +7063,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7056,25 +7079,27 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B93" s="8">
         <v>46181.61514019676</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46182.64119222222</v>
+        <v>46223.565612962964</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H93" s="9"/>
+        <v>90</v>
+      </c>
+      <c r="H93" s="9" t="s">
+        <v>90</v>
+      </c>
       <c r="I93" s="8">
         <v>46290</v>
       </c>
@@ -7091,13 +7116,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7107,7 +7132,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B94" s="5">
         <v>46181.609386111115</v>
@@ -7116,18 +7141,20 @@
         <v>46204.895157314815</v>
       </c>
       <c r="D94" s="5">
-        <v>46212.62246368056</v>
+        <v>46223.56717594907</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H94" s="6"/>
+        <v>90</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>90</v>
+      </c>
       <c r="I94" s="5">
         <v>46311</v>
       </c>
@@ -7144,13 +7171,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q94" s="5">
         <v>46311</v>
@@ -7170,7 +7197,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B95" s="8">
         <v>46181.60939194444</v>
@@ -7179,18 +7206,20 @@
         <v>46204.89505366898</v>
       </c>
       <c r="D95" s="8">
-        <v>46213.56773570602</v>
+        <v>46223.566525462964</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H95" s="9"/>
+        <v>90</v>
+      </c>
+      <c r="H95" s="9" t="s">
+        <v>90</v>
+      </c>
       <c r="I95" s="8">
         <v>46311</v>
       </c>
@@ -7207,13 +7236,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7223,7 +7252,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B96" s="5">
         <v>46181.61518315972</v>
@@ -7232,18 +7261,20 @@
         <v>46204.89514296297</v>
       </c>
       <c r="D96" s="5">
-        <v>46213.567735150464</v>
+        <v>46223.56652129629</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H96" s="6"/>
+        <v>90</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>90</v>
+      </c>
       <c r="I96" s="5">
         <v>46311</v>
       </c>
@@ -7260,10 +7291,10 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>26</v>
@@ -7276,7 +7307,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B97" s="8">
         <v>46181.60939866898</v>
@@ -7285,18 +7316,20 @@
         <v>46213.50489005787</v>
       </c>
       <c r="D97" s="8">
-        <v>46213.50490375</v>
+        <v>46223.56717180555</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H97" s="9"/>
+        <v>90</v>
+      </c>
+      <c r="H97" s="9" t="s">
+        <v>90</v>
+      </c>
       <c r="I97" s="8">
         <v>46315</v>
       </c>
@@ -7313,13 +7346,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q97" s="8">
         <v>46315</v>
@@ -7339,7 +7372,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B98" s="5">
         <v>46181.60940505787</v>
@@ -7348,18 +7381,20 @@
         <v>46213.50480490741</v>
       </c>
       <c r="D98" s="5">
-        <v>46213.56772277778</v>
+        <v>46223.56665253472</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H98" s="6"/>
+        <v>90</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>90</v>
+      </c>
       <c r="I98" s="5">
         <v>46315</v>
       </c>
@@ -7376,13 +7411,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7392,27 +7427,29 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B99" s="8">
         <v>46181.61523613426</v>
       </c>
       <c r="C99" s="8">
-        <v>46213.50487766204</v>
+        <v>46223.56667829861</v>
       </c>
       <c r="D99" s="8">
-        <v>46213.56772202546</v>
+        <v>46223.56667947916</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H99" s="9"/>
+        <v>90</v>
+      </c>
+      <c r="H99" s="9" t="s">
+        <v>90</v>
+      </c>
       <c r="I99" s="8">
         <v>46315</v>
       </c>
@@ -7429,10 +7466,10 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P99" s="9" t="s">
         <v>26</v>
@@ -7445,25 +7482,27 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B100" s="5">
         <v>46181.60941365741</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46212.62250564815</v>
+        <v>46223.56716021991</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H100" s="6"/>
+        <v>90</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>90</v>
+      </c>
       <c r="I100" s="5">
         <v>46317</v>
       </c>
@@ -7480,13 +7519,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q100" s="5">
         <v>46317</v>
@@ -7506,25 +7545,27 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B101" s="8">
         <v>46181.60941929398</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46213.56804261574</v>
+        <v>46223.566807800926</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H101" s="9"/>
+        <v>90</v>
+      </c>
+      <c r="H101" s="9" t="s">
+        <v>90</v>
+      </c>
       <c r="I101" s="8">
         <v>46317</v>
       </c>
@@ -7541,13 +7582,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7557,25 +7598,27 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B102" s="5">
         <v>46181.61528053241</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46213.568041192135</v>
+        <v>46223.56680710649</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H102" s="6"/>
+        <v>90</v>
+      </c>
+      <c r="H102" s="6" t="s">
+        <v>90</v>
+      </c>
       <c r="I102" s="5">
         <v>46317</v>
       </c>
@@ -7592,10 +7635,10 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>26</v>
@@ -7608,25 +7651,27 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B103" s="8">
         <v>46181.60942706019</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46212.62252259259</v>
+        <v>46223.56715939815</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H103" s="9"/>
+        <v>90</v>
+      </c>
+      <c r="H103" s="9" t="s">
+        <v>90</v>
+      </c>
       <c r="I103" s="8">
         <v>46321</v>
       </c>
@@ -7643,13 +7688,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q103" s="8">
         <v>46321</v>
@@ -7669,25 +7714,27 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B104" s="5">
         <v>46181.60943415509</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46182.641623125004</v>
+        <v>46223.566960972224</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H104" s="6"/>
+        <v>90</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>90</v>
+      </c>
       <c r="I104" s="5">
         <v>46321</v>
       </c>
@@ -7704,13 +7751,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7720,25 +7767,27 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B105" s="8">
         <v>46181.61532783565</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46182.64161924769</v>
+        <v>46223.56696034722</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H105" s="9"/>
+        <v>90</v>
+      </c>
+      <c r="H105" s="9" t="s">
+        <v>90</v>
+      </c>
       <c r="I105" s="8">
         <v>46321</v>
       </c>
@@ -7755,13 +7804,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -7771,25 +7820,27 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B106" s="5">
         <v>46181.60944410879</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46212.622555497685</v>
+        <v>46223.56715854167</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H106" s="6"/>
+        <v>90</v>
+      </c>
+      <c r="H106" s="6" t="s">
+        <v>90</v>
+      </c>
       <c r="I106" s="5">
         <v>46323</v>
       </c>
@@ -7806,13 +7857,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q106" s="5">
         <v>46323</v>
@@ -7832,25 +7883,27 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B107" s="8">
         <v>46181.60944996528</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46182.64173178241</v>
+        <v>46223.56705920139</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H107" s="9"/>
+        <v>90</v>
+      </c>
+      <c r="H107" s="9" t="s">
+        <v>90</v>
+      </c>
       <c r="I107" s="8">
         <v>46323</v>
       </c>
@@ -7867,13 +7920,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -7883,25 +7936,27 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B108" s="5">
         <v>46181.61537143518</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46182.64172883102</v>
+        <v>46223.56705859954</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H108" s="6"/>
+        <v>90</v>
+      </c>
+      <c r="H108" s="6" t="s">
+        <v>90</v>
+      </c>
       <c r="I108" s="5">
         <v>46323</v>
       </c>
@@ -7918,10 +7973,10 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>26</v>
@@ -7934,7 +7989,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B109" s="8">
         <v>46181.60945642361</v>
@@ -7944,7 +7999,7 @@
         <v>46182.634494212965</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>25</v>
@@ -7968,7 +8023,7 @@
         <v>26</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P109" s="9" t="s">
         <v>26</v>
@@ -7981,7 +8036,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B110" s="5">
         <v>46181.60946096065</v>
@@ -7991,16 +8046,16 @@
         <v>46182.64186350694</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="I110" s="5">
         <v>46324</v>
@@ -8018,13 +8073,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q110" s="5">
         <v>46324</v>
@@ -8044,7 +8099,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B111" s="8">
         <v>46181.60946868056</v>
@@ -8054,16 +8109,16 @@
         <v>46182.641845254635</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="I111" s="8">
         <v>46324</v>
@@ -8081,13 +8136,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q111" s="9"/>
       <c r="R111" s="9"/>
@@ -8097,7 +8152,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B112" s="5">
         <v>46181.609475034726</v>
@@ -8107,16 +8162,16 @@
         <v>46182.64184081019</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="I112" s="5">
         <v>46324</v>
@@ -8134,13 +8189,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8150,7 +8205,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B113" s="8">
         <v>46181.60947921296</v>
@@ -8166,10 +8221,10 @@
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="I113" s="8">
         <v>46324</v>
@@ -8187,7 +8242,7 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O113" s="9" t="s">
         <v>60</v>
@@ -8203,7 +8258,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B114" s="5">
         <v>46181.61605960648</v>
@@ -8219,10 +8274,10 @@
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="I114" s="5">
         <v>46324</v>
@@ -8240,7 +8295,7 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>60</v>
@@ -8256,7 +8311,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B115" s="8">
         <v>46181.61617203704</v>
@@ -8266,16 +8321,16 @@
         <v>46218.812014641204</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="I115" s="8">
         <v>46324</v>
@@ -8293,13 +8348,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O115" s="9" t="s">
         <v>26</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q115" s="9"/>
       <c r="R115" s="9"/>
@@ -8309,7 +8364,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B116" s="5">
         <v>46181.61620771991</v>
@@ -8319,16 +8374,16 @@
         <v>46216.715609837964</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="I116" s="5">
         <v>46324</v>
@@ -8346,13 +8401,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8362,7 +8417,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B117" s="8">
         <v>46181.616245833335</v>
@@ -8372,16 +8427,16 @@
         <v>46218.812044606486</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="I117" s="8">
         <v>46324</v>
@@ -8399,13 +8454,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8415,25 +8470,27 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B118" s="5">
         <v>46181.60948424769</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46182.64199267361</v>
+        <v>46223.567324097225</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H118" s="6"/>
+        <v>90</v>
+      </c>
+      <c r="H118" s="6" t="s">
+        <v>90</v>
+      </c>
       <c r="I118" s="5">
         <v>46325</v>
       </c>
@@ -8450,13 +8507,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q118" s="5">
         <v>46325</v>
@@ -8476,25 +8533,27 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B119" s="8">
         <v>46181.60948969907</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46182.641973854166</v>
+        <v>46223.56727827546</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H119" s="9"/>
+        <v>90</v>
+      </c>
+      <c r="H119" s="9" t="s">
+        <v>90</v>
+      </c>
       <c r="I119" s="8">
         <v>46325</v>
       </c>
@@ -8511,13 +8570,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8527,25 +8586,27 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B120" s="5">
         <v>46181.60949538194</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46182.64197085648</v>
+        <v>46223.567277685186</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H120" s="6"/>
+        <v>90</v>
+      </c>
+      <c r="H120" s="6" t="s">
+        <v>90</v>
+      </c>
       <c r="I120" s="5">
         <v>46325</v>
       </c>
@@ -8562,13 +8623,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8578,14 +8639,14 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B121" s="8">
         <v>46181.609560185185</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46182.641967118056</v>
+        <v>46223.56727706018</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>60</v>
@@ -8594,9 +8655,11 @@
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H121" s="9"/>
+        <v>90</v>
+      </c>
+      <c r="H121" s="9" t="s">
+        <v>90</v>
+      </c>
       <c r="I121" s="8">
         <v>46325</v>
       </c>
@@ -8613,7 +8676,7 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O121" s="9" t="s">
         <v>60</v>
@@ -8629,14 +8692,14 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B122" s="5">
         <v>46181.61659114584</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46182.64196408565</v>
+        <v>46223.56727646991</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>60</v>
@@ -8645,9 +8708,11 @@
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H122" s="6"/>
+        <v>90</v>
+      </c>
+      <c r="H122" s="6" t="s">
+        <v>90</v>
+      </c>
       <c r="I122" s="5">
         <v>46325</v>
       </c>
@@ -8664,7 +8729,7 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>60</v>
@@ -8680,25 +8745,27 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B123" s="8">
         <v>46181.61662431713</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46182.64196105324</v>
+        <v>46223.56727590278</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H123" s="9"/>
+        <v>90</v>
+      </c>
+      <c r="H123" s="9" t="s">
+        <v>90</v>
+      </c>
       <c r="I123" s="8">
         <v>46325</v>
       </c>
@@ -8715,13 +8782,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q123" s="9"/>
       <c r="R123" s="9"/>
@@ -8731,25 +8798,27 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B124" s="5">
         <v>46181.61666238426</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46182.64195453704</v>
+        <v>46223.56727532407</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H124" s="6"/>
+        <v>90</v>
+      </c>
+      <c r="H124" s="6" t="s">
+        <v>90</v>
+      </c>
       <c r="I124" s="5">
         <v>46325</v>
       </c>
@@ -8766,13 +8835,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8782,25 +8851,27 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B125" s="8">
         <v>46181.61670006944</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46182.64195372685</v>
+        <v>46223.56727472223</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H125" s="9"/>
+        <v>90</v>
+      </c>
+      <c r="H125" s="9" t="s">
+        <v>90</v>
+      </c>
       <c r="I125" s="8">
         <v>46325</v>
       </c>
@@ -8817,13 +8888,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -8833,7 +8904,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B126" s="5">
         <v>46181.60956560185</v>
@@ -8843,16 +8914,16 @@
         <v>46182.82952324074</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I126" s="5">
         <v>46328</v>
@@ -8870,13 +8941,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q126" s="5">
         <v>46328</v>
@@ -8896,7 +8967,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B127" s="8">
         <v>46181.60957188657</v>
@@ -8906,16 +8977,16 @@
         <v>46182.82945300926</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H127" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I127" s="8">
         <v>46328</v>
@@ -8933,13 +9004,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -8949,7 +9020,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B128" s="5">
         <v>46181.609583576384</v>
@@ -8959,16 +9030,16 @@
         <v>46182.829453784725</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I128" s="5">
         <v>46328</v>
@@ -8986,13 +9057,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9002,7 +9073,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B129" s="8">
         <v>46181.60958841435</v>
@@ -9018,10 +9089,10 @@
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I129" s="8">
         <v>46328</v>
@@ -9039,7 +9110,7 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O129" s="9" t="s">
         <v>60</v>
@@ -9055,7 +9126,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B130" s="5">
         <v>46181.616839849536</v>
@@ -9071,10 +9142,10 @@
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I130" s="5">
         <v>46328</v>
@@ -9092,7 +9163,7 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O130" s="6" t="s">
         <v>60</v>
@@ -9108,7 +9179,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B131" s="8">
         <v>46181.61689748843</v>
@@ -9118,16 +9189,16 @@
         <v>46182.8294564699</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I131" s="8">
         <v>46328</v>
@@ -9145,13 +9216,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
@@ -9161,7 +9232,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B132" s="5">
         <v>46181.616942569446</v>
@@ -9171,16 +9242,16 @@
         <v>46182.82945721065</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I132" s="5">
         <v>46328</v>
@@ -9198,13 +9269,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9214,7 +9285,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B133" s="8">
         <v>46181.6169815162</v>
@@ -9224,16 +9295,16 @@
         <v>46182.82945796296</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I133" s="8">
         <v>46328</v>
@@ -9251,13 +9322,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9267,7 +9338,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B134" s="5">
         <v>46181.609592673616</v>
@@ -9277,16 +9348,16 @@
         <v>46182.642407384265</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I134" s="5">
         <v>46329</v>
@@ -9304,13 +9375,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q134" s="5">
         <v>46329</v>
@@ -9330,7 +9401,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B135" s="8">
         <v>46181.60960517361</v>
@@ -9340,16 +9411,16 @@
         <v>46182.8294527199</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I135" s="8">
         <v>46329</v>
@@ -9367,13 +9438,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q135" s="9"/>
       <c r="R135" s="9"/>
@@ -9383,7 +9454,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B136" s="5">
         <v>46181.609610011576</v>
@@ -9393,16 +9464,16 @@
         <v>46182.829451909725</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I136" s="5">
         <v>46329</v>
@@ -9420,10 +9491,10 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P136" s="6" t="s">
         <v>26</v>
@@ -9436,7 +9507,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B137" s="8">
         <v>46181.609613796296</v>
@@ -9452,10 +9523,10 @@
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I137" s="8">
         <v>46329</v>
@@ -9473,7 +9544,7 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O137" s="9" t="s">
         <v>60</v>
@@ -9489,7 +9560,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B138" s="5">
         <v>46181.61712142361</v>
@@ -9505,10 +9576,10 @@
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I138" s="5">
         <v>46329</v>
@@ -9526,7 +9597,7 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O138" s="6" t="s">
         <v>60</v>
@@ -9542,7 +9613,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B139" s="8">
         <v>46181.61716094907</v>
@@ -9552,16 +9623,16 @@
         <v>46182.82945207176</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I139" s="8">
         <v>46329</v>
@@ -9579,10 +9650,10 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P139" s="9" t="s">
         <v>26</v>
@@ -9595,7 +9666,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B140" s="5">
         <v>46181.61719633102</v>
@@ -9605,16 +9676,16 @@
         <v>46182.829452025464</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I140" s="5">
         <v>46329</v>
@@ -9632,10 +9703,10 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P140" s="6" t="s">
         <v>26</v>
@@ -9648,7 +9719,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B141" s="8">
         <v>46181.617235451384</v>
@@ -9658,16 +9729,16 @@
         <v>46182.829452418984</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I141" s="8">
         <v>46329</v>
@@ -9685,10 +9756,10 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P141" s="9" t="s">
         <v>26</v>
@@ -9701,7 +9772,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B142" s="5">
         <v>46181.60961741898</v>
@@ -9711,7 +9782,7 @@
         <v>46182.63449439815</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>25</v>
@@ -9735,7 +9806,7 @@
         <v>26</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P142" s="6" t="s">
         <v>26</v>
@@ -9748,7 +9819,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B143" s="8">
         <v>46181.60962174769</v>
@@ -9758,16 +9829,16 @@
         <v>46182.64244836806</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="I143" s="8">
         <v>46330</v>
@@ -9785,13 +9856,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q143" s="8">
         <v>46330</v>
@@ -9811,7 +9882,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B144" s="5">
         <v>46181.60962780092</v>
@@ -9821,7 +9892,7 @@
         <v>46191.67892958333</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -9848,13 +9919,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q144" s="5">
         <v>46330</v>
@@ -9874,7 +9945,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B145" s="8">
         <v>46181.60963489584</v>
@@ -9884,7 +9955,7 @@
         <v>46182.63449431713</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>25</v>
@@ -9908,7 +9979,7 @@
         <v>26</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P145" s="9" t="s">
         <v>26</v>
@@ -9927,7 +9998,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B146" s="5">
         <v>46181.609640208335</v>
@@ -9937,7 +10008,7 @@
         <v>46182.64254377315</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -9964,13 +10035,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q146" s="5">
         <v>46330</v>
@@ -9990,7 +10061,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B147" s="8">
         <v>46181.609646365745</v>
@@ -10000,7 +10071,7 @@
         <v>46182.64254079861</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
@@ -10027,13 +10098,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q147" s="8">
         <v>46339</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -808,7 +808,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT2 4307 ZVN 1-9-86/2 </t>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1215506819773770</t>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46216.71555703704</v>
+        <v>46224.87838688657</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>240</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -808,7 +808,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
   </si>
   <si>
     <t>1215506819773770</t>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46224.87838688657</v>
+        <v>46225.009596805554</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>240</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -808,7 +808,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
+    <t xml:space="preserve">OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
   </si>
   <si>
     <t>1215506819773770</t>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46225.009596805554</v>
+        <v>46225.58945201389</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>240</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1720" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1720" uniqueCount="381">
   <si>
     <t>50001559 - FERROVIAL</t>
   </si>
@@ -349,6 +349,9 @@
     <t>propuesta nucleo rodete  ot 4347</t>
   </si>
   <si>
+    <t>NATALYA ESPINOZA</t>
+  </si>
+  <si>
     <t>nespinoza@zitron.com</t>
   </si>
   <si>
@@ -436,436 +439,436 @@
     <t>Materiales corte Laser ot 4347</t>
   </si>
   <si>
+    <t>1215506819635552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tableros ot 4348  </t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC   ot 4343 ,fabricación tableros   ot 4343 </t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>1215506819635564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tableros ot 4348  ,fabricación tableros   ot 4343 </t>
+  </si>
+  <si>
+    <t>1215506781705104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fabricación tableros   ot 4343 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tableros ot 4348  ,Recepcion Tableros OT 4348  </t>
+  </si>
+  <si>
+    <t>1215506781705121</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC materiales corte Laser ot 4342 -4344,Fabricacion Corte Laser ot 4342 -4344 </t>
+  </si>
+  <si>
+    <t>1215506781722628</t>
+  </si>
+  <si>
+    <t>Generación OC materiales corte Laser ot 4342 -4344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materiales corte Laser ot 4347,Fabricacion Corte Laser ot 4342 -4344 </t>
+  </si>
+  <si>
+    <t>1215506819659775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricacion Corte Laser ot 4342 -4344 </t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser OT 4347,Materiales corte Laser ot 4347</t>
+  </si>
+  <si>
+    <t>1215506819659795</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  ot 4347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC Corte Plasma  ot 4342 -4344 ,Fabricación Corte Plasma  ot 4342 -4344 </t>
+  </si>
+  <si>
+    <t>1215506781740443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materiales Corte Plasma  ot 4347,Fabricación Corte Plasma  ot 4342 -4344 </t>
+  </si>
+  <si>
+    <t>1215506781740460</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Corte Plasma  ot 4342 -4344 </t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  ot 4347,Recepcion Materiales corte plasma OT 4347</t>
+  </si>
+  <si>
+    <t>1215506819661452</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  ot 4347</t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo ot 4347,Generacion OC Fabricación Externa ot 4347</t>
+  </si>
+  <si>
+    <t>1215506819661464</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo ot 4347,Fabricación Externa  ot 4347</t>
+  </si>
+  <si>
+    <t>1215506639064735</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo ot 4347</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  ot 4347,Control de calidad fabricación externa  ot 4347,Recepcion fabricación externa  OT 4347</t>
+  </si>
+  <si>
+    <t>1215506639064752</t>
+  </si>
+  <si>
+    <t>Control de calidad fabricación externa  ot 4347</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1215506639064764</t>
+  </si>
+  <si>
+    <t>Mecanizado  ot 4347</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado ot 4342 -4344,Fabricación Mecanizado ot 4342 -4344</t>
+  </si>
+  <si>
+    <t>1215506639065883</t>
+  </si>
+  <si>
+    <t>Mecanizado  ot 4347,Fabricación Mecanizado ot 4342 -4344</t>
+  </si>
+  <si>
+    <t>1215506639065900</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado ot 4342 -4344</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado OT 4347,Mecanizado  ot 4347</t>
+  </si>
+  <si>
+    <t>1215506984807216</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1215506984807228</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4349- CODO 90° Ø1600MM</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>1215506639092978</t>
+  </si>
+  <si>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>Planos preliminar,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
+  </si>
+  <si>
+    <t>1215506639092995</t>
+  </si>
+  <si>
+    <t>OT 4349- CODO 90° Ø1600MM</t>
+  </si>
+  <si>
+    <t>OT 4349- CODO 90° Ø1600MM,Planos preliminar</t>
+  </si>
+  <si>
+    <t>1215504785833010</t>
+  </si>
+  <si>
+    <t>OT 4350 - CODO 135° Ø1600MM</t>
+  </si>
+  <si>
+    <t>1215504785833011</t>
+  </si>
+  <si>
+    <t>OT 4351 - DUCTO Ø1600MM L:1800MM</t>
+  </si>
+  <si>
+    <t>1215506992781082</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>1215506992781099</t>
+  </si>
+  <si>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1215506819701309</t>
+  </si>
+  <si>
+    <t>OT 4349- CODO 90° Ø1600MM,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1215504785833012</t>
+  </si>
+  <si>
+    <t>1215504785833013</t>
+  </si>
+  <si>
+    <t>1215506819701527</t>
+  </si>
+  <si>
+    <t>Propuesta Corte plasma  ot 4347,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Propuesta Mecanizado ot 4347,Propuesta Fabricación externa ot 4347 ,propuesta Corte Laser ot 4347,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
+  </si>
+  <si>
+    <t>1215506781840190</t>
+  </si>
+  <si>
+    <t>1215506781840207</t>
+  </si>
+  <si>
+    <t>1215504785833014</t>
+  </si>
+  <si>
+    <t>1215504785833017</t>
+  </si>
+  <si>
+    <t>1215506781849603</t>
+  </si>
+  <si>
+    <t>check pruebas FAT OT 4347</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>1215506781849615</t>
+  </si>
+  <si>
+    <t>check pruebas FAT OT 4347,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
+  </si>
+  <si>
+    <t>1215504785833018</t>
+  </si>
+  <si>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPO</t>
+  </si>
+  <si>
+    <t>1215506639141999</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser OT 4347,control de calidad corte laser  OT 4347</t>
+  </si>
+  <si>
+    <t>1215506639142011</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser OT 4347</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t>Bodega:,control de calidad corte laser  OT 4347</t>
+  </si>
+  <si>
+    <t>1215506984940147</t>
+  </si>
+  <si>
+    <t>control de calidad corte laser  OT 4347</t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma OT 4347,Recepcion materiales corte laser OT 4347</t>
+  </si>
+  <si>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Bodega:,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
+  </si>
+  <si>
+    <t>1215506984940169</t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma OT 4347</t>
+  </si>
+  <si>
+    <t>control de calidad corte laser  OT 4347,Control de calidad Corte plasma OT 4347</t>
+  </si>
+  <si>
+    <t>1215506819763590</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma OT 4347</t>
+  </si>
+  <si>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
+  </si>
+  <si>
+    <t>1215506819763607</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado OT 4347</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado OT 4347</t>
+  </si>
+  <si>
+    <t>1215506781913601</t>
+  </si>
+  <si>
+    <t>1215506992907639</t>
+  </si>
+  <si>
+    <t>Caldereria:</t>
+  </si>
+  <si>
+    <t>OT 4347 Armado,OT 4347 Control de calidad Armado,OT 4347 Preparación Materiales</t>
+  </si>
+  <si>
+    <t>1215506992907651</t>
+  </si>
+  <si>
+    <t>OT 4347 Preparación Materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1215506819773770</t>
+  </si>
+  <si>
+    <t>control de calidad corte laser  OT 4347,Control de calidad Mecanizado OT 4347,Control de calidad Corte plasma OT 4347</t>
+  </si>
+  <si>
+    <t>OT 4347 Preparación Materiales,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
+  </si>
+  <si>
+    <t>1215506819773797</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma OT 4347,Control de calidad Mecanizado OT 4347,control de calidad corte laser  OT 4347</t>
+  </si>
+  <si>
+    <t>1215506984972272</t>
+  </si>
+  <si>
+    <t>OT 4347 Armado</t>
+  </si>
+  <si>
+    <t>1215506984982888</t>
+  </si>
+  <si>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,check planos</t>
+  </si>
+  <si>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347 Armado</t>
+  </si>
+  <si>
+    <t>1215506984982910</t>
+  </si>
+  <si>
+    <t>1215506984991511</t>
+  </si>
+  <si>
+    <t>OT 4347 Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1215506819777596</t>
+  </si>
+  <si>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347 Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1215506819777618</t>
+  </si>
+  <si>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347 Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1215506929522878</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete OT 4347,Recepcion Alabe OT 4347,Recepcion motor OT 4347</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1215506819635552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tableros ot 4348  </t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC   ot 4343 ,fabricación tableros   ot 4343 </t>
-  </si>
-  <si>
-    <t>Media</t>
-  </si>
-  <si>
-    <t>1215506819635564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tableros ot 4348  ,fabricación tableros   ot 4343 </t>
-  </si>
-  <si>
-    <t>1215506781705104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fabricación tableros   ot 4343 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tableros ot 4348  ,Recepcion Tableros OT 4348  </t>
-  </si>
-  <si>
-    <t>1215506781705121</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC materiales corte Laser ot 4342 -4344,Fabricacion Corte Laser ot 4342 -4344 </t>
-  </si>
-  <si>
-    <t>1215506781722628</t>
-  </si>
-  <si>
-    <t>Generación OC materiales corte Laser ot 4342 -4344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Materiales corte Laser ot 4347,Fabricacion Corte Laser ot 4342 -4344 </t>
-  </si>
-  <si>
-    <t>1215506819659775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricacion Corte Laser ot 4342 -4344 </t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser OT 4347,Materiales corte Laser ot 4347</t>
-  </si>
-  <si>
-    <t>1215506819659795</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  ot 4347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC Corte Plasma  ot 4342 -4344 ,Fabricación Corte Plasma  ot 4342 -4344 </t>
-  </si>
-  <si>
-    <t>1215506781740443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Materiales Corte Plasma  ot 4347,Fabricación Corte Plasma  ot 4342 -4344 </t>
-  </si>
-  <si>
-    <t>1215506781740460</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Corte Plasma  ot 4342 -4344 </t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  ot 4347,Recepcion Materiales corte plasma OT 4347</t>
-  </si>
-  <si>
-    <t>1215506819661452</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  ot 4347</t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo ot 4347,Generacion OC Fabricación Externa ot 4347</t>
-  </si>
-  <si>
-    <t>1215506819661464</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo ot 4347,Fabricación Externa  ot 4347</t>
-  </si>
-  <si>
-    <t>1215506639064735</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo ot 4347</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  ot 4347,Control de calidad fabricación externa  ot 4347,Recepcion fabricación externa  OT 4347</t>
-  </si>
-  <si>
-    <t>1215506639064752</t>
-  </si>
-  <si>
-    <t>Control de calidad fabricación externa  ot 4347</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1215506639064764</t>
-  </si>
-  <si>
-    <t>Mecanizado  ot 4347</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado ot 4342 -4344,Fabricación Mecanizado ot 4342 -4344</t>
-  </si>
-  <si>
-    <t>1215506639065883</t>
-  </si>
-  <si>
-    <t>Mecanizado  ot 4347,Fabricación Mecanizado ot 4342 -4344</t>
-  </si>
-  <si>
-    <t>1215506639065900</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado ot 4342 -4344</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado OT 4347,Mecanizado  ot 4347</t>
-  </si>
-  <si>
-    <t>1215506984807216</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1215506984807228</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4349- CODO 90° Ø1600MM</t>
-  </si>
-  <si>
-    <t>Alta</t>
-  </si>
-  <si>
-    <t>1215506639092978</t>
-  </si>
-  <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Planos preliminar,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
-  </si>
-  <si>
-    <t>1215506639092995</t>
-  </si>
-  <si>
-    <t>OT 4349- CODO 90° Ø1600MM</t>
-  </si>
-  <si>
-    <t>OT 4349- CODO 90° Ø1600MM,Planos preliminar</t>
-  </si>
-  <si>
-    <t>1215504785833010</t>
-  </si>
-  <si>
-    <t>OT 4350 - CODO 135° Ø1600MM</t>
-  </si>
-  <si>
-    <t>1215504785833011</t>
-  </si>
-  <si>
-    <t>OT 4351 - DUCTO Ø1600MM L:1800MM</t>
-  </si>
-  <si>
-    <t>1215506992781082</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>1215506992781099</t>
-  </si>
-  <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1215506819701309</t>
-  </si>
-  <si>
-    <t>OT 4349- CODO 90° Ø1600MM,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1215504785833012</t>
-  </si>
-  <si>
-    <t>1215504785833013</t>
-  </si>
-  <si>
-    <t>1215506819701527</t>
-  </si>
-  <si>
-    <t>Propuesta Corte plasma  ot 4347,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Propuesta Mecanizado ot 4347,Propuesta Fabricación externa ot 4347 ,propuesta Corte Laser ot 4347,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
-  </si>
-  <si>
-    <t>1215506781840190</t>
-  </si>
-  <si>
-    <t>1215506781840207</t>
-  </si>
-  <si>
-    <t>1215504785833014</t>
-  </si>
-  <si>
-    <t>1215504785833017</t>
-  </si>
-  <si>
-    <t>1215506781849603</t>
-  </si>
-  <si>
-    <t>check pruebas FAT OT 4347</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>1215506781849615</t>
-  </si>
-  <si>
-    <t>check pruebas FAT OT 4347,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
-  </si>
-  <si>
-    <t>1215504785833018</t>
-  </si>
-  <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPO</t>
-  </si>
-  <si>
-    <t>1215506639141999</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser OT 4347,control de calidad corte laser  OT 4347</t>
-  </si>
-  <si>
-    <t>1215506639142011</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser OT 4347</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t>Bodega:,control de calidad corte laser  OT 4347</t>
-  </si>
-  <si>
-    <t>1215506984940147</t>
-  </si>
-  <si>
-    <t>control de calidad corte laser  OT 4347</t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma OT 4347,Recepcion materiales corte laser OT 4347</t>
-  </si>
-  <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Bodega:,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
-  </si>
-  <si>
-    <t>1215506984940169</t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma OT 4347</t>
-  </si>
-  <si>
-    <t>control de calidad corte laser  OT 4347,Control de calidad Corte plasma OT 4347</t>
-  </si>
-  <si>
-    <t>1215506819763590</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma OT 4347</t>
-  </si>
-  <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
-  </si>
-  <si>
-    <t>1215506819763607</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado OT 4347</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado OT 4347</t>
-  </si>
-  <si>
-    <t>1215506781913601</t>
-  </si>
-  <si>
-    <t>1215506992907639</t>
-  </si>
-  <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>OT 4347 Armado,OT 4347 Control de calidad Armado,OT 4347 Preparación Materiales</t>
-  </si>
-  <si>
-    <t>1215506992907651</t>
-  </si>
-  <si>
-    <t>OT 4347 Preparación Materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
-  </si>
-  <si>
-    <t>1215506819773770</t>
-  </si>
-  <si>
-    <t>control de calidad corte laser  OT 4347,Control de calidad Mecanizado OT 4347,Control de calidad Corte plasma OT 4347</t>
-  </si>
-  <si>
-    <t>OT 4347 Preparación Materiales,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
-  </si>
-  <si>
-    <t>1215506819773797</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma OT 4347,Control de calidad Mecanizado OT 4347,control de calidad corte laser  OT 4347</t>
-  </si>
-  <si>
-    <t>1215506984972272</t>
-  </si>
-  <si>
-    <t>OT 4347 Armado</t>
-  </si>
-  <si>
-    <t>1215506984982888</t>
-  </si>
-  <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,check planos</t>
-  </si>
-  <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347 Armado</t>
-  </si>
-  <si>
-    <t>1215506984982910</t>
-  </si>
-  <si>
-    <t>1215506984991511</t>
-  </si>
-  <si>
-    <t>OT 4347 Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1215506819777596</t>
-  </si>
-  <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347 Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1215506819777618</t>
-  </si>
-  <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347 Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1215506929522878</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete OT 4347,Recepcion Alabe OT 4347,Recepcion motor OT 4347</t>
   </si>
   <si>
     <t>1215506929522890</t>
@@ -2874,7 +2877,7 @@
         <v>90</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I21" s="8">
         <v>46174</v>
@@ -2898,7 +2901,7 @@
         <v>73</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q21" s="8">
         <v>46174</v>
@@ -2918,7 +2921,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B22" s="5">
         <v>46181.60888054398</v>
@@ -2930,7 +2933,7 @@
         <v>46223.56542827546</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -2939,7 +2942,7 @@
         <v>90</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I22" s="5">
         <v>46248</v>
@@ -2960,10 +2963,10 @@
         <v>80</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q22" s="5">
         <v>46248</v>
@@ -2983,7 +2986,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B23" s="8">
         <v>46181.60888559028</v>
@@ -2995,7 +2998,7 @@
         <v>46223.56542460648</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
@@ -3004,7 +3007,7 @@
         <v>90</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I23" s="8">
         <v>46248</v>
@@ -3025,10 +3028,10 @@
         <v>80</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q23" s="8">
         <v>46248</v>
@@ -3048,7 +3051,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B24" s="5">
         <v>46181.60888961806</v>
@@ -3060,7 +3063,7 @@
         <v>46223.56542116898</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -3069,7 +3072,7 @@
         <v>90</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I24" s="5">
         <v>46248</v>
@@ -3090,10 +3093,10 @@
         <v>80</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q24" s="5">
         <v>46248</v>
@@ -3113,7 +3116,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B25" s="8">
         <v>46181.6088934375</v>
@@ -3125,7 +3128,7 @@
         <v>46223.56541603009</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
@@ -3134,7 +3137,7 @@
         <v>90</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I25" s="8">
         <v>46248</v>
@@ -3155,10 +3158,10 @@
         <v>80</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q25" s="8">
         <v>46248</v>
@@ -3178,7 +3181,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B26" s="5">
         <v>46181.608897638886</v>
@@ -3190,7 +3193,7 @@
         <v>46190.67787061342</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
@@ -3223,7 +3226,7 @@
         <v>48</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q26" s="5">
         <v>46168</v>
@@ -3243,7 +3246,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B27" s="8">
         <v>46190.88204489583</v>
@@ -3255,7 +3258,7 @@
         <v>46197.424089050925</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>25</v>
@@ -3296,7 +3299,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B28" s="5">
         <v>46190.88321909722</v>
@@ -3308,7 +3311,7 @@
         <v>46223.56549825231</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
@@ -3317,7 +3320,7 @@
         <v>90</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I28" s="5">
         <v>46169</v>
@@ -3335,7 +3338,7 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>83</v>
@@ -3361,7 +3364,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B29" s="8">
         <v>46190.88327185185</v>
@@ -3373,7 +3376,7 @@
         <v>46223.565494525465</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
@@ -3382,7 +3385,7 @@
         <v>90</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I29" s="8">
         <v>46176</v>
@@ -3400,7 +3403,7 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O29" s="9" t="s">
         <v>86</v>
@@ -3426,7 +3429,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B30" s="5">
         <v>46190.88332659722</v>
@@ -3438,7 +3441,7 @@
         <v>46223.56549020833</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3447,7 +3450,7 @@
         <v>90</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I30" s="5">
         <v>46176</v>
@@ -3465,7 +3468,7 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>89</v>
@@ -3491,17 +3494,19 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B31" s="8">
         <v>46181.608652256946</v>
       </c>
-      <c r="C31" s="9"/>
+      <c r="C31" s="8">
+        <v>46225.68491253472</v>
+      </c>
       <c r="D31" s="8">
-        <v>46205.61719612269</v>
+        <v>46225.6849328588</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>25</v>
@@ -3525,7 +3530,7 @@
         <v>26</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P31" s="9" t="s">
         <v>26</v>
@@ -3533,9 +3538,11 @@
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
       <c r="S31" s="9"/>
-      <c r="T31" s="9"/>
-      <c r="U31" s="12" t="s">
-        <v>119</v>
+      <c r="T31" s="9">
+        <v>1</v>
+      </c>
+      <c r="U31" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
@@ -3579,7 +3586,7 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>124</v>
@@ -3617,7 +3624,7 @@
         <v>46195.68592747685</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
@@ -3647,7 +3654,7 @@
         <v>121</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P33" s="9" t="s">
         <v>127</v>
@@ -3702,7 +3709,7 @@
         <v>121</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>130</v>
@@ -3727,7 +3734,7 @@
         <v>46205.61719211805</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
@@ -3754,13 +3761,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O35" s="9" t="s">
         <v>134</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q35" s="8">
         <v>46252</v>
@@ -3819,10 +3826,10 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>137</v>
@@ -3880,7 +3887,7 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O37" s="9" t="s">
         <v>136</v>
@@ -3941,7 +3948,7 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>143</v>
@@ -3979,7 +3986,7 @@
         <v>46199.57256810185</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
@@ -4009,7 +4016,7 @@
         <v>142</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>145</v>
@@ -4064,7 +4071,7 @@
         <v>142</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>148</v>
@@ -4116,7 +4123,7 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O41" s="9" t="s">
         <v>153</v>
@@ -4154,7 +4161,7 @@
         <v>46204.67396857639</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
@@ -4184,7 +4191,7 @@
         <v>150</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>155</v>
@@ -4239,7 +4246,7 @@
         <v>150</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>158</v>
@@ -4344,7 +4351,7 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O45" s="9" t="s">
         <v>165</v>
@@ -4382,7 +4389,7 @@
         <v>46205.61283694445</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
@@ -4412,7 +4419,7 @@
         <v>164</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>167</v>
@@ -4467,7 +4474,7 @@
         <v>164</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P47" s="9" t="s">
         <v>170</v>
@@ -5115,7 +5122,7 @@
         <v>46191.54539826389</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
@@ -5205,13 +5212,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>181</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5258,13 +5265,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>186</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5311,7 +5318,7 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>189</v>
@@ -5364,7 +5371,7 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O63" s="9" t="s">
         <v>191</v>
@@ -5999,7 +6006,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46181.782424143516</v>
+        <v>46225.80634167824</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>237</v>
@@ -6044,9 +6051,11 @@
       <c r="B75" s="8">
         <v>46181.60922940972</v>
       </c>
-      <c r="C75" s="9"/>
+      <c r="C75" s="8">
+        <v>46225.80622738426</v>
+      </c>
       <c r="D75" s="8">
-        <v>46225.58945201389</v>
+        <v>46225.86188380787</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>240</v>
@@ -6094,10 +6103,10 @@
         <v>32</v>
       </c>
       <c r="T75" s="9">
-        <v>0</v>
-      </c>
-      <c r="U75" s="11" t="s">
-        <v>58</v>
+        <v>1</v>
+      </c>
+      <c r="U75" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -6107,9 +6116,11 @@
       <c r="B76" s="5">
         <v>46181.60923553241</v>
       </c>
-      <c r="C76" s="6"/>
+      <c r="C76" s="5">
+        <v>46225.80620184028</v>
+      </c>
       <c r="D76" s="5">
-        <v>46216.641273009256</v>
+        <v>46225.8062046875</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>181</v>
@@ -6160,9 +6171,11 @@
       <c r="B77" s="8">
         <v>46181.609241805556</v>
       </c>
-      <c r="C77" s="9"/>
+      <c r="C77" s="8">
+        <v>46225.806212870375</v>
+      </c>
       <c r="D77" s="8">
-        <v>46216.64127412037</v>
+        <v>46225.806214282406</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>181</v>
@@ -6213,9 +6226,11 @@
       <c r="B78" s="5">
         <v>46181.609247002314</v>
       </c>
-      <c r="C78" s="6"/>
+      <c r="C78" s="5">
+        <v>46225.806332569446</v>
+      </c>
       <c r="D78" s="5">
-        <v>46212.62258834491</v>
+        <v>46225.80634494213</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>250</v>
@@ -6263,10 +6278,10 @@
         <v>32</v>
       </c>
       <c r="T78" s="6">
-        <v>0</v>
-      </c>
-      <c r="U78" s="11" t="s">
-        <v>58</v>
+        <v>1</v>
+      </c>
+      <c r="U78" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -6276,9 +6291,11 @@
       <c r="B79" s="8">
         <v>46181.60925648148</v>
       </c>
-      <c r="C79" s="9"/>
+      <c r="C79" s="8">
+        <v>46225.80630726852</v>
+      </c>
       <c r="D79" s="8">
-        <v>46191.54540523148</v>
+        <v>46225.806309120366</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>181</v>
@@ -6329,9 +6346,11 @@
       <c r="B80" s="5">
         <v>46181.609262199076</v>
       </c>
-      <c r="C80" s="6"/>
+      <c r="C80" s="5">
+        <v>46225.80631783565</v>
+      </c>
       <c r="D80" s="5">
-        <v>46191.54540574074</v>
+        <v>46225.806319490744</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>181</v>
@@ -6384,7 +6403,7 @@
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46212.62263724537</v>
+        <v>46225.807607118055</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>256</v>
@@ -6447,7 +6466,7 @@
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46191.545403842596</v>
+        <v>46225.80631451389</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>181</v>
@@ -6500,7 +6519,7 @@
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46191.545404212964</v>
+        <v>46225.806324097226</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>181</v>
@@ -6590,12 +6609,12 @@
       <c r="S84" s="6"/>
       <c r="T84" s="6"/>
       <c r="U84" s="12" t="s">
-        <v>119</v>
+        <v>263</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B85" s="8">
         <v>46181.609286990744</v>
@@ -6607,7 +6626,7 @@
         <v>46213.56773226852</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
@@ -6640,7 +6659,7 @@
         <v>26</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q85" s="8">
         <v>46182</v>
@@ -6660,7 +6679,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B86" s="5">
         <v>46181.609292974535</v>
@@ -6672,7 +6691,7 @@
         <v>46213.56774653935</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6705,7 +6724,7 @@
         <v>26</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q86" s="5">
         <v>46290</v>
@@ -6725,7 +6744,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B87" s="8">
         <v>46181.60929881944</v>
@@ -6737,7 +6756,7 @@
         <v>46220.18663762731</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
@@ -6770,7 +6789,7 @@
         <v>26</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q87" s="8">
         <v>46226</v>
@@ -6790,7 +6809,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B88" s="5">
         <v>46181.60930480324</v>
@@ -6800,7 +6819,7 @@
         <v>46212.623013958335</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6833,7 +6852,7 @@
         <v>157</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q88" s="5">
         <v>46293</v>
@@ -6848,12 +6867,12 @@
         <v>0</v>
       </c>
       <c r="U88" s="12" t="s">
-        <v>119</v>
+        <v>263</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B89" s="8">
         <v>46181.60935271991</v>
@@ -6911,12 +6930,12 @@
         <v>0</v>
       </c>
       <c r="U89" s="12" t="s">
-        <v>119</v>
+        <v>263</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B90" s="5">
         <v>46181.60936674768</v>
@@ -6926,7 +6945,7 @@
         <v>46213.50490068287</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -6950,7 +6969,7 @@
         <v>26</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -6963,17 +6982,17 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B91" s="8">
         <v>46181.609371666666</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46223.56716226852</v>
+        <v>46225.82172349537</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -6982,7 +7001,7 @@
         <v>90</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I91" s="8">
         <v>46290</v>
@@ -7000,13 +7019,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q91" s="8">
         <v>46290</v>
@@ -7020,13 +7039,13 @@
       <c r="T91" s="9">
         <v>0</v>
       </c>
-      <c r="U91" s="11" t="s">
-        <v>58</v>
+      <c r="U91" s="12" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B92" s="5">
         <v>46181.609378587964</v>
@@ -7045,7 +7064,7 @@
         <v>90</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I92" s="5">
         <v>46290</v>
@@ -7063,13 +7082,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7079,7 +7098,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B93" s="8">
         <v>46181.61514019676</v>
@@ -7098,7 +7117,7 @@
         <v>90</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I93" s="8">
         <v>46290</v>
@@ -7116,13 +7135,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O93" s="9" t="s">
         <v>181</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7132,7 +7151,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B94" s="5">
         <v>46181.609386111115</v>
@@ -7144,7 +7163,7 @@
         <v>46223.56717594907</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7153,7 +7172,7 @@
         <v>90</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I94" s="5">
         <v>46311</v>
@@ -7171,13 +7190,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>181</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q94" s="5">
         <v>46311</v>
@@ -7197,7 +7216,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B95" s="8">
         <v>46181.60939194444</v>
@@ -7218,7 +7237,7 @@
         <v>90</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I95" s="8">
         <v>46311</v>
@@ -7236,13 +7255,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7252,7 +7271,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B96" s="5">
         <v>46181.61518315972</v>
@@ -7273,7 +7292,7 @@
         <v>90</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I96" s="5">
         <v>46311</v>
@@ -7291,10 +7310,10 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>26</v>
@@ -7307,7 +7326,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B97" s="8">
         <v>46181.60939866898</v>
@@ -7316,10 +7335,10 @@
         <v>46213.50489005787</v>
       </c>
       <c r="D97" s="8">
-        <v>46223.56717180555</v>
+        <v>46225.821835625</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
@@ -7328,7 +7347,7 @@
         <v>90</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I97" s="8">
         <v>46315</v>
@@ -7346,13 +7365,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O97" s="9" t="s">
         <v>181</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q97" s="8">
         <v>46315</v>
@@ -7366,13 +7385,13 @@
       <c r="T97" s="9">
         <v>1</v>
       </c>
-      <c r="U97" s="10" t="s">
-        <v>33</v>
+      <c r="U97" s="11" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B98" s="5">
         <v>46181.60940505787</v>
@@ -7393,7 +7412,7 @@
         <v>90</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I98" s="5">
         <v>46315</v>
@@ -7411,13 +7430,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7427,7 +7446,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B99" s="8">
         <v>46181.61523613426</v>
@@ -7448,7 +7467,7 @@
         <v>90</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I99" s="8">
         <v>46315</v>
@@ -7466,10 +7485,10 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P99" s="9" t="s">
         <v>26</v>
@@ -7482,7 +7501,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B100" s="5">
         <v>46181.60941365741</v>
@@ -7492,7 +7511,7 @@
         <v>46223.56716021991</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7501,7 +7520,7 @@
         <v>90</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I100" s="5">
         <v>46317</v>
@@ -7519,13 +7538,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>181</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q100" s="5">
         <v>46317</v>
@@ -7545,7 +7564,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B101" s="8">
         <v>46181.60941929398</v>
@@ -7564,7 +7583,7 @@
         <v>90</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I101" s="8">
         <v>46317</v>
@@ -7582,13 +7601,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7598,7 +7617,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B102" s="5">
         <v>46181.61528053241</v>
@@ -7617,7 +7636,7 @@
         <v>90</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I102" s="5">
         <v>46317</v>
@@ -7635,10 +7654,10 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>26</v>
@@ -7651,7 +7670,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B103" s="8">
         <v>46181.60942706019</v>
@@ -7661,7 +7680,7 @@
         <v>46223.56715939815</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -7670,7 +7689,7 @@
         <v>90</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I103" s="8">
         <v>46321</v>
@@ -7688,13 +7707,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O103" s="9" t="s">
         <v>181</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q103" s="8">
         <v>46321</v>
@@ -7714,7 +7733,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B104" s="5">
         <v>46181.60943415509</v>
@@ -7733,7 +7752,7 @@
         <v>90</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I104" s="5">
         <v>46321</v>
@@ -7751,13 +7770,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>181</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7767,7 +7786,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B105" s="8">
         <v>46181.61532783565</v>
@@ -7786,7 +7805,7 @@
         <v>90</v>
       </c>
       <c r="H105" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I105" s="8">
         <v>46321</v>
@@ -7804,7 +7823,7 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O105" s="9" t="s">
         <v>181</v>
@@ -7820,7 +7839,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B106" s="5">
         <v>46181.60944410879</v>
@@ -7830,7 +7849,7 @@
         <v>46223.56715854167</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7839,7 +7858,7 @@
         <v>90</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I106" s="5">
         <v>46323</v>
@@ -7857,13 +7876,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>181</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q106" s="5">
         <v>46323</v>
@@ -7883,7 +7902,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B107" s="8">
         <v>46181.60944996528</v>
@@ -7902,7 +7921,7 @@
         <v>90</v>
       </c>
       <c r="H107" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I107" s="8">
         <v>46323</v>
@@ -7920,13 +7939,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O107" s="9" t="s">
         <v>181</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -7936,7 +7955,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B108" s="5">
         <v>46181.61537143518</v>
@@ -7955,7 +7974,7 @@
         <v>90</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I108" s="5">
         <v>46323</v>
@@ -7973,7 +7992,7 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>213</v>
@@ -7989,7 +8008,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B109" s="8">
         <v>46181.60945642361</v>
@@ -7999,7 +8018,7 @@
         <v>46182.634494212965</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>25</v>
@@ -8023,7 +8042,7 @@
         <v>26</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P109" s="9" t="s">
         <v>26</v>
@@ -8036,7 +8055,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B110" s="5">
         <v>46181.60946096065</v>
@@ -8046,16 +8065,16 @@
         <v>46182.64186350694</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I110" s="5">
         <v>46324</v>
@@ -8073,13 +8092,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q110" s="5">
         <v>46324</v>
@@ -8099,7 +8118,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B111" s="8">
         <v>46181.60946868056</v>
@@ -8115,10 +8134,10 @@
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I111" s="8">
         <v>46324</v>
@@ -8136,13 +8155,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O111" s="9" t="s">
         <v>181</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q111" s="9"/>
       <c r="R111" s="9"/>
@@ -8152,7 +8171,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B112" s="5">
         <v>46181.609475034726</v>
@@ -8168,10 +8187,10 @@
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I112" s="5">
         <v>46324</v>
@@ -8189,7 +8208,7 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>181</v>
@@ -8205,7 +8224,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B113" s="8">
         <v>46181.60947921296</v>
@@ -8221,10 +8240,10 @@
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I113" s="8">
         <v>46324</v>
@@ -8242,7 +8261,7 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O113" s="9" t="s">
         <v>60</v>
@@ -8258,7 +8277,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B114" s="5">
         <v>46181.61605960648</v>
@@ -8274,10 +8293,10 @@
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I114" s="5">
         <v>46324</v>
@@ -8295,7 +8314,7 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>60</v>
@@ -8311,7 +8330,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B115" s="8">
         <v>46181.61617203704</v>
@@ -8327,10 +8346,10 @@
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I115" s="8">
         <v>46324</v>
@@ -8348,7 +8367,7 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O115" s="9" t="s">
         <v>26</v>
@@ -8364,7 +8383,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B116" s="5">
         <v>46181.61620771991</v>
@@ -8380,10 +8399,10 @@
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I116" s="5">
         <v>46324</v>
@@ -8401,7 +8420,7 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O116" s="6" t="s">
         <v>26</v>
@@ -8417,7 +8436,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B117" s="8">
         <v>46181.616245833335</v>
@@ -8427,16 +8446,16 @@
         <v>46218.812044606486</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I117" s="8">
         <v>46324</v>
@@ -8454,7 +8473,7 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O117" s="9" t="s">
         <v>26</v>
@@ -8470,7 +8489,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B118" s="5">
         <v>46181.60948424769</v>
@@ -8480,7 +8499,7 @@
         <v>46223.567324097225</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8489,7 +8508,7 @@
         <v>90</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I118" s="5">
         <v>46325</v>
@@ -8507,13 +8526,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>181</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q118" s="5">
         <v>46325</v>
@@ -8533,7 +8552,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B119" s="8">
         <v>46181.60948969907</v>
@@ -8552,7 +8571,7 @@
         <v>90</v>
       </c>
       <c r="H119" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I119" s="8">
         <v>46325</v>
@@ -8570,13 +8589,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O119" s="9" t="s">
         <v>181</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8586,7 +8605,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B120" s="5">
         <v>46181.60949538194</v>
@@ -8605,7 +8624,7 @@
         <v>90</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I120" s="5">
         <v>46325</v>
@@ -8623,7 +8642,7 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>181</v>
@@ -8639,7 +8658,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B121" s="8">
         <v>46181.609560185185</v>
@@ -8658,7 +8677,7 @@
         <v>90</v>
       </c>
       <c r="H121" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I121" s="8">
         <v>46325</v>
@@ -8676,7 +8695,7 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O121" s="9" t="s">
         <v>60</v>
@@ -8692,7 +8711,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B122" s="5">
         <v>46181.61659114584</v>
@@ -8711,7 +8730,7 @@
         <v>90</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I122" s="5">
         <v>46325</v>
@@ -8729,7 +8748,7 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>60</v>
@@ -8745,7 +8764,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B123" s="8">
         <v>46181.61662431713</v>
@@ -8764,7 +8783,7 @@
         <v>90</v>
       </c>
       <c r="H123" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I123" s="8">
         <v>46325</v>
@@ -8782,7 +8801,7 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O123" s="9" t="s">
         <v>186</v>
@@ -8798,7 +8817,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B124" s="5">
         <v>46181.61666238426</v>
@@ -8817,7 +8836,7 @@
         <v>90</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I124" s="5">
         <v>46325</v>
@@ -8835,7 +8854,7 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>189</v>
@@ -8851,7 +8870,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B125" s="8">
         <v>46181.61670006944</v>
@@ -8870,7 +8889,7 @@
         <v>90</v>
       </c>
       <c r="H125" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I125" s="8">
         <v>46325</v>
@@ -8888,10 +8907,10 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P125" s="9" t="s">
         <v>191</v>
@@ -8904,7 +8923,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B126" s="5">
         <v>46181.60956560185</v>
@@ -8914,7 +8933,7 @@
         <v>46182.82952324074</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -8941,13 +8960,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>181</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q126" s="5">
         <v>46328</v>
@@ -8967,7 +8986,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B127" s="8">
         <v>46181.60957188657</v>
@@ -9004,13 +9023,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O127" s="9" t="s">
         <v>181</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -9020,7 +9039,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B128" s="5">
         <v>46181.609583576384</v>
@@ -9057,7 +9076,7 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O128" s="6" t="s">
         <v>181</v>
@@ -9073,7 +9092,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B129" s="8">
         <v>46181.60958841435</v>
@@ -9110,7 +9129,7 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O129" s="9" t="s">
         <v>60</v>
@@ -9126,7 +9145,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B130" s="5">
         <v>46181.616839849536</v>
@@ -9163,7 +9182,7 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O130" s="6" t="s">
         <v>60</v>
@@ -9179,7 +9198,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B131" s="8">
         <v>46181.61689748843</v>
@@ -9216,7 +9235,7 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O131" s="9" t="s">
         <v>186</v>
@@ -9232,7 +9251,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B132" s="5">
         <v>46181.616942569446</v>
@@ -9269,7 +9288,7 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O132" s="6" t="s">
         <v>189</v>
@@ -9285,7 +9304,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B133" s="8">
         <v>46181.6169815162</v>
@@ -9322,7 +9341,7 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O133" s="9" t="s">
         <v>191</v>
@@ -9338,17 +9357,17 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B134" s="5">
         <v>46181.609592673616</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46182.642407384265</v>
+        <v>46225.823538819444</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9375,13 +9394,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>181</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q134" s="5">
         <v>46329</v>
@@ -9401,7 +9420,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B135" s="8">
         <v>46181.60960517361</v>
@@ -9438,13 +9457,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O135" s="9" t="s">
         <v>181</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q135" s="9"/>
       <c r="R135" s="9"/>
@@ -9454,7 +9473,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B136" s="5">
         <v>46181.609610011576</v>
@@ -9491,7 +9510,7 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O136" s="6" t="s">
         <v>181</v>
@@ -9507,7 +9526,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B137" s="8">
         <v>46181.609613796296</v>
@@ -9544,7 +9563,7 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O137" s="9" t="s">
         <v>60</v>
@@ -9560,7 +9579,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B138" s="5">
         <v>46181.61712142361</v>
@@ -9597,7 +9616,7 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O138" s="6" t="s">
         <v>60</v>
@@ -9613,7 +9632,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B139" s="8">
         <v>46181.61716094907</v>
@@ -9650,7 +9669,7 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O139" s="9" t="s">
         <v>186</v>
@@ -9666,7 +9685,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B140" s="5">
         <v>46181.61719633102</v>
@@ -9703,7 +9722,7 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O140" s="6" t="s">
         <v>189</v>
@@ -9719,7 +9738,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B141" s="8">
         <v>46181.617235451384</v>
@@ -9756,7 +9775,7 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O141" s="9" t="s">
         <v>191</v>
@@ -9772,7 +9791,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B142" s="5">
         <v>46181.60961741898</v>
@@ -9782,7 +9801,7 @@
         <v>46182.63449439815</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>25</v>
@@ -9806,7 +9825,7 @@
         <v>26</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P142" s="6" t="s">
         <v>26</v>
@@ -9819,7 +9838,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B143" s="8">
         <v>46181.60962174769</v>
@@ -9829,16 +9848,16 @@
         <v>46182.64244836806</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="I143" s="8">
         <v>46330</v>
@@ -9856,13 +9875,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q143" s="8">
         <v>46330</v>
@@ -9882,7 +9901,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B144" s="5">
         <v>46181.60962780092</v>
@@ -9892,7 +9911,7 @@
         <v>46191.67892958333</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -9919,13 +9938,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q144" s="5">
         <v>46330</v>
@@ -9945,7 +9964,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B145" s="8">
         <v>46181.60963489584</v>
@@ -9955,7 +9974,7 @@
         <v>46182.63449431713</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>25</v>
@@ -9979,7 +9998,7 @@
         <v>26</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="P145" s="9" t="s">
         <v>26</v>
@@ -9998,7 +10017,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B146" s="5">
         <v>46181.609640208335</v>
@@ -10008,7 +10027,7 @@
         <v>46182.64254377315</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10035,13 +10054,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q146" s="5">
         <v>46330</v>
@@ -10061,7 +10080,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B147" s="8">
         <v>46181.609646365745</v>
@@ -10071,7 +10090,7 @@
         <v>46182.64254079861</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
@@ -10098,13 +10117,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q147" s="8">
         <v>46339</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -454,442 +454,442 @@
     <t xml:space="preserve">Generación OC   ot 4343 ,fabricación tableros   ot 4343 </t>
   </si>
   <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>1215506819635564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tableros ot 4348  ,fabricación tableros   ot 4343 </t>
+  </si>
+  <si>
+    <t>1215506781705104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fabricación tableros   ot 4343 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tableros ot 4348  ,Recepcion Tableros OT 4348  </t>
+  </si>
+  <si>
+    <t>1215506781705121</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC materiales corte Laser ot 4342 -4344,Fabricacion Corte Laser ot 4342 -4344 </t>
+  </si>
+  <si>
+    <t>1215506781722628</t>
+  </si>
+  <si>
+    <t>Generación OC materiales corte Laser ot 4342 -4344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materiales corte Laser ot 4347,Fabricacion Corte Laser ot 4342 -4344 </t>
+  </si>
+  <si>
+    <t>1215506819659775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricacion Corte Laser ot 4342 -4344 </t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser OT 4347,Materiales corte Laser ot 4347</t>
+  </si>
+  <si>
+    <t>1215506819659795</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  ot 4347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC Corte Plasma  ot 4342 -4344 ,Fabricación Corte Plasma  ot 4342 -4344 </t>
+  </si>
+  <si>
+    <t>1215506781740443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materiales Corte Plasma  ot 4347,Fabricación Corte Plasma  ot 4342 -4344 </t>
+  </si>
+  <si>
+    <t>1215506781740460</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Corte Plasma  ot 4342 -4344 </t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  ot 4347,Recepcion Materiales corte plasma OT 4347</t>
+  </si>
+  <si>
+    <t>1215506819661452</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  ot 4347</t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo ot 4347,Generacion OC Fabricación Externa ot 4347</t>
+  </si>
+  <si>
+    <t>1215506819661464</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo ot 4347,Fabricación Externa  ot 4347</t>
+  </si>
+  <si>
+    <t>1215506639064735</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo ot 4347</t>
+  </si>
+  <si>
+    <t>Fabricación Externa  ot 4347,Control de calidad fabricación externa  ot 4347,Recepcion fabricación externa  OT 4347</t>
+  </si>
+  <si>
+    <t>1215506639064752</t>
+  </si>
+  <si>
+    <t>Control de calidad fabricación externa  ot 4347</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1215506639064764</t>
+  </si>
+  <si>
+    <t>Mecanizado  ot 4347</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado ot 4342 -4344,Fabricación Mecanizado ot 4342 -4344</t>
+  </si>
+  <si>
+    <t>1215506639065883</t>
+  </si>
+  <si>
+    <t>Mecanizado  ot 4347,Fabricación Mecanizado ot 4342 -4344</t>
+  </si>
+  <si>
+    <t>1215506639065900</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado ot 4342 -4344</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado OT 4347,Mecanizado  ot 4347</t>
+  </si>
+  <si>
+    <t>1215506984807216</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1215506984807228</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4349- CODO 90° Ø1600MM</t>
+  </si>
+  <si>
+    <t>1215506639092978</t>
+  </si>
+  <si>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>Planos preliminar,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
+  </si>
+  <si>
+    <t>1215506639092995</t>
+  </si>
+  <si>
+    <t>OT 4349- CODO 90° Ø1600MM</t>
+  </si>
+  <si>
+    <t>OT 4349- CODO 90° Ø1600MM,Planos preliminar</t>
+  </si>
+  <si>
+    <t>1215504785833010</t>
+  </si>
+  <si>
+    <t>OT 4350 - CODO 135° Ø1600MM</t>
+  </si>
+  <si>
+    <t>1215504785833011</t>
+  </si>
+  <si>
+    <t>OT 4351 - DUCTO Ø1600MM L:1800MM</t>
+  </si>
+  <si>
+    <t>1215506992781082</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>1215506992781099</t>
+  </si>
+  <si>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1215506819701309</t>
+  </si>
+  <si>
+    <t>OT 4349- CODO 90° Ø1600MM,Planos definitivos</t>
+  </si>
+  <si>
+    <t>1215504785833012</t>
+  </si>
+  <si>
+    <t>1215504785833013</t>
+  </si>
+  <si>
+    <t>1215506819701527</t>
+  </si>
+  <si>
+    <t>Propuesta Corte plasma  ot 4347,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Propuesta Mecanizado ot 4347,Propuesta Fabricación externa ot 4347 ,propuesta Corte Laser ot 4347,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
+  </si>
+  <si>
+    <t>1215506781840190</t>
+  </si>
+  <si>
+    <t>1215506781840207</t>
+  </si>
+  <si>
+    <t>1215504785833014</t>
+  </si>
+  <si>
+    <t>1215504785833017</t>
+  </si>
+  <si>
+    <t>1215506781849603</t>
+  </si>
+  <si>
+    <t>check pruebas FAT OT 4347</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>1215506781849615</t>
+  </si>
+  <si>
+    <t>check pruebas FAT OT 4347,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
+  </si>
+  <si>
+    <t>1215504785833018</t>
+  </si>
+  <si>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPO</t>
+  </si>
+  <si>
+    <t>1215506639141999</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser OT 4347,control de calidad corte laser  OT 4347</t>
+  </si>
+  <si>
+    <t>1215506639142011</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser OT 4347</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t>Bodega:,control de calidad corte laser  OT 4347</t>
+  </si>
+  <si>
+    <t>1215506984940147</t>
+  </si>
+  <si>
+    <t>control de calidad corte laser  OT 4347</t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma OT 4347,Recepcion materiales corte laser OT 4347</t>
+  </si>
+  <si>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Bodega:,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
+  </si>
+  <si>
+    <t>1215506984940169</t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma OT 4347</t>
+  </si>
+  <si>
+    <t>control de calidad corte laser  OT 4347,Control de calidad Corte plasma OT 4347</t>
+  </si>
+  <si>
+    <t>1215506819763590</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma OT 4347</t>
+  </si>
+  <si>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
+  </si>
+  <si>
+    <t>1215506819763607</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado OT 4347</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado OT 4347</t>
+  </si>
+  <si>
+    <t>1215506781913601</t>
+  </si>
+  <si>
+    <t>1215506992907639</t>
+  </si>
+  <si>
+    <t>Caldereria:</t>
+  </si>
+  <si>
+    <t>OT 4347 Armado,OT 4347 Control de calidad Armado,OT 4347 Preparación Materiales</t>
+  </si>
+  <si>
+    <t>1215506992907651</t>
+  </si>
+  <si>
+    <t>OT 4347 Preparación Materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t>1215506819773770</t>
+  </si>
+  <si>
+    <t>control de calidad corte laser  OT 4347,Control de calidad Mecanizado OT 4347,Control de calidad Corte plasma OT 4347</t>
+  </si>
+  <si>
+    <t>OT 4347 Preparación Materiales,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
+  </si>
+  <si>
+    <t>1215506819773797</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma OT 4347,Control de calidad Mecanizado OT 4347,control de calidad corte laser  OT 4347</t>
+  </si>
+  <si>
+    <t>1215506984972272</t>
+  </si>
+  <si>
+    <t>OT 4347 Armado</t>
+  </si>
+  <si>
+    <t>1215506984982888</t>
+  </si>
+  <si>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,check planos</t>
+  </si>
+  <si>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347 Armado</t>
+  </si>
+  <si>
+    <t>1215506984982910</t>
+  </si>
+  <si>
+    <t>1215506984991511</t>
+  </si>
+  <si>
+    <t>OT 4347 Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1215506819777596</t>
+  </si>
+  <si>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347 Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1215506819777618</t>
+  </si>
+  <si>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347 Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1215506929522878</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete OT 4347,Recepcion Alabe OT 4347,Recepcion motor OT 4347</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
+    <t>1215506929522890</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete OT 4347</t>
+  </si>
+  <si>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Bodega:</t>
+  </si>
+  <si>
+    <t>1215506992958412</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe OT 4347</t>
+  </si>
+  <si>
+    <t>1215506992960641</t>
+  </si>
+  <si>
+    <t>Recepcion motor OT 4347</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215506819635564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tableros ot 4348  ,fabricación tableros   ot 4343 </t>
-  </si>
-  <si>
-    <t>1215506781705104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fabricación tableros   ot 4343 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tableros ot 4348  ,Recepcion Tableros OT 4348  </t>
-  </si>
-  <si>
-    <t>1215506781705121</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC materiales corte Laser ot 4342 -4344,Fabricacion Corte Laser ot 4342 -4344 </t>
-  </si>
-  <si>
-    <t>1215506781722628</t>
-  </si>
-  <si>
-    <t>Generación OC materiales corte Laser ot 4342 -4344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Materiales corte Laser ot 4347,Fabricacion Corte Laser ot 4342 -4344 </t>
-  </si>
-  <si>
-    <t>1215506819659775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricacion Corte Laser ot 4342 -4344 </t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser OT 4347,Materiales corte Laser ot 4347</t>
-  </si>
-  <si>
-    <t>1215506819659795</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  ot 4347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC Corte Plasma  ot 4342 -4344 ,Fabricación Corte Plasma  ot 4342 -4344 </t>
-  </si>
-  <si>
-    <t>1215506781740443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Materiales Corte Plasma  ot 4347,Fabricación Corte Plasma  ot 4342 -4344 </t>
-  </si>
-  <si>
-    <t>1215506781740460</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Corte Plasma  ot 4342 -4344 </t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  ot 4347,Recepcion Materiales corte plasma OT 4347</t>
-  </si>
-  <si>
-    <t>1215506819661452</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  ot 4347</t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo ot 4347,Generacion OC Fabricación Externa ot 4347</t>
-  </si>
-  <si>
-    <t>1215506819661464</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo ot 4347,Fabricación Externa  ot 4347</t>
-  </si>
-  <si>
-    <t>1215506639064735</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo ot 4347</t>
-  </si>
-  <si>
-    <t>Fabricación Externa  ot 4347,Control de calidad fabricación externa  ot 4347,Recepcion fabricación externa  OT 4347</t>
-  </si>
-  <si>
-    <t>1215506639064752</t>
-  </si>
-  <si>
-    <t>Control de calidad fabricación externa  ot 4347</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1215506639064764</t>
-  </si>
-  <si>
-    <t>Mecanizado  ot 4347</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado ot 4342 -4344,Fabricación Mecanizado ot 4342 -4344</t>
-  </si>
-  <si>
-    <t>1215506639065883</t>
-  </si>
-  <si>
-    <t>Mecanizado  ot 4347,Fabricación Mecanizado ot 4342 -4344</t>
-  </si>
-  <si>
-    <t>1215506639065900</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado ot 4342 -4344</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado OT 4347,Mecanizado  ot 4347</t>
-  </si>
-  <si>
-    <t>1215506984807216</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1215506984807228</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4349- CODO 90° Ø1600MM</t>
-  </si>
-  <si>
-    <t>Alta</t>
-  </si>
-  <si>
-    <t>1215506639092978</t>
-  </si>
-  <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Planos preliminar,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
-  </si>
-  <si>
-    <t>1215506639092995</t>
-  </si>
-  <si>
-    <t>OT 4349- CODO 90° Ø1600MM</t>
-  </si>
-  <si>
-    <t>OT 4349- CODO 90° Ø1600MM,Planos preliminar</t>
-  </si>
-  <si>
-    <t>1215504785833010</t>
-  </si>
-  <si>
-    <t>OT 4350 - CODO 135° Ø1600MM</t>
-  </si>
-  <si>
-    <t>1215504785833011</t>
-  </si>
-  <si>
-    <t>OT 4351 - DUCTO Ø1600MM L:1800MM</t>
-  </si>
-  <si>
-    <t>1215506992781082</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>1215506992781099</t>
-  </si>
-  <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1215506819701309</t>
-  </si>
-  <si>
-    <t>OT 4349- CODO 90° Ø1600MM,Planos definitivos</t>
-  </si>
-  <si>
-    <t>1215504785833012</t>
-  </si>
-  <si>
-    <t>1215504785833013</t>
-  </si>
-  <si>
-    <t>1215506819701527</t>
-  </si>
-  <si>
-    <t>Propuesta Corte plasma  ot 4347,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Propuesta Mecanizado ot 4347,Propuesta Fabricación externa ot 4347 ,propuesta Corte Laser ot 4347,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
-  </si>
-  <si>
-    <t>1215506781840190</t>
-  </si>
-  <si>
-    <t>1215506781840207</t>
-  </si>
-  <si>
-    <t>1215504785833014</t>
-  </si>
-  <si>
-    <t>1215504785833017</t>
-  </si>
-  <si>
-    <t>1215506781849603</t>
-  </si>
-  <si>
-    <t>check pruebas FAT OT 4347</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>1215506781849615</t>
-  </si>
-  <si>
-    <t>check pruebas FAT OT 4347,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
-  </si>
-  <si>
-    <t>1215504785833018</t>
-  </si>
-  <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPO</t>
-  </si>
-  <si>
-    <t>1215506639141999</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser OT 4347,control de calidad corte laser  OT 4347</t>
-  </si>
-  <si>
-    <t>1215506639142011</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser OT 4347</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t>Bodega:,control de calidad corte laser  OT 4347</t>
-  </si>
-  <si>
-    <t>1215506984940147</t>
-  </si>
-  <si>
-    <t>control de calidad corte laser  OT 4347</t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma OT 4347,Recepcion materiales corte laser OT 4347</t>
-  </si>
-  <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Bodega:,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
-  </si>
-  <si>
-    <t>1215506984940169</t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma OT 4347</t>
-  </si>
-  <si>
-    <t>control de calidad corte laser  OT 4347,Control de calidad Corte plasma OT 4347</t>
-  </si>
-  <si>
-    <t>1215506819763590</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma OT 4347</t>
-  </si>
-  <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
-  </si>
-  <si>
-    <t>1215506819763607</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado OT 4347</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado OT 4347</t>
-  </si>
-  <si>
-    <t>1215506781913601</t>
-  </si>
-  <si>
-    <t>1215506992907639</t>
-  </si>
-  <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>OT 4347 Armado,OT 4347 Control de calidad Armado,OT 4347 Preparación Materiales</t>
-  </si>
-  <si>
-    <t>1215506992907651</t>
-  </si>
-  <si>
-    <t>OT 4347 Preparación Materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t>1215506819773770</t>
-  </si>
-  <si>
-    <t>control de calidad corte laser  OT 4347,Control de calidad Mecanizado OT 4347,Control de calidad Corte plasma OT 4347</t>
-  </si>
-  <si>
-    <t>OT 4347 Preparación Materiales,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
-  </si>
-  <si>
-    <t>1215506819773797</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma OT 4347,Control de calidad Mecanizado OT 4347,control de calidad corte laser  OT 4347</t>
-  </si>
-  <si>
-    <t>1215506984972272</t>
-  </si>
-  <si>
-    <t>OT 4347 Armado</t>
-  </si>
-  <si>
-    <t>1215506984982888</t>
-  </si>
-  <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,check planos</t>
-  </si>
-  <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347 Armado</t>
-  </si>
-  <si>
-    <t>1215506984982910</t>
-  </si>
-  <si>
-    <t>1215506984991511</t>
-  </si>
-  <si>
-    <t>OT 4347 Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1215506819777596</t>
-  </si>
-  <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347 Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1215506819777618</t>
-  </si>
-  <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347 Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1215506929522878</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete OT 4347,Recepcion Alabe OT 4347,Recepcion motor OT 4347</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1215506929522890</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete OT 4347</t>
-  </si>
-  <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,Bodega:</t>
-  </si>
-  <si>
-    <t>1215506992958412</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe OT 4347</t>
-  </si>
-  <si>
-    <t>1215506992960641</t>
-  </si>
-  <si>
-    <t>Recepcion motor OT 4347</t>
   </si>
   <si>
     <t>1215506992960663</t>
@@ -3556,7 +3556,7 @@
         <v>46217.69797177083</v>
       </c>
       <c r="D32" s="5">
-        <v>46218.18782881944</v>
+        <v>46226.182989305555</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>121</v>
@@ -3600,7 +3600,7 @@
       <c r="R32" s="5">
         <v>46225</v>
       </c>
-      <c r="S32" s="12" t="s">
+      <c r="S32" s="11" t="s">
         <v>125</v>
       </c>
       <c r="T32" s="6">
@@ -4594,7 +4594,7 @@
         <v>46191</v>
       </c>
       <c r="S49" s="11" t="s">
-        <v>179</v>
+        <v>125</v>
       </c>
       <c r="T49" s="9">
         <v>1</v>
@@ -4605,7 +4605,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B50" s="5">
         <v>46181.60908915509</v>
@@ -4617,16 +4617,16 @@
         <v>46190.70821390046</v>
       </c>
       <c r="E50" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G50" s="6" t="s">
+      <c r="H50" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I50" s="5">
         <v>46174</v>
@@ -4650,7 +4650,7 @@
         <v>77</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4660,7 +4660,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B51" s="8">
         <v>46181.60909384259</v>
@@ -4672,16 +4672,16 @@
         <v>46190.7082228125</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="H51" s="9" t="s">
         <v>182</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>183</v>
       </c>
       <c r="I51" s="8">
         <v>46174</v>
@@ -4705,7 +4705,7 @@
         <v>77</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4715,7 +4715,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B52" s="5">
         <v>46181.61221741898</v>
@@ -4727,16 +4727,16 @@
         <v>46190.708227337964</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I52" s="5">
         <v>46174</v>
@@ -4760,7 +4760,7 @@
         <v>77</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4770,7 +4770,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B53" s="8">
         <v>46181.612357199076</v>
@@ -4782,16 +4782,16 @@
         <v>46190.708233321755</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="H53" s="9" t="s">
         <v>182</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>183</v>
       </c>
       <c r="I53" s="8">
         <v>46174</v>
@@ -4815,7 +4815,7 @@
         <v>77</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -4825,7 +4825,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B54" s="5">
         <v>46181.609098182875</v>
@@ -4837,7 +4837,7 @@
         <v>46197.71584820602</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
@@ -4890,7 +4890,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B55" s="8">
         <v>46181.60910252314</v>
@@ -4902,16 +4902,16 @@
         <v>46191.54270819444</v>
       </c>
       <c r="E55" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G55" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="F55" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G55" s="9" t="s">
+      <c r="H55" s="9" t="s">
         <v>182</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>183</v>
       </c>
       <c r="I55" s="8">
         <v>46227</v>
@@ -4929,13 +4929,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4945,7 +4945,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B56" s="5">
         <v>46181.609107951386</v>
@@ -4957,16 +4957,16 @@
         <v>46191.54271703704</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I56" s="5">
         <v>46227</v>
@@ -4984,13 +4984,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5000,7 +5000,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B57" s="8">
         <v>46181.61393570602</v>
@@ -5012,16 +5012,16 @@
         <v>46190.70842170139</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="H57" s="9" t="s">
         <v>182</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>183</v>
       </c>
       <c r="I57" s="8">
         <v>46227</v>
@@ -5039,13 +5039,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5055,7 +5055,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B58" s="5">
         <v>46181.61396929398</v>
@@ -5067,16 +5067,16 @@
         <v>46190.708426550926</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I58" s="5">
         <v>46227</v>
@@ -5094,13 +5094,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5110,7 +5110,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B59" s="8">
         <v>46181.60911329861</v>
@@ -5128,10 +5128,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="H59" s="9" t="s">
         <v>182</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>183</v>
       </c>
       <c r="I59" s="8">
         <v>46247</v>
@@ -5155,7 +5155,7 @@
         <v>178</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q59" s="8">
         <v>46247</v>
@@ -5175,7 +5175,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B60" s="5">
         <v>46181.60912350695</v>
@@ -5187,16 +5187,16 @@
         <v>46191.54536050926</v>
       </c>
       <c r="E60" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="F60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G60" s="6" t="s">
+      <c r="H60" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I60" s="6"/>
       <c r="J60" s="5">
@@ -5215,7 +5215,7 @@
         <v>95</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>95</v>
@@ -5228,7 +5228,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B61" s="8">
         <v>46181.60912782408</v>
@@ -5240,16 +5240,16 @@
         <v>46191.54537386574</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="H61" s="9" t="s">
         <v>182</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>183</v>
       </c>
       <c r="I61" s="9"/>
       <c r="J61" s="8">
@@ -5268,7 +5268,7 @@
         <v>95</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>95</v>
@@ -5281,7 +5281,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B62" s="5">
         <v>46181.614119606485</v>
@@ -5293,16 +5293,16 @@
         <v>46190.721725358795</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="I62" s="6"/>
       <c r="J62" s="5">
@@ -5321,7 +5321,7 @@
         <v>95</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5334,7 +5334,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B63" s="8">
         <v>46181.61419627315</v>
@@ -5346,16 +5346,16 @@
         <v>46190.7217299537</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="H63" s="9" t="s">
         <v>182</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>183</v>
       </c>
       <c r="I63" s="9"/>
       <c r="J63" s="8">
@@ -5374,7 +5374,7 @@
         <v>95</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5387,7 +5387,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B64" s="5">
         <v>46181.60913207176</v>
@@ -5397,16 +5397,16 @@
         <v>46212.622826203704</v>
       </c>
       <c r="E64" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G64" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="F64" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G64" s="6" t="s">
+      <c r="H64" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I64" s="5">
         <v>46322</v>
@@ -5427,7 +5427,7 @@
         <v>172</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>26</v>
@@ -5450,7 +5450,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B65" s="8">
         <v>46181.609135833336</v>
@@ -5460,16 +5460,16 @@
         <v>46182.63311847222</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="H65" s="9" t="s">
         <v>208</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>209</v>
       </c>
       <c r="I65" s="8">
         <v>46322</v>
@@ -5487,13 +5487,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5503,7 +5503,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B66" s="5">
         <v>46181.614311909725</v>
@@ -5513,16 +5513,16 @@
         <v>46182.63311923611</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I66" s="5">
         <v>46322</v>
@@ -5540,13 +5540,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5556,7 +5556,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B67" s="8">
         <v>46181.60918671296</v>
@@ -5568,7 +5568,7 @@
         <v>46216.64129429398</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>25</v>
@@ -5592,7 +5592,7 @@
         <v>26</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>26</v>
@@ -5609,7 +5609,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B68" s="5">
         <v>46181.609196087964</v>
@@ -5621,16 +5621,16 @@
         <v>46213.56938424769</v>
       </c>
       <c r="E68" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G68" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="F68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G68" s="6" t="s">
+      <c r="H68" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I68" s="5">
         <v>46252</v>
@@ -5648,13 +5648,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>139</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q68" s="5">
         <v>46252</v>
@@ -5674,7 +5674,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B69" s="8">
         <v>46181.609201921296</v>
@@ -5686,7 +5686,7 @@
         <v>46216.71548459491</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
@@ -5713,13 +5713,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O69" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="P69" s="9" t="s">
         <v>224</v>
-      </c>
-      <c r="P69" s="9" t="s">
-        <v>225</v>
       </c>
       <c r="Q69" s="8">
         <v>46254</v>
@@ -5739,7 +5739,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B70" s="5">
         <v>46181.60920746528</v>
@@ -5751,16 +5751,16 @@
         <v>46213.569400231485</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I70" s="5">
         <v>46252</v>
@@ -5778,13 +5778,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>147</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q70" s="5">
         <v>46252</v>
@@ -5804,7 +5804,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B71" s="8">
         <v>46181.609212870375</v>
@@ -5816,7 +5816,7 @@
         <v>46216.715484733795</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
@@ -5843,13 +5843,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q71" s="8">
         <v>46254</v>
@@ -5869,7 +5869,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B72" s="5">
         <v>46181.60921715278</v>
@@ -5881,16 +5881,16 @@
         <v>46213.569419479165</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I72" s="5">
         <v>46252</v>
@@ -5908,13 +5908,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>169</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="Q72" s="5">
         <v>46252</v>
@@ -5934,7 +5934,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B73" s="8">
         <v>46181.60922180556</v>
@@ -5946,7 +5946,7 @@
         <v>46216.71548493055</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
@@ -5973,13 +5973,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q73" s="8">
         <v>46254</v>
@@ -5999,7 +5999,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B74" s="5">
         <v>46181.60922590278</v>
@@ -6009,7 +6009,7 @@
         <v>46225.80634167824</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>25</v>
@@ -6033,7 +6033,7 @@
         <v>26</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>26</v>
@@ -6046,7 +6046,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B75" s="8">
         <v>46181.60922940972</v>
@@ -6058,16 +6058,16 @@
         <v>46225.86188380787</v>
       </c>
       <c r="E75" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="F75" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G75" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="F75" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G75" s="9" t="s">
+      <c r="H75" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="I75" s="8">
         <v>46258</v>
@@ -6085,13 +6085,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Q75" s="8">
         <v>46258</v>
@@ -6111,7 +6111,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B76" s="5">
         <v>46181.60923553241</v>
@@ -6123,16 +6123,16 @@
         <v>46225.8062046875</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>241</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>242</v>
       </c>
       <c r="I76" s="5">
         <v>46258</v>
@@ -6150,13 +6150,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O76" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="P76" s="6" t="s">
         <v>245</v>
-      </c>
-      <c r="P76" s="6" t="s">
-        <v>246</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6166,7 +6166,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B77" s="8">
         <v>46181.609241805556</v>
@@ -6178,16 +6178,16 @@
         <v>46225.806214282406</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="H77" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="I77" s="8">
         <v>46258</v>
@@ -6205,13 +6205,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
@@ -6221,7 +6221,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B78" s="5">
         <v>46181.609247002314</v>
@@ -6233,16 +6233,16 @@
         <v>46225.80634494213</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>241</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>242</v>
       </c>
       <c r="I78" s="5">
         <v>46267</v>
@@ -6260,13 +6260,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Q78" s="5">
         <v>46267</v>
@@ -6286,7 +6286,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B79" s="8">
         <v>46181.60925648148</v>
@@ -6298,16 +6298,16 @@
         <v>46225.806309120366</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="H79" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="I79" s="8">
         <v>46267</v>
@@ -6325,13 +6325,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O79" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="P79" s="9" t="s">
         <v>252</v>
-      </c>
-      <c r="P79" s="9" t="s">
-        <v>253</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6341,7 +6341,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B80" s="5">
         <v>46181.609262199076</v>
@@ -6353,16 +6353,16 @@
         <v>46225.806319490744</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>241</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>242</v>
       </c>
       <c r="I80" s="5">
         <v>46267</v>
@@ -6380,13 +6380,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O80" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="P80" s="6" t="s">
         <v>252</v>
-      </c>
-      <c r="P80" s="6" t="s">
-        <v>253</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6396,7 +6396,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B81" s="8">
         <v>46181.60926783565</v>
@@ -6406,7 +6406,7 @@
         <v>46225.807607118055</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
@@ -6433,13 +6433,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Q81" s="8">
         <v>46289</v>
@@ -6459,7 +6459,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B82" s="5">
         <v>46181.60927226851</v>
@@ -6469,7 +6469,7 @@
         <v>46225.80631451389</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6496,13 +6496,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6512,7 +6512,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B83" s="8">
         <v>46181.60927799769</v>
@@ -6522,7 +6522,7 @@
         <v>46225.806324097226</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
@@ -6549,13 +6549,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6565,7 +6565,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B84" s="5">
         <v>46181.60928361111</v>
@@ -6575,7 +6575,7 @@
         <v>46213.56805377315</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>25</v>
@@ -6599,7 +6599,7 @@
         <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6609,12 +6609,12 @@
       <c r="S84" s="6"/>
       <c r="T84" s="6"/>
       <c r="U84" s="12" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B85" s="8">
         <v>46181.609286990744</v>
@@ -6626,16 +6626,16 @@
         <v>46213.56773226852</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="H85" s="9" t="s">
         <v>219</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>220</v>
       </c>
       <c r="I85" s="8">
         <v>46182</v>
@@ -6653,13 +6653,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Q85" s="8">
         <v>46182</v>
@@ -6668,7 +6668,7 @@
         <v>46183</v>
       </c>
       <c r="S85" s="11" t="s">
-        <v>179</v>
+        <v>125</v>
       </c>
       <c r="T85" s="9">
         <v>1</v>
@@ -6679,7 +6679,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B86" s="5">
         <v>46181.609292974535</v>
@@ -6691,16 +6691,16 @@
         <v>46213.56774653935</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I86" s="5">
         <v>46290</v>
@@ -6718,13 +6718,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Q86" s="5">
         <v>46290</v>
@@ -6744,7 +6744,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B87" s="8">
         <v>46181.60929881944</v>
@@ -6756,16 +6756,16 @@
         <v>46220.18663762731</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="H87" s="9" t="s">
         <v>219</v>
-      </c>
-      <c r="H87" s="9" t="s">
-        <v>220</v>
       </c>
       <c r="I87" s="8">
         <v>46226</v>
@@ -6783,13 +6783,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Q87" s="8">
         <v>46226</v>
@@ -6798,7 +6798,7 @@
         <v>46227</v>
       </c>
       <c r="S87" s="12" t="s">
-        <v>125</v>
+        <v>270</v>
       </c>
       <c r="T87" s="9">
         <v>1</v>
@@ -6825,10 +6825,10 @@
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="I88" s="5">
         <v>46293</v>
@@ -6846,7 +6846,7 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>157</v>
@@ -6867,7 +6867,7 @@
         <v>0</v>
       </c>
       <c r="U88" s="12" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
@@ -6888,10 +6888,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="H89" s="9" t="s">
         <v>219</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>220</v>
       </c>
       <c r="I89" s="8">
         <v>46226</v>
@@ -6909,7 +6909,7 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O89" s="9" t="s">
         <v>129</v>
@@ -6924,13 +6924,13 @@
         <v>46227</v>
       </c>
       <c r="S89" s="12" t="s">
-        <v>125</v>
+        <v>270</v>
       </c>
       <c r="T89" s="9">
         <v>0</v>
       </c>
       <c r="U89" s="12" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
@@ -7040,7 +7040,7 @@
         <v>0</v>
       </c>
       <c r="U91" s="12" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
@@ -7055,7 +7055,7 @@
         <v>46223.565613506944</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7108,7 +7108,7 @@
         <v>46223.565612962964</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -7138,7 +7138,7 @@
         <v>279</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P93" s="9" t="s">
         <v>284</v>
@@ -7193,7 +7193,7 @@
         <v>276</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>276</v>
@@ -7228,7 +7228,7 @@
         <v>46223.566525462964</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -7283,7 +7283,7 @@
         <v>46223.56652129629</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7368,7 +7368,7 @@
         <v>276</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P97" s="9" t="s">
         <v>276</v>
@@ -7403,7 +7403,7 @@
         <v>46223.56665253472</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7458,7 +7458,7 @@
         <v>46223.56667947916</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7541,7 +7541,7 @@
         <v>276</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>276</v>
@@ -7574,7 +7574,7 @@
         <v>46223.566807800926</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7627,7 +7627,7 @@
         <v>46223.56680710649</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7710,7 +7710,7 @@
         <v>276</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P103" s="9" t="s">
         <v>276</v>
@@ -7743,7 +7743,7 @@
         <v>46223.566960972224</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7773,7 +7773,7 @@
         <v>307</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P104" s="6" t="s">
         <v>309</v>
@@ -7796,7 +7796,7 @@
         <v>46223.56696034722</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -7826,10 +7826,10 @@
         <v>307</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -7879,7 +7879,7 @@
         <v>276</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>313</v>
@@ -7912,7 +7912,7 @@
         <v>46223.56705920139</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -7942,7 +7942,7 @@
         <v>312</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P107" s="9" t="s">
         <v>315</v>
@@ -7965,7 +7965,7 @@
         <v>46223.56705859954</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -7995,7 +7995,7 @@
         <v>312</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>26</v>
@@ -8128,7 +8128,7 @@
         <v>46182.641845254635</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8158,7 +8158,7 @@
         <v>321</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P111" s="9" t="s">
         <v>326</v>
@@ -8181,7 +8181,7 @@
         <v>46182.64184081019</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8211,10 +8211,10 @@
         <v>321</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8340,7 +8340,7 @@
         <v>46218.812014641204</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
@@ -8373,7 +8373,7 @@
         <v>26</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q115" s="9"/>
       <c r="R115" s="9"/>
@@ -8393,7 +8393,7 @@
         <v>46216.715609837964</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8426,7 +8426,7 @@
         <v>26</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8479,7 +8479,7 @@
         <v>26</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8529,7 +8529,7 @@
         <v>318</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>318</v>
@@ -8562,7 +8562,7 @@
         <v>46223.56727827546</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
@@ -8592,7 +8592,7 @@
         <v>335</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P119" s="9" t="s">
         <v>337</v>
@@ -8615,7 +8615,7 @@
         <v>46223.567277685186</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8645,10 +8645,10 @@
         <v>335</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8774,7 +8774,7 @@
         <v>46223.56727590278</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
@@ -8804,10 +8804,10 @@
         <v>335</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q123" s="9"/>
       <c r="R123" s="9"/>
@@ -8827,7 +8827,7 @@
         <v>46223.56727532407</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -8857,10 +8857,10 @@
         <v>335</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8880,7 +8880,7 @@
         <v>46223.56727472223</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -8913,7 +8913,7 @@
         <v>333</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -8939,10 +8939,10 @@
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="H126" s="6" t="s">
         <v>241</v>
-      </c>
-      <c r="H126" s="6" t="s">
-        <v>242</v>
       </c>
       <c r="I126" s="5">
         <v>46328</v>
@@ -8963,7 +8963,7 @@
         <v>318</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>318</v>
@@ -8996,16 +8996,16 @@
         <v>46182.82945300926</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="H127" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="H127" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="I127" s="8">
         <v>46328</v>
@@ -9026,7 +9026,7 @@
         <v>345</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P127" s="9" t="s">
         <v>347</v>
@@ -9049,16 +9049,16 @@
         <v>46182.829453784725</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="H128" s="6" t="s">
         <v>241</v>
-      </c>
-      <c r="H128" s="6" t="s">
-        <v>242</v>
       </c>
       <c r="I128" s="5">
         <v>46328</v>
@@ -9079,10 +9079,10 @@
         <v>345</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9108,10 +9108,10 @@
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="H129" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="H129" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="I129" s="8">
         <v>46328</v>
@@ -9161,10 +9161,10 @@
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="H130" s="6" t="s">
         <v>241</v>
-      </c>
-      <c r="H130" s="6" t="s">
-        <v>242</v>
       </c>
       <c r="I130" s="5">
         <v>46328</v>
@@ -9208,16 +9208,16 @@
         <v>46182.8294564699</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="H131" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="H131" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="I131" s="8">
         <v>46328</v>
@@ -9238,10 +9238,10 @@
         <v>345</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
@@ -9261,16 +9261,16 @@
         <v>46182.82945721065</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="H132" s="6" t="s">
         <v>241</v>
-      </c>
-      <c r="H132" s="6" t="s">
-        <v>242</v>
       </c>
       <c r="I132" s="5">
         <v>46328</v>
@@ -9291,10 +9291,10 @@
         <v>345</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9314,16 +9314,16 @@
         <v>46182.82945796296</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="H133" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="H133" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="I133" s="8">
         <v>46328</v>
@@ -9344,10 +9344,10 @@
         <v>345</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9373,10 +9373,10 @@
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="H134" s="6" t="s">
         <v>241</v>
-      </c>
-      <c r="H134" s="6" t="s">
-        <v>242</v>
       </c>
       <c r="I134" s="5">
         <v>46329</v>
@@ -9397,7 +9397,7 @@
         <v>318</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P134" s="6" t="s">
         <v>356</v>
@@ -9430,16 +9430,16 @@
         <v>46182.8294527199</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="H135" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="H135" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="I135" s="8">
         <v>46329</v>
@@ -9460,7 +9460,7 @@
         <v>355</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P135" s="9" t="s">
         <v>355</v>
@@ -9483,16 +9483,16 @@
         <v>46182.829451909725</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="H136" s="6" t="s">
         <v>241</v>
-      </c>
-      <c r="H136" s="6" t="s">
-        <v>242</v>
       </c>
       <c r="I136" s="5">
         <v>46329</v>
@@ -9513,7 +9513,7 @@
         <v>355</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P136" s="6" t="s">
         <v>26</v>
@@ -9542,10 +9542,10 @@
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="H137" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="H137" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="I137" s="8">
         <v>46329</v>
@@ -9595,10 +9595,10 @@
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="H138" s="6" t="s">
         <v>241</v>
-      </c>
-      <c r="H138" s="6" t="s">
-        <v>242</v>
       </c>
       <c r="I138" s="5">
         <v>46329</v>
@@ -9642,16 +9642,16 @@
         <v>46182.82945207176</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="H139" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="H139" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="I139" s="8">
         <v>46329</v>
@@ -9672,7 +9672,7 @@
         <v>355</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="P139" s="9" t="s">
         <v>26</v>
@@ -9695,16 +9695,16 @@
         <v>46182.829452025464</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="H140" s="6" t="s">
         <v>241</v>
-      </c>
-      <c r="H140" s="6" t="s">
-        <v>242</v>
       </c>
       <c r="I140" s="5">
         <v>46329</v>
@@ -9725,7 +9725,7 @@
         <v>355</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P140" s="6" t="s">
         <v>26</v>
@@ -9748,16 +9748,16 @@
         <v>46182.829452418984</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="H141" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="H141" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="I141" s="8">
         <v>46329</v>
@@ -9778,7 +9778,7 @@
         <v>355</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P141" s="9" t="s">
         <v>26</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1720" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1721" uniqueCount="380">
   <si>
     <t>50001559 - FERROVIAL</t>
   </si>
@@ -847,6 +847,9 @@
     <t>OT 4347 Control de calidad Armado</t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
     <t>1215506819777596</t>
   </si>
   <si>
@@ -865,9 +868,6 @@
     <t>Recepcion Rodete OT 4347,Recepcion Alabe OT 4347,Recepcion motor OT 4347</t>
   </si>
   <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
     <t>1215506929522890</t>
   </si>
   <si>
@@ -887,9 +887,6 @@
   </si>
   <si>
     <t>Recepcion motor OT 4347</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1215506992960663</t>
@@ -6004,9 +6001,11 @@
       <c r="B74" s="5">
         <v>46181.60922590278</v>
       </c>
-      <c r="C74" s="6"/>
+      <c r="C74" s="5">
+        <v>46226.72503126157</v>
+      </c>
       <c r="D74" s="5">
-        <v>46225.80634167824</v>
+        <v>46226.725049155095</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>236</v>
@@ -6041,8 +6040,12 @@
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
       <c r="S74" s="6"/>
-      <c r="T74" s="6"/>
-      <c r="U74" s="6"/>
+      <c r="T74" s="6">
+        <v>1</v>
+      </c>
+      <c r="U74" s="10" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
@@ -6401,9 +6404,11 @@
       <c r="B81" s="8">
         <v>46181.60926783565</v>
       </c>
-      <c r="C81" s="9"/>
+      <c r="C81" s="8">
+        <v>46226.72501033565</v>
+      </c>
       <c r="D81" s="8">
-        <v>46225.807607118055</v>
+        <v>46226.725539004634</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>255</v>
@@ -6451,22 +6456,24 @@
         <v>32</v>
       </c>
       <c r="T81" s="9">
-        <v>0</v>
-      </c>
-      <c r="U81" s="11" t="s">
-        <v>58</v>
+        <v>1</v>
+      </c>
+      <c r="U81" s="12" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B82" s="5">
         <v>46181.60927226851</v>
       </c>
-      <c r="C82" s="6"/>
+      <c r="C82" s="5">
+        <v>46226.72551456018</v>
+      </c>
       <c r="D82" s="5">
-        <v>46225.80631451389</v>
+        <v>46226.72551587963</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>180</v>
@@ -6502,7 +6509,7 @@
         <v>251</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6512,14 +6519,16 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B83" s="8">
         <v>46181.60927799769</v>
       </c>
-      <c r="C83" s="9"/>
+      <c r="C83" s="8">
+        <v>46226.72552170139</v>
+      </c>
       <c r="D83" s="8">
-        <v>46225.806324097226</v>
+        <v>46226.72552325232</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>180</v>
@@ -6555,7 +6564,7 @@
         <v>251</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6565,7 +6574,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B84" s="5">
         <v>46181.60928361111</v>
@@ -6599,7 +6608,7 @@
         <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6609,7 +6618,7 @@
       <c r="S84" s="6"/>
       <c r="T84" s="6"/>
       <c r="U84" s="12" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -6753,7 +6762,7 @@
         <v>46213.56803628472</v>
       </c>
       <c r="D87" s="8">
-        <v>46220.18663762731</v>
+        <v>46228.196411377314</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>269</v>
@@ -6797,8 +6806,8 @@
       <c r="R87" s="8">
         <v>46227</v>
       </c>
-      <c r="S87" s="12" t="s">
-        <v>270</v>
+      <c r="S87" s="11" t="s">
+        <v>125</v>
       </c>
       <c r="T87" s="9">
         <v>1</v>
@@ -6809,7 +6818,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B88" s="5">
         <v>46181.60930480324</v>
@@ -6819,7 +6828,7 @@
         <v>46212.623013958335</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6852,7 +6861,7 @@
         <v>157</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q88" s="5">
         <v>46293</v>
@@ -6867,19 +6876,19 @@
         <v>0</v>
       </c>
       <c r="U88" s="12" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B89" s="8">
         <v>46181.60935271991</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46220.186637569444</v>
+        <v>46228.19641133102</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>61</v>
@@ -6923,19 +6932,19 @@
       <c r="R89" s="8">
         <v>46227</v>
       </c>
-      <c r="S89" s="12" t="s">
-        <v>270</v>
+      <c r="S89" s="11" t="s">
+        <v>125</v>
       </c>
       <c r="T89" s="9">
         <v>0</v>
       </c>
       <c r="U89" s="12" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B90" s="5">
         <v>46181.60936674768</v>
@@ -6945,7 +6954,7 @@
         <v>46213.50490068287</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -6969,7 +6978,7 @@
         <v>26</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -6982,7 +6991,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B91" s="8">
         <v>46181.609371666666</v>
@@ -6992,7 +7001,7 @@
         <v>46225.82172349537</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -7019,13 +7028,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="Q91" s="8">
         <v>46290</v>
@@ -7040,19 +7049,19 @@
         <v>0</v>
       </c>
       <c r="U91" s="12" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B92" s="5">
         <v>46181.609378587964</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46223.565613506944</v>
+        <v>46226.725520844906</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>180</v>
@@ -7082,13 +7091,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7098,14 +7107,14 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B93" s="8">
         <v>46181.61514019676</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46223.565612962964</v>
+        <v>46226.725527256945</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>180</v>
@@ -7135,13 +7144,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="O93" s="9" t="s">
         <v>180</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7151,7 +7160,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B94" s="5">
         <v>46181.609386111115</v>
@@ -7163,7 +7172,7 @@
         <v>46223.56717594907</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7190,13 +7199,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>180</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="Q94" s="5">
         <v>46311</v>
@@ -7216,7 +7225,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B95" s="8">
         <v>46181.60939194444</v>
@@ -7255,13 +7264,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O95" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="P95" s="9" t="s">
         <v>288</v>
-      </c>
-      <c r="P95" s="9" t="s">
-        <v>289</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7271,7 +7280,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B96" s="5">
         <v>46181.61518315972</v>
@@ -7310,10 +7319,10 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>26</v>
@@ -7326,7 +7335,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B97" s="8">
         <v>46181.60939866898</v>
@@ -7338,7 +7347,7 @@
         <v>46225.821835625</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
@@ -7365,13 +7374,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O97" s="9" t="s">
         <v>180</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="Q97" s="8">
         <v>46315</v>
@@ -7391,7 +7400,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B98" s="5">
         <v>46181.60940505787</v>
@@ -7430,13 +7439,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O98" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="P98" s="6" t="s">
         <v>295</v>
-      </c>
-      <c r="P98" s="6" t="s">
-        <v>296</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7446,7 +7455,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B99" s="8">
         <v>46181.61523613426</v>
@@ -7485,10 +7494,10 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P99" s="9" t="s">
         <v>26</v>
@@ -7501,7 +7510,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B100" s="5">
         <v>46181.60941365741</v>
@@ -7511,7 +7520,7 @@
         <v>46223.56716021991</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7538,13 +7547,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>180</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="Q100" s="5">
         <v>46317</v>
@@ -7564,7 +7573,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B101" s="8">
         <v>46181.60941929398</v>
@@ -7601,13 +7610,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O101" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="P101" s="9" t="s">
         <v>302</v>
-      </c>
-      <c r="P101" s="9" t="s">
-        <v>303</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7617,7 +7626,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B102" s="5">
         <v>46181.61528053241</v>
@@ -7654,10 +7663,10 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>26</v>
@@ -7670,7 +7679,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B103" s="8">
         <v>46181.60942706019</v>
@@ -7680,7 +7689,7 @@
         <v>46223.56715939815</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -7707,13 +7716,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O103" s="9" t="s">
         <v>180</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="Q103" s="8">
         <v>46321</v>
@@ -7733,7 +7742,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B104" s="5">
         <v>46181.60943415509</v>
@@ -7770,13 +7779,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>180</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7786,7 +7795,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B105" s="8">
         <v>46181.61532783565</v>
@@ -7823,7 +7832,7 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O105" s="9" t="s">
         <v>180</v>
@@ -7839,7 +7848,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B106" s="5">
         <v>46181.60944410879</v>
@@ -7849,7 +7858,7 @@
         <v>46223.56715854167</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7876,13 +7885,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>180</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Q106" s="5">
         <v>46323</v>
@@ -7902,7 +7911,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B107" s="8">
         <v>46181.60944996528</v>
@@ -7939,13 +7948,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O107" s="9" t="s">
         <v>180</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -7955,7 +7964,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B108" s="5">
         <v>46181.61537143518</v>
@@ -7992,7 +8001,7 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>212</v>
@@ -8008,7 +8017,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B109" s="8">
         <v>46181.60945642361</v>
@@ -8018,7 +8027,7 @@
         <v>46182.634494212965</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>25</v>
@@ -8042,7 +8051,7 @@
         <v>26</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="P109" s="9" t="s">
         <v>26</v>
@@ -8055,7 +8064,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B110" s="5">
         <v>46181.60946096065</v>
@@ -8065,16 +8074,16 @@
         <v>46182.64186350694</v>
       </c>
       <c r="E110" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="F110" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G110" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="F110" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G110" s="6" t="s">
+      <c r="H110" s="6" t="s">
         <v>322</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>323</v>
       </c>
       <c r="I110" s="5">
         <v>46324</v>
@@ -8092,13 +8101,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Q110" s="5">
         <v>46324</v>
@@ -8118,7 +8127,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B111" s="8">
         <v>46181.60946868056</v>
@@ -8134,10 +8143,10 @@
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="H111" s="9" t="s">
         <v>322</v>
-      </c>
-      <c r="H111" s="9" t="s">
-        <v>323</v>
       </c>
       <c r="I111" s="8">
         <v>46324</v>
@@ -8155,13 +8164,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O111" s="9" t="s">
         <v>180</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="Q111" s="9"/>
       <c r="R111" s="9"/>
@@ -8171,14 +8180,14 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B112" s="5">
         <v>46181.609475034726</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46182.64184081019</v>
+        <v>46226.725528553245</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>180</v>
@@ -8187,10 +8196,10 @@
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="H112" s="6" t="s">
         <v>322</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>323</v>
       </c>
       <c r="I112" s="5">
         <v>46324</v>
@@ -8208,7 +8217,7 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>180</v>
@@ -8224,7 +8233,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B113" s="8">
         <v>46181.60947921296</v>
@@ -8240,10 +8249,10 @@
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="H113" s="9" t="s">
         <v>322</v>
-      </c>
-      <c r="H113" s="9" t="s">
-        <v>323</v>
       </c>
       <c r="I113" s="8">
         <v>46324</v>
@@ -8261,7 +8270,7 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O113" s="9" t="s">
         <v>60</v>
@@ -8277,7 +8286,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B114" s="5">
         <v>46181.61605960648</v>
@@ -8293,10 +8302,10 @@
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="H114" s="6" t="s">
         <v>322</v>
-      </c>
-      <c r="H114" s="6" t="s">
-        <v>323</v>
       </c>
       <c r="I114" s="5">
         <v>46324</v>
@@ -8314,7 +8323,7 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>60</v>
@@ -8330,7 +8339,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B115" s="8">
         <v>46181.61617203704</v>
@@ -8346,10 +8355,10 @@
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="H115" s="9" t="s">
         <v>322</v>
-      </c>
-      <c r="H115" s="9" t="s">
-        <v>323</v>
       </c>
       <c r="I115" s="8">
         <v>46324</v>
@@ -8367,7 +8376,7 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O115" s="9" t="s">
         <v>26</v>
@@ -8383,7 +8392,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B116" s="5">
         <v>46181.61620771991</v>
@@ -8399,10 +8408,10 @@
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="H116" s="6" t="s">
         <v>322</v>
-      </c>
-      <c r="H116" s="6" t="s">
-        <v>323</v>
       </c>
       <c r="I116" s="5">
         <v>46324</v>
@@ -8420,7 +8429,7 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O116" s="6" t="s">
         <v>26</v>
@@ -8436,7 +8445,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B117" s="8">
         <v>46181.616245833335</v>
@@ -8446,16 +8455,16 @@
         <v>46218.812044606486</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="H117" s="9" t="s">
         <v>322</v>
-      </c>
-      <c r="H117" s="9" t="s">
-        <v>323</v>
       </c>
       <c r="I117" s="8">
         <v>46324</v>
@@ -8473,7 +8482,7 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O117" s="9" t="s">
         <v>26</v>
@@ -8489,7 +8498,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B118" s="5">
         <v>46181.60948424769</v>
@@ -8499,7 +8508,7 @@
         <v>46223.567324097225</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8526,13 +8535,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>180</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Q118" s="5">
         <v>46325</v>
@@ -8552,7 +8561,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B119" s="8">
         <v>46181.60948969907</v>
@@ -8589,13 +8598,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O119" s="9" t="s">
         <v>180</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8605,7 +8614,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B120" s="5">
         <v>46181.60949538194</v>
@@ -8642,7 +8651,7 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>180</v>
@@ -8658,7 +8667,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B121" s="8">
         <v>46181.609560185185</v>
@@ -8695,7 +8704,7 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O121" s="9" t="s">
         <v>60</v>
@@ -8711,7 +8720,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B122" s="5">
         <v>46181.61659114584</v>
@@ -8748,7 +8757,7 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>60</v>
@@ -8764,7 +8773,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B123" s="8">
         <v>46181.61662431713</v>
@@ -8801,7 +8810,7 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O123" s="9" t="s">
         <v>185</v>
@@ -8817,7 +8826,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B124" s="5">
         <v>46181.61666238426</v>
@@ -8854,7 +8863,7 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>188</v>
@@ -8870,7 +8879,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B125" s="8">
         <v>46181.61670006944</v>
@@ -8907,10 +8916,10 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P125" s="9" t="s">
         <v>190</v>
@@ -8923,7 +8932,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B126" s="5">
         <v>46181.60956560185</v>
@@ -8933,7 +8942,7 @@
         <v>46182.82952324074</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -8960,13 +8969,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>180</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Q126" s="5">
         <v>46328</v>
@@ -8986,7 +8995,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B127" s="8">
         <v>46181.60957188657</v>
@@ -9023,13 +9032,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="O127" s="9" t="s">
         <v>180</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -9039,7 +9048,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B128" s="5">
         <v>46181.609583576384</v>
@@ -9076,7 +9085,7 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="O128" s="6" t="s">
         <v>180</v>
@@ -9092,7 +9101,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B129" s="8">
         <v>46181.60958841435</v>
@@ -9129,7 +9138,7 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="O129" s="9" t="s">
         <v>60</v>
@@ -9145,7 +9154,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B130" s="5">
         <v>46181.616839849536</v>
@@ -9182,7 +9191,7 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="O130" s="6" t="s">
         <v>60</v>
@@ -9198,7 +9207,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B131" s="8">
         <v>46181.61689748843</v>
@@ -9235,7 +9244,7 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="O131" s="9" t="s">
         <v>185</v>
@@ -9251,7 +9260,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B132" s="5">
         <v>46181.616942569446</v>
@@ -9288,7 +9297,7 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="O132" s="6" t="s">
         <v>188</v>
@@ -9304,7 +9313,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B133" s="8">
         <v>46181.6169815162</v>
@@ -9341,7 +9350,7 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="O133" s="9" t="s">
         <v>190</v>
@@ -9357,7 +9366,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B134" s="5">
         <v>46181.609592673616</v>
@@ -9367,7 +9376,7 @@
         <v>46225.823538819444</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9394,13 +9403,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>180</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="Q134" s="5">
         <v>46329</v>
@@ -9420,7 +9429,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B135" s="8">
         <v>46181.60960517361</v>
@@ -9457,13 +9466,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O135" s="9" t="s">
         <v>180</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Q135" s="9"/>
       <c r="R135" s="9"/>
@@ -9473,7 +9482,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B136" s="5">
         <v>46181.609610011576</v>
@@ -9510,7 +9519,7 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O136" s="6" t="s">
         <v>180</v>
@@ -9526,7 +9535,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B137" s="8">
         <v>46181.609613796296</v>
@@ -9563,7 +9572,7 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O137" s="9" t="s">
         <v>60</v>
@@ -9579,7 +9588,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B138" s="5">
         <v>46181.61712142361</v>
@@ -9616,7 +9625,7 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O138" s="6" t="s">
         <v>60</v>
@@ -9632,7 +9641,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B139" s="8">
         <v>46181.61716094907</v>
@@ -9669,7 +9678,7 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O139" s="9" t="s">
         <v>185</v>
@@ -9685,7 +9694,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B140" s="5">
         <v>46181.61719633102</v>
@@ -9722,7 +9731,7 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O140" s="6" t="s">
         <v>188</v>
@@ -9738,7 +9747,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B141" s="8">
         <v>46181.617235451384</v>
@@ -9775,7 +9784,7 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O141" s="9" t="s">
         <v>190</v>
@@ -9791,7 +9800,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B142" s="5">
         <v>46181.60961741898</v>
@@ -9801,7 +9810,7 @@
         <v>46182.63449439815</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>25</v>
@@ -9825,7 +9834,7 @@
         <v>26</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="P142" s="6" t="s">
         <v>26</v>
@@ -9838,7 +9847,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B143" s="8">
         <v>46181.60962174769</v>
@@ -9848,16 +9857,16 @@
         <v>46182.64244836806</v>
       </c>
       <c r="E143" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="F143" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G143" s="9" t="s">
         <v>368</v>
       </c>
-      <c r="F143" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G143" s="9" t="s">
+      <c r="H143" s="9" t="s">
         <v>369</v>
-      </c>
-      <c r="H143" s="9" t="s">
-        <v>370</v>
       </c>
       <c r="I143" s="8">
         <v>46330</v>
@@ -9875,13 +9884,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="Q143" s="8">
         <v>46330</v>
@@ -9901,7 +9910,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B144" s="5">
         <v>46181.60962780092</v>
@@ -9911,7 +9920,7 @@
         <v>46191.67892958333</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -9938,13 +9947,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="Q144" s="5">
         <v>46330</v>
@@ -9964,7 +9973,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B145" s="8">
         <v>46181.60963489584</v>
@@ -9974,7 +9983,7 @@
         <v>46182.63449431713</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>25</v>
@@ -9998,7 +10007,7 @@
         <v>26</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="P145" s="9" t="s">
         <v>26</v>
@@ -10017,7 +10026,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B146" s="5">
         <v>46181.609640208335</v>
@@ -10027,7 +10036,7 @@
         <v>46182.64254377315</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10054,13 +10063,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="Q146" s="5">
         <v>46330</v>
@@ -10080,7 +10089,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B147" s="8">
         <v>46181.609646365745</v>
@@ -10090,7 +10099,7 @@
         <v>46182.64254079861</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
@@ -10117,13 +10126,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Q147" s="8">
         <v>46339</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -8346,7 +8346,7 @@
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46218.812014641204</v>
+        <v>46230.85274487268</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>185</v>
@@ -8452,7 +8452,7 @@
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46218.812044606486</v>
+        <v>46230.85292063658</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>332</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1721" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1721" uniqueCount="381">
   <si>
     <t>50001559 - FERROVIAL</t>
   </si>
@@ -247,6 +247,9 @@
     <t>Ingenieria Servicios ,Coordinacion Entrega con Cliente</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>Tarea sin iniciar</t>
   </si>
   <si>
@@ -805,7 +808,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+    <t xml:space="preserve">OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
   </si>
   <si>
     <t>1215506819773770</t>
@@ -1285,12 +1288,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFe8384f"/>
+        <fgColor rgb="FFeec300"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFeec300"/>
+        <fgColor rgb="FFe8384f"/>
       </patternFill>
     </fill>
   </fills>
@@ -2260,7 +2263,7 @@
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="8">
-        <v>46210.824536712964</v>
+        <v>46231.19592238426</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>53</v>
@@ -2304,19 +2307,19 @@
       <c r="R11" s="8">
         <v>46238</v>
       </c>
-      <c r="S11" s="10" t="s">
-        <v>32</v>
+      <c r="S11" s="11" t="s">
+        <v>58</v>
       </c>
       <c r="T11" s="9">
         <v>0</v>
       </c>
-      <c r="U11" s="11" t="s">
-        <v>58</v>
+      <c r="U11" s="12" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="5">
         <v>46181.608834976854</v>
@@ -2326,7 +2329,7 @@
         <v>46182.62589634259</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
@@ -2356,10 +2359,10 @@
         <v>53</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Q12" s="6"/>
       <c r="R12" s="6"/>
@@ -2369,7 +2372,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B13" s="8">
         <v>46181.61813184028</v>
@@ -2379,7 +2382,7 @@
         <v>46182.625892881944</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>26</v>
@@ -2409,10 +2412,10 @@
         <v>53</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P13" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Q13" s="9"/>
       <c r="R13" s="9"/>
@@ -2422,7 +2425,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B14" s="5">
         <v>46181.60864021991</v>
@@ -2434,7 +2437,7 @@
         <v>46204.903260949075</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>25</v>
@@ -2458,7 +2461,7 @@
         <v>26</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P14" s="6" t="s">
         <v>26</v>
@@ -2475,7 +2478,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B15" s="8">
         <v>46181.60883864583</v>
@@ -2487,7 +2490,7 @@
         <v>46191.67892994213</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>26</v>
@@ -2508,19 +2511,19 @@
         <v>26</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M15" s="9" t="s">
         <v>26</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O15" s="9" t="s">
         <v>38</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q15" s="8">
         <v>46162</v>
@@ -2540,7 +2543,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B16" s="5">
         <v>46181.60884395833</v>
@@ -2552,7 +2555,7 @@
         <v>46191.67892980324</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
@@ -2573,19 +2576,19 @@
         <v>26</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>38</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q16" s="5">
         <v>46162</v>
@@ -2605,7 +2608,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B17" s="8">
         <v>46181.608850046294</v>
@@ -2617,7 +2620,7 @@
         <v>46191.67892980324</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>26</v>
@@ -2644,13 +2647,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O17" s="9" t="s">
         <v>38</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q17" s="8">
         <v>46162</v>
@@ -2670,7 +2673,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B18" s="5">
         <v>46181.60864670139</v>
@@ -2682,7 +2685,7 @@
         <v>46204.88880490741</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>25</v>
@@ -2706,7 +2709,7 @@
         <v>26</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P18" s="6" t="s">
         <v>26</v>
@@ -2723,7 +2726,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B19" s="8">
         <v>46181.608864236114</v>
@@ -2735,7 +2738,7 @@
         <v>46190.88639424769</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
@@ -2762,13 +2765,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q19" s="8">
         <v>46167</v>
@@ -2788,7 +2791,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B20" s="5">
         <v>46181.60886979167</v>
@@ -2800,7 +2803,7 @@
         <v>46190.88638454861</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2827,13 +2830,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q20" s="5">
         <v>46174</v>
@@ -2853,7 +2856,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B21" s="8">
         <v>46181.60887520833</v>
@@ -2865,16 +2868,16 @@
         <v>46223.56543164352</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I21" s="8">
         <v>46174</v>
@@ -2892,13 +2895,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q21" s="8">
         <v>46174</v>
@@ -2918,7 +2921,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B22" s="5">
         <v>46181.60888054398</v>
@@ -2930,16 +2933,16 @@
         <v>46223.56542827546</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I22" s="5">
         <v>46248</v>
@@ -2957,13 +2960,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q22" s="5">
         <v>46248</v>
@@ -2983,7 +2986,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B23" s="8">
         <v>46181.60888559028</v>
@@ -2995,16 +2998,16 @@
         <v>46223.56542460648</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I23" s="8">
         <v>46248</v>
@@ -3022,13 +3025,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q23" s="8">
         <v>46248</v>
@@ -3048,7 +3051,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B24" s="5">
         <v>46181.60888961806</v>
@@ -3060,16 +3063,16 @@
         <v>46223.56542116898</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I24" s="5">
         <v>46248</v>
@@ -3087,13 +3090,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q24" s="5">
         <v>46248</v>
@@ -3113,7 +3116,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B25" s="8">
         <v>46181.6088934375</v>
@@ -3125,16 +3128,16 @@
         <v>46223.56541603009</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I25" s="8">
         <v>46248</v>
@@ -3152,13 +3155,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q25" s="8">
         <v>46248</v>
@@ -3178,7 +3181,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B26" s="5">
         <v>46181.608897638886</v>
@@ -3190,7 +3193,7 @@
         <v>46190.67787061342</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
@@ -3217,13 +3220,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>48</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q26" s="5">
         <v>46168</v>
@@ -3243,7 +3246,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B27" s="8">
         <v>46190.88204489583</v>
@@ -3255,7 +3258,7 @@
         <v>46197.424089050925</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>25</v>
@@ -3296,7 +3299,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B28" s="5">
         <v>46190.88321909722</v>
@@ -3308,16 +3311,16 @@
         <v>46223.56549825231</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I28" s="5">
         <v>46169</v>
@@ -3335,10 +3338,10 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>26</v>
@@ -3361,7 +3364,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B29" s="8">
         <v>46190.88327185185</v>
@@ -3373,16 +3376,16 @@
         <v>46223.565494525465</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I29" s="8">
         <v>46176</v>
@@ -3400,10 +3403,10 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P29" s="9" t="s">
         <v>26</v>
@@ -3426,7 +3429,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B30" s="5">
         <v>46190.88332659722</v>
@@ -3438,16 +3441,16 @@
         <v>46223.56549020833</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I30" s="5">
         <v>46176</v>
@@ -3465,10 +3468,10 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>26</v>
@@ -3491,7 +3494,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B31" s="8">
         <v>46181.608652256946</v>
@@ -3503,7 +3506,7 @@
         <v>46225.6849328588</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>25</v>
@@ -3527,7 +3530,7 @@
         <v>26</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P31" s="9" t="s">
         <v>26</v>
@@ -3544,7 +3547,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B32" s="5">
         <v>46181.60900793981</v>
@@ -3556,16 +3559,16 @@
         <v>46226.182989305555</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I32" s="5">
         <v>46170</v>
@@ -3583,10 +3586,10 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3597,8 +3600,8 @@
       <c r="R32" s="5">
         <v>46225</v>
       </c>
-      <c r="S32" s="11" t="s">
-        <v>125</v>
+      <c r="S32" s="12" t="s">
+        <v>126</v>
       </c>
       <c r="T32" s="6">
         <v>1</v>
@@ -3609,7 +3612,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B33" s="8">
         <v>46181.60901165509</v>
@@ -3621,16 +3624,16 @@
         <v>46195.68592747685</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I33" s="8">
         <v>46170</v>
@@ -3648,13 +3651,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3664,7 +3667,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B34" s="5">
         <v>46181.60901612269</v>
@@ -3676,16 +3679,16 @@
         <v>46217.69795753472</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I34" s="5">
         <v>46177</v>
@@ -3703,13 +3706,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3719,7 +3722,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B35" s="8">
         <v>46181.60902011574</v>
@@ -3731,16 +3734,16 @@
         <v>46205.61719211805</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I35" s="8">
         <v>46252</v>
@@ -3758,13 +3761,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q35" s="8">
         <v>46252</v>
@@ -3784,7 +3787,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B36" s="5">
         <v>46181.60902488426</v>
@@ -3796,16 +3799,16 @@
         <v>46199.57115532407</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I36" s="5">
         <v>46252</v>
@@ -3823,13 +3826,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3839,13 +3842,13 @@
       <c r="T36" s="6">
         <v>0</v>
       </c>
-      <c r="U36" s="11" t="s">
-        <v>58</v>
+      <c r="U36" s="12" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B37" s="8">
         <v>46181.609029803236</v>
@@ -3857,16 +3860,16 @@
         <v>46205.61257221065</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I37" s="8">
         <v>46254</v>
@@ -3884,13 +3887,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3900,13 +3903,13 @@
       <c r="T37" s="9">
         <v>0</v>
       </c>
-      <c r="U37" s="11" t="s">
-        <v>58</v>
+      <c r="U37" s="12" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B38" s="5">
         <v>46181.60903511574</v>
@@ -3918,16 +3921,16 @@
         <v>46199.572352546296</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I38" s="5">
         <v>46252</v>
@@ -3945,10 +3948,10 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3971,7 +3974,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B39" s="8">
         <v>46181.60903861111</v>
@@ -3983,16 +3986,16 @@
         <v>46199.57256810185</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I39" s="8">
         <v>46252</v>
@@ -4010,13 +4013,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -4026,7 +4029,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B40" s="5">
         <v>46181.609042951386</v>
@@ -4038,16 +4041,16 @@
         <v>46199.57232634259</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I40" s="5">
         <v>46254</v>
@@ -4065,13 +4068,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4081,7 +4084,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B41" s="8">
         <v>46181.609047164355</v>
@@ -4093,16 +4096,16 @@
         <v>46212.82441381944</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I41" s="8">
         <v>46252</v>
@@ -4120,10 +4123,10 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P41" s="9" t="s">
         <v>26</v>
@@ -4146,7 +4149,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B42" s="5">
         <v>46181.60905075232</v>
@@ -4158,16 +4161,16 @@
         <v>46204.67396857639</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I42" s="5">
         <v>46252</v>
@@ -4185,13 +4188,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4201,7 +4204,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B43" s="8">
         <v>46181.60905546296</v>
@@ -4213,16 +4216,16 @@
         <v>46204.67391837963</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I43" s="8">
         <v>46261</v>
@@ -4240,13 +4243,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -4256,7 +4259,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B44" s="5">
         <v>46181.60906018519</v>
@@ -4266,16 +4269,16 @@
         <v>46204.67384744213</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I44" s="5">
         <v>46290</v>
@@ -4293,10 +4296,10 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>26</v>
@@ -4309,7 +4312,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B45" s="8">
         <v>46181.609063310185</v>
@@ -4321,16 +4324,16 @@
         <v>46205.61290721065</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I45" s="8">
         <v>46252</v>
@@ -4348,10 +4351,10 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>26</v>
@@ -4374,7 +4377,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B46" s="5">
         <v>46181.60906703703</v>
@@ -4386,16 +4389,16 @@
         <v>46205.61283694445</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I46" s="5">
         <v>46252</v>
@@ -4413,13 +4416,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4429,7 +4432,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B47" s="8">
         <v>46181.60907681713</v>
@@ -4441,16 +4444,16 @@
         <v>46205.612879328706</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I47" s="8">
         <v>46254</v>
@@ -4468,13 +4471,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
@@ -4484,7 +4487,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B48" s="5">
         <v>46181.6090815625</v>
@@ -4496,7 +4499,7 @@
         <v>46210.525643402776</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>25</v>
@@ -4520,7 +4523,7 @@
         <v>26</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>26</v>
@@ -4537,7 +4540,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B49" s="8">
         <v>46181.60908480324</v>
@@ -4549,16 +4552,16 @@
         <v>46197.7158150926</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I49" s="8">
         <v>46174</v>
@@ -4576,13 +4579,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q49" s="8">
         <v>46174</v>
@@ -4590,8 +4593,8 @@
       <c r="R49" s="8">
         <v>46191</v>
       </c>
-      <c r="S49" s="11" t="s">
-        <v>125</v>
+      <c r="S49" s="12" t="s">
+        <v>126</v>
       </c>
       <c r="T49" s="9">
         <v>1</v>
@@ -4602,7 +4605,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B50" s="5">
         <v>46181.60908915509</v>
@@ -4614,16 +4617,16 @@
         <v>46190.70821390046</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I50" s="5">
         <v>46174</v>
@@ -4641,13 +4644,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -4657,7 +4660,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B51" s="8">
         <v>46181.60909384259</v>
@@ -4669,16 +4672,16 @@
         <v>46190.7082228125</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I51" s="8">
         <v>46174</v>
@@ -4696,13 +4699,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4712,7 +4715,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B52" s="5">
         <v>46181.61221741898</v>
@@ -4724,16 +4727,16 @@
         <v>46190.708227337964</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I52" s="5">
         <v>46174</v>
@@ -4751,13 +4754,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4767,7 +4770,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B53" s="8">
         <v>46181.612357199076</v>
@@ -4779,16 +4782,16 @@
         <v>46190.708233321755</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I53" s="8">
         <v>46174</v>
@@ -4806,13 +4809,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -4822,7 +4825,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B54" s="5">
         <v>46181.609098182875</v>
@@ -4834,16 +4837,16 @@
         <v>46197.71584820602</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I54" s="5">
         <v>46227</v>
@@ -4861,13 +4864,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q54" s="5">
         <v>46227</v>
@@ -4887,7 +4890,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B55" s="8">
         <v>46181.60910252314</v>
@@ -4899,16 +4902,16 @@
         <v>46191.54270819444</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I55" s="8">
         <v>46227</v>
@@ -4926,13 +4929,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q55" s="9"/>
       <c r="R55" s="9"/>
@@ -4942,7 +4945,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B56" s="5">
         <v>46181.609107951386</v>
@@ -4954,16 +4957,16 @@
         <v>46191.54271703704</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I56" s="5">
         <v>46227</v>
@@ -4981,13 +4984,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4997,7 +5000,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B57" s="8">
         <v>46181.61393570602</v>
@@ -5009,16 +5012,16 @@
         <v>46190.70842170139</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I57" s="8">
         <v>46227</v>
@@ -5036,13 +5039,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5052,7 +5055,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B58" s="5">
         <v>46181.61396929398</v>
@@ -5064,16 +5067,16 @@
         <v>46190.708426550926</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I58" s="5">
         <v>46227</v>
@@ -5091,13 +5094,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5107,7 +5110,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B59" s="8">
         <v>46181.60911329861</v>
@@ -5119,16 +5122,16 @@
         <v>46191.54539826389</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I59" s="8">
         <v>46247</v>
@@ -5146,13 +5149,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q59" s="8">
         <v>46247</v>
@@ -5172,7 +5175,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B60" s="5">
         <v>46181.60912350695</v>
@@ -5184,16 +5187,16 @@
         <v>46191.54536050926</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I60" s="6"/>
       <c r="J60" s="5">
@@ -5209,13 +5212,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5225,7 +5228,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B61" s="8">
         <v>46181.60912782408</v>
@@ -5237,16 +5240,16 @@
         <v>46191.54537386574</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I61" s="9"/>
       <c r="J61" s="8">
@@ -5262,13 +5265,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5278,7 +5281,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B62" s="5">
         <v>46181.614119606485</v>
@@ -5290,16 +5293,16 @@
         <v>46190.721725358795</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I62" s="6"/>
       <c r="J62" s="5">
@@ -5315,10 +5318,10 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>26</v>
@@ -5331,7 +5334,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B63" s="8">
         <v>46181.61419627315</v>
@@ -5343,16 +5346,16 @@
         <v>46190.7217299537</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I63" s="9"/>
       <c r="J63" s="8">
@@ -5368,10 +5371,10 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5384,7 +5387,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B64" s="5">
         <v>46181.60913207176</v>
@@ -5394,16 +5397,16 @@
         <v>46212.622826203704</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I64" s="5">
         <v>46322</v>
@@ -5421,10 +5424,10 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>26</v>
@@ -5441,13 +5444,13 @@
       <c r="T64" s="6">
         <v>0</v>
       </c>
-      <c r="U64" s="11" t="s">
-        <v>58</v>
+      <c r="U64" s="12" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B65" s="8">
         <v>46181.609135833336</v>
@@ -5457,16 +5460,16 @@
         <v>46182.63311847222</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I65" s="8">
         <v>46322</v>
@@ -5484,13 +5487,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5500,7 +5503,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B66" s="5">
         <v>46181.614311909725</v>
@@ -5510,16 +5513,16 @@
         <v>46182.63311923611</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I66" s="5">
         <v>46322</v>
@@ -5537,13 +5540,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5553,7 +5556,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B67" s="8">
         <v>46181.60918671296</v>
@@ -5565,7 +5568,7 @@
         <v>46216.64129429398</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>25</v>
@@ -5589,7 +5592,7 @@
         <v>26</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>26</v>
@@ -5606,7 +5609,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B68" s="5">
         <v>46181.609196087964</v>
@@ -5618,16 +5621,16 @@
         <v>46213.56938424769</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I68" s="5">
         <v>46252</v>
@@ -5645,13 +5648,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q68" s="5">
         <v>46252</v>
@@ -5671,7 +5674,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B69" s="8">
         <v>46181.609201921296</v>
@@ -5683,16 +5686,16 @@
         <v>46216.71548459491</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I69" s="8">
         <v>46254</v>
@@ -5710,13 +5713,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q69" s="8">
         <v>46254</v>
@@ -5736,7 +5739,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B70" s="5">
         <v>46181.60920746528</v>
@@ -5748,16 +5751,16 @@
         <v>46213.569400231485</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I70" s="5">
         <v>46252</v>
@@ -5775,13 +5778,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q70" s="5">
         <v>46252</v>
@@ -5801,7 +5804,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B71" s="8">
         <v>46181.609212870375</v>
@@ -5813,16 +5816,16 @@
         <v>46216.715484733795</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I71" s="8">
         <v>46254</v>
@@ -5840,13 +5843,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q71" s="8">
         <v>46254</v>
@@ -5866,7 +5869,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B72" s="5">
         <v>46181.60921715278</v>
@@ -5878,16 +5881,16 @@
         <v>46213.569419479165</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I72" s="5">
         <v>46252</v>
@@ -5905,13 +5908,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q72" s="5">
         <v>46252</v>
@@ -5931,7 +5934,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B73" s="8">
         <v>46181.60922180556</v>
@@ -5943,16 +5946,16 @@
         <v>46216.71548493055</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I73" s="8">
         <v>46254</v>
@@ -5970,13 +5973,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q73" s="8">
         <v>46254</v>
@@ -5996,7 +5999,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B74" s="5">
         <v>46181.60922590278</v>
@@ -6008,7 +6011,7 @@
         <v>46226.725049155095</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>25</v>
@@ -6032,7 +6035,7 @@
         <v>26</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>26</v>
@@ -6049,7 +6052,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B75" s="8">
         <v>46181.60922940972</v>
@@ -6058,19 +6061,19 @@
         <v>46225.80622738426</v>
       </c>
       <c r="D75" s="8">
-        <v>46225.86188380787</v>
+        <v>46231.56036584491</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I75" s="8">
         <v>46258</v>
@@ -6088,13 +6091,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q75" s="8">
         <v>46258</v>
@@ -6114,7 +6117,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B76" s="5">
         <v>46181.60923553241</v>
@@ -6126,16 +6129,16 @@
         <v>46225.8062046875</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I76" s="5">
         <v>46258</v>
@@ -6153,13 +6156,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6169,7 +6172,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B77" s="8">
         <v>46181.609241805556</v>
@@ -6181,16 +6184,16 @@
         <v>46225.806214282406</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I77" s="8">
         <v>46258</v>
@@ -6208,13 +6211,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
@@ -6224,7 +6227,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B78" s="5">
         <v>46181.609247002314</v>
@@ -6236,16 +6239,16 @@
         <v>46225.80634494213</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I78" s="5">
         <v>46267</v>
@@ -6263,13 +6266,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q78" s="5">
         <v>46267</v>
@@ -6289,7 +6292,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B79" s="8">
         <v>46181.60925648148</v>
@@ -6301,16 +6304,16 @@
         <v>46225.806309120366</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I79" s="8">
         <v>46267</v>
@@ -6328,13 +6331,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6344,7 +6347,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B80" s="5">
         <v>46181.609262199076</v>
@@ -6356,16 +6359,16 @@
         <v>46225.806319490744</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I80" s="5">
         <v>46267</v>
@@ -6383,13 +6386,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6399,7 +6402,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B81" s="8">
         <v>46181.60926783565</v>
@@ -6411,16 +6414,16 @@
         <v>46226.725539004634</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I81" s="8">
         <v>46289</v>
@@ -6438,13 +6441,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q81" s="8">
         <v>46289</v>
@@ -6458,13 +6461,13 @@
       <c r="T81" s="9">
         <v>1</v>
       </c>
-      <c r="U81" s="12" t="s">
-        <v>256</v>
+      <c r="U81" s="11" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B82" s="5">
         <v>46181.60927226851</v>
@@ -6476,16 +6479,16 @@
         <v>46226.72551587963</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I82" s="5">
         <v>46289</v>
@@ -6503,13 +6506,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6519,7 +6522,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B83" s="8">
         <v>46181.60927799769</v>
@@ -6531,16 +6534,16 @@
         <v>46226.72552325232</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I83" s="8">
         <v>46289</v>
@@ -6558,13 +6561,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6574,7 +6577,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B84" s="5">
         <v>46181.60928361111</v>
@@ -6584,7 +6587,7 @@
         <v>46213.56805377315</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>25</v>
@@ -6608,7 +6611,7 @@
         <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6617,13 +6620,13 @@
       <c r="R84" s="6"/>
       <c r="S84" s="6"/>
       <c r="T84" s="6"/>
-      <c r="U84" s="12" t="s">
-        <v>256</v>
+      <c r="U84" s="11" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B85" s="8">
         <v>46181.609286990744</v>
@@ -6635,16 +6638,16 @@
         <v>46213.56773226852</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I85" s="8">
         <v>46182</v>
@@ -6662,13 +6665,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q85" s="8">
         <v>46182</v>
@@ -6676,8 +6679,8 @@
       <c r="R85" s="8">
         <v>46183</v>
       </c>
-      <c r="S85" s="11" t="s">
-        <v>125</v>
+      <c r="S85" s="12" t="s">
+        <v>126</v>
       </c>
       <c r="T85" s="9">
         <v>1</v>
@@ -6688,7 +6691,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B86" s="5">
         <v>46181.609292974535</v>
@@ -6700,16 +6703,16 @@
         <v>46213.56774653935</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I86" s="5">
         <v>46290</v>
@@ -6727,13 +6730,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q86" s="5">
         <v>46290</v>
@@ -6753,7 +6756,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B87" s="8">
         <v>46181.60929881944</v>
@@ -6765,16 +6768,16 @@
         <v>46228.196411377314</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I87" s="8">
         <v>46226</v>
@@ -6792,13 +6795,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q87" s="8">
         <v>46226</v>
@@ -6806,8 +6809,8 @@
       <c r="R87" s="8">
         <v>46227</v>
       </c>
-      <c r="S87" s="11" t="s">
-        <v>125</v>
+      <c r="S87" s="12" t="s">
+        <v>126</v>
       </c>
       <c r="T87" s="9">
         <v>1</v>
@@ -6818,7 +6821,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B88" s="5">
         <v>46181.60930480324</v>
@@ -6828,16 +6831,16 @@
         <v>46212.623013958335</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I88" s="5">
         <v>46293</v>
@@ -6855,13 +6858,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q88" s="5">
         <v>46293</v>
@@ -6875,13 +6878,13 @@
       <c r="T88" s="6">
         <v>0</v>
       </c>
-      <c r="U88" s="12" t="s">
-        <v>256</v>
+      <c r="U88" s="11" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B89" s="8">
         <v>46181.60935271991</v>
@@ -6891,16 +6894,16 @@
         <v>46228.19641133102</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I89" s="8">
         <v>46226</v>
@@ -6918,10 +6921,10 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P89" s="9" t="s">
         <v>56</v>
@@ -6932,19 +6935,19 @@
       <c r="R89" s="8">
         <v>46227</v>
       </c>
-      <c r="S89" s="11" t="s">
-        <v>125</v>
+      <c r="S89" s="12" t="s">
+        <v>126</v>
       </c>
       <c r="T89" s="9">
         <v>0</v>
       </c>
-      <c r="U89" s="12" t="s">
-        <v>256</v>
+      <c r="U89" s="11" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B90" s="5">
         <v>46181.60936674768</v>
@@ -6954,7 +6957,7 @@
         <v>46213.50490068287</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>25</v>
@@ -6978,7 +6981,7 @@
         <v>26</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>26</v>
@@ -6991,7 +6994,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B91" s="8">
         <v>46181.609371666666</v>
@@ -7001,16 +7004,16 @@
         <v>46225.82172349537</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I91" s="8">
         <v>46290</v>
@@ -7028,13 +7031,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q91" s="8">
         <v>46290</v>
@@ -7048,13 +7051,13 @@
       <c r="T91" s="9">
         <v>0</v>
       </c>
-      <c r="U91" s="12" t="s">
-        <v>256</v>
+      <c r="U91" s="11" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B92" s="5">
         <v>46181.609378587964</v>
@@ -7064,16 +7067,16 @@
         <v>46226.725520844906</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I92" s="5">
         <v>46290</v>
@@ -7091,13 +7094,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7107,7 +7110,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B93" s="8">
         <v>46181.61514019676</v>
@@ -7117,16 +7120,16 @@
         <v>46226.725527256945</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I93" s="8">
         <v>46290</v>
@@ -7144,13 +7147,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7160,7 +7163,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B94" s="5">
         <v>46181.609386111115</v>
@@ -7172,16 +7175,16 @@
         <v>46223.56717594907</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I94" s="5">
         <v>46311</v>
@@ -7199,13 +7202,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q94" s="5">
         <v>46311</v>
@@ -7225,7 +7228,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B95" s="8">
         <v>46181.60939194444</v>
@@ -7237,16 +7240,16 @@
         <v>46223.566525462964</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I95" s="8">
         <v>46311</v>
@@ -7264,13 +7267,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7280,7 +7283,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B96" s="5">
         <v>46181.61518315972</v>
@@ -7292,16 +7295,16 @@
         <v>46223.56652129629</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I96" s="5">
         <v>46311</v>
@@ -7319,10 +7322,10 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>26</v>
@@ -7335,7 +7338,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B97" s="8">
         <v>46181.60939866898</v>
@@ -7347,16 +7350,16 @@
         <v>46225.821835625</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I97" s="8">
         <v>46315</v>
@@ -7374,13 +7377,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q97" s="8">
         <v>46315</v>
@@ -7394,13 +7397,13 @@
       <c r="T97" s="9">
         <v>1</v>
       </c>
-      <c r="U97" s="11" t="s">
-        <v>58</v>
+      <c r="U97" s="12" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B98" s="5">
         <v>46181.60940505787</v>
@@ -7412,16 +7415,16 @@
         <v>46223.56665253472</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I98" s="5">
         <v>46315</v>
@@ -7439,13 +7442,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7455,7 +7458,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B99" s="8">
         <v>46181.61523613426</v>
@@ -7467,16 +7470,16 @@
         <v>46223.56667947916</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I99" s="8">
         <v>46315</v>
@@ -7494,10 +7497,10 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="P99" s="9" t="s">
         <v>26</v>
@@ -7510,7 +7513,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B100" s="5">
         <v>46181.60941365741</v>
@@ -7520,16 +7523,16 @@
         <v>46223.56716021991</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I100" s="5">
         <v>46317</v>
@@ -7547,13 +7550,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q100" s="5">
         <v>46317</v>
@@ -7567,13 +7570,13 @@
       <c r="T100" s="6">
         <v>0</v>
       </c>
-      <c r="U100" s="11" t="s">
-        <v>58</v>
+      <c r="U100" s="12" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B101" s="8">
         <v>46181.60941929398</v>
@@ -7583,16 +7586,16 @@
         <v>46223.566807800926</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I101" s="8">
         <v>46317</v>
@@ -7610,13 +7613,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7626,7 +7629,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B102" s="5">
         <v>46181.61528053241</v>
@@ -7636,16 +7639,16 @@
         <v>46223.56680710649</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I102" s="5">
         <v>46317</v>
@@ -7663,10 +7666,10 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>26</v>
@@ -7679,7 +7682,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B103" s="8">
         <v>46181.60942706019</v>
@@ -7689,16 +7692,16 @@
         <v>46223.56715939815</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I103" s="8">
         <v>46321</v>
@@ -7716,13 +7719,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q103" s="8">
         <v>46321</v>
@@ -7736,13 +7739,13 @@
       <c r="T103" s="9">
         <v>0</v>
       </c>
-      <c r="U103" s="11" t="s">
-        <v>58</v>
+      <c r="U103" s="12" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B104" s="5">
         <v>46181.60943415509</v>
@@ -7752,16 +7755,16 @@
         <v>46223.566960972224</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I104" s="5">
         <v>46321</v>
@@ -7779,13 +7782,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7795,7 +7798,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B105" s="8">
         <v>46181.61532783565</v>
@@ -7805,16 +7808,16 @@
         <v>46223.56696034722</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H105" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I105" s="8">
         <v>46321</v>
@@ -7832,13 +7835,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -7848,7 +7851,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B106" s="5">
         <v>46181.60944410879</v>
@@ -7858,16 +7861,16 @@
         <v>46223.56715854167</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I106" s="5">
         <v>46323</v>
@@ -7885,13 +7888,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q106" s="5">
         <v>46323</v>
@@ -7905,13 +7908,13 @@
       <c r="T106" s="6">
         <v>0</v>
       </c>
-      <c r="U106" s="11" t="s">
-        <v>58</v>
+      <c r="U106" s="12" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B107" s="8">
         <v>46181.60944996528</v>
@@ -7921,16 +7924,16 @@
         <v>46223.56705920139</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H107" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I107" s="8">
         <v>46323</v>
@@ -7948,13 +7951,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -7964,7 +7967,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B108" s="5">
         <v>46181.61537143518</v>
@@ -7974,16 +7977,16 @@
         <v>46223.56705859954</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I108" s="5">
         <v>46323</v>
@@ -8001,10 +8004,10 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>26</v>
@@ -8017,7 +8020,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B109" s="8">
         <v>46181.60945642361</v>
@@ -8027,7 +8030,7 @@
         <v>46182.634494212965</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>25</v>
@@ -8051,7 +8054,7 @@
         <v>26</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P109" s="9" t="s">
         <v>26</v>
@@ -8064,7 +8067,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B110" s="5">
         <v>46181.60946096065</v>
@@ -8074,16 +8077,16 @@
         <v>46182.64186350694</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I110" s="5">
         <v>46324</v>
@@ -8101,13 +8104,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q110" s="5">
         <v>46324</v>
@@ -8121,13 +8124,13 @@
       <c r="T110" s="6">
         <v>0</v>
       </c>
-      <c r="U110" s="11" t="s">
-        <v>58</v>
+      <c r="U110" s="12" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B111" s="8">
         <v>46181.60946868056</v>
@@ -8137,16 +8140,16 @@
         <v>46182.641845254635</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I111" s="8">
         <v>46324</v>
@@ -8164,13 +8167,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q111" s="9"/>
       <c r="R111" s="9"/>
@@ -8180,7 +8183,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B112" s="5">
         <v>46181.609475034726</v>
@@ -8190,16 +8193,16 @@
         <v>46226.725528553245</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I112" s="5">
         <v>46324</v>
@@ -8217,13 +8220,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8233,7 +8236,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B113" s="8">
         <v>46181.60947921296</v>
@@ -8243,16 +8246,16 @@
         <v>46182.641837766205</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I113" s="8">
         <v>46324</v>
@@ -8270,13 +8273,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8286,7 +8289,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B114" s="5">
         <v>46181.61605960648</v>
@@ -8296,16 +8299,16 @@
         <v>46182.641834548616</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I114" s="5">
         <v>46324</v>
@@ -8323,13 +8326,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8339,7 +8342,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B115" s="8">
         <v>46181.61617203704</v>
@@ -8349,16 +8352,16 @@
         <v>46230.85274487268</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I115" s="8">
         <v>46324</v>
@@ -8376,13 +8379,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O115" s="9" t="s">
         <v>26</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q115" s="9"/>
       <c r="R115" s="9"/>
@@ -8392,7 +8395,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B116" s="5">
         <v>46181.61620771991</v>
@@ -8402,16 +8405,16 @@
         <v>46216.715609837964</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I116" s="5">
         <v>46324</v>
@@ -8429,13 +8432,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8445,7 +8448,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B117" s="8">
         <v>46181.616245833335</v>
@@ -8455,16 +8458,16 @@
         <v>46230.85292063658</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I117" s="8">
         <v>46324</v>
@@ -8482,13 +8485,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8498,7 +8501,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B118" s="5">
         <v>46181.60948424769</v>
@@ -8508,16 +8511,16 @@
         <v>46223.567324097225</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I118" s="5">
         <v>46325</v>
@@ -8535,13 +8538,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q118" s="5">
         <v>46325</v>
@@ -8555,13 +8558,13 @@
       <c r="T118" s="6">
         <v>0</v>
       </c>
-      <c r="U118" s="11" t="s">
-        <v>58</v>
+      <c r="U118" s="12" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B119" s="8">
         <v>46181.60948969907</v>
@@ -8571,16 +8574,16 @@
         <v>46223.56727827546</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H119" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I119" s="8">
         <v>46325</v>
@@ -8598,13 +8601,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8614,7 +8617,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B120" s="5">
         <v>46181.60949538194</v>
@@ -8624,16 +8627,16 @@
         <v>46223.567277685186</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I120" s="5">
         <v>46325</v>
@@ -8651,13 +8654,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8667,7 +8670,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B121" s="8">
         <v>46181.609560185185</v>
@@ -8677,16 +8680,16 @@
         <v>46223.56727706018</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H121" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I121" s="8">
         <v>46325</v>
@@ -8704,13 +8707,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8720,7 +8723,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B122" s="5">
         <v>46181.61659114584</v>
@@ -8730,16 +8733,16 @@
         <v>46223.56727646991</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I122" s="5">
         <v>46325</v>
@@ -8757,13 +8760,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8773,7 +8776,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B123" s="8">
         <v>46181.61662431713</v>
@@ -8783,16 +8786,16 @@
         <v>46223.56727590278</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H123" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I123" s="8">
         <v>46325</v>
@@ -8810,13 +8813,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q123" s="9"/>
       <c r="R123" s="9"/>
@@ -8826,7 +8829,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B124" s="5">
         <v>46181.61666238426</v>
@@ -8836,16 +8839,16 @@
         <v>46223.56727532407</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I124" s="5">
         <v>46325</v>
@@ -8863,13 +8866,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -8879,7 +8882,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B125" s="8">
         <v>46181.61670006944</v>
@@ -8889,16 +8892,16 @@
         <v>46223.56727472223</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H125" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I125" s="8">
         <v>46325</v>
@@ -8916,13 +8919,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -8932,7 +8935,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B126" s="5">
         <v>46181.60956560185</v>
@@ -8942,16 +8945,16 @@
         <v>46182.82952324074</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I126" s="5">
         <v>46328</v>
@@ -8969,13 +8972,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q126" s="5">
         <v>46328</v>
@@ -8989,13 +8992,13 @@
       <c r="T126" s="6">
         <v>0</v>
       </c>
-      <c r="U126" s="11" t="s">
-        <v>58</v>
+      <c r="U126" s="12" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B127" s="8">
         <v>46181.60957188657</v>
@@ -9005,16 +9008,16 @@
         <v>46182.82945300926</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H127" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I127" s="8">
         <v>46328</v>
@@ -9032,13 +9035,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -9048,7 +9051,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B128" s="5">
         <v>46181.609583576384</v>
@@ -9058,16 +9061,16 @@
         <v>46182.829453784725</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I128" s="5">
         <v>46328</v>
@@ -9085,13 +9088,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9101,7 +9104,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B129" s="8">
         <v>46181.60958841435</v>
@@ -9111,16 +9114,16 @@
         <v>46182.829454583334</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I129" s="8">
         <v>46328</v>
@@ -9138,13 +9141,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q129" s="9"/>
       <c r="R129" s="9"/>
@@ -9154,7 +9157,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B130" s="5">
         <v>46181.616839849536</v>
@@ -9164,16 +9167,16 @@
         <v>46182.829455706014</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I130" s="5">
         <v>46328</v>
@@ -9191,13 +9194,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9207,7 +9210,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B131" s="8">
         <v>46181.61689748843</v>
@@ -9217,16 +9220,16 @@
         <v>46182.8294564699</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I131" s="8">
         <v>46328</v>
@@ -9244,13 +9247,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
@@ -9260,7 +9263,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B132" s="5">
         <v>46181.616942569446</v>
@@ -9270,16 +9273,16 @@
         <v>46182.82945721065</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I132" s="5">
         <v>46328</v>
@@ -9297,13 +9300,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9313,7 +9316,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B133" s="8">
         <v>46181.6169815162</v>
@@ -9323,16 +9326,16 @@
         <v>46182.82945796296</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I133" s="8">
         <v>46328</v>
@@ -9350,13 +9353,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9366,7 +9369,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B134" s="5">
         <v>46181.609592673616</v>
@@ -9376,16 +9379,16 @@
         <v>46225.823538819444</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I134" s="5">
         <v>46329</v>
@@ -9403,13 +9406,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q134" s="5">
         <v>46329</v>
@@ -9423,13 +9426,13 @@
       <c r="T134" s="6">
         <v>0</v>
       </c>
-      <c r="U134" s="11" t="s">
-        <v>58</v>
+      <c r="U134" s="12" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B135" s="8">
         <v>46181.60960517361</v>
@@ -9439,16 +9442,16 @@
         <v>46182.8294527199</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I135" s="8">
         <v>46329</v>
@@ -9466,13 +9469,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q135" s="9"/>
       <c r="R135" s="9"/>
@@ -9482,7 +9485,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B136" s="5">
         <v>46181.609610011576</v>
@@ -9492,16 +9495,16 @@
         <v>46182.829451909725</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I136" s="5">
         <v>46329</v>
@@ -9519,10 +9522,10 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P136" s="6" t="s">
         <v>26</v>
@@ -9535,7 +9538,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B137" s="8">
         <v>46181.609613796296</v>
@@ -9545,16 +9548,16 @@
         <v>46182.829452025464</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I137" s="8">
         <v>46329</v>
@@ -9572,10 +9575,10 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P137" s="9" t="s">
         <v>26</v>
@@ -9588,7 +9591,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B138" s="5">
         <v>46181.61712142361</v>
@@ -9598,16 +9601,16 @@
         <v>46182.82945197917</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I138" s="5">
         <v>46329</v>
@@ -9625,10 +9628,10 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P138" s="6" t="s">
         <v>26</v>
@@ -9641,7 +9644,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B139" s="8">
         <v>46181.61716094907</v>
@@ -9651,16 +9654,16 @@
         <v>46182.82945207176</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I139" s="8">
         <v>46329</v>
@@ -9678,10 +9681,10 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P139" s="9" t="s">
         <v>26</v>
@@ -9694,7 +9697,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B140" s="5">
         <v>46181.61719633102</v>
@@ -9704,16 +9707,16 @@
         <v>46182.829452025464</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I140" s="5">
         <v>46329</v>
@@ -9731,10 +9734,10 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P140" s="6" t="s">
         <v>26</v>
@@ -9747,7 +9750,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B141" s="8">
         <v>46181.617235451384</v>
@@ -9757,16 +9760,16 @@
         <v>46182.829452418984</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I141" s="8">
         <v>46329</v>
@@ -9784,10 +9787,10 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P141" s="9" t="s">
         <v>26</v>
@@ -9800,7 +9803,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B142" s="5">
         <v>46181.60961741898</v>
@@ -9810,7 +9813,7 @@
         <v>46182.63449439815</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>25</v>
@@ -9834,7 +9837,7 @@
         <v>26</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P142" s="6" t="s">
         <v>26</v>
@@ -9847,7 +9850,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B143" s="8">
         <v>46181.60962174769</v>
@@ -9857,16 +9860,16 @@
         <v>46182.64244836806</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="I143" s="8">
         <v>46330</v>
@@ -9884,13 +9887,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q143" s="8">
         <v>46330</v>
@@ -9904,13 +9907,13 @@
       <c r="T143" s="9">
         <v>0</v>
       </c>
-      <c r="U143" s="11" t="s">
-        <v>58</v>
+      <c r="U143" s="12" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B144" s="5">
         <v>46181.60962780092</v>
@@ -9920,7 +9923,7 @@
         <v>46191.67892958333</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -9947,13 +9950,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q144" s="5">
         <v>46330</v>
@@ -9967,13 +9970,13 @@
       <c r="T144" s="6">
         <v>0</v>
       </c>
-      <c r="U144" s="11" t="s">
-        <v>58</v>
+      <c r="U144" s="12" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B145" s="8">
         <v>46181.60963489584</v>
@@ -9983,7 +9986,7 @@
         <v>46182.63449431713</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>25</v>
@@ -10007,7 +10010,7 @@
         <v>26</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="P145" s="9" t="s">
         <v>26</v>
@@ -10020,13 +10023,13 @@
       <c r="T145" s="9">
         <v>0</v>
       </c>
-      <c r="U145" s="11" t="s">
-        <v>58</v>
+      <c r="U145" s="12" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B146" s="5">
         <v>46181.609640208335</v>
@@ -10036,7 +10039,7 @@
         <v>46182.64254377315</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10063,13 +10066,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q146" s="5">
         <v>46330</v>
@@ -10083,13 +10086,13 @@
       <c r="T146" s="6">
         <v>0</v>
       </c>
-      <c r="U146" s="11" t="s">
-        <v>58</v>
+      <c r="U146" s="12" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B147" s="8">
         <v>46181.609646365745</v>
@@ -10099,7 +10102,7 @@
         <v>46182.64254079861</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
@@ -10126,13 +10129,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q147" s="8">
         <v>46339</v>
@@ -10146,8 +10149,8 @@
       <c r="T147" s="9">
         <v>0</v>
       </c>
-      <c r="U147" s="11" t="s">
-        <v>58</v>
+      <c r="U147" s="12" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -6061,7 +6061,7 @@
         <v>46225.80622738426</v>
       </c>
       <c r="D75" s="8">
-        <v>46231.56036584491</v>
+        <v>46231.65309723379</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>240</v>
@@ -8349,7 +8349,7 @@
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46230.85274487268</v>
+        <v>46231.862803634256</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>186</v>
@@ -8455,7 +8455,7 @@
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46230.85292063658</v>
+        <v>46231.86380424768</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>333</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -808,7 +808,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+    <t xml:space="preserve">OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
   </si>
   <si>
     <t>1215506819773770</t>
@@ -6061,7 +6061,7 @@
         <v>46225.80622738426</v>
       </c>
       <c r="D75" s="8">
-        <v>46231.65309723379</v>
+        <v>46232.83598508102</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>240</v>

--- a/data/50001559 - FERROVIAL.xlsx
+++ b/data/50001559 - FERROVIAL.xlsx
@@ -250,7 +250,7 @@
     <t>Media</t>
   </si>
   <si>
-    <t>Tarea sin iniciar</t>
+    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1215506781521467</t>
@@ -496,6 +496,9 @@
     <t xml:space="preserve">Materiales corte Laser ot 4347,Fabricacion Corte Laser ot 4342 -4344 </t>
   </si>
   <si>
+    <t>Tarea sin iniciar</t>
+  </si>
+  <si>
     <t>1215506819659775</t>
   </si>
   <si>
@@ -808,7 +811,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+    <t>OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT2 4307 ZVN 1-9-86/2 ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4</t>
   </si>
   <si>
     <t>1215506819773770</t>
@@ -848,9 +851,6 @@
   </si>
   <si>
     <t>OT 4347 Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1215506819777596</t>
@@ -1852,7 +1852,7 @@
         <v>46190.67646162037</v>
       </c>
       <c r="D4" s="5">
-        <v>46191.77859822917</v>
+        <v>46233.51851459491</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="8">
-        <v>46231.19592238426</v>
+        <v>46233.51812